--- a/Backup/eGP_Monthly_Main_202609.xlsx
+++ b/Backup/eGP_Monthly_Main_202609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาและแก้ไขปัญหาการใช้เครื่องคอมพิวเตอร์ลูกข่ายและอุปกรณ์ต่อพ่วง สำนักงาน ป.ป.ส. ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาและแก้ไขอุปกรณ์สนับสนุนห้องปฏิบัติการคอมพิวเตอร์ (Data Center) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2c0c619e-e66c-497c-b456-26d731ea5b96</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d4c700d2-d110-4ee6-944c-fbfe3c3ccda4</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาและแก้ไขอุปกรณ์สนับสนุนห้องปฏิบัติการคอมพิวเตอร์ (Data Center) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบประชุมทางไกลผ่านจอภาพ (Video Conference)  ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (จอภาพ, ระบบประชุมทางไกล)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d4c700d2-d110-4ee6-944c-fbfe3c3ccda4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7087adf8-2cc8-4674-a130-694da727ee83</t>
         </is>
       </c>
     </row>
@@ -1313,15 +1313,15 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+          <t>กรมพัฒนาฝีมือแรงงาน</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1611</v>
+        <v>1704</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบประชุมทางไกลผ่านจอภาพ (Video Conference)  ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1331,12 +1331,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>★ (จอภาพ, ระบบประชุมทางไกล)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7087adf8-2cc8-4674-a130-694da727ee83</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e684df7d-e4aa-429f-90e2-baf69d050535</t>
         </is>
       </c>
     </row>
@@ -1348,15 +1348,15 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>กรมพัฒนาฝีมือแรงงาน</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1704</v>
+        <v>2102</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องกระตุกไฟฟ้าหัวใจชนิดอัตโนมัติ พร้อมตู้ตั้งพื้นจอแสดงผล และระบบสัญญาณเตือน จำนวน 10 เครื่อง สำหรับ รพ.พระปิยมหาราช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (จอแสดงผล)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e684df7d-e4aa-429f-90e2-baf69d050535</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5fb07982-c16a-4dd2-9379-726a8d5a7710</t>
         </is>
       </c>
     </row>
@@ -1383,15 +1383,15 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมอนามัย</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2102</v>
+        <v>2109</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องกระตุกไฟฟ้าหัวใจชนิดอัตโนมัติ พร้อมตู้ตั้งพื้นจอแสดงผล และระบบสัญญาณเตือน จำนวน 10 เครื่อง สำหรับ รพ.พระปิยมหาราช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบประชุมทางไกลออนไลน์ (Video Conference) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1401,32 +1401,32 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>★ (จอแสดงผล)</t>
+          <t>★ (ระบบประชุมทางไกล)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5fb07982-c16a-4dd2-9379-726a8d5a7710</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e9299467-894b-4d9f-930b-0673992d5759</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>กรมอนามัย</t>
+          <t>สำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2109</v>
+        <v>502</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบประชุมทางไกลออนไลน์ (Video Conference) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์ลูกข่ายและระบบเครือข่ายคอมพิวเตอร์ พร้อมทั้งอุปกรณ์ต่อพ่วง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>★ (ระบบประชุมทางไกล)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e9299467-894b-4d9f-930b-0673992d5759</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5925e432-6a1c-4246-aab2-f2094aeabd5b</t>
         </is>
       </c>
     </row>
@@ -1453,15 +1453,15 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>กรมศุลกากร</t>
+          <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>305</v>
+        <v>804</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าโครงการจัดเช่าวงจรเครือข่ายสื่อสารเพื่อการเชื่อมโยงข้อมูลระหว่างศูนย์คอมพิวเตอร์ (DC-DR) กรมศุลกากร ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อวัสดุคอมพิวเตอร์ จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d69cee18-1259-45c6-a63e-c0d7537f5335</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=69b5d49d-35a2-49b6-9c69-a77a74df0e9d</t>
         </is>
       </c>
     </row>
@@ -1488,15 +1488,15 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>502</v>
+        <v>806</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์ลูกข่ายและระบบเครือข่ายคอมพิวเตอร์ พร้อมทั้งอุปกรณ์ต่อพ่วง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์งานบ้านงานครัว จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5925e432-6a1c-4246-aab2-f2094aeabd5b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4b934857-93a6-4ef0-9708-1c258599416f</t>
         </is>
       </c>
     </row>
@@ -1523,15 +1523,15 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
+          <t>กรมการขนส่งทางราง</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อวัสดุคอมพิวเตอร์ จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ต่อพ่วง พร้อมการติดตั้ง จำนวน ๔ รายการ ของกรมการขนส่งทางราง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=69b5d49d-35a2-49b6-9c69-a77a74df0e9d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f5fcf75f-2a16-470f-9a41-1d640b04b1a1</t>
         </is>
       </c>
     </row>
@@ -1558,15 +1558,15 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>สำนักงานนโยบายและแผนทรัพยากรธรรมชาติและสิ่งแวดล้อม</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>806</v>
+        <v>911</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์งานบ้านงานครัว จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างต่ออายุสมาชิกโปรแกรมและบำรุงรักษาซ่อมแซมแก้ไขคอมพิวเตอร์แม่ข่ายและอุปกรณ์เครือข่ายไร้สาย ปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4b934857-93a6-4ef0-9708-1c258599416f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3327ec9-d212-4e24-aafb-36bbf05f5a34</t>
         </is>
       </c>
     </row>
@@ -1593,15 +1593,15 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางราง</t>
+          <t>สำนักงานกองทุนน้ำมันเชื้อเพลิง</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>812</v>
+        <v>1207</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ต่อพ่วง พร้อมการติดตั้ง จำนวน ๔ รายการ ของกรมการขนส่งทางราง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าคอมพิวเตอร์และอุปกรณ์ที่เกี่ยวข้อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f5fcf75f-2a16-470f-9a41-1d640b04b1a1</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1fb72e55-1c99-4e44-b4b3-370e1c2e8711</t>
         </is>
       </c>
     </row>
@@ -1628,15 +1628,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>สำนักงานนโยบายและแผนทรัพยากรธรรมชาติและสิ่งแวดล้อม</t>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>911</v>
+        <v>1302</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างต่ออายุสมาชิกโปรแกรมและบำรุงรักษาซ่อมแซมแก้ไขคอมพิวเตอร์แม่ข่ายและอุปกรณ์เครือข่ายไร้สาย ปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าระบบประชุมทางไกล (Web Conference Video Streaming) ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
+          <t>★ (ระบบประชุมทางไกล)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3327ec9-d212-4e24-aafb-36bbf05f5a34</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3d156308-f0d2-4d07-bf4a-27913c2c22b7</t>
         </is>
       </c>
     </row>
@@ -1663,15 +1663,15 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>สำนักงานกองทุนน้ำมันเชื้อเพลิง</t>
+          <t>กรมที่ดิน</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1207</v>
+        <v>1505</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าคอมพิวเตอร์และอุปกรณ์ที่เกี่ยวข้อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อโต๊ะและเก้าอี้เพื่อใช้ในราชการของสำนักงานที่ดินจังหวัดพิษณุโลก และสาขาฯ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1681,12 +1681,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (โต๊ะ, เก้าอี้)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1fb72e55-1c99-4e44-b4b3-370e1c2e8711</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=341e9241-c067-4ffa-9e06-734f19c6b999</t>
         </is>
       </c>
     </row>
@@ -1698,15 +1698,15 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+          <t>กรมพัฒนาฝีมือแรงงาน</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1302</v>
+        <v>1704</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าระบบประชุมทางไกล (Web Conference Video Streaming) ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาครุภัณฑ์คอมพิวเตอร์และระบบเครือข่าย ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1716,12 +1716,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>★ (ระบบประชุมทางไกล)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3d156308-f0d2-4d07-bf4a-27913c2c22b7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=677d75a8-aa89-4b8b-a742-eca4be741031</t>
         </is>
       </c>
     </row>
@@ -1733,15 +1733,15 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>กรมที่ดิน</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1505</v>
+        <v>2102</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อโต๊ะและเก้าอี้เพื่อใช้ในราชการของสำนักงานที่ดินจังหวัดพิษณุโลก และสาขาฯ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๓ รายการ ของสำนักงานสาธารณสุขจังหวัดกาญจนบุรี เพื่อโรงพยาบาลชุมชน จำนวน ๑๐ แห่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>★ (โต๊ะ, เก้าอี้)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=341e9241-c067-4ffa-9e06-734f19c6b999</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0424125a-176e-423d-9959-61c0ef9229f3</t>
         </is>
       </c>
     </row>
@@ -1768,15 +1768,15 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>กรมพัฒนาฝีมือแรงงาน</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1704</v>
+        <v>2102</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาครุภัณฑ์คอมพิวเตอร์และระบบเครือข่าย ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 6 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง จำนวน 1 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ.2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=677d75a8-aa89-4b8b-a742-eca4be741031</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ee066bf2-4c21-4580-8391-e1257afc7b11</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๓ รายการ ของสำนักงานสาธารณสุขจังหวัดกาญจนบุรี เพื่อโรงพยาบาลชุมชน จำนวน ๑๐ แห่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อตู้เย็นเก็บเลือดขนาดไม่น้อยกว่า 20 คิว จำนวน 1 เครื่อง สำหรับ รพ.พระปิยมหาราช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ตู้เย็น)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0424125a-176e-423d-9959-61c0ef9229f3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=985c4332-e608-4dc3-883b-e90257b97ad3</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 6 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง จำนวน 1 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ.2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์การแพทย์เพื่อการบริการประชาชน จำนวน 13 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ee066bf2-4c21-4580-8391-e1257afc7b11</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=db849b83-870c-446d-a004-6e2462b1b3a4</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อตู้เย็นเก็บเลือดขนาดไม่น้อยกว่า 20 คิว จำนวน 1 เครื่อง สำหรับ รพ.พระปิยมหาราช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนในเลือดของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 5 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1891,32 +1891,32 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>★ (ตู้เย็น)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=985c4332-e608-4dc3-883b-e90257b97ad3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e2347540-427f-4618-ac0a-6d2933980a00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สำนักงานปลัดกระทรวงการคลัง</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2102</v>
+        <v>302</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์การแพทย์เพื่อการบริการประชาชน จำนวน 13 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อสิทธิ์การใช้งานซอฟต์แวร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1926,32 +1926,32 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=db849b83-870c-446d-a004-6e2462b1b3a4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1732e367-2c09-431f-abc1-7384c0a94e8e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมศุลกากร</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2102</v>
+        <v>305</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนในเลือดของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 5 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าโครงการจัดเช่าวงจรเครือข่ายสื่อสารเพื่อการเชื่อมโยงข้อมูลระหว่างศูนย์คอมพิวเตอร์ (DC-DR) กรมศุลกากร ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1961,12 +1961,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e2347540-427f-4618-ac0a-6d2933980a00</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a09e3df4-34c1-4388-a91a-31d0494ea9da</t>
         </is>
       </c>
     </row>
@@ -1978,17 +1978,15 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการคลัง</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>0302</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>402</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อสิทธิ์การใช้งานซอฟต์แวร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการทำความสะอาด ณ อาคารกระทรวงการต่างประเทศ ถนนศรีอยุธยา อาคารกรมการกงสุลรวมถึงกองบรรณสารและห้องสมุด (ฝ่ายบรรณสาร) และศูนย์ราชการเฉลิมพระเกียรติฯ อาคาร B ชั้น 7 - 8 รวม 3 แห่ง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1998,12 +1996,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>★ (ซอฟต์แวร์)</t>
+          <t>★ (สมุด)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1732e367-2c09-431f-abc1-7384c0a94e8e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=61256c96-a851-4486-ba34-aeb06311fa64</t>
         </is>
       </c>
     </row>
@@ -2015,17 +2013,15 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>กรมศุลกากร</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>0305</t>
-        </is>
+          <t>กรมชลประทาน</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>703</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าโครงการจัดเช่าวงจรเครือข่ายสื่อสารเพื่อการเชื่อมโยงข้อมูลระหว่างศูนย์คอมพิวเตอร์ (DC-DR) กรมศุลกากร ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องสูบน้ำชนิดหอยโข่ง เเบบ End Suction ขับด้วยมอเตอร์ไฟฟ้า พร้อมติดตั้งอุปกรณ์ เเละระบบควบคุมไฟฟ้า ตามรายละเอียดคุณลักษณะเฉพาะ (Specification) ของกรมชลประทาน และอื่นๆ รวม ๓ รายการ สำหรับงานสถานีสูบน้ำด้วยไฟฟ้าพร้อมระบบส่งน้ำฝายคลองพอถาก ตำบลหน้าเขา อำเภอเขาพนม จังหวัดกระบี่ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2035,12 +2031,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a09e3df4-34c1-4388-a91a-31d0494ea9da</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f690008d-6ff3-4f11-84a7-08da3de166d4</t>
         </is>
       </c>
     </row>
@@ -2052,17 +2048,15 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
+          <t>กรมการขนส่งทางบก</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>804</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการทำความสะอาด ณ อาคารกระทรวงการต่างประเทศ ถนนศรีอยุธยา อาคารกรมการกงสุลรวมถึงกองบรรณสารและห้องสมุด (ฝ่ายบรรณสาร) และศูนย์ราชการเฉลิมพระเกียรติฯ อาคาร B ชั้น 7 - 8 รวม 3 แห่ง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์ Server และอุปกรณ์ที่ติดตั้ง ณ อาคารระบบข้อมูลกลางและสำรองข้อมูล สำนักงานขนส่งจังหวัดนนทบุรี ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2072,12 +2066,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>★ (สมุด)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=61256c96-a851-4486-ba34-aeb06311fa64</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7dbc77ce-d778-424c-9618-b2cc1659f8ad</t>
         </is>
       </c>
     </row>
@@ -2089,17 +2083,15 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>กรมชลประทาน</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>0703</t>
-        </is>
+          <t>กรมการขนส่งทางบก</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>804</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องสูบน้ำชนิดหอยโข่ง เเบบ End Suction ขับด้วยมอเตอร์ไฟฟ้า พร้อมติดตั้งอุปกรณ์ เเละระบบควบคุมไฟฟ้า ตามรายละเอียดคุณลักษณะเฉพาะ (Specification) ของกรมชลประทาน และอื่นๆ รวม ๓ รายการ สำหรับงานสถานีสูบน้ำด้วยไฟฟ้าพร้อมระบบส่งน้ำฝายคลองพอถาก ตำบลหน้าเขา อำเภอเขาพนม จังหวัดกระบี่ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมระบบคอมพิวเตอร์แม่ข่ายเสมือน (Server Virtualization) สำหรับให้บริการหน่วยงานต่างๆ ของกรมการขนส่งทางบกที่ใช้ในการสนับสนุน การปฏิบัติงานด้านความปลอดภัย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2109,12 +2101,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f690008d-6ff3-4f11-84a7-08da3de166d4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=60f2364f-32ae-4a8c-8c92-9936327bd8f9</t>
         </is>
       </c>
     </row>
@@ -2126,17 +2118,15 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>0804</t>
-        </is>
+          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>904</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์ Server และอุปกรณ์ที่ติดตั้ง ณ อาคารระบบข้อมูลกลางและสำรองข้อมูล สำนักงานขนส่งจังหวัดนนทบุรี ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการเช่าใช้บริการอินเทอร์เน็ตและสายสัญญาณเครือข่ายพร้อมอุปกรณ์ กรมทรัพยากรทางทะเลและชายฝั่ง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2146,12 +2136,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (สายสัญญาณ)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7dbc77ce-d778-424c-9618-b2cc1659f8ad</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ab266c44-4e3d-4e4c-a44e-a5e06ffb7d51</t>
         </is>
       </c>
     </row>
@@ -2163,17 +2153,15 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>0804</t>
-        </is>
+          <t>กรมที่ดิน</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1505</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมระบบคอมพิวเตอร์แม่ข่ายเสมือน (Server Virtualization) สำหรับให้บริการหน่วยงานต่างๆ ของกรมการขนส่งทางบกที่ใช้ในการสนับสนุน การปฏิบัติงานด้านความปลอดภัย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์และระบบคอมพิวเตอร์แม่ข่าย ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ระยะเวลา ๑๒ เดือน  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2188,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=60f2364f-32ae-4a8c-8c92-9936327bd8f9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ba59f24a-325d-4e38-8d86-eadcece33632</t>
         </is>
       </c>
     </row>
@@ -2200,17 +2188,15 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>0904</t>
-        </is>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1611</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการเช่าใช้บริการอินเทอร์เน็ตและสายสัญญาณเครือข่ายพร้อมอุปกรณ์ กรมทรัพยากรทางทะเลและชายฝั่ง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการถ่ายเอกสารพร้อมเครื่องถ่ายเอกสาร กระดาษ วัสดุสิ้นเปลือง และพนักงานประจำเครื่องของสำนักงาน ป.ป.ส. ดินแดง สำนักงาน ปปส.ทุ่งสองห้อง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2220,12 +2206,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>★ (สายสัญญาณ)</t>
+          <t>★ (กระดาษ)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ab266c44-4e3d-4e4c-a44e-a5e06ffb7d51</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ef490410-ac68-4d7a-9e38-c4dbf7dd4191</t>
         </is>
       </c>
     </row>
@@ -2237,17 +2223,15 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>กรมที่ดิน</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1611</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์และระบบคอมพิวเตอร์แม่ข่าย ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ระยะเวลา ๑๒ เดือน  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาซอฟต์แวร์และอุปกรณ์ระบบรักษาความปลอดภัยระบบเครือข่ายศูนย์คอมพิวเตอร์สำรอง ( DR-Site Firewall) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2257,12 +2241,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ba59f24a-325d-4e38-8d86-eadcece33632</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a430ff3c-1d84-458b-8d71-d54f8c065644</t>
         </is>
       </c>
     </row>
@@ -2277,14 +2261,12 @@
           <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1611</t>
-        </is>
+      <c r="C53" t="n">
+        <v>1611</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการถ่ายเอกสารพร้อมเครื่องถ่ายเอกสาร กระดาษ วัสดุสิ้นเปลือง และพนักงานประจำเครื่องของสำนักงาน ป.ป.ส. ดินแดง สำนักงาน ปปส.ทุ่งสองห้อง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบป้องกันการบุกรุกเครือข่ายคอมพิวเตอร์ สำนักงาน ป.ป.ส. (Client Zone Firewall) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2294,12 +2276,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>★ (กระดาษ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ef490410-ac68-4d7a-9e38-c4dbf7dd4191</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bfcbc7fd-4a5c-46e3-b5eb-5b51397db1cb</t>
         </is>
       </c>
     </row>
@@ -2314,14 +2296,12 @@
           <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1611</t>
-        </is>
+      <c r="C54" t="n">
+        <v>1611</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาซอฟต์แวร์และอุปกรณ์ระบบรักษาความปลอดภัยระบบเครือข่ายศูนย์คอมพิวเตอร์สำรอง ( DR-Site Firewall) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์เครื่องคอมพิวเตอร์แม่ข่ายพร้อมระบบปฏิบัติการ (Server) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2331,12 +2311,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ซอฟต์แวร์)</t>
+          <t>★ (คอมพิวเตอร์, ระบบปฏิบัติการ)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a430ff3c-1d84-458b-8d71-d54f8c065644</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4a59a370-30a9-4f35-abcd-cec87b36ed1e</t>
         </is>
       </c>
     </row>
@@ -2351,14 +2331,12 @@
           <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1611</t>
-        </is>
+      <c r="C55" t="n">
+        <v>1611</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบป้องกันการบุกรุกเครือข่ายคอมพิวเตอร์ สำนักงาน ป.ป.ส. (Client Zone Firewall) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์และซอฟต์แวร์ป้องกันระบบเครือข่าย (Firewall/Virus/VPN) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2368,12 +2346,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bfcbc7fd-4a5c-46e3-b5eb-5b51397db1cb</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=71058768-3f32-47a5-b07d-d89703297e8b</t>
         </is>
       </c>
     </row>
@@ -2388,14 +2366,12 @@
           <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1611</t>
-        </is>
+      <c r="C56" t="n">
+        <v>1611</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์เครื่องคอมพิวเตอร์แม่ข่ายพร้อมระบบปฏิบัติการ (Server) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาและแก้ไขปัญหาการใช้เครื่องคอมพิวเตอร์ลูกข่ายและอุปกรณ์ต่อพ่วง สำนักงาน ป.ป.ส. ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2405,12 +2381,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ระบบปฏิบัติการ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4a59a370-30a9-4f35-abcd-cec87b36ed1e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=04f4a224-3c0a-4630-9981-263ded303a56</t>
         </is>
       </c>
     </row>
@@ -2422,17 +2398,15 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1611</t>
-        </is>
+          <t>กรมส่งเสริมการเรียนรู้</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2033</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์และซอฟต์แวร์ป้องกันระบบเครือข่าย (Firewall/Virus/VPN) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2442,12 +2416,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>★ (ซอฟต์แวร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=71058768-3f32-47a5-b07d-d89703297e8b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=114943ef-9465-4b1b-af6c-d1fbd3564e05</t>
         </is>
       </c>
     </row>
@@ -2459,17 +2433,15 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>1611</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2102</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาและแก้ไขปัญหาการใช้เครื่องคอมพิวเตอร์ลูกข่ายและอุปกรณ์ต่อพ่วง สำนักงาน ป.ป.ส. ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการเครื่องดมยาสลบชนิดมาตรฐาน  จำนวน  ๑  เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2479,12 +2451,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=04f4a224-3c0a-4630-9981-263ded303a56</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e1f11ae5-c3d5-4fdc-a76f-351add1653a8</t>
         </is>
       </c>
     </row>
@@ -2496,17 +2468,15 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเรียนรู้</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2102</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการกล้องส่องตรวจและผ่าตัดภายในช่องท้องชนิดวีดิทัศน์แบบคมชัดสูงชนิดภาพ ๒ มิติ จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2516,12 +2486,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=114943ef-9465-4b1b-af6c-d1fbd3564e05</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3ff66642-757c-4554-a147-37146918afe9</t>
         </is>
       </c>
     </row>
@@ -2536,14 +2506,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C60" t="n">
+        <v>2102</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการเครื่องดมยาสลบชนิดมาตรฐาน  จำนวน  ๑  เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์โครงการจัดซื้อครุภัณฑ์การแพทย์เพื่อการบริการประชาชน จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2558,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e1f11ae5-c3d5-4fdc-a76f-351add1653a8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=921cfd0c-6740-4e24-84ce-20ad0ebfb382</t>
         </is>
       </c>
     </row>
@@ -2573,14 +2541,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C61" t="n">
+        <v>2102</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการกล้องส่องตรวจและผ่าตัดภายในช่องท้องชนิดวีดิทัศน์แบบคมชัดสูงชนิดภาพ ๒ มิติ จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันเคลื่อนย้ายได้ ของโรงพยาบาลชุมชน 8 แห่ง จำนวน 11 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2595,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3ff66642-757c-4554-a147-37146918afe9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2ac905f2-26be-4df4-b481-22676581f31a</t>
         </is>
       </c>
     </row>
@@ -2607,17 +2573,15 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>2113</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์โครงการจัดซื้อครุภัณฑ์การแพทย์เพื่อการบริการประชาชน จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องฟอกอากาศ แขวงทุ่งสองห้อง เขตหลักสี่ กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2627,34 +2591,34 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องฟอกอากาศ)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=921cfd0c-6740-4e24-84ce-20ad0ebfb382</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a91dc5dd-5f0e-49d2-8b3f-d7da9560b550</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สำนักงานรับรองมาตรฐานและประเมินคุณภาพการศึกษา (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>0116</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันเคลื่อนย้ายได้ ของโรงพยาบาลชุมชน 8 แห่ง จำนวน 11 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบ AQA ก) ระบบสารสนเทศเพื่อการประเมินคุณภาพภายนอก (AQA) ข) ระบบและซอฟต์แวร์สำหรับการจัดการไฟล์วิดีโอ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2664,49 +2628,900 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2ac905f2-26be-4df4-b481-22676581f31a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=15b527de-47eb-447e-8bc6-1bc4e5204254</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>กรมพลศึกษา</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>0503</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาดูแล ปรับปรุง บำรุงรักษา และพัฒนาระบบเครือข่ายและอุปกรณ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ff914fa4-2fa4-4a9c-bb1e-eb038590a95a</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>0704</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์  เครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล พร้อมชุดโปรแกรมระบบปฏิบัติการ สำหรับเครื่องคอมพิวเตอร์และเครื่องคอมพิวเตอร์โน้ตบุ๊ก แบบสิทธิการใช้งานภายในสำนักงาน ประเภทติดตั้งมาจากโรงงาน (OEM) ที่มีลิขสิทธิ์ที่ถูกต้องตามกฎหมาย ชุดโปรแกรมจัดการสานักงาน แบบที่ 2 ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย และชุดโปรแกรมป้องกันไวรัส จำนวน 15 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ระบบปฏิบัติการ, โปรแกรมป้องกันไวรัส, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2b1675a5-f593-4cd6-a100-2c0f3ac9c6e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>กรมประมง</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>0705</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน ๑ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7899c0ad-4727-4814-a039-57ea77f4e508</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>กรมประมง</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>0705</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อชุดจอภาพ LED พร้อมงานติดตั้งสำหรับห้องประชุมอานนท์ กรมประมง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>★ (จอภาพ)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a26dbb80-72fc-430c-8431-ba0133b850fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>กรมประมง</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>0705</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าเเละวิทยุ เครื่องกำเนิดไฟฟ้า ขนาด 100 กิโลวัตต์ พร้อมตู้ควบคุม ตำบลหูล่อง อำเภอปากพนัง จังหวัดนครศรีธรรมราช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=18464524-52ce-42bf-96c8-511cdf002607</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>กรมการข้าว</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>0718</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ต่อพ่วงเพื่อเพิ่มประสิทธิภาพการปฏิบัติงานของกรมการข้าว แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=aaaf180c-62ba-4ca4-9a9c-0333baa76276</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>กรมการข้าว</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>0718</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อทดแทนครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ต่อพ่วงเพื่อเพิ่มประสิทธิภาพการปฏิบัติงานของกรมการข้าว แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=15086036-ab87-4a45-b29c-edd87f507d1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>กรมการขนส่งทางบก</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>0804</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์และอุปกรณ์ตามโครงการระบบเครือข่ายเพื่อเพิ่มประสิทธิภาพในการปฏิบัติงานของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=faa5336e-2946-42fd-b66e-9583a9f24e44</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=44d1ec7f-04ab-49d0-b112-502799195d6b</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างโครงการจัดจ้างบำรุงรักษาเครื่องคอมพิวเตอร์แม่ข่ายและอุปกรณ์สำหรับระบบสารสนเทศบริหารเครื่องจักรกลและการเงินการบัญชีเพื่อการบริหารจัดการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=909fce3b-2a20-4eb7-b619-b2e32da6e18d</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>0904</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาและเพิ่มประสิทธิภาพระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรทางทะเลและชายฝั่ง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a2cbdca0-293f-4c68-b81a-7197ca7e532f</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>กรมทรัพยากรธรณี</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>0905</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาซ่อมบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรธรณี ปีงบประมาณ พ.ศ. 2570 จำนวน 1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3cc3bb5f-0d9f-428a-b588-18b0b71b8b6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>0909</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อและติดตั้งเครื่องคอมพิวเตอร์แม่ข่ายพร้อมอุปกรณ์ประกอบสำหรับรองรับการให้บริการระบบสารบรรณอิเล็กทรอนิกส์ของกรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=028b6dd5-2160-4f89-924f-f6c47b4b4995</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างโครงการจัดอบรมเตรียมความพร้อมผู้แต่งตั้งเป็นพนักงานเจ้าหน้าที่ตามพระราชบัญญัติว่าด้วยการกระทำความผิดเกี่ยวกับคอมพิวเตอร์ฯ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8de232df-b5c2-427b-9a5d-d9f5ca3342c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์สนับสนุนศูนย์ข้อมูลและเครือข่ายคอมพิวเตอร์ (Data Center) ของกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5065022-193d-466c-819b-b1533c1e1696</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>สถาบันส่งเสริมศิลปหัตถกรรมไทย (องค์การมหาชน)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1311</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างดำเนินการบำรุงรักษาระบบและอุปกรณ์ภายในห้อง Data Center และการต่อลิขสิทธิ์โปรแกรมคอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8c2b0f9b-210b-4328-a727-0ebda03f9ebc</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>กรมบังคับคดี</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1605</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างตรวจสอบเครื่องคอมพิวเตอร์ให้พร้อมใช้งานและบริการประชาชน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=590bcfa8-9d1a-43f4-b6c0-1d332cdf98ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>กรมศิลปากร</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1804</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบริการดูแลบำรุงรักษาเครื่องปรับอากาศ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>★ (เครื่องปรับอากาศ)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=560aab6a-379c-4e73-a426-35b147f0955f</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมการเรียนรู้</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c503f74c-2af9-417c-8231-870e22f9f0c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดอัตโนมัติ พร้อมตู้ตั้งพื้นจอแสดงผล และระบบสัญญาณเตือน จำนวน 39 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาล ในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>★ (จอแสดงผล, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f7659e63-27b4-4348-9cb8-c0e5ed5164a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องอุ่นเลือดและส่วนประกอบของเลือดชนิดไม่สัมผัสน้ำสามารถอุ่นเลือดได้ พร้อมกันไม่น้อยกว่า 3 ถุง ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 4 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dc9795b5-9883-4a59-bee5-16ba72ecd5c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเตียงผู้ป่วยชนิดสามไกร์ราวปีกนก พร้อมเบาะเสาน้ำเกลือตู้ข้างเตียงและถาดคร่อมเตียง ของโรงพยาบาลส่งเสริมสุขภาพตำบล 25 แห่ง จำนวน 25 เตียง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=43094cdc-968c-43e9-b0e7-915d25aa8621</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2107</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63c3a055-9106-4358-9ed6-5bf60d1e158c</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
           <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>2113</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>ประกวดราคาซื้อเครื่องฟอกอากาศ แขวงทุ่งสองห้อง เขตหลักสี่ กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>★ (เครื่องฟอกอากาศ)</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a91dc5dd-5f0e-49d2-8b3f-d7da9560b550</t>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและวิเคราะห์ระบบเก็บข้อมูลจราจรคอมพิวเตอร์ขั้นสูง (CSOC) สำนักงานหลักประกันสุขภาพแห่งชาติ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=516788e1-5adb-46f1-b0bc-48d9b91e8cd8</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202609.xlsx
+++ b/Backup/eGP_Monthly_Main_202609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2398,15 +2398,15 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเรียนรู้</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2033</v>
+        <v>2102</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการเครื่องดมยาสลบชนิดมาตรฐาน  จำนวน  ๑  เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2416,12 +2416,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=114943ef-9465-4b1b-af6c-d1fbd3564e05</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e1f11ae5-c3d5-4fdc-a76f-351add1653a8</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการเครื่องดมยาสลบชนิดมาตรฐาน  จำนวน  ๑  เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการกล้องส่องตรวจและผ่าตัดภายในช่องท้องชนิดวีดิทัศน์แบบคมชัดสูงชนิดภาพ ๒ มิติ จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e1f11ae5-c3d5-4fdc-a76f-351add1653a8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3ff66642-757c-4554-a147-37146918afe9</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการกล้องส่องตรวจและผ่าตัดภายในช่องท้องชนิดวีดิทัศน์แบบคมชัดสูงชนิดภาพ ๒ มิติ จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์โครงการจัดซื้อครุภัณฑ์การแพทย์เพื่อการบริการประชาชน จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3ff66642-757c-4554-a147-37146918afe9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=921cfd0c-6740-4e24-84ce-20ad0ebfb382</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์โครงการจัดซื้อครุภัณฑ์การแพทย์เพื่อการบริการประชาชน จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันเคลื่อนย้ายได้ ของโรงพยาบาลชุมชน 8 แห่ง จำนวน 11 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=921cfd0c-6740-4e24-84ce-20ad0ebfb382</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2ac905f2-26be-4df4-b481-22676581f31a</t>
         </is>
       </c>
     </row>
@@ -2538,15 +2538,15 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2102</v>
+        <v>2113</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันเคลื่อนย้ายได้ ของโรงพยาบาลชุมชน 8 แห่ง จำนวน 11 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องฟอกอากาศ แขวงทุ่งสองห้อง เขตหลักสี่ กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2556,32 +2556,32 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องฟอกอากาศ)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2ac905f2-26be-4df4-b481-22676581f31a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a91dc5dd-5f0e-49d2-8b3f-d7da9560b550</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+          <t>สำนักงานรับรองมาตรฐานและประเมินคุณภาพการศึกษา (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2113</v>
+        <v>116</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องฟอกอากาศ แขวงทุ่งสองห้อง เขตหลักสี่ กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบ AQA ก) ระบบสารสนเทศเพื่อการประเมินคุณภาพภายนอก (AQA) ข) ระบบและซอฟต์แวร์สำหรับการจัดการไฟล์วิดีโอ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>★ (เครื่องฟอกอากาศ)</t>
+          <t>★ (ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a91dc5dd-5f0e-49d2-8b3f-d7da9560b550</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=15b527de-47eb-447e-8bc6-1bc4e5204254</t>
         </is>
       </c>
     </row>
@@ -2608,17 +2608,15 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>สำนักงานรับรองมาตรฐานและประเมินคุณภาพการศึกษา (องค์การมหาชน)</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>0116</t>
-        </is>
+          <t>กรมพลศึกษา</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>503</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบ AQA ก) ระบบสารสนเทศเพื่อการประเมินคุณภาพภายนอก (AQA) ข) ระบบและซอฟต์แวร์สำหรับการจัดการไฟล์วิดีโอ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาดูแล ปรับปรุง บำรุงรักษา และพัฒนาระบบเครือข่ายและอุปกรณ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2628,12 +2626,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>★ (ซอฟต์แวร์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=15b527de-47eb-447e-8bc6-1bc4e5204254</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ff914fa4-2fa4-4a9c-bb1e-eb038590a95a</t>
         </is>
       </c>
     </row>
@@ -2645,17 +2643,15 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>กรมพลศึกษา</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>0503</t>
-        </is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>704</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาดูแล ปรับปรุง บำรุงรักษา และพัฒนาระบบเครือข่ายและอุปกรณ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์  เครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล พร้อมชุดโปรแกรมระบบปฏิบัติการ สำหรับเครื่องคอมพิวเตอร์และเครื่องคอมพิวเตอร์โน้ตบุ๊ก แบบสิทธิการใช้งานภายในสำนักงาน ประเภทติดตั้งมาจากโรงงาน (OEM) ที่มีลิขสิทธิ์ที่ถูกต้องตามกฎหมาย ชุดโปรแกรมจัดการสานักงาน แบบที่ 2 ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย และชุดโปรแกรมป้องกันไวรัส จำนวน 15 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2665,12 +2661,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ระบบปฏิบัติการ, โปรแกรมป้องกันไวรัส, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ff914fa4-2fa4-4a9c-bb1e-eb038590a95a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2b1675a5-f593-4cd6-a100-2c0f3ac9c6e2</t>
         </is>
       </c>
     </row>
@@ -2682,17 +2678,15 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>0704</t>
-        </is>
+          <t>กรมประมง</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>705</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์  เครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล พร้อมชุดโปรแกรมระบบปฏิบัติการ สำหรับเครื่องคอมพิวเตอร์และเครื่องคอมพิวเตอร์โน้ตบุ๊ก แบบสิทธิการใช้งานภายในสำนักงาน ประเภทติดตั้งมาจากโรงงาน (OEM) ที่มีลิขสิทธิ์ที่ถูกต้องตามกฎหมาย ชุดโปรแกรมจัดการสานักงาน แบบที่ 2 ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย และชุดโปรแกรมป้องกันไวรัส จำนวน 15 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน ๑ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2702,12 +2696,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ระบบปฏิบัติการ, โปรแกรมป้องกันไวรัส, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2b1675a5-f593-4cd6-a100-2c0f3ac9c6e2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7899c0ad-4727-4814-a039-57ea77f4e508</t>
         </is>
       </c>
     </row>
@@ -2722,14 +2716,12 @@
           <t>กรมประมง</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>0705</t>
-        </is>
+      <c r="C66" t="n">
+        <v>705</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน ๑ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อชุดจอภาพ LED พร้อมงานติดตั้งสำหรับห้องประชุมอานนท์ กรมประมง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2739,12 +2731,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (จอภาพ)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7899c0ad-4727-4814-a039-57ea77f4e508</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a26dbb80-72fc-430c-8431-ba0133b850fc</t>
         </is>
       </c>
     </row>
@@ -2759,14 +2751,12 @@
           <t>กรมประมง</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>0705</t>
-        </is>
+      <c r="C67" t="n">
+        <v>705</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อชุดจอภาพ LED พร้อมงานติดตั้งสำหรับห้องประชุมอานนท์ กรมประมง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าเเละวิทยุ เครื่องกำเนิดไฟฟ้า ขนาด 100 กิโลวัตต์ พร้อมตู้ควบคุม ตำบลหูล่อง อำเภอปากพนัง จังหวัดนครศรีธรรมราช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2776,12 +2766,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>★ (จอภาพ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a26dbb80-72fc-430c-8431-ba0133b850fc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=18464524-52ce-42bf-96c8-511cdf002607</t>
         </is>
       </c>
     </row>
@@ -2793,17 +2783,15 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>กรมประมง</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>0705</t>
-        </is>
+          <t>กรมการข้าว</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>718</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าเเละวิทยุ เครื่องกำเนิดไฟฟ้า ขนาด 100 กิโลวัตต์ พร้อมตู้ควบคุม ตำบลหูล่อง อำเภอปากพนัง จังหวัดนครศรีธรรมราช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ต่อพ่วงเพื่อเพิ่มประสิทธิภาพการปฏิบัติงานของกรมการข้าว แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2813,12 +2801,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=18464524-52ce-42bf-96c8-511cdf002607</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=aaaf180c-62ba-4ca4-9a9c-0333baa76276</t>
         </is>
       </c>
     </row>
@@ -2833,14 +2821,12 @@
           <t>กรมการข้าว</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>0718</t>
-        </is>
+      <c r="C69" t="n">
+        <v>718</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ต่อพ่วงเพื่อเพิ่มประสิทธิภาพการปฏิบัติงานของกรมการข้าว แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อทดแทนครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ต่อพ่วงเพื่อเพิ่มประสิทธิภาพการปฏิบัติงานของกรมการข้าว แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2855,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=aaaf180c-62ba-4ca4-9a9c-0333baa76276</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=15086036-ab87-4a45-b29c-edd87f507d1b</t>
         </is>
       </c>
     </row>
@@ -2867,17 +2853,15 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>กรมการข้าว</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>0718</t>
-        </is>
+          <t>กรมการขนส่งทางบก</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>804</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อทดแทนครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ต่อพ่วงเพื่อเพิ่มประสิทธิภาพการปฏิบัติงานของกรมการข้าว แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์และอุปกรณ์ตามโครงการระบบเครือข่ายเพื่อเพิ่มประสิทธิภาพในการปฏิบัติงานของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2887,12 +2871,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=15086036-ab87-4a45-b29c-edd87f507d1b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=faa5336e-2946-42fd-b66e-9583a9f24e44</t>
         </is>
       </c>
     </row>
@@ -2904,17 +2888,15 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>0804</t>
-        </is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>806</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์และอุปกรณ์ตามโครงการระบบเครือข่ายเพื่อเพิ่มประสิทธิภาพในการปฏิบัติงานของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2924,12 +2906,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=faa5336e-2946-42fd-b66e-9583a9f24e44</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=44d1ec7f-04ab-49d0-b112-502799195d6b</t>
         </is>
       </c>
     </row>
@@ -2944,14 +2926,12 @@
           <t>กรมทางหลวง</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>0806</t>
-        </is>
+      <c r="C72" t="n">
+        <v>806</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการจัดจ้างบำรุงรักษาเครื่องคอมพิวเตอร์แม่ข่ายและอุปกรณ์สำหรับระบบสารสนเทศบริหารเครื่องจักรกลและการเงินการบัญชีเพื่อการบริหารจัดการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2961,12 +2941,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=44d1ec7f-04ab-49d0-b112-502799195d6b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=909fce3b-2a20-4eb7-b619-b2e32da6e18d</t>
         </is>
       </c>
     </row>
@@ -2978,17 +2958,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>0806</t>
-        </is>
+          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>904</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการจัดจ้างบำรุงรักษาเครื่องคอมพิวเตอร์แม่ข่ายและอุปกรณ์สำหรับระบบสารสนเทศบริหารเครื่องจักรกลและการเงินการบัญชีเพื่อการบริหารจัดการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาและเพิ่มประสิทธิภาพระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรทางทะเลและชายฝั่ง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3003,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=909fce3b-2a20-4eb7-b619-b2e32da6e18d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a2cbdca0-293f-4c68-b81a-7197ca7e532f</t>
         </is>
       </c>
     </row>
@@ -3015,17 +2993,15 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>0904</t>
-        </is>
+          <t>กรมทรัพยากรธรณี</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>905</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการบำรุงรักษาและเพิ่มประสิทธิภาพระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรทางทะเลและชายฝั่ง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาซ่อมบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรธรณี ปีงบประมาณ พ.ศ. 2570 จำนวน 1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3040,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a2cbdca0-293f-4c68-b81a-7197ca7e532f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3cc3bb5f-0d9f-428a-b588-18b0b71b8b6e</t>
         </is>
       </c>
     </row>
@@ -3052,17 +3028,15 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>กรมทรัพยากรธรณี</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>0905</t>
-        </is>
+          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>909</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาซ่อมบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรธรณี ปีงบประมาณ พ.ศ. 2570 จำนวน 1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อและติดตั้งเครื่องคอมพิวเตอร์แม่ข่ายพร้อมอุปกรณ์ประกอบสำหรับรองรับการให้บริการระบบสารบรรณอิเล็กทรอนิกส์ของกรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3077,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3cc3bb5f-0d9f-428a-b588-18b0b71b8b6e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=028b6dd5-2160-4f89-924f-f6c47b4b4995</t>
         </is>
       </c>
     </row>
@@ -3089,17 +3063,15 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>0909</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1102</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อและติดตั้งเครื่องคอมพิวเตอร์แม่ข่ายพร้อมอุปกรณ์ประกอบสำหรับรองรับการให้บริการระบบสารบรรณอิเล็กทรอนิกส์ของกรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการจัดอบรมเตรียมความพร้อมผู้แต่งตั้งเป็นพนักงานเจ้าหน้าที่ตามพระราชบัญญัติว่าด้วยการกระทำความผิดเกี่ยวกับคอมพิวเตอร์ฯ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3114,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=028b6dd5-2160-4f89-924f-f6c47b4b4995</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8de232df-b5c2-427b-9a5d-d9f5ca3342c3</t>
         </is>
       </c>
     </row>
@@ -3126,17 +3098,15 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>1102</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1302</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการจัดอบรมเตรียมความพร้อมผู้แต่งตั้งเป็นพนักงานเจ้าหน้าที่ตามพระราชบัญญัติว่าด้วยการกระทำความผิดเกี่ยวกับคอมพิวเตอร์ฯ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์สนับสนุนศูนย์ข้อมูลและเครือข่ายคอมพิวเตอร์ (Data Center) ของกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3151,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8de232df-b5c2-427b-9a5d-d9f5ca3342c3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5065022-193d-466c-819b-b1533c1e1696</t>
         </is>
       </c>
     </row>
@@ -3163,17 +3133,15 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>1302</t>
-        </is>
+          <t>สถาบันส่งเสริมศิลปหัตถกรรมไทย (องค์การมหาชน)</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1311</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์สนับสนุนศูนย์ข้อมูลและเครือข่ายคอมพิวเตอร์ (Data Center) ของกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างดำเนินการบำรุงรักษาระบบและอุปกรณ์ภายในห้อง Data Center และการต่อลิขสิทธิ์โปรแกรมคอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3188,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5065022-193d-466c-819b-b1533c1e1696</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8c2b0f9b-210b-4328-a727-0ebda03f9ebc</t>
         </is>
       </c>
     </row>
@@ -3200,17 +3168,15 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>สถาบันส่งเสริมศิลปหัตถกรรมไทย (องค์การมหาชน)</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>1311</t>
-        </is>
+          <t>กรมบังคับคดี</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1605</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างดำเนินการบำรุงรักษาระบบและอุปกรณ์ภายในห้อง Data Center และการต่อลิขสิทธิ์โปรแกรมคอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างตรวจสอบเครื่องคอมพิวเตอร์ให้พร้อมใช้งานและบริการประชาชน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3225,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8c2b0f9b-210b-4328-a727-0ebda03f9ebc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=590bcfa8-9d1a-43f4-b6c0-1d332cdf98ac</t>
         </is>
       </c>
     </row>
@@ -3237,17 +3203,15 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>กรมบังคับคดี</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>1605</t>
-        </is>
+          <t>กรมศิลปากร</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1804</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างตรวจสอบเครื่องคอมพิวเตอร์ให้พร้อมใช้งานและบริการประชาชน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการดูแลบำรุงรักษาเครื่องปรับอากาศ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3257,12 +3221,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=590bcfa8-9d1a-43f4-b6c0-1d332cdf98ac</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=560aab6a-379c-4e73-a426-35b147f0955f</t>
         </is>
       </c>
     </row>
@@ -3274,17 +3238,15 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>กรมศิลปากร</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>1804</t>
-        </is>
+          <t>กรมส่งเสริมการเรียนรู้</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2033</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการดูแลบำรุงรักษาเครื่องปรับอากาศ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3294,12 +3256,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=560aab6a-379c-4e73-a426-35b147f0955f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c503f74c-2af9-417c-8231-870e22f9f0c0</t>
         </is>
       </c>
     </row>
@@ -3311,17 +3273,15 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเรียนรู้</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>2102</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดอัตโนมัติ พร้อมตู้ตั้งพื้นจอแสดงผล และระบบสัญญาณเตือน จำนวน 39 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาล ในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3331,12 +3291,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (จอแสดงผล, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c503f74c-2af9-417c-8231-870e22f9f0c0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f7659e63-27b4-4348-9cb8-c0e5ed5164a0</t>
         </is>
       </c>
     </row>
@@ -3351,14 +3311,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C83" t="n">
+        <v>2102</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดอัตโนมัติ พร้อมตู้ตั้งพื้นจอแสดงผล และระบบสัญญาณเตือน จำนวน 39 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาล ในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องอุ่นเลือดและส่วนประกอบของเลือดชนิดไม่สัมผัสน้ำสามารถอุ่นเลือดได้ พร้อมกันไม่น้อยกว่า 3 ถุง ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 4 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3368,12 +3326,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>★ (จอแสดงผล, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f7659e63-27b4-4348-9cb8-c0e5ed5164a0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dc9795b5-9883-4a59-bee5-16ba72ecd5c6</t>
         </is>
       </c>
     </row>
@@ -3388,14 +3346,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C84" t="n">
+        <v>2102</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องอุ่นเลือดและส่วนประกอบของเลือดชนิดไม่สัมผัสน้ำสามารถอุ่นเลือดได้ พร้อมกันไม่น้อยกว่า 3 ถุง ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 4 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเตียงผู้ป่วยชนิดสามไกร์ราวปีกนก พร้อมเบาะเสาน้ำเกลือตู้ข้างเตียงและถาดคร่อมเตียง ของโรงพยาบาลส่งเสริมสุขภาพตำบล 25 แห่ง จำนวน 25 เตียง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3410,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dc9795b5-9883-4a59-bee5-16ba72ecd5c6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=43094cdc-968c-43e9-b0e7-915d25aa8621</t>
         </is>
       </c>
     </row>
@@ -3422,17 +3378,15 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>2107</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเตียงผู้ป่วยชนิดสามไกร์ราวปีกนก พร้อมเบาะเสาน้ำเกลือตู้ข้างเตียงและถาดคร่อมเตียง ของโรงพยาบาลส่งเสริมสุขภาพตำบล 25 แห่ง จำนวน 25 เตียง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3447,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=43094cdc-968c-43e9-b0e7-915d25aa8621</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63c3a055-9106-4358-9ed6-5bf60d1e158c</t>
         </is>
       </c>
     </row>
@@ -3459,17 +3413,15 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>กรมสนับสนุนบริการสุขภาพ</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>2107</t>
-        </is>
+          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>2113</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและวิเคราะห์ระบบเก็บข้อมูลจราจรคอมพิวเตอร์ขั้นสูง (CSOC) สำนักงานหลักประกันสุขภาพแห่งชาติ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3479,34 +3431,34 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63c3a055-9106-4358-9ed6-5bf60d1e158c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=516788e1-5adb-46f1-b0bc-48d9b91e8cd8</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>0204</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและวิเคราะห์ระบบเก็บข้อมูลจราจรคอมพิวเตอร์ขั้นสูง (CSOC) สำนักงานหลักประกันสุขภาพแห่งชาติ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ และอุปกรณ์ประกอบเครื่องคอมพิวเตอร์ เพื่อทดแทน และพัฒนาระบบเทคโนโลยีสารสนเทศหน่วยบัญชาการป้องกันภัยทางอากาศ (นปอ.) จำนวน ๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3521,7 +3473,377 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=516788e1-5adb-46f1-b0bc-48d9b91e8cd8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8603566b-8b32-470f-b070-76bf84fb86b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>กองทัพบก</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>0204</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างก่อสร้างงานติดตั้งเครื่องปรับอากาศ ประจำอาคารหอประชุม หมายเลข ๙๖/๒๓ ของ โรงพยาบาลอานันทมหิดล จังหวัดลพบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>★ (เครื่องปรับอากาศ)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=97d16ed9-2390-479b-8218-55472ad15ea3</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>กรมชลประทาน</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>0703</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องสูบน้ำแบบจุ่มใช้มอเตอร์ไฟฟ้า และอื่นๆรวม 3 รายการ สำหรับงานปรับปรุงอาคารบังคับน้ำคลองทิวา-ต้นนา โครงการส่งน้ำและบำรุงรักษาบางพลวง ตำบลพนมสารคาม อำเภอพนมสารคาม จังหวัดฉะเชิงเทรา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>★ (มอเตอร์)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=641eb398-88f6-4784-9733-866ddfdb5ea8</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>0704</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์เครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล  จำนวน 12 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cae8cfd5-0a33-48de-bb0d-dd1597263622</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>0704</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล)  ขนาด ๑ ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า ๒,๔๐๐ ซีซี  หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า ๑๑๐ กิโลวัตต์ ขับเคลื่อน 4 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน ๑ คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=23493925-5f1a-442c-a9ec-afccbc470e45</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>0704</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อเครื่องคอมพิวเตอร์ และเครื่องคอมพิวเตอร์โน้ตบุ๊ก จำนวน 2 รายการ ของสำนักงานตรวจบัญชีสหกรณ์ชลบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=07006c6c-edf5-4030-b6c9-1078334342be</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ประกวดราคาเช่าโครงการเช่าเครื่องพิมพ์ 4 สี เพื่อการพิมพ์เอกสารแจ้งผู้ขับขี่เพื่อการเปรียบเทียบปรับตามกฎหมาย ของ กองบังคับการตำรวจทางหลวง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>★ (เครื่องพิมพ์)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3fdfa461-5479-46d3-90bc-5b8725bde7b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงแรงงาน</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1702</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดหาครุภัณฑ์คอมพิวเตอร์เพื่อทดแทนและเพิ่มประสิทธิภาพให้หน่วยงานในสังกัดสำนักงานปลัดกระทรวงแรงงาน ปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=eea981aa-edb1-4fdf-8067-e5fb7c92e854</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามการทุจริตในภาครัฐ</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2517</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาเครื่องคอมพิวเตอร์แม่ข่าย และระบบความปลอดภัยทางไซเบอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=39110c90-d236-47eb-913a-cb6b3cab18ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>สำนักงานการตรวจเงินแผ่นดิน</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2606</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างจ้างเหมาบริการขนย้ายเครื่องแม่ข่าย และอุปกรณ์พร้อมติดตั้ง ณ ศูนย์ข้อมูลหลัก ของสำนักงานการตรวจเงินแผ่นดิน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>★ (เครื่องแม่ข่าย)</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a89ffef4-4bf7-41f2-83ef-2e02a1a4e80c</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงการอุดมศึกษา วิทยาศาสตร์ วิจัยและนวัตกรรม</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>23002</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างจ้างเหมาบริการบำรุงรักษาเครื่องปรับอากาศ แบบรวมอะไหล่ จำนวน 606 เครื่อง ภายในอาคารอุดมศึกษา 1 อาคารอุดมศึกษา 2 อาคารพระจอมเกล้า และอาคารอเนกประสงค์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>★ (เครื่องปรับอากาศ)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4ed51246-9d93-42ff-bb32-e9acb8e03644</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202609.xlsx
+++ b/Backup/eGP_Monthly_Main_202609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3451,10 +3451,8 @@
           <t>กองทัพบก</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>0204</t>
-        </is>
+      <c r="C87" t="n">
+        <v>204</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -3488,10 +3486,8 @@
           <t>กองทัพบก</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>0204</t>
-        </is>
+      <c r="C88" t="n">
+        <v>204</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -3525,10 +3521,8 @@
           <t>กรมชลประทาน</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>0703</t>
-        </is>
+      <c r="C89" t="n">
+        <v>703</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -3562,10 +3556,8 @@
           <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>0704</t>
-        </is>
+      <c r="C90" t="n">
+        <v>704</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -3599,10 +3591,8 @@
           <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>0704</t>
-        </is>
+      <c r="C91" t="n">
+        <v>704</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -3636,10 +3626,8 @@
           <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>0704</t>
-        </is>
+      <c r="C92" t="n">
+        <v>704</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -3673,10 +3661,8 @@
           <t>กรมทางหลวง</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>0806</t>
-        </is>
+      <c r="C93" t="n">
+        <v>806</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -3710,10 +3696,8 @@
           <t>สำนักงานปลัดกระทรวงแรงงาน</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>1702</t>
-        </is>
+      <c r="C94" t="n">
+        <v>1702</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -3747,10 +3731,8 @@
           <t>สำนักงานคณะกรรมการป้องกันและปราบปรามการทุจริตในภาครัฐ</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>2517</t>
-        </is>
+      <c r="C95" t="n">
+        <v>2517</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -3784,10 +3766,8 @@
           <t>สำนักงานการตรวจเงินแผ่นดิน</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>2606</t>
-        </is>
+      <c r="C96" t="n">
+        <v>2606</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -3821,10 +3801,8 @@
           <t>สำนักงานปลัดกระทรวงการอุดมศึกษา วิทยาศาสตร์ วิจัยและนวัตกรรม</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>23002</t>
-        </is>
+      <c r="C97" t="n">
+        <v>23002</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -3844,6 +3822,709 @@
       <c r="G97" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4ed51246-9d93-42ff-bb32-e9acb8e03644</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>สำนักงานบริหารและพัฒนาองค์ความรู้ (องค์การมหาชน)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>0125</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=22d2e215-7492-48e1-8b48-52ebf11afb3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>กองทัพบก</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>0204</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ พร้อมอุปกรณ์ จำนวน ๘๐ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ed207e86-fa08-4bf6-b096-f66e9ea91205</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>กองทัพบก</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>0204</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อสป.สาย ส. ตามโครงการจัดหาอุปกรณ์คอมพิวเตอร์ เพื่อสนับสนุนงานออกแบบสถาปัตยกรรม วิศวกรรมและงานประมาณราคา (ยย.ทบ.) จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a5d0fbe1-af34-494f-b408-da6f60a04c26</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>กรมธนารักษ์</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์อาคารเก็บพัสดุสำนักงานธนารักษ์พื้นที่ชลบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=606b64be-13e1-468a-84bd-c7c5b46221da</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาดูแล บำรุงรักษา และล้างทำความสะอาดระบบเครื่องปรับอากาศ ณ อาคารกระทรวงการต่างประเทศ ถนนศรีอยุธยา และศูนย์ราชการเฉลิมพระเกียรติฯ อาคาร B ชั้น 7 - 8 รวม 2 แห่ง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>★ (เครื่องปรับอากาศ)</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4c0225b9-4c8b-4bbd-80d4-d42eccd0092e</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>กรมกิจการเด็กและเยาวชน</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>0605</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาเครื่องคอมพิวเตอร์ อุปกรณ์ต่อพ่วง และระบบสารสนเทศ ของ ดย. ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cb192597-9852-49f1-81d0-f9bd008c7f6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>0704</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อครุภัณฑ์ยานพาหนะและขนส่งรถโดยสารขนาด 12 ที่นั่ง (ดีเซล) จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3d257d5-116f-4d11-9cba-b2af7ffd9693</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>กรมประมง</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>0705</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างการจัดจ้างบำรุงรักษาครุภัณฑ์คอมพิวเตอร์สำหรับการรักษาความปลอดภัยของระบบเครือข่ายและคอมพิวเตอร์ จำนวน 1 งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=29210ba8-e1c2-4d7e-80d4-6acfeb801f71</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>กรมประมง</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>0705</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างการจัดจ้างบำรุงรักษาอุปกรณ์กระจายสัญญาณ จำนวน ๑ งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b2bbd6f5-c7a5-4bc3-be9e-fc1ddf4ac0a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>สำนักงานมาตรฐานสินค้าเกษตรและอาหารแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>0714</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างโครงการจ้างเหมาดูแลและบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์และระบบคอมพิวเตอร์พร้อมอุปกรณ์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d133e360-c57e-4330-bff5-2f10cf027da9</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องคอมพิวเตอร์และอุปกรณ์ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=04549f6b-e678-4005-91df-2993ee4bdb83</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่ายของสำนักงานพาณิชย์จังหวัด 76 จังหวัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f1e51f04-f935-4983-8200-42b44f480fc9</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>สถาบันส่งเสริมศิลปหัตถกรรมไทย (องค์การมหาชน)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>1311</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบริการจัดหาพนักงานดูแลหอนิทรรศการและห้องสมุด ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>★ (สมุด)</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ff1d2fa-ba06-4da0-bc6c-023504d3c9d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>1808</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์อื่นๆ (เครื่องแต่งกายโขน-ละคร) จำนวน 7 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8e14fee9-d40a-4d5f-b4ec-b5dd1cbdcc29</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมการเรียนรู้</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=988b1f6a-eb89-4ed1-bbe5-4e82ba43054b</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการตู้เย็นเก็บเลือดขนาดไม่น้อยกว่า 20 คิว ของโรงพยาบาลในจังหวัดสุรินทร์ 6 แห่ง จำนวน 7 ตู้ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์, ตู้เย็น)</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dfce18c4-7835-4a43-8ba6-fb9a2b9ab472</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>กรมอนามัย</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2109</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่าย กรมอนามัย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0f1ebcb1-8a09-4209-922e-0e2e49160cba</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2113</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์แม่ข่าย (Outsource System) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1c3629ca-59d6-4b8a-839b-92b06d6a1c43</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2113</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์เครือข่าย (Outsource Network) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b44df475-19c0-4304-b42e-0c379f2f6a07</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202609.xlsx
+++ b/Backup/eGP_Monthly_Main_202609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3238,15 +3238,15 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเรียนรู้</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2033</v>
+        <v>2102</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดอัตโนมัติ พร้อมตู้ตั้งพื้นจอแสดงผล และระบบสัญญาณเตือน จำนวน 39 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาล ในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3256,12 +3256,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (จอแสดงผล, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c503f74c-2af9-417c-8231-870e22f9f0c0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f7659e63-27b4-4348-9cb8-c0e5ed5164a0</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดอัตโนมัติ พร้อมตู้ตั้งพื้นจอแสดงผล และระบบสัญญาณเตือน จำนวน 39 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาล ในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องอุ่นเลือดและส่วนประกอบของเลือดชนิดไม่สัมผัสน้ำสามารถอุ่นเลือดได้ พร้อมกันไม่น้อยกว่า 3 ถุง ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 4 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3291,12 +3291,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>★ (จอแสดงผล, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f7659e63-27b4-4348-9cb8-c0e5ed5164a0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dc9795b5-9883-4a59-bee5-16ba72ecd5c6</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องอุ่นเลือดและส่วนประกอบของเลือดชนิดไม่สัมผัสน้ำสามารถอุ่นเลือดได้ พร้อมกันไม่น้อยกว่า 3 ถุง ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 4 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเตียงผู้ป่วยชนิดสามไกร์ราวปีกนก พร้อมเบาะเสาน้ำเกลือตู้ข้างเตียงและถาดคร่อมเตียง ของโรงพยาบาลส่งเสริมสุขภาพตำบล 25 แห่ง จำนวน 25 เตียง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dc9795b5-9883-4a59-bee5-16ba72ecd5c6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=43094cdc-968c-43e9-b0e7-915d25aa8621</t>
         </is>
       </c>
     </row>
@@ -3343,15 +3343,15 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2102</v>
+        <v>2107</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเตียงผู้ป่วยชนิดสามไกร์ราวปีกนก พร้อมเบาะเสาน้ำเกลือตู้ข้างเตียงและถาดคร่อมเตียง ของโรงพยาบาลส่งเสริมสุขภาพตำบล 25 แห่ง จำนวน 25 เตียง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=43094cdc-968c-43e9-b0e7-915d25aa8621</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63c3a055-9106-4358-9ed6-5bf60d1e158c</t>
         </is>
       </c>
     </row>
@@ -3378,15 +3378,15 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>กรมสนับสนุนบริการสุขภาพ</t>
+          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2107</v>
+        <v>2113</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและวิเคราะห์ระบบเก็บข้อมูลจราจรคอมพิวเตอร์ขั้นสูง (CSOC) สำนักงานหลักประกันสุขภาพแห่งชาติ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3396,32 +3396,32 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63c3a055-9106-4358-9ed6-5bf60d1e158c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=516788e1-5adb-46f1-b0bc-48d9b91e8cd8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2113</v>
+        <v>204</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและวิเคราะห์ระบบเก็บข้อมูลจราจรคอมพิวเตอร์ขั้นสูง (CSOC) สำนักงานหลักประกันสุขภาพแห่งชาติ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ และอุปกรณ์ประกอบเครื่องคอมพิวเตอร์ เพื่อทดแทน และพัฒนาระบบเทคโนโลยีสารสนเทศหน่วยบัญชาการป้องกันภัยทางอากาศ (นปอ.) จำนวน ๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=516788e1-5adb-46f1-b0bc-48d9b91e8cd8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8603566b-8b32-470f-b070-76bf84fb86b4</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ และอุปกรณ์ประกอบเครื่องคอมพิวเตอร์ เพื่อทดแทน และพัฒนาระบบเทคโนโลยีสารสนเทศหน่วยบัญชาการป้องกันภัยทางอากาศ (นปอ.) จำนวน ๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างงานติดตั้งเครื่องปรับอากาศ ประจำอาคารหอประชุม หมายเลข ๙๖/๒๓ ของ โรงพยาบาลอานันทมหิดล จังหวัดลพบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8603566b-8b32-470f-b070-76bf84fb86b4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=97d16ed9-2390-479b-8218-55472ad15ea3</t>
         </is>
       </c>
     </row>
@@ -3483,15 +3483,15 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กรมชลประทาน</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>204</v>
+        <v>703</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างงานติดตั้งเครื่องปรับอากาศ ประจำอาคารหอประชุม หมายเลข ๙๖/๒๓ ของ โรงพยาบาลอานันทมหิดล จังหวัดลพบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องสูบน้ำแบบจุ่มใช้มอเตอร์ไฟฟ้า และอื่นๆรวม 3 รายการ สำหรับงานปรับปรุงอาคารบังคับน้ำคลองทิวา-ต้นนา โครงการส่งน้ำและบำรุงรักษาบางพลวง ตำบลพนมสารคาม อำเภอพนมสารคาม จังหวัดฉะเชิงเทรา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=97d16ed9-2390-479b-8218-55472ad15ea3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=641eb398-88f6-4784-9733-866ddfdb5ea8</t>
         </is>
       </c>
     </row>
@@ -3518,15 +3518,15 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>กรมชลประทาน</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องสูบน้ำแบบจุ่มใช้มอเตอร์ไฟฟ้า และอื่นๆรวม 3 รายการ สำหรับงานปรับปรุงอาคารบังคับน้ำคลองทิวา-ต้นนา โครงการส่งน้ำและบำรุงรักษาบางพลวง ตำบลพนมสารคาม อำเภอพนมสารคาม จังหวัดฉะเชิงเทรา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์เครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล  จำนวน 12 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=641eb398-88f6-4784-9733-866ddfdb5ea8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cae8cfd5-0a33-48de-bb0d-dd1597263622</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์เครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล  จำนวน 12 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล)  ขนาด ๑ ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า ๒,๔๐๐ ซีซี  หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า ๑๑๐ กิโลวัตต์ ขับเคลื่อน 4 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน ๑ คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3571,12 +3571,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cae8cfd5-0a33-48de-bb0d-dd1597263622</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=23493925-5f1a-442c-a9ec-afccbc470e45</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล)  ขนาด ๑ ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า ๒,๔๐๐ ซีซี  หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า ๑๑๐ กิโลวัตต์ ขับเคลื่อน 4 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน ๑ คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อเครื่องคอมพิวเตอร์ และเครื่องคอมพิวเตอร์โน้ตบุ๊ก จำนวน 2 รายการ ของสำนักงานตรวจบัญชีสหกรณ์ชลบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=23493925-5f1a-442c-a9ec-afccbc470e45</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=07006c6c-edf5-4030-b6c9-1078334342be</t>
         </is>
       </c>
     </row>
@@ -3623,15 +3623,15 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>704</v>
+        <v>806</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อเครื่องคอมพิวเตอร์ และเครื่องคอมพิวเตอร์โน้ตบุ๊ก จำนวน 2 รายการ ของสำนักงานตรวจบัญชีสหกรณ์ชลบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าโครงการเช่าเครื่องพิมพ์ 4 สี เพื่อการพิมพ์เอกสารแจ้งผู้ขับขี่เพื่อการเปรียบเทียบปรับตามกฎหมาย ของ กองบังคับการตำรวจทางหลวง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=07006c6c-edf5-4030-b6c9-1078334342be</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3fdfa461-5479-46d3-90bc-5b8725bde7b5</t>
         </is>
       </c>
     </row>
@@ -3658,15 +3658,15 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>สำนักงานปลัดกระทรวงแรงงาน</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>806</v>
+        <v>1702</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าโครงการเช่าเครื่องพิมพ์ 4 สี เพื่อการพิมพ์เอกสารแจ้งผู้ขับขี่เพื่อการเปรียบเทียบปรับตามกฎหมาย ของ กองบังคับการตำรวจทางหลวง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดหาครุภัณฑ์คอมพิวเตอร์เพื่อทดแทนและเพิ่มประสิทธิภาพให้หน่วยงานในสังกัดสำนักงานปลัดกระทรวงแรงงาน ปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>★ (เครื่องพิมพ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3fdfa461-5479-46d3-90bc-5b8725bde7b5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=eea981aa-edb1-4fdf-8067-e5fb7c92e854</t>
         </is>
       </c>
     </row>
@@ -3693,15 +3693,15 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงแรงงาน</t>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามการทุจริตในภาครัฐ</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1702</v>
+        <v>2517</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดหาครุภัณฑ์คอมพิวเตอร์เพื่อทดแทนและเพิ่มประสิทธิภาพให้หน่วยงานในสังกัดสำนักงานปลัดกระทรวงแรงงาน ปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาเครื่องคอมพิวเตอร์แม่ข่าย และระบบความปลอดภัยทางไซเบอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=eea981aa-edb1-4fdf-8067-e5fb7c92e854</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=39110c90-d236-47eb-913a-cb6b3cab18ba</t>
         </is>
       </c>
     </row>
@@ -3728,15 +3728,15 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามการทุจริตในภาครัฐ</t>
+          <t>สำนักงานการตรวจเงินแผ่นดิน</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2517</v>
+        <v>2606</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการบำรุงรักษาเครื่องคอมพิวเตอร์แม่ข่าย และระบบความปลอดภัยทางไซเบอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างเหมาบริการขนย้ายเครื่องแม่ข่าย และอุปกรณ์พร้อมติดตั้ง ณ ศูนย์ข้อมูลหลัก ของสำนักงานการตรวจเงินแผ่นดิน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องแม่ข่าย)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=39110c90-d236-47eb-913a-cb6b3cab18ba</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a89ffef4-4bf7-41f2-83ef-2e02a1a4e80c</t>
         </is>
       </c>
     </row>
@@ -3763,15 +3763,15 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>สำนักงานการตรวจเงินแผ่นดิน</t>
+          <t>สำนักงานปลัดกระทรวงการอุดมศึกษา วิทยาศาสตร์ วิจัยและนวัตกรรม</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2606</v>
+        <v>23002</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างเหมาบริการขนย้ายเครื่องแม่ข่าย และอุปกรณ์พร้อมติดตั้ง ณ ศูนย์ข้อมูลหลัก ของสำนักงานการตรวจเงินแผ่นดิน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างเหมาบริการบำรุงรักษาเครื่องปรับอากาศ แบบรวมอะไหล่ จำนวน 606 เครื่อง ภายในอาคารอุดมศึกษา 1 อาคารอุดมศึกษา 2 อาคารพระจอมเกล้า และอาคารอเนกประสงค์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3781,32 +3781,32 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>★ (เครื่องแม่ข่าย)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a89ffef4-4bf7-41f2-83ef-2e02a1a4e80c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4ed51246-9d93-42ff-bb32-e9acb8e03644</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการอุดมศึกษา วิทยาศาสตร์ วิจัยและนวัตกรรม</t>
+          <t>สำนักงานบริหารและพัฒนาองค์ความรู้ (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>23002</v>
+        <v>125</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างเหมาบริการบำรุงรักษาเครื่องปรับอากาศ แบบรวมอะไหล่ จำนวน 606 เครื่อง ภายในอาคารอุดมศึกษา 1 อาคารอุดมศึกษา 2 อาคารพระจอมเกล้า และอาคารอเนกประสงค์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4ed51246-9d93-42ff-bb32-e9acb8e03644</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=22d2e215-7492-48e1-8b48-52ebf11afb3d</t>
         </is>
       </c>
     </row>
@@ -3833,17 +3833,15 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>สำนักงานบริหารและพัฒนาองค์ความรู้ (องค์การมหาชน)</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>0125</t>
-        </is>
+          <t>กองทัพบก</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>204</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ พร้อมอุปกรณ์ จำนวน ๘๐ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3858,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=22d2e215-7492-48e1-8b48-52ebf11afb3d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ed207e86-fa08-4bf6-b096-f66e9ea91205</t>
         </is>
       </c>
     </row>
@@ -3873,14 +3871,12 @@
           <t>กองทัพบก</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>0204</t>
-        </is>
+      <c r="C99" t="n">
+        <v>204</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ พร้อมอุปกรณ์ จำนวน ๘๐ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อสป.สาย ส. ตามโครงการจัดหาอุปกรณ์คอมพิวเตอร์ เพื่อสนับสนุนงานออกแบบสถาปัตยกรรม วิศวกรรมและงานประมาณราคา (ยย.ทบ.) จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3895,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ed207e86-fa08-4bf6-b096-f66e9ea91205</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a5d0fbe1-af34-494f-b408-da6f60a04c26</t>
         </is>
       </c>
     </row>
@@ -3907,17 +3903,15 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>0204</t>
-        </is>
+          <t>กรมธนารักษ์</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>303</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อสป.สาย ส. ตามโครงการจัดหาอุปกรณ์คอมพิวเตอร์ เพื่อสนับสนุนงานออกแบบสถาปัตยกรรม วิศวกรรมและงานประมาณราคา (ยย.ทบ.) จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์อาคารเก็บพัสดุสำนักงานธนารักษ์พื้นที่ชลบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3927,12 +3921,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a5d0fbe1-af34-494f-b408-da6f60a04c26</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=606b64be-13e1-468a-84bd-c7c5b46221da</t>
         </is>
       </c>
     </row>
@@ -3944,17 +3938,15 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>กรมธนารักษ์</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>402</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์อาคารเก็บพัสดุสำนักงานธนารักษ์พื้นที่ชลบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาดูแล บำรุงรักษา และล้างทำความสะอาดระบบเครื่องปรับอากาศ ณ อาคารกระทรวงการต่างประเทศ ถนนศรีอยุธยา และศูนย์ราชการเฉลิมพระเกียรติฯ อาคาร B ชั้น 7 - 8 รวม 2 แห่ง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3964,12 +3956,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=606b64be-13e1-468a-84bd-c7c5b46221da</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4c0225b9-4c8b-4bbd-80d4-d42eccd0092e</t>
         </is>
       </c>
     </row>
@@ -3981,17 +3973,15 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
+          <t>กรมกิจการเด็กและเยาวชน</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>605</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาดูแล บำรุงรักษา และล้างทำความสะอาดระบบเครื่องปรับอากาศ ณ อาคารกระทรวงการต่างประเทศ ถนนศรีอยุธยา และศูนย์ราชการเฉลิมพระเกียรติฯ อาคาร B ชั้น 7 - 8 รวม 2 แห่ง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาเครื่องคอมพิวเตอร์ อุปกรณ์ต่อพ่วง และระบบสารสนเทศ ของ ดย. ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4001,12 +3991,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4c0225b9-4c8b-4bbd-80d4-d42eccd0092e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cb192597-9852-49f1-81d0-f9bd008c7f6d</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4008,15 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>กรมกิจการเด็กและเยาวชน</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>0605</t>
-        </is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>704</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาเครื่องคอมพิวเตอร์ อุปกรณ์ต่อพ่วง และระบบสารสนเทศ ของ ดย. ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อครุภัณฑ์ยานพาหนะและขนส่งรถโดยสารขนาด 12 ที่นั่ง (ดีเซล) จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4038,12 +4026,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cb192597-9852-49f1-81d0-f9bd008c7f6d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3d257d5-116f-4d11-9cba-b2af7ffd9693</t>
         </is>
       </c>
     </row>
@@ -4055,17 +4043,15 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>0704</t>
-        </is>
+          <t>กรมประมง</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>705</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อครุภัณฑ์ยานพาหนะและขนส่งรถโดยสารขนาด 12 ที่นั่ง (ดีเซล) จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างการจัดจ้างบำรุงรักษาครุภัณฑ์คอมพิวเตอร์สำหรับการรักษาความปลอดภัยของระบบเครือข่ายและคอมพิวเตอร์ จำนวน 1 งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4075,12 +4061,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3d257d5-116f-4d11-9cba-b2af7ffd9693</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=29210ba8-e1c2-4d7e-80d4-6acfeb801f71</t>
         </is>
       </c>
     </row>
@@ -4095,14 +4081,12 @@
           <t>กรมประมง</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>0705</t>
-        </is>
+      <c r="C105" t="n">
+        <v>705</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างการจัดจ้างบำรุงรักษาครุภัณฑ์คอมพิวเตอร์สำหรับการรักษาความปลอดภัยของระบบเครือข่ายและคอมพิวเตอร์ จำนวน 1 งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างการจัดจ้างบำรุงรักษาอุปกรณ์กระจายสัญญาณ จำนวน ๑ งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4112,12 +4096,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=29210ba8-e1c2-4d7e-80d4-6acfeb801f71</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b2bbd6f5-c7a5-4bc3-be9e-fc1ddf4ac0a8</t>
         </is>
       </c>
     </row>
@@ -4129,17 +4113,15 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>กรมประมง</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>0705</t>
-        </is>
+          <t>สำนักงานมาตรฐานสินค้าเกษตรและอาหารแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>714</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างการจัดจ้างบำรุงรักษาอุปกรณ์กระจายสัญญาณ จำนวน ๑ งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการจ้างเหมาดูแลและบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์และระบบคอมพิวเตอร์พร้อมอุปกรณ์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4149,12 +4131,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b2bbd6f5-c7a5-4bc3-be9e-fc1ddf4ac0a8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d133e360-c57e-4330-bff5-2f10cf027da9</t>
         </is>
       </c>
     </row>
@@ -4166,17 +4148,15 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>สำนักงานมาตรฐานสินค้าเกษตรและอาหารแห่งชาติ</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>0714</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>1302</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการจ้างเหมาดูแลและบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์และระบบคอมพิวเตอร์พร้อมอุปกรณ์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องคอมพิวเตอร์และอุปกรณ์ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4191,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d133e360-c57e-4330-bff5-2f10cf027da9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=04549f6b-e678-4005-91df-2993ee4bdb83</t>
         </is>
       </c>
     </row>
@@ -4206,14 +4186,12 @@
           <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>1302</t>
-        </is>
+      <c r="C108" t="n">
+        <v>1302</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องคอมพิวเตอร์และอุปกรณ์ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่ายของสำนักงานพาณิชย์จังหวัด 76 จังหวัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4228,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=04549f6b-e678-4005-91df-2993ee4bdb83</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f1e51f04-f935-4983-8200-42b44f480fc9</t>
         </is>
       </c>
     </row>
@@ -4240,17 +4218,15 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>1302</t>
-        </is>
+          <t>สถาบันส่งเสริมศิลปหัตถกรรมไทย (องค์การมหาชน)</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>1311</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่ายของสำนักงานพาณิชย์จังหวัด 76 จังหวัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการจัดหาพนักงานดูแลหอนิทรรศการและห้องสมุด ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4260,12 +4236,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (สมุด)</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f1e51f04-f935-4983-8200-42b44f480fc9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ff1d2fa-ba06-4da0-bc6c-023504d3c9d6</t>
         </is>
       </c>
     </row>
@@ -4277,17 +4253,15 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>สถาบันส่งเสริมศิลปหัตถกรรมไทย (องค์การมหาชน)</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>1311</t>
-        </is>
+          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>1808</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการจัดหาพนักงานดูแลหอนิทรรศการและห้องสมุด ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์อื่นๆ (เครื่องแต่งกายโขน-ละคร) จำนวน 7 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4297,12 +4271,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>★ (สมุด)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ff1d2fa-ba06-4da0-bc6c-023504d3c9d6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8e14fee9-d40a-4d5f-b4ec-b5dd1cbdcc29</t>
         </is>
       </c>
     </row>
@@ -4314,17 +4288,15 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>1808</t>
-        </is>
+          <t>กรมส่งเสริมการเรียนรู้</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>2033</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์อื่นๆ (เครื่องแต่งกายโขน-ละคร) จำนวน 7 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4334,12 +4306,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8e14fee9-d40a-4d5f-b4ec-b5dd1cbdcc29</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=988b1f6a-eb89-4ed1-bbe5-4e82ba43054b</t>
         </is>
       </c>
     </row>
@@ -4351,17 +4323,15 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเรียนรู้</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>2102</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการตู้เย็นเก็บเลือดขนาดไม่น้อยกว่า 20 คิว ของโรงพยาบาลในจังหวัดสุรินทร์ 6 แห่ง จำนวน 7 ตู้ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4371,12 +4341,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์, ตู้เย็น)</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=988b1f6a-eb89-4ed1-bbe5-4e82ba43054b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dfce18c4-7835-4a43-8ba6-fb9a2b9ab472</t>
         </is>
       </c>
     </row>
@@ -4388,17 +4358,15 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+          <t>กรมอนามัย</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>2109</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการตู้เย็นเก็บเลือดขนาดไม่น้อยกว่า 20 คิว ของโรงพยาบาลในจังหวัดสุรินทร์ 6 แห่ง จำนวน 7 ตู้ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่าย กรมอนามัย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4408,12 +4376,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์, ตู้เย็น)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dfce18c4-7835-4a43-8ba6-fb9a2b9ab472</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0f1ebcb1-8a09-4209-922e-0e2e49160cba</t>
         </is>
       </c>
     </row>
@@ -4425,17 +4393,15 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>กรมอนามัย</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>2109</t>
-        </is>
+          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>2113</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่าย กรมอนามัย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์แม่ข่าย (Outsource System) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4450,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0f1ebcb1-8a09-4209-922e-0e2e49160cba</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1c3629ca-59d6-4b8a-839b-92b06d6a1c43</t>
         </is>
       </c>
     </row>
@@ -4465,14 +4431,12 @@
           <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>2113</t>
-        </is>
+      <c r="C115" t="n">
+        <v>2113</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์แม่ข่าย (Outsource System) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์เครือข่าย (Outsource Network) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4487,29 +4451,29 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1c3629ca-59d6-4b8a-839b-92b06d6a1c43</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b44df475-19c0-4304-b42e-0c379f2f6a07</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+          <t>กองทัพอากาศ</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>0206</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์เครือข่าย (Outsource Network) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโต๊ะและเก้าอี้ประชุม จำนวน ๒ รายการ (แจ้งที่ ๘๙๖/๖๙) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4519,12 +4483,604 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
+          <t>★ (โต๊ะ, เก้าอี้)</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c197cbba-6119-4a85-8655-64df092381b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>กรมศุลกากร</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>0305</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องปรับอากาศ แบบฝังฝ้าสี่ทิศทาง (ระบบ Inverter) ขนาด 48,000 บีทียู ด่านศุลกากรปาดังเบซาร์ ตำบลปาดังเบซาร์ อำเภอสะเดา จังหวัดสงขลา 12 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>★ (เครื่องปรับอากาศ)</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7ffdc802-88d9-422f-a01b-27711177cb61</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>กรมสรรพากร</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>0307</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบ ไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 2,400 ซีซี  หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ จำนวน 5 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e642705c-f34c-41db-ad86-705717edf0ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>0704</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5b0cc17-68bd-4696-805e-f78e075178e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>0704</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุด ไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=106210e4-0233-403f-957c-c894b083d53b</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมการเกษตร</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>0711</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดชื้อครุภัณฑ์ยานพาหนะและขนส่ง ประจำปีงบประมาณ พ.ศ 2570 โดยวิธีประกวดอิเล็กทรอนิกส์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ec4d9c1c-1aa5-4b14-b3ea-60845e7335fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>0712</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาบรรทุกขนาด 1 ตัน หลังคาไฟเบอร์กลาส หรือเหล็กหรือพลาสติกวิศวกรรม สำนักงานสหกรณ์จังหวัดศรีสะเกษ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=51b057ec-ffcf-432e-bf86-fe4029225a82</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>1202</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>ประกวดราคาเช่ารถส่วนภูมิภาค รถยนต์ไฟฟ้า ประเภทแบตเตอรี่ (BEV) ขนาดความจุของแบตเตอรี่มากกว่า 50 กิโลวัตต์ชั่วโมง (kWh) และกำลังมอเตอร์ไฟฟ้าสูงสุด ไม่เกิน 150 กิโลวัตต์ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>★ (มอเตอร์)</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=490958cc-932a-45a1-8497-c33d7a13f8c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>กรมพัฒนาธุรกิจการค้า</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>1308</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องคอมพิวเตอร์ลูกข่ายและอุปกรณ์ต่อพ่วง ปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
           <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b44df475-19c0-4304-b42e-0c379f2f6a07</t>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=be5cf0cb-614f-4d37-aac0-190b90321cb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>กรมโยธาธิการและผังเมือง</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>1507</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างก่อสร้างโครงการจัดหาสิ่งก่อสร้างและครุภัณฑ์ประกอบ อาคารสำนักงานแห่งใหม่ของสำนักงบประมาณ แขวงพญาไท เขตพญาไท กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8b31f2b3-f6fd-4e5c-979f-8575feda4bbf</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>กรมการศาสนา</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>1803</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อวัสดุสำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>★ (วัสดุสำนักงาน)</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=07f7d716-619d-4e73-9518-7f683a4a05ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการชุดกระเป๋าปฐมพยาบาลสนามประจำตัวเจ้าหน้าที่ (IFAK) ของโรงพยาบาลชุมชน 11 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบล 40 แห่ง จำนวน 117 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=197d72c1-0e0f-4f3d-a377-6f7e052fd668</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a903de26-6f92-4b12-bcdc-87924b3b825b</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อสิทธิ์ใช้งานซอฟต์แวร์จัดการความเสี่ยงเกี่ยวกับระบบสารสนเทศ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>★ (ซอฟต์แวร์)</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f182625c-e015-489e-84e0-ac3c9c8dc788</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ กล้องถ่ายภาพจอประสาทตาดิจิตอล (Digital Fundus Camera) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=810bd451-770f-4032-86a0-1216954db79a</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการอาหารและยา</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2110</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=69d9687c-b7f1-405c-843e-92b98ad29261</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>สถาบันพระบรมราชชนก</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2117</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อติดตั้งระบบกล้องวงจรปิด ของวิทยาลัยพยาบาลบรมราชชนนี นครศรีธรรมราช จำนวน 1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>★ (กล้องวงจรปิด)</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afa9b388-be98-4ed1-8fa9-0c791e5acf34</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202609.xlsx
+++ b/Backup/eGP_Monthly_Main_202609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G132"/>
+  <dimension ref="A1:G153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4466,10 +4466,8 @@
           <t>กองทัพอากาศ</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>0206</t>
-        </is>
+      <c r="C116" t="n">
+        <v>206</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -4503,10 +4501,8 @@
           <t>กรมศุลกากร</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>0305</t>
-        </is>
+      <c r="C117" t="n">
+        <v>305</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -4540,10 +4536,8 @@
           <t>กรมสรรพากร</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>0307</t>
-        </is>
+      <c r="C118" t="n">
+        <v>307</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -4577,10 +4571,8 @@
           <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>0704</t>
-        </is>
+      <c r="C119" t="n">
+        <v>704</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -4614,10 +4606,8 @@
           <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>0704</t>
-        </is>
+      <c r="C120" t="n">
+        <v>704</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -4651,10 +4641,8 @@
           <t>กรมส่งเสริมการเกษตร</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>0711</t>
-        </is>
+      <c r="C121" t="n">
+        <v>711</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -4688,10 +4676,8 @@
           <t>กรมส่งเสริมสหกรณ์</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>0712</t>
-        </is>
+      <c r="C122" t="n">
+        <v>712</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -4725,10 +4711,8 @@
           <t>สำนักงานปลัดกระทรวงพลังงาน</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>1202</t>
-        </is>
+      <c r="C123" t="n">
+        <v>1202</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -4762,10 +4746,8 @@
           <t>กรมพัฒนาธุรกิจการค้า</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>1308</t>
-        </is>
+      <c r="C124" t="n">
+        <v>1308</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -4799,10 +4781,8 @@
           <t>กรมโยธาธิการและผังเมือง</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>1507</t>
-        </is>
+      <c r="C125" t="n">
+        <v>1507</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -4836,10 +4816,8 @@
           <t>กรมการศาสนา</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
+      <c r="C126" t="n">
+        <v>1803</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -4873,10 +4851,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C127" t="n">
+        <v>2102</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -4910,10 +4886,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C128" t="n">
+        <v>2102</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -4947,10 +4921,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C129" t="n">
+        <v>2102</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -4984,10 +4956,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C130" t="n">
+        <v>2102</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -5021,10 +4991,8 @@
           <t>สำนักงานคณะกรรมการอาหารและยา</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>2110</t>
-        </is>
+      <c r="C131" t="n">
+        <v>2110</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -5058,29 +5026,804 @@
           <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C132" t="n">
+        <v>2117</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อติดตั้งระบบกล้องวงจรปิด ของวิทยาลัยพยาบาลบรมราชชนนี นครศรีธรรมราช จำนวน 1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>★ (กล้องวงจรปิด)</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afa9b388-be98-4ed1-8fa9-0c791e5acf34</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>กรมธนารักษ์</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบริการทำความสะอาดศูนย์คอมพิวเตอร์แห่งใหม่ ของกรมธนารักษ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=36f30dd7-0674-4711-a8ba-e71eee8e8ed2</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>0502</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างโครงการค่าใช้จ่ายโครงการค่าจ้างบำรุงรักษาและซ่อมแซมห้องปฏิบัติการระบบเครือข่ายคอมพิวเตอร์ (Data Center) ของสำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=056989d3-d491-44ed-b887-fca9a5a8f472</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมและพัฒนาคุณภาพชีวิตคนพิการ</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>0607</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์งานบ้านงานครัวและครุภัณฑ์สำนักงาน จำนวน ๒๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f387eaf-54e2-4cf6-8c1c-826da6e3d09e</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>0704</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี. หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บพร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b694aef3-f630-4422-a7fe-e31adb551c45</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>0704</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องปรับอากาศแบบแยกส่วน (ราคารวมค่าติดตั้ง) แบบตั้งพื้นหรือแบบแขวน(ระบบ Inverter) ขนาดไม่ต่ำกว่า 36,000 บีทียู จำนวน 13 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>★ (เครื่องปรับอากาศ)</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=08075ad1-9390-4520-9d46-f5c2637228e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>0712</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=282d8226-b5a6-422f-ad5a-96682acbb042</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องตรวจวัดปริมาณแอลกอฮอล์ จำนวน 10 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>★ (แอลกอฮอล์)</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=152668c9-b054-48b8-9423-57975423ef48</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>กรมการเปลี่ยนแปลงสภาพภูมิอากาศและสิ่งแวดล้อม</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>0908</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาอุปกรณ์ห้อง Data center และเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3fa0cd84-f2db-47df-b581-c3555885f305</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>1202</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์เครือข่ายและอุปกรณ์คอมพิวเตอร์แม่ข่าย และอุปกรณ์สำรองข้อมูล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=86fe9b9f-c1ba-4f83-8b12-70dbc5d76baa</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์สำหรับงานจดทะเบียนและตรวจสอบธุรกิจผิดกฎหมาย กลุ่มทะเบียนธุรกิจและอำนวยความสะดวกทางการค้าของสำนักงานพาณิชย์จังหวัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=06246921-2a22-4f4d-822b-d5abae1c7c8c</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>กรมสอบสวนคดีพิเศษ</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>1608</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>ประกวดราคาเช่าเช่าใช้บริการสายสัญญาณเชื่อมโยงเครือข่ายอินเตอร์เน็ตพร้อมระบบ Internet Data Center ประจำปีงบประมาณ พ.ศ. 2570 (เดือนตุลาคม 2569  เดือนกันยายน 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>★ (สายสัญญาณ)</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f0c10124-df0c-410d-961c-bb4afe1ea16a</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบประชุมทางไกลผ่านจอภาพ (Video Conference)  ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>★ (จอภาพ, ระบบประชุมทางไกล)</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bb2e1625-bd6e-49b0-bf5e-6f3975c796e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันขนาดกลาง โรงพยาบาลเขาย้อย ตำบลเขาย้อย อำเภอเขาย้อย จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4d438ead-6d3b-40c3-8e25-0c855ca2699d</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง โรงพยาบาลหนองหญ้าปล้อง ตำบลหนองหญ้าปล้อง อำเภอหนองหญ้าปล้อง จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=38179365-12e6-43e5-ac4b-973f7d7d62c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดัน ขนาดใหญ่ จำนวน 2 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2c8651ab-6342-4cf7-b1d4-44acb01ef167</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดเล็ก ของโรงพยาบาลชุมชน 2 แห่ง จำนวน 6 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=092dea18-169e-423d-bdf4-cbb905df5ef4</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องเอกซเรย์เคลื่อนที่ขนาดไม่น้อยกว่า 300 mA.ขับเคลื่อนด้วยมอเตอร์ไฟฟ้า ของโรงพยาบาลในจังหวัดสุรินทร์ 3 แห่ง จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์, มอเตอร์)</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=587ceaac-9b51-4f53-a40b-ba6307295dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>กรมการแพทย์แผนไทยและการแพทย์ทางเลือก</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างจ้างบำรุงรักษาและซ่อมแซมแก้ไขปัญหาเครื่องคอมพิวเตอร์แม่ข่ายและอุปกรณ์ระบบเครือข่าย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a18ab514-a7bf-42a3-be34-78ab2073afdd</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2106</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน ๙ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70e80b61-ece5-4761-bcba-cb1ce4f2a872</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>สถาบันพระบรมราชชนก</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
         <is>
           <t>2117</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>ประกวดราคาซื้อติดตั้งระบบกล้องวงจรปิด ของวิทยาลัยพยาบาลบรมราชชนนี นครศรีธรรมราช จำนวน 1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>★ (กล้องวงจรปิด)</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afa9b388-be98-4ed1-8fa9-0c791e5acf34</t>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อึครุภัณฑ์สำนักงาน รายการเครื่องปรับอากาศและพัดลม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ, พัดลม)</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8cf26d57-cf1b-4ebf-8134-fcf45b7f7c54</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>สถาบันพระบรมราชชนก</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2117</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง (รถยนต์บรรทุกโดยสาร 6 ล้อ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=37a7653e-4e42-4513-bc7a-c74cd6a83f90</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202609.xlsx
+++ b/Backup/eGP_Monthly_Main_202609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G153"/>
+  <dimension ref="A1:G169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1033,15 +1033,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา</t>
+          <t>กรมพลศึกษา</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการค่าใช้จ่ายโครงการค่าจ้างบำรุงรักษาและซ่อมแซมห้องปฏิบัติการระบบเครือข่ายคอมพิวเตอร์ (Data Center) ของสำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างเหมาบริการขนย้ายอุปกรณ์สำนักงานอุปกรณ์ฟิตเนส และเครื่องมือวิทยาศาสตร์การกีฬา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (อุปกรณ์สำนักงาน)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2d1c7b53-847a-4bf6-b522-1960eec33718</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=68d145d2-7e86-4ce2-83ae-2d369ff13869</t>
         </is>
       </c>
     </row>
@@ -1068,15 +1068,15 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>กรมพลศึกษา</t>
+          <t>สำนักงานปลัดกระทรวงการพัฒนาสังคมและความมั่นคงของมนุษย์</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>503</v>
+        <v>602</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างเหมาบริการขนย้ายอุปกรณ์สำนักงานอุปกรณ์ฟิตเนส และเครื่องมือวิทยาศาสตร์การกีฬา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าลิขสิทธิ์ตามโครงการต่ออายุลิขสิทธิ์การใช้งานเครื่องคอมพิวเตอร์แม่ข่าย และอุปกรณ์เครือข่าย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>★ (อุปกรณ์สำนักงาน)</t>
+          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=68d145d2-7e86-4ce2-83ae-2d369ff13869</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ad102932-1c37-4684-9245-ad75dc78ac1b</t>
         </is>
       </c>
     </row>
@@ -1103,15 +1103,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการพัฒนาสังคมและความมั่นคงของมนุษย์</t>
+          <t>สำนักงานปลัดกระทรวงเกษตรและสหกรณ์</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>602</v>
+        <v>702</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าลิขสิทธิ์ตามโครงการต่ออายุลิขสิทธิ์การใช้งานเครื่องคอมพิวเตอร์แม่ข่าย และอุปกรณ์เครือข่าย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาเอกชนบริการล้างทำความสะอาดและบำรุงรักษาเครื่องปรับอากาศ ภายในอาคารที่ทำการกระทรวงเกษตรและสหกรณ์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ad102932-1c37-4684-9245-ad75dc78ac1b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=36d7c59c-cec2-4f2d-a850-b67c193ca197</t>
         </is>
       </c>
     </row>
@@ -1138,15 +1138,15 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงเกษตรและสหกรณ์</t>
+          <t>กรมป้องกันและบรรเทาสาธารณภัย</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>702</v>
+        <v>1506</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาเอกชนบริการล้างทำความสะอาดและบำรุงรักษาเครื่องปรับอากาศ ภายในอาคารที่ทำการกระทรวงเกษตรและสหกรณ์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาชุดกล้องวงจรปิดพร้อมอุปกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (กล้องวงจรปิด)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=36d7c59c-cec2-4f2d-a850-b67c193ca197</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=08888f93-7ea8-4e78-95a7-c73a160f680b</t>
         </is>
       </c>
     </row>
@@ -1173,15 +1173,15 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>กรมป้องกันและบรรเทาสาธารณภัย</t>
+          <t>กรมโยธาธิการและผังเมือง</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาชุดกล้องวงจรปิดพร้อมอุปกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน ๖ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>★ (กล้องวงจรปิด)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=08888f93-7ea8-4e78-95a7-c73a160f680b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ade5ffa-bced-41dd-990a-e25bb0710b03</t>
         </is>
       </c>
     </row>
@@ -1208,15 +1208,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>กรมโยธาธิการและผังเมือง</t>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1507</v>
+        <v>1611</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน ๖ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาและแก้ไขอุปกรณ์สนับสนุนห้องปฏิบัติการคอมพิวเตอร์ (Data Center) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ade5ffa-bced-41dd-990a-e25bb0710b03</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d4c700d2-d110-4ee6-944c-fbfe3c3ccda4</t>
         </is>
       </c>
     </row>
@@ -1243,15 +1243,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+          <t>กรมพัฒนาฝีมือแรงงาน</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1611</v>
+        <v>1704</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาและแก้ไขอุปกรณ์สนับสนุนห้องปฏิบัติการคอมพิวเตอร์ (Data Center) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d4c700d2-d110-4ee6-944c-fbfe3c3ccda4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e684df7d-e4aa-429f-90e2-baf69d050535</t>
         </is>
       </c>
     </row>
@@ -1278,15 +1278,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1611</v>
+        <v>2102</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบประชุมทางไกลผ่านจอภาพ (Video Conference)  ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องกระตุกไฟฟ้าหัวใจชนิดอัตโนมัติ พร้อมตู้ตั้งพื้นจอแสดงผล และระบบสัญญาณเตือน จำนวน 10 เครื่อง สำหรับ รพ.พระปิยมหาราช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>★ (จอภาพ, ระบบประชุมทางไกล)</t>
+          <t>★ (จอแสดงผล)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7087adf8-2cc8-4674-a130-694da727ee83</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5fb07982-c16a-4dd2-9379-726a8d5a7710</t>
         </is>
       </c>
     </row>
@@ -1313,15 +1313,15 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>กรมพัฒนาฝีมือแรงงาน</t>
+          <t>กรมอนามัย</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1704</v>
+        <v>2109</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบประชุมทางไกลออนไลน์ (Video Conference) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ระบบประชุมทางไกล)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e684df7d-e4aa-429f-90e2-baf69d050535</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e9299467-894b-4d9f-930b-0673992d5759</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2102</v>
+        <v>502</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องกระตุกไฟฟ้าหัวใจชนิดอัตโนมัติ พร้อมตู้ตั้งพื้นจอแสดงผล และระบบสัญญาณเตือน จำนวน 10 เครื่อง สำหรับ รพ.พระปิยมหาราช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์ลูกข่ายและระบบเครือข่ายคอมพิวเตอร์ พร้อมทั้งอุปกรณ์ต่อพ่วง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1366,32 +1366,32 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>★ (จอแสดงผล)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5fb07982-c16a-4dd2-9379-726a8d5a7710</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5925e432-6a1c-4246-aab2-f2094aeabd5b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>กรมอนามัย</t>
+          <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2109</v>
+        <v>804</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบประชุมทางไกลออนไลน์ (Video Conference) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อวัสดุคอมพิวเตอร์ จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>★ (ระบบประชุมทางไกล)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e9299467-894b-4d9f-930b-0673992d5759</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=69b5d49d-35a2-49b6-9c69-a77a74df0e9d</t>
         </is>
       </c>
     </row>
@@ -1418,15 +1418,15 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>502</v>
+        <v>806</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์ลูกข่ายและระบบเครือข่ายคอมพิวเตอร์ พร้อมทั้งอุปกรณ์ต่อพ่วง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์งานบ้านงานครัว จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5925e432-6a1c-4246-aab2-f2094aeabd5b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4b934857-93a6-4ef0-9708-1c258599416f</t>
         </is>
       </c>
     </row>
@@ -1453,15 +1453,15 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
+          <t>กรมการขนส่งทางราง</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อวัสดุคอมพิวเตอร์ จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ต่อพ่วง พร้อมการติดตั้ง จำนวน ๔ รายการ ของกรมการขนส่งทางราง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=69b5d49d-35a2-49b6-9c69-a77a74df0e9d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f5fcf75f-2a16-470f-9a41-1d640b04b1a1</t>
         </is>
       </c>
     </row>
@@ -1488,15 +1488,15 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>สำนักงานนโยบายและแผนทรัพยากรธรรมชาติและสิ่งแวดล้อม</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>806</v>
+        <v>911</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์งานบ้านงานครัว จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างต่ออายุสมาชิกโปรแกรมและบำรุงรักษาซ่อมแซมแก้ไขคอมพิวเตอร์แม่ข่ายและอุปกรณ์เครือข่ายไร้สาย ปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4b934857-93a6-4ef0-9708-1c258599416f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3327ec9-d212-4e24-aafb-36bbf05f5a34</t>
         </is>
       </c>
     </row>
@@ -1523,15 +1523,15 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางราง</t>
+          <t>สำนักงานกองทุนน้ำมันเชื้อเพลิง</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>812</v>
+        <v>1207</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ต่อพ่วง พร้อมการติดตั้ง จำนวน ๔ รายการ ของกรมการขนส่งทางราง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าคอมพิวเตอร์และอุปกรณ์ที่เกี่ยวข้อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f5fcf75f-2a16-470f-9a41-1d640b04b1a1</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1fb72e55-1c99-4e44-b4b3-370e1c2e8711</t>
         </is>
       </c>
     </row>
@@ -1558,15 +1558,15 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>สำนักงานนโยบายและแผนทรัพยากรธรรมชาติและสิ่งแวดล้อม</t>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>911</v>
+        <v>1302</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างต่ออายุสมาชิกโปรแกรมและบำรุงรักษาซ่อมแซมแก้ไขคอมพิวเตอร์แม่ข่ายและอุปกรณ์เครือข่ายไร้สาย ปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าระบบประชุมทางไกล (Web Conference Video Streaming) ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
+          <t>★ (ระบบประชุมทางไกล)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3327ec9-d212-4e24-aafb-36bbf05f5a34</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3d156308-f0d2-4d07-bf4a-27913c2c22b7</t>
         </is>
       </c>
     </row>
@@ -1593,15 +1593,15 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>สำนักงานกองทุนน้ำมันเชื้อเพลิง</t>
+          <t>กรมที่ดิน</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1207</v>
+        <v>1505</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าคอมพิวเตอร์และอุปกรณ์ที่เกี่ยวข้อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อโต๊ะและเก้าอี้เพื่อใช้ในราชการของสำนักงานที่ดินจังหวัดพิษณุโลก และสาขาฯ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (โต๊ะ, เก้าอี้)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1fb72e55-1c99-4e44-b4b3-370e1c2e8711</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=341e9241-c067-4ffa-9e06-734f19c6b999</t>
         </is>
       </c>
     </row>
@@ -1628,15 +1628,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+          <t>กรมพัฒนาฝีมือแรงงาน</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1302</v>
+        <v>1704</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าระบบประชุมทางไกล (Web Conference Video Streaming) ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาครุภัณฑ์คอมพิวเตอร์และระบบเครือข่าย ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>★ (ระบบประชุมทางไกล)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3d156308-f0d2-4d07-bf4a-27913c2c22b7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=677d75a8-aa89-4b8b-a742-eca4be741031</t>
         </is>
       </c>
     </row>
@@ -1663,15 +1663,15 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>กรมที่ดิน</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1505</v>
+        <v>2102</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อโต๊ะและเก้าอี้เพื่อใช้ในราชการของสำนักงานที่ดินจังหวัดพิษณุโลก และสาขาฯ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๓ รายการ ของสำนักงานสาธารณสุขจังหวัดกาญจนบุรี เพื่อโรงพยาบาลชุมชน จำนวน ๑๐ แห่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1681,12 +1681,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>★ (โต๊ะ, เก้าอี้)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=341e9241-c067-4ffa-9e06-734f19c6b999</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0424125a-176e-423d-9959-61c0ef9229f3</t>
         </is>
       </c>
     </row>
@@ -1698,15 +1698,15 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>กรมพัฒนาฝีมือแรงงาน</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1704</v>
+        <v>2102</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาครุภัณฑ์คอมพิวเตอร์และระบบเครือข่าย ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 6 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง จำนวน 1 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ.2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1716,12 +1716,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=677d75a8-aa89-4b8b-a742-eca4be741031</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ee066bf2-4c21-4580-8391-e1257afc7b11</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๓ รายการ ของสำนักงานสาธารณสุขจังหวัดกาญจนบุรี เพื่อโรงพยาบาลชุมชน จำนวน ๑๐ แห่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อตู้เย็นเก็บเลือดขนาดไม่น้อยกว่า 20 คิว จำนวน 1 เครื่อง สำหรับ รพ.พระปิยมหาราช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ตู้เย็น)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0424125a-176e-423d-9959-61c0ef9229f3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=985c4332-e608-4dc3-883b-e90257b97ad3</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 6 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง จำนวน 1 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ.2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์การแพทย์เพื่อการบริการประชาชน จำนวน 13 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ee066bf2-4c21-4580-8391-e1257afc7b11</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=db849b83-870c-446d-a004-6e2462b1b3a4</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อตู้เย็นเก็บเลือดขนาดไม่น้อยกว่า 20 คิว จำนวน 1 เครื่อง สำหรับ รพ.พระปิยมหาราช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนในเลือดของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 5 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1821,32 +1821,32 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>★ (ตู้เย็น)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=985c4332-e608-4dc3-883b-e90257b97ad3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e2347540-427f-4618-ac0a-6d2933980a00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สำนักงานปลัดกระทรวงการคลัง</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2102</v>
+        <v>302</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์การแพทย์เพื่อการบริการประชาชน จำนวน 13 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อสิทธิ์การใช้งานซอฟต์แวร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1856,32 +1856,32 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=db849b83-870c-446d-a004-6e2462b1b3a4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1732e367-2c09-431f-abc1-7384c0a94e8e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมศุลกากร</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2102</v>
+        <v>305</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนในเลือดของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 5 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าโครงการจัดเช่าวงจรเครือข่ายสื่อสารเพื่อการเชื่อมโยงข้อมูลระหว่างศูนย์คอมพิวเตอร์ (DC-DR) กรมศุลกากร ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e2347540-427f-4618-ac0a-6d2933980a00</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a09e3df4-34c1-4388-a91a-31d0494ea9da</t>
         </is>
       </c>
     </row>
@@ -1908,15 +1908,15 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการคลัง</t>
+          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>302</v>
+        <v>402</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อสิทธิ์การใช้งานซอฟต์แวร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการทำความสะอาด ณ อาคารกระทรวงการต่างประเทศ ถนนศรีอยุธยา อาคารกรมการกงสุลรวมถึงกองบรรณสารและห้องสมุด (ฝ่ายบรรณสาร) และศูนย์ราชการเฉลิมพระเกียรติฯ อาคาร B ชั้น 7 - 8 รวม 3 แห่ง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1926,12 +1926,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>★ (ซอฟต์แวร์)</t>
+          <t>★ (สมุด)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1732e367-2c09-431f-abc1-7384c0a94e8e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=61256c96-a851-4486-ba34-aeb06311fa64</t>
         </is>
       </c>
     </row>
@@ -1943,15 +1943,15 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>กรมศุลกากร</t>
+          <t>กรมชลประทาน</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>305</v>
+        <v>703</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าโครงการจัดเช่าวงจรเครือข่ายสื่อสารเพื่อการเชื่อมโยงข้อมูลระหว่างศูนย์คอมพิวเตอร์ (DC-DR) กรมศุลกากร ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องสูบน้ำชนิดหอยโข่ง เเบบ End Suction ขับด้วยมอเตอร์ไฟฟ้า พร้อมติดตั้งอุปกรณ์ เเละระบบควบคุมไฟฟ้า ตามรายละเอียดคุณลักษณะเฉพาะ (Specification) ของกรมชลประทาน และอื่นๆ รวม ๓ รายการ สำหรับงานสถานีสูบน้ำด้วยไฟฟ้าพร้อมระบบส่งน้ำฝายคลองพอถาก ตำบลหน้าเขา อำเภอเขาพนม จังหวัดกระบี่ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1961,12 +1961,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a09e3df4-34c1-4388-a91a-31d0494ea9da</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f690008d-6ff3-4f11-84a7-08da3de166d4</t>
         </is>
       </c>
     </row>
@@ -1978,15 +1978,15 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
+          <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>402</v>
+        <v>804</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการทำความสะอาด ณ อาคารกระทรวงการต่างประเทศ ถนนศรีอยุธยา อาคารกรมการกงสุลรวมถึงกองบรรณสารและห้องสมุด (ฝ่ายบรรณสาร) และศูนย์ราชการเฉลิมพระเกียรติฯ อาคาร B ชั้น 7 - 8 รวม 3 แห่ง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์ Server และอุปกรณ์ที่ติดตั้ง ณ อาคารระบบข้อมูลกลางและสำรองข้อมูล สำนักงานขนส่งจังหวัดนนทบุรี ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>★ (สมุด)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=61256c96-a851-4486-ba34-aeb06311fa64</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7dbc77ce-d778-424c-9618-b2cc1659f8ad</t>
         </is>
       </c>
     </row>
@@ -2013,15 +2013,15 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>กรมชลประทาน</t>
+          <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>703</v>
+        <v>804</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องสูบน้ำชนิดหอยโข่ง เเบบ End Suction ขับด้วยมอเตอร์ไฟฟ้า พร้อมติดตั้งอุปกรณ์ เเละระบบควบคุมไฟฟ้า ตามรายละเอียดคุณลักษณะเฉพาะ (Specification) ของกรมชลประทาน และอื่นๆ รวม ๓ รายการ สำหรับงานสถานีสูบน้ำด้วยไฟฟ้าพร้อมระบบส่งน้ำฝายคลองพอถาก ตำบลหน้าเขา อำเภอเขาพนม จังหวัดกระบี่ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมระบบคอมพิวเตอร์แม่ข่ายเสมือน (Server Virtualization) สำหรับให้บริการหน่วยงานต่างๆ ของกรมการขนส่งทางบกที่ใช้ในการสนับสนุน การปฏิบัติงานด้านความปลอดภัย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f690008d-6ff3-4f11-84a7-08da3de166d4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=60f2364f-32ae-4a8c-8c92-9936327bd8f9</t>
         </is>
       </c>
     </row>
@@ -2048,15 +2048,15 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
+          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>804</v>
+        <v>904</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์ Server และอุปกรณ์ที่ติดตั้ง ณ อาคารระบบข้อมูลกลางและสำรองข้อมูล สำนักงานขนส่งจังหวัดนนทบุรี ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการเช่าใช้บริการอินเทอร์เน็ตและสายสัญญาณเครือข่ายพร้อมอุปกรณ์ กรมทรัพยากรทางทะเลและชายฝั่ง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (สายสัญญาณ)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7dbc77ce-d778-424c-9618-b2cc1659f8ad</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ab266c44-4e3d-4e4c-a44e-a5e06ffb7d51</t>
         </is>
       </c>
     </row>
@@ -2083,15 +2083,15 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
+          <t>กรมที่ดิน</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>804</v>
+        <v>1505</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมระบบคอมพิวเตอร์แม่ข่ายเสมือน (Server Virtualization) สำหรับให้บริการหน่วยงานต่างๆ ของกรมการขนส่งทางบกที่ใช้ในการสนับสนุน การปฏิบัติงานด้านความปลอดภัย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์และระบบคอมพิวเตอร์แม่ข่าย ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ระยะเวลา ๑๒ เดือน  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=60f2364f-32ae-4a8c-8c92-9936327bd8f9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ba59f24a-325d-4e38-8d86-eadcece33632</t>
         </is>
       </c>
     </row>
@@ -2118,15 +2118,15 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>904</v>
+        <v>1611</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการเช่าใช้บริการอินเทอร์เน็ตและสายสัญญาณเครือข่ายพร้อมอุปกรณ์ กรมทรัพยากรทางทะเลและชายฝั่ง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการถ่ายเอกสารพร้อมเครื่องถ่ายเอกสาร กระดาษ วัสดุสิ้นเปลือง และพนักงานประจำเครื่องของสำนักงาน ป.ป.ส. ดินแดง สำนักงาน ปปส.ทุ่งสองห้อง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>★ (สายสัญญาณ)</t>
+          <t>★ (กระดาษ)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ab266c44-4e3d-4e4c-a44e-a5e06ffb7d51</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ef490410-ac68-4d7a-9e38-c4dbf7dd4191</t>
         </is>
       </c>
     </row>
@@ -2153,15 +2153,15 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>กรมที่ดิน</t>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1505</v>
+        <v>1611</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์และระบบคอมพิวเตอร์แม่ข่าย ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ระยะเวลา ๑๒ เดือน  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาซอฟต์แวร์และอุปกรณ์ระบบรักษาความปลอดภัยระบบเครือข่ายศูนย์คอมพิวเตอร์สำรอง ( DR-Site Firewall) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ba59f24a-325d-4e38-8d86-eadcece33632</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a430ff3c-1d84-458b-8d71-d54f8c065644</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการถ่ายเอกสารพร้อมเครื่องถ่ายเอกสาร กระดาษ วัสดุสิ้นเปลือง และพนักงานประจำเครื่องของสำนักงาน ป.ป.ส. ดินแดง สำนักงาน ปปส.ทุ่งสองห้อง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบป้องกันการบุกรุกเครือข่ายคอมพิวเตอร์ สำนักงาน ป.ป.ส. (Client Zone Firewall) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>★ (กระดาษ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ef490410-ac68-4d7a-9e38-c4dbf7dd4191</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bfcbc7fd-4a5c-46e3-b5eb-5b51397db1cb</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาซอฟต์แวร์และอุปกรณ์ระบบรักษาความปลอดภัยระบบเครือข่ายศูนย์คอมพิวเตอร์สำรอง ( DR-Site Firewall) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์เครื่องคอมพิวเตอร์แม่ข่ายพร้อมระบบปฏิบัติการ (Server) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ซอฟต์แวร์)</t>
+          <t>★ (คอมพิวเตอร์, ระบบปฏิบัติการ)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a430ff3c-1d84-458b-8d71-d54f8c065644</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4a59a370-30a9-4f35-abcd-cec87b36ed1e</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบป้องกันการบุกรุกเครือข่ายคอมพิวเตอร์ สำนักงาน ป.ป.ส. (Client Zone Firewall) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์และซอฟต์แวร์ป้องกันระบบเครือข่าย (Firewall/Virus/VPN) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bfcbc7fd-4a5c-46e3-b5eb-5b51397db1cb</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=71058768-3f32-47a5-b07d-d89703297e8b</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์เครื่องคอมพิวเตอร์แม่ข่ายพร้อมระบบปฏิบัติการ (Server) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาและแก้ไขปัญหาการใช้เครื่องคอมพิวเตอร์ลูกข่ายและอุปกรณ์ต่อพ่วง สำนักงาน ป.ป.ส. ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ระบบปฏิบัติการ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4a59a370-30a9-4f35-abcd-cec87b36ed1e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=04f4a224-3c0a-4630-9981-263ded303a56</t>
         </is>
       </c>
     </row>
@@ -2328,15 +2328,15 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1611</v>
+        <v>2102</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์และซอฟต์แวร์ป้องกันระบบเครือข่าย (Firewall/Virus/VPN) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการเครื่องดมยาสลบชนิดมาตรฐาน  จำนวน  ๑  เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>★ (ซอฟต์แวร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=71058768-3f32-47a5-b07d-d89703297e8b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e1f11ae5-c3d5-4fdc-a76f-351add1653a8</t>
         </is>
       </c>
     </row>
@@ -2363,15 +2363,15 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1611</v>
+        <v>2102</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาและแก้ไขปัญหาการใช้เครื่องคอมพิวเตอร์ลูกข่ายและอุปกรณ์ต่อพ่วง สำนักงาน ป.ป.ส. ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการกล้องส่องตรวจและผ่าตัดภายในช่องท้องชนิดวีดิทัศน์แบบคมชัดสูงชนิดภาพ ๒ มิติ จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=04f4a224-3c0a-4630-9981-263ded303a56</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3ff66642-757c-4554-a147-37146918afe9</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการเครื่องดมยาสลบชนิดมาตรฐาน  จำนวน  ๑  เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์โครงการจัดซื้อครุภัณฑ์การแพทย์เพื่อการบริการประชาชน จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e1f11ae5-c3d5-4fdc-a76f-351add1653a8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=921cfd0c-6740-4e24-84ce-20ad0ebfb382</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการกล้องส่องตรวจและผ่าตัดภายในช่องท้องชนิดวีดิทัศน์แบบคมชัดสูงชนิดภาพ ๒ มิติ จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันเคลื่อนย้ายได้ ของโรงพยาบาลชุมชน 8 แห่ง จำนวน 11 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3ff66642-757c-4554-a147-37146918afe9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2ac905f2-26be-4df4-b481-22676581f31a</t>
         </is>
       </c>
     </row>
@@ -2468,15 +2468,15 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2102</v>
+        <v>2113</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์โครงการจัดซื้อครุภัณฑ์การแพทย์เพื่อการบริการประชาชน จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องฟอกอากาศ แขวงทุ่งสองห้อง เขตหลักสี่ กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2486,32 +2486,32 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องฟอกอากาศ)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=921cfd0c-6740-4e24-84ce-20ad0ebfb382</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a91dc5dd-5f0e-49d2-8b3f-d7da9560b550</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สำนักงานรับรองมาตรฐานและประเมินคุณภาพการศึกษา (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2102</v>
+        <v>116</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันเคลื่อนย้ายได้ ของโรงพยาบาลชุมชน 8 แห่ง จำนวน 11 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบ AQA ก) ระบบสารสนเทศเพื่อการประเมินคุณภาพภายนอก (AQA) ข) ระบบและซอฟต์แวร์สำหรับการจัดการไฟล์วิดีโอ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2521,32 +2521,32 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2ac905f2-26be-4df4-b481-22676581f31a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=15b527de-47eb-447e-8bc6-1bc4e5204254</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+          <t>กรมพลศึกษา</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2113</v>
+        <v>503</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องฟอกอากาศ แขวงทุ่งสองห้อง เขตหลักสี่ กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาดูแล ปรับปรุง บำรุงรักษา และพัฒนาระบบเครือข่ายและอุปกรณ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>★ (เครื่องฟอกอากาศ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a91dc5dd-5f0e-49d2-8b3f-d7da9560b550</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ff914fa4-2fa4-4a9c-bb1e-eb038590a95a</t>
         </is>
       </c>
     </row>
@@ -2573,15 +2573,15 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>สำนักงานรับรองมาตรฐานและประเมินคุณภาพการศึกษา (องค์การมหาชน)</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>116</v>
+        <v>704</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบ AQA ก) ระบบสารสนเทศเพื่อการประเมินคุณภาพภายนอก (AQA) ข) ระบบและซอฟต์แวร์สำหรับการจัดการไฟล์วิดีโอ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์  เครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล พร้อมชุดโปรแกรมระบบปฏิบัติการ สำหรับเครื่องคอมพิวเตอร์และเครื่องคอมพิวเตอร์โน้ตบุ๊ก แบบสิทธิการใช้งานภายในสำนักงาน ประเภทติดตั้งมาจากโรงงาน (OEM) ที่มีลิขสิทธิ์ที่ถูกต้องตามกฎหมาย ชุดโปรแกรมจัดการสานักงาน แบบที่ 2 ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย และชุดโปรแกรมป้องกันไวรัส จำนวน 15 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>★ (ซอฟต์แวร์)</t>
+          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ระบบปฏิบัติการ, โปรแกรมป้องกันไวรัส, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=15b527de-47eb-447e-8bc6-1bc4e5204254</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2b1675a5-f593-4cd6-a100-2c0f3ac9c6e2</t>
         </is>
       </c>
     </row>
@@ -2608,15 +2608,15 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>กรมพลศึกษา</t>
+          <t>กรมประมง</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>503</v>
+        <v>705</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาดูแล ปรับปรุง บำรุงรักษา และพัฒนาระบบเครือข่ายและอุปกรณ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน ๑ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ff914fa4-2fa4-4a9c-bb1e-eb038590a95a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7899c0ad-4727-4814-a039-57ea77f4e508</t>
         </is>
       </c>
     </row>
@@ -2643,15 +2643,15 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมประมง</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์  เครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล พร้อมชุดโปรแกรมระบบปฏิบัติการ สำหรับเครื่องคอมพิวเตอร์และเครื่องคอมพิวเตอร์โน้ตบุ๊ก แบบสิทธิการใช้งานภายในสำนักงาน ประเภทติดตั้งมาจากโรงงาน (OEM) ที่มีลิขสิทธิ์ที่ถูกต้องตามกฎหมาย ชุดโปรแกรมจัดการสานักงาน แบบที่ 2 ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย และชุดโปรแกรมป้องกันไวรัส จำนวน 15 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อชุดจอภาพ LED พร้อมงานติดตั้งสำหรับห้องประชุมอานนท์ กรมประมง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2661,12 +2661,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ระบบปฏิบัติการ, โปรแกรมป้องกันไวรัส, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (จอภาพ)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2b1675a5-f593-4cd6-a100-2c0f3ac9c6e2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a26dbb80-72fc-430c-8431-ba0133b850fc</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน ๑ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าเเละวิทยุ เครื่องกำเนิดไฟฟ้า ขนาด 100 กิโลวัตต์ พร้อมตู้ควบคุม ตำบลหูล่อง อำเภอปากพนัง จังหวัดนครศรีธรรมราช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7899c0ad-4727-4814-a039-57ea77f4e508</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=18464524-52ce-42bf-96c8-511cdf002607</t>
         </is>
       </c>
     </row>
@@ -2713,15 +2713,15 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>กรมประมง</t>
+          <t>กรมการข้าว</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>705</v>
+        <v>718</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อชุดจอภาพ LED พร้อมงานติดตั้งสำหรับห้องประชุมอานนท์ กรมประมง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ต่อพ่วงเพื่อเพิ่มประสิทธิภาพการปฏิบัติงานของกรมการข้าว แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>★ (จอภาพ)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a26dbb80-72fc-430c-8431-ba0133b850fc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=aaaf180c-62ba-4ca4-9a9c-0333baa76276</t>
         </is>
       </c>
     </row>
@@ -2748,15 +2748,15 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>กรมประมง</t>
+          <t>กรมการข้าว</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>705</v>
+        <v>718</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าเเละวิทยุ เครื่องกำเนิดไฟฟ้า ขนาด 100 กิโลวัตต์ พร้อมตู้ควบคุม ตำบลหูล่อง อำเภอปากพนัง จังหวัดนครศรีธรรมราช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อทดแทนครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ต่อพ่วงเพื่อเพิ่มประสิทธิภาพการปฏิบัติงานของกรมการข้าว แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=18464524-52ce-42bf-96c8-511cdf002607</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=15086036-ab87-4a45-b29c-edd87f507d1b</t>
         </is>
       </c>
     </row>
@@ -2783,15 +2783,15 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>กรมการข้าว</t>
+          <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>718</v>
+        <v>804</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ต่อพ่วงเพื่อเพิ่มประสิทธิภาพการปฏิบัติงานของกรมการข้าว แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์และอุปกรณ์ตามโครงการระบบเครือข่ายเพื่อเพิ่มประสิทธิภาพในการปฏิบัติงานของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2801,12 +2801,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=aaaf180c-62ba-4ca4-9a9c-0333baa76276</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=faa5336e-2946-42fd-b66e-9583a9f24e44</t>
         </is>
       </c>
     </row>
@@ -2818,15 +2818,15 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>กรมการข้าว</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>718</v>
+        <v>806</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อทดแทนครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ต่อพ่วงเพื่อเพิ่มประสิทธิภาพการปฏิบัติงานของกรมการข้าว แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=15086036-ab87-4a45-b29c-edd87f507d1b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=44d1ec7f-04ab-49d0-b112-502799195d6b</t>
         </is>
       </c>
     </row>
@@ -2853,15 +2853,15 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์และอุปกรณ์ตามโครงการระบบเครือข่ายเพื่อเพิ่มประสิทธิภาพในการปฏิบัติงานของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการจัดจ้างบำรุงรักษาเครื่องคอมพิวเตอร์แม่ข่ายและอุปกรณ์สำหรับระบบสารสนเทศบริหารเครื่องจักรกลและการเงินการบัญชีเพื่อการบริหารจัดการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=faa5336e-2946-42fd-b66e-9583a9f24e44</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=909fce3b-2a20-4eb7-b619-b2e32da6e18d</t>
         </is>
       </c>
     </row>
@@ -2888,15 +2888,15 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>806</v>
+        <v>904</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาและเพิ่มประสิทธิภาพระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรทางทะเลและชายฝั่ง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=44d1ec7f-04ab-49d0-b112-502799195d6b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a2cbdca0-293f-4c68-b81a-7197ca7e532f</t>
         </is>
       </c>
     </row>
@@ -2923,15 +2923,15 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>กรมทรัพยากรธรณี</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>806</v>
+        <v>905</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการจัดจ้างบำรุงรักษาเครื่องคอมพิวเตอร์แม่ข่ายและอุปกรณ์สำหรับระบบสารสนเทศบริหารเครื่องจักรกลและการเงินการบัญชีเพื่อการบริหารจัดการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาซ่อมบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรธรณี ปีงบประมาณ พ.ศ. 2570 จำนวน 1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=909fce3b-2a20-4eb7-b619-b2e32da6e18d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3cc3bb5f-0d9f-428a-b588-18b0b71b8b6e</t>
         </is>
       </c>
     </row>
@@ -2958,15 +2958,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
+          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการบำรุงรักษาและเพิ่มประสิทธิภาพระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรทางทะเลและชายฝั่ง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อและติดตั้งเครื่องคอมพิวเตอร์แม่ข่ายพร้อมอุปกรณ์ประกอบสำหรับรองรับการให้บริการระบบสารบรรณอิเล็กทรอนิกส์ของกรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a2cbdca0-293f-4c68-b81a-7197ca7e532f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=028b6dd5-2160-4f89-924f-f6c47b4b4995</t>
         </is>
       </c>
     </row>
@@ -2993,15 +2993,15 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>กรมทรัพยากรธรณี</t>
+          <t>สำนักงานปลัดกระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>905</v>
+        <v>1102</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาซ่อมบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรธรณี ปีงบประมาณ พ.ศ. 2570 จำนวน 1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการจัดอบรมเตรียมความพร้อมผู้แต่งตั้งเป็นพนักงานเจ้าหน้าที่ตามพระราชบัญญัติว่าด้วยการกระทำความผิดเกี่ยวกับคอมพิวเตอร์ฯ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3cc3bb5f-0d9f-428a-b588-18b0b71b8b6e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8de232df-b5c2-427b-9a5d-d9f5ca3342c3</t>
         </is>
       </c>
     </row>
@@ -3028,15 +3028,15 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>909</v>
+        <v>1302</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อและติดตั้งเครื่องคอมพิวเตอร์แม่ข่ายพร้อมอุปกรณ์ประกอบสำหรับรองรับการให้บริการระบบสารบรรณอิเล็กทรอนิกส์ของกรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์สนับสนุนศูนย์ข้อมูลและเครือข่ายคอมพิวเตอร์ (Data Center) ของกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=028b6dd5-2160-4f89-924f-f6c47b4b4995</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5065022-193d-466c-819b-b1533c1e1696</t>
         </is>
       </c>
     </row>
@@ -3063,15 +3063,15 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม</t>
+          <t>สถาบันส่งเสริมศิลปหัตถกรรมไทย (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1102</v>
+        <v>1311</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการจัดอบรมเตรียมความพร้อมผู้แต่งตั้งเป็นพนักงานเจ้าหน้าที่ตามพระราชบัญญัติว่าด้วยการกระทำความผิดเกี่ยวกับคอมพิวเตอร์ฯ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างดำเนินการบำรุงรักษาระบบและอุปกรณ์ภายในห้อง Data Center และการต่อลิขสิทธิ์โปรแกรมคอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8de232df-b5c2-427b-9a5d-d9f5ca3342c3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8c2b0f9b-210b-4328-a727-0ebda03f9ebc</t>
         </is>
       </c>
     </row>
@@ -3098,15 +3098,15 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+          <t>กรมบังคับคดี</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1302</v>
+        <v>1605</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์สนับสนุนศูนย์ข้อมูลและเครือข่ายคอมพิวเตอร์ (Data Center) ของกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างตรวจสอบเครื่องคอมพิวเตอร์ให้พร้อมใช้งานและบริการประชาชน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5065022-193d-466c-819b-b1533c1e1696</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=590bcfa8-9d1a-43f4-b6c0-1d332cdf98ac</t>
         </is>
       </c>
     </row>
@@ -3133,15 +3133,15 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>สถาบันส่งเสริมศิลปหัตถกรรมไทย (องค์การมหาชน)</t>
+          <t>กรมศิลปากร</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1311</v>
+        <v>1804</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างดำเนินการบำรุงรักษาระบบและอุปกรณ์ภายในห้อง Data Center และการต่อลิขสิทธิ์โปรแกรมคอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการดูแลบำรุงรักษาเครื่องปรับอากาศ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8c2b0f9b-210b-4328-a727-0ebda03f9ebc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=560aab6a-379c-4e73-a426-35b147f0955f</t>
         </is>
       </c>
     </row>
@@ -3168,15 +3168,15 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>กรมบังคับคดี</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1605</v>
+        <v>2102</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างตรวจสอบเครื่องคอมพิวเตอร์ให้พร้อมใช้งานและบริการประชาชน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดอัตโนมัติ พร้อมตู้ตั้งพื้นจอแสดงผล และระบบสัญญาณเตือน จำนวน 39 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาล ในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (จอแสดงผล, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=590bcfa8-9d1a-43f4-b6c0-1d332cdf98ac</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f7659e63-27b4-4348-9cb8-c0e5ed5164a0</t>
         </is>
       </c>
     </row>
@@ -3203,15 +3203,15 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>กรมศิลปากร</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1804</v>
+        <v>2102</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการดูแลบำรุงรักษาเครื่องปรับอากาศ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องอุ่นเลือดและส่วนประกอบของเลือดชนิดไม่สัมผัสน้ำสามารถอุ่นเลือดได้ พร้อมกันไม่น้อยกว่า 3 ถุง ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 4 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=560aab6a-379c-4e73-a426-35b147f0955f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dc9795b5-9883-4a59-bee5-16ba72ecd5c6</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดอัตโนมัติ พร้อมตู้ตั้งพื้นจอแสดงผล และระบบสัญญาณเตือน จำนวน 39 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาล ในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเตียงผู้ป่วยชนิดสามไกร์ราวปีกนก พร้อมเบาะเสาน้ำเกลือตู้ข้างเตียงและถาดคร่อมเตียง ของโรงพยาบาลส่งเสริมสุขภาพตำบล 25 แห่ง จำนวน 25 เตียง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3256,12 +3256,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>★ (จอแสดงผล, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f7659e63-27b4-4348-9cb8-c0e5ed5164a0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=43094cdc-968c-43e9-b0e7-915d25aa8621</t>
         </is>
       </c>
     </row>
@@ -3273,15 +3273,15 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2102</v>
+        <v>2107</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องอุ่นเลือดและส่วนประกอบของเลือดชนิดไม่สัมผัสน้ำสามารถอุ่นเลือดได้ พร้อมกันไม่น้อยกว่า 3 ถุง ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 4 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dc9795b5-9883-4a59-bee5-16ba72ecd5c6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63c3a055-9106-4358-9ed6-5bf60d1e158c</t>
         </is>
       </c>
     </row>
@@ -3308,15 +3308,15 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2102</v>
+        <v>2113</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเตียงผู้ป่วยชนิดสามไกร์ราวปีกนก พร้อมเบาะเสาน้ำเกลือตู้ข้างเตียงและถาดคร่อมเตียง ของโรงพยาบาลส่งเสริมสุขภาพตำบล 25 แห่ง จำนวน 25 เตียง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและวิเคราะห์ระบบเก็บข้อมูลจราจรคอมพิวเตอร์ขั้นสูง (CSOC) สำนักงานหลักประกันสุขภาพแห่งชาติ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3326,32 +3326,32 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=43094cdc-968c-43e9-b0e7-915d25aa8621</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=516788e1-5adb-46f1-b0bc-48d9b91e8cd8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>กรมสนับสนุนบริการสุขภาพ</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2107</v>
+        <v>204</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ และอุปกรณ์ประกอบเครื่องคอมพิวเตอร์ เพื่อทดแทน และพัฒนาระบบเทคโนโลยีสารสนเทศหน่วยบัญชาการป้องกันภัยทางอากาศ (นปอ.) จำนวน ๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3361,32 +3361,32 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63c3a055-9106-4358-9ed6-5bf60d1e158c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8603566b-8b32-470f-b070-76bf84fb86b4</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2113</v>
+        <v>204</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและวิเคราะห์ระบบเก็บข้อมูลจราจรคอมพิวเตอร์ขั้นสูง (CSOC) สำนักงานหลักประกันสุขภาพแห่งชาติ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างงานติดตั้งเครื่องปรับอากาศ ประจำอาคารหอประชุม หมายเลข ๙๖/๒๓ ของ โรงพยาบาลอานันทมหิดล จังหวัดลพบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=516788e1-5adb-46f1-b0bc-48d9b91e8cd8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=97d16ed9-2390-479b-8218-55472ad15ea3</t>
         </is>
       </c>
     </row>
@@ -3413,15 +3413,15 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กรมชลประทาน</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>204</v>
+        <v>703</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ และอุปกรณ์ประกอบเครื่องคอมพิวเตอร์ เพื่อทดแทน และพัฒนาระบบเทคโนโลยีสารสนเทศหน่วยบัญชาการป้องกันภัยทางอากาศ (นปอ.) จำนวน ๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องสูบน้ำแบบจุ่มใช้มอเตอร์ไฟฟ้า และอื่นๆรวม 3 รายการ สำหรับงานปรับปรุงอาคารบังคับน้ำคลองทิวา-ต้นนา โครงการส่งน้ำและบำรุงรักษาบางพลวง ตำบลพนมสารคาม อำเภอพนมสารคาม จังหวัดฉะเชิงเทรา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8603566b-8b32-470f-b070-76bf84fb86b4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=641eb398-88f6-4784-9733-866ddfdb5ea8</t>
         </is>
       </c>
     </row>
@@ -3448,15 +3448,15 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>204</v>
+        <v>704</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างงานติดตั้งเครื่องปรับอากาศ ประจำอาคารหอประชุม หมายเลข ๙๖/๒๓ ของ โรงพยาบาลอานันทมหิดล จังหวัดลพบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์เครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล  จำนวน 12 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=97d16ed9-2390-479b-8218-55472ad15ea3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cae8cfd5-0a33-48de-bb0d-dd1597263622</t>
         </is>
       </c>
     </row>
@@ -3483,15 +3483,15 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>กรมชลประทาน</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องสูบน้ำแบบจุ่มใช้มอเตอร์ไฟฟ้า และอื่นๆรวม 3 รายการ สำหรับงานปรับปรุงอาคารบังคับน้ำคลองทิวา-ต้นนา โครงการส่งน้ำและบำรุงรักษาบางพลวง ตำบลพนมสารคาม อำเภอพนมสารคาม จังหวัดฉะเชิงเทรา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล)  ขนาด ๑ ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า ๒,๔๐๐ ซีซี  หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า ๑๑๐ กิโลวัตต์ ขับเคลื่อน 4 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน ๑ คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=641eb398-88f6-4784-9733-866ddfdb5ea8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=23493925-5f1a-442c-a9ec-afccbc470e45</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์เครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล  จำนวน 12 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อเครื่องคอมพิวเตอร์ และเครื่องคอมพิวเตอร์โน้ตบุ๊ก จำนวน 2 รายการ ของสำนักงานตรวจบัญชีสหกรณ์ชลบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cae8cfd5-0a33-48de-bb0d-dd1597263622</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=07006c6c-edf5-4030-b6c9-1078334342be</t>
         </is>
       </c>
     </row>
@@ -3553,15 +3553,15 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>704</v>
+        <v>806</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล)  ขนาด ๑ ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า ๒,๔๐๐ ซีซี  หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า ๑๑๐ กิโลวัตต์ ขับเคลื่อน 4 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน ๑ คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าโครงการเช่าเครื่องพิมพ์ 4 สี เพื่อการพิมพ์เอกสารแจ้งผู้ขับขี่เพื่อการเปรียบเทียบปรับตามกฎหมาย ของ กองบังคับการตำรวจทางหลวง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3571,12 +3571,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=23493925-5f1a-442c-a9ec-afccbc470e45</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3fdfa461-5479-46d3-90bc-5b8725bde7b5</t>
         </is>
       </c>
     </row>
@@ -3588,15 +3588,15 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>สำนักงานปลัดกระทรวงแรงงาน</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>704</v>
+        <v>1702</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อเครื่องคอมพิวเตอร์ และเครื่องคอมพิวเตอร์โน้ตบุ๊ก จำนวน 2 รายการ ของสำนักงานตรวจบัญชีสหกรณ์ชลบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดหาครุภัณฑ์คอมพิวเตอร์เพื่อทดแทนและเพิ่มประสิทธิภาพให้หน่วยงานในสังกัดสำนักงานปลัดกระทรวงแรงงาน ปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=07006c6c-edf5-4030-b6c9-1078334342be</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=eea981aa-edb1-4fdf-8067-e5fb7c92e854</t>
         </is>
       </c>
     </row>
@@ -3623,15 +3623,15 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามการทุจริตในภาครัฐ</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>806</v>
+        <v>2517</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าโครงการเช่าเครื่องพิมพ์ 4 สี เพื่อการพิมพ์เอกสารแจ้งผู้ขับขี่เพื่อการเปรียบเทียบปรับตามกฎหมาย ของ กองบังคับการตำรวจทางหลวง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาเครื่องคอมพิวเตอร์แม่ข่าย และระบบความปลอดภัยทางไซเบอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>★ (เครื่องพิมพ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3fdfa461-5479-46d3-90bc-5b8725bde7b5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=39110c90-d236-47eb-913a-cb6b3cab18ba</t>
         </is>
       </c>
     </row>
@@ -3658,15 +3658,15 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงแรงงาน</t>
+          <t>สำนักงานการตรวจเงินแผ่นดิน</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1702</v>
+        <v>2606</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดหาครุภัณฑ์คอมพิวเตอร์เพื่อทดแทนและเพิ่มประสิทธิภาพให้หน่วยงานในสังกัดสำนักงานปลัดกระทรวงแรงงาน ปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างเหมาบริการขนย้ายเครื่องแม่ข่าย และอุปกรณ์พร้อมติดตั้ง ณ ศูนย์ข้อมูลหลัก ของสำนักงานการตรวจเงินแผ่นดิน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (เครื่องแม่ข่าย)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=eea981aa-edb1-4fdf-8067-e5fb7c92e854</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a89ffef4-4bf7-41f2-83ef-2e02a1a4e80c</t>
         </is>
       </c>
     </row>
@@ -3693,15 +3693,15 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามการทุจริตในภาครัฐ</t>
+          <t>สำนักงานปลัดกระทรวงการอุดมศึกษา วิทยาศาสตร์ วิจัยและนวัตกรรม</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2517</v>
+        <v>23002</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการบำรุงรักษาเครื่องคอมพิวเตอร์แม่ข่าย และระบบความปลอดภัยทางไซเบอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างเหมาบริการบำรุงรักษาเครื่องปรับอากาศ แบบรวมอะไหล่ จำนวน 606 เครื่อง ภายในอาคารอุดมศึกษา 1 อาคารอุดมศึกษา 2 อาคารพระจอมเกล้า และอาคารอเนกประสงค์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3711,32 +3711,32 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=39110c90-d236-47eb-913a-cb6b3cab18ba</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4ed51246-9d93-42ff-bb32-e9acb8e03644</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>สำนักงานการตรวจเงินแผ่นดิน</t>
+          <t>สำนักงานบริหารและพัฒนาองค์ความรู้ (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2606</v>
+        <v>125</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างเหมาบริการขนย้ายเครื่องแม่ข่าย และอุปกรณ์พร้อมติดตั้ง ณ ศูนย์ข้อมูลหลัก ของสำนักงานการตรวจเงินแผ่นดิน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3746,32 +3746,32 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>★ (เครื่องแม่ข่าย)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a89ffef4-4bf7-41f2-83ef-2e02a1a4e80c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=22d2e215-7492-48e1-8b48-52ebf11afb3d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการอุดมศึกษา วิทยาศาสตร์ วิจัยและนวัตกรรม</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>23002</v>
+        <v>204</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างเหมาบริการบำรุงรักษาเครื่องปรับอากาศ แบบรวมอะไหล่ จำนวน 606 เครื่อง ภายในอาคารอุดมศึกษา 1 อาคารอุดมศึกษา 2 อาคารพระจอมเกล้า และอาคารอเนกประสงค์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ พร้อมอุปกรณ์ จำนวน ๘๐ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4ed51246-9d93-42ff-bb32-e9acb8e03644</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ed207e86-fa08-4bf6-b096-f66e9ea91205</t>
         </is>
       </c>
     </row>
@@ -3798,15 +3798,15 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>สำนักงานบริหารและพัฒนาองค์ความรู้ (องค์การมหาชน)</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>125</v>
+        <v>204</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อสป.สาย ส. ตามโครงการจัดหาอุปกรณ์คอมพิวเตอร์ เพื่อสนับสนุนงานออกแบบสถาปัตยกรรม วิศวกรรมและงานประมาณราคา (ยย.ทบ.) จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=22d2e215-7492-48e1-8b48-52ebf11afb3d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a5d0fbe1-af34-494f-b408-da6f60a04c26</t>
         </is>
       </c>
     </row>
@@ -3833,15 +3833,15 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กรมธนารักษ์</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>204</v>
+        <v>303</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ พร้อมอุปกรณ์ จำนวน ๘๐ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์อาคารเก็บพัสดุสำนักงานธนารักษ์พื้นที่ชลบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ed207e86-fa08-4bf6-b096-f66e9ea91205</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=606b64be-13e1-468a-84bd-c7c5b46221da</t>
         </is>
       </c>
     </row>
@@ -3868,15 +3868,15 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>204</v>
+        <v>402</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อสป.สาย ส. ตามโครงการจัดหาอุปกรณ์คอมพิวเตอร์ เพื่อสนับสนุนงานออกแบบสถาปัตยกรรม วิศวกรรมและงานประมาณราคา (ยย.ทบ.) จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาดูแล บำรุงรักษา และล้างทำความสะอาดระบบเครื่องปรับอากาศ ณ อาคารกระทรวงการต่างประเทศ ถนนศรีอยุธยา และศูนย์ราชการเฉลิมพระเกียรติฯ อาคาร B ชั้น 7 - 8 รวม 2 แห่ง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a5d0fbe1-af34-494f-b408-da6f60a04c26</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4c0225b9-4c8b-4bbd-80d4-d42eccd0092e</t>
         </is>
       </c>
     </row>
@@ -3903,15 +3903,15 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>กรมธนารักษ์</t>
+          <t>กรมกิจการเด็กและเยาวชน</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>303</v>
+        <v>605</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์อาคารเก็บพัสดุสำนักงานธนารักษ์พื้นที่ชลบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาเครื่องคอมพิวเตอร์ อุปกรณ์ต่อพ่วง และระบบสารสนเทศ ของ ดย. ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=606b64be-13e1-468a-84bd-c7c5b46221da</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cb192597-9852-49f1-81d0-f9bd008c7f6d</t>
         </is>
       </c>
     </row>
@@ -3938,15 +3938,15 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>402</v>
+        <v>704</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาดูแล บำรุงรักษา และล้างทำความสะอาดระบบเครื่องปรับอากาศ ณ อาคารกระทรวงการต่างประเทศ ถนนศรีอยุธยา และศูนย์ราชการเฉลิมพระเกียรติฯ อาคาร B ชั้น 7 - 8 รวม 2 แห่ง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อครุภัณฑ์ยานพาหนะและขนส่งรถโดยสารขนาด 12 ที่นั่ง (ดีเซล) จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4c0225b9-4c8b-4bbd-80d4-d42eccd0092e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3d257d5-116f-4d11-9cba-b2af7ffd9693</t>
         </is>
       </c>
     </row>
@@ -3973,15 +3973,15 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>กรมกิจการเด็กและเยาวชน</t>
+          <t>กรมประมง</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>605</v>
+        <v>705</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาเครื่องคอมพิวเตอร์ อุปกรณ์ต่อพ่วง และระบบสารสนเทศ ของ ดย. ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างการจัดจ้างบำรุงรักษาครุภัณฑ์คอมพิวเตอร์สำหรับการรักษาความปลอดภัยของระบบเครือข่ายและคอมพิวเตอร์ จำนวน 1 งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cb192597-9852-49f1-81d0-f9bd008c7f6d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=29210ba8-e1c2-4d7e-80d4-6acfeb801f71</t>
         </is>
       </c>
     </row>
@@ -4008,15 +4008,15 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมประมง</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อครุภัณฑ์ยานพาหนะและขนส่งรถโดยสารขนาด 12 ที่นั่ง (ดีเซล) จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างการจัดจ้างบำรุงรักษาอุปกรณ์กระจายสัญญาณ จำนวน ๑ งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3d257d5-116f-4d11-9cba-b2af7ffd9693</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b2bbd6f5-c7a5-4bc3-be9e-fc1ddf4ac0a8</t>
         </is>
       </c>
     </row>
@@ -4043,15 +4043,15 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>กรมประมง</t>
+          <t>สำนักงานมาตรฐานสินค้าเกษตรและอาหารแห่งชาติ</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>705</v>
+        <v>714</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างการจัดจ้างบำรุงรักษาครุภัณฑ์คอมพิวเตอร์สำหรับการรักษาความปลอดภัยของระบบเครือข่ายและคอมพิวเตอร์ จำนวน 1 งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการจ้างเหมาดูแลและบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์และระบบคอมพิวเตอร์พร้อมอุปกรณ์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4061,12 +4061,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=29210ba8-e1c2-4d7e-80d4-6acfeb801f71</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d133e360-c57e-4330-bff5-2f10cf027da9</t>
         </is>
       </c>
     </row>
@@ -4078,15 +4078,15 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>กรมประมง</t>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>705</v>
+        <v>1302</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างการจัดจ้างบำรุงรักษาอุปกรณ์กระจายสัญญาณ จำนวน ๑ งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องคอมพิวเตอร์และอุปกรณ์ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b2bbd6f5-c7a5-4bc3-be9e-fc1ddf4ac0a8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=04549f6b-e678-4005-91df-2993ee4bdb83</t>
         </is>
       </c>
     </row>
@@ -4113,15 +4113,15 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>สำนักงานมาตรฐานสินค้าเกษตรและอาหารแห่งชาติ</t>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>714</v>
+        <v>1302</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการจ้างเหมาดูแลและบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์และระบบคอมพิวเตอร์พร้อมอุปกรณ์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่ายของสำนักงานพาณิชย์จังหวัด 76 จังหวัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d133e360-c57e-4330-bff5-2f10cf027da9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f1e51f04-f935-4983-8200-42b44f480fc9</t>
         </is>
       </c>
     </row>
@@ -4148,15 +4148,15 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+          <t>สถาบันส่งเสริมศิลปหัตถกรรมไทย (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1302</v>
+        <v>1311</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องคอมพิวเตอร์และอุปกรณ์ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการจัดหาพนักงานดูแลหอนิทรรศการและห้องสมุด ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (สมุด)</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=04549f6b-e678-4005-91df-2993ee4bdb83</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ff1d2fa-ba06-4da0-bc6c-023504d3c9d6</t>
         </is>
       </c>
     </row>
@@ -4183,15 +4183,15 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1302</v>
+        <v>1808</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่ายของสำนักงานพาณิชย์จังหวัด 76 จังหวัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์อื่นๆ (เครื่องแต่งกายโขน-ละคร) จำนวน 7 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f1e51f04-f935-4983-8200-42b44f480fc9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8e14fee9-d40a-4d5f-b4ec-b5dd1cbdcc29</t>
         </is>
       </c>
     </row>
@@ -4218,15 +4218,15 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>สถาบันส่งเสริมศิลปหัตถกรรมไทย (องค์การมหาชน)</t>
+          <t>กรมส่งเสริมการเรียนรู้</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1311</v>
+        <v>2033</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการจัดหาพนักงานดูแลหอนิทรรศการและห้องสมุด ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>★ (สมุด)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ff1d2fa-ba06-4da0-bc6c-023504d3c9d6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=988b1f6a-eb89-4ed1-bbe5-4e82ba43054b</t>
         </is>
       </c>
     </row>
@@ -4253,15 +4253,15 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1808</v>
+        <v>2102</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์อื่นๆ (เครื่องแต่งกายโขน-ละคร) จำนวน 7 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการตู้เย็นเก็บเลือดขนาดไม่น้อยกว่า 20 คิว ของโรงพยาบาลในจังหวัดสุรินทร์ 6 แห่ง จำนวน 7 ตู้ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์, ตู้เย็น)</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8e14fee9-d40a-4d5f-b4ec-b5dd1cbdcc29</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dfce18c4-7835-4a43-8ba6-fb9a2b9ab472</t>
         </is>
       </c>
     </row>
@@ -4288,15 +4288,15 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเรียนรู้</t>
+          <t>กรมอนามัย</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2033</v>
+        <v>2109</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่าย กรมอนามัย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=988b1f6a-eb89-4ed1-bbe5-4e82ba43054b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0f1ebcb1-8a09-4209-922e-0e2e49160cba</t>
         </is>
       </c>
     </row>
@@ -4323,15 +4323,15 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2102</v>
+        <v>2113</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการตู้เย็นเก็บเลือดขนาดไม่น้อยกว่า 20 คิว ของโรงพยาบาลในจังหวัดสุรินทร์ 6 แห่ง จำนวน 7 ตู้ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์แม่ข่าย (Outsource System) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์, ตู้เย็น)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dfce18c4-7835-4a43-8ba6-fb9a2b9ab472</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1c3629ca-59d6-4b8a-839b-92b06d6a1c43</t>
         </is>
       </c>
     </row>
@@ -4358,15 +4358,15 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>กรมอนามัย</t>
+          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2109</v>
+        <v>2113</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่าย กรมอนามัย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์เครือข่าย (Outsource Network) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4381,27 +4381,27 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0f1ebcb1-8a09-4209-922e-0e2e49160cba</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b44df475-19c0-4304-b42e-0c379f2f6a07</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+          <t>กองทัพอากาศ</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>2113</v>
+        <v>206</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์แม่ข่าย (Outsource System) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโต๊ะและเก้าอี้ประชุม จำนวน ๒ รายการ (แจ้งที่ ๘๙๖/๖๙) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4411,32 +4411,32 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (โต๊ะ, เก้าอี้)</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1c3629ca-59d6-4b8a-839b-92b06d6a1c43</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c197cbba-6119-4a85-8655-64df092381b8</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+          <t>กรมศุลกากร</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>2113</v>
+        <v>305</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์เครือข่าย (Outsource Network) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องปรับอากาศ แบบฝังฝ้าสี่ทิศทาง (ระบบ Inverter) ขนาด 48,000 บีทียู ด่านศุลกากรปาดังเบซาร์ ตำบลปาดังเบซาร์ อำเภอสะเดา จังหวัดสงขลา 12 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b44df475-19c0-4304-b42e-0c379f2f6a07</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7ffdc802-88d9-422f-a01b-27711177cb61</t>
         </is>
       </c>
     </row>
@@ -4463,15 +4463,15 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>กองทัพอากาศ</t>
+          <t>กรมสรรพากร</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>206</v>
+        <v>307</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโต๊ะและเก้าอี้ประชุม จำนวน ๒ รายการ (แจ้งที่ ๘๙๖/๖๙) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบ ไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 2,400 ซีซี  หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ จำนวน 5 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>★ (โต๊ะ, เก้าอี้)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c197cbba-6119-4a85-8655-64df092381b8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e642705c-f34c-41db-ad86-705717edf0ea</t>
         </is>
       </c>
     </row>
@@ -4498,15 +4498,15 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>กรมศุลกากร</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>305</v>
+        <v>704</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องปรับอากาศ แบบฝังฝ้าสี่ทิศทาง (ระบบ Inverter) ขนาด 48,000 บีทียู ด่านศุลกากรปาดังเบซาร์ ตำบลปาดังเบซาร์ อำเภอสะเดา จังหวัดสงขลา 12 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7ffdc802-88d9-422f-a01b-27711177cb61</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5b0cc17-68bd-4696-805e-f78e075178e3</t>
         </is>
       </c>
     </row>
@@ -4533,15 +4533,15 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>กรมสรรพากร</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>307</v>
+        <v>704</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบ ไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 2,400 ซีซี  หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ จำนวน 5 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุด ไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e642705c-f34c-41db-ad86-705717edf0ea</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=106210e4-0233-403f-957c-c894b083d53b</t>
         </is>
       </c>
     </row>
@@ -4568,15 +4568,15 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมส่งเสริมการเกษตร</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดชื้อครุภัณฑ์ยานพาหนะและขนส่ง ประจำปีงบประมาณ พ.ศ 2570 โดยวิธีประกวดอิเล็กทรอนิกส์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4586,12 +4586,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5b0cc17-68bd-4696-805e-f78e075178e3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ec4d9c1c-1aa5-4b14-b3ea-60845e7335fb</t>
         </is>
       </c>
     </row>
@@ -4603,15 +4603,15 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมส่งเสริมสหกรณ์</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุด ไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาบรรทุกขนาด 1 ตัน หลังคาไฟเบอร์กลาส หรือเหล็กหรือพลาสติกวิศวกรรม สำนักงานสหกรณ์จังหวัดศรีสะเกษ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=106210e4-0233-403f-957c-c894b083d53b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=51b057ec-ffcf-432e-bf86-fe4029225a82</t>
         </is>
       </c>
     </row>
@@ -4638,15 +4638,15 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเกษตร</t>
+          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>711</v>
+        <v>1202</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดชื้อครุภัณฑ์ยานพาหนะและขนส่ง ประจำปีงบประมาณ พ.ศ 2570 โดยวิธีประกวดอิเล็กทรอนิกส์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่ารถส่วนภูมิภาค รถยนต์ไฟฟ้า ประเภทแบตเตอรี่ (BEV) ขนาดความจุของแบตเตอรี่มากกว่า 50 กิโลวัตต์ชั่วโมง (kWh) และกำลังมอเตอร์ไฟฟ้าสูงสุด ไม่เกิน 150 กิโลวัตต์ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ec4d9c1c-1aa5-4b14-b3ea-60845e7335fb</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=490958cc-932a-45a1-8497-c33d7a13f8c6</t>
         </is>
       </c>
     </row>
@@ -4673,15 +4673,15 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมสหกรณ์</t>
+          <t>กรมพัฒนาธุรกิจการค้า</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>712</v>
+        <v>1308</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาบรรทุกขนาด 1 ตัน หลังคาไฟเบอร์กลาส หรือเหล็กหรือพลาสติกวิศวกรรม สำนักงานสหกรณ์จังหวัดศรีสะเกษ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องคอมพิวเตอร์ลูกข่ายและอุปกรณ์ต่อพ่วง ปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=51b057ec-ffcf-432e-bf86-fe4029225a82</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=be5cf0cb-614f-4d37-aac0-190b90321cb6</t>
         </is>
       </c>
     </row>
@@ -4708,15 +4708,15 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
+          <t>กรมโยธาธิการและผังเมือง</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1202</v>
+        <v>1507</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่ารถส่วนภูมิภาค รถยนต์ไฟฟ้า ประเภทแบตเตอรี่ (BEV) ขนาดความจุของแบตเตอรี่มากกว่า 50 กิโลวัตต์ชั่วโมง (kWh) และกำลังมอเตอร์ไฟฟ้าสูงสุด ไม่เกิน 150 กิโลวัตต์ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างโครงการจัดหาสิ่งก่อสร้างและครุภัณฑ์ประกอบ อาคารสำนักงานแห่งใหม่ของสำนักงบประมาณ แขวงพญาไท เขตพญาไท กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=490958cc-932a-45a1-8497-c33d7a13f8c6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8b31f2b3-f6fd-4e5c-979f-8575feda4bbf</t>
         </is>
       </c>
     </row>
@@ -4743,15 +4743,15 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>กรมพัฒนาธุรกิจการค้า</t>
+          <t>กรมการศาสนา</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1308</v>
+        <v>1803</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องคอมพิวเตอร์ลูกข่ายและอุปกรณ์ต่อพ่วง ปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อวัสดุสำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (วัสดุสำนักงาน)</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=be5cf0cb-614f-4d37-aac0-190b90321cb6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=07f7d716-619d-4e73-9518-7f683a4a05ed</t>
         </is>
       </c>
     </row>
@@ -4778,15 +4778,15 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>กรมโยธาธิการและผังเมือง</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1507</v>
+        <v>2102</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างโครงการจัดหาสิ่งก่อสร้างและครุภัณฑ์ประกอบ อาคารสำนักงานแห่งใหม่ของสำนักงบประมาณ แขวงพญาไท เขตพญาไท กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการชุดกระเป๋าปฐมพยาบาลสนามประจำตัวเจ้าหน้าที่ (IFAK) ของโรงพยาบาลชุมชน 11 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบล 40 แห่ง จำนวน 117 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8b31f2b3-f6fd-4e5c-979f-8575feda4bbf</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=197d72c1-0e0f-4f3d-a377-6f7e052fd668</t>
         </is>
       </c>
     </row>
@@ -4813,15 +4813,15 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>กรมการศาสนา</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1803</v>
+        <v>2102</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อวัสดุสำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>★ (วัสดุสำนักงาน)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=07f7d716-619d-4e73-9518-7f683a4a05ed</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a903de26-6f92-4b12-bcdc-87924b3b825b</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการชุดกระเป๋าปฐมพยาบาลสนามประจำตัวเจ้าหน้าที่ (IFAK) ของโรงพยาบาลชุมชน 11 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบล 40 แห่ง จำนวน 117 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อสิทธิ์ใช้งานซอฟต์แวร์จัดการความเสี่ยงเกี่ยวกับระบบสารสนเทศ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=197d72c1-0e0f-4f3d-a377-6f7e052fd668</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f182625c-e015-489e-84e0-ac3c9c8dc788</t>
         </is>
       </c>
     </row>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ กล้องถ่ายภาพจอประสาทตาดิจิตอล (Digital Fundus Camera) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a903de26-6f92-4b12-bcdc-87924b3b825b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=810bd451-770f-4032-86a0-1216954db79a</t>
         </is>
       </c>
     </row>
@@ -4918,15 +4918,15 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สำนักงานคณะกรรมการอาหารและยา</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>2102</v>
+        <v>2110</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อสิทธิ์ใช้งานซอฟต์แวร์จัดการความเสี่ยงเกี่ยวกับระบบสารสนเทศ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>★ (ซอฟต์แวร์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f182625c-e015-489e-84e0-ac3c9c8dc788</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=69d9687c-b7f1-405c-843e-92b98ad29261</t>
         </is>
       </c>
     </row>
@@ -4953,15 +4953,15 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>2102</v>
+        <v>2117</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ กล้องถ่ายภาพจอประสาทตาดิจิตอล (Digital Fundus Camera) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อติดตั้งระบบกล้องวงจรปิด ของวิทยาลัยพยาบาลบรมราชชนนี นครศรีธรรมราช จำนวน 1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4971,32 +4971,32 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (กล้องวงจรปิด)</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=810bd451-770f-4032-86a0-1216954db79a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afa9b388-be98-4ed1-8fa9-0c791e5acf34</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการอาหารและยา</t>
+          <t>กรมธนารักษ์</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>2110</v>
+        <v>303</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการทำความสะอาดศูนย์คอมพิวเตอร์แห่งใหม่ ของกรมธนารักษ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5011,27 +5011,27 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=69d9687c-b7f1-405c-843e-92b98ad29261</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=36f30dd7-0674-4711-a8ba-e71eee8e8ed2</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>สำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>2117</v>
+        <v>502</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อติดตั้งระบบกล้องวงจรปิด ของวิทยาลัยพยาบาลบรมราชชนนี นครศรีธรรมราช จำนวน 1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการค่าใช้จ่ายโครงการค่าจ้างบำรุงรักษาและซ่อมแซมห้องปฏิบัติการระบบเครือข่ายคอมพิวเตอร์ (Data Center) ของสำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>★ (กล้องวงจรปิด)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afa9b388-be98-4ed1-8fa9-0c791e5acf34</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=056989d3-d491-44ed-b887-fca9a5a8f472</t>
         </is>
       </c>
     </row>
@@ -5058,17 +5058,15 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>กรมธนารักษ์</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
+          <t>กรมส่งเสริมและพัฒนาคุณภาพชีวิตคนพิการ</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>607</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการทำความสะอาดศูนย์คอมพิวเตอร์แห่งใหม่ ของกรมธนารักษ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์งานบ้านงานครัวและครุภัณฑ์สำนักงาน จำนวน ๒๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5078,12 +5076,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=36f30dd7-0674-4711-a8ba-e71eee8e8ed2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f387eaf-54e2-4cf6-8c1c-826da6e3d09e</t>
         </is>
       </c>
     </row>
@@ -5095,17 +5093,15 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>0502</t>
-        </is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>704</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการค่าใช้จ่ายโครงการค่าจ้างบำรุงรักษาและซ่อมแซมห้องปฏิบัติการระบบเครือข่ายคอมพิวเตอร์ (Data Center) ของสำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี. หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บพร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -5115,12 +5111,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=056989d3-d491-44ed-b887-fca9a5a8f472</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b694aef3-f630-4422-a7fe-e31adb551c45</t>
         </is>
       </c>
     </row>
@@ -5132,17 +5128,15 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมและพัฒนาคุณภาพชีวิตคนพิการ</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>0607</t>
-        </is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>704</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์งานบ้านงานครัวและครุภัณฑ์สำนักงาน จำนวน ๒๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องปรับอากาศแบบแยกส่วน (ราคารวมค่าติดตั้ง) แบบตั้งพื้นหรือแบบแขวน(ระบบ Inverter) ขนาดไม่ต่ำกว่า 36,000 บีทียู จำนวน 13 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5152,12 +5146,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f387eaf-54e2-4cf6-8c1c-826da6e3d09e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=08075ad1-9390-4520-9d46-f5c2637228e2</t>
         </is>
       </c>
     </row>
@@ -5169,17 +5163,15 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>0704</t>
-        </is>
+          <t>กรมส่งเสริมสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>712</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี. หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บพร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5194,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b694aef3-f630-4422-a7fe-e31adb551c45</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=282d8226-b5a6-422f-ad5a-96682acbb042</t>
         </is>
       </c>
     </row>
@@ -5206,17 +5198,15 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>0704</t>
-        </is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>806</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องปรับอากาศแบบแยกส่วน (ราคารวมค่าติดตั้ง) แบบตั้งพื้นหรือแบบแขวน(ระบบ Inverter) ขนาดไม่ต่ำกว่า 36,000 บีทียู จำนวน 13 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องตรวจวัดปริมาณแอลกอฮอล์ จำนวน 10 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5226,12 +5216,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (แอลกอฮอล์)</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=08075ad1-9390-4520-9d46-f5c2637228e2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=152668c9-b054-48b8-9423-57975423ef48</t>
         </is>
       </c>
     </row>
@@ -5243,17 +5233,15 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมสหกรณ์</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>0712</t>
-        </is>
+          <t>กรมการเปลี่ยนแปลงสภาพภูมิอากาศและสิ่งแวดล้อม</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>908</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาอุปกรณ์ห้อง Data center และเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5263,12 +5251,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=282d8226-b5a6-422f-ad5a-96682acbb042</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3fa0cd84-f2db-47df-b581-c3555885f305</t>
         </is>
       </c>
     </row>
@@ -5280,17 +5268,15 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>0806</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>1202</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องตรวจวัดปริมาณแอลกอฮอล์ จำนวน 10 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์เครือข่ายและอุปกรณ์คอมพิวเตอร์แม่ข่าย และอุปกรณ์สำรองข้อมูล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5300,12 +5286,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>★ (แอลกอฮอล์)</t>
+          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=152668c9-b054-48b8-9423-57975423ef48</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=86fe9b9f-c1ba-4f83-8b12-70dbc5d76baa</t>
         </is>
       </c>
     </row>
@@ -5317,17 +5303,15 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>กรมการเปลี่ยนแปลงสภาพภูมิอากาศและสิ่งแวดล้อม</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>0908</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>1302</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาอุปกรณ์ห้อง Data center และเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์สำหรับงานจดทะเบียนและตรวจสอบธุรกิจผิดกฎหมาย กลุ่มทะเบียนธุรกิจและอำนวยความสะดวกทางการค้าของสำนักงานพาณิชย์จังหวัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5337,12 +5321,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3fa0cd84-f2db-47df-b581-c3555885f305</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=06246921-2a22-4f4d-822b-d5abae1c7c8c</t>
         </is>
       </c>
     </row>
@@ -5354,17 +5338,15 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>1202</t>
-        </is>
+          <t>กรมสอบสวนคดีพิเศษ</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>1608</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์เครือข่ายและอุปกรณ์คอมพิวเตอร์แม่ข่าย และอุปกรณ์สำรองข้อมูล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าเช่าใช้บริการสายสัญญาณเชื่อมโยงเครือข่ายอินเตอร์เน็ตพร้อมระบบ Internet Data Center ประจำปีงบประมาณ พ.ศ. 2570 (เดือนตุลาคม 2569  เดือนกันยายน 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5374,12 +5356,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
+          <t>★ (สายสัญญาณ)</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=86fe9b9f-c1ba-4f83-8b12-70dbc5d76baa</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f0c10124-df0c-410d-961c-bb4afe1ea16a</t>
         </is>
       </c>
     </row>
@@ -5391,17 +5373,15 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>1302</t>
-        </is>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>1611</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์สำหรับงานจดทะเบียนและตรวจสอบธุรกิจผิดกฎหมาย กลุ่มทะเบียนธุรกิจและอำนวยความสะดวกทางการค้าของสำนักงานพาณิชย์จังหวัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบประชุมทางไกลผ่านจอภาพ (Video Conference)  ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -5411,12 +5391,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (จอภาพ, ระบบประชุมทางไกล)</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=06246921-2a22-4f4d-822b-d5abae1c7c8c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bb2e1625-bd6e-49b0-bf5e-6f3975c796e5</t>
         </is>
       </c>
     </row>
@@ -5428,17 +5408,15 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>กรมสอบสวนคดีพิเศษ</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>1608</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>2102</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าเช่าใช้บริการสายสัญญาณเชื่อมโยงเครือข่ายอินเตอร์เน็ตพร้อมระบบ Internet Data Center ประจำปีงบประมาณ พ.ศ. 2570 (เดือนตุลาคม 2569  เดือนกันยายน 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันขนาดกลาง โรงพยาบาลเขาย้อย ตำบลเขาย้อย อำเภอเขาย้อย จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5448,12 +5426,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>★ (สายสัญญาณ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f0c10124-df0c-410d-961c-bb4afe1ea16a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4d438ead-6d3b-40c3-8e25-0c855ca2699d</t>
         </is>
       </c>
     </row>
@@ -5465,17 +5443,15 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>1611</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>2102</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบประชุมทางไกลผ่านจอภาพ (Video Conference)  ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง โรงพยาบาลหนองหญ้าปล้อง ตำบลหนองหญ้าปล้อง อำเภอหนองหญ้าปล้อง จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5485,12 +5461,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>★ (จอภาพ, ระบบประชุมทางไกล)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bb2e1625-bd6e-49b0-bf5e-6f3975c796e5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=38179365-12e6-43e5-ac4b-973f7d7d62c9</t>
         </is>
       </c>
     </row>
@@ -5505,14 +5481,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C145" t="n">
+        <v>2102</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันขนาดกลาง โรงพยาบาลเขาย้อย ตำบลเขาย้อย อำเภอเขาย้อย จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดัน ขนาดใหญ่ จำนวน 2 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5527,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4d438ead-6d3b-40c3-8e25-0c855ca2699d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2c8651ab-6342-4cf7-b1d4-44acb01ef167</t>
         </is>
       </c>
     </row>
@@ -5542,14 +5516,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C146" t="n">
+        <v>2102</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง โรงพยาบาลหนองหญ้าปล้อง ตำบลหนองหญ้าปล้อง อำเภอหนองหญ้าปล้อง จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดเล็ก ของโรงพยาบาลชุมชน 2 แห่ง จำนวน 6 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5564,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=38179365-12e6-43e5-ac4b-973f7d7d62c9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=092dea18-169e-423d-bdf4-cbb905df5ef4</t>
         </is>
       </c>
     </row>
@@ -5579,14 +5551,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C147" t="n">
+        <v>2102</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดัน ขนาดใหญ่ จำนวน 2 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องเอกซเรย์เคลื่อนที่ขนาดไม่น้อยกว่า 300 mA.ขับเคลื่อนด้วยมอเตอร์ไฟฟ้า ของโรงพยาบาลในจังหวัดสุรินทร์ 3 แห่ง จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5596,12 +5566,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์, มอเตอร์)</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2c8651ab-6342-4cf7-b1d4-44acb01ef167</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=587ceaac-9b51-4f53-a40b-ba6307295dbc</t>
         </is>
       </c>
     </row>
@@ -5613,17 +5583,15 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+          <t>กรมการแพทย์แผนไทยและการแพทย์ทางเลือก</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>2105</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดเล็ก ของโรงพยาบาลชุมชน 2 แห่ง จำนวน 6 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างบำรุงรักษาและซ่อมแซมแก้ไขปัญหาเครื่องคอมพิวเตอร์แม่ข่ายและอุปกรณ์ระบบเครือข่าย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -5633,12 +5601,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=092dea18-169e-423d-bdf4-cbb905df5ef4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a18ab514-a7bf-42a3-be34-78ab2073afdd</t>
         </is>
       </c>
     </row>
@@ -5650,17 +5618,15 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>2106</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องเอกซเรย์เคลื่อนที่ขนาดไม่น้อยกว่า 300 mA.ขับเคลื่อนด้วยมอเตอร์ไฟฟ้า ของโรงพยาบาลในจังหวัดสุรินทร์ 3 แห่ง จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน ๙ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5670,12 +5636,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์, มอเตอร์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=587ceaac-9b51-4f53-a40b-ba6307295dbc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70e80b61-ece5-4761-bcba-cb1ce4f2a872</t>
         </is>
       </c>
     </row>
@@ -5687,17 +5653,15 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>กรมการแพทย์แผนไทยและการแพทย์ทางเลือก</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>2105</t>
-        </is>
+          <t>สถาบันพระบรมราชชนก</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>2117</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างบำรุงรักษาและซ่อมแซมแก้ไขปัญหาเครื่องคอมพิวเตอร์แม่ข่ายและอุปกรณ์ระบบเครือข่าย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อึครุภัณฑ์สำนักงาน รายการเครื่องปรับอากาศและพัดลม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5707,12 +5671,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ, พัดลม)</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a18ab514-a7bf-42a3-be34-78ab2073afdd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8cf26d57-cf1b-4ebf-8134-fcf45b7f7c54</t>
         </is>
       </c>
     </row>
@@ -5724,17 +5688,15 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>กรมวิทยาศาสตร์การแพทย์</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>2106</t>
-        </is>
+          <t>สถาบันพระบรมราชชนก</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>2117</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน ๙ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง (รถยนต์บรรทุกโดยสาร 6 ล้อ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -5744,34 +5706,34 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70e80b61-ece5-4761-bcba-cb1ce4f2a872</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=37a7653e-4e42-4513-bc7a-c74cd6a83f90</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>สถาบันเทคโนโลยีป้องกันประเทศ</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อึครุภัณฑ์สำนักงาน รายการเครื่องปรับอากาศและพัดลม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างซ่อมบำรุงตามวงรอบเครื่องปรับอากาศ อาคาร สป. (แจ้งวัฒนะ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -5781,34 +5743,34 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ, พัดลม)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8cf26d57-cf1b-4ebf-8134-fcf45b7f7c54</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=97592008-d14e-46f6-93ee-062a71e2e9a9</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>สำนักงานปลัดกระทรวงการคลัง</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>0302</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง (รถยนต์บรรทุกโดยสาร 6 ล้อ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อการจัดซื้อหมึกพิมพ์สำหรับ GFMIS Terminal Set เพื่อใช้งานในระบบ New GFMIS Thai ของกรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5818,12 +5780,604 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
+          <t>★ (หมึกพิมพ์)</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=95f4ee7d-0617-43e5-8099-6f58ee3f83c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>กรมชลประทาน</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>0703</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างจัดหาและติดตั้งเครื่องสูบน้ำชนิดหอยโข่งแบบ Horizontal Split Case ขับด้วยมอเตอร์ไฟฟ้าอัตราสูบน้ำ ๐.๒๕ ลบ.ม. /วินาที ระยะยกน้ำไม่น้อยกว่า ๔๕ เมตร และอื่นๆ รวม ๔ รายการ  สำหรับงานสถานีสูบน้ำด้วยไฟฟ้าพร้อมระบบส่งน้ำ บ้านสุขสำราญ ตำบลเหล่าต่างคำ อำเภอโพนพิสัย จังหวัดหนองคาย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>★ (มอเตอร์)</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=766b91be-9aee-491f-bc67-3378c2319ca0</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>กรมประมง</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>0705</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน 4 รายการ วิธีประกาศเชิญชวน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
           <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=37a7653e-4e42-4513-bc7a-c74cd6a83f90</t>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6af84224-9211-4bd4-b2c3-7790e12e9c3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>กรมประมง</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>0705</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน 4 รายการ  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=106fd353-637b-4b85-b19c-e5222b434807</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>สำนักงานเศรษฐกิจการเกษตร</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>0715</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์หรือระบบสารสนเทศ (โครงการจ้างบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์เครือข่ายและเครื่องคอมพิวเตอร์แม่ข่าย ประจำปีงบประมาณ พ.ศ. 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e3936fb8-2fe4-4ded-a393-134ec5675427</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>กรมการขนส่งทางบก</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>0804</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์พร้อมอุปกรณ์ของระบบการคุ้มครองผู้โดยสารและ การบังคับใช้กฎหมายทั่วไทย (1584 และปรับทั่วไทย) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f5c51a3c-9d4b-4662-a9c5-a560b97ab60f</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>กรมการขนส่งทางบก</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>0804</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างก่อสร้างรั้ว ประตูทางเข้า - ออก ป้ายชื่อสำนักงาน และป้อมยามรักษาการณ์ สำนักงานขนส่งจังหวัดลำปาง ตำบลพระบาท อำเภอเมือง จังหวัดลำปาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>★ (ป้ายชื่อ)</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f104579c-ae74-4bdb-a71c-250b1777b2c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>กรมการขนส่งทางบก</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>0804</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขเครื่องคอมพิวเตอร์พร้อมอุปกรณ์ที่ใช้ในการพัฒนาความรู้สารสนเทศ  ด้านความปลอดภัยของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a8c5a924-f969-4f66-a783-51c748bd5141</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>กรมอุตุนิยมวิทยา</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>1104</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาอุปกรณ์กระจายสัญญาณหลัก (Core Switch) ประจำปีงบประมาณ พ.ศ.2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b6951565-26a5-4131-b672-af48d4974842</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>กรมที่ดิน</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโต๊ะและเก้าอี้เพื่อใช้ในราชการของสำนักงานที่ดินจังหวัดพิษณุโลก และสาขา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>★ (โต๊ะ, เก้าอี้)</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=06a6ae3e-1109-434c-becf-df99302f96f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>กรมที่ดิน</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบงานและอุปกรณ์คอมพิวเตอร์ ตามโครงการพัฒนาระบบสารสนเทศที่ดิน (ระยะที่ ๒) ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0e343fde-5a22-4f02-b2b3-bcf7cfd99bf2</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>1808</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์การศึกษา (ห้องเรียนอัจฉริยะไฮบริด Smart Hybrid Classroom) ห้องเรียนวิชาชีพ จำนวน 1 ห้อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a6ddc2c9-4ad2-4cd7-93c9-2b5e9a715cfd</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>1808</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์โฆษณาแะเผยแพร่ (ระบบภาพ LED Display พร้อมติดตั้งภายนอกอาคาร) จำนวน  1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7b99fd52-1723-486a-a5ce-43a450641ed9</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>สำนักงานนวัตกรรมแห่งชาติ (องค์การมหาชน)</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>1913</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างจ้างเหมาบริการบำรุงรักษาอุปกรณ์ภายในศูนย์ข้อมูลคอมพิวเตอร์(Data Center) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70ea1f2e-64d2-48c7-888f-f39d061663c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5dcaa2f-3e4d-49bc-9324-4c94f510ab5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องควบคุมการให้สารน้ำทางหลอดเลือดดำชนิด 1 สาย ของโรงพยาบาลในจังหวัดสุรินทร์ 9 แห่ง จำนวน 66 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=af446873-e18e-4ed1-bd5c-bd34b74e9b76</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>กรมการแพทย์</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์เครื่องเสริมสร้างความแข็งแรงของกล้ามเนื้ออุ้งเชิงกราน รักษาอาการปัสสาวะเล็ด ลดอาการปวดจากกล้ามเนื้อและระบบประสาทบริเวณ อุ้งเชิงกรานและหลังด้วยคลื่นแม่เหล็กไฟฟ้า สถาบันเวชศาสตร์สมเด็จพระสังฆราชญาณสังวรเพื่อผู้สูงอายุ ตำบลตลาดขวัญ อำเภอเมือง จังหวัดนนทบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=543d641e-2bab-40db-bddc-5b9d81caf16b</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202609.xlsx
+++ b/Backup/eGP_Monthly_Main_202609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G169"/>
+  <dimension ref="A1:G182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5726,10 +5726,8 @@
           <t>สถาบันเทคโนโลยีป้องกันประเทศ</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>0209</t>
-        </is>
+      <c r="C152" t="n">
+        <v>209</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -5763,10 +5761,8 @@
           <t>สำนักงานปลัดกระทรวงการคลัง</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>0302</t>
-        </is>
+      <c r="C153" t="n">
+        <v>302</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -5800,10 +5796,8 @@
           <t>กรมชลประทาน</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>0703</t>
-        </is>
+      <c r="C154" t="n">
+        <v>703</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -5837,10 +5831,8 @@
           <t>กรมประมง</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>0705</t>
-        </is>
+      <c r="C155" t="n">
+        <v>705</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -5874,10 +5866,8 @@
           <t>กรมประมง</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>0705</t>
-        </is>
+      <c r="C156" t="n">
+        <v>705</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -5911,10 +5901,8 @@
           <t>สำนักงานเศรษฐกิจการเกษตร</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>0715</t>
-        </is>
+      <c r="C157" t="n">
+        <v>715</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -5948,10 +5936,8 @@
           <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>0804</t>
-        </is>
+      <c r="C158" t="n">
+        <v>804</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -5985,10 +5971,8 @@
           <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>0804</t>
-        </is>
+      <c r="C159" t="n">
+        <v>804</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -6022,10 +6006,8 @@
           <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>0804</t>
-        </is>
+      <c r="C160" t="n">
+        <v>804</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -6059,10 +6041,8 @@
           <t>กรมอุตุนิยมวิทยา</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>1104</t>
-        </is>
+      <c r="C161" t="n">
+        <v>1104</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -6096,10 +6076,8 @@
           <t>กรมที่ดิน</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
+      <c r="C162" t="n">
+        <v>1505</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -6133,10 +6111,8 @@
           <t>กรมที่ดิน</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
+      <c r="C163" t="n">
+        <v>1505</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -6170,10 +6146,8 @@
           <t>สถาบันบัณฑิตพัฒนศิลป์</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>1808</t>
-        </is>
+      <c r="C164" t="n">
+        <v>1808</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -6207,10 +6181,8 @@
           <t>สถาบันบัณฑิตพัฒนศิลป์</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>1808</t>
-        </is>
+      <c r="C165" t="n">
+        <v>1808</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -6244,10 +6216,8 @@
           <t>สำนักงานนวัตกรรมแห่งชาติ (องค์การมหาชน)</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>1913</t>
-        </is>
+      <c r="C166" t="n">
+        <v>1913</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -6281,10 +6251,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C167" t="n">
+        <v>2102</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -6318,10 +6286,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C168" t="n">
+        <v>2102</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -6355,10 +6321,8 @@
           <t>กรมการแพทย์</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>2103</t>
-        </is>
+      <c r="C169" t="n">
+        <v>2103</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -6378,6 +6342,487 @@
       <c r="G169" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=543d641e-2bab-40db-bddc-5b9d81caf16b</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>กองทัพบก</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>0204</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำหรับงานซ่อมปรับปรุงสนามกีฬาของ หน่วยบัญชาการสงครามพิเศษ เพื่อรองรับการแข่งขันกีฬา กองทัพบก ครั้งที่ 74 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=91712891-37fd-4bbc-ae6c-0044106ce3a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>0704</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะ รถโดยสารขนาด 12 ที่นั่ง (ดีเซล) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6d9307c6-812c-4689-9154-bd79b77edeed</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>0704</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องคอมพิวเตอร์โน๊ตบุ๊ค สำหรับงานประมวลผล พร้อมชุดโปรแกรมระบบปฏิบัติการสำหรับคอมพิวเตอร์และเครี่องคอมพิวเตอร์โน๊ตบุ๊ค แบบสิทธิการใช้งานภายในสำนักงาน ประเภทติดตั้งมาจากโรงงาน (OEM) ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย ชุดโปรแกรมจัดการสำนักงาน แบบที่ 2   ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย และชุดโปรแกรมป้องกันไวรัส จำนวน 21 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, โน๊ตบุ๊ค, ระบบปฏิบัติการ, โปรแกรมป้องกันไวรัส)</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ac28390d-f1a5-41e3-8fed-7350ce5638bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>กรมท่าอากาศยาน</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานหัวหิน ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>★ (รถเข็น)</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f40b4d90-5120-4848-a5d2-b177de8a9a09</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>กรมพัฒนาธุรกิจการค้า</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>1308</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์แม่ข่ายและอุปกรณ์รักษาความปลอดภัย ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=652c12bb-908d-48aa-a87c-f244b33e9ad3</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>กรมที่ดิน</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมอุปกรณ์ รวม ๘ รายการ สำหรับใช้ในราชการกองเทคโนโลยีทำแผนที่ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c85d670f-a209-4413-8ade-5dba1d3d0298</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์โครงการห้องปฏิบัติการทดสอบด้านวิศวกรรมการใช้งาน (Usability Engineering) ผลิตภัณฑ์ซอฟต์แวร์หุ่นยนต์ทางการแพทย์และเครื่องมือแพทย์ตามมาตรฐานสากล (Usability Engineering Laboratories for Software, Medical Robotics, and Medical Devices under International Standards) จํานวน ๑ ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>★ (ซอฟต์แวร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0415b5bd-8794-467b-9e54-5ae4bdabae87</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องอุ่นเลือดและส่วนประกอบของเลือดชนิดไม่สัมผัสน้ำสามารถอุ่นเลือดได้ พร้อมกันไม่น้อยกว่า 3 ถุง จำนวน 4 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย -  กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2157b09f-d16e-4bcf-b720-de1088bc7b0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องควบคุมการให้สารละลายโดยใช้กระบอกฉีด ของโรงพยาบาลในจังหวัดสุรินทร์ 5 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบลสำเภาลูน จำนวน 26 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=33f2d0df-213d-44c4-a6fa-d31b0eb2e1f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2106</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาซ่อมแซมแก้ไขระบบเครือข่ายและเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=77d1f891-c26e-4f3d-a9e2-7ca16c4196b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2107</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b600d06e-5f90-400c-80fc-24c6ae2ef280</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>สถาบันพระบรมราชชนก</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2117</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์วิทยาศาสตร์การแพทย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a3db48e8-9e8b-4535-84a6-a14f5811619b</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>สำนักงานพระพุทธศาสนาแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2503</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=285cc870-c52b-429d-b866-52f939bc7fd0</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202609.xlsx
+++ b/Backup/eGP_Monthly_Main_202609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G182"/>
+  <dimension ref="A1:G200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6356,10 +6356,8 @@
           <t>กองทัพบก</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>0204</t>
-        </is>
+      <c r="C170" t="n">
+        <v>204</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -6393,10 +6391,8 @@
           <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>0704</t>
-        </is>
+      <c r="C171" t="n">
+        <v>704</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -6430,10 +6426,8 @@
           <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>0704</t>
-        </is>
+      <c r="C172" t="n">
+        <v>704</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -6467,10 +6461,8 @@
           <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
+      <c r="C173" t="n">
+        <v>805</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -6504,10 +6496,8 @@
           <t>กรมพัฒนาธุรกิจการค้า</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>1308</t>
-        </is>
+      <c r="C174" t="n">
+        <v>1308</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -6541,10 +6531,8 @@
           <t>กรมที่ดิน</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
+      <c r="C175" t="n">
+        <v>1505</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -6578,10 +6566,8 @@
           <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>1905</t>
-        </is>
+      <c r="C176" t="n">
+        <v>1905</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -6615,10 +6601,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C177" t="n">
+        <v>2102</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -6652,10 +6636,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C178" t="n">
+        <v>2102</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -6689,10 +6671,8 @@
           <t>กรมวิทยาศาสตร์การแพทย์</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>2106</t>
-        </is>
+      <c r="C179" t="n">
+        <v>2106</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -6726,10 +6706,8 @@
           <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>2107</t>
-        </is>
+      <c r="C180" t="n">
+        <v>2107</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -6763,10 +6741,8 @@
           <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>2117</t>
-        </is>
+      <c r="C181" t="n">
+        <v>2117</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -6800,10 +6776,8 @@
           <t>สำนักงานพระพุทธศาสนาแห่งชาติ</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>2503</t>
-        </is>
+      <c r="C182" t="n">
+        <v>2503</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -6823,6 +6797,672 @@
       <c r="G182" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=285cc870-c52b-429d-b866-52f939bc7fd0</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>กรมพัฒนาที่ดิน</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>0708</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจอแสดงผล LED พร้อมอุปกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>★ (จอแสดงผล)</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=45d8cd64-624e-4582-a8d1-3fe3d01e41b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>กรมการข้าว</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>0718</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องปรับอากาศ แบบแยกส่วน แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>★ (เครื่องปรับอากาศ)</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2475fb18-8633-42d5-8fe6-f520615dc6f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ และ ครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 13 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0b00828b-7442-420e-85c9-ad09d2f6e16f</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>กรมทรัพยากรน้ำบาดาล</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>0907</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องสูบน้ำไฟฟ้าชนิดมอเตอร์จุ่มใต้น้ำ พร้อมอุปกรณ์ และชุดฝาปิดปากบ่อน้ำบาดาล จำนวน ๖ ชุด โครงการพัฒนาน้ำบาดาลเพื่อความมั่นคงระดับชุมชน ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ (งบเหลือจ่าย) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>★ (มอเตอร์)</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=03ba8462-a0d1-4d13-92c2-a7ae76fed3d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>0909</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทเรือหางยาวสำหรับการลาดตระเวนพื้นที่ทางน้ำ เพื่อเพิ่มประสิทธิภาพการปฏิบัติงานอุทยานแห่งชาติเขาแหลม จังหวัดกาญจนบุรี  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63f7333f-eb0c-40fa-8c06-5f683d543bce</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>กรมการปกครอง</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อวัสดุครุภัณฑ์สำนักงานที่ทำการปกครองอำเภอตาพระยา จังหวัดสระแก้ว ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=de60da4a-56f9-434f-bd1c-60d19d95f672</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>กรมที่ดิน</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์เพื่อการบริหารจัดการหน่วยงานส่วนกลาง (Hardware และ Software) ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a80802ed-6d42-4b60-b93c-de21fb24e5c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>กรมการจัดหางาน</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>1703</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ทดแทนและเพิ่มประสิทธิภาพของสำนักบริหารแรงงานต่างด้าว ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f3092a7e-5bf1-488f-8f3f-6657ba0fe2fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>กรมพัฒนาฝีมือแรงงาน</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>1704</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ (ระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop) ขนาด 3 เฟส 15 กิโลวัตต์ ตำบลบ่อ อำเภอขลุง จังหวัดจันทบุรี จำนวน 1 ระบบ และระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop) ขนาด 3 เฟส 20 กิโลวัตต์ ตำบลบ่อ อำเภอขลุง จังหวัดจันทบุรี จำนวน 1 ระบบ) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d90e4389-d0ce-48d4-b93a-03874d22d178</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>กรมการศาสนา</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>1803</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อหมึกเครื่องพิมพ์ (ครั้งที่ 2)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>★ (หมึกเครื่องพิมพ์, เครื่องพิมพ์)</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8ffdb256-bac2-4342-bdf6-7616e2ae5b25</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>สถาบันมาตรวิทยาแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>1907</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างค่าบำรุงรักษาอุปกรณ์เครือข่ายประจำอาคาร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>★ (อุปกรณ์เครือข่าย)</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b698a86e-10e2-45f2-be5e-f7ec03fa0ce9</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการรถพยาบาลพร้อมอุปกรณ์ช่วยชีวิตชั้นสูง ของโรงพยาบาลชุมชน 4 แห่ง จำนวน 4 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f77b490-654b-45ac-9d8e-cc1f4f3fd4fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดออกซิเจนในเลือดอัตโนมัติชนิดพกพา จำนวน 39 เครื่องๆ งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f13af428-4413-4d73-9542-bd582ed6e240</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจคลื่นไฟฟ้าหัวใจ พร้อมเชื่อมต่อระบบแพทย์ทางไกล จำนวน 27 เครื่อง งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9350a991-2cda-4337-b005-93d114caf75c</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการตู้เย็นเก็บเลือด ขนาดไม่น้อยกว่า 20 คิว จำนวน 4 ตู้ งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์  การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์, ตู้เย็น)</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=83dc4a91-4e74-465d-b378-562e91d2b662</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ เครื่องให้การรักษาอาการปวดและกระตุ้นเซลล์ประสาทส่วนปลายด้วยสนามแม่เหล็กไฟฟ้า(PMS) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=35bbde9c-eb8e-445f-b94e-915454477995</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2106</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมระบบปฏิบัติการและชุดโปรแกรมจัดการสำนักงาน จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ระบบปฏิบัติการ, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=414ac115-ac50-4d65-a54d-d2a9e03b621b</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2107</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ เครื่องวิเคราะห์การทำงานตู้อบเด็ก จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9d04622a-81b1-4cfd-9a05-6c2aec6751f7</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202609.xlsx
+++ b/Backup/eGP_Monthly_Main_202609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G200"/>
+  <dimension ref="A1:G216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6811,10 +6811,8 @@
           <t>กรมพัฒนาที่ดิน</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>0708</t>
-        </is>
+      <c r="C183" t="n">
+        <v>708</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -6848,10 +6846,8 @@
           <t>กรมการข้าว</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>0718</t>
-        </is>
+      <c r="C184" t="n">
+        <v>718</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -6885,10 +6881,8 @@
           <t>กรมทางหลวง</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>0806</t>
-        </is>
+      <c r="C185" t="n">
+        <v>806</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -6922,10 +6916,8 @@
           <t>กรมทรัพยากรน้ำบาดาล</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>0907</t>
-        </is>
+      <c r="C186" t="n">
+        <v>907</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -6959,10 +6951,8 @@
           <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>0909</t>
-        </is>
+      <c r="C187" t="n">
+        <v>909</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -6996,10 +6986,8 @@
           <t>กรมการปกครอง</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>1503</t>
-        </is>
+      <c r="C188" t="n">
+        <v>1503</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -7033,10 +7021,8 @@
           <t>กรมที่ดิน</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
+      <c r="C189" t="n">
+        <v>1505</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -7070,10 +7056,8 @@
           <t>กรมการจัดหางาน</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>1703</t>
-        </is>
+      <c r="C190" t="n">
+        <v>1703</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -7107,10 +7091,8 @@
           <t>กรมพัฒนาฝีมือแรงงาน</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>1704</t>
-        </is>
+      <c r="C191" t="n">
+        <v>1704</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -7144,10 +7126,8 @@
           <t>กรมการศาสนา</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
+      <c r="C192" t="n">
+        <v>1803</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -7181,10 +7161,8 @@
           <t>สถาบันมาตรวิทยาแห่งชาติ</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>1907</t>
-        </is>
+      <c r="C193" t="n">
+        <v>1907</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -7218,10 +7196,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C194" t="n">
+        <v>2102</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -7255,10 +7231,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C195" t="n">
+        <v>2102</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -7292,10 +7266,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C196" t="n">
+        <v>2102</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -7329,10 +7301,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C197" t="n">
+        <v>2102</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -7366,10 +7336,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C198" t="n">
+        <v>2102</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -7403,10 +7371,8 @@
           <t>กรมวิทยาศาสตร์การแพทย์</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>2106</t>
-        </is>
+      <c r="C199" t="n">
+        <v>2106</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -7440,10 +7406,8 @@
           <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>2107</t>
-        </is>
+      <c r="C200" t="n">
+        <v>2107</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -7463,6 +7427,598 @@
       <c r="G200" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9d04622a-81b1-4cfd-9a05-6c2aec6751f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>กรมบัญชีกลาง</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>0304</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาและซ่อมแซมแก้ไขเครื่องปรับอากาศ (แบบรวมอะไหล่) จำนวน 474 เครื่อง ซ่อมแซมแก้ไขระบบไฟฟ้า และระบบสุขาภิบาล อาคาร 3 อาคาร 9 อาคารใหม่ ชั้นใต้ดิน และห้องลิฟต์ กรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>★ (เครื่องปรับอากาศ)</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=273a8add-ac17-48f1-8ff9-c94a946e8273</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>0704</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1607645e-ac86-48f0-a820-917a3a4fe54d</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>0704</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ พร้อมชุดโปรแกรมปฎิบัติงาน โปรแกรมจัดการสำนักงาน และโปรแกรมป้องกันไวรัส จำนวน 18 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, โปรแกรมป้องกันไวรัส, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0511e3cd-537d-45d3-880c-de7433b1eb48</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>กรมประมง</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>0705</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อชุดจอภาพ LED พร้อมงานติดตั้งสำหรับห้องประชุมอานนท์ กรมประมง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>★ (จอภาพ)</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b0679766-012d-497b-8e41-2296e1c7ba51</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>กรมปศุสัตว์</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>0706</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f70d294-53f0-4fd1-b9bc-ef06d20b1657</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>สำนักงานนโยบายและแผนการขนส่งและจราจร</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>0808</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์ของ สนข. ประจำปีงบประมาณ พ.ศ. 2570  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=069d5584-a6b1-426d-9714-115f2fdc7025</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>0904</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาและเพิ่มประสิทธิภาพระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรทางทะเลและชายฝั่ง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f112758f-839d-4660-91b5-12181a1297d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>1202</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>ประกวดราคาเช่ารถส่วนภูมิภาค รถยนต์ไฟฟ้า ประเภทแบตเตอรี่ (BEV) ขนาดความจุของแบตเตอรี่มากกว่า 50 กิโลวัตต์ชั่วโมง (kWh) และกำลังมอเตอร์ไฟฟ้าสูงสุด ไม่เกิน 150 กิโลวัตต์ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>★ (มอเตอร์)</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=40cb45e4-0e08-48b9-a763-7a9aa44d7959</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>กรมการปกครอง</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 5 รายการ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ac3547dc-0f12-4694-b5a3-e216678ce172</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>กรมการศาสนา</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>1803</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อวัสดุสำนักงานส่วนกลาง ประจำปีงบประมาณ พ.ศ. 2569 (ครั้งที่ 2)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>★ (วัสดุสำนักงาน)</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c6f2fbd0-4267-42c4-926d-d8fc49d8a3ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องผลิตออกซิเจนขนาด 5 ลิตร ของโรงพยาบาลสนม และโรงพยาบาลส่งเสริมสุขภาพตำบล 18 แห่ง จำนวน 33 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=655601b1-75a6-4eee-9bc7-ee3ce427abf6</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดความดันโลหิตชนิดอัตโนมัติ วัดความอิ่มตัวของออกซิเจนในเลือด อุณหภูมิร่างกาย พร้อมระบบเชื่อมต่อฐานข้อมูล ของโรงพยาบาลในจังหวัดสุรินทร์ 12 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบล 10 แห่ง จำนวน 50 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=65a2753e-e63f-4be2-b228-0fe250379934</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการชุดอุปกรณ์เคลื่อนย้ายผู้ป่วยในสถานการณ์ฉุกเฉิน ของโรงพยาบาลชุมชน 8 แห่ง จำนวน 10 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=886059b7-d984-4e19-b7d7-6d90ebc9b2e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงชนิดสี 2 หัวตรวจ ของโรงพยาบาลชุมชน 6 แห่ง จำนวน 8 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fc233297-ee25-42e4-bc90-16f41ac8db6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดออกซิเจนในเลือดอัตโนมัติชนิดพกพา ของโรงพยาบาลส่งเสริมสุขภาพตำบลและโรงพยาบาลชุมชน 24 แห่ง จำนวน 68 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3d2922a2-6499-49fa-b182-1e95dc5131d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องเอกซเรย์ทั่วไปขนาดไม่น้อยกว่า 500 mA. แบบแขวนเพดาน โรงพยาบาลแก่งกระจาน ตำบลวังจันทร์ อำเภอแก่งกระจาน จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6f21d5fd-56e9-4486-915b-90fd4be0f39b</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202609.xlsx
+++ b/Backup/eGP_Monthly_Main_202609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G216"/>
+  <dimension ref="A1:G231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อชุดจอภาพ LED พร้อมงานติดตั้งสำหรับห้องประชุมอานนท์ กรมประมง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าเเละวิทยุ เครื่องกำเนิดไฟฟ้า ขนาด 100 กิโลวัตต์ พร้อมตู้ควบคุม ตำบลหูล่อง อำเภอปากพนัง จังหวัดนครศรีธรรมราช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2661,12 +2661,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>★ (จอภาพ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a26dbb80-72fc-430c-8431-ba0133b850fc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=18464524-52ce-42bf-96c8-511cdf002607</t>
         </is>
       </c>
     </row>
@@ -2678,15 +2678,15 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>กรมประมง</t>
+          <t>กรมการข้าว</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>705</v>
+        <v>718</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าเเละวิทยุ เครื่องกำเนิดไฟฟ้า ขนาด 100 กิโลวัตต์ พร้อมตู้ควบคุม ตำบลหูล่อง อำเภอปากพนัง จังหวัดนครศรีธรรมราช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ต่อพ่วงเพื่อเพิ่มประสิทธิภาพการปฏิบัติงานของกรมการข้าว แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=18464524-52ce-42bf-96c8-511cdf002607</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=aaaf180c-62ba-4ca4-9a9c-0333baa76276</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ต่อพ่วงเพื่อเพิ่มประสิทธิภาพการปฏิบัติงานของกรมการข้าว แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อทดแทนครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ต่อพ่วงเพื่อเพิ่มประสิทธิภาพการปฏิบัติงานของกรมการข้าว แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=aaaf180c-62ba-4ca4-9a9c-0333baa76276</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=15086036-ab87-4a45-b29c-edd87f507d1b</t>
         </is>
       </c>
     </row>
@@ -2748,15 +2748,15 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>กรมการข้าว</t>
+          <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>718</v>
+        <v>804</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อทดแทนครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ต่อพ่วงเพื่อเพิ่มประสิทธิภาพการปฏิบัติงานของกรมการข้าว แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์และอุปกรณ์ตามโครงการระบบเครือข่ายเพื่อเพิ่มประสิทธิภาพในการปฏิบัติงานของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=15086036-ab87-4a45-b29c-edd87f507d1b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=faa5336e-2946-42fd-b66e-9583a9f24e44</t>
         </is>
       </c>
     </row>
@@ -2783,15 +2783,15 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์และอุปกรณ์ตามโครงการระบบเครือข่ายเพื่อเพิ่มประสิทธิภาพในการปฏิบัติงานของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2801,12 +2801,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=faa5336e-2946-42fd-b66e-9583a9f24e44</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=44d1ec7f-04ab-49d0-b112-502799195d6b</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการจัดจ้างบำรุงรักษาเครื่องคอมพิวเตอร์แม่ข่ายและอุปกรณ์สำหรับระบบสารสนเทศบริหารเครื่องจักรกลและการเงินการบัญชีเพื่อการบริหารจัดการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=44d1ec7f-04ab-49d0-b112-502799195d6b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=909fce3b-2a20-4eb7-b619-b2e32da6e18d</t>
         </is>
       </c>
     </row>
@@ -2853,15 +2853,15 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>กรมทรัพยากรธรณี</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>806</v>
+        <v>905</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการจัดจ้างบำรุงรักษาเครื่องคอมพิวเตอร์แม่ข่ายและอุปกรณ์สำหรับระบบสารสนเทศบริหารเครื่องจักรกลและการเงินการบัญชีเพื่อการบริหารจัดการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาซ่อมบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรธรณี ปีงบประมาณ พ.ศ. 2570 จำนวน 1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=909fce3b-2a20-4eb7-b619-b2e32da6e18d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3cc3bb5f-0d9f-428a-b588-18b0b71b8b6e</t>
         </is>
       </c>
     </row>
@@ -2888,15 +2888,15 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
+          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการบำรุงรักษาและเพิ่มประสิทธิภาพระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรทางทะเลและชายฝั่ง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อและติดตั้งเครื่องคอมพิวเตอร์แม่ข่ายพร้อมอุปกรณ์ประกอบสำหรับรองรับการให้บริการระบบสารบรรณอิเล็กทรอนิกส์ของกรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a2cbdca0-293f-4c68-b81a-7197ca7e532f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=028b6dd5-2160-4f89-924f-f6c47b4b4995</t>
         </is>
       </c>
     </row>
@@ -2923,15 +2923,15 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>กรมทรัพยากรธรณี</t>
+          <t>สำนักงานปลัดกระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>905</v>
+        <v>1102</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาซ่อมบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรธรณี ปีงบประมาณ พ.ศ. 2570 จำนวน 1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการจัดอบรมเตรียมความพร้อมผู้แต่งตั้งเป็นพนักงานเจ้าหน้าที่ตามพระราชบัญญัติว่าด้วยการกระทำความผิดเกี่ยวกับคอมพิวเตอร์ฯ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3cc3bb5f-0d9f-428a-b588-18b0b71b8b6e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8de232df-b5c2-427b-9a5d-d9f5ca3342c3</t>
         </is>
       </c>
     </row>
@@ -2958,15 +2958,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>909</v>
+        <v>1302</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อและติดตั้งเครื่องคอมพิวเตอร์แม่ข่ายพร้อมอุปกรณ์ประกอบสำหรับรองรับการให้บริการระบบสารบรรณอิเล็กทรอนิกส์ของกรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์สนับสนุนศูนย์ข้อมูลและเครือข่ายคอมพิวเตอร์ (Data Center) ของกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=028b6dd5-2160-4f89-924f-f6c47b4b4995</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5065022-193d-466c-819b-b1533c1e1696</t>
         </is>
       </c>
     </row>
@@ -2993,15 +2993,15 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม</t>
+          <t>สถาบันส่งเสริมศิลปหัตถกรรมไทย (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1102</v>
+        <v>1311</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการจัดอบรมเตรียมความพร้อมผู้แต่งตั้งเป็นพนักงานเจ้าหน้าที่ตามพระราชบัญญัติว่าด้วยการกระทำความผิดเกี่ยวกับคอมพิวเตอร์ฯ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างดำเนินการบำรุงรักษาระบบและอุปกรณ์ภายในห้อง Data Center และการต่อลิขสิทธิ์โปรแกรมคอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8de232df-b5c2-427b-9a5d-d9f5ca3342c3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8c2b0f9b-210b-4328-a727-0ebda03f9ebc</t>
         </is>
       </c>
     </row>
@@ -3028,15 +3028,15 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+          <t>กรมบังคับคดี</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1302</v>
+        <v>1605</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์สนับสนุนศูนย์ข้อมูลและเครือข่ายคอมพิวเตอร์ (Data Center) ของกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างตรวจสอบเครื่องคอมพิวเตอร์ให้พร้อมใช้งานและบริการประชาชน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5065022-193d-466c-819b-b1533c1e1696</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=590bcfa8-9d1a-43f4-b6c0-1d332cdf98ac</t>
         </is>
       </c>
     </row>
@@ -3063,15 +3063,15 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>สถาบันส่งเสริมศิลปหัตถกรรมไทย (องค์การมหาชน)</t>
+          <t>กรมศิลปากร</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1311</v>
+        <v>1804</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างดำเนินการบำรุงรักษาระบบและอุปกรณ์ภายในห้อง Data Center และการต่อลิขสิทธิ์โปรแกรมคอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการดูแลบำรุงรักษาเครื่องปรับอากาศ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8c2b0f9b-210b-4328-a727-0ebda03f9ebc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=560aab6a-379c-4e73-a426-35b147f0955f</t>
         </is>
       </c>
     </row>
@@ -3098,15 +3098,15 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>กรมบังคับคดี</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1605</v>
+        <v>2102</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างตรวจสอบเครื่องคอมพิวเตอร์ให้พร้อมใช้งานและบริการประชาชน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดอัตโนมัติ พร้อมตู้ตั้งพื้นจอแสดงผล และระบบสัญญาณเตือน จำนวน 39 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาล ในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (จอแสดงผล, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=590bcfa8-9d1a-43f4-b6c0-1d332cdf98ac</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f7659e63-27b4-4348-9cb8-c0e5ed5164a0</t>
         </is>
       </c>
     </row>
@@ -3133,15 +3133,15 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>กรมศิลปากร</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1804</v>
+        <v>2102</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการดูแลบำรุงรักษาเครื่องปรับอากาศ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องอุ่นเลือดและส่วนประกอบของเลือดชนิดไม่สัมผัสน้ำสามารถอุ่นเลือดได้ พร้อมกันไม่น้อยกว่า 3 ถุง ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 4 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=560aab6a-379c-4e73-a426-35b147f0955f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dc9795b5-9883-4a59-bee5-16ba72ecd5c6</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดอัตโนมัติ พร้อมตู้ตั้งพื้นจอแสดงผล และระบบสัญญาณเตือน จำนวน 39 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาล ในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเตียงผู้ป่วยชนิดสามไกร์ราวปีกนก พร้อมเบาะเสาน้ำเกลือตู้ข้างเตียงและถาดคร่อมเตียง ของโรงพยาบาลส่งเสริมสุขภาพตำบล 25 แห่ง จำนวน 25 เตียง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>★ (จอแสดงผล, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f7659e63-27b4-4348-9cb8-c0e5ed5164a0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=43094cdc-968c-43e9-b0e7-915d25aa8621</t>
         </is>
       </c>
     </row>
@@ -3203,15 +3203,15 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2102</v>
+        <v>2107</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องอุ่นเลือดและส่วนประกอบของเลือดชนิดไม่สัมผัสน้ำสามารถอุ่นเลือดได้ พร้อมกันไม่น้อยกว่า 3 ถุง ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 4 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dc9795b5-9883-4a59-bee5-16ba72ecd5c6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63c3a055-9106-4358-9ed6-5bf60d1e158c</t>
         </is>
       </c>
     </row>
@@ -3238,15 +3238,15 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2102</v>
+        <v>2113</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเตียงผู้ป่วยชนิดสามไกร์ราวปีกนก พร้อมเบาะเสาน้ำเกลือตู้ข้างเตียงและถาดคร่อมเตียง ของโรงพยาบาลส่งเสริมสุขภาพตำบล 25 แห่ง จำนวน 25 เตียง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและวิเคราะห์ระบบเก็บข้อมูลจราจรคอมพิวเตอร์ขั้นสูง (CSOC) สำนักงานหลักประกันสุขภาพแห่งชาติ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3256,32 +3256,32 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=43094cdc-968c-43e9-b0e7-915d25aa8621</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=516788e1-5adb-46f1-b0bc-48d9b91e8cd8</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>กรมสนับสนุนบริการสุขภาพ</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2107</v>
+        <v>204</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ และอุปกรณ์ประกอบเครื่องคอมพิวเตอร์ เพื่อทดแทน และพัฒนาระบบเทคโนโลยีสารสนเทศหน่วยบัญชาการป้องกันภัยทางอากาศ (นปอ.) จำนวน ๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63c3a055-9106-4358-9ed6-5bf60d1e158c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8603566b-8b32-470f-b070-76bf84fb86b4</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2113</v>
+        <v>204</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและวิเคราะห์ระบบเก็บข้อมูลจราจรคอมพิวเตอร์ขั้นสูง (CSOC) สำนักงานหลักประกันสุขภาพแห่งชาติ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างงานติดตั้งเครื่องปรับอากาศ ประจำอาคารหอประชุม หมายเลข ๙๖/๒๓ ของ โรงพยาบาลอานันทมหิดล จังหวัดลพบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3326,12 +3326,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=516788e1-5adb-46f1-b0bc-48d9b91e8cd8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=97d16ed9-2390-479b-8218-55472ad15ea3</t>
         </is>
       </c>
     </row>
@@ -3343,15 +3343,15 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กรมชลประทาน</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>204</v>
+        <v>703</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ และอุปกรณ์ประกอบเครื่องคอมพิวเตอร์ เพื่อทดแทน และพัฒนาระบบเทคโนโลยีสารสนเทศหน่วยบัญชาการป้องกันภัยทางอากาศ (นปอ.) จำนวน ๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องสูบน้ำแบบจุ่มใช้มอเตอร์ไฟฟ้า และอื่นๆรวม 3 รายการ สำหรับงานปรับปรุงอาคารบังคับน้ำคลองทิวา-ต้นนา โครงการส่งน้ำและบำรุงรักษาบางพลวง ตำบลพนมสารคาม อำเภอพนมสารคาม จังหวัดฉะเชิงเทรา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8603566b-8b32-470f-b070-76bf84fb86b4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=641eb398-88f6-4784-9733-866ddfdb5ea8</t>
         </is>
       </c>
     </row>
@@ -3378,15 +3378,15 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>204</v>
+        <v>704</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างงานติดตั้งเครื่องปรับอากาศ ประจำอาคารหอประชุม หมายเลข ๙๖/๒๓ ของ โรงพยาบาลอานันทมหิดล จังหวัดลพบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์เครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล  จำนวน 12 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=97d16ed9-2390-479b-8218-55472ad15ea3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cae8cfd5-0a33-48de-bb0d-dd1597263622</t>
         </is>
       </c>
     </row>
@@ -3413,15 +3413,15 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>กรมชลประทาน</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องสูบน้ำแบบจุ่มใช้มอเตอร์ไฟฟ้า และอื่นๆรวม 3 รายการ สำหรับงานปรับปรุงอาคารบังคับน้ำคลองทิวา-ต้นนา โครงการส่งน้ำและบำรุงรักษาบางพลวง ตำบลพนมสารคาม อำเภอพนมสารคาม จังหวัดฉะเชิงเทรา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล)  ขนาด ๑ ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า ๒,๔๐๐ ซีซี  หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า ๑๑๐ กิโลวัตต์ ขับเคลื่อน 4 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน ๑ คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=641eb398-88f6-4784-9733-866ddfdb5ea8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=23493925-5f1a-442c-a9ec-afccbc470e45</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์เครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล  จำนวน 12 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อเครื่องคอมพิวเตอร์ และเครื่องคอมพิวเตอร์โน้ตบุ๊ก จำนวน 2 รายการ ของสำนักงานตรวจบัญชีสหกรณ์ชลบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cae8cfd5-0a33-48de-bb0d-dd1597263622</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=07006c6c-edf5-4030-b6c9-1078334342be</t>
         </is>
       </c>
     </row>
@@ -3483,15 +3483,15 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>704</v>
+        <v>806</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล)  ขนาด ๑ ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า ๒,๔๐๐ ซีซี  หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า ๑๑๐ กิโลวัตต์ ขับเคลื่อน 4 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน ๑ คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าโครงการเช่าเครื่องพิมพ์ 4 สี เพื่อการพิมพ์เอกสารแจ้งผู้ขับขี่เพื่อการเปรียบเทียบปรับตามกฎหมาย ของ กองบังคับการตำรวจทางหลวง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=23493925-5f1a-442c-a9ec-afccbc470e45</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3fdfa461-5479-46d3-90bc-5b8725bde7b5</t>
         </is>
       </c>
     </row>
@@ -3518,15 +3518,15 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>สำนักงานปลัดกระทรวงแรงงาน</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>704</v>
+        <v>1702</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อเครื่องคอมพิวเตอร์ และเครื่องคอมพิวเตอร์โน้ตบุ๊ก จำนวน 2 รายการ ของสำนักงานตรวจบัญชีสหกรณ์ชลบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดหาครุภัณฑ์คอมพิวเตอร์เพื่อทดแทนและเพิ่มประสิทธิภาพให้หน่วยงานในสังกัดสำนักงานปลัดกระทรวงแรงงาน ปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=07006c6c-edf5-4030-b6c9-1078334342be</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=eea981aa-edb1-4fdf-8067-e5fb7c92e854</t>
         </is>
       </c>
     </row>
@@ -3553,15 +3553,15 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามการทุจริตในภาครัฐ</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>806</v>
+        <v>2517</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าโครงการเช่าเครื่องพิมพ์ 4 สี เพื่อการพิมพ์เอกสารแจ้งผู้ขับขี่เพื่อการเปรียบเทียบปรับตามกฎหมาย ของ กองบังคับการตำรวจทางหลวง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาเครื่องคอมพิวเตอร์แม่ข่าย และระบบความปลอดภัยทางไซเบอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3571,12 +3571,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>★ (เครื่องพิมพ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3fdfa461-5479-46d3-90bc-5b8725bde7b5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=39110c90-d236-47eb-913a-cb6b3cab18ba</t>
         </is>
       </c>
     </row>
@@ -3588,15 +3588,15 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงแรงงาน</t>
+          <t>สำนักงานการตรวจเงินแผ่นดิน</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1702</v>
+        <v>2606</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดหาครุภัณฑ์คอมพิวเตอร์เพื่อทดแทนและเพิ่มประสิทธิภาพให้หน่วยงานในสังกัดสำนักงานปลัดกระทรวงแรงงาน ปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างเหมาบริการขนย้ายเครื่องแม่ข่าย และอุปกรณ์พร้อมติดตั้ง ณ ศูนย์ข้อมูลหลัก ของสำนักงานการตรวจเงินแผ่นดิน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (เครื่องแม่ข่าย)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=eea981aa-edb1-4fdf-8067-e5fb7c92e854</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a89ffef4-4bf7-41f2-83ef-2e02a1a4e80c</t>
         </is>
       </c>
     </row>
@@ -3623,15 +3623,15 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามการทุจริตในภาครัฐ</t>
+          <t>สำนักงานปลัดกระทรวงการอุดมศึกษา วิทยาศาสตร์ วิจัยและนวัตกรรม</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2517</v>
+        <v>23002</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการบำรุงรักษาเครื่องคอมพิวเตอร์แม่ข่าย และระบบความปลอดภัยทางไซเบอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างเหมาบริการบำรุงรักษาเครื่องปรับอากาศ แบบรวมอะไหล่ จำนวน 606 เครื่อง ภายในอาคารอุดมศึกษา 1 อาคารอุดมศึกษา 2 อาคารพระจอมเกล้า และอาคารอเนกประสงค์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3641,32 +3641,32 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=39110c90-d236-47eb-913a-cb6b3cab18ba</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4ed51246-9d93-42ff-bb32-e9acb8e03644</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>สำนักงานการตรวจเงินแผ่นดิน</t>
+          <t>สำนักงานบริหารและพัฒนาองค์ความรู้ (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2606</v>
+        <v>125</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างเหมาบริการขนย้ายเครื่องแม่ข่าย และอุปกรณ์พร้อมติดตั้ง ณ ศูนย์ข้อมูลหลัก ของสำนักงานการตรวจเงินแผ่นดิน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3676,32 +3676,32 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>★ (เครื่องแม่ข่าย)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a89ffef4-4bf7-41f2-83ef-2e02a1a4e80c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=22d2e215-7492-48e1-8b48-52ebf11afb3d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการอุดมศึกษา วิทยาศาสตร์ วิจัยและนวัตกรรม</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>23002</v>
+        <v>204</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างเหมาบริการบำรุงรักษาเครื่องปรับอากาศ แบบรวมอะไหล่ จำนวน 606 เครื่อง ภายในอาคารอุดมศึกษา 1 อาคารอุดมศึกษา 2 อาคารพระจอมเกล้า และอาคารอเนกประสงค์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ พร้อมอุปกรณ์ จำนวน ๘๐ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4ed51246-9d93-42ff-bb32-e9acb8e03644</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ed207e86-fa08-4bf6-b096-f66e9ea91205</t>
         </is>
       </c>
     </row>
@@ -3728,15 +3728,15 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>สำนักงานบริหารและพัฒนาองค์ความรู้ (องค์การมหาชน)</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>125</v>
+        <v>204</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อสป.สาย ส. ตามโครงการจัดหาอุปกรณ์คอมพิวเตอร์ เพื่อสนับสนุนงานออกแบบสถาปัตยกรรม วิศวกรรมและงานประมาณราคา (ยย.ทบ.) จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=22d2e215-7492-48e1-8b48-52ebf11afb3d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a5d0fbe1-af34-494f-b408-da6f60a04c26</t>
         </is>
       </c>
     </row>
@@ -3763,15 +3763,15 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กรมธนารักษ์</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>204</v>
+        <v>303</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ พร้อมอุปกรณ์ จำนวน ๘๐ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์อาคารเก็บพัสดุสำนักงานธนารักษ์พื้นที่ชลบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ed207e86-fa08-4bf6-b096-f66e9ea91205</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=606b64be-13e1-468a-84bd-c7c5b46221da</t>
         </is>
       </c>
     </row>
@@ -3798,15 +3798,15 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>204</v>
+        <v>402</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อสป.สาย ส. ตามโครงการจัดหาอุปกรณ์คอมพิวเตอร์ เพื่อสนับสนุนงานออกแบบสถาปัตยกรรม วิศวกรรมและงานประมาณราคา (ยย.ทบ.) จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาดูแล บำรุงรักษา และล้างทำความสะอาดระบบเครื่องปรับอากาศ ณ อาคารกระทรวงการต่างประเทศ ถนนศรีอยุธยา และศูนย์ราชการเฉลิมพระเกียรติฯ อาคาร B ชั้น 7 - 8 รวม 2 แห่ง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a5d0fbe1-af34-494f-b408-da6f60a04c26</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4c0225b9-4c8b-4bbd-80d4-d42eccd0092e</t>
         </is>
       </c>
     </row>
@@ -3833,15 +3833,15 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>กรมธนารักษ์</t>
+          <t>กรมกิจการเด็กและเยาวชน</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>303</v>
+        <v>605</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์อาคารเก็บพัสดุสำนักงานธนารักษ์พื้นที่ชลบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาเครื่องคอมพิวเตอร์ อุปกรณ์ต่อพ่วง และระบบสารสนเทศ ของ ดย. ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=606b64be-13e1-468a-84bd-c7c5b46221da</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cb192597-9852-49f1-81d0-f9bd008c7f6d</t>
         </is>
       </c>
     </row>
@@ -3868,15 +3868,15 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>402</v>
+        <v>704</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาดูแล บำรุงรักษา และล้างทำความสะอาดระบบเครื่องปรับอากาศ ณ อาคารกระทรวงการต่างประเทศ ถนนศรีอยุธยา และศูนย์ราชการเฉลิมพระเกียรติฯ อาคาร B ชั้น 7 - 8 รวม 2 แห่ง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อครุภัณฑ์ยานพาหนะและขนส่งรถโดยสารขนาด 12 ที่นั่ง (ดีเซล) จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4c0225b9-4c8b-4bbd-80d4-d42eccd0092e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3d257d5-116f-4d11-9cba-b2af7ffd9693</t>
         </is>
       </c>
     </row>
@@ -3903,15 +3903,15 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>กรมกิจการเด็กและเยาวชน</t>
+          <t>กรมประมง</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>605</v>
+        <v>705</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาเครื่องคอมพิวเตอร์ อุปกรณ์ต่อพ่วง และระบบสารสนเทศ ของ ดย. ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างการจัดจ้างบำรุงรักษาครุภัณฑ์คอมพิวเตอร์สำหรับการรักษาความปลอดภัยของระบบเครือข่ายและคอมพิวเตอร์ จำนวน 1 งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cb192597-9852-49f1-81d0-f9bd008c7f6d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=29210ba8-e1c2-4d7e-80d4-6acfeb801f71</t>
         </is>
       </c>
     </row>
@@ -3938,15 +3938,15 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมประมง</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อครุภัณฑ์ยานพาหนะและขนส่งรถโดยสารขนาด 12 ที่นั่ง (ดีเซล) จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างการจัดจ้างบำรุงรักษาอุปกรณ์กระจายสัญญาณ จำนวน ๑ งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3d257d5-116f-4d11-9cba-b2af7ffd9693</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b2bbd6f5-c7a5-4bc3-be9e-fc1ddf4ac0a8</t>
         </is>
       </c>
     </row>
@@ -3973,15 +3973,15 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>กรมประมง</t>
+          <t>สำนักงานมาตรฐานสินค้าเกษตรและอาหารแห่งชาติ</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>705</v>
+        <v>714</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างการจัดจ้างบำรุงรักษาครุภัณฑ์คอมพิวเตอร์สำหรับการรักษาความปลอดภัยของระบบเครือข่ายและคอมพิวเตอร์ จำนวน 1 งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการจ้างเหมาดูแลและบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์และระบบคอมพิวเตอร์พร้อมอุปกรณ์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=29210ba8-e1c2-4d7e-80d4-6acfeb801f71</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d133e360-c57e-4330-bff5-2f10cf027da9</t>
         </is>
       </c>
     </row>
@@ -4008,15 +4008,15 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>กรมประมง</t>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>705</v>
+        <v>1302</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างการจัดจ้างบำรุงรักษาอุปกรณ์กระจายสัญญาณ จำนวน ๑ งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องคอมพิวเตอร์และอุปกรณ์ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b2bbd6f5-c7a5-4bc3-be9e-fc1ddf4ac0a8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=04549f6b-e678-4005-91df-2993ee4bdb83</t>
         </is>
       </c>
     </row>
@@ -4043,15 +4043,15 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>สำนักงานมาตรฐานสินค้าเกษตรและอาหารแห่งชาติ</t>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>714</v>
+        <v>1302</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการจ้างเหมาดูแลและบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์และระบบคอมพิวเตอร์พร้อมอุปกรณ์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่ายของสำนักงานพาณิชย์จังหวัด 76 จังหวัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d133e360-c57e-4330-bff5-2f10cf027da9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f1e51f04-f935-4983-8200-42b44f480fc9</t>
         </is>
       </c>
     </row>
@@ -4078,15 +4078,15 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+          <t>สถาบันส่งเสริมศิลปหัตถกรรมไทย (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1302</v>
+        <v>1311</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องคอมพิวเตอร์และอุปกรณ์ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการจัดหาพนักงานดูแลหอนิทรรศการและห้องสมุด ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (สมุด)</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=04549f6b-e678-4005-91df-2993ee4bdb83</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ff1d2fa-ba06-4da0-bc6c-023504d3c9d6</t>
         </is>
       </c>
     </row>
@@ -4113,15 +4113,15 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1302</v>
+        <v>1808</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่ายของสำนักงานพาณิชย์จังหวัด 76 จังหวัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์อื่นๆ (เครื่องแต่งกายโขน-ละคร) จำนวน 7 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4131,12 +4131,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f1e51f04-f935-4983-8200-42b44f480fc9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8e14fee9-d40a-4d5f-b4ec-b5dd1cbdcc29</t>
         </is>
       </c>
     </row>
@@ -4148,15 +4148,15 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>สถาบันส่งเสริมศิลปหัตถกรรมไทย (องค์การมหาชน)</t>
+          <t>กรมส่งเสริมการเรียนรู้</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1311</v>
+        <v>2033</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการจัดหาพนักงานดูแลหอนิทรรศการและห้องสมุด ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>★ (สมุด)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ff1d2fa-ba06-4da0-bc6c-023504d3c9d6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=988b1f6a-eb89-4ed1-bbe5-4e82ba43054b</t>
         </is>
       </c>
     </row>
@@ -4183,15 +4183,15 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1808</v>
+        <v>2102</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์อื่นๆ (เครื่องแต่งกายโขน-ละคร) จำนวน 7 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการตู้เย็นเก็บเลือดขนาดไม่น้อยกว่า 20 คิว ของโรงพยาบาลในจังหวัดสุรินทร์ 6 แห่ง จำนวน 7 ตู้ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์, ตู้เย็น)</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8e14fee9-d40a-4d5f-b4ec-b5dd1cbdcc29</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dfce18c4-7835-4a43-8ba6-fb9a2b9ab472</t>
         </is>
       </c>
     </row>
@@ -4218,15 +4218,15 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเรียนรู้</t>
+          <t>กรมอนามัย</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2033</v>
+        <v>2109</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่าย กรมอนามัย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=988b1f6a-eb89-4ed1-bbe5-4e82ba43054b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0f1ebcb1-8a09-4209-922e-0e2e49160cba</t>
         </is>
       </c>
     </row>
@@ -4253,15 +4253,15 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>2102</v>
+        <v>2113</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการตู้เย็นเก็บเลือดขนาดไม่น้อยกว่า 20 คิว ของโรงพยาบาลในจังหวัดสุรินทร์ 6 แห่ง จำนวน 7 ตู้ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์แม่ข่าย (Outsource System) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์, ตู้เย็น)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dfce18c4-7835-4a43-8ba6-fb9a2b9ab472</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1c3629ca-59d6-4b8a-839b-92b06d6a1c43</t>
         </is>
       </c>
     </row>
@@ -4288,15 +4288,15 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>กรมอนามัย</t>
+          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2109</v>
+        <v>2113</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่าย กรมอนามัย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์เครือข่าย (Outsource Network) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4311,27 +4311,27 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0f1ebcb1-8a09-4209-922e-0e2e49160cba</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b44df475-19c0-4304-b42e-0c379f2f6a07</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+          <t>กองทัพอากาศ</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2113</v>
+        <v>206</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์แม่ข่าย (Outsource System) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโต๊ะและเก้าอี้ประชุม จำนวน ๒ รายการ (แจ้งที่ ๘๙๖/๖๙) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4341,32 +4341,32 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (โต๊ะ, เก้าอี้)</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1c3629ca-59d6-4b8a-839b-92b06d6a1c43</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c197cbba-6119-4a85-8655-64df092381b8</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+          <t>กรมศุลกากร</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2113</v>
+        <v>305</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์เครือข่าย (Outsource Network) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องปรับอากาศ แบบฝังฝ้าสี่ทิศทาง (ระบบ Inverter) ขนาด 48,000 บีทียู ด่านศุลกากรปาดังเบซาร์ ตำบลปาดังเบซาร์ อำเภอสะเดา จังหวัดสงขลา 12 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4376,12 +4376,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b44df475-19c0-4304-b42e-0c379f2f6a07</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7ffdc802-88d9-422f-a01b-27711177cb61</t>
         </is>
       </c>
     </row>
@@ -4393,15 +4393,15 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>กองทัพอากาศ</t>
+          <t>กรมสรรพากร</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>206</v>
+        <v>307</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโต๊ะและเก้าอี้ประชุม จำนวน ๒ รายการ (แจ้งที่ ๘๙๖/๖๙) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบ ไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 2,400 ซีซี  หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ จำนวน 5 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>★ (โต๊ะ, เก้าอี้)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c197cbba-6119-4a85-8655-64df092381b8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e642705c-f34c-41db-ad86-705717edf0ea</t>
         </is>
       </c>
     </row>
@@ -4428,15 +4428,15 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>กรมศุลกากร</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>305</v>
+        <v>704</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องปรับอากาศ แบบฝังฝ้าสี่ทิศทาง (ระบบ Inverter) ขนาด 48,000 บีทียู ด่านศุลกากรปาดังเบซาร์ ตำบลปาดังเบซาร์ อำเภอสะเดา จังหวัดสงขลา 12 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7ffdc802-88d9-422f-a01b-27711177cb61</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5b0cc17-68bd-4696-805e-f78e075178e3</t>
         </is>
       </c>
     </row>
@@ -4463,15 +4463,15 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>กรมสรรพากร</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>307</v>
+        <v>704</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบ ไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 2,400 ซีซี  หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ จำนวน 5 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุด ไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e642705c-f34c-41db-ad86-705717edf0ea</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=106210e4-0233-403f-957c-c894b083d53b</t>
         </is>
       </c>
     </row>
@@ -4498,15 +4498,15 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมส่งเสริมการเกษตร</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดชื้อครุภัณฑ์ยานพาหนะและขนส่ง ประจำปีงบประมาณ พ.ศ 2570 โดยวิธีประกวดอิเล็กทรอนิกส์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5b0cc17-68bd-4696-805e-f78e075178e3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ec4d9c1c-1aa5-4b14-b3ea-60845e7335fb</t>
         </is>
       </c>
     </row>
@@ -4533,15 +4533,15 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมส่งเสริมสหกรณ์</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุด ไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาบรรทุกขนาด 1 ตัน หลังคาไฟเบอร์กลาส หรือเหล็กหรือพลาสติกวิศวกรรม สำนักงานสหกรณ์จังหวัดศรีสะเกษ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=106210e4-0233-403f-957c-c894b083d53b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=51b057ec-ffcf-432e-bf86-fe4029225a82</t>
         </is>
       </c>
     </row>
@@ -4568,15 +4568,15 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเกษตร</t>
+          <t>กรมพัฒนาธุรกิจการค้า</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>711</v>
+        <v>1308</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดชื้อครุภัณฑ์ยานพาหนะและขนส่ง ประจำปีงบประมาณ พ.ศ 2570 โดยวิธีประกวดอิเล็กทรอนิกส์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องคอมพิวเตอร์ลูกข่ายและอุปกรณ์ต่อพ่วง ปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4586,12 +4586,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ec4d9c1c-1aa5-4b14-b3ea-60845e7335fb</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=be5cf0cb-614f-4d37-aac0-190b90321cb6</t>
         </is>
       </c>
     </row>
@@ -4603,15 +4603,15 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมสหกรณ์</t>
+          <t>กรมโยธาธิการและผังเมือง</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>712</v>
+        <v>1507</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาบรรทุกขนาด 1 ตัน หลังคาไฟเบอร์กลาส หรือเหล็กหรือพลาสติกวิศวกรรม สำนักงานสหกรณ์จังหวัดศรีสะเกษ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างโครงการจัดหาสิ่งก่อสร้างและครุภัณฑ์ประกอบ อาคารสำนักงานแห่งใหม่ของสำนักงบประมาณ แขวงพญาไท เขตพญาไท กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=51b057ec-ffcf-432e-bf86-fe4029225a82</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8b31f2b3-f6fd-4e5c-979f-8575feda4bbf</t>
         </is>
       </c>
     </row>
@@ -4638,15 +4638,15 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
+          <t>กรมการศาสนา</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1202</v>
+        <v>1803</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่ารถส่วนภูมิภาค รถยนต์ไฟฟ้า ประเภทแบตเตอรี่ (BEV) ขนาดความจุของแบตเตอรี่มากกว่า 50 กิโลวัตต์ชั่วโมง (kWh) และกำลังมอเตอร์ไฟฟ้าสูงสุด ไม่เกิน 150 กิโลวัตต์ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อวัสดุสำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (วัสดุสำนักงาน)</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=490958cc-932a-45a1-8497-c33d7a13f8c6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=07f7d716-619d-4e73-9518-7f683a4a05ed</t>
         </is>
       </c>
     </row>
@@ -4673,15 +4673,15 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>กรมพัฒนาธุรกิจการค้า</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1308</v>
+        <v>2102</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องคอมพิวเตอร์ลูกข่ายและอุปกรณ์ต่อพ่วง ปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการชุดกระเป๋าปฐมพยาบาลสนามประจำตัวเจ้าหน้าที่ (IFAK) ของโรงพยาบาลชุมชน 11 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบล 40 แห่ง จำนวน 117 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=be5cf0cb-614f-4d37-aac0-190b90321cb6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=197d72c1-0e0f-4f3d-a377-6f7e052fd668</t>
         </is>
       </c>
     </row>
@@ -4708,15 +4708,15 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>กรมโยธาธิการและผังเมือง</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1507</v>
+        <v>2102</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างโครงการจัดหาสิ่งก่อสร้างและครุภัณฑ์ประกอบ อาคารสำนักงานแห่งใหม่ของสำนักงบประมาณ แขวงพญาไท เขตพญาไท กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8b31f2b3-f6fd-4e5c-979f-8575feda4bbf</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a903de26-6f92-4b12-bcdc-87924b3b825b</t>
         </is>
       </c>
     </row>
@@ -4743,15 +4743,15 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>กรมการศาสนา</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1803</v>
+        <v>2102</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อวัสดุสำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อสิทธิ์ใช้งานซอฟต์แวร์จัดการความเสี่ยงเกี่ยวกับระบบสารสนเทศ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>★ (วัสดุสำนักงาน)</t>
+          <t>★ (ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=07f7d716-619d-4e73-9518-7f683a4a05ed</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f182625c-e015-489e-84e0-ac3c9c8dc788</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการชุดกระเป๋าปฐมพยาบาลสนามประจำตัวเจ้าหน้าที่ (IFAK) ของโรงพยาบาลชุมชน 11 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบล 40 แห่ง จำนวน 117 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ กล้องถ่ายภาพจอประสาทตาดิจิตอล (Digital Fundus Camera) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=197d72c1-0e0f-4f3d-a377-6f7e052fd668</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=810bd451-770f-4032-86a0-1216954db79a</t>
         </is>
       </c>
     </row>
@@ -4813,15 +4813,15 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สำนักงานคณะกรรมการอาหารและยา</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2102</v>
+        <v>2110</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a903de26-6f92-4b12-bcdc-87924b3b825b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=69d9687c-b7f1-405c-843e-92b98ad29261</t>
         </is>
       </c>
     </row>
@@ -4848,15 +4848,15 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2102</v>
+        <v>2117</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อสิทธิ์ใช้งานซอฟต์แวร์จัดการความเสี่ยงเกี่ยวกับระบบสารสนเทศ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อติดตั้งระบบกล้องวงจรปิด ของวิทยาลัยพยาบาลบรมราชชนนี นครศรีธรรมราช จำนวน 1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4866,32 +4866,32 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>★ (ซอฟต์แวร์)</t>
+          <t>★ (กล้องวงจรปิด)</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f182625c-e015-489e-84e0-ac3c9c8dc788</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afa9b388-be98-4ed1-8fa9-0c791e5acf34</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมธนารักษ์</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2102</v>
+        <v>303</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ กล้องถ่ายภาพจอประสาทตาดิจิตอล (Digital Fundus Camera) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการทำความสะอาดศูนย์คอมพิวเตอร์แห่งใหม่ ของกรมธนารักษ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4901,32 +4901,32 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=810bd451-770f-4032-86a0-1216954db79a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=36f30dd7-0674-4711-a8ba-e71eee8e8ed2</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการอาหารและยา</t>
+          <t>สำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>2110</v>
+        <v>502</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการค่าใช้จ่ายโครงการค่าจ้างบำรุงรักษาและซ่อมแซมห้องปฏิบัติการระบบเครือข่ายคอมพิวเตอร์ (Data Center) ของสำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4941,27 +4941,27 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=69d9687c-b7f1-405c-843e-92b98ad29261</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=056989d3-d491-44ed-b887-fca9a5a8f472</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>กรมส่งเสริมและพัฒนาคุณภาพชีวิตคนพิการ</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>2117</v>
+        <v>607</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อติดตั้งระบบกล้องวงจรปิด ของวิทยาลัยพยาบาลบรมราชชนนี นครศรีธรรมราช จำนวน 1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์งานบ้านงานครัวและครุภัณฑ์สำนักงาน จำนวน ๒๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>★ (กล้องวงจรปิด)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afa9b388-be98-4ed1-8fa9-0c791e5acf34</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f387eaf-54e2-4cf6-8c1c-826da6e3d09e</t>
         </is>
       </c>
     </row>
@@ -4988,15 +4988,15 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>กรมธนารักษ์</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>303</v>
+        <v>704</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการทำความสะอาดศูนย์คอมพิวเตอร์แห่งใหม่ ของกรมธนารักษ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี. หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บพร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=36f30dd7-0674-4711-a8ba-e71eee8e8ed2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b694aef3-f630-4422-a7fe-e31adb551c45</t>
         </is>
       </c>
     </row>
@@ -5023,15 +5023,15 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>502</v>
+        <v>704</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการค่าใช้จ่ายโครงการค่าจ้างบำรุงรักษาและซ่อมแซมห้องปฏิบัติการระบบเครือข่ายคอมพิวเตอร์ (Data Center) ของสำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องปรับอากาศแบบแยกส่วน (ราคารวมค่าติดตั้ง) แบบตั้งพื้นหรือแบบแขวน(ระบบ Inverter) ขนาดไม่ต่ำกว่า 36,000 บีทียู จำนวน 13 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=056989d3-d491-44ed-b887-fca9a5a8f472</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=08075ad1-9390-4520-9d46-f5c2637228e2</t>
         </is>
       </c>
     </row>
@@ -5058,15 +5058,15 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมและพัฒนาคุณภาพชีวิตคนพิการ</t>
+          <t>กรมส่งเสริมสหกรณ์</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>607</v>
+        <v>712</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์งานบ้านงานครัวและครุภัณฑ์สำนักงาน จำนวน ๒๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f387eaf-54e2-4cf6-8c1c-826da6e3d09e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=282d8226-b5a6-422f-ad5a-96682acbb042</t>
         </is>
       </c>
     </row>
@@ -5093,15 +5093,15 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>704</v>
+        <v>806</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี. หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บพร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องตรวจวัดปริมาณแอลกอฮอล์ จำนวน 10 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (แอลกอฮอล์)</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b694aef3-f630-4422-a7fe-e31adb551c45</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=152668c9-b054-48b8-9423-57975423ef48</t>
         </is>
       </c>
     </row>
@@ -5128,15 +5128,15 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมการเปลี่ยนแปลงสภาพภูมิอากาศและสิ่งแวดล้อม</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>704</v>
+        <v>908</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องปรับอากาศแบบแยกส่วน (ราคารวมค่าติดตั้ง) แบบตั้งพื้นหรือแบบแขวน(ระบบ Inverter) ขนาดไม่ต่ำกว่า 36,000 บีทียู จำนวน 13 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาอุปกรณ์ห้อง Data center และเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=08075ad1-9390-4520-9d46-f5c2637228e2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3fa0cd84-f2db-47df-b581-c3555885f305</t>
         </is>
       </c>
     </row>
@@ -5163,15 +5163,15 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมสหกรณ์</t>
+          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>712</v>
+        <v>1202</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์เครือข่ายและอุปกรณ์คอมพิวเตอร์แม่ข่าย และอุปกรณ์สำรองข้อมูล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=282d8226-b5a6-422f-ad5a-96682acbb042</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=86fe9b9f-c1ba-4f83-8b12-70dbc5d76baa</t>
         </is>
       </c>
     </row>
@@ -5198,15 +5198,15 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>806</v>
+        <v>1302</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องตรวจวัดปริมาณแอลกอฮอล์ จำนวน 10 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์สำหรับงานจดทะเบียนและตรวจสอบธุรกิจผิดกฎหมาย กลุ่มทะเบียนธุรกิจและอำนวยความสะดวกทางการค้าของสำนักงานพาณิชย์จังหวัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>★ (แอลกอฮอล์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=152668c9-b054-48b8-9423-57975423ef48</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=06246921-2a22-4f4d-822b-d5abae1c7c8c</t>
         </is>
       </c>
     </row>
@@ -5233,15 +5233,15 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>กรมการเปลี่ยนแปลงสภาพภูมิอากาศและสิ่งแวดล้อม</t>
+          <t>กรมสอบสวนคดีพิเศษ</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>908</v>
+        <v>1608</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาอุปกรณ์ห้อง Data center และเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าเช่าใช้บริการสายสัญญาณเชื่อมโยงเครือข่ายอินเตอร์เน็ตพร้อมระบบ Internet Data Center ประจำปีงบประมาณ พ.ศ. 2570 (เดือนตุลาคม 2569  เดือนกันยายน 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (สายสัญญาณ)</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3fa0cd84-f2db-47df-b581-c3555885f305</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f0c10124-df0c-410d-961c-bb4afe1ea16a</t>
         </is>
       </c>
     </row>
@@ -5268,15 +5268,15 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1202</v>
+        <v>1611</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์เครือข่ายและอุปกรณ์คอมพิวเตอร์แม่ข่าย และอุปกรณ์สำรองข้อมูล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบประชุมทางไกลผ่านจอภาพ (Video Conference)  ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5286,12 +5286,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
+          <t>★ (จอภาพ, ระบบประชุมทางไกล)</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=86fe9b9f-c1ba-4f83-8b12-70dbc5d76baa</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bb2e1625-bd6e-49b0-bf5e-6f3975c796e5</t>
         </is>
       </c>
     </row>
@@ -5303,15 +5303,15 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1302</v>
+        <v>2102</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์สำหรับงานจดทะเบียนและตรวจสอบธุรกิจผิดกฎหมาย กลุ่มทะเบียนธุรกิจและอำนวยความสะดวกทางการค้าของสำนักงานพาณิชย์จังหวัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันขนาดกลาง โรงพยาบาลเขาย้อย ตำบลเขาย้อย อำเภอเขาย้อย จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=06246921-2a22-4f4d-822b-d5abae1c7c8c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4d438ead-6d3b-40c3-8e25-0c855ca2699d</t>
         </is>
       </c>
     </row>
@@ -5338,15 +5338,15 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>กรมสอบสวนคดีพิเศษ</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1608</v>
+        <v>2102</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าเช่าใช้บริการสายสัญญาณเชื่อมโยงเครือข่ายอินเตอร์เน็ตพร้อมระบบ Internet Data Center ประจำปีงบประมาณ พ.ศ. 2570 (เดือนตุลาคม 2569  เดือนกันยายน 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง โรงพยาบาลหนองหญ้าปล้อง ตำบลหนองหญ้าปล้อง อำเภอหนองหญ้าปล้อง จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>★ (สายสัญญาณ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f0c10124-df0c-410d-961c-bb4afe1ea16a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=38179365-12e6-43e5-ac4b-973f7d7d62c9</t>
         </is>
       </c>
     </row>
@@ -5373,15 +5373,15 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1611</v>
+        <v>2102</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบประชุมทางไกลผ่านจอภาพ (Video Conference)  ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดัน ขนาดใหญ่ จำนวน 2 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -5391,12 +5391,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>★ (จอภาพ, ระบบประชุมทางไกล)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bb2e1625-bd6e-49b0-bf5e-6f3975c796e5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2c8651ab-6342-4cf7-b1d4-44acb01ef167</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันขนาดกลาง โรงพยาบาลเขาย้อย ตำบลเขาย้อย อำเภอเขาย้อย จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดเล็ก ของโรงพยาบาลชุมชน 2 แห่ง จำนวน 6 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4d438ead-6d3b-40c3-8e25-0c855ca2699d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=092dea18-169e-423d-bdf4-cbb905df5ef4</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง โรงพยาบาลหนองหญ้าปล้อง ตำบลหนองหญ้าปล้อง อำเภอหนองหญ้าปล้อง จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องเอกซเรย์เคลื่อนที่ขนาดไม่น้อยกว่า 300 mA.ขับเคลื่อนด้วยมอเตอร์ไฟฟ้า ของโรงพยาบาลในจังหวัดสุรินทร์ 3 แห่ง จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์, มอเตอร์)</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=38179365-12e6-43e5-ac4b-973f7d7d62c9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=587ceaac-9b51-4f53-a40b-ba6307295dbc</t>
         </is>
       </c>
     </row>
@@ -5478,15 +5478,15 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมการแพทย์แผนไทยและการแพทย์ทางเลือก</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>2102</v>
+        <v>2105</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดัน ขนาดใหญ่ จำนวน 2 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างบำรุงรักษาและซ่อมแซมแก้ไขปัญหาเครื่องคอมพิวเตอร์แม่ข่ายและอุปกรณ์ระบบเครือข่าย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2c8651ab-6342-4cf7-b1d4-44acb01ef167</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a18ab514-a7bf-42a3-be34-78ab2073afdd</t>
         </is>
       </c>
     </row>
@@ -5513,15 +5513,15 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>2102</v>
+        <v>2106</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดเล็ก ของโรงพยาบาลชุมชน 2 แห่ง จำนวน 6 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน ๙ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5531,12 +5531,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=092dea18-169e-423d-bdf4-cbb905df5ef4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70e80b61-ece5-4761-bcba-cb1ce4f2a872</t>
         </is>
       </c>
     </row>
@@ -5548,15 +5548,15 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>2102</v>
+        <v>2117</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องเอกซเรย์เคลื่อนที่ขนาดไม่น้อยกว่า 300 mA.ขับเคลื่อนด้วยมอเตอร์ไฟฟ้า ของโรงพยาบาลในจังหวัดสุรินทร์ 3 แห่ง จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อึครุภัณฑ์สำนักงาน รายการเครื่องปรับอากาศและพัดลม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์, มอเตอร์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ, พัดลม)</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=587ceaac-9b51-4f53-a40b-ba6307295dbc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8cf26d57-cf1b-4ebf-8134-fcf45b7f7c54</t>
         </is>
       </c>
     </row>
@@ -5583,15 +5583,15 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>กรมการแพทย์แผนไทยและการแพทย์ทางเลือก</t>
+          <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>2105</v>
+        <v>2117</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างบำรุงรักษาและซ่อมแซมแก้ไขปัญหาเครื่องคอมพิวเตอร์แม่ข่ายและอุปกรณ์ระบบเครือข่าย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง (รถยนต์บรรทุกโดยสาร 6 ล้อ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -5601,32 +5601,32 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a18ab514-a7bf-42a3-be34-78ab2073afdd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=37a7653e-4e42-4513-bc7a-c74cd6a83f90</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>กรมวิทยาศาสตร์การแพทย์</t>
+          <t>สถาบันเทคโนโลยีป้องกันประเทศ</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>2106</v>
+        <v>209</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน ๙ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างซ่อมบำรุงตามวงรอบเครื่องปรับอากาศ อาคาร สป. (แจ้งวัฒนะ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5636,32 +5636,32 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70e80b61-ece5-4761-bcba-cb1ce4f2a872</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=97592008-d14e-46f6-93ee-062a71e2e9a9</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>สำนักงานปลัดกระทรวงการคลัง</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>2117</v>
+        <v>302</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อึครุภัณฑ์สำนักงาน รายการเครื่องปรับอากาศและพัดลม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อการจัดซื้อหมึกพิมพ์สำหรับ GFMIS Terminal Set เพื่อใช้งานในระบบ New GFMIS Thai ของกรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5671,32 +5671,32 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ, พัดลม)</t>
+          <t>★ (หมึกพิมพ์)</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8cf26d57-cf1b-4ebf-8134-fcf45b7f7c54</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=95f4ee7d-0617-43e5-8099-6f58ee3f83c4</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>กรมชลประทาน</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>2117</v>
+        <v>703</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง (รถยนต์บรรทุกโดยสาร 6 ล้อ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจัดหาและติดตั้งเครื่องสูบน้ำชนิดหอยโข่งแบบ Horizontal Split Case ขับด้วยมอเตอร์ไฟฟ้าอัตราสูบน้ำ ๐.๒๕ ลบ.ม. /วินาที ระยะยกน้ำไม่น้อยกว่า ๔๕ เมตร และอื่นๆ รวม ๔ รายการ  สำหรับงานสถานีสูบน้ำด้วยไฟฟ้าพร้อมระบบส่งน้ำ บ้านสุขสำราญ ตำบลเหล่าต่างคำ อำเภอโพนพิสัย จังหวัดหนองคาย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=37a7653e-4e42-4513-bc7a-c74cd6a83f90</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=766b91be-9aee-491f-bc67-3378c2319ca0</t>
         </is>
       </c>
     </row>
@@ -5723,15 +5723,15 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>สถาบันเทคโนโลยีป้องกันประเทศ</t>
+          <t>กรมประมง</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>209</v>
+        <v>705</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างซ่อมบำรุงตามวงรอบเครื่องปรับอากาศ อาคาร สป. (แจ้งวัฒนะ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน 4 รายการ วิธีประกาศเชิญชวน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=97592008-d14e-46f6-93ee-062a71e2e9a9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6af84224-9211-4bd4-b2c3-7790e12e9c3f</t>
         </is>
       </c>
     </row>
@@ -5758,15 +5758,15 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการคลัง</t>
+          <t>กรมประมง</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>302</v>
+        <v>705</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อการจัดซื้อหมึกพิมพ์สำหรับ GFMIS Terminal Set เพื่อใช้งานในระบบ New GFMIS Thai ของกรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน 4 รายการ  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>★ (หมึกพิมพ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=95f4ee7d-0617-43e5-8099-6f58ee3f83c4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=106fd353-637b-4b85-b19c-e5222b434807</t>
         </is>
       </c>
     </row>
@@ -5793,15 +5793,15 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>กรมชลประทาน</t>
+          <t>สำนักงานเศรษฐกิจการเกษตร</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>703</v>
+        <v>715</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจัดหาและติดตั้งเครื่องสูบน้ำชนิดหอยโข่งแบบ Horizontal Split Case ขับด้วยมอเตอร์ไฟฟ้าอัตราสูบน้ำ ๐.๒๕ ลบ.ม. /วินาที ระยะยกน้ำไม่น้อยกว่า ๔๕ เมตร และอื่นๆ รวม ๔ รายการ  สำหรับงานสถานีสูบน้ำด้วยไฟฟ้าพร้อมระบบส่งน้ำ บ้านสุขสำราญ ตำบลเหล่าต่างคำ อำเภอโพนพิสัย จังหวัดหนองคาย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์หรือระบบสารสนเทศ (โครงการจ้างบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์เครือข่ายและเครื่องคอมพิวเตอร์แม่ข่าย ประจำปีงบประมาณ พ.ศ. 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=766b91be-9aee-491f-bc67-3378c2319ca0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e3936fb8-2fe4-4ded-a393-134ec5675427</t>
         </is>
       </c>
     </row>
@@ -5828,15 +5828,15 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>กรมประมง</t>
+          <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>705</v>
+        <v>804</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน 4 รายการ วิธีประกาศเชิญชวน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์พร้อมอุปกรณ์ของระบบการคุ้มครองผู้โดยสารและ การบังคับใช้กฎหมายทั่วไทย (1584 และปรับทั่วไทย) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6af84224-9211-4bd4-b2c3-7790e12e9c3f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f5c51a3c-9d4b-4662-a9c5-a560b97ab60f</t>
         </is>
       </c>
     </row>
@@ -5863,15 +5863,15 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>กรมประมง</t>
+          <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>705</v>
+        <v>804</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน 4 รายการ  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างรั้ว ประตูทางเข้า - ออก ป้ายชื่อสำนักงาน และป้อมยามรักษาการณ์ สำนักงานขนส่งจังหวัดลำปาง ตำบลพระบาท อำเภอเมือง จังหวัดลำปาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -5881,12 +5881,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ป้ายชื่อ)</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=106fd353-637b-4b85-b19c-e5222b434807</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f104579c-ae74-4bdb-a71c-250b1777b2c9</t>
         </is>
       </c>
     </row>
@@ -5898,15 +5898,15 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>สำนักงานเศรษฐกิจการเกษตร</t>
+          <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>715</v>
+        <v>804</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์หรือระบบสารสนเทศ (โครงการจ้างบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์เครือข่ายและเครื่องคอมพิวเตอร์แม่ข่าย ประจำปีงบประมาณ พ.ศ. 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขเครื่องคอมพิวเตอร์พร้อมอุปกรณ์ที่ใช้ในการพัฒนาความรู้สารสนเทศ  ด้านความปลอดภัยของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e3936fb8-2fe4-4ded-a393-134ec5675427</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a8c5a924-f969-4f66-a783-51c748bd5141</t>
         </is>
       </c>
     </row>
@@ -5933,15 +5933,15 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
+          <t>กรมอุตุนิยมวิทยา</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>804</v>
+        <v>1104</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์พร้อมอุปกรณ์ของระบบการคุ้มครองผู้โดยสารและ การบังคับใช้กฎหมายทั่วไทย (1584 และปรับทั่วไทย) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาอุปกรณ์กระจายสัญญาณหลัก (Core Switch) ประจำปีงบประมาณ พ.ศ.2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f5c51a3c-9d4b-4662-a9c5-a560b97ab60f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b6951565-26a5-4131-b672-af48d4974842</t>
         </is>
       </c>
     </row>
@@ -5968,15 +5968,15 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
+          <t>กรมที่ดิน</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>804</v>
+        <v>1505</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างรั้ว ประตูทางเข้า - ออก ป้ายชื่อสำนักงาน และป้อมยามรักษาการณ์ สำนักงานขนส่งจังหวัดลำปาง ตำบลพระบาท อำเภอเมือง จังหวัดลำปาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโต๊ะและเก้าอี้เพื่อใช้ในราชการของสำนักงานที่ดินจังหวัดพิษณุโลก และสาขา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -5986,12 +5986,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>★ (ป้ายชื่อ)</t>
+          <t>★ (โต๊ะ, เก้าอี้)</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f104579c-ae74-4bdb-a71c-250b1777b2c9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=06a6ae3e-1109-434c-becf-df99302f96f5</t>
         </is>
       </c>
     </row>
@@ -6003,15 +6003,15 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
+          <t>กรมที่ดิน</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>804</v>
+        <v>1505</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขเครื่องคอมพิวเตอร์พร้อมอุปกรณ์ที่ใช้ในการพัฒนาความรู้สารสนเทศ  ด้านความปลอดภัยของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบงานและอุปกรณ์คอมพิวเตอร์ ตามโครงการพัฒนาระบบสารสนเทศที่ดิน (ระยะที่ ๒) ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a8c5a924-f969-4f66-a783-51c748bd5141</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0e343fde-5a22-4f02-b2b3-bcf7cfd99bf2</t>
         </is>
       </c>
     </row>
@@ -6038,15 +6038,15 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>กรมอุตุนิยมวิทยา</t>
+          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1104</v>
+        <v>1808</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาอุปกรณ์กระจายสัญญาณหลัก (Core Switch) ประจำปีงบประมาณ พ.ศ.2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์การศึกษา (ห้องเรียนอัจฉริยะไฮบริด Smart Hybrid Classroom) ห้องเรียนวิชาชีพ จำนวน 1 ห้อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b6951565-26a5-4131-b672-af48d4974842</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a6ddc2c9-4ad2-4cd7-93c9-2b5e9a715cfd</t>
         </is>
       </c>
     </row>
@@ -6073,15 +6073,15 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>กรมที่ดิน</t>
+          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1505</v>
+        <v>1808</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโต๊ะและเก้าอี้เพื่อใช้ในราชการของสำนักงานที่ดินจังหวัดพิษณุโลก และสาขา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์โฆษณาแะเผยแพร่ (ระบบภาพ LED Display พร้อมติดตั้งภายนอกอาคาร) จำนวน  1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>★ (โต๊ะ, เก้าอี้)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=06a6ae3e-1109-434c-becf-df99302f96f5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7b99fd52-1723-486a-a5ce-43a450641ed9</t>
         </is>
       </c>
     </row>
@@ -6108,15 +6108,15 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>กรมที่ดิน</t>
+          <t>สำนักงานนวัตกรรมแห่งชาติ (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1505</v>
+        <v>1913</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบงานและอุปกรณ์คอมพิวเตอร์ ตามโครงการพัฒนาระบบสารสนเทศที่ดิน (ระยะที่ ๒) ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างเหมาบริการบำรุงรักษาอุปกรณ์ภายในศูนย์ข้อมูลคอมพิวเตอร์(Data Center) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0e343fde-5a22-4f02-b2b3-bcf7cfd99bf2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70ea1f2e-64d2-48c7-888f-f39d061663c3</t>
         </is>
       </c>
     </row>
@@ -6143,15 +6143,15 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1808</v>
+        <v>2102</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์การศึกษา (ห้องเรียนอัจฉริยะไฮบริด Smart Hybrid Classroom) ห้องเรียนวิชาชีพ จำนวน 1 ห้อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a6ddc2c9-4ad2-4cd7-93c9-2b5e9a715cfd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5dcaa2f-3e4d-49bc-9324-4c94f510ab5f</t>
         </is>
       </c>
     </row>
@@ -6178,15 +6178,15 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1808</v>
+        <v>2102</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์โฆษณาแะเผยแพร่ (ระบบภาพ LED Display พร้อมติดตั้งภายนอกอาคาร) จำนวน  1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องควบคุมการให้สารน้ำทางหลอดเลือดดำชนิด 1 สาย ของโรงพยาบาลในจังหวัดสุรินทร์ 9 แห่ง จำนวน 66 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7b99fd52-1723-486a-a5ce-43a450641ed9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=af446873-e18e-4ed1-bd5c-bd34b74e9b76</t>
         </is>
       </c>
     </row>
@@ -6213,15 +6213,15 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>สำนักงานนวัตกรรมแห่งชาติ (องค์การมหาชน)</t>
+          <t>กรมการแพทย์</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1913</v>
+        <v>2103</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างเหมาบริการบำรุงรักษาอุปกรณ์ภายในศูนย์ข้อมูลคอมพิวเตอร์(Data Center) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์เครื่องเสริมสร้างความแข็งแรงของกล้ามเนื้ออุ้งเชิงกราน รักษาอาการปัสสาวะเล็ด ลดอาการปวดจากกล้ามเนื้อและระบบประสาทบริเวณ อุ้งเชิงกรานและหลังด้วยคลื่นแม่เหล็กไฟฟ้า สถาบันเวชศาสตร์สมเด็จพระสังฆราชญาณสังวรเพื่อผู้สูงอายุ ตำบลตลาดขวัญ อำเภอเมือง จังหวัดนนทบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -6231,32 +6231,32 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70ea1f2e-64d2-48c7-888f-f39d061663c3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=543d641e-2bab-40db-bddc-5b9d81caf16b</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>2102</v>
+        <v>204</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำหรับงานซ่อมปรับปรุงสนามกีฬาของ หน่วยบัญชาการสงครามพิเศษ เพื่อรองรับการแข่งขันกีฬา กองทัพบก ครั้งที่ 74 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -6271,27 +6271,27 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5dcaa2f-3e4d-49bc-9324-4c94f510ab5f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=91712891-37fd-4bbc-ae6c-0044106ce3a9</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>2102</v>
+        <v>704</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องควบคุมการให้สารน้ำทางหลอดเลือดดำชนิด 1 สาย ของโรงพยาบาลในจังหวัดสุรินทร์ 9 แห่ง จำนวน 66 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะ รถโดยสารขนาด 12 ที่นั่ง (ดีเซล) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -6306,27 +6306,27 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=af446873-e18e-4ed1-bd5c-bd34b74e9b76</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6d9307c6-812c-4689-9154-bd79b77edeed</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>กรมการแพทย์</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>2103</v>
+        <v>704</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์เครื่องเสริมสร้างความแข็งแรงของกล้ามเนื้ออุ้งเชิงกราน รักษาอาการปัสสาวะเล็ด ลดอาการปวดจากกล้ามเนื้อและระบบประสาทบริเวณ อุ้งเชิงกรานและหลังด้วยคลื่นแม่เหล็กไฟฟ้า สถาบันเวชศาสตร์สมเด็จพระสังฆราชญาณสังวรเพื่อผู้สูงอายุ ตำบลตลาดขวัญ อำเภอเมือง จังหวัดนนทบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องคอมพิวเตอร์โน๊ตบุ๊ค สำหรับงานประมวลผล พร้อมชุดโปรแกรมระบบปฏิบัติการสำหรับคอมพิวเตอร์และเครี่องคอมพิวเตอร์โน๊ตบุ๊ค แบบสิทธิการใช้งานภายในสำนักงาน ประเภทติดตั้งมาจากโรงงาน (OEM) ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย ชุดโปรแกรมจัดการสำนักงาน แบบที่ 2   ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย และชุดโปรแกรมป้องกันไวรัส จำนวน 21 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, โน๊ตบุ๊ค, ระบบปฏิบัติการ, โปรแกรมป้องกันไวรัส)</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=543d641e-2bab-40db-bddc-5b9d81caf16b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ac28390d-f1a5-41e3-8fed-7350ce5638bc</t>
         </is>
       </c>
     </row>
@@ -6353,15 +6353,15 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>204</v>
+        <v>805</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์สำหรับงานซ่อมปรับปรุงสนามกีฬาของ หน่วยบัญชาการสงครามพิเศษ เพื่อรองรับการแข่งขันกีฬา กองทัพบก ครั้งที่ 74 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานหัวหิน ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (รถเข็น)</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=91712891-37fd-4bbc-ae6c-0044106ce3a9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f40b4d90-5120-4848-a5d2-b177de8a9a09</t>
         </is>
       </c>
     </row>
@@ -6388,15 +6388,15 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมพัฒนาธุรกิจการค้า</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>704</v>
+        <v>1308</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะ รถโดยสารขนาด 12 ที่นั่ง (ดีเซล) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์แม่ข่ายและอุปกรณ์รักษาความปลอดภัย ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6d9307c6-812c-4689-9154-bd79b77edeed</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=652c12bb-908d-48aa-a87c-f244b33e9ad3</t>
         </is>
       </c>
     </row>
@@ -6423,15 +6423,15 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมที่ดิน</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>704</v>
+        <v>1505</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องคอมพิวเตอร์โน๊ตบุ๊ค สำหรับงานประมวลผล พร้อมชุดโปรแกรมระบบปฏิบัติการสำหรับคอมพิวเตอร์และเครี่องคอมพิวเตอร์โน๊ตบุ๊ค แบบสิทธิการใช้งานภายในสำนักงาน ประเภทติดตั้งมาจากโรงงาน (OEM) ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย ชุดโปรแกรมจัดการสำนักงาน แบบที่ 2   ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย และชุดโปรแกรมป้องกันไวรัส จำนวน 21 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมอุปกรณ์ รวม ๘ รายการ สำหรับใช้ในราชการกองเทคโนโลยีทำแผนที่ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, โน๊ตบุ๊ค, ระบบปฏิบัติการ, โปรแกรมป้องกันไวรัส)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ac28390d-f1a5-41e3-8fed-7350ce5638bc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c85d670f-a209-4413-8ade-5dba1d3d0298</t>
         </is>
       </c>
     </row>
@@ -6458,15 +6458,15 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
+          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>805</v>
+        <v>1905</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานหัวหิน ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์โครงการห้องปฏิบัติการทดสอบด้านวิศวกรรมการใช้งาน (Usability Engineering) ผลิตภัณฑ์ซอฟต์แวร์หุ่นยนต์ทางการแพทย์และเครื่องมือแพทย์ตามมาตรฐานสากล (Usability Engineering Laboratories for Software, Medical Robotics, and Medical Devices under International Standards) จํานวน ๑ ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>★ (รถเข็น)</t>
+          <t>★ (ซอฟต์แวร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f40b4d90-5120-4848-a5d2-b177de8a9a09</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0415b5bd-8794-467b-9e54-5ae4bdabae87</t>
         </is>
       </c>
     </row>
@@ -6493,15 +6493,15 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>กรมพัฒนาธุรกิจการค้า</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1308</v>
+        <v>2102</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์แม่ข่ายและอุปกรณ์รักษาความปลอดภัย ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องอุ่นเลือดและส่วนประกอบของเลือดชนิดไม่สัมผัสน้ำสามารถอุ่นเลือดได้ พร้อมกันไม่น้อยกว่า 3 ถุง จำนวน 4 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย -  กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=652c12bb-908d-48aa-a87c-f244b33e9ad3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2157b09f-d16e-4bcf-b720-de1088bc7b0e</t>
         </is>
       </c>
     </row>
@@ -6528,15 +6528,15 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>กรมที่ดิน</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1505</v>
+        <v>2102</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมอุปกรณ์ รวม ๘ รายการ สำหรับใช้ในราชการกองเทคโนโลยีทำแผนที่ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องควบคุมการให้สารละลายโดยใช้กระบอกฉีด ของโรงพยาบาลในจังหวัดสุรินทร์ 5 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบลสำเภาลูน จำนวน 26 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -6546,12 +6546,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c85d670f-a209-4413-8ade-5dba1d3d0298</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=33f2d0df-213d-44c4-a6fa-d31b0eb2e1f6</t>
         </is>
       </c>
     </row>
@@ -6563,15 +6563,15 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1905</v>
+        <v>2106</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์โครงการห้องปฏิบัติการทดสอบด้านวิศวกรรมการใช้งาน (Usability Engineering) ผลิตภัณฑ์ซอฟต์แวร์หุ่นยนต์ทางการแพทย์และเครื่องมือแพทย์ตามมาตรฐานสากล (Usability Engineering Laboratories for Software, Medical Robotics, and Medical Devices under International Standards) จํานวน ๑ ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาซ่อมแซมแก้ไขระบบเครือข่ายและเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -6581,12 +6581,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>★ (ซอฟต์แวร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0415b5bd-8794-467b-9e54-5ae4bdabae87</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=77d1f891-c26e-4f3d-a9e2-7ca16c4196b3</t>
         </is>
       </c>
     </row>
@@ -6598,15 +6598,15 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>2102</v>
+        <v>2107</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องอุ่นเลือดและส่วนประกอบของเลือดชนิดไม่สัมผัสน้ำสามารถอุ่นเลือดได้ พร้อมกันไม่น้อยกว่า 3 ถุง จำนวน 4 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย -  กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2157b09f-d16e-4bcf-b720-de1088bc7b0e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b600d06e-5f90-400c-80fc-24c6ae2ef280</t>
         </is>
       </c>
     </row>
@@ -6633,15 +6633,15 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>2102</v>
+        <v>2117</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องควบคุมการให้สารละลายโดยใช้กระบอกฉีด ของโรงพยาบาลในจังหวัดสุรินทร์ 5 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบลสำเภาลูน จำนวน 26 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์วิทยาศาสตร์การแพทย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=33f2d0df-213d-44c4-a6fa-d31b0eb2e1f6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a3db48e8-9e8b-4535-84a6-a14f5811619b</t>
         </is>
       </c>
     </row>
@@ -6668,15 +6668,15 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>กรมวิทยาศาสตร์การแพทย์</t>
+          <t>สำนักงานพระพุทธศาสนาแห่งชาติ</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>2106</v>
+        <v>2503</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาซ่อมแซมแก้ไขระบบเครือข่ายและเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -6686,32 +6686,32 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=77d1f891-c26e-4f3d-a9e2-7ca16c4196b3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=285cc870-c52b-429d-b866-52f939bc7fd0</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>กรมสนับสนุนบริการสุขภาพ</t>
+          <t>กรมพัฒนาที่ดิน</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>2107</v>
+        <v>708</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจอแสดงผล LED พร้อมอุปกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -6721,32 +6721,32 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (จอแสดงผล)</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b600d06e-5f90-400c-80fc-24c6ae2ef280</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=45d8cd64-624e-4582-a8d1-3fe3d01e41b6</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>กรมการข้าว</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>2117</v>
+        <v>718</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์วิทยาศาสตร์การแพทย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องปรับอากาศ แบบแยกส่วน แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -6756,32 +6756,32 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a3db48e8-9e8b-4535-84a6-a14f5811619b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2475fb18-8633-42d5-8fe6-f520615dc6f7</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>สำนักงานพระพุทธศาสนาแห่งชาติ</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>2503</v>
+        <v>806</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ และ ครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 13 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=285cc870-c52b-429d-b866-52f939bc7fd0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0b00828b-7442-420e-85c9-ad09d2f6e16f</t>
         </is>
       </c>
     </row>
@@ -6808,15 +6808,15 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>กรมพัฒนาที่ดิน</t>
+          <t>กรมทรัพยากรน้ำบาดาล</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>708</v>
+        <v>907</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจอแสดงผล LED พร้อมอุปกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องสูบน้ำไฟฟ้าชนิดมอเตอร์จุ่มใต้น้ำ พร้อมอุปกรณ์ และชุดฝาปิดปากบ่อน้ำบาดาล จำนวน ๖ ชุด โครงการพัฒนาน้ำบาดาลเพื่อความมั่นคงระดับชุมชน ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ (งบเหลือจ่าย) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -6826,12 +6826,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>★ (จอแสดงผล)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=45d8cd64-624e-4582-a8d1-3fe3d01e41b6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=03ba8462-a0d1-4d13-92c2-a7ae76fed3d0</t>
         </is>
       </c>
     </row>
@@ -6843,15 +6843,15 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>กรมการข้าว</t>
+          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>718</v>
+        <v>909</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องปรับอากาศ แบบแยกส่วน แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทเรือหางยาวสำหรับการลาดตระเวนพื้นที่ทางน้ำ เพื่อเพิ่มประสิทธิภาพการปฏิบัติงานอุทยานแห่งชาติเขาแหลม จังหวัดกาญจนบุรี  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -6861,12 +6861,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2475fb18-8633-42d5-8fe6-f520615dc6f7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63f7333f-eb0c-40fa-8c06-5f683d543bce</t>
         </is>
       </c>
     </row>
@@ -6878,15 +6878,15 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>กรมการปกครอง</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>806</v>
+        <v>1503</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ และ ครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 13 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อวัสดุครุภัณฑ์สำนักงานที่ทำการปกครองอำเภอตาพระยา จังหวัดสระแก้ว ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -6896,12 +6896,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0b00828b-7442-420e-85c9-ad09d2f6e16f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=de60da4a-56f9-434f-bd1c-60d19d95f672</t>
         </is>
       </c>
     </row>
@@ -6913,15 +6913,15 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>กรมทรัพยากรน้ำบาดาล</t>
+          <t>กรมที่ดิน</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>907</v>
+        <v>1505</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องสูบน้ำไฟฟ้าชนิดมอเตอร์จุ่มใต้น้ำ พร้อมอุปกรณ์ และชุดฝาปิดปากบ่อน้ำบาดาล จำนวน ๖ ชุด โครงการพัฒนาน้ำบาดาลเพื่อความมั่นคงระดับชุมชน ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ (งบเหลือจ่าย) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์เพื่อการบริหารจัดการหน่วยงานส่วนกลาง (Hardware และ Software) ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=03ba8462-a0d1-4d13-92c2-a7ae76fed3d0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a80802ed-6d42-4b60-b93c-de21fb24e5c0</t>
         </is>
       </c>
     </row>
@@ -6948,15 +6948,15 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
+          <t>กรมการจัดหางาน</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>909</v>
+        <v>1703</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทเรือหางยาวสำหรับการลาดตระเวนพื้นที่ทางน้ำ เพื่อเพิ่มประสิทธิภาพการปฏิบัติงานอุทยานแห่งชาติเขาแหลม จังหวัดกาญจนบุรี  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ทดแทนและเพิ่มประสิทธิภาพของสำนักบริหารแรงงานต่างด้าว ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63f7333f-eb0c-40fa-8c06-5f683d543bce</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f3092a7e-5bf1-488f-8f3f-6657ba0fe2fd</t>
         </is>
       </c>
     </row>
@@ -6983,15 +6983,15 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>กรมการปกครอง</t>
+          <t>กรมพัฒนาฝีมือแรงงาน</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1503</v>
+        <v>1704</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อวัสดุครุภัณฑ์สำนักงานที่ทำการปกครองอำเภอตาพระยา จังหวัดสระแก้ว ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ (ระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop) ขนาด 3 เฟส 15 กิโลวัตต์ ตำบลบ่อ อำเภอขลุง จังหวัดจันทบุรี จำนวน 1 ระบบ และระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop) ขนาด 3 เฟส 20 กิโลวัตต์ ตำบลบ่อ อำเภอขลุง จังหวัดจันทบุรี จำนวน 1 ระบบ) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -7001,12 +7001,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=de60da4a-56f9-434f-bd1c-60d19d95f672</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d90e4389-d0ce-48d4-b93a-03874d22d178</t>
         </is>
       </c>
     </row>
@@ -7018,15 +7018,15 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>กรมที่ดิน</t>
+          <t>กรมการศาสนา</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1505</v>
+        <v>1803</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์เพื่อการบริหารจัดการหน่วยงานส่วนกลาง (Hardware และ Software) ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อหมึกเครื่องพิมพ์ (ครั้งที่ 2)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -7036,12 +7036,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (หมึกเครื่องพิมพ์, เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a80802ed-6d42-4b60-b93c-de21fb24e5c0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8ffdb256-bac2-4342-bdf6-7616e2ae5b25</t>
         </is>
       </c>
     </row>
@@ -7053,15 +7053,15 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>กรมการจัดหางาน</t>
+          <t>สถาบันมาตรวิทยาแห่งชาติ</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1703</v>
+        <v>1907</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ทดแทนและเพิ่มประสิทธิภาพของสำนักบริหารแรงงานต่างด้าว ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างค่าบำรุงรักษาอุปกรณ์เครือข่ายประจำอาคาร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -7071,12 +7071,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (อุปกรณ์เครือข่าย)</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f3092a7e-5bf1-488f-8f3f-6657ba0fe2fd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b698a86e-10e2-45f2-be5e-f7ec03fa0ce9</t>
         </is>
       </c>
     </row>
@@ -7088,15 +7088,15 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>กรมพัฒนาฝีมือแรงงาน</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1704</v>
+        <v>2102</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ (ระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop) ขนาด 3 เฟส 15 กิโลวัตต์ ตำบลบ่อ อำเภอขลุง จังหวัดจันทบุรี จำนวน 1 ระบบ และระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop) ขนาด 3 เฟส 20 กิโลวัตต์ ตำบลบ่อ อำเภอขลุง จังหวัดจันทบุรี จำนวน 1 ระบบ) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการรถพยาบาลพร้อมอุปกรณ์ช่วยชีวิตชั้นสูง ของโรงพยาบาลชุมชน 4 แห่ง จำนวน 4 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d90e4389-d0ce-48d4-b93a-03874d22d178</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f77b490-654b-45ac-9d8e-cc1f4f3fd4fb</t>
         </is>
       </c>
     </row>
@@ -7123,15 +7123,15 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>กรมการศาสนา</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1803</v>
+        <v>2102</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อหมึกเครื่องพิมพ์ (ครั้งที่ 2)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดออกซิเจนในเลือดอัตโนมัติชนิดพกพา จำนวน 39 เครื่องๆ งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>★ (หมึกเครื่องพิมพ์, เครื่องพิมพ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8ffdb256-bac2-4342-bdf6-7616e2ae5b25</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f13af428-4413-4d73-9542-bd582ed6e240</t>
         </is>
       </c>
     </row>
@@ -7158,15 +7158,15 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>สถาบันมาตรวิทยาแห่งชาติ</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1907</v>
+        <v>2102</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างค่าบำรุงรักษาอุปกรณ์เครือข่ายประจำอาคาร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจคลื่นไฟฟ้าหัวใจ พร้อมเชื่อมต่อระบบแพทย์ทางไกล จำนวน 27 เครื่อง งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>★ (อุปกรณ์เครือข่าย)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b698a86e-10e2-45f2-be5e-f7ec03fa0ce9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9350a991-2cda-4337-b005-93d114caf75c</t>
         </is>
       </c>
     </row>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการรถพยาบาลพร้อมอุปกรณ์ช่วยชีวิตชั้นสูง ของโรงพยาบาลชุมชน 4 แห่ง จำนวน 4 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการตู้เย็นเก็บเลือด ขนาดไม่น้อยกว่า 20 คิว จำนวน 4 ตู้ งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์  การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -7211,12 +7211,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์, ตู้เย็น)</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f77b490-654b-45ac-9d8e-cc1f4f3fd4fb</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=83dc4a91-4e74-465d-b378-562e91d2b662</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดออกซิเจนในเลือดอัตโนมัติชนิดพกพา จำนวน 39 เครื่องๆ งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ เครื่องให้การรักษาอาการปวดและกระตุ้นเซลล์ประสาทส่วนปลายด้วยสนามแม่เหล็กไฟฟ้า(PMS) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f13af428-4413-4d73-9542-bd582ed6e240</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=35bbde9c-eb8e-445f-b94e-915454477995</t>
         </is>
       </c>
     </row>
@@ -7263,15 +7263,15 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>2102</v>
+        <v>2106</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจคลื่นไฟฟ้าหัวใจ พร้อมเชื่อมต่อระบบแพทย์ทางไกล จำนวน 27 เครื่อง งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมระบบปฏิบัติการและชุดโปรแกรมจัดการสำนักงาน จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -7281,12 +7281,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ระบบปฏิบัติการ, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9350a991-2cda-4337-b005-93d114caf75c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=414ac115-ac50-4d65-a54d-d2a9e03b621b</t>
         </is>
       </c>
     </row>
@@ -7298,15 +7298,15 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>2102</v>
+        <v>2107</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการตู้เย็นเก็บเลือด ขนาดไม่น้อยกว่า 20 คิว จำนวน 4 ตู้ งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์  การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ เครื่องวิเคราะห์การทำงานตู้อบเด็ก จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -7316,32 +7316,32 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์, ตู้เย็น)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=83dc4a91-4e74-465d-b378-562e91d2b662</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9d04622a-81b1-4cfd-9a05-6c2aec6751f7</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมบัญชีกลาง</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>2102</v>
+        <v>304</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ เครื่องให้การรักษาอาการปวดและกระตุ้นเซลล์ประสาทส่วนปลายด้วยสนามแม่เหล็กไฟฟ้า(PMS) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาและซ่อมแซมแก้ไขเครื่องปรับอากาศ (แบบรวมอะไหล่) จำนวน 474 เครื่อง ซ่อมแซมแก้ไขระบบไฟฟ้า และระบบสุขาภิบาล อาคาร 3 อาคาร 9 อาคารใหม่ ชั้นใต้ดิน และห้องลิฟต์ กรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -7351,32 +7351,32 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=35bbde9c-eb8e-445f-b94e-915454477995</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=273a8add-ac17-48f1-8ff9-c94a946e8273</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>กรมวิทยาศาสตร์การแพทย์</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>2106</v>
+        <v>704</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมระบบปฏิบัติการและชุดโปรแกรมจัดการสำนักงาน จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -7386,32 +7386,32 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ระบบปฏิบัติการ, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=414ac115-ac50-4d65-a54d-d2a9e03b621b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1607645e-ac86-48f0-a820-917a3a4fe54d</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>กรมสนับสนุนบริการสุขภาพ</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>2107</v>
+        <v>704</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ เครื่องวิเคราะห์การทำงานตู้อบเด็ก จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ พร้อมชุดโปรแกรมปฎิบัติงาน โปรแกรมจัดการสำนักงาน และโปรแกรมป้องกันไวรัส จำนวน 18 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, โปรแกรมป้องกันไวรัส, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9d04622a-81b1-4cfd-9a05-6c2aec6751f7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0511e3cd-537d-45d3-880c-de7433b1eb48</t>
         </is>
       </c>
     </row>
@@ -7438,17 +7438,15 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>กรมบัญชีกลาง</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>0304</t>
-        </is>
+          <t>กรมประมง</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>705</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาและซ่อมแซมแก้ไขเครื่องปรับอากาศ (แบบรวมอะไหล่) จำนวน 474 เครื่อง ซ่อมแซมแก้ไขระบบไฟฟ้า และระบบสุขาภิบาล อาคาร 3 อาคาร 9 อาคารใหม่ ชั้นใต้ดิน และห้องลิฟต์ กรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อชุดจอภาพ LED พร้อมงานติดตั้งสำหรับห้องประชุมอานนท์ กรมประมง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -7458,12 +7456,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (จอภาพ)</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=273a8add-ac17-48f1-8ff9-c94a946e8273</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b0679766-012d-497b-8e41-2296e1c7ba51</t>
         </is>
       </c>
     </row>
@@ -7475,17 +7473,15 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>0704</t>
-        </is>
+          <t>กรมปศุสัตว์</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>706</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -7495,12 +7491,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1607645e-ac86-48f0-a820-917a3a4fe54d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f70d294-53f0-4fd1-b9bc-ef06d20b1657</t>
         </is>
       </c>
     </row>
@@ -7512,17 +7508,15 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>0704</t>
-        </is>
+          <t>สำนักงานนโยบายและแผนการขนส่งและจราจร</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>808</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ พร้อมชุดโปรแกรมปฎิบัติงาน โปรแกรมจัดการสำนักงาน และโปรแกรมป้องกันไวรัส จำนวน 18 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์ของ สนข. ประจำปีงบประมาณ พ.ศ. 2570  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -7532,12 +7526,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, โปรแกรมป้องกันไวรัส, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0511e3cd-537d-45d3-880c-de7433b1eb48</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=069d5584-a6b1-426d-9714-115f2fdc7025</t>
         </is>
       </c>
     </row>
@@ -7549,17 +7543,15 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>กรมประมง</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>0705</t>
-        </is>
+          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>904</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อชุดจอภาพ LED พร้อมงานติดตั้งสำหรับห้องประชุมอานนท์ กรมประมง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาและเพิ่มประสิทธิภาพระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรทางทะเลและชายฝั่ง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -7569,12 +7561,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>★ (จอภาพ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b0679766-012d-497b-8e41-2296e1c7ba51</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f112758f-839d-4660-91b5-12181a1297d2</t>
         </is>
       </c>
     </row>
@@ -7586,17 +7578,15 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>กรมปศุสัตว์</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>0706</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>1202</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่ารถส่วนภูมิภาค รถยนต์ไฟฟ้า ประเภทแบตเตอรี่ (BEV) ขนาดความจุของแบตเตอรี่มากกว่า 50 กิโลวัตต์ชั่วโมง (kWh) และกำลังมอเตอร์ไฟฟ้าสูงสุด ไม่เกิน 150 กิโลวัตต์ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -7606,12 +7596,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f70d294-53f0-4fd1-b9bc-ef06d20b1657</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=40cb45e4-0e08-48b9-a763-7a9aa44d7959</t>
         </is>
       </c>
     </row>
@@ -7623,17 +7613,15 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>สำนักงานนโยบายและแผนการขนส่งและจราจร</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>0808</t>
-        </is>
+          <t>กรมการปกครอง</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>1503</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์ของ สนข. ประจำปีงบประมาณ พ.ศ. 2570  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 5 รายการ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -7643,12 +7631,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=069d5584-a6b1-426d-9714-115f2fdc7025</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ac3547dc-0f12-4694-b5a3-e216678ce172</t>
         </is>
       </c>
     </row>
@@ -7660,17 +7648,15 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>0904</t>
-        </is>
+          <t>กรมการศาสนา</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>1803</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการบำรุงรักษาและเพิ่มประสิทธิภาพระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรทางทะเลและชายฝั่ง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อวัสดุสำนักงานส่วนกลาง ประจำปีงบประมาณ พ.ศ. 2569 (ครั้งที่ 2)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -7680,12 +7666,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (วัสดุสำนักงาน)</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f112758f-839d-4660-91b5-12181a1297d2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c6f2fbd0-4267-42c4-926d-d8fc49d8a3ff</t>
         </is>
       </c>
     </row>
@@ -7697,17 +7683,15 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>1202</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>2102</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่ารถส่วนภูมิภาค รถยนต์ไฟฟ้า ประเภทแบตเตอรี่ (BEV) ขนาดความจุของแบตเตอรี่มากกว่า 50 กิโลวัตต์ชั่วโมง (kWh) และกำลังมอเตอร์ไฟฟ้าสูงสุด ไม่เกิน 150 กิโลวัตต์ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องผลิตออกซิเจนขนาด 5 ลิตร ของโรงพยาบาลสนม และโรงพยาบาลส่งเสริมสุขภาพตำบล 18 แห่ง จำนวน 33 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -7717,12 +7701,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=40cb45e4-0e08-48b9-a763-7a9aa44d7959</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=655601b1-75a6-4eee-9bc7-ee3ce427abf6</t>
         </is>
       </c>
     </row>
@@ -7734,17 +7718,15 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>กรมการปกครอง</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>1503</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>2102</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 5 รายการ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดความดันโลหิตชนิดอัตโนมัติ วัดความอิ่มตัวของออกซิเจนในเลือด อุณหภูมิร่างกาย พร้อมระบบเชื่อมต่อฐานข้อมูล ของโรงพยาบาลในจังหวัดสุรินทร์ 12 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบล 10 แห่ง จำนวน 50 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -7759,7 +7741,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ac3547dc-0f12-4694-b5a3-e216678ce172</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=65a2753e-e63f-4be2-b228-0fe250379934</t>
         </is>
       </c>
     </row>
@@ -7771,17 +7753,15 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>กรมการศาสนา</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>2102</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อวัสดุสำนักงานส่วนกลาง ประจำปีงบประมาณ พ.ศ. 2569 (ครั้งที่ 2)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการชุดอุปกรณ์เคลื่อนย้ายผู้ป่วยในสถานการณ์ฉุกเฉิน ของโรงพยาบาลชุมชน 8 แห่ง จำนวน 10 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -7791,12 +7771,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>★ (วัสดุสำนักงาน)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c6f2fbd0-4267-42c4-926d-d8fc49d8a3ff</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=886059b7-d984-4e19-b7d7-6d90ebc9b2e0</t>
         </is>
       </c>
     </row>
@@ -7811,14 +7791,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C211" t="n">
+        <v>2102</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องผลิตออกซิเจนขนาด 5 ลิตร ของโรงพยาบาลสนม และโรงพยาบาลส่งเสริมสุขภาพตำบล 18 แห่ง จำนวน 33 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงชนิดสี 2 หัวตรวจ ของโรงพยาบาลชุมชน 6 แห่ง จำนวน 8 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -7833,7 +7811,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=655601b1-75a6-4eee-9bc7-ee3ce427abf6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fc233297-ee25-42e4-bc90-16f41ac8db6a</t>
         </is>
       </c>
     </row>
@@ -7848,14 +7826,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C212" t="n">
+        <v>2102</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดความดันโลหิตชนิดอัตโนมัติ วัดความอิ่มตัวของออกซิเจนในเลือด อุณหภูมิร่างกาย พร้อมระบบเชื่อมต่อฐานข้อมูล ของโรงพยาบาลในจังหวัดสุรินทร์ 12 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบล 10 แห่ง จำนวน 50 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดออกซิเจนในเลือดอัตโนมัติชนิดพกพา ของโรงพยาบาลส่งเสริมสุขภาพตำบลและโรงพยาบาลชุมชน 24 แห่ง จำนวน 68 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -7870,7 +7846,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=65a2753e-e63f-4be2-b228-0fe250379934</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3d2922a2-6499-49fa-b182-1e95dc5131d7</t>
         </is>
       </c>
     </row>
@@ -7885,14 +7861,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C213" t="n">
+        <v>2102</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการชุดอุปกรณ์เคลื่อนย้ายผู้ป่วยในสถานการณ์ฉุกเฉิน ของโรงพยาบาลชุมชน 8 แห่ง จำนวน 10 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องเอกซเรย์ทั่วไปขนาดไม่น้อยกว่า 500 mA. แบบแขวนเพดาน โรงพยาบาลแก่งกระจาน ตำบลวังจันทร์ อำเภอแก่งกระจาน จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -7907,29 +7881,29 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=886059b7-d984-4e19-b7d7-6d90ebc9b2e0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6f21d5fd-56e9-4486-915b-90fd4be0f39b</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กองทัพอากาศ</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>0206</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงชนิดสี 2 หัวตรวจ ของโรงพยาบาลชุมชน 6 แห่ง จำนวน 8 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบริการบำรุงรักษาเครื่องเอกซเรย์ควบคุมด้วยระบบคอมพิวเตอร์ขนาดไม่น้อยกว่า 300 mA พร้อมอุปกรณ์ ยี่ห้อ DRGEM รุ่น GXR-52S ของ โรงพยาบาลกองบิน กองบิน 1, โรงพยาบาลกองบิน กองบิน 2, โรงพยาบาลกองบิน กองบิน 7, โรงพยาบาลกองบิน กองบิน 41, โรงพยาบาลกองบิน กองบิน 46 จำนวน ๑ งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -7939,34 +7913,34 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fc233297-ee25-42e4-bc90-16f41ac8db6a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ffb67ab2-d749-4ab0-87f1-1b11432ab218</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมธนารักษ์</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดออกซิเจนในเลือดอัตโนมัติชนิดพกพา ของโรงพยาบาลส่งเสริมสุขภาพตำบลและโรงพยาบาลชุมชน 24 แห่ง จำนวน 68 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องอากาศยานซึ่งไม่มีนักบิน (Drone)  พร้อมชุดอุปกรณ์ภาคสนามและระบบซอฟต์แวร์ประมวลผลแผนที่ความละเอียดสูง จำนวน 12 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -7976,49 +7950,604 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3d2922a2-6499-49fa-b182-1e95dc5131d7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e88cabea-0e2e-4af8-8b8b-4aa4e7eb040a</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
+          <t>สำนักงานเศรษฐกิจการคลัง</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>0311</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างโครงการจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์สำหรับโครงการพัฒนาระบบสารสนเทศสถาบันการเงินประชาชนของสำนักงานเศรษฐกิจการคลัง (ระบบงาน PFI) ประจำปีงบประมาณ พ.ศ. 2570  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a787a49a-4035-46d3-b8a4-a996ac96341d</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>กรมพัฒนาสังคมและสวัสดิการ</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์สำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=857f0ccd-d38e-47b0-8d6d-913ef2cb1583</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>0704</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=01c185be-f27c-41bc-868e-accd57e4a95c</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>กรมการขนส่งทางบก</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>0804</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์พร้อมอุปกรณ์สำหรับศูนย์รวมข้อมูลการขนส่งด้วยรถบรรทุกเพื่อส่งเสริมการขนส่งด้วยรถบรรทุกให้มีประสิทธิภาพ ปลอดภัยและได้มาตรฐาน (TDSC) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70381c19-a073-41d0-8f0b-08c5e68fca7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>กรมท่าอากาศยาน</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบไฟฟ้า ตู้สวิตช์บอร์ด ๒๖ ท่าอากาศยาน และกรมท่าอากาศยาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>★ (สวิตช์)</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7f19e47d-04ea-4596-a45a-a42e0fd28eea</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 7 รายการ ศูนย์สร้างทางลำปาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f6fbb9a3-863a-430c-ab4d-c57fc8032ba8</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>กรมป่าไม้</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>0912</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fd72b9d1-6722-4578-b8e5-e2d45779204d</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>ประกวดราคาเช่าระบบประชุมทางไกล (Web Conference Video Streaming) ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>★ (ระบบประชุมทางไกล)</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6c4b6c7d-fa54-4634-9070-01779d28362f</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>กรมโยธาธิการและผังเมือง</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>1507</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างก่อสร้างงานปรับปรุงระบบดับเพลิงพิเศษอัตโนมัติ (Clean Agent Fire Suppression System) ภายในห้องคอมพิวเตอร์แม่ข่าย (Server Room) อาคาร 4 ชั้น 1 กรมโยธาธิการและผังเมือง ถนนพระราม 9 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a61be7d0-de39-476c-b4f8-7a3ec47bbd62</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบริการถ่ายเอกสารพร้อมเครื่องถ่ายเอกสาร กระดาษ วัสดุสิ้นเปลือง และพนักงานประจำเครื่องของสำนักงาน ป.ป.ส. ดินแดง/สำนักงาน ป.ป.ส. ทุ่งสองห้อง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>★ (กระดาษ)</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=325eb565-d1b7-456f-86c5-076a6e3f94fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr">
+      <c r="C226" t="inlineStr">
         <is>
           <t>2102</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องเอกซเรย์ทั่วไปขนาดไม่น้อยกว่า 500 mA. แบบแขวนเพดาน โรงพยาบาลแก่งกระจาน ตำบลวังจันทร์ อำเภอแก่งกระจาน จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องนึ่งฆ่าเชื้อจุลินทรีย์ด้วยไอน้ำระบบอัตโนมัติ ขนาดไม่น้อยกว่า 850 ลิตร ห้องนึ่งทรงเหลี่ยมชนิด 1 ประตู โรงพยาบาลบ้านลาด ตำบลท่าช้าง อำเภอบ้านลาด จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
         <is>
           <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6f21d5fd-56e9-4486-915b-90fd4be0f39b</t>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4d2f3086-64b4-4e82-a4f3-6299ee3aa880</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องล้างเครื่องมืออัลตร้าโซนิก ชนิด 3 หลุมล้าง ขนาดความจุไม่น้อยกว่า 80 ลิตร โรงพยาบาลชะอำ ตำบลชะอำ อำเภอชะอำ จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b7c95cfb-63e4-43a3-9eeb-4e9c5df71f85</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่ายกลาง (Backbone) กระทรวงสาธารณสุข ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3a5cafe5-5313-4cb0-ab08-4b09c244ba61</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนและคาร์บอนไดออกไซด์ในเลือด ของโรงพยาบาลในจังหวัดสุรินทร์ 7 แห่ง จำนวน 12 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d5f4c614-78c4-4363-a75d-31e52b8e81d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 8 เตียง ของโรงพยาบาลท่าตูม จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=261f4b2d-359f-4fbc-9c62-4971724a772f</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันขนาดใหญ่ ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 6 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9cc00102-4e57-443e-a94c-3787d155fe6b</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202609.xlsx
+++ b/Backup/eGP_Monthly_Main_202609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G231"/>
+  <dimension ref="A1:G255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1558,15 +1558,15 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+          <t>กรมที่ดิน</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1302</v>
+        <v>1505</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าระบบประชุมทางไกล (Web Conference Video Streaming) ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อโต๊ะและเก้าอี้เพื่อใช้ในราชการของสำนักงานที่ดินจังหวัดพิษณุโลก และสาขาฯ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>★ (ระบบประชุมทางไกล)</t>
+          <t>★ (โต๊ะ, เก้าอี้)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3d156308-f0d2-4d07-bf4a-27913c2c22b7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=341e9241-c067-4ffa-9e06-734f19c6b999</t>
         </is>
       </c>
     </row>
@@ -1593,15 +1593,15 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>กรมที่ดิน</t>
+          <t>กรมพัฒนาฝีมือแรงงาน</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1505</v>
+        <v>1704</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อโต๊ะและเก้าอี้เพื่อใช้ในราชการของสำนักงานที่ดินจังหวัดพิษณุโลก และสาขาฯ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาครุภัณฑ์คอมพิวเตอร์และระบบเครือข่าย ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>★ (โต๊ะ, เก้าอี้)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=341e9241-c067-4ffa-9e06-734f19c6b999</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=677d75a8-aa89-4b8b-a742-eca4be741031</t>
         </is>
       </c>
     </row>
@@ -1628,15 +1628,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>กรมพัฒนาฝีมือแรงงาน</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1704</v>
+        <v>2102</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาครุภัณฑ์คอมพิวเตอร์และระบบเครือข่าย ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๓ รายการ ของสำนักงานสาธารณสุขจังหวัดกาญจนบุรี เพื่อโรงพยาบาลชุมชน จำนวน ๑๐ แห่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=677d75a8-aa89-4b8b-a742-eca4be741031</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0424125a-176e-423d-9959-61c0ef9229f3</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๓ รายการ ของสำนักงานสาธารณสุขจังหวัดกาญจนบุรี เพื่อโรงพยาบาลชุมชน จำนวน ๑๐ แห่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 6 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง จำนวน 1 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ.2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0424125a-176e-423d-9959-61c0ef9229f3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ee066bf2-4c21-4580-8391-e1257afc7b11</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 6 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง จำนวน 1 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ.2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อตู้เย็นเก็บเลือดขนาดไม่น้อยกว่า 20 คิว จำนวน 1 เครื่อง สำหรับ รพ.พระปิยมหาราช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1716,12 +1716,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ตู้เย็น)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ee066bf2-4c21-4580-8391-e1257afc7b11</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=985c4332-e608-4dc3-883b-e90257b97ad3</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อตู้เย็นเก็บเลือดขนาดไม่น้อยกว่า 20 คิว จำนวน 1 เครื่อง สำหรับ รพ.พระปิยมหาราช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์การแพทย์เพื่อการบริการประชาชน จำนวน 13 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>★ (ตู้เย็น)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=985c4332-e608-4dc3-883b-e90257b97ad3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=db849b83-870c-446d-a004-6e2462b1b3a4</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์การแพทย์เพื่อการบริการประชาชน จำนวน 13 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนในเลือดของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 5 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1791,27 +1791,27 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=db849b83-870c-446d-a004-6e2462b1b3a4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e2347540-427f-4618-ac0a-6d2933980a00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สำนักงานปลัดกระทรวงการคลัง</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2102</v>
+        <v>302</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนในเลือดของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 5 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อสิทธิ์การใช้งานซอฟต์แวร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e2347540-427f-4618-ac0a-6d2933980a00</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1732e367-2c09-431f-abc1-7384c0a94e8e</t>
         </is>
       </c>
     </row>
@@ -1838,15 +1838,15 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการคลัง</t>
+          <t>กรมศุลกากร</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อสิทธิ์การใช้งานซอฟต์แวร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าโครงการจัดเช่าวงจรเครือข่ายสื่อสารเพื่อการเชื่อมโยงข้อมูลระหว่างศูนย์คอมพิวเตอร์ (DC-DR) กรมศุลกากร ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1856,12 +1856,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>★ (ซอฟต์แวร์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1732e367-2c09-431f-abc1-7384c0a94e8e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a09e3df4-34c1-4388-a91a-31d0494ea9da</t>
         </is>
       </c>
     </row>
@@ -1873,15 +1873,15 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>กรมศุลกากร</t>
+          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>305</v>
+        <v>402</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าโครงการจัดเช่าวงจรเครือข่ายสื่อสารเพื่อการเชื่อมโยงข้อมูลระหว่างศูนย์คอมพิวเตอร์ (DC-DR) กรมศุลกากร ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการทำความสะอาด ณ อาคารกระทรวงการต่างประเทศ ถนนศรีอยุธยา อาคารกรมการกงสุลรวมถึงกองบรรณสารและห้องสมุด (ฝ่ายบรรณสาร) และศูนย์ราชการเฉลิมพระเกียรติฯ อาคาร B ชั้น 7 - 8 รวม 3 แห่ง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (สมุด)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a09e3df4-34c1-4388-a91a-31d0494ea9da</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=61256c96-a851-4486-ba34-aeb06311fa64</t>
         </is>
       </c>
     </row>
@@ -1908,15 +1908,15 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
+          <t>กรมชลประทาน</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>402</v>
+        <v>703</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการทำความสะอาด ณ อาคารกระทรวงการต่างประเทศ ถนนศรีอยุธยา อาคารกรมการกงสุลรวมถึงกองบรรณสารและห้องสมุด (ฝ่ายบรรณสาร) และศูนย์ราชการเฉลิมพระเกียรติฯ อาคาร B ชั้น 7 - 8 รวม 3 แห่ง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องสูบน้ำชนิดหอยโข่ง เเบบ End Suction ขับด้วยมอเตอร์ไฟฟ้า พร้อมติดตั้งอุปกรณ์ เเละระบบควบคุมไฟฟ้า ตามรายละเอียดคุณลักษณะเฉพาะ (Specification) ของกรมชลประทาน และอื่นๆ รวม ๓ รายการ สำหรับงานสถานีสูบน้ำด้วยไฟฟ้าพร้อมระบบส่งน้ำฝายคลองพอถาก ตำบลหน้าเขา อำเภอเขาพนม จังหวัดกระบี่ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1926,12 +1926,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>★ (สมุด)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=61256c96-a851-4486-ba34-aeb06311fa64</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f690008d-6ff3-4f11-84a7-08da3de166d4</t>
         </is>
       </c>
     </row>
@@ -1943,15 +1943,15 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>กรมชลประทาน</t>
+          <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>703</v>
+        <v>804</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องสูบน้ำชนิดหอยโข่ง เเบบ End Suction ขับด้วยมอเตอร์ไฟฟ้า พร้อมติดตั้งอุปกรณ์ เเละระบบควบคุมไฟฟ้า ตามรายละเอียดคุณลักษณะเฉพาะ (Specification) ของกรมชลประทาน และอื่นๆ รวม ๓ รายการ สำหรับงานสถานีสูบน้ำด้วยไฟฟ้าพร้อมระบบส่งน้ำฝายคลองพอถาก ตำบลหน้าเขา อำเภอเขาพนม จังหวัดกระบี่ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์ Server และอุปกรณ์ที่ติดตั้ง ณ อาคารระบบข้อมูลกลางและสำรองข้อมูล สำนักงานขนส่งจังหวัดนนทบุรี ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1961,12 +1961,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f690008d-6ff3-4f11-84a7-08da3de166d4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7dbc77ce-d778-424c-9618-b2cc1659f8ad</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์ Server และอุปกรณ์ที่ติดตั้ง ณ อาคารระบบข้อมูลกลางและสำรองข้อมูล สำนักงานขนส่งจังหวัดนนทบุรี ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมระบบคอมพิวเตอร์แม่ข่ายเสมือน (Server Virtualization) สำหรับให้บริการหน่วยงานต่างๆ ของกรมการขนส่งทางบกที่ใช้ในการสนับสนุน การปฏิบัติงานด้านความปลอดภัย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7dbc77ce-d778-424c-9618-b2cc1659f8ad</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=60f2364f-32ae-4a8c-8c92-9936327bd8f9</t>
         </is>
       </c>
     </row>
@@ -2013,15 +2013,15 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
+          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>804</v>
+        <v>904</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมระบบคอมพิวเตอร์แม่ข่ายเสมือน (Server Virtualization) สำหรับให้บริการหน่วยงานต่างๆ ของกรมการขนส่งทางบกที่ใช้ในการสนับสนุน การปฏิบัติงานด้านความปลอดภัย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการเช่าใช้บริการอินเทอร์เน็ตและสายสัญญาณเครือข่ายพร้อมอุปกรณ์ กรมทรัพยากรทางทะเลและชายฝั่ง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (สายสัญญาณ)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=60f2364f-32ae-4a8c-8c92-9936327bd8f9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ab266c44-4e3d-4e4c-a44e-a5e06ffb7d51</t>
         </is>
       </c>
     </row>
@@ -2048,15 +2048,15 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
+          <t>กรมที่ดิน</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>904</v>
+        <v>1505</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการเช่าใช้บริการอินเทอร์เน็ตและสายสัญญาณเครือข่ายพร้อมอุปกรณ์ กรมทรัพยากรทางทะเลและชายฝั่ง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์และระบบคอมพิวเตอร์แม่ข่าย ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ระยะเวลา ๑๒ เดือน  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>★ (สายสัญญาณ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ab266c44-4e3d-4e4c-a44e-a5e06ffb7d51</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ba59f24a-325d-4e38-8d86-eadcece33632</t>
         </is>
       </c>
     </row>
@@ -2083,15 +2083,15 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>กรมที่ดิน</t>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1505</v>
+        <v>1611</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์และระบบคอมพิวเตอร์แม่ข่าย ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ระยะเวลา ๑๒ เดือน  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการถ่ายเอกสารพร้อมเครื่องถ่ายเอกสาร กระดาษ วัสดุสิ้นเปลือง และพนักงานประจำเครื่องของสำนักงาน ป.ป.ส. ดินแดง สำนักงาน ปปส.ทุ่งสองห้อง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (กระดาษ)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ba59f24a-325d-4e38-8d86-eadcece33632</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ef490410-ac68-4d7a-9e38-c4dbf7dd4191</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการถ่ายเอกสารพร้อมเครื่องถ่ายเอกสาร กระดาษ วัสดุสิ้นเปลือง และพนักงานประจำเครื่องของสำนักงาน ป.ป.ส. ดินแดง สำนักงาน ปปส.ทุ่งสองห้อง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาซอฟต์แวร์และอุปกรณ์ระบบรักษาความปลอดภัยระบบเครือข่ายศูนย์คอมพิวเตอร์สำรอง ( DR-Site Firewall) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>★ (กระดาษ)</t>
+          <t>★ (คอมพิวเตอร์, ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ef490410-ac68-4d7a-9e38-c4dbf7dd4191</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a430ff3c-1d84-458b-8d71-d54f8c065644</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาซอฟต์แวร์และอุปกรณ์ระบบรักษาความปลอดภัยระบบเครือข่ายศูนย์คอมพิวเตอร์สำรอง ( DR-Site Firewall) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบป้องกันการบุกรุกเครือข่ายคอมพิวเตอร์ สำนักงาน ป.ป.ส. (Client Zone Firewall) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ซอฟต์แวร์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a430ff3c-1d84-458b-8d71-d54f8c065644</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bfcbc7fd-4a5c-46e3-b5eb-5b51397db1cb</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบป้องกันการบุกรุกเครือข่ายคอมพิวเตอร์ สำนักงาน ป.ป.ส. (Client Zone Firewall) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์เครื่องคอมพิวเตอร์แม่ข่ายพร้อมระบบปฏิบัติการ (Server) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ระบบปฏิบัติการ)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bfcbc7fd-4a5c-46e3-b5eb-5b51397db1cb</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4a59a370-30a9-4f35-abcd-cec87b36ed1e</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์เครื่องคอมพิวเตอร์แม่ข่ายพร้อมระบบปฏิบัติการ (Server) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์และซอฟต์แวร์ป้องกันระบบเครือข่าย (Firewall/Virus/VPN) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ระบบปฏิบัติการ)</t>
+          <t>★ (ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4a59a370-30a9-4f35-abcd-cec87b36ed1e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=71058768-3f32-47a5-b07d-d89703297e8b</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์และซอฟต์แวร์ป้องกันระบบเครือข่าย (Firewall/Virus/VPN) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาและแก้ไขปัญหาการใช้เครื่องคอมพิวเตอร์ลูกข่ายและอุปกรณ์ต่อพ่วง สำนักงาน ป.ป.ส. ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>★ (ซอฟต์แวร์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=71058768-3f32-47a5-b07d-d89703297e8b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=04f4a224-3c0a-4630-9981-263ded303a56</t>
         </is>
       </c>
     </row>
@@ -2293,15 +2293,15 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1611</v>
+        <v>2102</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาและแก้ไขปัญหาการใช้เครื่องคอมพิวเตอร์ลูกข่ายและอุปกรณ์ต่อพ่วง สำนักงาน ป.ป.ส. ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการเครื่องดมยาสลบชนิดมาตรฐาน  จำนวน  ๑  เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=04f4a224-3c0a-4630-9981-263ded303a56</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e1f11ae5-c3d5-4fdc-a76f-351add1653a8</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการเครื่องดมยาสลบชนิดมาตรฐาน  จำนวน  ๑  เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการกล้องส่องตรวจและผ่าตัดภายในช่องท้องชนิดวีดิทัศน์แบบคมชัดสูงชนิดภาพ ๒ มิติ จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e1f11ae5-c3d5-4fdc-a76f-351add1653a8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3ff66642-757c-4554-a147-37146918afe9</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการกล้องส่องตรวจและผ่าตัดภายในช่องท้องชนิดวีดิทัศน์แบบคมชัดสูงชนิดภาพ ๒ มิติ จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์โครงการจัดซื้อครุภัณฑ์การแพทย์เพื่อการบริการประชาชน จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3ff66642-757c-4554-a147-37146918afe9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=921cfd0c-6740-4e24-84ce-20ad0ebfb382</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์โครงการจัดซื้อครุภัณฑ์การแพทย์เพื่อการบริการประชาชน จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันเคลื่อนย้ายได้ ของโรงพยาบาลชุมชน 8 แห่ง จำนวน 11 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=921cfd0c-6740-4e24-84ce-20ad0ebfb382</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2ac905f2-26be-4df4-b481-22676581f31a</t>
         </is>
       </c>
     </row>
@@ -2433,15 +2433,15 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2102</v>
+        <v>2113</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันเคลื่อนย้ายได้ ของโรงพยาบาลชุมชน 8 แห่ง จำนวน 11 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องฟอกอากาศ แขวงทุ่งสองห้อง เขตหลักสี่ กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2451,32 +2451,32 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องฟอกอากาศ)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2ac905f2-26be-4df4-b481-22676581f31a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a91dc5dd-5f0e-49d2-8b3f-d7da9560b550</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+          <t>สำนักงานรับรองมาตรฐานและประเมินคุณภาพการศึกษา (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2113</v>
+        <v>116</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องฟอกอากาศ แขวงทุ่งสองห้อง เขตหลักสี่ กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบ AQA ก) ระบบสารสนเทศเพื่อการประเมินคุณภาพภายนอก (AQA) ข) ระบบและซอฟต์แวร์สำหรับการจัดการไฟล์วิดีโอ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>★ (เครื่องฟอกอากาศ)</t>
+          <t>★ (ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a91dc5dd-5f0e-49d2-8b3f-d7da9560b550</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=15b527de-47eb-447e-8bc6-1bc4e5204254</t>
         </is>
       </c>
     </row>
@@ -2503,15 +2503,15 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>สำนักงานรับรองมาตรฐานและประเมินคุณภาพการศึกษา (องค์การมหาชน)</t>
+          <t>กรมพลศึกษา</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>116</v>
+        <v>503</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบ AQA ก) ระบบสารสนเทศเพื่อการประเมินคุณภาพภายนอก (AQA) ข) ระบบและซอฟต์แวร์สำหรับการจัดการไฟล์วิดีโอ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาดูแล ปรับปรุง บำรุงรักษา และพัฒนาระบบเครือข่ายและอุปกรณ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>★ (ซอฟต์แวร์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=15b527de-47eb-447e-8bc6-1bc4e5204254</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ff914fa4-2fa4-4a9c-bb1e-eb038590a95a</t>
         </is>
       </c>
     </row>
@@ -2538,15 +2538,15 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>กรมพลศึกษา</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>503</v>
+        <v>704</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาดูแล ปรับปรุง บำรุงรักษา และพัฒนาระบบเครือข่ายและอุปกรณ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์  เครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล พร้อมชุดโปรแกรมระบบปฏิบัติการ สำหรับเครื่องคอมพิวเตอร์และเครื่องคอมพิวเตอร์โน้ตบุ๊ก แบบสิทธิการใช้งานภายในสำนักงาน ประเภทติดตั้งมาจากโรงงาน (OEM) ที่มีลิขสิทธิ์ที่ถูกต้องตามกฎหมาย ชุดโปรแกรมจัดการสานักงาน แบบที่ 2 ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย และชุดโปรแกรมป้องกันไวรัส จำนวน 15 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ระบบปฏิบัติการ, โปรแกรมป้องกันไวรัส, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ff914fa4-2fa4-4a9c-bb1e-eb038590a95a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2b1675a5-f593-4cd6-a100-2c0f3ac9c6e2</t>
         </is>
       </c>
     </row>
@@ -2573,15 +2573,15 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมประมง</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์  เครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล พร้อมชุดโปรแกรมระบบปฏิบัติการ สำหรับเครื่องคอมพิวเตอร์และเครื่องคอมพิวเตอร์โน้ตบุ๊ก แบบสิทธิการใช้งานภายในสำนักงาน ประเภทติดตั้งมาจากโรงงาน (OEM) ที่มีลิขสิทธิ์ที่ถูกต้องตามกฎหมาย ชุดโปรแกรมจัดการสานักงาน แบบที่ 2 ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย และชุดโปรแกรมป้องกันไวรัส จำนวน 15 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน ๑ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ระบบปฏิบัติการ, โปรแกรมป้องกันไวรัส, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2b1675a5-f593-4cd6-a100-2c0f3ac9c6e2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7899c0ad-4727-4814-a039-57ea77f4e508</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน ๑ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าเเละวิทยุ เครื่องกำเนิดไฟฟ้า ขนาด 100 กิโลวัตต์ พร้อมตู้ควบคุม ตำบลหูล่อง อำเภอปากพนัง จังหวัดนครศรีธรรมราช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7899c0ad-4727-4814-a039-57ea77f4e508</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=18464524-52ce-42bf-96c8-511cdf002607</t>
         </is>
       </c>
     </row>
@@ -2643,15 +2643,15 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>กรมประมง</t>
+          <t>กรมการข้าว</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>705</v>
+        <v>718</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าเเละวิทยุ เครื่องกำเนิดไฟฟ้า ขนาด 100 กิโลวัตต์ พร้อมตู้ควบคุม ตำบลหูล่อง อำเภอปากพนัง จังหวัดนครศรีธรรมราช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ต่อพ่วงเพื่อเพิ่มประสิทธิภาพการปฏิบัติงานของกรมการข้าว แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2661,12 +2661,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=18464524-52ce-42bf-96c8-511cdf002607</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=aaaf180c-62ba-4ca4-9a9c-0333baa76276</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ต่อพ่วงเพื่อเพิ่มประสิทธิภาพการปฏิบัติงานของกรมการข้าว แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อทดแทนครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ต่อพ่วงเพื่อเพิ่มประสิทธิภาพการปฏิบัติงานของกรมการข้าว แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=aaaf180c-62ba-4ca4-9a9c-0333baa76276</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=15086036-ab87-4a45-b29c-edd87f507d1b</t>
         </is>
       </c>
     </row>
@@ -2713,15 +2713,15 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>กรมการข้าว</t>
+          <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>718</v>
+        <v>804</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อทดแทนครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ต่อพ่วงเพื่อเพิ่มประสิทธิภาพการปฏิบัติงานของกรมการข้าว แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์และอุปกรณ์ตามโครงการระบบเครือข่ายเพื่อเพิ่มประสิทธิภาพในการปฏิบัติงานของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=15086036-ab87-4a45-b29c-edd87f507d1b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=faa5336e-2946-42fd-b66e-9583a9f24e44</t>
         </is>
       </c>
     </row>
@@ -2748,15 +2748,15 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์และอุปกรณ์ตามโครงการระบบเครือข่ายเพื่อเพิ่มประสิทธิภาพในการปฏิบัติงานของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=faa5336e-2946-42fd-b66e-9583a9f24e44</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=44d1ec7f-04ab-49d0-b112-502799195d6b</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการจัดจ้างบำรุงรักษาเครื่องคอมพิวเตอร์แม่ข่ายและอุปกรณ์สำหรับระบบสารสนเทศบริหารเครื่องจักรกลและการเงินการบัญชีเพื่อการบริหารจัดการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2801,12 +2801,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=44d1ec7f-04ab-49d0-b112-502799195d6b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=909fce3b-2a20-4eb7-b619-b2e32da6e18d</t>
         </is>
       </c>
     </row>
@@ -2818,15 +2818,15 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>กรมทรัพยากรธรณี</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>806</v>
+        <v>905</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการจัดจ้างบำรุงรักษาเครื่องคอมพิวเตอร์แม่ข่ายและอุปกรณ์สำหรับระบบสารสนเทศบริหารเครื่องจักรกลและการเงินการบัญชีเพื่อการบริหารจัดการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาซ่อมบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรธรณี ปีงบประมาณ พ.ศ. 2570 จำนวน 1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=909fce3b-2a20-4eb7-b619-b2e32da6e18d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3cc3bb5f-0d9f-428a-b588-18b0b71b8b6e</t>
         </is>
       </c>
     </row>
@@ -2853,15 +2853,15 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>กรมทรัพยากรธรณี</t>
+          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาซ่อมบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรธรณี ปีงบประมาณ พ.ศ. 2570 จำนวน 1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อและติดตั้งเครื่องคอมพิวเตอร์แม่ข่ายพร้อมอุปกรณ์ประกอบสำหรับรองรับการให้บริการระบบสารบรรณอิเล็กทรอนิกส์ของกรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3cc3bb5f-0d9f-428a-b588-18b0b71b8b6e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=028b6dd5-2160-4f89-924f-f6c47b4b4995</t>
         </is>
       </c>
     </row>
@@ -2888,15 +2888,15 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
+          <t>สำนักงานปลัดกระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>909</v>
+        <v>1102</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อและติดตั้งเครื่องคอมพิวเตอร์แม่ข่ายพร้อมอุปกรณ์ประกอบสำหรับรองรับการให้บริการระบบสารบรรณอิเล็กทรอนิกส์ของกรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการจัดอบรมเตรียมความพร้อมผู้แต่งตั้งเป็นพนักงานเจ้าหน้าที่ตามพระราชบัญญัติว่าด้วยการกระทำความผิดเกี่ยวกับคอมพิวเตอร์ฯ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=028b6dd5-2160-4f89-924f-f6c47b4b4995</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8de232df-b5c2-427b-9a5d-d9f5ca3342c3</t>
         </is>
       </c>
     </row>
@@ -2923,15 +2923,15 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม</t>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1102</v>
+        <v>1302</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการจัดอบรมเตรียมความพร้อมผู้แต่งตั้งเป็นพนักงานเจ้าหน้าที่ตามพระราชบัญญัติว่าด้วยการกระทำความผิดเกี่ยวกับคอมพิวเตอร์ฯ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์สนับสนุนศูนย์ข้อมูลและเครือข่ายคอมพิวเตอร์ (Data Center) ของกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8de232df-b5c2-427b-9a5d-d9f5ca3342c3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5065022-193d-466c-819b-b1533c1e1696</t>
         </is>
       </c>
     </row>
@@ -2958,15 +2958,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+          <t>สถาบันส่งเสริมศิลปหัตถกรรมไทย (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1302</v>
+        <v>1311</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์สนับสนุนศูนย์ข้อมูลและเครือข่ายคอมพิวเตอร์ (Data Center) ของกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างดำเนินการบำรุงรักษาระบบและอุปกรณ์ภายในห้อง Data Center และการต่อลิขสิทธิ์โปรแกรมคอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5065022-193d-466c-819b-b1533c1e1696</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8c2b0f9b-210b-4328-a727-0ebda03f9ebc</t>
         </is>
       </c>
     </row>
@@ -2993,15 +2993,15 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>สถาบันส่งเสริมศิลปหัตถกรรมไทย (องค์การมหาชน)</t>
+          <t>กรมบังคับคดี</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1311</v>
+        <v>1605</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างดำเนินการบำรุงรักษาระบบและอุปกรณ์ภายในห้อง Data Center และการต่อลิขสิทธิ์โปรแกรมคอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างตรวจสอบเครื่องคอมพิวเตอร์ให้พร้อมใช้งานและบริการประชาชน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8c2b0f9b-210b-4328-a727-0ebda03f9ebc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=590bcfa8-9d1a-43f4-b6c0-1d332cdf98ac</t>
         </is>
       </c>
     </row>
@@ -3028,15 +3028,15 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>กรมบังคับคดี</t>
+          <t>กรมศิลปากร</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1605</v>
+        <v>1804</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างตรวจสอบเครื่องคอมพิวเตอร์ให้พร้อมใช้งานและบริการประชาชน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการดูแลบำรุงรักษาเครื่องปรับอากาศ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3046,12 +3046,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=590bcfa8-9d1a-43f4-b6c0-1d332cdf98ac</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=560aab6a-379c-4e73-a426-35b147f0955f</t>
         </is>
       </c>
     </row>
@@ -3063,15 +3063,15 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>กรมศิลปากร</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1804</v>
+        <v>2102</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการดูแลบำรุงรักษาเครื่องปรับอากาศ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดอัตโนมัติ พร้อมตู้ตั้งพื้นจอแสดงผล และระบบสัญญาณเตือน จำนวน 39 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาล ในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (จอแสดงผล, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=560aab6a-379c-4e73-a426-35b147f0955f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f7659e63-27b4-4348-9cb8-c0e5ed5164a0</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดอัตโนมัติ พร้อมตู้ตั้งพื้นจอแสดงผล และระบบสัญญาณเตือน จำนวน 39 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาล ในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องอุ่นเลือดและส่วนประกอบของเลือดชนิดไม่สัมผัสน้ำสามารถอุ่นเลือดได้ พร้อมกันไม่น้อยกว่า 3 ถุง ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 4 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>★ (จอแสดงผล, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f7659e63-27b4-4348-9cb8-c0e5ed5164a0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dc9795b5-9883-4a59-bee5-16ba72ecd5c6</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องอุ่นเลือดและส่วนประกอบของเลือดชนิดไม่สัมผัสน้ำสามารถอุ่นเลือดได้ พร้อมกันไม่น้อยกว่า 3 ถุง ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 4 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเตียงผู้ป่วยชนิดสามไกร์ราวปีกนก พร้อมเบาะเสาน้ำเกลือตู้ข้างเตียงและถาดคร่อมเตียง ของโรงพยาบาลส่งเสริมสุขภาพตำบล 25 แห่ง จำนวน 25 เตียง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dc9795b5-9883-4a59-bee5-16ba72ecd5c6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=43094cdc-968c-43e9-b0e7-915d25aa8621</t>
         </is>
       </c>
     </row>
@@ -3168,15 +3168,15 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2102</v>
+        <v>2107</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเตียงผู้ป่วยชนิดสามไกร์ราวปีกนก พร้อมเบาะเสาน้ำเกลือตู้ข้างเตียงและถาดคร่อมเตียง ของโรงพยาบาลส่งเสริมสุขภาพตำบล 25 แห่ง จำนวน 25 เตียง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=43094cdc-968c-43e9-b0e7-915d25aa8621</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63c3a055-9106-4358-9ed6-5bf60d1e158c</t>
         </is>
       </c>
     </row>
@@ -3203,15 +3203,15 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>กรมสนับสนุนบริการสุขภาพ</t>
+          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2107</v>
+        <v>2113</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและวิเคราะห์ระบบเก็บข้อมูลจราจรคอมพิวเตอร์ขั้นสูง (CSOC) สำนักงานหลักประกันสุขภาพแห่งชาติ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3221,32 +3221,32 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63c3a055-9106-4358-9ed6-5bf60d1e158c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=516788e1-5adb-46f1-b0bc-48d9b91e8cd8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2113</v>
+        <v>204</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและวิเคราะห์ระบบเก็บข้อมูลจราจรคอมพิวเตอร์ขั้นสูง (CSOC) สำนักงานหลักประกันสุขภาพแห่งชาติ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ และอุปกรณ์ประกอบเครื่องคอมพิวเตอร์ เพื่อทดแทน และพัฒนาระบบเทคโนโลยีสารสนเทศหน่วยบัญชาการป้องกันภัยทางอากาศ (นปอ.) จำนวน ๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=516788e1-5adb-46f1-b0bc-48d9b91e8cd8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8603566b-8b32-470f-b070-76bf84fb86b4</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ และอุปกรณ์ประกอบเครื่องคอมพิวเตอร์ เพื่อทดแทน และพัฒนาระบบเทคโนโลยีสารสนเทศหน่วยบัญชาการป้องกันภัยทางอากาศ (นปอ.) จำนวน ๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างงานติดตั้งเครื่องปรับอากาศ ประจำอาคารหอประชุม หมายเลข ๙๖/๒๓ ของ โรงพยาบาลอานันทมหิดล จังหวัดลพบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3291,12 +3291,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8603566b-8b32-470f-b070-76bf84fb86b4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=97d16ed9-2390-479b-8218-55472ad15ea3</t>
         </is>
       </c>
     </row>
@@ -3308,15 +3308,15 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กรมชลประทาน</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>204</v>
+        <v>703</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างงานติดตั้งเครื่องปรับอากาศ ประจำอาคารหอประชุม หมายเลข ๙๖/๒๓ ของ โรงพยาบาลอานันทมหิดล จังหวัดลพบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องสูบน้ำแบบจุ่มใช้มอเตอร์ไฟฟ้า และอื่นๆรวม 3 รายการ สำหรับงานปรับปรุงอาคารบังคับน้ำคลองทิวา-ต้นนา โครงการส่งน้ำและบำรุงรักษาบางพลวง ตำบลพนมสารคาม อำเภอพนมสารคาม จังหวัดฉะเชิงเทรา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3326,12 +3326,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=97d16ed9-2390-479b-8218-55472ad15ea3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=641eb398-88f6-4784-9733-866ddfdb5ea8</t>
         </is>
       </c>
     </row>
@@ -3343,15 +3343,15 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>กรมชลประทาน</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องสูบน้ำแบบจุ่มใช้มอเตอร์ไฟฟ้า และอื่นๆรวม 3 รายการ สำหรับงานปรับปรุงอาคารบังคับน้ำคลองทิวา-ต้นนา โครงการส่งน้ำและบำรุงรักษาบางพลวง ตำบลพนมสารคาม อำเภอพนมสารคาม จังหวัดฉะเชิงเทรา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์เครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล  จำนวน 12 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=641eb398-88f6-4784-9733-866ddfdb5ea8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cae8cfd5-0a33-48de-bb0d-dd1597263622</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์เครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล  จำนวน 12 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล)  ขนาด ๑ ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า ๒,๔๐๐ ซีซี  หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า ๑๑๐ กิโลวัตต์ ขับเคลื่อน 4 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน ๑ คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cae8cfd5-0a33-48de-bb0d-dd1597263622</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=23493925-5f1a-442c-a9ec-afccbc470e45</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล)  ขนาด ๑ ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า ๒,๔๐๐ ซีซี  หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า ๑๑๐ กิโลวัตต์ ขับเคลื่อน 4 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน ๑ คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อเครื่องคอมพิวเตอร์ และเครื่องคอมพิวเตอร์โน้ตบุ๊ก จำนวน 2 รายการ ของสำนักงานตรวจบัญชีสหกรณ์ชลบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=23493925-5f1a-442c-a9ec-afccbc470e45</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=07006c6c-edf5-4030-b6c9-1078334342be</t>
         </is>
       </c>
     </row>
@@ -3448,15 +3448,15 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>704</v>
+        <v>806</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อเครื่องคอมพิวเตอร์ และเครื่องคอมพิวเตอร์โน้ตบุ๊ก จำนวน 2 รายการ ของสำนักงานตรวจบัญชีสหกรณ์ชลบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าโครงการเช่าเครื่องพิมพ์ 4 สี เพื่อการพิมพ์เอกสารแจ้งผู้ขับขี่เพื่อการเปรียบเทียบปรับตามกฎหมาย ของ กองบังคับการตำรวจทางหลวง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=07006c6c-edf5-4030-b6c9-1078334342be</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3fdfa461-5479-46d3-90bc-5b8725bde7b5</t>
         </is>
       </c>
     </row>
@@ -3483,15 +3483,15 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>สำนักงานปลัดกระทรวงแรงงาน</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>806</v>
+        <v>1702</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าโครงการเช่าเครื่องพิมพ์ 4 สี เพื่อการพิมพ์เอกสารแจ้งผู้ขับขี่เพื่อการเปรียบเทียบปรับตามกฎหมาย ของ กองบังคับการตำรวจทางหลวง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดหาครุภัณฑ์คอมพิวเตอร์เพื่อทดแทนและเพิ่มประสิทธิภาพให้หน่วยงานในสังกัดสำนักงานปลัดกระทรวงแรงงาน ปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>★ (เครื่องพิมพ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3fdfa461-5479-46d3-90bc-5b8725bde7b5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=eea981aa-edb1-4fdf-8067-e5fb7c92e854</t>
         </is>
       </c>
     </row>
@@ -3518,15 +3518,15 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงแรงงาน</t>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามการทุจริตในภาครัฐ</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1702</v>
+        <v>2517</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดหาครุภัณฑ์คอมพิวเตอร์เพื่อทดแทนและเพิ่มประสิทธิภาพให้หน่วยงานในสังกัดสำนักงานปลัดกระทรวงแรงงาน ปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาเครื่องคอมพิวเตอร์แม่ข่าย และระบบความปลอดภัยทางไซเบอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=eea981aa-edb1-4fdf-8067-e5fb7c92e854</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=39110c90-d236-47eb-913a-cb6b3cab18ba</t>
         </is>
       </c>
     </row>
@@ -3553,15 +3553,15 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามการทุจริตในภาครัฐ</t>
+          <t>สำนักงานการตรวจเงินแผ่นดิน</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2517</v>
+        <v>2606</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการบำรุงรักษาเครื่องคอมพิวเตอร์แม่ข่าย และระบบความปลอดภัยทางไซเบอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างเหมาบริการขนย้ายเครื่องแม่ข่าย และอุปกรณ์พร้อมติดตั้ง ณ ศูนย์ข้อมูลหลัก ของสำนักงานการตรวจเงินแผ่นดิน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3571,12 +3571,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องแม่ข่าย)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=39110c90-d236-47eb-913a-cb6b3cab18ba</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a89ffef4-4bf7-41f2-83ef-2e02a1a4e80c</t>
         </is>
       </c>
     </row>
@@ -3588,15 +3588,15 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>สำนักงานการตรวจเงินแผ่นดิน</t>
+          <t>สำนักงานปลัดกระทรวงการอุดมศึกษา วิทยาศาสตร์ วิจัยและนวัตกรรม</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2606</v>
+        <v>23002</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างเหมาบริการขนย้ายเครื่องแม่ข่าย และอุปกรณ์พร้อมติดตั้ง ณ ศูนย์ข้อมูลหลัก ของสำนักงานการตรวจเงินแผ่นดิน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างเหมาบริการบำรุงรักษาเครื่องปรับอากาศ แบบรวมอะไหล่ จำนวน 606 เครื่อง ภายในอาคารอุดมศึกษา 1 อาคารอุดมศึกษา 2 อาคารพระจอมเกล้า และอาคารอเนกประสงค์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3606,32 +3606,32 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>★ (เครื่องแม่ข่าย)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a89ffef4-4bf7-41f2-83ef-2e02a1a4e80c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4ed51246-9d93-42ff-bb32-e9acb8e03644</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการอุดมศึกษา วิทยาศาสตร์ วิจัยและนวัตกรรม</t>
+          <t>สำนักงานบริหารและพัฒนาองค์ความรู้ (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>23002</v>
+        <v>125</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างเหมาบริการบำรุงรักษาเครื่องปรับอากาศ แบบรวมอะไหล่ จำนวน 606 เครื่อง ภายในอาคารอุดมศึกษา 1 อาคารอุดมศึกษา 2 อาคารพระจอมเกล้า และอาคารอเนกประสงค์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4ed51246-9d93-42ff-bb32-e9acb8e03644</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=22d2e215-7492-48e1-8b48-52ebf11afb3d</t>
         </is>
       </c>
     </row>
@@ -3658,15 +3658,15 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>สำนักงานบริหารและพัฒนาองค์ความรู้ (องค์การมหาชน)</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>125</v>
+        <v>204</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ พร้อมอุปกรณ์ จำนวน ๘๐ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=22d2e215-7492-48e1-8b48-52ebf11afb3d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ed207e86-fa08-4bf6-b096-f66e9ea91205</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ พร้อมอุปกรณ์ จำนวน ๘๐ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อสป.สาย ส. ตามโครงการจัดหาอุปกรณ์คอมพิวเตอร์ เพื่อสนับสนุนงานออกแบบสถาปัตยกรรม วิศวกรรมและงานประมาณราคา (ยย.ทบ.) จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ed207e86-fa08-4bf6-b096-f66e9ea91205</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a5d0fbe1-af34-494f-b408-da6f60a04c26</t>
         </is>
       </c>
     </row>
@@ -3728,15 +3728,15 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กรมธนารักษ์</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>204</v>
+        <v>303</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อสป.สาย ส. ตามโครงการจัดหาอุปกรณ์คอมพิวเตอร์ เพื่อสนับสนุนงานออกแบบสถาปัตยกรรม วิศวกรรมและงานประมาณราคา (ยย.ทบ.) จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์อาคารเก็บพัสดุสำนักงานธนารักษ์พื้นที่ชลบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a5d0fbe1-af34-494f-b408-da6f60a04c26</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=606b64be-13e1-468a-84bd-c7c5b46221da</t>
         </is>
       </c>
     </row>
@@ -3763,15 +3763,15 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>กรมธนารักษ์</t>
+          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>303</v>
+        <v>402</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์อาคารเก็บพัสดุสำนักงานธนารักษ์พื้นที่ชลบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาดูแล บำรุงรักษา และล้างทำความสะอาดระบบเครื่องปรับอากาศ ณ อาคารกระทรวงการต่างประเทศ ถนนศรีอยุธยา และศูนย์ราชการเฉลิมพระเกียรติฯ อาคาร B ชั้น 7 - 8 รวม 2 แห่ง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=606b64be-13e1-468a-84bd-c7c5b46221da</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4c0225b9-4c8b-4bbd-80d4-d42eccd0092e</t>
         </is>
       </c>
     </row>
@@ -3798,15 +3798,15 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
+          <t>กรมกิจการเด็กและเยาวชน</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>402</v>
+        <v>605</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาดูแล บำรุงรักษา และล้างทำความสะอาดระบบเครื่องปรับอากาศ ณ อาคารกระทรวงการต่างประเทศ ถนนศรีอยุธยา และศูนย์ราชการเฉลิมพระเกียรติฯ อาคาร B ชั้น 7 - 8 รวม 2 แห่ง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาเครื่องคอมพิวเตอร์ อุปกรณ์ต่อพ่วง และระบบสารสนเทศ ของ ดย. ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4c0225b9-4c8b-4bbd-80d4-d42eccd0092e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cb192597-9852-49f1-81d0-f9bd008c7f6d</t>
         </is>
       </c>
     </row>
@@ -3833,15 +3833,15 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>กรมกิจการเด็กและเยาวชน</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>605</v>
+        <v>704</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาเครื่องคอมพิวเตอร์ อุปกรณ์ต่อพ่วง และระบบสารสนเทศ ของ ดย. ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อครุภัณฑ์ยานพาหนะและขนส่งรถโดยสารขนาด 12 ที่นั่ง (ดีเซล) จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cb192597-9852-49f1-81d0-f9bd008c7f6d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3d257d5-116f-4d11-9cba-b2af7ffd9693</t>
         </is>
       </c>
     </row>
@@ -3868,15 +3868,15 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมประมง</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อครุภัณฑ์ยานพาหนะและขนส่งรถโดยสารขนาด 12 ที่นั่ง (ดีเซล) จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างการจัดจ้างบำรุงรักษาครุภัณฑ์คอมพิวเตอร์สำหรับการรักษาความปลอดภัยของระบบเครือข่ายและคอมพิวเตอร์ จำนวน 1 งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3d257d5-116f-4d11-9cba-b2af7ffd9693</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=29210ba8-e1c2-4d7e-80d4-6acfeb801f71</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างการจัดจ้างบำรุงรักษาครุภัณฑ์คอมพิวเตอร์สำหรับการรักษาความปลอดภัยของระบบเครือข่ายและคอมพิวเตอร์ จำนวน 1 งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างการจัดจ้างบำรุงรักษาอุปกรณ์กระจายสัญญาณ จำนวน ๑ งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=29210ba8-e1c2-4d7e-80d4-6acfeb801f71</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b2bbd6f5-c7a5-4bc3-be9e-fc1ddf4ac0a8</t>
         </is>
       </c>
     </row>
@@ -3938,15 +3938,15 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>กรมประมง</t>
+          <t>สำนักงานมาตรฐานสินค้าเกษตรและอาหารแห่งชาติ</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>705</v>
+        <v>714</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างการจัดจ้างบำรุงรักษาอุปกรณ์กระจายสัญญาณ จำนวน ๑ งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการจ้างเหมาดูแลและบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์และระบบคอมพิวเตอร์พร้อมอุปกรณ์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b2bbd6f5-c7a5-4bc3-be9e-fc1ddf4ac0a8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d133e360-c57e-4330-bff5-2f10cf027da9</t>
         </is>
       </c>
     </row>
@@ -3973,15 +3973,15 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>สำนักงานมาตรฐานสินค้าเกษตรและอาหารแห่งชาติ</t>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>714</v>
+        <v>1302</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการจ้างเหมาดูแลและบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์และระบบคอมพิวเตอร์พร้อมอุปกรณ์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องคอมพิวเตอร์และอุปกรณ์ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d133e360-c57e-4330-bff5-2f10cf027da9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=04549f6b-e678-4005-91df-2993ee4bdb83</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องคอมพิวเตอร์และอุปกรณ์ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่ายของสำนักงานพาณิชย์จังหวัด 76 จังหวัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=04549f6b-e678-4005-91df-2993ee4bdb83</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f1e51f04-f935-4983-8200-42b44f480fc9</t>
         </is>
       </c>
     </row>
@@ -4043,15 +4043,15 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+          <t>สถาบันส่งเสริมศิลปหัตถกรรมไทย (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1302</v>
+        <v>1311</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่ายของสำนักงานพาณิชย์จังหวัด 76 จังหวัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการจัดหาพนักงานดูแลหอนิทรรศการและห้องสมุด ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4061,12 +4061,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (สมุด)</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f1e51f04-f935-4983-8200-42b44f480fc9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ff1d2fa-ba06-4da0-bc6c-023504d3c9d6</t>
         </is>
       </c>
     </row>
@@ -4078,15 +4078,15 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>สถาบันส่งเสริมศิลปหัตถกรรมไทย (องค์การมหาชน)</t>
+          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1311</v>
+        <v>1808</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการจัดหาพนักงานดูแลหอนิทรรศการและห้องสมุด ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์อื่นๆ (เครื่องแต่งกายโขน-ละคร) จำนวน 7 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>★ (สมุด)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ff1d2fa-ba06-4da0-bc6c-023504d3c9d6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8e14fee9-d40a-4d5f-b4ec-b5dd1cbdcc29</t>
         </is>
       </c>
     </row>
@@ -4113,15 +4113,15 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
+          <t>กรมส่งเสริมการเรียนรู้</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1808</v>
+        <v>2033</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์อื่นๆ (เครื่องแต่งกายโขน-ละคร) จำนวน 7 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4131,12 +4131,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8e14fee9-d40a-4d5f-b4ec-b5dd1cbdcc29</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=988b1f6a-eb89-4ed1-bbe5-4e82ba43054b</t>
         </is>
       </c>
     </row>
@@ -4148,15 +4148,15 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเรียนรู้</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>2033</v>
+        <v>2102</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการตู้เย็นเก็บเลือดขนาดไม่น้อยกว่า 20 คิว ของโรงพยาบาลในจังหวัดสุรินทร์ 6 แห่ง จำนวน 7 ตู้ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์, ตู้เย็น)</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=988b1f6a-eb89-4ed1-bbe5-4e82ba43054b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dfce18c4-7835-4a43-8ba6-fb9a2b9ab472</t>
         </is>
       </c>
     </row>
@@ -4183,15 +4183,15 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมอนามัย</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>2102</v>
+        <v>2109</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการตู้เย็นเก็บเลือดขนาดไม่น้อยกว่า 20 คิว ของโรงพยาบาลในจังหวัดสุรินทร์ 6 แห่ง จำนวน 7 ตู้ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่าย กรมอนามัย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์, ตู้เย็น)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dfce18c4-7835-4a43-8ba6-fb9a2b9ab472</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0f1ebcb1-8a09-4209-922e-0e2e49160cba</t>
         </is>
       </c>
     </row>
@@ -4218,15 +4218,15 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>กรมอนามัย</t>
+          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2109</v>
+        <v>2113</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่าย กรมอนามัย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์แม่ข่าย (Outsource System) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0f1ebcb1-8a09-4209-922e-0e2e49160cba</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1c3629ca-59d6-4b8a-839b-92b06d6a1c43</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์แม่ข่าย (Outsource System) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์เครือข่าย (Outsource Network) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4276,27 +4276,27 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1c3629ca-59d6-4b8a-839b-92b06d6a1c43</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b44df475-19c0-4304-b42e-0c379f2f6a07</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+          <t>กองทัพอากาศ</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2113</v>
+        <v>206</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์เครือข่าย (Outsource Network) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโต๊ะและเก้าอี้ประชุม จำนวน ๒ รายการ (แจ้งที่ ๘๙๖/๖๙) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (โต๊ะ, เก้าอี้)</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b44df475-19c0-4304-b42e-0c379f2f6a07</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c197cbba-6119-4a85-8655-64df092381b8</t>
         </is>
       </c>
     </row>
@@ -4323,15 +4323,15 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>กองทัพอากาศ</t>
+          <t>กรมศุลกากร</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>206</v>
+        <v>305</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโต๊ะและเก้าอี้ประชุม จำนวน ๒ รายการ (แจ้งที่ ๘๙๖/๖๙) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องปรับอากาศ แบบฝังฝ้าสี่ทิศทาง (ระบบ Inverter) ขนาด 48,000 บีทียู ด่านศุลกากรปาดังเบซาร์ ตำบลปาดังเบซาร์ อำเภอสะเดา จังหวัดสงขลา 12 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>★ (โต๊ะ, เก้าอี้)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c197cbba-6119-4a85-8655-64df092381b8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7ffdc802-88d9-422f-a01b-27711177cb61</t>
         </is>
       </c>
     </row>
@@ -4358,15 +4358,15 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>กรมศุลกากร</t>
+          <t>กรมสรรพากร</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องปรับอากาศ แบบฝังฝ้าสี่ทิศทาง (ระบบ Inverter) ขนาด 48,000 บีทียู ด่านศุลกากรปาดังเบซาร์ ตำบลปาดังเบซาร์ อำเภอสะเดา จังหวัดสงขลา 12 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบ ไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 2,400 ซีซี  หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ จำนวน 5 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4376,12 +4376,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7ffdc802-88d9-422f-a01b-27711177cb61</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e642705c-f34c-41db-ad86-705717edf0ea</t>
         </is>
       </c>
     </row>
@@ -4393,15 +4393,15 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>กรมสรรพากร</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>307</v>
+        <v>704</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบ ไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 2,400 ซีซี  หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ จำนวน 5 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e642705c-f34c-41db-ad86-705717edf0ea</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5b0cc17-68bd-4696-805e-f78e075178e3</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุด ไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5b0cc17-68bd-4696-805e-f78e075178e3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=106210e4-0233-403f-957c-c894b083d53b</t>
         </is>
       </c>
     </row>
@@ -4463,15 +4463,15 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมส่งเสริมการเกษตร</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุด ไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดชื้อครุภัณฑ์ยานพาหนะและขนส่ง ประจำปีงบประมาณ พ.ศ 2570 โดยวิธีประกวดอิเล็กทรอนิกส์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=106210e4-0233-403f-957c-c894b083d53b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ec4d9c1c-1aa5-4b14-b3ea-60845e7335fb</t>
         </is>
       </c>
     </row>
@@ -4498,15 +4498,15 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเกษตร</t>
+          <t>กรมส่งเสริมสหกรณ์</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดชื้อครุภัณฑ์ยานพาหนะและขนส่ง ประจำปีงบประมาณ พ.ศ 2570 โดยวิธีประกวดอิเล็กทรอนิกส์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาบรรทุกขนาด 1 ตัน หลังคาไฟเบอร์กลาส หรือเหล็กหรือพลาสติกวิศวกรรม สำนักงานสหกรณ์จังหวัดศรีสะเกษ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ec4d9c1c-1aa5-4b14-b3ea-60845e7335fb</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=51b057ec-ffcf-432e-bf86-fe4029225a82</t>
         </is>
       </c>
     </row>
@@ -4533,15 +4533,15 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมสหกรณ์</t>
+          <t>กรมพัฒนาธุรกิจการค้า</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>712</v>
+        <v>1308</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาบรรทุกขนาด 1 ตัน หลังคาไฟเบอร์กลาส หรือเหล็กหรือพลาสติกวิศวกรรม สำนักงานสหกรณ์จังหวัดศรีสะเกษ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องคอมพิวเตอร์ลูกข่ายและอุปกรณ์ต่อพ่วง ปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=51b057ec-ffcf-432e-bf86-fe4029225a82</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=be5cf0cb-614f-4d37-aac0-190b90321cb6</t>
         </is>
       </c>
     </row>
@@ -4568,15 +4568,15 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>กรมพัฒนาธุรกิจการค้า</t>
+          <t>กรมโยธาธิการและผังเมือง</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1308</v>
+        <v>1507</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องคอมพิวเตอร์ลูกข่ายและอุปกรณ์ต่อพ่วง ปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างโครงการจัดหาสิ่งก่อสร้างและครุภัณฑ์ประกอบ อาคารสำนักงานแห่งใหม่ของสำนักงบประมาณ แขวงพญาไท เขตพญาไท กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4586,12 +4586,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=be5cf0cb-614f-4d37-aac0-190b90321cb6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8b31f2b3-f6fd-4e5c-979f-8575feda4bbf</t>
         </is>
       </c>
     </row>
@@ -4603,15 +4603,15 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>กรมโยธาธิการและผังเมือง</t>
+          <t>กรมการศาสนา</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1507</v>
+        <v>1803</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างโครงการจัดหาสิ่งก่อสร้างและครุภัณฑ์ประกอบ อาคารสำนักงานแห่งใหม่ของสำนักงบประมาณ แขวงพญาไท เขตพญาไท กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อวัสดุสำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (วัสดุสำนักงาน)</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8b31f2b3-f6fd-4e5c-979f-8575feda4bbf</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=07f7d716-619d-4e73-9518-7f683a4a05ed</t>
         </is>
       </c>
     </row>
@@ -4638,15 +4638,15 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>กรมการศาสนา</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1803</v>
+        <v>2102</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อวัสดุสำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการชุดกระเป๋าปฐมพยาบาลสนามประจำตัวเจ้าหน้าที่ (IFAK) ของโรงพยาบาลชุมชน 11 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบล 40 แห่ง จำนวน 117 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>★ (วัสดุสำนักงาน)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=07f7d716-619d-4e73-9518-7f683a4a05ed</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=197d72c1-0e0f-4f3d-a377-6f7e052fd668</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการชุดกระเป๋าปฐมพยาบาลสนามประจำตัวเจ้าหน้าที่ (IFAK) ของโรงพยาบาลชุมชน 11 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบล 40 แห่ง จำนวน 117 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=197d72c1-0e0f-4f3d-a377-6f7e052fd668</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a903de26-6f92-4b12-bcdc-87924b3b825b</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อสิทธิ์ใช้งานซอฟต์แวร์จัดการความเสี่ยงเกี่ยวกับระบบสารสนเทศ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a903de26-6f92-4b12-bcdc-87924b3b825b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f182625c-e015-489e-84e0-ac3c9c8dc788</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อสิทธิ์ใช้งานซอฟต์แวร์จัดการความเสี่ยงเกี่ยวกับระบบสารสนเทศ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ กล้องถ่ายภาพจอประสาทตาดิจิตอล (Digital Fundus Camera) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>★ (ซอฟต์แวร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f182625c-e015-489e-84e0-ac3c9c8dc788</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=810bd451-770f-4032-86a0-1216954db79a</t>
         </is>
       </c>
     </row>
@@ -4778,15 +4778,15 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สำนักงานคณะกรรมการอาหารและยา</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2102</v>
+        <v>2110</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ กล้องถ่ายภาพจอประสาทตาดิจิตอล (Digital Fundus Camera) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=810bd451-770f-4032-86a0-1216954db79a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=69d9687c-b7f1-405c-843e-92b98ad29261</t>
         </is>
       </c>
     </row>
@@ -4813,15 +4813,15 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการอาหารและยา</t>
+          <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2110</v>
+        <v>2117</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อติดตั้งระบบกล้องวงจรปิด ของวิทยาลัยพยาบาลบรมราชชนนี นครศรีธรรมราช จำนวน 1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4831,32 +4831,32 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (กล้องวงจรปิด)</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=69d9687c-b7f1-405c-843e-92b98ad29261</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afa9b388-be98-4ed1-8fa9-0c791e5acf34</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>กรมธนารักษ์</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2117</v>
+        <v>303</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อติดตั้งระบบกล้องวงจรปิด ของวิทยาลัยพยาบาลบรมราชชนนี นครศรีธรรมราช จำนวน 1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการทำความสะอาดศูนย์คอมพิวเตอร์แห่งใหม่ ของกรมธนารักษ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>★ (กล้องวงจรปิด)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afa9b388-be98-4ed1-8fa9-0c791e5acf34</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=36f30dd7-0674-4711-a8ba-e71eee8e8ed2</t>
         </is>
       </c>
     </row>
@@ -4883,15 +4883,15 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>กรมธนารักษ์</t>
+          <t>สำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>303</v>
+        <v>502</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการทำความสะอาดศูนย์คอมพิวเตอร์แห่งใหม่ ของกรมธนารักษ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการค่าใช้จ่ายโครงการค่าจ้างบำรุงรักษาและซ่อมแซมห้องปฏิบัติการระบบเครือข่ายคอมพิวเตอร์ (Data Center) ของสำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=36f30dd7-0674-4711-a8ba-e71eee8e8ed2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=056989d3-d491-44ed-b887-fca9a5a8f472</t>
         </is>
       </c>
     </row>
@@ -4918,15 +4918,15 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา</t>
+          <t>กรมส่งเสริมและพัฒนาคุณภาพชีวิตคนพิการ</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>502</v>
+        <v>607</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการค่าใช้จ่ายโครงการค่าจ้างบำรุงรักษาและซ่อมแซมห้องปฏิบัติการระบบเครือข่ายคอมพิวเตอร์ (Data Center) ของสำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์งานบ้านงานครัวและครุภัณฑ์สำนักงาน จำนวน ๒๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=056989d3-d491-44ed-b887-fca9a5a8f472</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f387eaf-54e2-4cf6-8c1c-826da6e3d09e</t>
         </is>
       </c>
     </row>
@@ -4953,15 +4953,15 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมและพัฒนาคุณภาพชีวิตคนพิการ</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>607</v>
+        <v>704</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์งานบ้านงานครัวและครุภัณฑ์สำนักงาน จำนวน ๒๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี. หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บพร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f387eaf-54e2-4cf6-8c1c-826da6e3d09e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b694aef3-f630-4422-a7fe-e31adb551c45</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี. หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บพร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องปรับอากาศแบบแยกส่วน (ราคารวมค่าติดตั้ง) แบบตั้งพื้นหรือแบบแขวน(ระบบ Inverter) ขนาดไม่ต่ำกว่า 36,000 บีทียู จำนวน 13 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b694aef3-f630-4422-a7fe-e31adb551c45</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=08075ad1-9390-4520-9d46-f5c2637228e2</t>
         </is>
       </c>
     </row>
@@ -5023,15 +5023,15 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมส่งเสริมสหกรณ์</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องปรับอากาศแบบแยกส่วน (ราคารวมค่าติดตั้ง) แบบตั้งพื้นหรือแบบแขวน(ระบบ Inverter) ขนาดไม่ต่ำกว่า 36,000 บีทียู จำนวน 13 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=08075ad1-9390-4520-9d46-f5c2637228e2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=282d8226-b5a6-422f-ad5a-96682acbb042</t>
         </is>
       </c>
     </row>
@@ -5058,15 +5058,15 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมสหกรณ์</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>712</v>
+        <v>806</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องตรวจวัดปริมาณแอลกอฮอล์ จำนวน 10 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (แอลกอฮอล์)</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=282d8226-b5a6-422f-ad5a-96682acbb042</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=152668c9-b054-48b8-9423-57975423ef48</t>
         </is>
       </c>
     </row>
@@ -5093,15 +5093,15 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>กรมการเปลี่ยนแปลงสภาพภูมิอากาศและสิ่งแวดล้อม</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>806</v>
+        <v>908</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องตรวจวัดปริมาณแอลกอฮอล์ จำนวน 10 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาอุปกรณ์ห้อง Data center และเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>★ (แอลกอฮอล์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=152668c9-b054-48b8-9423-57975423ef48</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3fa0cd84-f2db-47df-b581-c3555885f305</t>
         </is>
       </c>
     </row>
@@ -5128,15 +5128,15 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>กรมการเปลี่ยนแปลงสภาพภูมิอากาศและสิ่งแวดล้อม</t>
+          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>908</v>
+        <v>1202</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาอุปกรณ์ห้อง Data center และเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์เครือข่ายและอุปกรณ์คอมพิวเตอร์แม่ข่าย และอุปกรณ์สำรองข้อมูล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3fa0cd84-f2db-47df-b581-c3555885f305</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=86fe9b9f-c1ba-4f83-8b12-70dbc5d76baa</t>
         </is>
       </c>
     </row>
@@ -5163,15 +5163,15 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1202</v>
+        <v>1302</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์เครือข่ายและอุปกรณ์คอมพิวเตอร์แม่ข่าย และอุปกรณ์สำรองข้อมูล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์สำหรับงานจดทะเบียนและตรวจสอบธุรกิจผิดกฎหมาย กลุ่มทะเบียนธุรกิจและอำนวยความสะดวกทางการค้าของสำนักงานพาณิชย์จังหวัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=86fe9b9f-c1ba-4f83-8b12-70dbc5d76baa</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=06246921-2a22-4f4d-822b-d5abae1c7c8c</t>
         </is>
       </c>
     </row>
@@ -5198,15 +5198,15 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+          <t>กรมสอบสวนคดีพิเศษ</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1302</v>
+        <v>1608</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์สำหรับงานจดทะเบียนและตรวจสอบธุรกิจผิดกฎหมาย กลุ่มทะเบียนธุรกิจและอำนวยความสะดวกทางการค้าของสำนักงานพาณิชย์จังหวัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าเช่าใช้บริการสายสัญญาณเชื่อมโยงเครือข่ายอินเตอร์เน็ตพร้อมระบบ Internet Data Center ประจำปีงบประมาณ พ.ศ. 2570 (เดือนตุลาคม 2569  เดือนกันยายน 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (สายสัญญาณ)</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=06246921-2a22-4f4d-822b-d5abae1c7c8c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f0c10124-df0c-410d-961c-bb4afe1ea16a</t>
         </is>
       </c>
     </row>
@@ -5233,15 +5233,15 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>กรมสอบสวนคดีพิเศษ</t>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าเช่าใช้บริการสายสัญญาณเชื่อมโยงเครือข่ายอินเตอร์เน็ตพร้อมระบบ Internet Data Center ประจำปีงบประมาณ พ.ศ. 2570 (เดือนตุลาคม 2569  เดือนกันยายน 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบประชุมทางไกลผ่านจอภาพ (Video Conference)  ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>★ (สายสัญญาณ)</t>
+          <t>★ (จอภาพ, ระบบประชุมทางไกล)</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f0c10124-df0c-410d-961c-bb4afe1ea16a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bb2e1625-bd6e-49b0-bf5e-6f3975c796e5</t>
         </is>
       </c>
     </row>
@@ -5268,15 +5268,15 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1611</v>
+        <v>2102</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบประชุมทางไกลผ่านจอภาพ (Video Conference)  ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันขนาดกลาง โรงพยาบาลเขาย้อย ตำบลเขาย้อย อำเภอเขาย้อย จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5286,12 +5286,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>★ (จอภาพ, ระบบประชุมทางไกล)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bb2e1625-bd6e-49b0-bf5e-6f3975c796e5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4d438ead-6d3b-40c3-8e25-0c855ca2699d</t>
         </is>
       </c>
     </row>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันขนาดกลาง โรงพยาบาลเขาย้อย ตำบลเขาย้อย อำเภอเขาย้อย จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง โรงพยาบาลหนองหญ้าปล้อง ตำบลหนองหญ้าปล้อง อำเภอหนองหญ้าปล้อง จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4d438ead-6d3b-40c3-8e25-0c855ca2699d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=38179365-12e6-43e5-ac4b-973f7d7d62c9</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง โรงพยาบาลหนองหญ้าปล้อง ตำบลหนองหญ้าปล้อง อำเภอหนองหญ้าปล้อง จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดัน ขนาดใหญ่ จำนวน 2 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=38179365-12e6-43e5-ac4b-973f7d7d62c9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2c8651ab-6342-4cf7-b1d4-44acb01ef167</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดัน ขนาดใหญ่ จำนวน 2 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดเล็ก ของโรงพยาบาลชุมชน 2 แห่ง จำนวน 6 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2c8651ab-6342-4cf7-b1d4-44acb01ef167</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=092dea18-169e-423d-bdf4-cbb905df5ef4</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดเล็ก ของโรงพยาบาลชุมชน 2 แห่ง จำนวน 6 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องเอกซเรย์เคลื่อนที่ขนาดไม่น้อยกว่า 300 mA.ขับเคลื่อนด้วยมอเตอร์ไฟฟ้า ของโรงพยาบาลในจังหวัดสุรินทร์ 3 แห่ง จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์, มอเตอร์)</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=092dea18-169e-423d-bdf4-cbb905df5ef4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=587ceaac-9b51-4f53-a40b-ba6307295dbc</t>
         </is>
       </c>
     </row>
@@ -5443,15 +5443,15 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมการแพทย์แผนไทยและการแพทย์ทางเลือก</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>2102</v>
+        <v>2105</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องเอกซเรย์เคลื่อนที่ขนาดไม่น้อยกว่า 300 mA.ขับเคลื่อนด้วยมอเตอร์ไฟฟ้า ของโรงพยาบาลในจังหวัดสุรินทร์ 3 แห่ง จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างบำรุงรักษาและซ่อมแซมแก้ไขปัญหาเครื่องคอมพิวเตอร์แม่ข่ายและอุปกรณ์ระบบเครือข่าย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์, มอเตอร์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=587ceaac-9b51-4f53-a40b-ba6307295dbc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a18ab514-a7bf-42a3-be34-78ab2073afdd</t>
         </is>
       </c>
     </row>
@@ -5478,15 +5478,15 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>กรมการแพทย์แผนไทยและการแพทย์ทางเลือก</t>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างบำรุงรักษาและซ่อมแซมแก้ไขปัญหาเครื่องคอมพิวเตอร์แม่ข่ายและอุปกรณ์ระบบเครือข่าย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน ๙ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a18ab514-a7bf-42a3-be34-78ab2073afdd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70e80b61-ece5-4761-bcba-cb1ce4f2a872</t>
         </is>
       </c>
     </row>
@@ -5513,15 +5513,15 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>กรมวิทยาศาสตร์การแพทย์</t>
+          <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>2106</v>
+        <v>2117</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน ๙ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อึครุภัณฑ์สำนักงาน รายการเครื่องปรับอากาศและพัดลม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5531,12 +5531,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ, พัดลม)</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70e80b61-ece5-4761-bcba-cb1ce4f2a872</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8cf26d57-cf1b-4ebf-8134-fcf45b7f7c54</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อึครุภัณฑ์สำนักงาน รายการเครื่องปรับอากาศและพัดลม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง (รถยนต์บรรทุกโดยสาร 6 ล้อ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5566,32 +5566,32 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ, พัดลม)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8cf26d57-cf1b-4ebf-8134-fcf45b7f7c54</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=37a7653e-4e42-4513-bc7a-c74cd6a83f90</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>สถาบันเทคโนโลยีป้องกันประเทศ</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>2117</v>
+        <v>209</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง (รถยนต์บรรทุกโดยสาร 6 ล้อ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างซ่อมบำรุงตามวงรอบเครื่องปรับอากาศ อาคาร สป. (แจ้งวัฒนะ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=37a7653e-4e42-4513-bc7a-c74cd6a83f90</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=97592008-d14e-46f6-93ee-062a71e2e9a9</t>
         </is>
       </c>
     </row>
@@ -5618,15 +5618,15 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>สถาบันเทคโนโลยีป้องกันประเทศ</t>
+          <t>สำนักงานปลัดกระทรวงการคลัง</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>209</v>
+        <v>302</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างซ่อมบำรุงตามวงรอบเครื่องปรับอากาศ อาคาร สป. (แจ้งวัฒนะ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อการจัดซื้อหมึกพิมพ์สำหรับ GFMIS Terminal Set เพื่อใช้งานในระบบ New GFMIS Thai ของกรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (หมึกพิมพ์)</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=97592008-d14e-46f6-93ee-062a71e2e9a9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=95f4ee7d-0617-43e5-8099-6f58ee3f83c4</t>
         </is>
       </c>
     </row>
@@ -5653,15 +5653,15 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการคลัง</t>
+          <t>กรมชลประทาน</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>302</v>
+        <v>703</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อการจัดซื้อหมึกพิมพ์สำหรับ GFMIS Terminal Set เพื่อใช้งานในระบบ New GFMIS Thai ของกรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจัดหาและติดตั้งเครื่องสูบน้ำชนิดหอยโข่งแบบ Horizontal Split Case ขับด้วยมอเตอร์ไฟฟ้าอัตราสูบน้ำ ๐.๒๕ ลบ.ม. /วินาที ระยะยกน้ำไม่น้อยกว่า ๔๕ เมตร และอื่นๆ รวม ๔ รายการ  สำหรับงานสถานีสูบน้ำด้วยไฟฟ้าพร้อมระบบส่งน้ำ บ้านสุขสำราญ ตำบลเหล่าต่างคำ อำเภอโพนพิสัย จังหวัดหนองคาย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>★ (หมึกพิมพ์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=95f4ee7d-0617-43e5-8099-6f58ee3f83c4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=766b91be-9aee-491f-bc67-3378c2319ca0</t>
         </is>
       </c>
     </row>
@@ -5688,15 +5688,15 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>กรมชลประทาน</t>
+          <t>กรมประมง</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจัดหาและติดตั้งเครื่องสูบน้ำชนิดหอยโข่งแบบ Horizontal Split Case ขับด้วยมอเตอร์ไฟฟ้าอัตราสูบน้ำ ๐.๒๕ ลบ.ม. /วินาที ระยะยกน้ำไม่น้อยกว่า ๔๕ เมตร และอื่นๆ รวม ๔ รายการ  สำหรับงานสถานีสูบน้ำด้วยไฟฟ้าพร้อมระบบส่งน้ำ บ้านสุขสำราญ ตำบลเหล่าต่างคำ อำเภอโพนพิสัย จังหวัดหนองคาย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน 4 รายการ วิธีประกาศเชิญชวน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=766b91be-9aee-491f-bc67-3378c2319ca0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6af84224-9211-4bd4-b2c3-7790e12e9c3f</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน 4 รายการ วิธีประกาศเชิญชวน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน 4 รายการ  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6af84224-9211-4bd4-b2c3-7790e12e9c3f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=106fd353-637b-4b85-b19c-e5222b434807</t>
         </is>
       </c>
     </row>
@@ -5758,15 +5758,15 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>กรมประมง</t>
+          <t>สำนักงานเศรษฐกิจการเกษตร</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน 4 รายการ  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์หรือระบบสารสนเทศ (โครงการจ้างบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์เครือข่ายและเครื่องคอมพิวเตอร์แม่ข่าย ประจำปีงบประมาณ พ.ศ. 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=106fd353-637b-4b85-b19c-e5222b434807</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e3936fb8-2fe4-4ded-a393-134ec5675427</t>
         </is>
       </c>
     </row>
@@ -5793,15 +5793,15 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>สำนักงานเศรษฐกิจการเกษตร</t>
+          <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>715</v>
+        <v>804</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์หรือระบบสารสนเทศ (โครงการจ้างบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์เครือข่ายและเครื่องคอมพิวเตอร์แม่ข่าย ประจำปีงบประมาณ พ.ศ. 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์พร้อมอุปกรณ์ของระบบการคุ้มครองผู้โดยสารและ การบังคับใช้กฎหมายทั่วไทย (1584 และปรับทั่วไทย) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e3936fb8-2fe4-4ded-a393-134ec5675427</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f5c51a3c-9d4b-4662-a9c5-a560b97ab60f</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์พร้อมอุปกรณ์ของระบบการคุ้มครองผู้โดยสารและ การบังคับใช้กฎหมายทั่วไทย (1584 และปรับทั่วไทย) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างรั้ว ประตูทางเข้า - ออก ป้ายชื่อสำนักงาน และป้อมยามรักษาการณ์ สำนักงานขนส่งจังหวัดลำปาง ตำบลพระบาท อำเภอเมือง จังหวัดลำปาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ป้ายชื่อ)</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f5c51a3c-9d4b-4662-a9c5-a560b97ab60f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f104579c-ae74-4bdb-a71c-250b1777b2c9</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างรั้ว ประตูทางเข้า - ออก ป้ายชื่อสำนักงาน และป้อมยามรักษาการณ์ สำนักงานขนส่งจังหวัดลำปาง ตำบลพระบาท อำเภอเมือง จังหวัดลำปาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขเครื่องคอมพิวเตอร์พร้อมอุปกรณ์ที่ใช้ในการพัฒนาความรู้สารสนเทศ  ด้านความปลอดภัยของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -5881,12 +5881,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>★ (ป้ายชื่อ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f104579c-ae74-4bdb-a71c-250b1777b2c9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a8c5a924-f969-4f66-a783-51c748bd5141</t>
         </is>
       </c>
     </row>
@@ -5898,15 +5898,15 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
+          <t>กรมอุตุนิยมวิทยา</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>804</v>
+        <v>1104</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขเครื่องคอมพิวเตอร์พร้อมอุปกรณ์ที่ใช้ในการพัฒนาความรู้สารสนเทศ  ด้านความปลอดภัยของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาอุปกรณ์กระจายสัญญาณหลัก (Core Switch) ประจำปีงบประมาณ พ.ศ.2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a8c5a924-f969-4f66-a783-51c748bd5141</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b6951565-26a5-4131-b672-af48d4974842</t>
         </is>
       </c>
     </row>
@@ -5933,15 +5933,15 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>กรมอุตุนิยมวิทยา</t>
+          <t>กรมที่ดิน</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1104</v>
+        <v>1505</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาอุปกรณ์กระจายสัญญาณหลัก (Core Switch) ประจำปีงบประมาณ พ.ศ.2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโต๊ะและเก้าอี้เพื่อใช้ในราชการของสำนักงานที่ดินจังหวัดพิษณุโลก และสาขา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
+          <t>★ (โต๊ะ, เก้าอี้)</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b6951565-26a5-4131-b672-af48d4974842</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=06a6ae3e-1109-434c-becf-df99302f96f5</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโต๊ะและเก้าอี้เพื่อใช้ในราชการของสำนักงานที่ดินจังหวัดพิษณุโลก และสาขา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบงานและอุปกรณ์คอมพิวเตอร์ ตามโครงการพัฒนาระบบสารสนเทศที่ดิน (ระยะที่ ๒) ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -5986,12 +5986,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>★ (โต๊ะ, เก้าอี้)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=06a6ae3e-1109-434c-becf-df99302f96f5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0e343fde-5a22-4f02-b2b3-bcf7cfd99bf2</t>
         </is>
       </c>
     </row>
@@ -6003,15 +6003,15 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>กรมที่ดิน</t>
+          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1505</v>
+        <v>1808</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบงานและอุปกรณ์คอมพิวเตอร์ ตามโครงการพัฒนาระบบสารสนเทศที่ดิน (ระยะที่ ๒) ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์การศึกษา (ห้องเรียนอัจฉริยะไฮบริด Smart Hybrid Classroom) ห้องเรียนวิชาชีพ จำนวน 1 ห้อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0e343fde-5a22-4f02-b2b3-bcf7cfd99bf2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a6ddc2c9-4ad2-4cd7-93c9-2b5e9a715cfd</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์การศึกษา (ห้องเรียนอัจฉริยะไฮบริด Smart Hybrid Classroom) ห้องเรียนวิชาชีพ จำนวน 1 ห้อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์โฆษณาแะเผยแพร่ (ระบบภาพ LED Display พร้อมติดตั้งภายนอกอาคาร) จำนวน  1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a6ddc2c9-4ad2-4cd7-93c9-2b5e9a715cfd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7b99fd52-1723-486a-a5ce-43a450641ed9</t>
         </is>
       </c>
     </row>
@@ -6073,15 +6073,15 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
+          <t>สำนักงานนวัตกรรมแห่งชาติ (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1808</v>
+        <v>1913</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์โฆษณาแะเผยแพร่ (ระบบภาพ LED Display พร้อมติดตั้งภายนอกอาคาร) จำนวน  1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างเหมาบริการบำรุงรักษาอุปกรณ์ภายในศูนย์ข้อมูลคอมพิวเตอร์(Data Center) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7b99fd52-1723-486a-a5ce-43a450641ed9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70ea1f2e-64d2-48c7-888f-f39d061663c3</t>
         </is>
       </c>
     </row>
@@ -6108,15 +6108,15 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>สำนักงานนวัตกรรมแห่งชาติ (องค์การมหาชน)</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1913</v>
+        <v>2102</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างเหมาบริการบำรุงรักษาอุปกรณ์ภายในศูนย์ข้อมูลคอมพิวเตอร์(Data Center) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70ea1f2e-64d2-48c7-888f-f39d061663c3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5dcaa2f-3e4d-49bc-9324-4c94f510ab5f</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องควบคุมการให้สารน้ำทางหลอดเลือดดำชนิด 1 สาย ของโรงพยาบาลในจังหวัดสุรินทร์ 9 แห่ง จำนวน 66 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5dcaa2f-3e4d-49bc-9324-4c94f510ab5f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=af446873-e18e-4ed1-bd5c-bd34b74e9b76</t>
         </is>
       </c>
     </row>
@@ -6178,15 +6178,15 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมการแพทย์</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องควบคุมการให้สารน้ำทางหลอดเลือดดำชนิด 1 สาย ของโรงพยาบาลในจังหวัดสุรินทร์ 9 แห่ง จำนวน 66 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์เครื่องเสริมสร้างความแข็งแรงของกล้ามเนื้ออุ้งเชิงกราน รักษาอาการปัสสาวะเล็ด ลดอาการปวดจากกล้ามเนื้อและระบบประสาทบริเวณ อุ้งเชิงกรานและหลังด้วยคลื่นแม่เหล็กไฟฟ้า สถาบันเวชศาสตร์สมเด็จพระสังฆราชญาณสังวรเพื่อผู้สูงอายุ ตำบลตลาดขวัญ อำเภอเมือง จังหวัดนนทบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -6201,27 +6201,27 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=af446873-e18e-4ed1-bd5c-bd34b74e9b76</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=543d641e-2bab-40db-bddc-5b9d81caf16b</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>กรมการแพทย์</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>2103</v>
+        <v>204</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์เครื่องเสริมสร้างความแข็งแรงของกล้ามเนื้ออุ้งเชิงกราน รักษาอาการปัสสาวะเล็ด ลดอาการปวดจากกล้ามเนื้อและระบบประสาทบริเวณ อุ้งเชิงกรานและหลังด้วยคลื่นแม่เหล็กไฟฟ้า สถาบันเวชศาสตร์สมเด็จพระสังฆราชญาณสังวรเพื่อผู้สูงอายุ ตำบลตลาดขวัญ อำเภอเมือง จังหวัดนนทบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำหรับงานซ่อมปรับปรุงสนามกีฬาของ หน่วยบัญชาการสงครามพิเศษ เพื่อรองรับการแข่งขันกีฬา กองทัพบก ครั้งที่ 74 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=543d641e-2bab-40db-bddc-5b9d81caf16b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=91712891-37fd-4bbc-ae6c-0044106ce3a9</t>
         </is>
       </c>
     </row>
@@ -6248,15 +6248,15 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>204</v>
+        <v>704</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์สำหรับงานซ่อมปรับปรุงสนามกีฬาของ หน่วยบัญชาการสงครามพิเศษ เพื่อรองรับการแข่งขันกีฬา กองทัพบก ครั้งที่ 74 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะ รถโดยสารขนาด 12 ที่นั่ง (ดีเซล) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=91712891-37fd-4bbc-ae6c-0044106ce3a9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6d9307c6-812c-4689-9154-bd79b77edeed</t>
         </is>
       </c>
     </row>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะ รถโดยสารขนาด 12 ที่นั่ง (ดีเซล) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องคอมพิวเตอร์โน๊ตบุ๊ค สำหรับงานประมวลผล พร้อมชุดโปรแกรมระบบปฏิบัติการสำหรับคอมพิวเตอร์และเครี่องคอมพิวเตอร์โน๊ตบุ๊ค แบบสิทธิการใช้งานภายในสำนักงาน ประเภทติดตั้งมาจากโรงงาน (OEM) ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย ชุดโปรแกรมจัดการสำนักงาน แบบที่ 2   ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย และชุดโปรแกรมป้องกันไวรัส จำนวน 21 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -6301,12 +6301,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, โน๊ตบุ๊ค, ระบบปฏิบัติการ, โปรแกรมป้องกันไวรัส)</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6d9307c6-812c-4689-9154-bd79b77edeed</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ac28390d-f1a5-41e3-8fed-7350ce5638bc</t>
         </is>
       </c>
     </row>
@@ -6318,15 +6318,15 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>704</v>
+        <v>805</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องคอมพิวเตอร์โน๊ตบุ๊ค สำหรับงานประมวลผล พร้อมชุดโปรแกรมระบบปฏิบัติการสำหรับคอมพิวเตอร์และเครี่องคอมพิวเตอร์โน๊ตบุ๊ค แบบสิทธิการใช้งานภายในสำนักงาน ประเภทติดตั้งมาจากโรงงาน (OEM) ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย ชุดโปรแกรมจัดการสำนักงาน แบบที่ 2   ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย และชุดโปรแกรมป้องกันไวรัส จำนวน 21 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานหัวหิน ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, โน๊ตบุ๊ค, ระบบปฏิบัติการ, โปรแกรมป้องกันไวรัส)</t>
+          <t>★ (รถเข็น)</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ac28390d-f1a5-41e3-8fed-7350ce5638bc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f40b4d90-5120-4848-a5d2-b177de8a9a09</t>
         </is>
       </c>
     </row>
@@ -6353,15 +6353,15 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
+          <t>กรมพัฒนาธุรกิจการค้า</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>805</v>
+        <v>1308</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานหัวหิน ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์แม่ข่ายและอุปกรณ์รักษาความปลอดภัย ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>★ (รถเข็น)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f40b4d90-5120-4848-a5d2-b177de8a9a09</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=652c12bb-908d-48aa-a87c-f244b33e9ad3</t>
         </is>
       </c>
     </row>
@@ -6388,15 +6388,15 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>กรมพัฒนาธุรกิจการค้า</t>
+          <t>กรมที่ดิน</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1308</v>
+        <v>1505</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์แม่ข่ายและอุปกรณ์รักษาความปลอดภัย ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมอุปกรณ์ รวม ๘ รายการ สำหรับใช้ในราชการกองเทคโนโลยีทำแผนที่ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=652c12bb-908d-48aa-a87c-f244b33e9ad3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c85d670f-a209-4413-8ade-5dba1d3d0298</t>
         </is>
       </c>
     </row>
@@ -6423,15 +6423,15 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>กรมที่ดิน</t>
+          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1505</v>
+        <v>1905</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมอุปกรณ์ รวม ๘ รายการ สำหรับใช้ในราชการกองเทคโนโลยีทำแผนที่ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์โครงการห้องปฏิบัติการทดสอบด้านวิศวกรรมการใช้งาน (Usability Engineering) ผลิตภัณฑ์ซอฟต์แวร์หุ่นยนต์ทางการแพทย์และเครื่องมือแพทย์ตามมาตรฐานสากล (Usability Engineering Laboratories for Software, Medical Robotics, and Medical Devices under International Standards) จํานวน ๑ ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ซอฟต์แวร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c85d670f-a209-4413-8ade-5dba1d3d0298</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0415b5bd-8794-467b-9e54-5ae4bdabae87</t>
         </is>
       </c>
     </row>
@@ -6458,15 +6458,15 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1905</v>
+        <v>2102</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์โครงการห้องปฏิบัติการทดสอบด้านวิศวกรรมการใช้งาน (Usability Engineering) ผลิตภัณฑ์ซอฟต์แวร์หุ่นยนต์ทางการแพทย์และเครื่องมือแพทย์ตามมาตรฐานสากล (Usability Engineering Laboratories for Software, Medical Robotics, and Medical Devices under International Standards) จํานวน ๑ ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องอุ่นเลือดและส่วนประกอบของเลือดชนิดไม่สัมผัสน้ำสามารถอุ่นเลือดได้ พร้อมกันไม่น้อยกว่า 3 ถุง จำนวน 4 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย -  กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>★ (ซอฟต์แวร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0415b5bd-8794-467b-9e54-5ae4bdabae87</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2157b09f-d16e-4bcf-b720-de1088bc7b0e</t>
         </is>
       </c>
     </row>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องอุ่นเลือดและส่วนประกอบของเลือดชนิดไม่สัมผัสน้ำสามารถอุ่นเลือดได้ พร้อมกันไม่น้อยกว่า 3 ถุง จำนวน 4 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย -  กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องควบคุมการให้สารละลายโดยใช้กระบอกฉีด ของโรงพยาบาลในจังหวัดสุรินทร์ 5 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบลสำเภาลูน จำนวน 26 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2157b09f-d16e-4bcf-b720-de1088bc7b0e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=33f2d0df-213d-44c4-a6fa-d31b0eb2e1f6</t>
         </is>
       </c>
     </row>
@@ -6528,15 +6528,15 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>2102</v>
+        <v>2106</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องควบคุมการให้สารละลายโดยใช้กระบอกฉีด ของโรงพยาบาลในจังหวัดสุรินทร์ 5 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบลสำเภาลูน จำนวน 26 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาซ่อมแซมแก้ไขระบบเครือข่ายและเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -6546,12 +6546,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=33f2d0df-213d-44c4-a6fa-d31b0eb2e1f6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=77d1f891-c26e-4f3d-a9e2-7ca16c4196b3</t>
         </is>
       </c>
     </row>
@@ -6563,15 +6563,15 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>กรมวิทยาศาสตร์การแพทย์</t>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาซ่อมแซมแก้ไขระบบเครือข่ายและเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -6581,12 +6581,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=77d1f891-c26e-4f3d-a9e2-7ca16c4196b3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b600d06e-5f90-400c-80fc-24c6ae2ef280</t>
         </is>
       </c>
     </row>
@@ -6598,15 +6598,15 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>กรมสนับสนุนบริการสุขภาพ</t>
+          <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>2107</v>
+        <v>2117</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์วิทยาศาสตร์การแพทย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b600d06e-5f90-400c-80fc-24c6ae2ef280</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a3db48e8-9e8b-4535-84a6-a14f5811619b</t>
         </is>
       </c>
     </row>
@@ -6633,15 +6633,15 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>สำนักงานพระพุทธศาสนาแห่งชาติ</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>2117</v>
+        <v>2503</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์วิทยาศาสตร์การแพทย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -6651,32 +6651,32 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a3db48e8-9e8b-4535-84a6-a14f5811619b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=285cc870-c52b-429d-b866-52f939bc7fd0</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>สำนักงานพระพุทธศาสนาแห่งชาติ</t>
+          <t>กรมพัฒนาที่ดิน</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>2503</v>
+        <v>708</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจอแสดงผล LED พร้อมอุปกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (จอแสดงผล)</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=285cc870-c52b-429d-b866-52f939bc7fd0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=45d8cd64-624e-4582-a8d1-3fe3d01e41b6</t>
         </is>
       </c>
     </row>
@@ -6703,15 +6703,15 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>กรมพัฒนาที่ดิน</t>
+          <t>กรมการข้าว</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจอแสดงผล LED พร้อมอุปกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องปรับอากาศ แบบแยกส่วน แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>★ (จอแสดงผล)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=45d8cd64-624e-4582-a8d1-3fe3d01e41b6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2475fb18-8633-42d5-8fe6-f520615dc6f7</t>
         </is>
       </c>
     </row>
@@ -6738,15 +6738,15 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>กรมการข้าว</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>718</v>
+        <v>806</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องปรับอากาศ แบบแยกส่วน แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ และ ครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 13 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -6756,12 +6756,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2475fb18-8633-42d5-8fe6-f520615dc6f7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0b00828b-7442-420e-85c9-ad09d2f6e16f</t>
         </is>
       </c>
     </row>
@@ -6773,15 +6773,15 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>กรมทรัพยากรน้ำบาดาล</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>806</v>
+        <v>907</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ และ ครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 13 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องสูบน้ำไฟฟ้าชนิดมอเตอร์จุ่มใต้น้ำ พร้อมอุปกรณ์ และชุดฝาปิดปากบ่อน้ำบาดาล จำนวน ๖ ชุด โครงการพัฒนาน้ำบาดาลเพื่อความมั่นคงระดับชุมชน ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ (งบเหลือจ่าย) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0b00828b-7442-420e-85c9-ad09d2f6e16f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=03ba8462-a0d1-4d13-92c2-a7ae76fed3d0</t>
         </is>
       </c>
     </row>
@@ -6808,15 +6808,15 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>กรมทรัพยากรน้ำบาดาล</t>
+          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องสูบน้ำไฟฟ้าชนิดมอเตอร์จุ่มใต้น้ำ พร้อมอุปกรณ์ และชุดฝาปิดปากบ่อน้ำบาดาล จำนวน ๖ ชุด โครงการพัฒนาน้ำบาดาลเพื่อความมั่นคงระดับชุมชน ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ (งบเหลือจ่าย) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทเรือหางยาวสำหรับการลาดตระเวนพื้นที่ทางน้ำ เพื่อเพิ่มประสิทธิภาพการปฏิบัติงานอุทยานแห่งชาติเขาแหลม จังหวัดกาญจนบุรี  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -6826,12 +6826,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=03ba8462-a0d1-4d13-92c2-a7ae76fed3d0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63f7333f-eb0c-40fa-8c06-5f683d543bce</t>
         </is>
       </c>
     </row>
@@ -6843,15 +6843,15 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
+          <t>กรมการปกครอง</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>909</v>
+        <v>1503</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทเรือหางยาวสำหรับการลาดตระเวนพื้นที่ทางน้ำ เพื่อเพิ่มประสิทธิภาพการปฏิบัติงานอุทยานแห่งชาติเขาแหลม จังหวัดกาญจนบุรี  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อวัสดุครุภัณฑ์สำนักงานที่ทำการปกครองอำเภอตาพระยา จังหวัดสระแก้ว ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -6861,12 +6861,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63f7333f-eb0c-40fa-8c06-5f683d543bce</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=de60da4a-56f9-434f-bd1c-60d19d95f672</t>
         </is>
       </c>
     </row>
@@ -6878,15 +6878,15 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>กรมการปกครอง</t>
+          <t>กรมที่ดิน</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อวัสดุครุภัณฑ์สำนักงานที่ทำการปกครองอำเภอตาพระยา จังหวัดสระแก้ว ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์เพื่อการบริหารจัดการหน่วยงานส่วนกลาง (Hardware และ Software) ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -6896,12 +6896,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=de60da4a-56f9-434f-bd1c-60d19d95f672</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a80802ed-6d42-4b60-b93c-de21fb24e5c0</t>
         </is>
       </c>
     </row>
@@ -6913,15 +6913,15 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>กรมที่ดิน</t>
+          <t>กรมการจัดหางาน</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1505</v>
+        <v>1703</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์เพื่อการบริหารจัดการหน่วยงานส่วนกลาง (Hardware และ Software) ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ทดแทนและเพิ่มประสิทธิภาพของสำนักบริหารแรงงานต่างด้าว ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a80802ed-6d42-4b60-b93c-de21fb24e5c0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f3092a7e-5bf1-488f-8f3f-6657ba0fe2fd</t>
         </is>
       </c>
     </row>
@@ -6948,15 +6948,15 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>กรมการจัดหางาน</t>
+          <t>กรมพัฒนาฝีมือแรงงาน</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ทดแทนและเพิ่มประสิทธิภาพของสำนักบริหารแรงงานต่างด้าว ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ (ระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop) ขนาด 3 เฟส 15 กิโลวัตต์ ตำบลบ่อ อำเภอขลุง จังหวัดจันทบุรี จำนวน 1 ระบบ และระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop) ขนาด 3 เฟส 20 กิโลวัตต์ ตำบลบ่อ อำเภอขลุง จังหวัดจันทบุรี จำนวน 1 ระบบ) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f3092a7e-5bf1-488f-8f3f-6657ba0fe2fd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d90e4389-d0ce-48d4-b93a-03874d22d178</t>
         </is>
       </c>
     </row>
@@ -6983,15 +6983,15 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>กรมพัฒนาฝีมือแรงงาน</t>
+          <t>กรมการศาสนา</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1704</v>
+        <v>1803</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ (ระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop) ขนาด 3 เฟส 15 กิโลวัตต์ ตำบลบ่อ อำเภอขลุง จังหวัดจันทบุรี จำนวน 1 ระบบ และระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop) ขนาด 3 เฟส 20 กิโลวัตต์ ตำบลบ่อ อำเภอขลุง จังหวัดจันทบุรี จำนวน 1 ระบบ) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อหมึกเครื่องพิมพ์ (ครั้งที่ 2)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -7001,12 +7001,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (หมึกเครื่องพิมพ์, เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d90e4389-d0ce-48d4-b93a-03874d22d178</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8ffdb256-bac2-4342-bdf6-7616e2ae5b25</t>
         </is>
       </c>
     </row>
@@ -7018,15 +7018,15 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>กรมการศาสนา</t>
+          <t>สถาบันมาตรวิทยาแห่งชาติ</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1803</v>
+        <v>1907</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อหมึกเครื่องพิมพ์ (ครั้งที่ 2)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างค่าบำรุงรักษาอุปกรณ์เครือข่ายประจำอาคาร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -7036,12 +7036,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>★ (หมึกเครื่องพิมพ์, เครื่องพิมพ์)</t>
+          <t>★ (อุปกรณ์เครือข่าย)</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8ffdb256-bac2-4342-bdf6-7616e2ae5b25</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b698a86e-10e2-45f2-be5e-f7ec03fa0ce9</t>
         </is>
       </c>
     </row>
@@ -7053,15 +7053,15 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>สถาบันมาตรวิทยาแห่งชาติ</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1907</v>
+        <v>2102</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างค่าบำรุงรักษาอุปกรณ์เครือข่ายประจำอาคาร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการรถพยาบาลพร้อมอุปกรณ์ช่วยชีวิตชั้นสูง ของโรงพยาบาลชุมชน 4 แห่ง จำนวน 4 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -7071,12 +7071,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>★ (อุปกรณ์เครือข่าย)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b698a86e-10e2-45f2-be5e-f7ec03fa0ce9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f77b490-654b-45ac-9d8e-cc1f4f3fd4fb</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการรถพยาบาลพร้อมอุปกรณ์ช่วยชีวิตชั้นสูง ของโรงพยาบาลชุมชน 4 แห่ง จำนวน 4 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดออกซิเจนในเลือดอัตโนมัติชนิดพกพา จำนวน 39 เครื่องๆ งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f77b490-654b-45ac-9d8e-cc1f4f3fd4fb</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f13af428-4413-4d73-9542-bd582ed6e240</t>
         </is>
       </c>
     </row>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดออกซิเจนในเลือดอัตโนมัติชนิดพกพา จำนวน 39 เครื่องๆ งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจคลื่นไฟฟ้าหัวใจ พร้อมเชื่อมต่อระบบแพทย์ทางไกล จำนวน 27 เครื่อง งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f13af428-4413-4d73-9542-bd582ed6e240</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9350a991-2cda-4337-b005-93d114caf75c</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจคลื่นไฟฟ้าหัวใจ พร้อมเชื่อมต่อระบบแพทย์ทางไกล จำนวน 27 เครื่อง งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการตู้เย็นเก็บเลือด ขนาดไม่น้อยกว่า 20 คิว จำนวน 4 ตู้ งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์  การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์, ตู้เย็น)</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9350a991-2cda-4337-b005-93d114caf75c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=83dc4a91-4e74-465d-b378-562e91d2b662</t>
         </is>
       </c>
     </row>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการตู้เย็นเก็บเลือด ขนาดไม่น้อยกว่า 20 คิว จำนวน 4 ตู้ งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์  การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ เครื่องให้การรักษาอาการปวดและกระตุ้นเซลล์ประสาทส่วนปลายด้วยสนามแม่เหล็กไฟฟ้า(PMS) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -7211,12 +7211,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์, ตู้เย็น)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=83dc4a91-4e74-465d-b378-562e91d2b662</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=35bbde9c-eb8e-445f-b94e-915454477995</t>
         </is>
       </c>
     </row>
@@ -7228,15 +7228,15 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>2102</v>
+        <v>2106</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ เครื่องให้การรักษาอาการปวดและกระตุ้นเซลล์ประสาทส่วนปลายด้วยสนามแม่เหล็กไฟฟ้า(PMS) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมระบบปฏิบัติการและชุดโปรแกรมจัดการสำนักงาน จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ระบบปฏิบัติการ, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=35bbde9c-eb8e-445f-b94e-915454477995</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=414ac115-ac50-4d65-a54d-d2a9e03b621b</t>
         </is>
       </c>
     </row>
@@ -7263,15 +7263,15 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>กรมวิทยาศาสตร์การแพทย์</t>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมระบบปฏิบัติการและชุดโปรแกรมจัดการสำนักงาน จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ เครื่องวิเคราะห์การทำงานตู้อบเด็ก จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -7281,32 +7281,32 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ระบบปฏิบัติการ, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=414ac115-ac50-4d65-a54d-d2a9e03b621b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9d04622a-81b1-4cfd-9a05-6c2aec6751f7</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>กรมสนับสนุนบริการสุขภาพ</t>
+          <t>กรมบัญชีกลาง</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>2107</v>
+        <v>304</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ เครื่องวิเคราะห์การทำงานตู้อบเด็ก จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาและซ่อมแซมแก้ไขเครื่องปรับอากาศ (แบบรวมอะไหล่) จำนวน 474 เครื่อง ซ่อมแซมแก้ไขระบบไฟฟ้า และระบบสุขาภิบาล อาคาร 3 อาคาร 9 อาคารใหม่ ชั้นใต้ดิน และห้องลิฟต์ กรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -7316,12 +7316,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9d04622a-81b1-4cfd-9a05-6c2aec6751f7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=273a8add-ac17-48f1-8ff9-c94a946e8273</t>
         </is>
       </c>
     </row>
@@ -7333,15 +7333,15 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>กรมบัญชีกลาง</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>304</v>
+        <v>704</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาและซ่อมแซมแก้ไขเครื่องปรับอากาศ (แบบรวมอะไหล่) จำนวน 474 เครื่อง ซ่อมแซมแก้ไขระบบไฟฟ้า และระบบสุขาภิบาล อาคาร 3 อาคาร 9 อาคารใหม่ ชั้นใต้ดิน และห้องลิฟต์ กรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ พร้อมชุดโปรแกรมปฎิบัติงาน โปรแกรมจัดการสำนักงาน และโปรแกรมป้องกันไวรัส จำนวน 18 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (คอมพิวเตอร์, โปรแกรมป้องกันไวรัส, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=273a8add-ac17-48f1-8ff9-c94a946e8273</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0511e3cd-537d-45d3-880c-de7433b1eb48</t>
         </is>
       </c>
     </row>
@@ -7368,15 +7368,15 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมประมง</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อชุดจอภาพ LED พร้อมงานติดตั้งสำหรับห้องประชุมอานนท์ กรมประมง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (จอภาพ)</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1607645e-ac86-48f0-a820-917a3a4fe54d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b0679766-012d-497b-8e41-2296e1c7ba51</t>
         </is>
       </c>
     </row>
@@ -7403,15 +7403,15 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมปศุสัตว์</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ พร้อมชุดโปรแกรมปฎิบัติงาน โปรแกรมจัดการสำนักงาน และโปรแกรมป้องกันไวรัส จำนวน 18 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, โปรแกรมป้องกันไวรัส, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0511e3cd-537d-45d3-880c-de7433b1eb48</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f70d294-53f0-4fd1-b9bc-ef06d20b1657</t>
         </is>
       </c>
     </row>
@@ -7438,15 +7438,15 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>กรมประมง</t>
+          <t>สำนักงานนโยบายและแผนการขนส่งและจราจร</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>705</v>
+        <v>808</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อชุดจอภาพ LED พร้อมงานติดตั้งสำหรับห้องประชุมอานนท์ กรมประมง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์ของ สนข. ประจำปีงบประมาณ พ.ศ. 2570  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>★ (จอภาพ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b0679766-012d-497b-8e41-2296e1c7ba51</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=069d5584-a6b1-426d-9714-115f2fdc7025</t>
         </is>
       </c>
     </row>
@@ -7473,15 +7473,15 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>กรมปศุสัตว์</t>
+          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>706</v>
+        <v>904</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาและเพิ่มประสิทธิภาพระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรทางทะเลและชายฝั่ง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f70d294-53f0-4fd1-b9bc-ef06d20b1657</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f112758f-839d-4660-91b5-12181a1297d2</t>
         </is>
       </c>
     </row>
@@ -7508,15 +7508,15 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>สำนักงานนโยบายและแผนการขนส่งและจราจร</t>
+          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>808</v>
+        <v>1202</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์ของ สนข. ประจำปีงบประมาณ พ.ศ. 2570  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่ารถส่วนภูมิภาค รถยนต์ไฟฟ้า ประเภทแบตเตอรี่ (BEV) ขนาดความจุของแบตเตอรี่มากกว่า 50 กิโลวัตต์ชั่วโมง (kWh) และกำลังมอเตอร์ไฟฟ้าสูงสุด ไม่เกิน 150 กิโลวัตต์ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=069d5584-a6b1-426d-9714-115f2fdc7025</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=40cb45e4-0e08-48b9-a763-7a9aa44d7959</t>
         </is>
       </c>
     </row>
@@ -7543,15 +7543,15 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
+          <t>กรมการปกครอง</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>904</v>
+        <v>1503</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการบำรุงรักษาและเพิ่มประสิทธิภาพระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรทางทะเลและชายฝั่ง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 5 รายการ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f112758f-839d-4660-91b5-12181a1297d2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ac3547dc-0f12-4694-b5a3-e216678ce172</t>
         </is>
       </c>
     </row>
@@ -7578,15 +7578,15 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
+          <t>กรมการศาสนา</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1202</v>
+        <v>1803</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่ารถส่วนภูมิภาค รถยนต์ไฟฟ้า ประเภทแบตเตอรี่ (BEV) ขนาดความจุของแบตเตอรี่มากกว่า 50 กิโลวัตต์ชั่วโมง (kWh) และกำลังมอเตอร์ไฟฟ้าสูงสุด ไม่เกิน 150 กิโลวัตต์ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อวัสดุสำนักงานส่วนกลาง ประจำปีงบประมาณ พ.ศ. 2569 (ครั้งที่ 2)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (วัสดุสำนักงาน)</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=40cb45e4-0e08-48b9-a763-7a9aa44d7959</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c6f2fbd0-4267-42c4-926d-d8fc49d8a3ff</t>
         </is>
       </c>
     </row>
@@ -7613,15 +7613,15 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>กรมการปกครอง</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>1503</v>
+        <v>2102</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 5 รายการ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องผลิตออกซิเจนขนาด 5 ลิตร ของโรงพยาบาลสนม และโรงพยาบาลส่งเสริมสุขภาพตำบล 18 แห่ง จำนวน 33 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ac3547dc-0f12-4694-b5a3-e216678ce172</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=655601b1-75a6-4eee-9bc7-ee3ce427abf6</t>
         </is>
       </c>
     </row>
@@ -7648,15 +7648,15 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>กรมการศาสนา</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>1803</v>
+        <v>2102</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อวัสดุสำนักงานส่วนกลาง ประจำปีงบประมาณ พ.ศ. 2569 (ครั้งที่ 2)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดความดันโลหิตชนิดอัตโนมัติ วัดความอิ่มตัวของออกซิเจนในเลือด อุณหภูมิร่างกาย พร้อมระบบเชื่อมต่อฐานข้อมูล ของโรงพยาบาลในจังหวัดสุรินทร์ 12 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบล 10 แห่ง จำนวน 50 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>★ (วัสดุสำนักงาน)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c6f2fbd0-4267-42c4-926d-d8fc49d8a3ff</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=65a2753e-e63f-4be2-b228-0fe250379934</t>
         </is>
       </c>
     </row>
@@ -7691,7 +7691,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องผลิตออกซิเจนขนาด 5 ลิตร ของโรงพยาบาลสนม และโรงพยาบาลส่งเสริมสุขภาพตำบล 18 แห่ง จำนวน 33 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการชุดอุปกรณ์เคลื่อนย้ายผู้ป่วยในสถานการณ์ฉุกเฉิน ของโรงพยาบาลชุมชน 8 แห่ง จำนวน 10 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=655601b1-75a6-4eee-9bc7-ee3ce427abf6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=886059b7-d984-4e19-b7d7-6d90ebc9b2e0</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดความดันโลหิตชนิดอัตโนมัติ วัดความอิ่มตัวของออกซิเจนในเลือด อุณหภูมิร่างกาย พร้อมระบบเชื่อมต่อฐานข้อมูล ของโรงพยาบาลในจังหวัดสุรินทร์ 12 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบล 10 แห่ง จำนวน 50 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงชนิดสี 2 หัวตรวจ ของโรงพยาบาลชุมชน 6 แห่ง จำนวน 8 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=65a2753e-e63f-4be2-b228-0fe250379934</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fc233297-ee25-42e4-bc90-16f41ac8db6a</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการชุดอุปกรณ์เคลื่อนย้ายผู้ป่วยในสถานการณ์ฉุกเฉิน ของโรงพยาบาลชุมชน 8 แห่ง จำนวน 10 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดออกซิเจนในเลือดอัตโนมัติชนิดพกพา ของโรงพยาบาลส่งเสริมสุขภาพตำบลและโรงพยาบาลชุมชน 24 แห่ง จำนวน 68 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=886059b7-d984-4e19-b7d7-6d90ebc9b2e0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3d2922a2-6499-49fa-b182-1e95dc5131d7</t>
         </is>
       </c>
     </row>
@@ -7796,7 +7796,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงชนิดสี 2 หัวตรวจ ของโรงพยาบาลชุมชน 6 แห่ง จำนวน 8 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องเอกซเรย์ทั่วไปขนาดไม่น้อยกว่า 500 mA. แบบแขวนเพดาน โรงพยาบาลแก่งกระจาน ตำบลวังจันทร์ อำเภอแก่งกระจาน จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -7811,27 +7811,27 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fc233297-ee25-42e4-bc90-16f41ac8db6a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6f21d5fd-56e9-4486-915b-90fd4be0f39b</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กองทัพอากาศ</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>2102</v>
+        <v>206</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดออกซิเจนในเลือดอัตโนมัติชนิดพกพา ของโรงพยาบาลส่งเสริมสุขภาพตำบลและโรงพยาบาลชุมชน 24 แห่ง จำนวน 68 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบริการบำรุงรักษาเครื่องเอกซเรย์ควบคุมด้วยระบบคอมพิวเตอร์ขนาดไม่น้อยกว่า 300 mA พร้อมอุปกรณ์ ยี่ห้อ DRGEM รุ่น GXR-52S ของ โรงพยาบาลกองบิน กองบิน 1, โรงพยาบาลกองบิน กองบิน 2, โรงพยาบาลกองบิน กองบิน 7, โรงพยาบาลกองบิน กองบิน 41, โรงพยาบาลกองบิน กองบิน 46 จำนวน ๑ งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -7841,32 +7841,32 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3d2922a2-6499-49fa-b182-1e95dc5131d7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ffb67ab2-d749-4ab0-87f1-1b11432ab218</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมธนารักษ์</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>2102</v>
+        <v>303</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องเอกซเรย์ทั่วไปขนาดไม่น้อยกว่า 500 mA. แบบแขวนเพดาน โรงพยาบาลแก่งกระจาน ตำบลวังจันทร์ อำเภอแก่งกระจาน จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องอากาศยานซึ่งไม่มีนักบิน (Drone)  พร้อมชุดอุปกรณ์ภาคสนามและระบบซอฟต์แวร์ประมวลผลแผนที่ความละเอียดสูง จำนวน 12 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6f21d5fd-56e9-4486-915b-90fd4be0f39b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e88cabea-0e2e-4af8-8b8b-4aa4e7eb040a</t>
         </is>
       </c>
     </row>
@@ -7893,17 +7893,15 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>กองทัพอากาศ</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>0206</t>
-        </is>
+          <t>สำนักงานเศรษฐกิจการคลัง</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>311</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบริการบำรุงรักษาเครื่องเอกซเรย์ควบคุมด้วยระบบคอมพิวเตอร์ขนาดไม่น้อยกว่า 300 mA พร้อมอุปกรณ์ ยี่ห้อ DRGEM รุ่น GXR-52S ของ โรงพยาบาลกองบิน กองบิน 1, โรงพยาบาลกองบิน กองบิน 2, โรงพยาบาลกองบิน กองบิน 7, โรงพยาบาลกองบิน กองบิน 41, โรงพยาบาลกองบิน กองบิน 46 จำนวน ๑ งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์สำหรับโครงการพัฒนาระบบสารสนเทศสถาบันการเงินประชาชนของสำนักงานเศรษฐกิจการคลัง (ระบบงาน PFI) ประจำปีงบประมาณ พ.ศ. 2570  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -7918,7 +7916,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ffb67ab2-d749-4ab0-87f1-1b11432ab218</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a787a49a-4035-46d3-b8a4-a996ac96341d</t>
         </is>
       </c>
     </row>
@@ -7930,17 +7928,15 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>กรมธนารักษ์</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>0303</t>
-        </is>
+          <t>กรมพัฒนาสังคมและสวัสดิการ</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>603</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องอากาศยานซึ่งไม่มีนักบิน (Drone)  พร้อมชุดอุปกรณ์ภาคสนามและระบบซอฟต์แวร์ประมวลผลแผนที่ความละเอียดสูง จำนวน 12 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์สำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -7950,12 +7946,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>★ (ซอฟต์แวร์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e88cabea-0e2e-4af8-8b8b-4aa4e7eb040a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=857f0ccd-d38e-47b0-8d6d-913ef2cb1583</t>
         </is>
       </c>
     </row>
@@ -7967,17 +7963,15 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>สำนักงานเศรษฐกิจการคลัง</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>0311</t>
-        </is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>704</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์สำหรับโครงการพัฒนาระบบสารสนเทศสถาบันการเงินประชาชนของสำนักงานเศรษฐกิจการคลัง (ระบบงาน PFI) ประจำปีงบประมาณ พ.ศ. 2570  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -7987,12 +7981,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a787a49a-4035-46d3-b8a4-a996ac96341d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=01c185be-f27c-41bc-868e-accd57e4a95c</t>
         </is>
       </c>
     </row>
@@ -8004,17 +7998,15 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>กรมพัฒนาสังคมและสวัสดิการ</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>0603</t>
-        </is>
+          <t>กรมการขนส่งทางบก</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>804</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์สำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์พร้อมอุปกรณ์สำหรับศูนย์รวมข้อมูลการขนส่งด้วยรถบรรทุกเพื่อส่งเสริมการขนส่งด้วยรถบรรทุกให้มีประสิทธิภาพ ปลอดภัยและได้มาตรฐาน (TDSC) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -8024,12 +8016,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=857f0ccd-d38e-47b0-8d6d-913ef2cb1583</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70381c19-a073-41d0-8f0b-08c5e68fca7c</t>
         </is>
       </c>
     </row>
@@ -8041,17 +8033,15 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>0704</t>
-        </is>
+          <t>กรมท่าอากาศยาน</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>805</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบไฟฟ้า ตู้สวิตช์บอร์ด ๒๖ ท่าอากาศยาน และกรมท่าอากาศยาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -8061,12 +8051,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (สวิตช์)</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=01c185be-f27c-41bc-868e-accd57e4a95c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7f19e47d-04ea-4596-a45a-a42e0fd28eea</t>
         </is>
       </c>
     </row>
@@ -8078,17 +8068,15 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>0804</t>
-        </is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>806</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์พร้อมอุปกรณ์สำหรับศูนย์รวมข้อมูลการขนส่งด้วยรถบรรทุกเพื่อส่งเสริมการขนส่งด้วยรถบรรทุกให้มีประสิทธิภาพ ปลอดภัยและได้มาตรฐาน (TDSC) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 7 รายการ ศูนย์สร้างทางลำปาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -8098,12 +8086,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70381c19-a073-41d0-8f0b-08c5e68fca7c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f6fbb9a3-863a-430c-ab4d-c57fc8032ba8</t>
         </is>
       </c>
     </row>
@@ -8115,17 +8103,15 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
+          <t>กรมป่าไม้</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>912</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบไฟฟ้า ตู้สวิตช์บอร์ด ๒๖ ท่าอากาศยาน และกรมท่าอากาศยาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -8135,12 +8121,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>★ (สวิตช์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7f19e47d-04ea-4596-a45a-a42e0fd28eea</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fd72b9d1-6722-4578-b8e5-e2d45779204d</t>
         </is>
       </c>
     </row>
@@ -8152,17 +8138,15 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>0806</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>1302</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 7 รายการ ศูนย์สร้างทางลำปาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าระบบประชุมทางไกล (Web Conference Video Streaming) ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -8172,12 +8156,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ระบบประชุมทางไกล)</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f6fbb9a3-863a-430c-ab4d-c57fc8032ba8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6c4b6c7d-fa54-4634-9070-01779d28362f</t>
         </is>
       </c>
     </row>
@@ -8189,17 +8173,15 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>กรมป่าไม้</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>0912</t>
-        </is>
+          <t>กรมโยธาธิการและผังเมือง</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>1507</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างงานปรับปรุงระบบดับเพลิงพิเศษอัตโนมัติ (Clean Agent Fire Suppression System) ภายในห้องคอมพิวเตอร์แม่ข่าย (Server Room) อาคาร 4 ชั้น 1 กรมโยธาธิการและผังเมือง ถนนพระราม 9 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -8209,12 +8191,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fd72b9d1-6722-4578-b8e5-e2d45779204d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a61be7d0-de39-476c-b4f8-7a3ec47bbd62</t>
         </is>
       </c>
     </row>
@@ -8226,17 +8208,15 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>1302</t>
-        </is>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>1611</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าระบบประชุมทางไกล (Web Conference Video Streaming) ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการถ่ายเอกสารพร้อมเครื่องถ่ายเอกสาร กระดาษ วัสดุสิ้นเปลือง และพนักงานประจำเครื่องของสำนักงาน ป.ป.ส. ดินแดง/สำนักงาน ป.ป.ส. ทุ่งสองห้อง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -8246,12 +8226,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>★ (ระบบประชุมทางไกล)</t>
+          <t>★ (กระดาษ)</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6c4b6c7d-fa54-4634-9070-01779d28362f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=325eb565-d1b7-456f-86c5-076a6e3f94fd</t>
         </is>
       </c>
     </row>
@@ -8263,17 +8243,15 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>กรมโยธาธิการและผังเมือง</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>1507</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>2102</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างงานปรับปรุงระบบดับเพลิงพิเศษอัตโนมัติ (Clean Agent Fire Suppression System) ภายในห้องคอมพิวเตอร์แม่ข่าย (Server Room) อาคาร 4 ชั้น 1 กรมโยธาธิการและผังเมือง ถนนพระราม 9 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องนึ่งฆ่าเชื้อจุลินทรีย์ด้วยไอน้ำระบบอัตโนมัติ ขนาดไม่น้อยกว่า 850 ลิตร ห้องนึ่งทรงเหลี่ยมชนิด 1 ประตู โรงพยาบาลบ้านลาด ตำบลท่าช้าง อำเภอบ้านลาด จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -8283,12 +8261,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a61be7d0-de39-476c-b4f8-7a3ec47bbd62</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4d2f3086-64b4-4e82-a4f3-6299ee3aa880</t>
         </is>
       </c>
     </row>
@@ -8300,17 +8278,15 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>1611</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>2102</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการถ่ายเอกสารพร้อมเครื่องถ่ายเอกสาร กระดาษ วัสดุสิ้นเปลือง และพนักงานประจำเครื่องของสำนักงาน ป.ป.ส. ดินแดง/สำนักงาน ป.ป.ส. ทุ่งสองห้อง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องล้างเครื่องมืออัลตร้าโซนิก ชนิด 3 หลุมล้าง ขนาดความจุไม่น้อยกว่า 80 ลิตร โรงพยาบาลชะอำ ตำบลชะอำ อำเภอชะอำ จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -8320,12 +8296,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>★ (กระดาษ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=325eb565-d1b7-456f-86c5-076a6e3f94fd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b7c95cfb-63e4-43a3-9eeb-4e9c5df71f85</t>
         </is>
       </c>
     </row>
@@ -8340,14 +8316,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C226" t="n">
+        <v>2102</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องนึ่งฆ่าเชื้อจุลินทรีย์ด้วยไอน้ำระบบอัตโนมัติ ขนาดไม่น้อยกว่า 850 ลิตร ห้องนึ่งทรงเหลี่ยมชนิด 1 ประตู โรงพยาบาลบ้านลาด ตำบลท่าช้าง อำเภอบ้านลาด จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่ายกลาง (Backbone) กระทรวงสาธารณสุข ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -8357,12 +8331,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4d2f3086-64b4-4e82-a4f3-6299ee3aa880</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3a5cafe5-5313-4cb0-ab08-4b09c244ba61</t>
         </is>
       </c>
     </row>
@@ -8377,14 +8351,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C227" t="n">
+        <v>2102</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องล้างเครื่องมืออัลตร้าโซนิก ชนิด 3 หลุมล้าง ขนาดความจุไม่น้อยกว่า 80 ลิตร โรงพยาบาลชะอำ ตำบลชะอำ อำเภอชะอำ จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนและคาร์บอนไดออกไซด์ในเลือด ของโรงพยาบาลในจังหวัดสุรินทร์ 7 แห่ง จำนวน 12 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -8399,7 +8371,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b7c95cfb-63e4-43a3-9eeb-4e9c5df71f85</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d5f4c614-78c4-4363-a75d-31e52b8e81d7</t>
         </is>
       </c>
     </row>
@@ -8414,14 +8386,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C228" t="n">
+        <v>2102</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่ายกลาง (Backbone) กระทรวงสาธารณสุข ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 8 เตียง ของโรงพยาบาลท่าตูม จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -8431,12 +8401,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3a5cafe5-5313-4cb0-ab08-4b09c244ba61</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=261f4b2d-359f-4fbc-9c62-4971724a772f</t>
         </is>
       </c>
     </row>
@@ -8451,14 +8421,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C229" t="n">
+        <v>2102</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนและคาร์บอนไดออกไซด์ในเลือด ของโรงพยาบาลในจังหวัดสุรินทร์ 7 แห่ง จำนวน 12 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันขนาดใหญ่ ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 6 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -8473,29 +8441,29 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d5f4c614-78c4-4363-a75d-31e52b8e81d7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9cc00102-4e57-443e-a94c-3787d155fe6b</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สำนักงานคณะกรรมการคุ้มครองผู้บริโภค</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>0103</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 8 เตียง ของโรงพยาบาลท่าตูม จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาเครือข่าย เครื่องคอมพิวเตอร์แม่ข่าย เครื่องคอมพิวเตอร์ อุปกรณ์คอมพิวเตอร์และห้องปฏิบัติการคอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -8505,49 +8473,937 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=261f4b2d-359f-4fbc-9c62-4971724a772f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6f8747c6-3579-4b1b-992e-7c6f55a197b3</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
+          <t>กองทัพบก</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>0204</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ประจำอาคาร งานก่อสร้างโรงเลี้ยง 400 คน (แบบ กห 08 - 7) ของ มทบ.29 ค่ายกฤษณ์สีวะรา อ.เมือง จว.ส.น. แผนงานเพิ่มเติมระหว่างปีงบประมาณ พ.ศ. 2569 ให้กับ ช.2 พัน.202 ดำเนินการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=daeb7717-b81c-405b-94a2-aa71f55ea8af</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>กองทัพอากาศ</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>0206</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องพิมพ์สีแผ่นไวนิล จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>★ (เครื่องพิมพ์)</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e4172805-a5ea-4e60-b1e4-787b55b54a34</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>0704</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน เครื่องปรับอากาศแบบแยกส่วน ชนิดแขวน ระบบ Inverter ขนาด 30,000 บีทียู จำนวน 12 เครื่อง พร้อมติดตั้ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ)</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dc7ebea2-3d95-4ced-a85f-84f2cb8e77c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>กรมปศุสัตว์</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>0706</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์  จำนวน  5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a7913502-7863-4804-9095-3f717c939f36</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมการเกษตร</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>0711</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์ สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม สำนักงานเกษตรอำเภอนาวัง ตำบลนาเหล่าอำเภอนาวัง  จังหวัดหนองบัวลำภู  จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1cb87987-0702-433c-8678-5f41220c5aa5</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมการเกษตร</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>0711</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบ ไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 4 ล้อ แบบดับเบิ้ลแค็บ  พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม ศูนย์ส่งเสริมเทคโนโลยีการเกษตรด้านอารักขาพืช จังหวัดพิษณุโลก ตำบลอรัญญิก อำเภอเมืองพิษณุโลก จังหวัดพิษณุโลก 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=21728512-3d55-4336-a433-756fa816ccd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>กรมการขนส่งทางบก</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>0804</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและซ่อมแซมระบบคอมพิวเตอร์แม่ข่ายและอุปกรณ์ตามโครงการพัฒนาระบบฐานข้อมูลกลางเพื่อบูรณาการข้อมูลสนับสนุนการให้บริการของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1089b549-2663-46b4-8f30-3b752498b76d</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 7 รายการ ศูนย์สร้างทางลำปาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=74dbade6-07ca-4df1-9aaa-c33e529e04b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=486fc308-1dd1-40ac-9b5f-16595e40c39d</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องสำรองไฟฟ้า ขนาด 2 kVA จำนวน 138 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>★ (เครื่องสำรองไฟฟ้า, เครื่องสำรองไฟ)</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=66aa18c1-0eb7-4c9c-bc97-eb6c9f84ea61</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>กรมอุตุนิยมวิทยา</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>1104</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาเครื่องสำรองไฟฟ้าต่อเนื่อง (UPS) และเครื่องกำเนิดไฟฟ้า (Generator) ประจำปีงบประมาณ พ.ศ.๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>★ (เครื่องสำรองไฟฟ้า, เครื่องสำรองไฟ)</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b04b2aed-150c-4a6a-9fe6-de4abe606304</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>กรมเจรจาการค้าระหว่างประเทศ</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างโครงการปรับปรุงระบบสายสัญญาณเครือข่าย ระบบไฟฟ้า และระบบโทรศัพท์พร้อมอุปกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>★ (สายสัญญาณ)</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bac0b85b-275a-4ed6-a580-b3e8bfeb237f</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมการค้าระหว่างประเทศ</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>1309</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาระบบคอมพิวเตอร์และระบบเครือข่ายพร้อมอุปกรณ์ ปี ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f059ad38-40c4-42cf-9270-e3def8289626</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>กรมการปกครอง</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อวัสดุสำหรับเครื่องพิมพ์คอมพิวเตอร์เพื่อสนับสนุนการดำเนินงานในระบบสารสนเทศทรัพยากรบุคคลระดับกรม (DPIS) ประจำปีงบประมาณ  พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, เครื่องพิมพ์)</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ec8d68fe-3f09-45d1-a6c2-b10acc4b8aff</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>กรมการศาสนา</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>1803</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อหมึกเครื่องพิมพ์ (ครั้งที่ 3) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>★ (หมึกเครื่องพิมพ์, เครื่องพิมพ์)</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cad3c999-2a59-4f98-9a16-5cd0e9b965e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr">
+      <c r="C246" t="inlineStr">
         <is>
           <t>2102</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันขนาดใหญ่ ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 6 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ กล้องจุลทรรศน์ตรวจตาชนิดลำแสงแคบพร้อมระบบเก็บภาพดิจิตอล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
         <is>
           <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9cc00102-4e57-443e-a94c-3787d155fe6b</t>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b7dc6e3c-c6d3-4740-8dfd-746b3c47ce99</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดใหญ่ ของโรงพยาบาลในจังหวัดสุรินทร์ 2 แห่ง จำนวน 7 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9e482ce2-8b0c-4125-ac7c-be9fb421af4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงแบบพกพาไม่ต้องชาร์จไฟฟ้าพร้อมระบบแพทย์ทางไกล ของโรงพยาบาลชุมชน 3 แห่ง จำนวน 4 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=49ab0e04-32b5-4441-9d77-b629429b1571</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ เครื่องตรวจวิเคราะห์แยกชั้นจอประสาทตาชนิดถ่ายภาพจอประสาทตา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=165b7f39-161c-4e36-abf9-9ab28afdef12</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องรับสัญญาณภาพเอกซเรย์เป็นดิจิตอล ชนิดชุดรับภาพแฟลตพาแนลไร้สาย โรงพยาบาลแก่งกระจาน ตำบลวังจันทร์ อำเภอแก่งกระจาน จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=23fd4481-d3c5-4060-a810-ba6addb1516c</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๒ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e59b2ed4-9af0-48e9-a768-f2323d942f2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิคพร้อมภาควัดออกซิเจนและคาร์บอนไดออกไซด์ในเลือด จำนวน 25 เครื่อง งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาล ในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b80f6866-243b-41ee-8a1f-f04456bc5061</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>2107</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ 11 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fa5cc489-cfac-46c2-b92b-18e107acc682</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>กรมอนามัย</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>2109</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=eada32a9-3333-40e2-ad51-54e8d12647cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>สำนักงานพระพุทธศาสนาแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>2503</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน ๑๒ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=54340df1-ec2b-4471-bb8f-6779c938e36b</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202609.xlsx
+++ b/Backup/eGP_Monthly_Main_202609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G255"/>
+  <dimension ref="A1:G274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการจัดจ้างบำรุงรักษาเครื่องคอมพิวเตอร์แม่ข่ายและอุปกรณ์สำหรับระบบสารสนเทศบริหารเครื่องจักรกลและการเงินการบัญชีเพื่อการบริหารจัดการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=44d1ec7f-04ab-49d0-b112-502799195d6b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=909fce3b-2a20-4eb7-b619-b2e32da6e18d</t>
         </is>
       </c>
     </row>
@@ -2783,15 +2783,15 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>กรมทรัพยากรธรณี</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>806</v>
+        <v>905</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการจัดจ้างบำรุงรักษาเครื่องคอมพิวเตอร์แม่ข่ายและอุปกรณ์สำหรับระบบสารสนเทศบริหารเครื่องจักรกลและการเงินการบัญชีเพื่อการบริหารจัดการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาซ่อมบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรธรณี ปีงบประมาณ พ.ศ. 2570 จำนวน 1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=909fce3b-2a20-4eb7-b619-b2e32da6e18d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3cc3bb5f-0d9f-428a-b588-18b0b71b8b6e</t>
         </is>
       </c>
     </row>
@@ -2818,15 +2818,15 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>กรมทรัพยากรธรณี</t>
+          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาซ่อมบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรธรณี ปีงบประมาณ พ.ศ. 2570 จำนวน 1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อและติดตั้งเครื่องคอมพิวเตอร์แม่ข่ายพร้อมอุปกรณ์ประกอบสำหรับรองรับการให้บริการระบบสารบรรณอิเล็กทรอนิกส์ของกรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3cc3bb5f-0d9f-428a-b588-18b0b71b8b6e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=028b6dd5-2160-4f89-924f-f6c47b4b4995</t>
         </is>
       </c>
     </row>
@@ -2853,15 +2853,15 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
+          <t>สำนักงานปลัดกระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>909</v>
+        <v>1102</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อและติดตั้งเครื่องคอมพิวเตอร์แม่ข่ายพร้อมอุปกรณ์ประกอบสำหรับรองรับการให้บริการระบบสารบรรณอิเล็กทรอนิกส์ของกรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการจัดอบรมเตรียมความพร้อมผู้แต่งตั้งเป็นพนักงานเจ้าหน้าที่ตามพระราชบัญญัติว่าด้วยการกระทำความผิดเกี่ยวกับคอมพิวเตอร์ฯ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=028b6dd5-2160-4f89-924f-f6c47b4b4995</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8de232df-b5c2-427b-9a5d-d9f5ca3342c3</t>
         </is>
       </c>
     </row>
@@ -2888,15 +2888,15 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม</t>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1102</v>
+        <v>1302</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการจัดอบรมเตรียมความพร้อมผู้แต่งตั้งเป็นพนักงานเจ้าหน้าที่ตามพระราชบัญญัติว่าด้วยการกระทำความผิดเกี่ยวกับคอมพิวเตอร์ฯ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์สนับสนุนศูนย์ข้อมูลและเครือข่ายคอมพิวเตอร์ (Data Center) ของกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8de232df-b5c2-427b-9a5d-d9f5ca3342c3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5065022-193d-466c-819b-b1533c1e1696</t>
         </is>
       </c>
     </row>
@@ -2923,15 +2923,15 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+          <t>สถาบันส่งเสริมศิลปหัตถกรรมไทย (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1302</v>
+        <v>1311</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์สนับสนุนศูนย์ข้อมูลและเครือข่ายคอมพิวเตอร์ (Data Center) ของกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างดำเนินการบำรุงรักษาระบบและอุปกรณ์ภายในห้อง Data Center และการต่อลิขสิทธิ์โปรแกรมคอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5065022-193d-466c-819b-b1533c1e1696</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8c2b0f9b-210b-4328-a727-0ebda03f9ebc</t>
         </is>
       </c>
     </row>
@@ -2958,15 +2958,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>สถาบันส่งเสริมศิลปหัตถกรรมไทย (องค์การมหาชน)</t>
+          <t>กรมบังคับคดี</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1311</v>
+        <v>1605</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างดำเนินการบำรุงรักษาระบบและอุปกรณ์ภายในห้อง Data Center และการต่อลิขสิทธิ์โปรแกรมคอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างตรวจสอบเครื่องคอมพิวเตอร์ให้พร้อมใช้งานและบริการประชาชน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8c2b0f9b-210b-4328-a727-0ebda03f9ebc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=590bcfa8-9d1a-43f4-b6c0-1d332cdf98ac</t>
         </is>
       </c>
     </row>
@@ -2993,15 +2993,15 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>กรมบังคับคดี</t>
+          <t>กรมศิลปากร</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1605</v>
+        <v>1804</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างตรวจสอบเครื่องคอมพิวเตอร์ให้พร้อมใช้งานและบริการประชาชน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการดูแลบำรุงรักษาเครื่องปรับอากาศ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3011,12 +3011,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=590bcfa8-9d1a-43f4-b6c0-1d332cdf98ac</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=560aab6a-379c-4e73-a426-35b147f0955f</t>
         </is>
       </c>
     </row>
@@ -3028,15 +3028,15 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>กรมศิลปากร</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1804</v>
+        <v>2102</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการดูแลบำรุงรักษาเครื่องปรับอากาศ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดอัตโนมัติ พร้อมตู้ตั้งพื้นจอแสดงผล และระบบสัญญาณเตือน จำนวน 39 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาล ในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3046,12 +3046,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (จอแสดงผล, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=560aab6a-379c-4e73-a426-35b147f0955f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f7659e63-27b4-4348-9cb8-c0e5ed5164a0</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดอัตโนมัติ พร้อมตู้ตั้งพื้นจอแสดงผล และระบบสัญญาณเตือน จำนวน 39 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาล ในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องอุ่นเลือดและส่วนประกอบของเลือดชนิดไม่สัมผัสน้ำสามารถอุ่นเลือดได้ พร้อมกันไม่น้อยกว่า 3 ถุง ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 4 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>★ (จอแสดงผล, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f7659e63-27b4-4348-9cb8-c0e5ed5164a0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dc9795b5-9883-4a59-bee5-16ba72ecd5c6</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องอุ่นเลือดและส่วนประกอบของเลือดชนิดไม่สัมผัสน้ำสามารถอุ่นเลือดได้ พร้อมกันไม่น้อยกว่า 3 ถุง ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 4 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเตียงผู้ป่วยชนิดสามไกร์ราวปีกนก พร้อมเบาะเสาน้ำเกลือตู้ข้างเตียงและถาดคร่อมเตียง ของโรงพยาบาลส่งเสริมสุขภาพตำบล 25 แห่ง จำนวน 25 เตียง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dc9795b5-9883-4a59-bee5-16ba72ecd5c6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=43094cdc-968c-43e9-b0e7-915d25aa8621</t>
         </is>
       </c>
     </row>
@@ -3133,15 +3133,15 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2102</v>
+        <v>2107</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเตียงผู้ป่วยชนิดสามไกร์ราวปีกนก พร้อมเบาะเสาน้ำเกลือตู้ข้างเตียงและถาดคร่อมเตียง ของโรงพยาบาลส่งเสริมสุขภาพตำบล 25 แห่ง จำนวน 25 เตียง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=43094cdc-968c-43e9-b0e7-915d25aa8621</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63c3a055-9106-4358-9ed6-5bf60d1e158c</t>
         </is>
       </c>
     </row>
@@ -3168,15 +3168,15 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>กรมสนับสนุนบริการสุขภาพ</t>
+          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2107</v>
+        <v>2113</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและวิเคราะห์ระบบเก็บข้อมูลจราจรคอมพิวเตอร์ขั้นสูง (CSOC) สำนักงานหลักประกันสุขภาพแห่งชาติ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3186,32 +3186,32 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63c3a055-9106-4358-9ed6-5bf60d1e158c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=516788e1-5adb-46f1-b0bc-48d9b91e8cd8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2113</v>
+        <v>204</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและวิเคราะห์ระบบเก็บข้อมูลจราจรคอมพิวเตอร์ขั้นสูง (CSOC) สำนักงานหลักประกันสุขภาพแห่งชาติ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ และอุปกรณ์ประกอบเครื่องคอมพิวเตอร์ เพื่อทดแทน และพัฒนาระบบเทคโนโลยีสารสนเทศหน่วยบัญชาการป้องกันภัยทางอากาศ (นปอ.) จำนวน ๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=516788e1-5adb-46f1-b0bc-48d9b91e8cd8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8603566b-8b32-470f-b070-76bf84fb86b4</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ และอุปกรณ์ประกอบเครื่องคอมพิวเตอร์ เพื่อทดแทน และพัฒนาระบบเทคโนโลยีสารสนเทศหน่วยบัญชาการป้องกันภัยทางอากาศ (นปอ.) จำนวน ๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างงานติดตั้งเครื่องปรับอากาศ ประจำอาคารหอประชุม หมายเลข ๙๖/๒๓ ของ โรงพยาบาลอานันทมหิดล จังหวัดลพบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3256,12 +3256,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8603566b-8b32-470f-b070-76bf84fb86b4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=97d16ed9-2390-479b-8218-55472ad15ea3</t>
         </is>
       </c>
     </row>
@@ -3273,15 +3273,15 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กรมชลประทาน</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>204</v>
+        <v>703</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างงานติดตั้งเครื่องปรับอากาศ ประจำอาคารหอประชุม หมายเลข ๙๖/๒๓ ของ โรงพยาบาลอานันทมหิดล จังหวัดลพบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องสูบน้ำแบบจุ่มใช้มอเตอร์ไฟฟ้า และอื่นๆรวม 3 รายการ สำหรับงานปรับปรุงอาคารบังคับน้ำคลองทิวา-ต้นนา โครงการส่งน้ำและบำรุงรักษาบางพลวง ตำบลพนมสารคาม อำเภอพนมสารคาม จังหวัดฉะเชิงเทรา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3291,12 +3291,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=97d16ed9-2390-479b-8218-55472ad15ea3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=641eb398-88f6-4784-9733-866ddfdb5ea8</t>
         </is>
       </c>
     </row>
@@ -3308,15 +3308,15 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>กรมชลประทาน</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องสูบน้ำแบบจุ่มใช้มอเตอร์ไฟฟ้า และอื่นๆรวม 3 รายการ สำหรับงานปรับปรุงอาคารบังคับน้ำคลองทิวา-ต้นนา โครงการส่งน้ำและบำรุงรักษาบางพลวง ตำบลพนมสารคาม อำเภอพนมสารคาม จังหวัดฉะเชิงเทรา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์เครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล  จำนวน 12 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3326,12 +3326,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=641eb398-88f6-4784-9733-866ddfdb5ea8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cae8cfd5-0a33-48de-bb0d-dd1597263622</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์เครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล  จำนวน 12 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล)  ขนาด ๑ ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า ๒,๔๐๐ ซีซี  หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า ๑๑๐ กิโลวัตต์ ขับเคลื่อน 4 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน ๑ คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cae8cfd5-0a33-48de-bb0d-dd1597263622</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=23493925-5f1a-442c-a9ec-afccbc470e45</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล)  ขนาด ๑ ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า ๒,๔๐๐ ซีซี  หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า ๑๑๐ กิโลวัตต์ ขับเคลื่อน 4 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน ๑ คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อเครื่องคอมพิวเตอร์ และเครื่องคอมพิวเตอร์โน้ตบุ๊ก จำนวน 2 รายการ ของสำนักงานตรวจบัญชีสหกรณ์ชลบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=23493925-5f1a-442c-a9ec-afccbc470e45</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=07006c6c-edf5-4030-b6c9-1078334342be</t>
         </is>
       </c>
     </row>
@@ -3413,15 +3413,15 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>704</v>
+        <v>806</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อเครื่องคอมพิวเตอร์ และเครื่องคอมพิวเตอร์โน้ตบุ๊ก จำนวน 2 รายการ ของสำนักงานตรวจบัญชีสหกรณ์ชลบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าโครงการเช่าเครื่องพิมพ์ 4 สี เพื่อการพิมพ์เอกสารแจ้งผู้ขับขี่เพื่อการเปรียบเทียบปรับตามกฎหมาย ของ กองบังคับการตำรวจทางหลวง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=07006c6c-edf5-4030-b6c9-1078334342be</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3fdfa461-5479-46d3-90bc-5b8725bde7b5</t>
         </is>
       </c>
     </row>
@@ -3448,15 +3448,15 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>สำนักงานปลัดกระทรวงแรงงาน</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>806</v>
+        <v>1702</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าโครงการเช่าเครื่องพิมพ์ 4 สี เพื่อการพิมพ์เอกสารแจ้งผู้ขับขี่เพื่อการเปรียบเทียบปรับตามกฎหมาย ของ กองบังคับการตำรวจทางหลวง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดหาครุภัณฑ์คอมพิวเตอร์เพื่อทดแทนและเพิ่มประสิทธิภาพให้หน่วยงานในสังกัดสำนักงานปลัดกระทรวงแรงงาน ปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>★ (เครื่องพิมพ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3fdfa461-5479-46d3-90bc-5b8725bde7b5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=eea981aa-edb1-4fdf-8067-e5fb7c92e854</t>
         </is>
       </c>
     </row>
@@ -3483,15 +3483,15 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงแรงงาน</t>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามการทุจริตในภาครัฐ</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1702</v>
+        <v>2517</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดหาครุภัณฑ์คอมพิวเตอร์เพื่อทดแทนและเพิ่มประสิทธิภาพให้หน่วยงานในสังกัดสำนักงานปลัดกระทรวงแรงงาน ปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาเครื่องคอมพิวเตอร์แม่ข่าย และระบบความปลอดภัยทางไซเบอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=eea981aa-edb1-4fdf-8067-e5fb7c92e854</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=39110c90-d236-47eb-913a-cb6b3cab18ba</t>
         </is>
       </c>
     </row>
@@ -3518,15 +3518,15 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามการทุจริตในภาครัฐ</t>
+          <t>สำนักงานการตรวจเงินแผ่นดิน</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2517</v>
+        <v>2606</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการบำรุงรักษาเครื่องคอมพิวเตอร์แม่ข่าย และระบบความปลอดภัยทางไซเบอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างเหมาบริการขนย้ายเครื่องแม่ข่าย และอุปกรณ์พร้อมติดตั้ง ณ ศูนย์ข้อมูลหลัก ของสำนักงานการตรวจเงินแผ่นดิน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องแม่ข่าย)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=39110c90-d236-47eb-913a-cb6b3cab18ba</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a89ffef4-4bf7-41f2-83ef-2e02a1a4e80c</t>
         </is>
       </c>
     </row>
@@ -3553,15 +3553,15 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>สำนักงานการตรวจเงินแผ่นดิน</t>
+          <t>สำนักงานปลัดกระทรวงการอุดมศึกษา วิทยาศาสตร์ วิจัยและนวัตกรรม</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2606</v>
+        <v>23002</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างเหมาบริการขนย้ายเครื่องแม่ข่าย และอุปกรณ์พร้อมติดตั้ง ณ ศูนย์ข้อมูลหลัก ของสำนักงานการตรวจเงินแผ่นดิน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างเหมาบริการบำรุงรักษาเครื่องปรับอากาศ แบบรวมอะไหล่ จำนวน 606 เครื่อง ภายในอาคารอุดมศึกษา 1 อาคารอุดมศึกษา 2 อาคารพระจอมเกล้า และอาคารอเนกประสงค์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3571,32 +3571,32 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>★ (เครื่องแม่ข่าย)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a89ffef4-4bf7-41f2-83ef-2e02a1a4e80c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4ed51246-9d93-42ff-bb32-e9acb8e03644</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการอุดมศึกษา วิทยาศาสตร์ วิจัยและนวัตกรรม</t>
+          <t>สำนักงานบริหารและพัฒนาองค์ความรู้ (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>23002</v>
+        <v>125</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างเหมาบริการบำรุงรักษาเครื่องปรับอากาศ แบบรวมอะไหล่ จำนวน 606 เครื่อง ภายในอาคารอุดมศึกษา 1 อาคารอุดมศึกษา 2 อาคารพระจอมเกล้า และอาคารอเนกประสงค์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4ed51246-9d93-42ff-bb32-e9acb8e03644</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=22d2e215-7492-48e1-8b48-52ebf11afb3d</t>
         </is>
       </c>
     </row>
@@ -3623,15 +3623,15 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>สำนักงานบริหารและพัฒนาองค์ความรู้ (องค์การมหาชน)</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>125</v>
+        <v>204</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ พร้อมอุปกรณ์ จำนวน ๘๐ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=22d2e215-7492-48e1-8b48-52ebf11afb3d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ed207e86-fa08-4bf6-b096-f66e9ea91205</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ พร้อมอุปกรณ์ จำนวน ๘๐ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อสป.สาย ส. ตามโครงการจัดหาอุปกรณ์คอมพิวเตอร์ เพื่อสนับสนุนงานออกแบบสถาปัตยกรรม วิศวกรรมและงานประมาณราคา (ยย.ทบ.) จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ed207e86-fa08-4bf6-b096-f66e9ea91205</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a5d0fbe1-af34-494f-b408-da6f60a04c26</t>
         </is>
       </c>
     </row>
@@ -3693,15 +3693,15 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กรมธนารักษ์</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>204</v>
+        <v>303</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อสป.สาย ส. ตามโครงการจัดหาอุปกรณ์คอมพิวเตอร์ เพื่อสนับสนุนงานออกแบบสถาปัตยกรรม วิศวกรรมและงานประมาณราคา (ยย.ทบ.) จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์อาคารเก็บพัสดุสำนักงานธนารักษ์พื้นที่ชลบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a5d0fbe1-af34-494f-b408-da6f60a04c26</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=606b64be-13e1-468a-84bd-c7c5b46221da</t>
         </is>
       </c>
     </row>
@@ -3728,15 +3728,15 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>กรมธนารักษ์</t>
+          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>303</v>
+        <v>402</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์อาคารเก็บพัสดุสำนักงานธนารักษ์พื้นที่ชลบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาดูแล บำรุงรักษา และล้างทำความสะอาดระบบเครื่องปรับอากาศ ณ อาคารกระทรวงการต่างประเทศ ถนนศรีอยุธยา และศูนย์ราชการเฉลิมพระเกียรติฯ อาคาร B ชั้น 7 - 8 รวม 2 แห่ง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=606b64be-13e1-468a-84bd-c7c5b46221da</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4c0225b9-4c8b-4bbd-80d4-d42eccd0092e</t>
         </is>
       </c>
     </row>
@@ -3763,15 +3763,15 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
+          <t>กรมกิจการเด็กและเยาวชน</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>402</v>
+        <v>605</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาดูแล บำรุงรักษา และล้างทำความสะอาดระบบเครื่องปรับอากาศ ณ อาคารกระทรวงการต่างประเทศ ถนนศรีอยุธยา และศูนย์ราชการเฉลิมพระเกียรติฯ อาคาร B ชั้น 7 - 8 รวม 2 แห่ง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาเครื่องคอมพิวเตอร์ อุปกรณ์ต่อพ่วง และระบบสารสนเทศ ของ ดย. ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4c0225b9-4c8b-4bbd-80d4-d42eccd0092e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cb192597-9852-49f1-81d0-f9bd008c7f6d</t>
         </is>
       </c>
     </row>
@@ -3798,15 +3798,15 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>กรมกิจการเด็กและเยาวชน</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>605</v>
+        <v>704</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาเครื่องคอมพิวเตอร์ อุปกรณ์ต่อพ่วง และระบบสารสนเทศ ของ ดย. ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อครุภัณฑ์ยานพาหนะและขนส่งรถโดยสารขนาด 12 ที่นั่ง (ดีเซล) จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cb192597-9852-49f1-81d0-f9bd008c7f6d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3d257d5-116f-4d11-9cba-b2af7ffd9693</t>
         </is>
       </c>
     </row>
@@ -3833,15 +3833,15 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมประมง</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อครุภัณฑ์ยานพาหนะและขนส่งรถโดยสารขนาด 12 ที่นั่ง (ดีเซล) จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างการจัดจ้างบำรุงรักษาครุภัณฑ์คอมพิวเตอร์สำหรับการรักษาความปลอดภัยของระบบเครือข่ายและคอมพิวเตอร์ จำนวน 1 งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3d257d5-116f-4d11-9cba-b2af7ffd9693</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=29210ba8-e1c2-4d7e-80d4-6acfeb801f71</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างการจัดจ้างบำรุงรักษาครุภัณฑ์คอมพิวเตอร์สำหรับการรักษาความปลอดภัยของระบบเครือข่ายและคอมพิวเตอร์ จำนวน 1 งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างการจัดจ้างบำรุงรักษาอุปกรณ์กระจายสัญญาณ จำนวน ๑ งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=29210ba8-e1c2-4d7e-80d4-6acfeb801f71</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b2bbd6f5-c7a5-4bc3-be9e-fc1ddf4ac0a8</t>
         </is>
       </c>
     </row>
@@ -3903,15 +3903,15 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>กรมประมง</t>
+          <t>สำนักงานมาตรฐานสินค้าเกษตรและอาหารแห่งชาติ</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>705</v>
+        <v>714</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างการจัดจ้างบำรุงรักษาอุปกรณ์กระจายสัญญาณ จำนวน ๑ งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการจ้างเหมาดูแลและบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์และระบบคอมพิวเตอร์พร้อมอุปกรณ์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b2bbd6f5-c7a5-4bc3-be9e-fc1ddf4ac0a8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d133e360-c57e-4330-bff5-2f10cf027da9</t>
         </is>
       </c>
     </row>
@@ -3938,15 +3938,15 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>สำนักงานมาตรฐานสินค้าเกษตรและอาหารแห่งชาติ</t>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>714</v>
+        <v>1302</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการจ้างเหมาดูแลและบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์และระบบคอมพิวเตอร์พร้อมอุปกรณ์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องคอมพิวเตอร์และอุปกรณ์ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d133e360-c57e-4330-bff5-2f10cf027da9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=04549f6b-e678-4005-91df-2993ee4bdb83</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องคอมพิวเตอร์และอุปกรณ์ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่ายของสำนักงานพาณิชย์จังหวัด 76 จังหวัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=04549f6b-e678-4005-91df-2993ee4bdb83</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f1e51f04-f935-4983-8200-42b44f480fc9</t>
         </is>
       </c>
     </row>
@@ -4008,15 +4008,15 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+          <t>สถาบันส่งเสริมศิลปหัตถกรรมไทย (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1302</v>
+        <v>1311</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่ายของสำนักงานพาณิชย์จังหวัด 76 จังหวัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการจัดหาพนักงานดูแลหอนิทรรศการและห้องสมุด ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (สมุด)</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f1e51f04-f935-4983-8200-42b44f480fc9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ff1d2fa-ba06-4da0-bc6c-023504d3c9d6</t>
         </is>
       </c>
     </row>
@@ -4043,15 +4043,15 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>สถาบันส่งเสริมศิลปหัตถกรรมไทย (องค์การมหาชน)</t>
+          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1311</v>
+        <v>1808</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการจัดหาพนักงานดูแลหอนิทรรศการและห้องสมุด ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์อื่นๆ (เครื่องแต่งกายโขน-ละคร) จำนวน 7 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4061,12 +4061,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>★ (สมุด)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ff1d2fa-ba06-4da0-bc6c-023504d3c9d6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8e14fee9-d40a-4d5f-b4ec-b5dd1cbdcc29</t>
         </is>
       </c>
     </row>
@@ -4078,15 +4078,15 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
+          <t>กรมส่งเสริมการเรียนรู้</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1808</v>
+        <v>2033</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์อื่นๆ (เครื่องแต่งกายโขน-ละคร) จำนวน 7 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8e14fee9-d40a-4d5f-b4ec-b5dd1cbdcc29</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=988b1f6a-eb89-4ed1-bbe5-4e82ba43054b</t>
         </is>
       </c>
     </row>
@@ -4113,15 +4113,15 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเรียนรู้</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2033</v>
+        <v>2102</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการตู้เย็นเก็บเลือดขนาดไม่น้อยกว่า 20 คิว ของโรงพยาบาลในจังหวัดสุรินทร์ 6 แห่ง จำนวน 7 ตู้ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4131,12 +4131,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์, ตู้เย็น)</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=988b1f6a-eb89-4ed1-bbe5-4e82ba43054b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dfce18c4-7835-4a43-8ba6-fb9a2b9ab472</t>
         </is>
       </c>
     </row>
@@ -4148,15 +4148,15 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมอนามัย</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>2102</v>
+        <v>2109</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการตู้เย็นเก็บเลือดขนาดไม่น้อยกว่า 20 คิว ของโรงพยาบาลในจังหวัดสุรินทร์ 6 แห่ง จำนวน 7 ตู้ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่าย กรมอนามัย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์, ตู้เย็น)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dfce18c4-7835-4a43-8ba6-fb9a2b9ab472</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0f1ebcb1-8a09-4209-922e-0e2e49160cba</t>
         </is>
       </c>
     </row>
@@ -4183,15 +4183,15 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>กรมอนามัย</t>
+          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>2109</v>
+        <v>2113</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่าย กรมอนามัย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์แม่ข่าย (Outsource System) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0f1ebcb1-8a09-4209-922e-0e2e49160cba</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1c3629ca-59d6-4b8a-839b-92b06d6a1c43</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์แม่ข่าย (Outsource System) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์เครือข่าย (Outsource Network) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4241,27 +4241,27 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1c3629ca-59d6-4b8a-839b-92b06d6a1c43</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b44df475-19c0-4304-b42e-0c379f2f6a07</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+          <t>กองทัพอากาศ</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>2113</v>
+        <v>206</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์เครือข่าย (Outsource Network) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโต๊ะและเก้าอี้ประชุม จำนวน ๒ รายการ (แจ้งที่ ๘๙๖/๖๙) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (โต๊ะ, เก้าอี้)</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b44df475-19c0-4304-b42e-0c379f2f6a07</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c197cbba-6119-4a85-8655-64df092381b8</t>
         </is>
       </c>
     </row>
@@ -4288,15 +4288,15 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>กองทัพอากาศ</t>
+          <t>กรมศุลกากร</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>206</v>
+        <v>305</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโต๊ะและเก้าอี้ประชุม จำนวน ๒ รายการ (แจ้งที่ ๘๙๖/๖๙) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องปรับอากาศ แบบฝังฝ้าสี่ทิศทาง (ระบบ Inverter) ขนาด 48,000 บีทียู ด่านศุลกากรปาดังเบซาร์ ตำบลปาดังเบซาร์ อำเภอสะเดา จังหวัดสงขลา 12 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>★ (โต๊ะ, เก้าอี้)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c197cbba-6119-4a85-8655-64df092381b8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7ffdc802-88d9-422f-a01b-27711177cb61</t>
         </is>
       </c>
     </row>
@@ -4323,15 +4323,15 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>กรมศุลกากร</t>
+          <t>กรมสรรพากร</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องปรับอากาศ แบบฝังฝ้าสี่ทิศทาง (ระบบ Inverter) ขนาด 48,000 บีทียู ด่านศุลกากรปาดังเบซาร์ ตำบลปาดังเบซาร์ อำเภอสะเดา จังหวัดสงขลา 12 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบ ไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 2,400 ซีซี  หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ จำนวน 5 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7ffdc802-88d9-422f-a01b-27711177cb61</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e642705c-f34c-41db-ad86-705717edf0ea</t>
         </is>
       </c>
     </row>
@@ -4358,15 +4358,15 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>กรมสรรพากร</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>307</v>
+        <v>704</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบ ไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 2,400 ซีซี  หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ จำนวน 5 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4376,12 +4376,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e642705c-f34c-41db-ad86-705717edf0ea</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5b0cc17-68bd-4696-805e-f78e075178e3</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุด ไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5b0cc17-68bd-4696-805e-f78e075178e3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=106210e4-0233-403f-957c-c894b083d53b</t>
         </is>
       </c>
     </row>
@@ -4428,15 +4428,15 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมส่งเสริมการเกษตร</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุด ไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดชื้อครุภัณฑ์ยานพาหนะและขนส่ง ประจำปีงบประมาณ พ.ศ 2570 โดยวิธีประกวดอิเล็กทรอนิกส์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=106210e4-0233-403f-957c-c894b083d53b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ec4d9c1c-1aa5-4b14-b3ea-60845e7335fb</t>
         </is>
       </c>
     </row>
@@ -4463,15 +4463,15 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเกษตร</t>
+          <t>กรมส่งเสริมสหกรณ์</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดชื้อครุภัณฑ์ยานพาหนะและขนส่ง ประจำปีงบประมาณ พ.ศ 2570 โดยวิธีประกวดอิเล็กทรอนิกส์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาบรรทุกขนาด 1 ตัน หลังคาไฟเบอร์กลาส หรือเหล็กหรือพลาสติกวิศวกรรม สำนักงานสหกรณ์จังหวัดศรีสะเกษ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ec4d9c1c-1aa5-4b14-b3ea-60845e7335fb</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=51b057ec-ffcf-432e-bf86-fe4029225a82</t>
         </is>
       </c>
     </row>
@@ -4498,15 +4498,15 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมสหกรณ์</t>
+          <t>กรมพัฒนาธุรกิจการค้า</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>712</v>
+        <v>1308</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาบรรทุกขนาด 1 ตัน หลังคาไฟเบอร์กลาส หรือเหล็กหรือพลาสติกวิศวกรรม สำนักงานสหกรณ์จังหวัดศรีสะเกษ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องคอมพิวเตอร์ลูกข่ายและอุปกรณ์ต่อพ่วง ปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=51b057ec-ffcf-432e-bf86-fe4029225a82</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=be5cf0cb-614f-4d37-aac0-190b90321cb6</t>
         </is>
       </c>
     </row>
@@ -4533,15 +4533,15 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>กรมพัฒนาธุรกิจการค้า</t>
+          <t>กรมโยธาธิการและผังเมือง</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1308</v>
+        <v>1507</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องคอมพิวเตอร์ลูกข่ายและอุปกรณ์ต่อพ่วง ปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างโครงการจัดหาสิ่งก่อสร้างและครุภัณฑ์ประกอบ อาคารสำนักงานแห่งใหม่ของสำนักงบประมาณ แขวงพญาไท เขตพญาไท กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=be5cf0cb-614f-4d37-aac0-190b90321cb6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8b31f2b3-f6fd-4e5c-979f-8575feda4bbf</t>
         </is>
       </c>
     </row>
@@ -4568,15 +4568,15 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>กรมโยธาธิการและผังเมือง</t>
+          <t>กรมการศาสนา</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1507</v>
+        <v>1803</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างโครงการจัดหาสิ่งก่อสร้างและครุภัณฑ์ประกอบ อาคารสำนักงานแห่งใหม่ของสำนักงบประมาณ แขวงพญาไท เขตพญาไท กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อวัสดุสำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4586,12 +4586,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (วัสดุสำนักงาน)</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8b31f2b3-f6fd-4e5c-979f-8575feda4bbf</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=07f7d716-619d-4e73-9518-7f683a4a05ed</t>
         </is>
       </c>
     </row>
@@ -4603,15 +4603,15 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>กรมการศาสนา</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1803</v>
+        <v>2102</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อวัสดุสำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการชุดกระเป๋าปฐมพยาบาลสนามประจำตัวเจ้าหน้าที่ (IFAK) ของโรงพยาบาลชุมชน 11 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบล 40 แห่ง จำนวน 117 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>★ (วัสดุสำนักงาน)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=07f7d716-619d-4e73-9518-7f683a4a05ed</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=197d72c1-0e0f-4f3d-a377-6f7e052fd668</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการชุดกระเป๋าปฐมพยาบาลสนามประจำตัวเจ้าหน้าที่ (IFAK) ของโรงพยาบาลชุมชน 11 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบล 40 แห่ง จำนวน 117 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=197d72c1-0e0f-4f3d-a377-6f7e052fd668</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a903de26-6f92-4b12-bcdc-87924b3b825b</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อสิทธิ์ใช้งานซอฟต์แวร์จัดการความเสี่ยงเกี่ยวกับระบบสารสนเทศ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a903de26-6f92-4b12-bcdc-87924b3b825b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f182625c-e015-489e-84e0-ac3c9c8dc788</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อสิทธิ์ใช้งานซอฟต์แวร์จัดการความเสี่ยงเกี่ยวกับระบบสารสนเทศ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ กล้องถ่ายภาพจอประสาทตาดิจิตอล (Digital Fundus Camera) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>★ (ซอฟต์แวร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f182625c-e015-489e-84e0-ac3c9c8dc788</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=810bd451-770f-4032-86a0-1216954db79a</t>
         </is>
       </c>
     </row>
@@ -4743,15 +4743,15 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สำนักงานคณะกรรมการอาหารและยา</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2102</v>
+        <v>2110</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ กล้องถ่ายภาพจอประสาทตาดิจิตอล (Digital Fundus Camera) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=810bd451-770f-4032-86a0-1216954db79a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=69d9687c-b7f1-405c-843e-92b98ad29261</t>
         </is>
       </c>
     </row>
@@ -4778,15 +4778,15 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการอาหารและยา</t>
+          <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2110</v>
+        <v>2117</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อติดตั้งระบบกล้องวงจรปิด ของวิทยาลัยพยาบาลบรมราชชนนี นครศรีธรรมราช จำนวน 1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4796,32 +4796,32 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (กล้องวงจรปิด)</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=69d9687c-b7f1-405c-843e-92b98ad29261</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afa9b388-be98-4ed1-8fa9-0c791e5acf34</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>กรมธนารักษ์</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2117</v>
+        <v>303</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อติดตั้งระบบกล้องวงจรปิด ของวิทยาลัยพยาบาลบรมราชชนนี นครศรีธรรมราช จำนวน 1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการทำความสะอาดศูนย์คอมพิวเตอร์แห่งใหม่ ของกรมธนารักษ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>★ (กล้องวงจรปิด)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afa9b388-be98-4ed1-8fa9-0c791e5acf34</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=36f30dd7-0674-4711-a8ba-e71eee8e8ed2</t>
         </is>
       </c>
     </row>
@@ -4848,15 +4848,15 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>กรมธนารักษ์</t>
+          <t>สำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>303</v>
+        <v>502</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการทำความสะอาดศูนย์คอมพิวเตอร์แห่งใหม่ ของกรมธนารักษ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการค่าใช้จ่ายโครงการค่าจ้างบำรุงรักษาและซ่อมแซมห้องปฏิบัติการระบบเครือข่ายคอมพิวเตอร์ (Data Center) ของสำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=36f30dd7-0674-4711-a8ba-e71eee8e8ed2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=056989d3-d491-44ed-b887-fca9a5a8f472</t>
         </is>
       </c>
     </row>
@@ -4883,15 +4883,15 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา</t>
+          <t>กรมส่งเสริมและพัฒนาคุณภาพชีวิตคนพิการ</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>502</v>
+        <v>607</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการค่าใช้จ่ายโครงการค่าจ้างบำรุงรักษาและซ่อมแซมห้องปฏิบัติการระบบเครือข่ายคอมพิวเตอร์ (Data Center) ของสำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์งานบ้านงานครัวและครุภัณฑ์สำนักงาน จำนวน ๒๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=056989d3-d491-44ed-b887-fca9a5a8f472</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f387eaf-54e2-4cf6-8c1c-826da6e3d09e</t>
         </is>
       </c>
     </row>
@@ -4918,15 +4918,15 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมและพัฒนาคุณภาพชีวิตคนพิการ</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>607</v>
+        <v>704</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์งานบ้านงานครัวและครุภัณฑ์สำนักงาน จำนวน ๒๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี. หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บพร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f387eaf-54e2-4cf6-8c1c-826da6e3d09e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b694aef3-f630-4422-a7fe-e31adb551c45</t>
         </is>
       </c>
     </row>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี. หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บพร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องปรับอากาศแบบแยกส่วน (ราคารวมค่าติดตั้ง) แบบตั้งพื้นหรือแบบแขวน(ระบบ Inverter) ขนาดไม่ต่ำกว่า 36,000 บีทียู จำนวน 13 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b694aef3-f630-4422-a7fe-e31adb551c45</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=08075ad1-9390-4520-9d46-f5c2637228e2</t>
         </is>
       </c>
     </row>
@@ -4988,15 +4988,15 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมส่งเสริมสหกรณ์</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องปรับอากาศแบบแยกส่วน (ราคารวมค่าติดตั้ง) แบบตั้งพื้นหรือแบบแขวน(ระบบ Inverter) ขนาดไม่ต่ำกว่า 36,000 บีทียู จำนวน 13 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=08075ad1-9390-4520-9d46-f5c2637228e2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=282d8226-b5a6-422f-ad5a-96682acbb042</t>
         </is>
       </c>
     </row>
@@ -5023,15 +5023,15 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมสหกรณ์</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>712</v>
+        <v>806</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องตรวจวัดปริมาณแอลกอฮอล์ จำนวน 10 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (แอลกอฮอล์)</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=282d8226-b5a6-422f-ad5a-96682acbb042</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=152668c9-b054-48b8-9423-57975423ef48</t>
         </is>
       </c>
     </row>
@@ -5058,15 +5058,15 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>กรมการเปลี่ยนแปลงสภาพภูมิอากาศและสิ่งแวดล้อม</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>806</v>
+        <v>908</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องตรวจวัดปริมาณแอลกอฮอล์ จำนวน 10 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาอุปกรณ์ห้อง Data center และเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>★ (แอลกอฮอล์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=152668c9-b054-48b8-9423-57975423ef48</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3fa0cd84-f2db-47df-b581-c3555885f305</t>
         </is>
       </c>
     </row>
@@ -5093,15 +5093,15 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>กรมการเปลี่ยนแปลงสภาพภูมิอากาศและสิ่งแวดล้อม</t>
+          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>908</v>
+        <v>1202</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาอุปกรณ์ห้อง Data center และเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์เครือข่ายและอุปกรณ์คอมพิวเตอร์แม่ข่าย และอุปกรณ์สำรองข้อมูล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3fa0cd84-f2db-47df-b581-c3555885f305</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=86fe9b9f-c1ba-4f83-8b12-70dbc5d76baa</t>
         </is>
       </c>
     </row>
@@ -5128,15 +5128,15 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1202</v>
+        <v>1302</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์เครือข่ายและอุปกรณ์คอมพิวเตอร์แม่ข่าย และอุปกรณ์สำรองข้อมูล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์สำหรับงานจดทะเบียนและตรวจสอบธุรกิจผิดกฎหมาย กลุ่มทะเบียนธุรกิจและอำนวยความสะดวกทางการค้าของสำนักงานพาณิชย์จังหวัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=86fe9b9f-c1ba-4f83-8b12-70dbc5d76baa</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=06246921-2a22-4f4d-822b-d5abae1c7c8c</t>
         </is>
       </c>
     </row>
@@ -5163,15 +5163,15 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+          <t>กรมสอบสวนคดีพิเศษ</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1302</v>
+        <v>1608</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์สำหรับงานจดทะเบียนและตรวจสอบธุรกิจผิดกฎหมาย กลุ่มทะเบียนธุรกิจและอำนวยความสะดวกทางการค้าของสำนักงานพาณิชย์จังหวัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าเช่าใช้บริการสายสัญญาณเชื่อมโยงเครือข่ายอินเตอร์เน็ตพร้อมระบบ Internet Data Center ประจำปีงบประมาณ พ.ศ. 2570 (เดือนตุลาคม 2569  เดือนกันยายน 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (สายสัญญาณ)</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=06246921-2a22-4f4d-822b-d5abae1c7c8c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f0c10124-df0c-410d-961c-bb4afe1ea16a</t>
         </is>
       </c>
     </row>
@@ -5198,15 +5198,15 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>กรมสอบสวนคดีพิเศษ</t>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าเช่าใช้บริการสายสัญญาณเชื่อมโยงเครือข่ายอินเตอร์เน็ตพร้อมระบบ Internet Data Center ประจำปีงบประมาณ พ.ศ. 2570 (เดือนตุลาคม 2569  เดือนกันยายน 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบประชุมทางไกลผ่านจอภาพ (Video Conference)  ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>★ (สายสัญญาณ)</t>
+          <t>★ (จอภาพ, ระบบประชุมทางไกล)</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f0c10124-df0c-410d-961c-bb4afe1ea16a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bb2e1625-bd6e-49b0-bf5e-6f3975c796e5</t>
         </is>
       </c>
     </row>
@@ -5233,15 +5233,15 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1611</v>
+        <v>2102</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบประชุมทางไกลผ่านจอภาพ (Video Conference)  ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันขนาดกลาง โรงพยาบาลเขาย้อย ตำบลเขาย้อย อำเภอเขาย้อย จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>★ (จอภาพ, ระบบประชุมทางไกล)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bb2e1625-bd6e-49b0-bf5e-6f3975c796e5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4d438ead-6d3b-40c3-8e25-0c855ca2699d</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันขนาดกลาง โรงพยาบาลเขาย้อย ตำบลเขาย้อย อำเภอเขาย้อย จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง โรงพยาบาลหนองหญ้าปล้อง ตำบลหนองหญ้าปล้อง อำเภอหนองหญ้าปล้อง จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4d438ead-6d3b-40c3-8e25-0c855ca2699d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=38179365-12e6-43e5-ac4b-973f7d7d62c9</t>
         </is>
       </c>
     </row>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง โรงพยาบาลหนองหญ้าปล้อง ตำบลหนองหญ้าปล้อง อำเภอหนองหญ้าปล้อง จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดัน ขนาดใหญ่ จำนวน 2 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=38179365-12e6-43e5-ac4b-973f7d7d62c9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2c8651ab-6342-4cf7-b1d4-44acb01ef167</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดัน ขนาดใหญ่ จำนวน 2 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดเล็ก ของโรงพยาบาลชุมชน 2 แห่ง จำนวน 6 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2c8651ab-6342-4cf7-b1d4-44acb01ef167</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=092dea18-169e-423d-bdf4-cbb905df5ef4</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดเล็ก ของโรงพยาบาลชุมชน 2 แห่ง จำนวน 6 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องเอกซเรย์เคลื่อนที่ขนาดไม่น้อยกว่า 300 mA.ขับเคลื่อนด้วยมอเตอร์ไฟฟ้า ของโรงพยาบาลในจังหวัดสุรินทร์ 3 แห่ง จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -5391,12 +5391,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์, มอเตอร์)</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=092dea18-169e-423d-bdf4-cbb905df5ef4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=587ceaac-9b51-4f53-a40b-ba6307295dbc</t>
         </is>
       </c>
     </row>
@@ -5408,15 +5408,15 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมการแพทย์แผนไทยและการแพทย์ทางเลือก</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>2102</v>
+        <v>2105</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องเอกซเรย์เคลื่อนที่ขนาดไม่น้อยกว่า 300 mA.ขับเคลื่อนด้วยมอเตอร์ไฟฟ้า ของโรงพยาบาลในจังหวัดสุรินทร์ 3 แห่ง จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างบำรุงรักษาและซ่อมแซมแก้ไขปัญหาเครื่องคอมพิวเตอร์แม่ข่ายและอุปกรณ์ระบบเครือข่าย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์, มอเตอร์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=587ceaac-9b51-4f53-a40b-ba6307295dbc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a18ab514-a7bf-42a3-be34-78ab2073afdd</t>
         </is>
       </c>
     </row>
@@ -5443,15 +5443,15 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>กรมการแพทย์แผนไทยและการแพทย์ทางเลือก</t>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างบำรุงรักษาและซ่อมแซมแก้ไขปัญหาเครื่องคอมพิวเตอร์แม่ข่ายและอุปกรณ์ระบบเครือข่าย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน ๙ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a18ab514-a7bf-42a3-be34-78ab2073afdd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70e80b61-ece5-4761-bcba-cb1ce4f2a872</t>
         </is>
       </c>
     </row>
@@ -5478,15 +5478,15 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>กรมวิทยาศาสตร์การแพทย์</t>
+          <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>2106</v>
+        <v>2117</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน ๙ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อึครุภัณฑ์สำนักงาน รายการเครื่องปรับอากาศและพัดลม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ, พัดลม)</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70e80b61-ece5-4761-bcba-cb1ce4f2a872</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8cf26d57-cf1b-4ebf-8134-fcf45b7f7c54</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อึครุภัณฑ์สำนักงาน รายการเครื่องปรับอากาศและพัดลม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง (รถยนต์บรรทุกโดยสาร 6 ล้อ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5531,32 +5531,32 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ, พัดลม)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8cf26d57-cf1b-4ebf-8134-fcf45b7f7c54</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=37a7653e-4e42-4513-bc7a-c74cd6a83f90</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>สถาบันเทคโนโลยีป้องกันประเทศ</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>2117</v>
+        <v>209</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง (รถยนต์บรรทุกโดยสาร 6 ล้อ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างซ่อมบำรุงตามวงรอบเครื่องปรับอากาศ อาคาร สป. (แจ้งวัฒนะ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=37a7653e-4e42-4513-bc7a-c74cd6a83f90</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=97592008-d14e-46f6-93ee-062a71e2e9a9</t>
         </is>
       </c>
     </row>
@@ -5583,15 +5583,15 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>สถาบันเทคโนโลยีป้องกันประเทศ</t>
+          <t>สำนักงานปลัดกระทรวงการคลัง</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>209</v>
+        <v>302</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างซ่อมบำรุงตามวงรอบเครื่องปรับอากาศ อาคาร สป. (แจ้งวัฒนะ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อการจัดซื้อหมึกพิมพ์สำหรับ GFMIS Terminal Set เพื่อใช้งานในระบบ New GFMIS Thai ของกรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (หมึกพิมพ์)</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=97592008-d14e-46f6-93ee-062a71e2e9a9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=95f4ee7d-0617-43e5-8099-6f58ee3f83c4</t>
         </is>
       </c>
     </row>
@@ -5618,15 +5618,15 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการคลัง</t>
+          <t>กรมชลประทาน</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>302</v>
+        <v>703</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อการจัดซื้อหมึกพิมพ์สำหรับ GFMIS Terminal Set เพื่อใช้งานในระบบ New GFMIS Thai ของกรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจัดหาและติดตั้งเครื่องสูบน้ำชนิดหอยโข่งแบบ Horizontal Split Case ขับด้วยมอเตอร์ไฟฟ้าอัตราสูบน้ำ ๐.๒๕ ลบ.ม. /วินาที ระยะยกน้ำไม่น้อยกว่า ๔๕ เมตร และอื่นๆ รวม ๔ รายการ  สำหรับงานสถานีสูบน้ำด้วยไฟฟ้าพร้อมระบบส่งน้ำ บ้านสุขสำราญ ตำบลเหล่าต่างคำ อำเภอโพนพิสัย จังหวัดหนองคาย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>★ (หมึกพิมพ์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=95f4ee7d-0617-43e5-8099-6f58ee3f83c4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=766b91be-9aee-491f-bc67-3378c2319ca0</t>
         </is>
       </c>
     </row>
@@ -5653,15 +5653,15 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>กรมชลประทาน</t>
+          <t>กรมประมง</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจัดหาและติดตั้งเครื่องสูบน้ำชนิดหอยโข่งแบบ Horizontal Split Case ขับด้วยมอเตอร์ไฟฟ้าอัตราสูบน้ำ ๐.๒๕ ลบ.ม. /วินาที ระยะยกน้ำไม่น้อยกว่า ๔๕ เมตร และอื่นๆ รวม ๔ รายการ  สำหรับงานสถานีสูบน้ำด้วยไฟฟ้าพร้อมระบบส่งน้ำ บ้านสุขสำราญ ตำบลเหล่าต่างคำ อำเภอโพนพิสัย จังหวัดหนองคาย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน 4 รายการ วิธีประกาศเชิญชวน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=766b91be-9aee-491f-bc67-3378c2319ca0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6af84224-9211-4bd4-b2c3-7790e12e9c3f</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน 4 รายการ วิธีประกาศเชิญชวน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน 4 รายการ  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6af84224-9211-4bd4-b2c3-7790e12e9c3f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=106fd353-637b-4b85-b19c-e5222b434807</t>
         </is>
       </c>
     </row>
@@ -5723,15 +5723,15 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>กรมประมง</t>
+          <t>สำนักงานเศรษฐกิจการเกษตร</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน 4 รายการ  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์หรือระบบสารสนเทศ (โครงการจ้างบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์เครือข่ายและเครื่องคอมพิวเตอร์แม่ข่าย ประจำปีงบประมาณ พ.ศ. 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=106fd353-637b-4b85-b19c-e5222b434807</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e3936fb8-2fe4-4ded-a393-134ec5675427</t>
         </is>
       </c>
     </row>
@@ -5758,15 +5758,15 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>สำนักงานเศรษฐกิจการเกษตร</t>
+          <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>715</v>
+        <v>804</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์หรือระบบสารสนเทศ (โครงการจ้างบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์เครือข่ายและเครื่องคอมพิวเตอร์แม่ข่าย ประจำปีงบประมาณ พ.ศ. 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์พร้อมอุปกรณ์ของระบบการคุ้มครองผู้โดยสารและ การบังคับใช้กฎหมายทั่วไทย (1584 และปรับทั่วไทย) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e3936fb8-2fe4-4ded-a393-134ec5675427</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f5c51a3c-9d4b-4662-a9c5-a560b97ab60f</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์พร้อมอุปกรณ์ของระบบการคุ้มครองผู้โดยสารและ การบังคับใช้กฎหมายทั่วไทย (1584 และปรับทั่วไทย) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างรั้ว ประตูทางเข้า - ออก ป้ายชื่อสำนักงาน และป้อมยามรักษาการณ์ สำนักงานขนส่งจังหวัดลำปาง ตำบลพระบาท อำเภอเมือง จังหวัดลำปาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ป้ายชื่อ)</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f5c51a3c-9d4b-4662-a9c5-a560b97ab60f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f104579c-ae74-4bdb-a71c-250b1777b2c9</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างรั้ว ประตูทางเข้า - ออก ป้ายชื่อสำนักงาน และป้อมยามรักษาการณ์ สำนักงานขนส่งจังหวัดลำปาง ตำบลพระบาท อำเภอเมือง จังหวัดลำปาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขเครื่องคอมพิวเตอร์พร้อมอุปกรณ์ที่ใช้ในการพัฒนาความรู้สารสนเทศ  ด้านความปลอดภัยของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>★ (ป้ายชื่อ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f104579c-ae74-4bdb-a71c-250b1777b2c9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a8c5a924-f969-4f66-a783-51c748bd5141</t>
         </is>
       </c>
     </row>
@@ -5863,15 +5863,15 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
+          <t>กรมอุตุนิยมวิทยา</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>804</v>
+        <v>1104</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขเครื่องคอมพิวเตอร์พร้อมอุปกรณ์ที่ใช้ในการพัฒนาความรู้สารสนเทศ  ด้านความปลอดภัยของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาอุปกรณ์กระจายสัญญาณหลัก (Core Switch) ประจำปีงบประมาณ พ.ศ.2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -5881,12 +5881,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a8c5a924-f969-4f66-a783-51c748bd5141</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b6951565-26a5-4131-b672-af48d4974842</t>
         </is>
       </c>
     </row>
@@ -5898,15 +5898,15 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>กรมอุตุนิยมวิทยา</t>
+          <t>กรมที่ดิน</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1104</v>
+        <v>1505</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาอุปกรณ์กระจายสัญญาณหลัก (Core Switch) ประจำปีงบประมาณ พ.ศ.2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโต๊ะและเก้าอี้เพื่อใช้ในราชการของสำนักงานที่ดินจังหวัดพิษณุโลก และสาขา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
+          <t>★ (โต๊ะ, เก้าอี้)</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b6951565-26a5-4131-b672-af48d4974842</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=06a6ae3e-1109-434c-becf-df99302f96f5</t>
         </is>
       </c>
     </row>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโต๊ะและเก้าอี้เพื่อใช้ในราชการของสำนักงานที่ดินจังหวัดพิษณุโลก และสาขา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบงานและอุปกรณ์คอมพิวเตอร์ ตามโครงการพัฒนาระบบสารสนเทศที่ดิน (ระยะที่ ๒) ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>★ (โต๊ะ, เก้าอี้)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=06a6ae3e-1109-434c-becf-df99302f96f5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0e343fde-5a22-4f02-b2b3-bcf7cfd99bf2</t>
         </is>
       </c>
     </row>
@@ -5968,15 +5968,15 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>กรมที่ดิน</t>
+          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1505</v>
+        <v>1808</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบงานและอุปกรณ์คอมพิวเตอร์ ตามโครงการพัฒนาระบบสารสนเทศที่ดิน (ระยะที่ ๒) ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์การศึกษา (ห้องเรียนอัจฉริยะไฮบริด Smart Hybrid Classroom) ห้องเรียนวิชาชีพ จำนวน 1 ห้อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -5986,12 +5986,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0e343fde-5a22-4f02-b2b3-bcf7cfd99bf2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a6ddc2c9-4ad2-4cd7-93c9-2b5e9a715cfd</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์การศึกษา (ห้องเรียนอัจฉริยะไฮบริด Smart Hybrid Classroom) ห้องเรียนวิชาชีพ จำนวน 1 ห้อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์โฆษณาแะเผยแพร่ (ระบบภาพ LED Display พร้อมติดตั้งภายนอกอาคาร) จำนวน  1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a6ddc2c9-4ad2-4cd7-93c9-2b5e9a715cfd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7b99fd52-1723-486a-a5ce-43a450641ed9</t>
         </is>
       </c>
     </row>
@@ -6038,15 +6038,15 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
+          <t>สำนักงานนวัตกรรมแห่งชาติ (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1808</v>
+        <v>1913</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์โฆษณาแะเผยแพร่ (ระบบภาพ LED Display พร้อมติดตั้งภายนอกอาคาร) จำนวน  1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างเหมาบริการบำรุงรักษาอุปกรณ์ภายในศูนย์ข้อมูลคอมพิวเตอร์(Data Center) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7b99fd52-1723-486a-a5ce-43a450641ed9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70ea1f2e-64d2-48c7-888f-f39d061663c3</t>
         </is>
       </c>
     </row>
@@ -6073,15 +6073,15 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>สำนักงานนวัตกรรมแห่งชาติ (องค์การมหาชน)</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1913</v>
+        <v>2102</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างเหมาบริการบำรุงรักษาอุปกรณ์ภายในศูนย์ข้อมูลคอมพิวเตอร์(Data Center) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70ea1f2e-64d2-48c7-888f-f39d061663c3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5dcaa2f-3e4d-49bc-9324-4c94f510ab5f</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องควบคุมการให้สารน้ำทางหลอดเลือดดำชนิด 1 สาย ของโรงพยาบาลในจังหวัดสุรินทร์ 9 แห่ง จำนวน 66 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5dcaa2f-3e4d-49bc-9324-4c94f510ab5f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=af446873-e18e-4ed1-bd5c-bd34b74e9b76</t>
         </is>
       </c>
     </row>
@@ -6143,15 +6143,15 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมการแพทย์</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องควบคุมการให้สารน้ำทางหลอดเลือดดำชนิด 1 สาย ของโรงพยาบาลในจังหวัดสุรินทร์ 9 แห่ง จำนวน 66 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์เครื่องเสริมสร้างความแข็งแรงของกล้ามเนื้ออุ้งเชิงกราน รักษาอาการปัสสาวะเล็ด ลดอาการปวดจากกล้ามเนื้อและระบบประสาทบริเวณ อุ้งเชิงกรานและหลังด้วยคลื่นแม่เหล็กไฟฟ้า สถาบันเวชศาสตร์สมเด็จพระสังฆราชญาณสังวรเพื่อผู้สูงอายุ ตำบลตลาดขวัญ อำเภอเมือง จังหวัดนนทบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -6166,27 +6166,27 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=af446873-e18e-4ed1-bd5c-bd34b74e9b76</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=543d641e-2bab-40db-bddc-5b9d81caf16b</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>กรมการแพทย์</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>2103</v>
+        <v>204</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์เครื่องเสริมสร้างความแข็งแรงของกล้ามเนื้ออุ้งเชิงกราน รักษาอาการปัสสาวะเล็ด ลดอาการปวดจากกล้ามเนื้อและระบบประสาทบริเวณ อุ้งเชิงกรานและหลังด้วยคลื่นแม่เหล็กไฟฟ้า สถาบันเวชศาสตร์สมเด็จพระสังฆราชญาณสังวรเพื่อผู้สูงอายุ ตำบลตลาดขวัญ อำเภอเมือง จังหวัดนนทบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำหรับงานซ่อมปรับปรุงสนามกีฬาของ หน่วยบัญชาการสงครามพิเศษ เพื่อรองรับการแข่งขันกีฬา กองทัพบก ครั้งที่ 74 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=543d641e-2bab-40db-bddc-5b9d81caf16b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=91712891-37fd-4bbc-ae6c-0044106ce3a9</t>
         </is>
       </c>
     </row>
@@ -6213,15 +6213,15 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>204</v>
+        <v>704</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์สำหรับงานซ่อมปรับปรุงสนามกีฬาของ หน่วยบัญชาการสงครามพิเศษ เพื่อรองรับการแข่งขันกีฬา กองทัพบก ครั้งที่ 74 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะ รถโดยสารขนาด 12 ที่นั่ง (ดีเซล) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=91712891-37fd-4bbc-ae6c-0044106ce3a9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6d9307c6-812c-4689-9154-bd79b77edeed</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะ รถโดยสารขนาด 12 ที่นั่ง (ดีเซล) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องคอมพิวเตอร์โน๊ตบุ๊ค สำหรับงานประมวลผล พร้อมชุดโปรแกรมระบบปฏิบัติการสำหรับคอมพิวเตอร์และเครี่องคอมพิวเตอร์โน๊ตบุ๊ค แบบสิทธิการใช้งานภายในสำนักงาน ประเภทติดตั้งมาจากโรงงาน (OEM) ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย ชุดโปรแกรมจัดการสำนักงาน แบบที่ 2   ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย และชุดโปรแกรมป้องกันไวรัส จำนวน 21 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -6266,12 +6266,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, โน๊ตบุ๊ค, ระบบปฏิบัติการ, โปรแกรมป้องกันไวรัส)</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6d9307c6-812c-4689-9154-bd79b77edeed</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ac28390d-f1a5-41e3-8fed-7350ce5638bc</t>
         </is>
       </c>
     </row>
@@ -6283,15 +6283,15 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>704</v>
+        <v>805</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องคอมพิวเตอร์โน๊ตบุ๊ค สำหรับงานประมวลผล พร้อมชุดโปรแกรมระบบปฏิบัติการสำหรับคอมพิวเตอร์และเครี่องคอมพิวเตอร์โน๊ตบุ๊ค แบบสิทธิการใช้งานภายในสำนักงาน ประเภทติดตั้งมาจากโรงงาน (OEM) ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย ชุดโปรแกรมจัดการสำนักงาน แบบที่ 2   ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย และชุดโปรแกรมป้องกันไวรัส จำนวน 21 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานหัวหิน ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -6301,12 +6301,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, โน๊ตบุ๊ค, ระบบปฏิบัติการ, โปรแกรมป้องกันไวรัส)</t>
+          <t>★ (รถเข็น)</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ac28390d-f1a5-41e3-8fed-7350ce5638bc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f40b4d90-5120-4848-a5d2-b177de8a9a09</t>
         </is>
       </c>
     </row>
@@ -6318,15 +6318,15 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
+          <t>กรมพัฒนาธุรกิจการค้า</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>805</v>
+        <v>1308</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานหัวหิน ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์แม่ข่ายและอุปกรณ์รักษาความปลอดภัย ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>★ (รถเข็น)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f40b4d90-5120-4848-a5d2-b177de8a9a09</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=652c12bb-908d-48aa-a87c-f244b33e9ad3</t>
         </is>
       </c>
     </row>
@@ -6353,15 +6353,15 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>กรมพัฒนาธุรกิจการค้า</t>
+          <t>กรมที่ดิน</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1308</v>
+        <v>1505</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์แม่ข่ายและอุปกรณ์รักษาความปลอดภัย ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมอุปกรณ์ รวม ๘ รายการ สำหรับใช้ในราชการกองเทคโนโลยีทำแผนที่ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=652c12bb-908d-48aa-a87c-f244b33e9ad3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c85d670f-a209-4413-8ade-5dba1d3d0298</t>
         </is>
       </c>
     </row>
@@ -6388,15 +6388,15 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>กรมที่ดิน</t>
+          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1505</v>
+        <v>1905</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมอุปกรณ์ รวม ๘ รายการ สำหรับใช้ในราชการกองเทคโนโลยีทำแผนที่ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์โครงการห้องปฏิบัติการทดสอบด้านวิศวกรรมการใช้งาน (Usability Engineering) ผลิตภัณฑ์ซอฟต์แวร์หุ่นยนต์ทางการแพทย์และเครื่องมือแพทย์ตามมาตรฐานสากล (Usability Engineering Laboratories for Software, Medical Robotics, and Medical Devices under International Standards) จํานวน ๑ ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ซอฟต์แวร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c85d670f-a209-4413-8ade-5dba1d3d0298</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0415b5bd-8794-467b-9e54-5ae4bdabae87</t>
         </is>
       </c>
     </row>
@@ -6423,15 +6423,15 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1905</v>
+        <v>2102</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์โครงการห้องปฏิบัติการทดสอบด้านวิศวกรรมการใช้งาน (Usability Engineering) ผลิตภัณฑ์ซอฟต์แวร์หุ่นยนต์ทางการแพทย์และเครื่องมือแพทย์ตามมาตรฐานสากล (Usability Engineering Laboratories for Software, Medical Robotics, and Medical Devices under International Standards) จํานวน ๑ ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องอุ่นเลือดและส่วนประกอบของเลือดชนิดไม่สัมผัสน้ำสามารถอุ่นเลือดได้ พร้อมกันไม่น้อยกว่า 3 ถุง จำนวน 4 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย -  กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>★ (ซอฟต์แวร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0415b5bd-8794-467b-9e54-5ae4bdabae87</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2157b09f-d16e-4bcf-b720-de1088bc7b0e</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องอุ่นเลือดและส่วนประกอบของเลือดชนิดไม่สัมผัสน้ำสามารถอุ่นเลือดได้ พร้อมกันไม่น้อยกว่า 3 ถุง จำนวน 4 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย -  กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องควบคุมการให้สารละลายโดยใช้กระบอกฉีด ของโรงพยาบาลในจังหวัดสุรินทร์ 5 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบลสำเภาลูน จำนวน 26 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2157b09f-d16e-4bcf-b720-de1088bc7b0e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=33f2d0df-213d-44c4-a6fa-d31b0eb2e1f6</t>
         </is>
       </c>
     </row>
@@ -6493,15 +6493,15 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>2102</v>
+        <v>2106</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องควบคุมการให้สารละลายโดยใช้กระบอกฉีด ของโรงพยาบาลในจังหวัดสุรินทร์ 5 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบลสำเภาลูน จำนวน 26 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาซ่อมแซมแก้ไขระบบเครือข่ายและเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=33f2d0df-213d-44c4-a6fa-d31b0eb2e1f6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=77d1f891-c26e-4f3d-a9e2-7ca16c4196b3</t>
         </is>
       </c>
     </row>
@@ -6528,15 +6528,15 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>กรมวิทยาศาสตร์การแพทย์</t>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาซ่อมแซมแก้ไขระบบเครือข่ายและเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -6546,12 +6546,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=77d1f891-c26e-4f3d-a9e2-7ca16c4196b3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b600d06e-5f90-400c-80fc-24c6ae2ef280</t>
         </is>
       </c>
     </row>
@@ -6563,15 +6563,15 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>กรมสนับสนุนบริการสุขภาพ</t>
+          <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>2107</v>
+        <v>2117</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์วิทยาศาสตร์การแพทย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b600d06e-5f90-400c-80fc-24c6ae2ef280</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a3db48e8-9e8b-4535-84a6-a14f5811619b</t>
         </is>
       </c>
     </row>
@@ -6598,15 +6598,15 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>สำนักงานพระพุทธศาสนาแห่งชาติ</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>2117</v>
+        <v>2503</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์วิทยาศาสตร์การแพทย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -6616,32 +6616,32 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a3db48e8-9e8b-4535-84a6-a14f5811619b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=285cc870-c52b-429d-b866-52f939bc7fd0</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>สำนักงานพระพุทธศาสนาแห่งชาติ</t>
+          <t>กรมพัฒนาที่ดิน</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>2503</v>
+        <v>708</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจอแสดงผล LED พร้อมอุปกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -6651,12 +6651,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (จอแสดงผล)</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=285cc870-c52b-429d-b866-52f939bc7fd0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=45d8cd64-624e-4582-a8d1-3fe3d01e41b6</t>
         </is>
       </c>
     </row>
@@ -6668,15 +6668,15 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>กรมพัฒนาที่ดิน</t>
+          <t>กรมการข้าว</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจอแสดงผล LED พร้อมอุปกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องปรับอากาศ แบบแยกส่วน แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>★ (จอแสดงผล)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=45d8cd64-624e-4582-a8d1-3fe3d01e41b6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2475fb18-8633-42d5-8fe6-f520615dc6f7</t>
         </is>
       </c>
     </row>
@@ -6703,15 +6703,15 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>กรมการข้าว</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>718</v>
+        <v>806</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องปรับอากาศ แบบแยกส่วน แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ และ ครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 13 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2475fb18-8633-42d5-8fe6-f520615dc6f7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0b00828b-7442-420e-85c9-ad09d2f6e16f</t>
         </is>
       </c>
     </row>
@@ -6738,15 +6738,15 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>กรมทรัพยากรน้ำบาดาล</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>806</v>
+        <v>907</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ และ ครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 13 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องสูบน้ำไฟฟ้าชนิดมอเตอร์จุ่มใต้น้ำ พร้อมอุปกรณ์ และชุดฝาปิดปากบ่อน้ำบาดาล จำนวน ๖ ชุด โครงการพัฒนาน้ำบาดาลเพื่อความมั่นคงระดับชุมชน ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ (งบเหลือจ่าย) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -6756,12 +6756,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0b00828b-7442-420e-85c9-ad09d2f6e16f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=03ba8462-a0d1-4d13-92c2-a7ae76fed3d0</t>
         </is>
       </c>
     </row>
@@ -6773,15 +6773,15 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>กรมทรัพยากรน้ำบาดาล</t>
+          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องสูบน้ำไฟฟ้าชนิดมอเตอร์จุ่มใต้น้ำ พร้อมอุปกรณ์ และชุดฝาปิดปากบ่อน้ำบาดาล จำนวน ๖ ชุด โครงการพัฒนาน้ำบาดาลเพื่อความมั่นคงระดับชุมชน ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ (งบเหลือจ่าย) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทเรือหางยาวสำหรับการลาดตระเวนพื้นที่ทางน้ำ เพื่อเพิ่มประสิทธิภาพการปฏิบัติงานอุทยานแห่งชาติเขาแหลม จังหวัดกาญจนบุรี  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=03ba8462-a0d1-4d13-92c2-a7ae76fed3d0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63f7333f-eb0c-40fa-8c06-5f683d543bce</t>
         </is>
       </c>
     </row>
@@ -6808,15 +6808,15 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
+          <t>กรมการปกครอง</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>909</v>
+        <v>1503</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทเรือหางยาวสำหรับการลาดตระเวนพื้นที่ทางน้ำ เพื่อเพิ่มประสิทธิภาพการปฏิบัติงานอุทยานแห่งชาติเขาแหลม จังหวัดกาญจนบุรี  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อวัสดุครุภัณฑ์สำนักงานที่ทำการปกครองอำเภอตาพระยา จังหวัดสระแก้ว ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -6826,12 +6826,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63f7333f-eb0c-40fa-8c06-5f683d543bce</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=de60da4a-56f9-434f-bd1c-60d19d95f672</t>
         </is>
       </c>
     </row>
@@ -6843,15 +6843,15 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>กรมการปกครอง</t>
+          <t>กรมที่ดิน</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อวัสดุครุภัณฑ์สำนักงานที่ทำการปกครองอำเภอตาพระยา จังหวัดสระแก้ว ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์เพื่อการบริหารจัดการหน่วยงานส่วนกลาง (Hardware และ Software) ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -6861,12 +6861,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=de60da4a-56f9-434f-bd1c-60d19d95f672</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a80802ed-6d42-4b60-b93c-de21fb24e5c0</t>
         </is>
       </c>
     </row>
@@ -6878,15 +6878,15 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>กรมที่ดิน</t>
+          <t>กรมการจัดหางาน</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1505</v>
+        <v>1703</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์เพื่อการบริหารจัดการหน่วยงานส่วนกลาง (Hardware และ Software) ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ทดแทนและเพิ่มประสิทธิภาพของสำนักบริหารแรงงานต่างด้าว ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -6896,12 +6896,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a80802ed-6d42-4b60-b93c-de21fb24e5c0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f3092a7e-5bf1-488f-8f3f-6657ba0fe2fd</t>
         </is>
       </c>
     </row>
@@ -6913,15 +6913,15 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>กรมการจัดหางาน</t>
+          <t>กรมพัฒนาฝีมือแรงงาน</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ทดแทนและเพิ่มประสิทธิภาพของสำนักบริหารแรงงานต่างด้าว ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ (ระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop) ขนาด 3 เฟส 15 กิโลวัตต์ ตำบลบ่อ อำเภอขลุง จังหวัดจันทบุรี จำนวน 1 ระบบ และระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop) ขนาด 3 เฟส 20 กิโลวัตต์ ตำบลบ่อ อำเภอขลุง จังหวัดจันทบุรี จำนวน 1 ระบบ) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f3092a7e-5bf1-488f-8f3f-6657ba0fe2fd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d90e4389-d0ce-48d4-b93a-03874d22d178</t>
         </is>
       </c>
     </row>
@@ -6948,15 +6948,15 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>กรมพัฒนาฝีมือแรงงาน</t>
+          <t>กรมการศาสนา</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1704</v>
+        <v>1803</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ (ระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop) ขนาด 3 เฟส 15 กิโลวัตต์ ตำบลบ่อ อำเภอขลุง จังหวัดจันทบุรี จำนวน 1 ระบบ และระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop) ขนาด 3 เฟส 20 กิโลวัตต์ ตำบลบ่อ อำเภอขลุง จังหวัดจันทบุรี จำนวน 1 ระบบ) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อหมึกเครื่องพิมพ์ (ครั้งที่ 2)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (หมึกเครื่องพิมพ์, เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d90e4389-d0ce-48d4-b93a-03874d22d178</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8ffdb256-bac2-4342-bdf6-7616e2ae5b25</t>
         </is>
       </c>
     </row>
@@ -6983,15 +6983,15 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>กรมการศาสนา</t>
+          <t>สถาบันมาตรวิทยาแห่งชาติ</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1803</v>
+        <v>1907</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อหมึกเครื่องพิมพ์ (ครั้งที่ 2)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างค่าบำรุงรักษาอุปกรณ์เครือข่ายประจำอาคาร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -7001,12 +7001,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>★ (หมึกเครื่องพิมพ์, เครื่องพิมพ์)</t>
+          <t>★ (อุปกรณ์เครือข่าย)</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8ffdb256-bac2-4342-bdf6-7616e2ae5b25</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b698a86e-10e2-45f2-be5e-f7ec03fa0ce9</t>
         </is>
       </c>
     </row>
@@ -7018,15 +7018,15 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>สถาบันมาตรวิทยาแห่งชาติ</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1907</v>
+        <v>2102</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างค่าบำรุงรักษาอุปกรณ์เครือข่ายประจำอาคาร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการรถพยาบาลพร้อมอุปกรณ์ช่วยชีวิตชั้นสูง ของโรงพยาบาลชุมชน 4 แห่ง จำนวน 4 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -7036,12 +7036,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>★ (อุปกรณ์เครือข่าย)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b698a86e-10e2-45f2-be5e-f7ec03fa0ce9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f77b490-654b-45ac-9d8e-cc1f4f3fd4fb</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการรถพยาบาลพร้อมอุปกรณ์ช่วยชีวิตชั้นสูง ของโรงพยาบาลชุมชน 4 แห่ง จำนวน 4 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดออกซิเจนในเลือดอัตโนมัติชนิดพกพา จำนวน 39 เครื่องๆ งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f77b490-654b-45ac-9d8e-cc1f4f3fd4fb</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f13af428-4413-4d73-9542-bd582ed6e240</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดออกซิเจนในเลือดอัตโนมัติชนิดพกพา จำนวน 39 เครื่องๆ งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจคลื่นไฟฟ้าหัวใจ พร้อมเชื่อมต่อระบบแพทย์ทางไกล จำนวน 27 เครื่อง งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f13af428-4413-4d73-9542-bd582ed6e240</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9350a991-2cda-4337-b005-93d114caf75c</t>
         </is>
       </c>
     </row>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจคลื่นไฟฟ้าหัวใจ พร้อมเชื่อมต่อระบบแพทย์ทางไกล จำนวน 27 เครื่อง งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการตู้เย็นเก็บเลือด ขนาดไม่น้อยกว่า 20 คิว จำนวน 4 ตู้ งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์  การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์, ตู้เย็น)</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9350a991-2cda-4337-b005-93d114caf75c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=83dc4a91-4e74-465d-b378-562e91d2b662</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการตู้เย็นเก็บเลือด ขนาดไม่น้อยกว่า 20 คิว จำนวน 4 ตู้ งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์  การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ เครื่องให้การรักษาอาการปวดและกระตุ้นเซลล์ประสาทส่วนปลายด้วยสนามแม่เหล็กไฟฟ้า(PMS) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์, ตู้เย็น)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=83dc4a91-4e74-465d-b378-562e91d2b662</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=35bbde9c-eb8e-445f-b94e-915454477995</t>
         </is>
       </c>
     </row>
@@ -7193,15 +7193,15 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>2102</v>
+        <v>2106</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ เครื่องให้การรักษาอาการปวดและกระตุ้นเซลล์ประสาทส่วนปลายด้วยสนามแม่เหล็กไฟฟ้า(PMS) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมระบบปฏิบัติการและชุดโปรแกรมจัดการสำนักงาน จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -7211,12 +7211,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ระบบปฏิบัติการ, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=35bbde9c-eb8e-445f-b94e-915454477995</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=414ac115-ac50-4d65-a54d-d2a9e03b621b</t>
         </is>
       </c>
     </row>
@@ -7228,15 +7228,15 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>กรมวิทยาศาสตร์การแพทย์</t>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมระบบปฏิบัติการและชุดโปรแกรมจัดการสำนักงาน จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ เครื่องวิเคราะห์การทำงานตู้อบเด็ก จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -7246,32 +7246,32 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ระบบปฏิบัติการ, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=414ac115-ac50-4d65-a54d-d2a9e03b621b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9d04622a-81b1-4cfd-9a05-6c2aec6751f7</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>กรมสนับสนุนบริการสุขภาพ</t>
+          <t>กรมบัญชีกลาง</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>2107</v>
+        <v>304</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ เครื่องวิเคราะห์การทำงานตู้อบเด็ก จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาและซ่อมแซมแก้ไขเครื่องปรับอากาศ (แบบรวมอะไหล่) จำนวน 474 เครื่อง ซ่อมแซมแก้ไขระบบไฟฟ้า และระบบสุขาภิบาล อาคาร 3 อาคาร 9 อาคารใหม่ ชั้นใต้ดิน และห้องลิฟต์ กรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -7281,12 +7281,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9d04622a-81b1-4cfd-9a05-6c2aec6751f7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=273a8add-ac17-48f1-8ff9-c94a946e8273</t>
         </is>
       </c>
     </row>
@@ -7298,15 +7298,15 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>กรมบัญชีกลาง</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>304</v>
+        <v>704</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาและซ่อมแซมแก้ไขเครื่องปรับอากาศ (แบบรวมอะไหล่) จำนวน 474 เครื่อง ซ่อมแซมแก้ไขระบบไฟฟ้า และระบบสุขาภิบาล อาคาร 3 อาคาร 9 อาคารใหม่ ชั้นใต้ดิน และห้องลิฟต์ กรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ พร้อมชุดโปรแกรมปฎิบัติงาน โปรแกรมจัดการสำนักงาน และโปรแกรมป้องกันไวรัส จำนวน 18 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -7316,12 +7316,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (คอมพิวเตอร์, โปรแกรมป้องกันไวรัส, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=273a8add-ac17-48f1-8ff9-c94a946e8273</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0511e3cd-537d-45d3-880c-de7433b1eb48</t>
         </is>
       </c>
     </row>
@@ -7333,15 +7333,15 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมประมง</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ พร้อมชุดโปรแกรมปฎิบัติงาน โปรแกรมจัดการสำนักงาน และโปรแกรมป้องกันไวรัส จำนวน 18 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อชุดจอภาพ LED พร้อมงานติดตั้งสำหรับห้องประชุมอานนท์ กรมประมง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, โปรแกรมป้องกันไวรัส, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (จอภาพ)</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0511e3cd-537d-45d3-880c-de7433b1eb48</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b0679766-012d-497b-8e41-2296e1c7ba51</t>
         </is>
       </c>
     </row>
@@ -7368,15 +7368,15 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>กรมประมง</t>
+          <t>กรมปศุสัตว์</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อชุดจอภาพ LED พร้อมงานติดตั้งสำหรับห้องประชุมอานนท์ กรมประมง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>★ (จอภาพ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b0679766-012d-497b-8e41-2296e1c7ba51</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f70d294-53f0-4fd1-b9bc-ef06d20b1657</t>
         </is>
       </c>
     </row>
@@ -7403,15 +7403,15 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>กรมปศุสัตว์</t>
+          <t>สำนักงานนโยบายและแผนการขนส่งและจราจร</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>706</v>
+        <v>808</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์ของ สนข. ประจำปีงบประมาณ พ.ศ. 2570  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f70d294-53f0-4fd1-b9bc-ef06d20b1657</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=069d5584-a6b1-426d-9714-115f2fdc7025</t>
         </is>
       </c>
     </row>
@@ -7438,15 +7438,15 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>สำนักงานนโยบายและแผนการขนส่งและจราจร</t>
+          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>808</v>
+        <v>904</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์ของ สนข. ประจำปีงบประมาณ พ.ศ. 2570  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาและเพิ่มประสิทธิภาพระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรทางทะเลและชายฝั่ง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=069d5584-a6b1-426d-9714-115f2fdc7025</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f112758f-839d-4660-91b5-12181a1297d2</t>
         </is>
       </c>
     </row>
@@ -7473,15 +7473,15 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
+          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>904</v>
+        <v>1202</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการบำรุงรักษาและเพิ่มประสิทธิภาพระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรทางทะเลและชายฝั่ง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่ารถส่วนภูมิภาค รถยนต์ไฟฟ้า ประเภทแบตเตอรี่ (BEV) ขนาดความจุของแบตเตอรี่มากกว่า 50 กิโลวัตต์ชั่วโมง (kWh) และกำลังมอเตอร์ไฟฟ้าสูงสุด ไม่เกิน 150 กิโลวัตต์ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f112758f-839d-4660-91b5-12181a1297d2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=40cb45e4-0e08-48b9-a763-7a9aa44d7959</t>
         </is>
       </c>
     </row>
@@ -7508,15 +7508,15 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
+          <t>กรมการปกครอง</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1202</v>
+        <v>1503</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่ารถส่วนภูมิภาค รถยนต์ไฟฟ้า ประเภทแบตเตอรี่ (BEV) ขนาดความจุของแบตเตอรี่มากกว่า 50 กิโลวัตต์ชั่วโมง (kWh) และกำลังมอเตอร์ไฟฟ้าสูงสุด ไม่เกิน 150 กิโลวัตต์ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 5 รายการ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=40cb45e4-0e08-48b9-a763-7a9aa44d7959</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ac3547dc-0f12-4694-b5a3-e216678ce172</t>
         </is>
       </c>
     </row>
@@ -7543,15 +7543,15 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>กรมการปกครอง</t>
+          <t>กรมการศาสนา</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1503</v>
+        <v>1803</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 5 รายการ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อวัสดุสำนักงานส่วนกลาง ประจำปีงบประมาณ พ.ศ. 2569 (ครั้งที่ 2)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (วัสดุสำนักงาน)</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ac3547dc-0f12-4694-b5a3-e216678ce172</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c6f2fbd0-4267-42c4-926d-d8fc49d8a3ff</t>
         </is>
       </c>
     </row>
@@ -7578,15 +7578,15 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>กรมการศาสนา</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1803</v>
+        <v>2102</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อวัสดุสำนักงานส่วนกลาง ประจำปีงบประมาณ พ.ศ. 2569 (ครั้งที่ 2)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องผลิตออกซิเจนขนาด 5 ลิตร ของโรงพยาบาลสนม และโรงพยาบาลส่งเสริมสุขภาพตำบล 18 แห่ง จำนวน 33 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>★ (วัสดุสำนักงาน)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c6f2fbd0-4267-42c4-926d-d8fc49d8a3ff</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=655601b1-75a6-4eee-9bc7-ee3ce427abf6</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องผลิตออกซิเจนขนาด 5 ลิตร ของโรงพยาบาลสนม และโรงพยาบาลส่งเสริมสุขภาพตำบล 18 แห่ง จำนวน 33 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดความดันโลหิตชนิดอัตโนมัติ วัดความอิ่มตัวของออกซิเจนในเลือด อุณหภูมิร่างกาย พร้อมระบบเชื่อมต่อฐานข้อมูล ของโรงพยาบาลในจังหวัดสุรินทร์ 12 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบล 10 แห่ง จำนวน 50 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=655601b1-75a6-4eee-9bc7-ee3ce427abf6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=65a2753e-e63f-4be2-b228-0fe250379934</t>
         </is>
       </c>
     </row>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดความดันโลหิตชนิดอัตโนมัติ วัดความอิ่มตัวของออกซิเจนในเลือด อุณหภูมิร่างกาย พร้อมระบบเชื่อมต่อฐานข้อมูล ของโรงพยาบาลในจังหวัดสุรินทร์ 12 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบล 10 แห่ง จำนวน 50 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการชุดอุปกรณ์เคลื่อนย้ายผู้ป่วยในสถานการณ์ฉุกเฉิน ของโรงพยาบาลชุมชน 8 แห่ง จำนวน 10 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=65a2753e-e63f-4be2-b228-0fe250379934</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=886059b7-d984-4e19-b7d7-6d90ebc9b2e0</t>
         </is>
       </c>
     </row>
@@ -7691,7 +7691,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการชุดอุปกรณ์เคลื่อนย้ายผู้ป่วยในสถานการณ์ฉุกเฉิน ของโรงพยาบาลชุมชน 8 แห่ง จำนวน 10 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงชนิดสี 2 หัวตรวจ ของโรงพยาบาลชุมชน 6 แห่ง จำนวน 8 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=886059b7-d984-4e19-b7d7-6d90ebc9b2e0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fc233297-ee25-42e4-bc90-16f41ac8db6a</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงชนิดสี 2 หัวตรวจ ของโรงพยาบาลชุมชน 6 แห่ง จำนวน 8 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดออกซิเจนในเลือดอัตโนมัติชนิดพกพา ของโรงพยาบาลส่งเสริมสุขภาพตำบลและโรงพยาบาลชุมชน 24 แห่ง จำนวน 68 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fc233297-ee25-42e4-bc90-16f41ac8db6a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3d2922a2-6499-49fa-b182-1e95dc5131d7</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดออกซิเจนในเลือดอัตโนมัติชนิดพกพา ของโรงพยาบาลส่งเสริมสุขภาพตำบลและโรงพยาบาลชุมชน 24 แห่ง จำนวน 68 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องเอกซเรย์ทั่วไปขนาดไม่น้อยกว่า 500 mA. แบบแขวนเพดาน โรงพยาบาลแก่งกระจาน ตำบลวังจันทร์ อำเภอแก่งกระจาน จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -7776,27 +7776,27 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3d2922a2-6499-49fa-b182-1e95dc5131d7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6f21d5fd-56e9-4486-915b-90fd4be0f39b</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กองทัพอากาศ</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>2102</v>
+        <v>206</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องเอกซเรย์ทั่วไปขนาดไม่น้อยกว่า 500 mA. แบบแขวนเพดาน โรงพยาบาลแก่งกระจาน ตำบลวังจันทร์ อำเภอแก่งกระจาน จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบริการบำรุงรักษาเครื่องเอกซเรย์ควบคุมด้วยระบบคอมพิวเตอร์ขนาดไม่น้อยกว่า 300 mA พร้อมอุปกรณ์ ยี่ห้อ DRGEM รุ่น GXR-52S ของ โรงพยาบาลกองบิน กองบิน 1, โรงพยาบาลกองบิน กองบิน 2, โรงพยาบาลกองบิน กองบิน 7, โรงพยาบาลกองบิน กองบิน 41, โรงพยาบาลกองบิน กองบิน 46 จำนวน ๑ งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6f21d5fd-56e9-4486-915b-90fd4be0f39b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ffb67ab2-d749-4ab0-87f1-1b11432ab218</t>
         </is>
       </c>
     </row>
@@ -7823,15 +7823,15 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>กองทัพอากาศ</t>
+          <t>กรมธนารักษ์</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>206</v>
+        <v>303</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบริการบำรุงรักษาเครื่องเอกซเรย์ควบคุมด้วยระบบคอมพิวเตอร์ขนาดไม่น้อยกว่า 300 mA พร้อมอุปกรณ์ ยี่ห้อ DRGEM รุ่น GXR-52S ของ โรงพยาบาลกองบิน กองบิน 1, โรงพยาบาลกองบิน กองบิน 2, โรงพยาบาลกองบิน กองบิน 7, โรงพยาบาลกองบิน กองบิน 41, โรงพยาบาลกองบิน กองบิน 46 จำนวน ๑ งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องอากาศยานซึ่งไม่มีนักบิน (Drone)  พร้อมชุดอุปกรณ์ภาคสนามและระบบซอฟต์แวร์ประมวลผลแผนที่ความละเอียดสูง จำนวน 12 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ffb67ab2-d749-4ab0-87f1-1b11432ab218</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e88cabea-0e2e-4af8-8b8b-4aa4e7eb040a</t>
         </is>
       </c>
     </row>
@@ -7858,15 +7858,15 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>กรมธนารักษ์</t>
+          <t>สำนักงานเศรษฐกิจการคลัง</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องอากาศยานซึ่งไม่มีนักบิน (Drone)  พร้อมชุดอุปกรณ์ภาคสนามและระบบซอฟต์แวร์ประมวลผลแผนที่ความละเอียดสูง จำนวน 12 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์สำหรับโครงการพัฒนาระบบสารสนเทศสถาบันการเงินประชาชนของสำนักงานเศรษฐกิจการคลัง (ระบบงาน PFI) ประจำปีงบประมาณ พ.ศ. 2570  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>★ (ซอฟต์แวร์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e88cabea-0e2e-4af8-8b8b-4aa4e7eb040a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a787a49a-4035-46d3-b8a4-a996ac96341d</t>
         </is>
       </c>
     </row>
@@ -7893,15 +7893,15 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>สำนักงานเศรษฐกิจการคลัง</t>
+          <t>กรมพัฒนาสังคมและสวัสดิการ</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>311</v>
+        <v>603</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์สำหรับโครงการพัฒนาระบบสารสนเทศสถาบันการเงินประชาชนของสำนักงานเศรษฐกิจการคลัง (ระบบงาน PFI) ประจำปีงบประมาณ พ.ศ. 2570  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์สำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -7911,12 +7911,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a787a49a-4035-46d3-b8a4-a996ac96341d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=857f0ccd-d38e-47b0-8d6d-913ef2cb1583</t>
         </is>
       </c>
     </row>
@@ -7928,15 +7928,15 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>กรมพัฒนาสังคมและสวัสดิการ</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>603</v>
+        <v>704</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์สำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -7946,12 +7946,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=857f0ccd-d38e-47b0-8d6d-913ef2cb1583</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=01c185be-f27c-41bc-868e-accd57e4a95c</t>
         </is>
       </c>
     </row>
@@ -7963,15 +7963,15 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>704</v>
+        <v>804</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์พร้อมอุปกรณ์สำหรับศูนย์รวมข้อมูลการขนส่งด้วยรถบรรทุกเพื่อส่งเสริมการขนส่งด้วยรถบรรทุกให้มีประสิทธิภาพ ปลอดภัยและได้มาตรฐาน (TDSC) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=01c185be-f27c-41bc-868e-accd57e4a95c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70381c19-a073-41d0-8f0b-08c5e68fca7c</t>
         </is>
       </c>
     </row>
@@ -7998,15 +7998,15 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
+          <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์พร้อมอุปกรณ์สำหรับศูนย์รวมข้อมูลการขนส่งด้วยรถบรรทุกเพื่อส่งเสริมการขนส่งด้วยรถบรรทุกให้มีประสิทธิภาพ ปลอดภัยและได้มาตรฐาน (TDSC) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบไฟฟ้า ตู้สวิตช์บอร์ด ๒๖ ท่าอากาศยาน และกรมท่าอากาศยาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (สวิตช์)</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70381c19-a073-41d0-8f0b-08c5e68fca7c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7f19e47d-04ea-4596-a45a-a42e0fd28eea</t>
         </is>
       </c>
     </row>
@@ -8033,15 +8033,15 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
+          <t>กรมป่าไม้</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>805</v>
+        <v>912</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบไฟฟ้า ตู้สวิตช์บอร์ด ๒๖ ท่าอากาศยาน และกรมท่าอากาศยาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>★ (สวิตช์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7f19e47d-04ea-4596-a45a-a42e0fd28eea</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fd72b9d1-6722-4578-b8e5-e2d45779204d</t>
         </is>
       </c>
     </row>
@@ -8068,15 +8068,15 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>806</v>
+        <v>1302</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 7 รายการ ศูนย์สร้างทางลำปาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าระบบประชุมทางไกล (Web Conference Video Streaming) ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ระบบประชุมทางไกล)</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f6fbb9a3-863a-430c-ab4d-c57fc8032ba8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6c4b6c7d-fa54-4634-9070-01779d28362f</t>
         </is>
       </c>
     </row>
@@ -8103,15 +8103,15 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>กรมป่าไม้</t>
+          <t>กรมโยธาธิการและผังเมือง</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>912</v>
+        <v>1507</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างงานปรับปรุงระบบดับเพลิงพิเศษอัตโนมัติ (Clean Agent Fire Suppression System) ภายในห้องคอมพิวเตอร์แม่ข่าย (Server Room) อาคาร 4 ชั้น 1 กรมโยธาธิการและผังเมือง ถนนพระราม 9 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fd72b9d1-6722-4578-b8e5-e2d45779204d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a61be7d0-de39-476c-b4f8-7a3ec47bbd62</t>
         </is>
       </c>
     </row>
@@ -8138,15 +8138,15 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>1302</v>
+        <v>1611</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าระบบประชุมทางไกล (Web Conference Video Streaming) ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการถ่ายเอกสารพร้อมเครื่องถ่ายเอกสาร กระดาษ วัสดุสิ้นเปลือง และพนักงานประจำเครื่องของสำนักงาน ป.ป.ส. ดินแดง/สำนักงาน ป.ป.ส. ทุ่งสองห้อง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -8156,12 +8156,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>★ (ระบบประชุมทางไกล)</t>
+          <t>★ (กระดาษ)</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6c4b6c7d-fa54-4634-9070-01779d28362f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=325eb565-d1b7-456f-86c5-076a6e3f94fd</t>
         </is>
       </c>
     </row>
@@ -8173,15 +8173,15 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>กรมโยธาธิการและผังเมือง</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>1507</v>
+        <v>2102</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างงานปรับปรุงระบบดับเพลิงพิเศษอัตโนมัติ (Clean Agent Fire Suppression System) ภายในห้องคอมพิวเตอร์แม่ข่าย (Server Room) อาคาร 4 ชั้น 1 กรมโยธาธิการและผังเมือง ถนนพระราม 9 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องนึ่งฆ่าเชื้อจุลินทรีย์ด้วยไอน้ำระบบอัตโนมัติ ขนาดไม่น้อยกว่า 850 ลิตร ห้องนึ่งทรงเหลี่ยมชนิด 1 ประตู โรงพยาบาลบ้านลาด ตำบลท่าช้าง อำเภอบ้านลาด จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a61be7d0-de39-476c-b4f8-7a3ec47bbd62</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4d2f3086-64b4-4e82-a4f3-6299ee3aa880</t>
         </is>
       </c>
     </row>
@@ -8208,15 +8208,15 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>1611</v>
+        <v>2102</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการถ่ายเอกสารพร้อมเครื่องถ่ายเอกสาร กระดาษ วัสดุสิ้นเปลือง และพนักงานประจำเครื่องของสำนักงาน ป.ป.ส. ดินแดง/สำนักงาน ป.ป.ส. ทุ่งสองห้อง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องล้างเครื่องมืออัลตร้าโซนิก ชนิด 3 หลุมล้าง ขนาดความจุไม่น้อยกว่า 80 ลิตร โรงพยาบาลชะอำ ตำบลชะอำ อำเภอชะอำ จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>★ (กระดาษ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=325eb565-d1b7-456f-86c5-076a6e3f94fd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b7c95cfb-63e4-43a3-9eeb-4e9c5df71f85</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องนึ่งฆ่าเชื้อจุลินทรีย์ด้วยไอน้ำระบบอัตโนมัติ ขนาดไม่น้อยกว่า 850 ลิตร ห้องนึ่งทรงเหลี่ยมชนิด 1 ประตู โรงพยาบาลบ้านลาด ตำบลท่าช้าง อำเภอบ้านลาด จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่ายกลาง (Backbone) กระทรวงสาธารณสุข ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4d2f3086-64b4-4e82-a4f3-6299ee3aa880</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3a5cafe5-5313-4cb0-ab08-4b09c244ba61</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องล้างเครื่องมืออัลตร้าโซนิก ชนิด 3 หลุมล้าง ขนาดความจุไม่น้อยกว่า 80 ลิตร โรงพยาบาลชะอำ ตำบลชะอำ อำเภอชะอำ จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนและคาร์บอนไดออกไซด์ในเลือด ของโรงพยาบาลในจังหวัดสุรินทร์ 7 แห่ง จำนวน 12 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b7c95cfb-63e4-43a3-9eeb-4e9c5df71f85</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d5f4c614-78c4-4363-a75d-31e52b8e81d7</t>
         </is>
       </c>
     </row>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่ายกลาง (Backbone) กระทรวงสาธารณสุข ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 8 เตียง ของโรงพยาบาลท่าตูม จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -8331,12 +8331,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3a5cafe5-5313-4cb0-ab08-4b09c244ba61</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=261f4b2d-359f-4fbc-9c62-4971724a772f</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนและคาร์บอนไดออกไซด์ในเลือด ของโรงพยาบาลในจังหวัดสุรินทร์ 7 แห่ง จำนวน 12 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันขนาดใหญ่ ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 6 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -8371,27 +8371,27 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d5f4c614-78c4-4363-a75d-31e52b8e81d7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9cc00102-4e57-443e-a94c-3787d155fe6b</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สำนักงานคณะกรรมการคุ้มครองผู้บริโภค</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>2102</v>
+        <v>103</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 8 เตียง ของโรงพยาบาลท่าตูม จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาเครือข่าย เครื่องคอมพิวเตอร์แม่ข่าย เครื่องคอมพิวเตอร์ อุปกรณ์คอมพิวเตอร์และห้องปฏิบัติการคอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -8401,32 +8401,32 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=261f4b2d-359f-4fbc-9c62-4971724a772f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6f8747c6-3579-4b1b-992e-7c6f55a197b3</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>2102</v>
+        <v>204</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันขนาดใหญ่ ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 6 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ประจำอาคาร งานก่อสร้างโรงเลี้ยง 400 คน (แบบ กห 08 - 7) ของ มทบ.29 ค่ายกฤษณ์สีวะรา อ.เมือง จว.ส.น. แผนงานเพิ่มเติมระหว่างปีงบประมาณ พ.ศ. 2569 ให้กับ ช.2 พัน.202 ดำเนินการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9cc00102-4e57-443e-a94c-3787d155fe6b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=daeb7717-b81c-405b-94a2-aa71f55ea8af</t>
         </is>
       </c>
     </row>
@@ -8453,17 +8453,15 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการคุ้มครองผู้บริโภค</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>0103</t>
-        </is>
+          <t>กองทัพอากาศ</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>206</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการบำรุงรักษาเครือข่าย เครื่องคอมพิวเตอร์แม่ข่าย เครื่องคอมพิวเตอร์ อุปกรณ์คอมพิวเตอร์และห้องปฏิบัติการคอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องพิมพ์สีแผ่นไวนิล จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -8473,12 +8471,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6f8747c6-3579-4b1b-992e-7c6f55a197b3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e4172805-a5ea-4e60-b1e4-787b55b54a34</t>
         </is>
       </c>
     </row>
@@ -8490,17 +8488,15 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>0204</t>
-        </is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>704</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ประจำอาคาร งานก่อสร้างโรงเลี้ยง 400 คน (แบบ กห 08 - 7) ของ มทบ.29 ค่ายกฤษณ์สีวะรา อ.เมือง จว.ส.น. แผนงานเพิ่มเติมระหว่างปีงบประมาณ พ.ศ. 2569 ให้กับ ช.2 พัน.202 ดำเนินการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน เครื่องปรับอากาศแบบแยกส่วน ชนิดแขวน ระบบ Inverter ขนาด 30,000 บีทียู จำนวน 12 เครื่อง พร้อมติดตั้ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -8510,12 +8506,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=daeb7717-b81c-405b-94a2-aa71f55ea8af</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dc7ebea2-3d95-4ced-a85f-84f2cb8e77c2</t>
         </is>
       </c>
     </row>
@@ -8527,17 +8523,15 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>กองทัพอากาศ</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>0206</t>
-        </is>
+          <t>กรมปศุสัตว์</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>706</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องพิมพ์สีแผ่นไวนิล จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์  จำนวน  5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -8547,12 +8541,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>★ (เครื่องพิมพ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e4172805-a5ea-4e60-b1e4-787b55b54a34</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a7913502-7863-4804-9095-3f717c939f36</t>
         </is>
       </c>
     </row>
@@ -8564,17 +8558,15 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>0704</t>
-        </is>
+          <t>กรมส่งเสริมการเกษตร</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>711</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน เครื่องปรับอากาศแบบแยกส่วน ชนิดแขวน ระบบ Inverter ขนาด 30,000 บีทียู จำนวน 12 เครื่อง พร้อมติดตั้ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์ สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม สำนักงานเกษตรอำเภอนาวัง ตำบลนาเหล่าอำเภอนาวัง  จังหวัดหนองบัวลำภู  จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -8584,12 +8576,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dc7ebea2-3d95-4ced-a85f-84f2cb8e77c2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1cb87987-0702-433c-8678-5f41220c5aa5</t>
         </is>
       </c>
     </row>
@@ -8601,17 +8593,15 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>กรมปศุสัตว์</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>0706</t>
-        </is>
+          <t>กรมส่งเสริมการเกษตร</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>711</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์  จำนวน  5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบ ไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 4 ล้อ แบบดับเบิ้ลแค็บ  พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม ศูนย์ส่งเสริมเทคโนโลยีการเกษตรด้านอารักขาพืช จังหวัดพิษณุโลก ตำบลอรัญญิก อำเภอเมืองพิษณุโลก จังหวัดพิษณุโลก 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -8621,12 +8611,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a7913502-7863-4804-9095-3f717c939f36</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=21728512-3d55-4336-a433-756fa816ccd6</t>
         </is>
       </c>
     </row>
@@ -8638,17 +8628,15 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเกษตร</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>0711</t>
-        </is>
+          <t>กรมการขนส่งทางบก</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>804</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์ สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม สำนักงานเกษตรอำเภอนาวัง ตำบลนาเหล่าอำเภอนาวัง  จังหวัดหนองบัวลำภู  จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและซ่อมแซมระบบคอมพิวเตอร์แม่ข่ายและอุปกรณ์ตามโครงการพัฒนาระบบฐานข้อมูลกลางเพื่อบูรณาการข้อมูลสนับสนุนการให้บริการของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -8658,12 +8646,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1cb87987-0702-433c-8678-5f41220c5aa5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1089b549-2663-46b4-8f30-3b752498b76d</t>
         </is>
       </c>
     </row>
@@ -8675,17 +8663,15 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเกษตร</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>0711</t>
-        </is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>806</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบ ไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 4 ล้อ แบบดับเบิ้ลแค็บ  พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม ศูนย์ส่งเสริมเทคโนโลยีการเกษตรด้านอารักขาพืช จังหวัดพิษณุโลก ตำบลอรัญญิก อำเภอเมืองพิษณุโลก จังหวัดพิษณุโลก 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 7 รายการ ศูนย์สร้างทางลำปาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -8695,12 +8681,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=21728512-3d55-4336-a433-756fa816ccd6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=74dbade6-07ca-4df1-9aaa-c33e529e04b5</t>
         </is>
       </c>
     </row>
@@ -8712,17 +8698,15 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>0804</t>
-        </is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>806</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและซ่อมแซมระบบคอมพิวเตอร์แม่ข่ายและอุปกรณ์ตามโครงการพัฒนาระบบฐานข้อมูลกลางเพื่อบูรณาการข้อมูลสนับสนุนการให้บริการของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -8732,12 +8716,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1089b549-2663-46b4-8f30-3b752498b76d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=486fc308-1dd1-40ac-9b5f-16595e40c39d</t>
         </is>
       </c>
     </row>
@@ -8752,14 +8736,12 @@
           <t>กรมทางหลวง</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>0806</t>
-        </is>
+      <c r="C238" t="n">
+        <v>806</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 7 รายการ ศูนย์สร้างทางลำปาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องสำรองไฟฟ้า ขนาด 2 kVA จำนวน 138 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -8769,12 +8751,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (เครื่องสำรองไฟฟ้า, เครื่องสำรองไฟ)</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=74dbade6-07ca-4df1-9aaa-c33e529e04b5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=66aa18c1-0eb7-4c9c-bc97-eb6c9f84ea61</t>
         </is>
       </c>
     </row>
@@ -8786,17 +8768,15 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>0806</t>
-        </is>
+          <t>กรมอุตุนิยมวิทยา</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>1104</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาเครื่องสำรองไฟฟ้าต่อเนื่อง (UPS) และเครื่องกำเนิดไฟฟ้า (Generator) ประจำปีงบประมาณ พ.ศ.๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -8806,12 +8786,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (เครื่องสำรองไฟฟ้า, เครื่องสำรองไฟ)</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=486fc308-1dd1-40ac-9b5f-16595e40c39d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b04b2aed-150c-4a6a-9fe6-de4abe606304</t>
         </is>
       </c>
     </row>
@@ -8823,17 +8803,15 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>0806</t>
-        </is>
+          <t>กรมเจรจาการค้าระหว่างประเทศ</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>1306</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องสำรองไฟฟ้า ขนาด 2 kVA จำนวน 138 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการปรับปรุงระบบสายสัญญาณเครือข่าย ระบบไฟฟ้า และระบบโทรศัพท์พร้อมอุปกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -8843,12 +8821,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>★ (เครื่องสำรองไฟฟ้า, เครื่องสำรองไฟ)</t>
+          <t>★ (สายสัญญาณ)</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=66aa18c1-0eb7-4c9c-bc97-eb6c9f84ea61</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bac0b85b-275a-4ed6-a580-b3e8bfeb237f</t>
         </is>
       </c>
     </row>
@@ -8860,17 +8838,15 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>กรมอุตุนิยมวิทยา</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>1104</t>
-        </is>
+          <t>กรมส่งเสริมการค้าระหว่างประเทศ</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>1309</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาเครื่องสำรองไฟฟ้าต่อเนื่อง (UPS) และเครื่องกำเนิดไฟฟ้า (Generator) ประจำปีงบประมาณ พ.ศ.๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาระบบคอมพิวเตอร์และระบบเครือข่ายพร้อมอุปกรณ์ ปี ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -8880,12 +8856,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>★ (เครื่องสำรองไฟฟ้า, เครื่องสำรองไฟ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b04b2aed-150c-4a6a-9fe6-de4abe606304</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f059ad38-40c4-42cf-9270-e3def8289626</t>
         </is>
       </c>
     </row>
@@ -8897,17 +8873,15 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>กรมเจรจาการค้าระหว่างประเทศ</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>1306</t>
-        </is>
+          <t>กรมการปกครอง</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>1503</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการปรับปรุงระบบสายสัญญาณเครือข่าย ระบบไฟฟ้า และระบบโทรศัพท์พร้อมอุปกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อวัสดุสำหรับเครื่องพิมพ์คอมพิวเตอร์เพื่อสนับสนุนการดำเนินงานในระบบสารสนเทศทรัพยากรบุคคลระดับกรม (DPIS) ประจำปีงบประมาณ  พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -8917,12 +8891,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>★ (สายสัญญาณ)</t>
+          <t>★ (คอมพิวเตอร์, เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bac0b85b-275a-4ed6-a580-b3e8bfeb237f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ec8d68fe-3f09-45d1-a6c2-b10acc4b8aff</t>
         </is>
       </c>
     </row>
@@ -8934,17 +8908,15 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการค้าระหว่างประเทศ</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>1309</t>
-        </is>
+          <t>กรมการศาสนา</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>1803</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการบำรุงรักษาระบบคอมพิวเตอร์และระบบเครือข่ายพร้อมอุปกรณ์ ปี ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อหมึกเครื่องพิมพ์ (ครั้งที่ 3) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -8954,12 +8926,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (หมึกเครื่องพิมพ์, เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f059ad38-40c4-42cf-9270-e3def8289626</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cad3c999-2a59-4f98-9a16-5cd0e9b965e5</t>
         </is>
       </c>
     </row>
@@ -8971,17 +8943,15 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>กรมการปกครอง</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>1503</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>2102</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อวัสดุสำหรับเครื่องพิมพ์คอมพิวเตอร์เพื่อสนับสนุนการดำเนินงานในระบบสารสนเทศทรัพยากรบุคคลระดับกรม (DPIS) ประจำปีงบประมาณ  พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ กล้องจุลทรรศน์ตรวจตาชนิดลำแสงแคบพร้อมระบบเก็บภาพดิจิตอล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -8991,12 +8961,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, เครื่องพิมพ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ec8d68fe-3f09-45d1-a6c2-b10acc4b8aff</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b7dc6e3c-c6d3-4740-8dfd-746b3c47ce99</t>
         </is>
       </c>
     </row>
@@ -9008,17 +8978,15 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>กรมการศาสนา</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>2102</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อหมึกเครื่องพิมพ์ (ครั้งที่ 3) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดใหญ่ ของโรงพยาบาลในจังหวัดสุรินทร์ 2 แห่ง จำนวน 7 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -9028,12 +8996,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>★ (หมึกเครื่องพิมพ์, เครื่องพิมพ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cad3c999-2a59-4f98-9a16-5cd0e9b965e5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9e482ce2-8b0c-4125-ac7c-be9fb421af4d</t>
         </is>
       </c>
     </row>
@@ -9048,14 +9016,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C246" t="n">
+        <v>2102</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ กล้องจุลทรรศน์ตรวจตาชนิดลำแสงแคบพร้อมระบบเก็บภาพดิจิตอล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงแบบพกพาไม่ต้องชาร์จไฟฟ้าพร้อมระบบแพทย์ทางไกล ของโรงพยาบาลชุมชน 3 แห่ง จำนวน 4 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -9070,7 +9036,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b7dc6e3c-c6d3-4740-8dfd-746b3c47ce99</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=49ab0e04-32b5-4441-9d77-b629429b1571</t>
         </is>
       </c>
     </row>
@@ -9085,14 +9051,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C247" t="n">
+        <v>2102</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดใหญ่ ของโรงพยาบาลในจังหวัดสุรินทร์ 2 แห่ง จำนวน 7 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ เครื่องตรวจวิเคราะห์แยกชั้นจอประสาทตาชนิดถ่ายภาพจอประสาทตา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -9107,7 +9071,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9e482ce2-8b0c-4125-ac7c-be9fb421af4d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=165b7f39-161c-4e36-abf9-9ab28afdef12</t>
         </is>
       </c>
     </row>
@@ -9122,14 +9086,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C248" t="n">
+        <v>2102</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงแบบพกพาไม่ต้องชาร์จไฟฟ้าพร้อมระบบแพทย์ทางไกล ของโรงพยาบาลชุมชน 3 แห่ง จำนวน 4 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องรับสัญญาณภาพเอกซเรย์เป็นดิจิตอล ชนิดชุดรับภาพแฟลตพาแนลไร้สาย โรงพยาบาลแก่งกระจาน ตำบลวังจันทร์ อำเภอแก่งกระจาน จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -9144,7 +9106,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=49ab0e04-32b5-4441-9d77-b629429b1571</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=23fd4481-d3c5-4060-a810-ba6addb1516c</t>
         </is>
       </c>
     </row>
@@ -9159,14 +9121,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C249" t="n">
+        <v>2102</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ เครื่องตรวจวิเคราะห์แยกชั้นจอประสาทตาชนิดถ่ายภาพจอประสาทตา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๒ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -9181,7 +9141,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=165b7f39-161c-4e36-abf9-9ab28afdef12</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e59b2ed4-9af0-48e9-a768-f2323d942f2e</t>
         </is>
       </c>
     </row>
@@ -9196,14 +9156,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C250" t="n">
+        <v>2102</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องรับสัญญาณภาพเอกซเรย์เป็นดิจิตอล ชนิดชุดรับภาพแฟลตพาแนลไร้สาย โรงพยาบาลแก่งกระจาน ตำบลวังจันทร์ อำเภอแก่งกระจาน จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิคพร้อมภาควัดออกซิเจนและคาร์บอนไดออกไซด์ในเลือด จำนวน 25 เครื่อง งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาล ในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -9218,7 +9176,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=23fd4481-d3c5-4060-a810-ba6addb1516c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b80f6866-243b-41ee-8a1f-f04456bc5061</t>
         </is>
       </c>
     </row>
@@ -9230,17 +9188,15 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>2107</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๒ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ 11 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -9255,7 +9211,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e59b2ed4-9af0-48e9-a768-f2323d942f2e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fa5cc489-cfac-46c2-b92b-18e107acc682</t>
         </is>
       </c>
     </row>
@@ -9267,17 +9223,15 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+          <t>กรมอนามัย</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>2109</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิคพร้อมภาควัดออกซิเจนและคาร์บอนไดออกไซด์ในเลือด จำนวน 25 เครื่อง งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาล ในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -9292,7 +9246,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b80f6866-243b-41ee-8a1f-f04456bc5061</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=eada32a9-3333-40e2-ad51-54e8d12647cf</t>
         </is>
       </c>
     </row>
@@ -9304,17 +9258,15 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>กรมสนับสนุนบริการสุขภาพ</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>2107</t>
-        </is>
+          <t>สำนักงานพระพุทธศาสนาแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>2503</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ 11 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน ๑๒ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -9324,34 +9276,34 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fa5cc489-cfac-46c2-b92b-18e107acc682</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=54340df1-ec2b-4471-bb8f-6779c938e36b</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>กรมอนามัย</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>0204</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ประจำอาคาร จำนวน 14 รายการ เพิื่อใช้ในงานปรับปรุงอาคารของ กรมทหารม้าที่ 1 รักษาพระองค์ (กองร้อยสนับสนุนส่วนหน้า 1 กองพันซ่อมบำรุง กรมสนับสนุนที่ 12 ) เป็น โรงเรียนหน่วยเฉพาะกิจทหารมหาดเล็กรักษาพระองค์ ส่วนที่ 2 เป็นแผนงานเพิ่มเติมระหว่างปีงบประมาณ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -9366,29 +9318,29 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=eada32a9-3333-40e2-ad51-54e8d12647cf</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dca076ec-64c4-4fee-9ef2-8a6665ae36fb</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>สำนักงานพระพุทธศาสนาแห่งชาติ</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>0204</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน ๑๒ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ประจำอาคาร จำนวน 2 รายการ เพื่อใช้ในงานซ่อมแซมอาคารแหล่งสมาคมนายทหาร หมายเลข 144/30 ของ  กรมทหารปืนใหญ่ที่ 2 รักษาพระองค์ เป็นแผนงานเพิ่มเติมระหว่างปีงบประมาณ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -9398,12 +9350,715 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=54340df1-ec2b-4471-bb8f-6779c938e36b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1c52e71e-02d3-4d1f-bea4-a37dea913a20</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>กรมบัญชีกลาง</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>0304</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างทำความสะอาดอาคารศูนย์คอมพิวเตอร์หลักของกรมบัญชีกลาง (Data Center) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=27271442-a270-4c56-a150-8d5f8833fed3</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>กรมศุลกากร</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>0305</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อเครื่องปรับอากาศแบบแยกส่วน ติดผนัง ขนาด 18000 บีทียู จำนวน 24 เครื่อง และขนาด 12000 บีทียู จำนวน 24 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>★ (เครื่องปรับอากาศ)</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=38f0f8e6-37c7-4c1b-85f7-816a83796f90</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>กรมชลประทาน</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>0703</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างจัดหาและติดตั้งเครื่องสูบน้ำชนิดหอยโข่งแบบ Horizontal Split Case ขับด้วยมอเตอร์ไฟฟ้าอัตราสูบน้ำ ๐.๒๐ ลบ.ม./วินาที ระยะยกน้ำไม่น้อยกว่า ๔๕ เมตร และอื่นๆ รวม ๔ รายการ  สำหรับงานสถานีสูบน้ำด้วยไฟฟ้าพร้อมระบบส่งน้ำ บ้านสุขสำราญ ตำบลเหล่าต่างคำ อำเภอโพนพิสัย จังหวัดหนองคาย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>★ (มอเตอร์)</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=824576ac-9b6f-4dcc-af9a-f70ac3b918df</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>กรมการข้าว</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>0718</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การเกษตร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=144b5b77-0cf7-4926-847e-f0fd1bd8f4b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>กรมท่าอากาศยาน</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบงานสารสนเทศ ระบบเครือข่าย และบริการแก้ไขคอมพิวเตอร์และอุปกรณ์ต่อพ่วง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f9ae0aa5-414d-4a63-88c4-8cc52f83f6ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>กรมทางหลวงชนบท</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>0807</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องพิมพ์ Tag Thermal Printer จำนวน 2 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>★ (เครื่องพิมพ์)</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=754696e0-bbea-44e1-9a55-42fce741c6ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>กรมพัฒนาพลังงานทดแทนและอนุรักษ์พลังงาน</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>1205</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์ อุปกรณ์เครือข่ายและอุปกรณ์หน่วยความจำสำรองสำหรับระบบฐานข้อมูล  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, หน่วยความจำ, อุปกรณ์เครือข่าย)</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6b70ca7e-b8a0-4edd-a187-b48e924a78fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>กรมการปกครอง</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อวัสดุผงหมึกและดรัมสำหรับเครื่องพิมพ์คอมพิวเตอร์ จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>★ (ดรัม, คอมพิวเตอร์, เครื่องพิมพ์)</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ce5f2a5e-58b0-4355-b3f5-66c43c2247d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>กรมสอบสวนคดีพิเศษ</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>1608</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องคอมพิวเตอร์ประสิทธิภาพสูงสำหรับประมวลผลความสัมพันธ์ทางธุรกรรมและวิเคราะห์เส้นทางการเงินของคดีพิเศษและเรื่องสืบสวน กรมสอบสวนคดีพิเศษ  แขวงทุ่งสองห้อง เขตหลักสี่ กรุงเทพมหานคร 3 ชุด ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cd272b14-6e4a-4165-9eab-d4725c6ca271</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>สำนักงานประกันสังคม</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>1706</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อวัสดุคอมพิวเตอร์ จำนวน ๑ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a2ef415e-d086-45a2-854c-add8955d6fdb</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตาม   การทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดใหญ่ จำนวน 12 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ.2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5a6e7a1-9557-4e6f-8ecc-2de9fdd94405</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>2107</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ  จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fdb52cbf-ad05-423e-b1d8-e2f17eae5c8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>สำนักงานตำรวจแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>2507</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดหาคอมพิวเตอร์ (Notebook) สำหรับนักเรียนนายร้อยตำรวจรุ่นที่ 84 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c5ba14d7-29e1-4cb6-a64d-e89688b4e1f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>สำนักงานอัยการสูงสุด</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>2509</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=caeb26b1-ae0a-40d1-878c-18926a5cd2cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามการทุจริตแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>2605</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์พกพาแบบหน้าจอสัมผัส จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, คอมพิวเตอร์พกพา)</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=380be6fa-be50-4cc9-a85d-d4912f73145e</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>องค์การบริหารส่วนจังหวัดระยอง</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>2210101</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 2 รายการ ดังนี้ (1) รถยนต์โดยสารปรับอากาศ ไม่น้อยกว่า 22 ที่นั่ง แบบขับเคลื่อนด้วยระบบไฟฟ้า จำนวน 2 คัน  (2) รถยนต์โดยสารปรับอากาศ ไม่น้อยกว่า 40 ที่นั่ง แบบขับเคลื่อนด้วยระบบไฟฟ้า จำนวน 2 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=56da4e4f-a0c5-43d9-b499-ef666d60c6ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>มหาวิทยาลัยเชียงใหม่</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>1450100400</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=37e13d96-615f-47ec-98fa-80e208e1c3cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>มหาวิทยาลัยเชียงใหม่</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>1450100400</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อรายการครุภัณฑ์ระบบบันไดเลื่อน จำนวน 2 รายการ (ตามรายละเอียดแนบท้าย) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0552eafd-ca4e-4f42-b20b-de0194dda26f</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>มหาวิทยาลัยเชียงใหม่</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>1450100400</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อรายการครุภัณฑ์ลิฟต์ จำนวน 2 รายการ (ตามรายละเอียดแนบท้าย) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ccd9e657-8e19-4067-9762-ca2a3da4e3af</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202609.xlsx
+++ b/Backup/eGP_Monthly_Main_202609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G274"/>
+  <dimension ref="A1:G295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9296,10 +9296,8 @@
           <t>กองทัพบก</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>0204</t>
-        </is>
+      <c r="C254" t="n">
+        <v>204</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -9333,10 +9331,8 @@
           <t>กองทัพบก</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>0204</t>
-        </is>
+      <c r="C255" t="n">
+        <v>204</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -9370,10 +9366,8 @@
           <t>กรมบัญชีกลาง</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>0304</t>
-        </is>
+      <c r="C256" t="n">
+        <v>304</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -9407,10 +9401,8 @@
           <t>กรมศุลกากร</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>0305</t>
-        </is>
+      <c r="C257" t="n">
+        <v>305</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -9444,10 +9436,8 @@
           <t>กรมชลประทาน</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>0703</t>
-        </is>
+      <c r="C258" t="n">
+        <v>703</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -9481,10 +9471,8 @@
           <t>กรมการข้าว</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>0718</t>
-        </is>
+      <c r="C259" t="n">
+        <v>718</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -9518,10 +9506,8 @@
           <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
+      <c r="C260" t="n">
+        <v>805</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -9555,10 +9541,8 @@
           <t>กรมทางหลวงชนบท</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>0807</t>
-        </is>
+      <c r="C261" t="n">
+        <v>807</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -9592,10 +9576,8 @@
           <t>กรมพัฒนาพลังงานทดแทนและอนุรักษ์พลังงาน</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>1205</t>
-        </is>
+      <c r="C262" t="n">
+        <v>1205</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -9629,10 +9611,8 @@
           <t>กรมการปกครอง</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>1503</t>
-        </is>
+      <c r="C263" t="n">
+        <v>1503</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -9666,10 +9646,8 @@
           <t>กรมสอบสวนคดีพิเศษ</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>1608</t>
-        </is>
+      <c r="C264" t="n">
+        <v>1608</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -9703,10 +9681,8 @@
           <t>สำนักงานประกันสังคม</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>1706</t>
-        </is>
+      <c r="C265" t="n">
+        <v>1706</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -9740,10 +9716,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C266" t="n">
+        <v>2102</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -9777,10 +9751,8 @@
           <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>2107</t>
-        </is>
+      <c r="C267" t="n">
+        <v>2107</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -9814,10 +9786,8 @@
           <t>สำนักงานตำรวจแห่งชาติ</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>2507</t>
-        </is>
+      <c r="C268" t="n">
+        <v>2507</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -9851,10 +9821,8 @@
           <t>สำนักงานอัยการสูงสุด</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>2509</t>
-        </is>
+      <c r="C269" t="n">
+        <v>2509</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -9888,10 +9856,8 @@
           <t>สำนักงานคณะกรรมการป้องกันและปราบปรามการทุจริตแห่งชาติ</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>2605</t>
-        </is>
+      <c r="C270" t="n">
+        <v>2605</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -9925,10 +9891,8 @@
           <t>องค์การบริหารส่วนจังหวัดระยอง</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>2210101</t>
-        </is>
+      <c r="C271" t="n">
+        <v>2210101</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -9962,10 +9926,8 @@
           <t>มหาวิทยาลัยเชียงใหม่</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>1450100400</t>
-        </is>
+      <c r="C272" t="n">
+        <v>1450100400</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -9999,10 +9961,8 @@
           <t>มหาวิทยาลัยเชียงใหม่</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>1450100400</t>
-        </is>
+      <c r="C273" t="n">
+        <v>1450100400</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -10036,10 +9996,8 @@
           <t>มหาวิทยาลัยเชียงใหม่</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>1450100400</t>
-        </is>
+      <c r="C274" t="n">
+        <v>1450100400</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -10059,6 +10017,783 @@
       <c r="G274" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ccd9e657-8e19-4067-9762-ca2a3da4e3af</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>กองอำนวยการรักษาความมั่นคงภายใน</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>0119</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อวัสดุสำนักงาน ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ สนับสนุน นขต.กอ.รมน. (ส่วนกลาง) ครั้งที่ ๒        ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>★ (วัสดุสำนักงาน)</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=245d59e4-9af3-49a2-b319-a01e5d97af03</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>กองทัพบก</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>0204</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อระบบคอมพิวเตอร์และอุปกรณ์ เพื่อสนับสนุนการใช้งานข่าวกรอง ฝขว.ศปก.ทบ. จำนวน ๑๘ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=500e03b5-e6b1-4ade-b4e0-75cee602b358</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>กองทัพเรือ</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>0205</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์เครื่องช่วยการศึกษา สาย ยศ.ทร. ในการปรับปรุงอาคาร กพร.ทร.แห่งใหม่ (อาคาร บก.พธ.ทร.เดิม) จำนวน ๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ee6ef62-218a-4804-b810-005dc5140bcf</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>กองบัญชาการกองทัพไทย</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างผลิตครุภัณฑ์งานบ้านงานครัว พร้อมติดตั้ง ณ ครัวห้องอาหาร ๖/๑ และ ๖/๒ อาคาร ๑ บก.ทท. งบประมาณเพิ่มเติมระหว่างปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=78cb42b4-9ab9-4e73-b45c-e4dff9b52cfd</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>กองบัญชาการกองทัพไทย</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์งานบ้านงานครัว พร้อมติดตั้ง ณ ครัวห้องอาหาร 6/1 และ 6/2 อาคาร 1 บก.ทท. ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b75a499d-7f24-4c81-8f7c-efa6f5c08c11</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>กรมบัญชีกลาง</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>0304</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์คอมพิวเตอร์สำหรับห้องประชุม 4 (ห้องปฏิบัติการคอมพิวเตอร์) อาคาร 9 ชั้น 7 กรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b3a0480b-6840-48c0-aaba-8b41474df7ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>กรมสรรพากร</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>0307</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภท รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2f4faa45-b32a-4d9e-b08c-b82d5884c153</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงการพัฒนาสังคมและความมั่นคงของมนุษย์</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>0602</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาและเพิ่มประสิทธิภาพระบบสมุดพกครอบครัวอิเล็กทรอนิกส์ (MSO-Logbook) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>★ (สมุด)</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1026aa3b-bb28-4576-aadf-d4cf4a678716</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>0704</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี. หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บพร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a73013cc-9e52-49f3-b910-4e936275bfe1</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องตรวจสมรรถภาพปอดด้วยเครื่องคอมพิวเตอร์ จำนวน ๓ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=10b04086-63b0-4d42-95a0-904c88c6e41f</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องให้การรักษาอาการปวดและกระตุ้นเซลล์ประสาทส่วนปลายด้วยสนามแม่เหล็กไฟฟ้า (PMS) สำหรับโรงพยาบาลกงไกรลาศ จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4a641a15-b74d-402f-ab9c-60aa9fb564a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องเอกซเรย์ทั่วไปขนาดไม่น้อยกว่า ๑,๐๐๐ mA. แบบแขวนเพดาน สำหรับโรงพยาบาลศรีนคร จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a37d5071-0a7d-4d2f-84fe-d0f774026ac5</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูง ชนิด 2 หัวตรวจ สำหรับโรงพยาบาลทุ่งเสลี่ยม จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9aa030b2-096a-4e59-a881-6f2d1737ed5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องตรวจอวัยวะภายในด้วยเครื่องเสียงความถี่สูงระดับความคมชัดสูง ๓ หัวตรวจ ชนิดเคลื่อนย้ายได้ สำหรับโรงพยาบาลบ้านด่านลานหอย จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afe2fdf2-3a41-4668-9d7c-c5718e064adc</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องให้การรักษาทางกายภาพด้วยคลื่นแม่เหล็กไฟฟ้า  สำหรับโรงพยาบาลศรีสัชนาลัย จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1eeea1f2-b27e-42f8-b37f-8cd9d17e4bb2</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนในเลือด ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 5 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a54472bd-463e-4919-a81a-3790d34b7b27</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องผลิตออกซิเจน ขนาด 10 ลิตร จำนวน 39 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย-กัมพูชา ปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1bc9002a-e6eb-4764-add9-7faccb225729</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ รายการเตียงผ่าตัดศัลยกรรมออร์โธปิดิกส์ จำนวน ๒ เตียง สำหรับโรงพยาบาลลับแลและโรงพยาบาลพิชัย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=30fcc177-cd34-422d-af09-c8aa1f9cb406</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างปรับปรุงสายสัญญาณอินเทอร์เน็ตอาคาร 1 และสายไฟฟ้าอาคาร 9 สำนักงานปลัดกระทรวงสาธารณสุข ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>★ (สายสัญญาณ)</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afd11c75-a6db-43e5-a0f3-035fadd64936</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องตรวจสมรรถภาพปอดด้วยเครื่องคอมพิวเตอร์ จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=de38cd7a-4053-4ddd-a509-d16c262cf02a</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>กรมอนามัย</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>2109</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ทางการแพทย์ เครื่องวิเคราะห์องค์ประกอบร่างกายแบบแยกส่วนของโรงพยาบาล ส่งเสริมสุขภาพ ศูนย์อนามัยที่ ๖ ชลบุรี ปีงบประมาณ พ.ศ. ๒๕๗๐ จำนวน ๑ รายการ ( จำนวน ๒ เครื่อง) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=adb22b5a-03b6-4872-8f4a-1ba04569341a</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202609.xlsx
+++ b/Backup/eGP_Monthly_Main_202609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G295"/>
+  <dimension ref="A1:G306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี. หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บพร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องปรับอากาศแบบแยกส่วน (ราคารวมค่าติดตั้ง) แบบตั้งพื้นหรือแบบแขวน(ระบบ Inverter) ขนาดไม่ต่ำกว่า 36,000 บีทียู จำนวน 13 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b694aef3-f630-4422-a7fe-e31adb551c45</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=08075ad1-9390-4520-9d46-f5c2637228e2</t>
         </is>
       </c>
     </row>
@@ -4953,15 +4953,15 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมส่งเสริมสหกรณ์</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องปรับอากาศแบบแยกส่วน (ราคารวมค่าติดตั้ง) แบบตั้งพื้นหรือแบบแขวน(ระบบ Inverter) ขนาดไม่ต่ำกว่า 36,000 บีทียู จำนวน 13 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=08075ad1-9390-4520-9d46-f5c2637228e2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=282d8226-b5a6-422f-ad5a-96682acbb042</t>
         </is>
       </c>
     </row>
@@ -4988,15 +4988,15 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมสหกรณ์</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>712</v>
+        <v>806</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องตรวจวัดปริมาณแอลกอฮอล์ จำนวน 10 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (แอลกอฮอล์)</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=282d8226-b5a6-422f-ad5a-96682acbb042</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=152668c9-b054-48b8-9423-57975423ef48</t>
         </is>
       </c>
     </row>
@@ -5023,15 +5023,15 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>กรมการเปลี่ยนแปลงสภาพภูมิอากาศและสิ่งแวดล้อม</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>806</v>
+        <v>908</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องตรวจวัดปริมาณแอลกอฮอล์ จำนวน 10 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาอุปกรณ์ห้อง Data center และเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>★ (แอลกอฮอล์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=152668c9-b054-48b8-9423-57975423ef48</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3fa0cd84-f2db-47df-b581-c3555885f305</t>
         </is>
       </c>
     </row>
@@ -5058,15 +5058,15 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>กรมการเปลี่ยนแปลงสภาพภูมิอากาศและสิ่งแวดล้อม</t>
+          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>908</v>
+        <v>1202</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาอุปกรณ์ห้อง Data center และเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์เครือข่ายและอุปกรณ์คอมพิวเตอร์แม่ข่าย และอุปกรณ์สำรองข้อมูล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3fa0cd84-f2db-47df-b581-c3555885f305</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=86fe9b9f-c1ba-4f83-8b12-70dbc5d76baa</t>
         </is>
       </c>
     </row>
@@ -5093,15 +5093,15 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1202</v>
+        <v>1302</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์เครือข่ายและอุปกรณ์คอมพิวเตอร์แม่ข่าย และอุปกรณ์สำรองข้อมูล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์สำหรับงานจดทะเบียนและตรวจสอบธุรกิจผิดกฎหมาย กลุ่มทะเบียนธุรกิจและอำนวยความสะดวกทางการค้าของสำนักงานพาณิชย์จังหวัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=86fe9b9f-c1ba-4f83-8b12-70dbc5d76baa</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=06246921-2a22-4f4d-822b-d5abae1c7c8c</t>
         </is>
       </c>
     </row>
@@ -5128,15 +5128,15 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+          <t>กรมสอบสวนคดีพิเศษ</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1302</v>
+        <v>1608</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์สำหรับงานจดทะเบียนและตรวจสอบธุรกิจผิดกฎหมาย กลุ่มทะเบียนธุรกิจและอำนวยความสะดวกทางการค้าของสำนักงานพาณิชย์จังหวัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าเช่าใช้บริการสายสัญญาณเชื่อมโยงเครือข่ายอินเตอร์เน็ตพร้อมระบบ Internet Data Center ประจำปีงบประมาณ พ.ศ. 2570 (เดือนตุลาคม 2569  เดือนกันยายน 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (สายสัญญาณ)</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=06246921-2a22-4f4d-822b-d5abae1c7c8c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f0c10124-df0c-410d-961c-bb4afe1ea16a</t>
         </is>
       </c>
     </row>
@@ -5163,15 +5163,15 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>กรมสอบสวนคดีพิเศษ</t>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าเช่าใช้บริการสายสัญญาณเชื่อมโยงเครือข่ายอินเตอร์เน็ตพร้อมระบบ Internet Data Center ประจำปีงบประมาณ พ.ศ. 2570 (เดือนตุลาคม 2569  เดือนกันยายน 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบประชุมทางไกลผ่านจอภาพ (Video Conference)  ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>★ (สายสัญญาณ)</t>
+          <t>★ (จอภาพ, ระบบประชุมทางไกล)</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f0c10124-df0c-410d-961c-bb4afe1ea16a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bb2e1625-bd6e-49b0-bf5e-6f3975c796e5</t>
         </is>
       </c>
     </row>
@@ -5198,15 +5198,15 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1611</v>
+        <v>2102</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบประชุมทางไกลผ่านจอภาพ (Video Conference)  ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันขนาดกลาง โรงพยาบาลเขาย้อย ตำบลเขาย้อย อำเภอเขาย้อย จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>★ (จอภาพ, ระบบประชุมทางไกล)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bb2e1625-bd6e-49b0-bf5e-6f3975c796e5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4d438ead-6d3b-40c3-8e25-0c855ca2699d</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันขนาดกลาง โรงพยาบาลเขาย้อย ตำบลเขาย้อย อำเภอเขาย้อย จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง โรงพยาบาลหนองหญ้าปล้อง ตำบลหนองหญ้าปล้อง อำเภอหนองหญ้าปล้อง จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4d438ead-6d3b-40c3-8e25-0c855ca2699d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=38179365-12e6-43e5-ac4b-973f7d7d62c9</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง โรงพยาบาลหนองหญ้าปล้อง ตำบลหนองหญ้าปล้อง อำเภอหนองหญ้าปล้อง จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดัน ขนาดใหญ่ จำนวน 2 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=38179365-12e6-43e5-ac4b-973f7d7d62c9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2c8651ab-6342-4cf7-b1d4-44acb01ef167</t>
         </is>
       </c>
     </row>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดัน ขนาดใหญ่ จำนวน 2 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดเล็ก ของโรงพยาบาลชุมชน 2 แห่ง จำนวน 6 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2c8651ab-6342-4cf7-b1d4-44acb01ef167</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=092dea18-169e-423d-bdf4-cbb905df5ef4</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดเล็ก ของโรงพยาบาลชุมชน 2 แห่ง จำนวน 6 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องเอกซเรย์เคลื่อนที่ขนาดไม่น้อยกว่า 300 mA.ขับเคลื่อนด้วยมอเตอร์ไฟฟ้า ของโรงพยาบาลในจังหวัดสุรินทร์ 3 แห่ง จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์, มอเตอร์)</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=092dea18-169e-423d-bdf4-cbb905df5ef4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=587ceaac-9b51-4f53-a40b-ba6307295dbc</t>
         </is>
       </c>
     </row>
@@ -5373,15 +5373,15 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมการแพทย์แผนไทยและการแพทย์ทางเลือก</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>2102</v>
+        <v>2105</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องเอกซเรย์เคลื่อนที่ขนาดไม่น้อยกว่า 300 mA.ขับเคลื่อนด้วยมอเตอร์ไฟฟ้า ของโรงพยาบาลในจังหวัดสุรินทร์ 3 แห่ง จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างบำรุงรักษาและซ่อมแซมแก้ไขปัญหาเครื่องคอมพิวเตอร์แม่ข่ายและอุปกรณ์ระบบเครือข่าย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -5391,12 +5391,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์, มอเตอร์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=587ceaac-9b51-4f53-a40b-ba6307295dbc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a18ab514-a7bf-42a3-be34-78ab2073afdd</t>
         </is>
       </c>
     </row>
@@ -5408,15 +5408,15 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>กรมการแพทย์แผนไทยและการแพทย์ทางเลือก</t>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างบำรุงรักษาและซ่อมแซมแก้ไขปัญหาเครื่องคอมพิวเตอร์แม่ข่ายและอุปกรณ์ระบบเครือข่าย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน ๙ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a18ab514-a7bf-42a3-be34-78ab2073afdd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70e80b61-ece5-4761-bcba-cb1ce4f2a872</t>
         </is>
       </c>
     </row>
@@ -5443,15 +5443,15 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>กรมวิทยาศาสตร์การแพทย์</t>
+          <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>2106</v>
+        <v>2117</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน ๙ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อึครุภัณฑ์สำนักงาน รายการเครื่องปรับอากาศและพัดลม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ, พัดลม)</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70e80b61-ece5-4761-bcba-cb1ce4f2a872</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8cf26d57-cf1b-4ebf-8134-fcf45b7f7c54</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อึครุภัณฑ์สำนักงาน รายการเครื่องปรับอากาศและพัดลม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง (รถยนต์บรรทุกโดยสาร 6 ล้อ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5496,32 +5496,32 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ, พัดลม)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8cf26d57-cf1b-4ebf-8134-fcf45b7f7c54</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=37a7653e-4e42-4513-bc7a-c74cd6a83f90</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>สถาบันเทคโนโลยีป้องกันประเทศ</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>2117</v>
+        <v>209</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง (รถยนต์บรรทุกโดยสาร 6 ล้อ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างซ่อมบำรุงตามวงรอบเครื่องปรับอากาศ อาคาร สป. (แจ้งวัฒนะ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5531,12 +5531,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=37a7653e-4e42-4513-bc7a-c74cd6a83f90</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=97592008-d14e-46f6-93ee-062a71e2e9a9</t>
         </is>
       </c>
     </row>
@@ -5548,15 +5548,15 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>สถาบันเทคโนโลยีป้องกันประเทศ</t>
+          <t>สำนักงานปลัดกระทรวงการคลัง</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>209</v>
+        <v>302</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างซ่อมบำรุงตามวงรอบเครื่องปรับอากาศ อาคาร สป. (แจ้งวัฒนะ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อการจัดซื้อหมึกพิมพ์สำหรับ GFMIS Terminal Set เพื่อใช้งานในระบบ New GFMIS Thai ของกรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (หมึกพิมพ์)</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=97592008-d14e-46f6-93ee-062a71e2e9a9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=95f4ee7d-0617-43e5-8099-6f58ee3f83c4</t>
         </is>
       </c>
     </row>
@@ -5583,15 +5583,15 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการคลัง</t>
+          <t>กรมชลประทาน</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>302</v>
+        <v>703</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อการจัดซื้อหมึกพิมพ์สำหรับ GFMIS Terminal Set เพื่อใช้งานในระบบ New GFMIS Thai ของกรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจัดหาและติดตั้งเครื่องสูบน้ำชนิดหอยโข่งแบบ Horizontal Split Case ขับด้วยมอเตอร์ไฟฟ้าอัตราสูบน้ำ ๐.๒๕ ลบ.ม. /วินาที ระยะยกน้ำไม่น้อยกว่า ๔๕ เมตร และอื่นๆ รวม ๔ รายการ  สำหรับงานสถานีสูบน้ำด้วยไฟฟ้าพร้อมระบบส่งน้ำ บ้านสุขสำราญ ตำบลเหล่าต่างคำ อำเภอโพนพิสัย จังหวัดหนองคาย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>★ (หมึกพิมพ์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=95f4ee7d-0617-43e5-8099-6f58ee3f83c4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=766b91be-9aee-491f-bc67-3378c2319ca0</t>
         </is>
       </c>
     </row>
@@ -5618,15 +5618,15 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>กรมชลประทาน</t>
+          <t>กรมประมง</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจัดหาและติดตั้งเครื่องสูบน้ำชนิดหอยโข่งแบบ Horizontal Split Case ขับด้วยมอเตอร์ไฟฟ้าอัตราสูบน้ำ ๐.๒๕ ลบ.ม. /วินาที ระยะยกน้ำไม่น้อยกว่า ๔๕ เมตร และอื่นๆ รวม ๔ รายการ  สำหรับงานสถานีสูบน้ำด้วยไฟฟ้าพร้อมระบบส่งน้ำ บ้านสุขสำราญ ตำบลเหล่าต่างคำ อำเภอโพนพิสัย จังหวัดหนองคาย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน 4 รายการ วิธีประกาศเชิญชวน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=766b91be-9aee-491f-bc67-3378c2319ca0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6af84224-9211-4bd4-b2c3-7790e12e9c3f</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน 4 รายการ วิธีประกาศเชิญชวน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน 4 รายการ  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6af84224-9211-4bd4-b2c3-7790e12e9c3f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=106fd353-637b-4b85-b19c-e5222b434807</t>
         </is>
       </c>
     </row>
@@ -5688,15 +5688,15 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>กรมประมง</t>
+          <t>สำนักงานเศรษฐกิจการเกษตร</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน 4 รายการ  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์หรือระบบสารสนเทศ (โครงการจ้างบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์เครือข่ายและเครื่องคอมพิวเตอร์แม่ข่าย ประจำปีงบประมาณ พ.ศ. 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=106fd353-637b-4b85-b19c-e5222b434807</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e3936fb8-2fe4-4ded-a393-134ec5675427</t>
         </is>
       </c>
     </row>
@@ -5723,15 +5723,15 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>สำนักงานเศรษฐกิจการเกษตร</t>
+          <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>715</v>
+        <v>804</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์หรือระบบสารสนเทศ (โครงการจ้างบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์เครือข่ายและเครื่องคอมพิวเตอร์แม่ข่าย ประจำปีงบประมาณ พ.ศ. 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์พร้อมอุปกรณ์ของระบบการคุ้มครองผู้โดยสารและ การบังคับใช้กฎหมายทั่วไทย (1584 และปรับทั่วไทย) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e3936fb8-2fe4-4ded-a393-134ec5675427</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f5c51a3c-9d4b-4662-a9c5-a560b97ab60f</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์พร้อมอุปกรณ์ของระบบการคุ้มครองผู้โดยสารและ การบังคับใช้กฎหมายทั่วไทย (1584 และปรับทั่วไทย) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างรั้ว ประตูทางเข้า - ออก ป้ายชื่อสำนักงาน และป้อมยามรักษาการณ์ สำนักงานขนส่งจังหวัดลำปาง ตำบลพระบาท อำเภอเมือง จังหวัดลำปาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ป้ายชื่อ)</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f5c51a3c-9d4b-4662-a9c5-a560b97ab60f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f104579c-ae74-4bdb-a71c-250b1777b2c9</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างรั้ว ประตูทางเข้า - ออก ป้ายชื่อสำนักงาน และป้อมยามรักษาการณ์ สำนักงานขนส่งจังหวัดลำปาง ตำบลพระบาท อำเภอเมือง จังหวัดลำปาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขเครื่องคอมพิวเตอร์พร้อมอุปกรณ์ที่ใช้ในการพัฒนาความรู้สารสนเทศ  ด้านความปลอดภัยของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>★ (ป้ายชื่อ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f104579c-ae74-4bdb-a71c-250b1777b2c9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a8c5a924-f969-4f66-a783-51c748bd5141</t>
         </is>
       </c>
     </row>
@@ -5828,15 +5828,15 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
+          <t>กรมอุตุนิยมวิทยา</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>804</v>
+        <v>1104</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขเครื่องคอมพิวเตอร์พร้อมอุปกรณ์ที่ใช้ในการพัฒนาความรู้สารสนเทศ  ด้านความปลอดภัยของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาอุปกรณ์กระจายสัญญาณหลัก (Core Switch) ประจำปีงบประมาณ พ.ศ.2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a8c5a924-f969-4f66-a783-51c748bd5141</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b6951565-26a5-4131-b672-af48d4974842</t>
         </is>
       </c>
     </row>
@@ -5863,15 +5863,15 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>กรมอุตุนิยมวิทยา</t>
+          <t>กรมที่ดิน</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1104</v>
+        <v>1505</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาอุปกรณ์กระจายสัญญาณหลัก (Core Switch) ประจำปีงบประมาณ พ.ศ.2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโต๊ะและเก้าอี้เพื่อใช้ในราชการของสำนักงานที่ดินจังหวัดพิษณุโลก และสาขา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -5881,12 +5881,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
+          <t>★ (โต๊ะ, เก้าอี้)</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b6951565-26a5-4131-b672-af48d4974842</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=06a6ae3e-1109-434c-becf-df99302f96f5</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโต๊ะและเก้าอี้เพื่อใช้ในราชการของสำนักงานที่ดินจังหวัดพิษณุโลก และสาขา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบงานและอุปกรณ์คอมพิวเตอร์ ตามโครงการพัฒนาระบบสารสนเทศที่ดิน (ระยะที่ ๒) ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>★ (โต๊ะ, เก้าอี้)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=06a6ae3e-1109-434c-becf-df99302f96f5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0e343fde-5a22-4f02-b2b3-bcf7cfd99bf2</t>
         </is>
       </c>
     </row>
@@ -5933,15 +5933,15 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>กรมที่ดิน</t>
+          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1505</v>
+        <v>1808</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบงานและอุปกรณ์คอมพิวเตอร์ ตามโครงการพัฒนาระบบสารสนเทศที่ดิน (ระยะที่ ๒) ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์การศึกษา (ห้องเรียนอัจฉริยะไฮบริด Smart Hybrid Classroom) ห้องเรียนวิชาชีพ จำนวน 1 ห้อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0e343fde-5a22-4f02-b2b3-bcf7cfd99bf2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a6ddc2c9-4ad2-4cd7-93c9-2b5e9a715cfd</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์การศึกษา (ห้องเรียนอัจฉริยะไฮบริด Smart Hybrid Classroom) ห้องเรียนวิชาชีพ จำนวน 1 ห้อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์โฆษณาแะเผยแพร่ (ระบบภาพ LED Display พร้อมติดตั้งภายนอกอาคาร) จำนวน  1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a6ddc2c9-4ad2-4cd7-93c9-2b5e9a715cfd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7b99fd52-1723-486a-a5ce-43a450641ed9</t>
         </is>
       </c>
     </row>
@@ -6003,15 +6003,15 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
+          <t>สำนักงานนวัตกรรมแห่งชาติ (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1808</v>
+        <v>1913</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์โฆษณาแะเผยแพร่ (ระบบภาพ LED Display พร้อมติดตั้งภายนอกอาคาร) จำนวน  1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างเหมาบริการบำรุงรักษาอุปกรณ์ภายในศูนย์ข้อมูลคอมพิวเตอร์(Data Center) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7b99fd52-1723-486a-a5ce-43a450641ed9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70ea1f2e-64d2-48c7-888f-f39d061663c3</t>
         </is>
       </c>
     </row>
@@ -6038,15 +6038,15 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>สำนักงานนวัตกรรมแห่งชาติ (องค์การมหาชน)</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1913</v>
+        <v>2102</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างเหมาบริการบำรุงรักษาอุปกรณ์ภายในศูนย์ข้อมูลคอมพิวเตอร์(Data Center) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70ea1f2e-64d2-48c7-888f-f39d061663c3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5dcaa2f-3e4d-49bc-9324-4c94f510ab5f</t>
         </is>
       </c>
     </row>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องควบคุมการให้สารน้ำทางหลอดเลือดดำชนิด 1 สาย ของโรงพยาบาลในจังหวัดสุรินทร์ 9 แห่ง จำนวน 66 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5dcaa2f-3e4d-49bc-9324-4c94f510ab5f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=af446873-e18e-4ed1-bd5c-bd34b74e9b76</t>
         </is>
       </c>
     </row>
@@ -6108,15 +6108,15 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมการแพทย์</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องควบคุมการให้สารน้ำทางหลอดเลือดดำชนิด 1 สาย ของโรงพยาบาลในจังหวัดสุรินทร์ 9 แห่ง จำนวน 66 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์เครื่องเสริมสร้างความแข็งแรงของกล้ามเนื้ออุ้งเชิงกราน รักษาอาการปัสสาวะเล็ด ลดอาการปวดจากกล้ามเนื้อและระบบประสาทบริเวณ อุ้งเชิงกรานและหลังด้วยคลื่นแม่เหล็กไฟฟ้า สถาบันเวชศาสตร์สมเด็จพระสังฆราชญาณสังวรเพื่อผู้สูงอายุ ตำบลตลาดขวัญ อำเภอเมือง จังหวัดนนทบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -6131,27 +6131,27 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=af446873-e18e-4ed1-bd5c-bd34b74e9b76</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=543d641e-2bab-40db-bddc-5b9d81caf16b</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>กรมการแพทย์</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>2103</v>
+        <v>204</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์เครื่องเสริมสร้างความแข็งแรงของกล้ามเนื้ออุ้งเชิงกราน รักษาอาการปัสสาวะเล็ด ลดอาการปวดจากกล้ามเนื้อและระบบประสาทบริเวณ อุ้งเชิงกรานและหลังด้วยคลื่นแม่เหล็กไฟฟ้า สถาบันเวชศาสตร์สมเด็จพระสังฆราชญาณสังวรเพื่อผู้สูงอายุ ตำบลตลาดขวัญ อำเภอเมือง จังหวัดนนทบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำหรับงานซ่อมปรับปรุงสนามกีฬาของ หน่วยบัญชาการสงครามพิเศษ เพื่อรองรับการแข่งขันกีฬา กองทัพบก ครั้งที่ 74 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=543d641e-2bab-40db-bddc-5b9d81caf16b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=91712891-37fd-4bbc-ae6c-0044106ce3a9</t>
         </is>
       </c>
     </row>
@@ -6178,15 +6178,15 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>204</v>
+        <v>704</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์สำหรับงานซ่อมปรับปรุงสนามกีฬาของ หน่วยบัญชาการสงครามพิเศษ เพื่อรองรับการแข่งขันกีฬา กองทัพบก ครั้งที่ 74 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะ รถโดยสารขนาด 12 ที่นั่ง (ดีเซล) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=91712891-37fd-4bbc-ae6c-0044106ce3a9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6d9307c6-812c-4689-9154-bd79b77edeed</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะ รถโดยสารขนาด 12 ที่นั่ง (ดีเซล) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องคอมพิวเตอร์โน๊ตบุ๊ค สำหรับงานประมวลผล พร้อมชุดโปรแกรมระบบปฏิบัติการสำหรับคอมพิวเตอร์และเครี่องคอมพิวเตอร์โน๊ตบุ๊ค แบบสิทธิการใช้งานภายในสำนักงาน ประเภทติดตั้งมาจากโรงงาน (OEM) ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย ชุดโปรแกรมจัดการสำนักงาน แบบที่ 2   ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย และชุดโปรแกรมป้องกันไวรัส จำนวน 21 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -6231,12 +6231,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, โน๊ตบุ๊ค, ระบบปฏิบัติการ, โปรแกรมป้องกันไวรัส)</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6d9307c6-812c-4689-9154-bd79b77edeed</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ac28390d-f1a5-41e3-8fed-7350ce5638bc</t>
         </is>
       </c>
     </row>
@@ -6248,15 +6248,15 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>704</v>
+        <v>805</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องคอมพิวเตอร์โน๊ตบุ๊ค สำหรับงานประมวลผล พร้อมชุดโปรแกรมระบบปฏิบัติการสำหรับคอมพิวเตอร์และเครี่องคอมพิวเตอร์โน๊ตบุ๊ค แบบสิทธิการใช้งานภายในสำนักงาน ประเภทติดตั้งมาจากโรงงาน (OEM) ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย ชุดโปรแกรมจัดการสำนักงาน แบบที่ 2   ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย และชุดโปรแกรมป้องกันไวรัส จำนวน 21 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานหัวหิน ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -6266,12 +6266,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, โน๊ตบุ๊ค, ระบบปฏิบัติการ, โปรแกรมป้องกันไวรัส)</t>
+          <t>★ (รถเข็น)</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ac28390d-f1a5-41e3-8fed-7350ce5638bc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f40b4d90-5120-4848-a5d2-b177de8a9a09</t>
         </is>
       </c>
     </row>
@@ -6283,15 +6283,15 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
+          <t>กรมพัฒนาธุรกิจการค้า</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>805</v>
+        <v>1308</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานหัวหิน ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์แม่ข่ายและอุปกรณ์รักษาความปลอดภัย ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -6301,12 +6301,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>★ (รถเข็น)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f40b4d90-5120-4848-a5d2-b177de8a9a09</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=652c12bb-908d-48aa-a87c-f244b33e9ad3</t>
         </is>
       </c>
     </row>
@@ -6318,15 +6318,15 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>กรมพัฒนาธุรกิจการค้า</t>
+          <t>กรมที่ดิน</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1308</v>
+        <v>1505</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์แม่ข่ายและอุปกรณ์รักษาความปลอดภัย ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมอุปกรณ์ รวม ๘ รายการ สำหรับใช้ในราชการกองเทคโนโลยีทำแผนที่ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=652c12bb-908d-48aa-a87c-f244b33e9ad3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c85d670f-a209-4413-8ade-5dba1d3d0298</t>
         </is>
       </c>
     </row>
@@ -6353,15 +6353,15 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>กรมที่ดิน</t>
+          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1505</v>
+        <v>1905</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมอุปกรณ์ รวม ๘ รายการ สำหรับใช้ในราชการกองเทคโนโลยีทำแผนที่ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์โครงการห้องปฏิบัติการทดสอบด้านวิศวกรรมการใช้งาน (Usability Engineering) ผลิตภัณฑ์ซอฟต์แวร์หุ่นยนต์ทางการแพทย์และเครื่องมือแพทย์ตามมาตรฐานสากล (Usability Engineering Laboratories for Software, Medical Robotics, and Medical Devices under International Standards) จํานวน ๑ ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ซอฟต์แวร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c85d670f-a209-4413-8ade-5dba1d3d0298</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0415b5bd-8794-467b-9e54-5ae4bdabae87</t>
         </is>
       </c>
     </row>
@@ -6388,15 +6388,15 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1905</v>
+        <v>2102</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์โครงการห้องปฏิบัติการทดสอบด้านวิศวกรรมการใช้งาน (Usability Engineering) ผลิตภัณฑ์ซอฟต์แวร์หุ่นยนต์ทางการแพทย์และเครื่องมือแพทย์ตามมาตรฐานสากล (Usability Engineering Laboratories for Software, Medical Robotics, and Medical Devices under International Standards) จํานวน ๑ ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องอุ่นเลือดและส่วนประกอบของเลือดชนิดไม่สัมผัสน้ำสามารถอุ่นเลือดได้ พร้อมกันไม่น้อยกว่า 3 ถุง จำนวน 4 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย -  กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>★ (ซอฟต์แวร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0415b5bd-8794-467b-9e54-5ae4bdabae87</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2157b09f-d16e-4bcf-b720-de1088bc7b0e</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องอุ่นเลือดและส่วนประกอบของเลือดชนิดไม่สัมผัสน้ำสามารถอุ่นเลือดได้ พร้อมกันไม่น้อยกว่า 3 ถุง จำนวน 4 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย -  กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องควบคุมการให้สารละลายโดยใช้กระบอกฉีด ของโรงพยาบาลในจังหวัดสุรินทร์ 5 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบลสำเภาลูน จำนวน 26 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2157b09f-d16e-4bcf-b720-de1088bc7b0e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=33f2d0df-213d-44c4-a6fa-d31b0eb2e1f6</t>
         </is>
       </c>
     </row>
@@ -6458,15 +6458,15 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>2102</v>
+        <v>2106</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องควบคุมการให้สารละลายโดยใช้กระบอกฉีด ของโรงพยาบาลในจังหวัดสุรินทร์ 5 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบลสำเภาลูน จำนวน 26 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาซ่อมแซมแก้ไขระบบเครือข่ายและเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=33f2d0df-213d-44c4-a6fa-d31b0eb2e1f6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=77d1f891-c26e-4f3d-a9e2-7ca16c4196b3</t>
         </is>
       </c>
     </row>
@@ -6493,15 +6493,15 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>กรมวิทยาศาสตร์การแพทย์</t>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาซ่อมแซมแก้ไขระบบเครือข่ายและเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=77d1f891-c26e-4f3d-a9e2-7ca16c4196b3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b600d06e-5f90-400c-80fc-24c6ae2ef280</t>
         </is>
       </c>
     </row>
@@ -6528,15 +6528,15 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>กรมสนับสนุนบริการสุขภาพ</t>
+          <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>2107</v>
+        <v>2117</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์วิทยาศาสตร์การแพทย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b600d06e-5f90-400c-80fc-24c6ae2ef280</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a3db48e8-9e8b-4535-84a6-a14f5811619b</t>
         </is>
       </c>
     </row>
@@ -6563,15 +6563,15 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>สำนักงานพระพุทธศาสนาแห่งชาติ</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>2117</v>
+        <v>2503</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์วิทยาศาสตร์การแพทย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -6581,32 +6581,32 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a3db48e8-9e8b-4535-84a6-a14f5811619b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=285cc870-c52b-429d-b866-52f939bc7fd0</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>สำนักงานพระพุทธศาสนาแห่งชาติ</t>
+          <t>กรมพัฒนาที่ดิน</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>2503</v>
+        <v>708</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจอแสดงผล LED พร้อมอุปกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -6616,12 +6616,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (จอแสดงผล)</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=285cc870-c52b-429d-b866-52f939bc7fd0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=45d8cd64-624e-4582-a8d1-3fe3d01e41b6</t>
         </is>
       </c>
     </row>
@@ -6633,15 +6633,15 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>กรมพัฒนาที่ดิน</t>
+          <t>กรมการข้าว</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจอแสดงผล LED พร้อมอุปกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องปรับอากาศ แบบแยกส่วน แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -6651,12 +6651,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>★ (จอแสดงผล)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=45d8cd64-624e-4582-a8d1-3fe3d01e41b6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2475fb18-8633-42d5-8fe6-f520615dc6f7</t>
         </is>
       </c>
     </row>
@@ -6668,15 +6668,15 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>กรมการข้าว</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>718</v>
+        <v>806</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องปรับอากาศ แบบแยกส่วน แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ และ ครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 13 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2475fb18-8633-42d5-8fe6-f520615dc6f7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0b00828b-7442-420e-85c9-ad09d2f6e16f</t>
         </is>
       </c>
     </row>
@@ -6703,15 +6703,15 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>กรมทรัพยากรน้ำบาดาล</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>806</v>
+        <v>907</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ และ ครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 13 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องสูบน้ำไฟฟ้าชนิดมอเตอร์จุ่มใต้น้ำ พร้อมอุปกรณ์ และชุดฝาปิดปากบ่อน้ำบาดาล จำนวน ๖ ชุด โครงการพัฒนาน้ำบาดาลเพื่อความมั่นคงระดับชุมชน ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ (งบเหลือจ่าย) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0b00828b-7442-420e-85c9-ad09d2f6e16f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=03ba8462-a0d1-4d13-92c2-a7ae76fed3d0</t>
         </is>
       </c>
     </row>
@@ -6738,15 +6738,15 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>กรมทรัพยากรน้ำบาดาล</t>
+          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องสูบน้ำไฟฟ้าชนิดมอเตอร์จุ่มใต้น้ำ พร้อมอุปกรณ์ และชุดฝาปิดปากบ่อน้ำบาดาล จำนวน ๖ ชุด โครงการพัฒนาน้ำบาดาลเพื่อความมั่นคงระดับชุมชน ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ (งบเหลือจ่าย) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทเรือหางยาวสำหรับการลาดตระเวนพื้นที่ทางน้ำ เพื่อเพิ่มประสิทธิภาพการปฏิบัติงานอุทยานแห่งชาติเขาแหลม จังหวัดกาญจนบุรี  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -6756,12 +6756,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=03ba8462-a0d1-4d13-92c2-a7ae76fed3d0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63f7333f-eb0c-40fa-8c06-5f683d543bce</t>
         </is>
       </c>
     </row>
@@ -6773,15 +6773,15 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
+          <t>กรมการปกครอง</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>909</v>
+        <v>1503</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทเรือหางยาวสำหรับการลาดตระเวนพื้นที่ทางน้ำ เพื่อเพิ่มประสิทธิภาพการปฏิบัติงานอุทยานแห่งชาติเขาแหลม จังหวัดกาญจนบุรี  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อวัสดุครุภัณฑ์สำนักงานที่ทำการปกครองอำเภอตาพระยา จังหวัดสระแก้ว ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63f7333f-eb0c-40fa-8c06-5f683d543bce</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=de60da4a-56f9-434f-bd1c-60d19d95f672</t>
         </is>
       </c>
     </row>
@@ -6808,15 +6808,15 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>กรมการปกครอง</t>
+          <t>กรมที่ดิน</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อวัสดุครุภัณฑ์สำนักงานที่ทำการปกครองอำเภอตาพระยา จังหวัดสระแก้ว ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์เพื่อการบริหารจัดการหน่วยงานส่วนกลาง (Hardware และ Software) ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -6826,12 +6826,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=de60da4a-56f9-434f-bd1c-60d19d95f672</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a80802ed-6d42-4b60-b93c-de21fb24e5c0</t>
         </is>
       </c>
     </row>
@@ -6843,15 +6843,15 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>กรมที่ดิน</t>
+          <t>กรมการจัดหางาน</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1505</v>
+        <v>1703</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์เพื่อการบริหารจัดการหน่วยงานส่วนกลาง (Hardware และ Software) ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ทดแทนและเพิ่มประสิทธิภาพของสำนักบริหารแรงงานต่างด้าว ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -6861,12 +6861,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a80802ed-6d42-4b60-b93c-de21fb24e5c0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f3092a7e-5bf1-488f-8f3f-6657ba0fe2fd</t>
         </is>
       </c>
     </row>
@@ -6878,15 +6878,15 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>กรมการจัดหางาน</t>
+          <t>กรมพัฒนาฝีมือแรงงาน</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ทดแทนและเพิ่มประสิทธิภาพของสำนักบริหารแรงงานต่างด้าว ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ (ระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop) ขนาด 3 เฟส 15 กิโลวัตต์ ตำบลบ่อ อำเภอขลุง จังหวัดจันทบุรี จำนวน 1 ระบบ และระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop) ขนาด 3 เฟส 20 กิโลวัตต์ ตำบลบ่อ อำเภอขลุง จังหวัดจันทบุรี จำนวน 1 ระบบ) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -6896,12 +6896,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f3092a7e-5bf1-488f-8f3f-6657ba0fe2fd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d90e4389-d0ce-48d4-b93a-03874d22d178</t>
         </is>
       </c>
     </row>
@@ -6913,15 +6913,15 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>กรมพัฒนาฝีมือแรงงาน</t>
+          <t>กรมการศาสนา</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1704</v>
+        <v>1803</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ (ระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop) ขนาด 3 เฟส 15 กิโลวัตต์ ตำบลบ่อ อำเภอขลุง จังหวัดจันทบุรี จำนวน 1 ระบบ และระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop) ขนาด 3 เฟส 20 กิโลวัตต์ ตำบลบ่อ อำเภอขลุง จังหวัดจันทบุรี จำนวน 1 ระบบ) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อหมึกเครื่องพิมพ์ (ครั้งที่ 2)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (หมึกเครื่องพิมพ์, เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d90e4389-d0ce-48d4-b93a-03874d22d178</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8ffdb256-bac2-4342-bdf6-7616e2ae5b25</t>
         </is>
       </c>
     </row>
@@ -6948,15 +6948,15 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>กรมการศาสนา</t>
+          <t>สถาบันมาตรวิทยาแห่งชาติ</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1803</v>
+        <v>1907</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อหมึกเครื่องพิมพ์ (ครั้งที่ 2)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างค่าบำรุงรักษาอุปกรณ์เครือข่ายประจำอาคาร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>★ (หมึกเครื่องพิมพ์, เครื่องพิมพ์)</t>
+          <t>★ (อุปกรณ์เครือข่าย)</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8ffdb256-bac2-4342-bdf6-7616e2ae5b25</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b698a86e-10e2-45f2-be5e-f7ec03fa0ce9</t>
         </is>
       </c>
     </row>
@@ -6983,15 +6983,15 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>สถาบันมาตรวิทยาแห่งชาติ</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1907</v>
+        <v>2102</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างค่าบำรุงรักษาอุปกรณ์เครือข่ายประจำอาคาร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการรถพยาบาลพร้อมอุปกรณ์ช่วยชีวิตชั้นสูง ของโรงพยาบาลชุมชน 4 แห่ง จำนวน 4 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -7001,12 +7001,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>★ (อุปกรณ์เครือข่าย)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b698a86e-10e2-45f2-be5e-f7ec03fa0ce9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f77b490-654b-45ac-9d8e-cc1f4f3fd4fb</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการรถพยาบาลพร้อมอุปกรณ์ช่วยชีวิตชั้นสูง ของโรงพยาบาลชุมชน 4 แห่ง จำนวน 4 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดออกซิเจนในเลือดอัตโนมัติชนิดพกพา จำนวน 39 เครื่องๆ งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f77b490-654b-45ac-9d8e-cc1f4f3fd4fb</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f13af428-4413-4d73-9542-bd582ed6e240</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดออกซิเจนในเลือดอัตโนมัติชนิดพกพา จำนวน 39 เครื่องๆ งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจคลื่นไฟฟ้าหัวใจ พร้อมเชื่อมต่อระบบแพทย์ทางไกล จำนวน 27 เครื่อง งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f13af428-4413-4d73-9542-bd582ed6e240</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9350a991-2cda-4337-b005-93d114caf75c</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจคลื่นไฟฟ้าหัวใจ พร้อมเชื่อมต่อระบบแพทย์ทางไกล จำนวน 27 เครื่อง งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการตู้เย็นเก็บเลือด ขนาดไม่น้อยกว่า 20 คิว จำนวน 4 ตู้ งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์  การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -7106,12 +7106,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์, ตู้เย็น)</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9350a991-2cda-4337-b005-93d114caf75c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=83dc4a91-4e74-465d-b378-562e91d2b662</t>
         </is>
       </c>
     </row>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการตู้เย็นเก็บเลือด ขนาดไม่น้อยกว่า 20 คิว จำนวน 4 ตู้ งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์  การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ เครื่องให้การรักษาอาการปวดและกระตุ้นเซลล์ประสาทส่วนปลายด้วยสนามแม่เหล็กไฟฟ้า(PMS) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์, ตู้เย็น)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=83dc4a91-4e74-465d-b378-562e91d2b662</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=35bbde9c-eb8e-445f-b94e-915454477995</t>
         </is>
       </c>
     </row>
@@ -7158,15 +7158,15 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>2102</v>
+        <v>2106</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ เครื่องให้การรักษาอาการปวดและกระตุ้นเซลล์ประสาทส่วนปลายด้วยสนามแม่เหล็กไฟฟ้า(PMS) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมระบบปฏิบัติการและชุดโปรแกรมจัดการสำนักงาน จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ระบบปฏิบัติการ, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=35bbde9c-eb8e-445f-b94e-915454477995</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=414ac115-ac50-4d65-a54d-d2a9e03b621b</t>
         </is>
       </c>
     </row>
@@ -7193,15 +7193,15 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>กรมวิทยาศาสตร์การแพทย์</t>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมระบบปฏิบัติการและชุดโปรแกรมจัดการสำนักงาน จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ เครื่องวิเคราะห์การทำงานตู้อบเด็ก จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -7211,32 +7211,32 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ระบบปฏิบัติการ, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=414ac115-ac50-4d65-a54d-d2a9e03b621b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9d04622a-81b1-4cfd-9a05-6c2aec6751f7</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>กรมสนับสนุนบริการสุขภาพ</t>
+          <t>กรมบัญชีกลาง</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>2107</v>
+        <v>304</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ เครื่องวิเคราะห์การทำงานตู้อบเด็ก จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาและซ่อมแซมแก้ไขเครื่องปรับอากาศ (แบบรวมอะไหล่) จำนวน 474 เครื่อง ซ่อมแซมแก้ไขระบบไฟฟ้า และระบบสุขาภิบาล อาคาร 3 อาคาร 9 อาคารใหม่ ชั้นใต้ดิน และห้องลิฟต์ กรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9d04622a-81b1-4cfd-9a05-6c2aec6751f7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=273a8add-ac17-48f1-8ff9-c94a946e8273</t>
         </is>
       </c>
     </row>
@@ -7263,15 +7263,15 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>กรมบัญชีกลาง</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>304</v>
+        <v>704</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาและซ่อมแซมแก้ไขเครื่องปรับอากาศ (แบบรวมอะไหล่) จำนวน 474 เครื่อง ซ่อมแซมแก้ไขระบบไฟฟ้า และระบบสุขาภิบาล อาคาร 3 อาคาร 9 อาคารใหม่ ชั้นใต้ดิน และห้องลิฟต์ กรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ พร้อมชุดโปรแกรมปฎิบัติงาน โปรแกรมจัดการสำนักงาน และโปรแกรมป้องกันไวรัส จำนวน 18 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -7281,12 +7281,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (คอมพิวเตอร์, โปรแกรมป้องกันไวรัส, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=273a8add-ac17-48f1-8ff9-c94a946e8273</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0511e3cd-537d-45d3-880c-de7433b1eb48</t>
         </is>
       </c>
     </row>
@@ -7298,15 +7298,15 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมประมง</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ พร้อมชุดโปรแกรมปฎิบัติงาน โปรแกรมจัดการสำนักงาน และโปรแกรมป้องกันไวรัส จำนวน 18 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อชุดจอภาพ LED พร้อมงานติดตั้งสำหรับห้องประชุมอานนท์ กรมประมง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -7316,12 +7316,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, โปรแกรมป้องกันไวรัส, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (จอภาพ)</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0511e3cd-537d-45d3-880c-de7433b1eb48</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b0679766-012d-497b-8e41-2296e1c7ba51</t>
         </is>
       </c>
     </row>
@@ -7333,15 +7333,15 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>กรมประมง</t>
+          <t>กรมปศุสัตว์</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อชุดจอภาพ LED พร้อมงานติดตั้งสำหรับห้องประชุมอานนท์ กรมประมง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>★ (จอภาพ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b0679766-012d-497b-8e41-2296e1c7ba51</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f70d294-53f0-4fd1-b9bc-ef06d20b1657</t>
         </is>
       </c>
     </row>
@@ -7368,15 +7368,15 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>กรมปศุสัตว์</t>
+          <t>สำนักงานนโยบายและแผนการขนส่งและจราจร</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>706</v>
+        <v>808</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์ของ สนข. ประจำปีงบประมาณ พ.ศ. 2570  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f70d294-53f0-4fd1-b9bc-ef06d20b1657</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=069d5584-a6b1-426d-9714-115f2fdc7025</t>
         </is>
       </c>
     </row>
@@ -7403,15 +7403,15 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>สำนักงานนโยบายและแผนการขนส่งและจราจร</t>
+          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>808</v>
+        <v>904</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์ของ สนข. ประจำปีงบประมาณ พ.ศ. 2570  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาและเพิ่มประสิทธิภาพระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรทางทะเลและชายฝั่ง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=069d5584-a6b1-426d-9714-115f2fdc7025</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f112758f-839d-4660-91b5-12181a1297d2</t>
         </is>
       </c>
     </row>
@@ -7438,15 +7438,15 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
+          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>904</v>
+        <v>1202</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการบำรุงรักษาและเพิ่มประสิทธิภาพระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรทางทะเลและชายฝั่ง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่ารถส่วนภูมิภาค รถยนต์ไฟฟ้า ประเภทแบตเตอรี่ (BEV) ขนาดความจุของแบตเตอรี่มากกว่า 50 กิโลวัตต์ชั่วโมง (kWh) และกำลังมอเตอร์ไฟฟ้าสูงสุด ไม่เกิน 150 กิโลวัตต์ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f112758f-839d-4660-91b5-12181a1297d2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=40cb45e4-0e08-48b9-a763-7a9aa44d7959</t>
         </is>
       </c>
     </row>
@@ -7473,15 +7473,15 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
+          <t>กรมการปกครอง</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1202</v>
+        <v>1503</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่ารถส่วนภูมิภาค รถยนต์ไฟฟ้า ประเภทแบตเตอรี่ (BEV) ขนาดความจุของแบตเตอรี่มากกว่า 50 กิโลวัตต์ชั่วโมง (kWh) และกำลังมอเตอร์ไฟฟ้าสูงสุด ไม่เกิน 150 กิโลวัตต์ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 5 รายการ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=40cb45e4-0e08-48b9-a763-7a9aa44d7959</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ac3547dc-0f12-4694-b5a3-e216678ce172</t>
         </is>
       </c>
     </row>
@@ -7508,15 +7508,15 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>กรมการปกครอง</t>
+          <t>กรมการศาสนา</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1503</v>
+        <v>1803</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 5 รายการ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อวัสดุสำนักงานส่วนกลาง ประจำปีงบประมาณ พ.ศ. 2569 (ครั้งที่ 2)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (วัสดุสำนักงาน)</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ac3547dc-0f12-4694-b5a3-e216678ce172</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c6f2fbd0-4267-42c4-926d-d8fc49d8a3ff</t>
         </is>
       </c>
     </row>
@@ -7543,15 +7543,15 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>กรมการศาสนา</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1803</v>
+        <v>2102</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อวัสดุสำนักงานส่วนกลาง ประจำปีงบประมาณ พ.ศ. 2569 (ครั้งที่ 2)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องผลิตออกซิเจนขนาด 5 ลิตร ของโรงพยาบาลสนม และโรงพยาบาลส่งเสริมสุขภาพตำบล 18 แห่ง จำนวน 33 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>★ (วัสดุสำนักงาน)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c6f2fbd0-4267-42c4-926d-d8fc49d8a3ff</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=655601b1-75a6-4eee-9bc7-ee3ce427abf6</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องผลิตออกซิเจนขนาด 5 ลิตร ของโรงพยาบาลสนม และโรงพยาบาลส่งเสริมสุขภาพตำบล 18 แห่ง จำนวน 33 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดความดันโลหิตชนิดอัตโนมัติ วัดความอิ่มตัวของออกซิเจนในเลือด อุณหภูมิร่างกาย พร้อมระบบเชื่อมต่อฐานข้อมูล ของโรงพยาบาลในจังหวัดสุรินทร์ 12 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบล 10 แห่ง จำนวน 50 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=655601b1-75a6-4eee-9bc7-ee3ce427abf6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=65a2753e-e63f-4be2-b228-0fe250379934</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดความดันโลหิตชนิดอัตโนมัติ วัดความอิ่มตัวของออกซิเจนในเลือด อุณหภูมิร่างกาย พร้อมระบบเชื่อมต่อฐานข้อมูล ของโรงพยาบาลในจังหวัดสุรินทร์ 12 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบล 10 แห่ง จำนวน 50 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการชุดอุปกรณ์เคลื่อนย้ายผู้ป่วยในสถานการณ์ฉุกเฉิน ของโรงพยาบาลชุมชน 8 แห่ง จำนวน 10 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=65a2753e-e63f-4be2-b228-0fe250379934</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=886059b7-d984-4e19-b7d7-6d90ebc9b2e0</t>
         </is>
       </c>
     </row>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการชุดอุปกรณ์เคลื่อนย้ายผู้ป่วยในสถานการณ์ฉุกเฉิน ของโรงพยาบาลชุมชน 8 แห่ง จำนวน 10 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงชนิดสี 2 หัวตรวจ ของโรงพยาบาลชุมชน 6 แห่ง จำนวน 8 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=886059b7-d984-4e19-b7d7-6d90ebc9b2e0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fc233297-ee25-42e4-bc90-16f41ac8db6a</t>
         </is>
       </c>
     </row>
@@ -7691,7 +7691,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงชนิดสี 2 หัวตรวจ ของโรงพยาบาลชุมชน 6 แห่ง จำนวน 8 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดออกซิเจนในเลือดอัตโนมัติชนิดพกพา ของโรงพยาบาลส่งเสริมสุขภาพตำบลและโรงพยาบาลชุมชน 24 แห่ง จำนวน 68 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fc233297-ee25-42e4-bc90-16f41ac8db6a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3d2922a2-6499-49fa-b182-1e95dc5131d7</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดออกซิเจนในเลือดอัตโนมัติชนิดพกพา ของโรงพยาบาลส่งเสริมสุขภาพตำบลและโรงพยาบาลชุมชน 24 แห่ง จำนวน 68 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องเอกซเรย์ทั่วไปขนาดไม่น้อยกว่า 500 mA. แบบแขวนเพดาน โรงพยาบาลแก่งกระจาน ตำบลวังจันทร์ อำเภอแก่งกระจาน จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -7741,27 +7741,27 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3d2922a2-6499-49fa-b182-1e95dc5131d7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6f21d5fd-56e9-4486-915b-90fd4be0f39b</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กองทัพอากาศ</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>2102</v>
+        <v>206</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องเอกซเรย์ทั่วไปขนาดไม่น้อยกว่า 500 mA. แบบแขวนเพดาน โรงพยาบาลแก่งกระจาน ตำบลวังจันทร์ อำเภอแก่งกระจาน จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบริการบำรุงรักษาเครื่องเอกซเรย์ควบคุมด้วยระบบคอมพิวเตอร์ขนาดไม่น้อยกว่า 300 mA พร้อมอุปกรณ์ ยี่ห้อ DRGEM รุ่น GXR-52S ของ โรงพยาบาลกองบิน กองบิน 1, โรงพยาบาลกองบิน กองบิน 2, โรงพยาบาลกองบิน กองบิน 7, โรงพยาบาลกองบิน กองบิน 41, โรงพยาบาลกองบิน กองบิน 46 จำนวน ๑ งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6f21d5fd-56e9-4486-915b-90fd4be0f39b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ffb67ab2-d749-4ab0-87f1-1b11432ab218</t>
         </is>
       </c>
     </row>
@@ -7788,15 +7788,15 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>กองทัพอากาศ</t>
+          <t>กรมธนารักษ์</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>206</v>
+        <v>303</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบริการบำรุงรักษาเครื่องเอกซเรย์ควบคุมด้วยระบบคอมพิวเตอร์ขนาดไม่น้อยกว่า 300 mA พร้อมอุปกรณ์ ยี่ห้อ DRGEM รุ่น GXR-52S ของ โรงพยาบาลกองบิน กองบิน 1, โรงพยาบาลกองบิน กองบิน 2, โรงพยาบาลกองบิน กองบิน 7, โรงพยาบาลกองบิน กองบิน 41, โรงพยาบาลกองบิน กองบิน 46 จำนวน ๑ งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องอากาศยานซึ่งไม่มีนักบิน (Drone)  พร้อมชุดอุปกรณ์ภาคสนามและระบบซอฟต์แวร์ประมวลผลแผนที่ความละเอียดสูง จำนวน 12 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ffb67ab2-d749-4ab0-87f1-1b11432ab218</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e88cabea-0e2e-4af8-8b8b-4aa4e7eb040a</t>
         </is>
       </c>
     </row>
@@ -7823,15 +7823,15 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>กรมธนารักษ์</t>
+          <t>สำนักงานเศรษฐกิจการคลัง</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องอากาศยานซึ่งไม่มีนักบิน (Drone)  พร้อมชุดอุปกรณ์ภาคสนามและระบบซอฟต์แวร์ประมวลผลแผนที่ความละเอียดสูง จำนวน 12 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์สำหรับโครงการพัฒนาระบบสารสนเทศสถาบันการเงินประชาชนของสำนักงานเศรษฐกิจการคลัง (ระบบงาน PFI) ประจำปีงบประมาณ พ.ศ. 2570  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>★ (ซอฟต์แวร์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e88cabea-0e2e-4af8-8b8b-4aa4e7eb040a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a787a49a-4035-46d3-b8a4-a996ac96341d</t>
         </is>
       </c>
     </row>
@@ -7858,15 +7858,15 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>สำนักงานเศรษฐกิจการคลัง</t>
+          <t>กรมพัฒนาสังคมและสวัสดิการ</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>311</v>
+        <v>603</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์สำหรับโครงการพัฒนาระบบสารสนเทศสถาบันการเงินประชาชนของสำนักงานเศรษฐกิจการคลัง (ระบบงาน PFI) ประจำปีงบประมาณ พ.ศ. 2570  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์สำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a787a49a-4035-46d3-b8a4-a996ac96341d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=857f0ccd-d38e-47b0-8d6d-913ef2cb1583</t>
         </is>
       </c>
     </row>
@@ -7893,15 +7893,15 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>กรมพัฒนาสังคมและสวัสดิการ</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>603</v>
+        <v>704</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์สำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -7911,12 +7911,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=857f0ccd-d38e-47b0-8d6d-913ef2cb1583</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=01c185be-f27c-41bc-868e-accd57e4a95c</t>
         </is>
       </c>
     </row>
@@ -7928,15 +7928,15 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>704</v>
+        <v>804</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์พร้อมอุปกรณ์สำหรับศูนย์รวมข้อมูลการขนส่งด้วยรถบรรทุกเพื่อส่งเสริมการขนส่งด้วยรถบรรทุกให้มีประสิทธิภาพ ปลอดภัยและได้มาตรฐาน (TDSC) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -7946,12 +7946,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=01c185be-f27c-41bc-868e-accd57e4a95c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70381c19-a073-41d0-8f0b-08c5e68fca7c</t>
         </is>
       </c>
     </row>
@@ -7963,15 +7963,15 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
+          <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์พร้อมอุปกรณ์สำหรับศูนย์รวมข้อมูลการขนส่งด้วยรถบรรทุกเพื่อส่งเสริมการขนส่งด้วยรถบรรทุกให้มีประสิทธิภาพ ปลอดภัยและได้มาตรฐาน (TDSC) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบไฟฟ้า ตู้สวิตช์บอร์ด ๒๖ ท่าอากาศยาน และกรมท่าอากาศยาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (สวิตช์)</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70381c19-a073-41d0-8f0b-08c5e68fca7c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7f19e47d-04ea-4596-a45a-a42e0fd28eea</t>
         </is>
       </c>
     </row>
@@ -7998,15 +7998,15 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
+          <t>กรมป่าไม้</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>805</v>
+        <v>912</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบไฟฟ้า ตู้สวิตช์บอร์ด ๒๖ ท่าอากาศยาน และกรมท่าอากาศยาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>★ (สวิตช์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7f19e47d-04ea-4596-a45a-a42e0fd28eea</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fd72b9d1-6722-4578-b8e5-e2d45779204d</t>
         </is>
       </c>
     </row>
@@ -8033,15 +8033,15 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>กรมป่าไม้</t>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>912</v>
+        <v>1302</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าระบบประชุมทางไกล (Web Conference Video Streaming) ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ระบบประชุมทางไกล)</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fd72b9d1-6722-4578-b8e5-e2d45779204d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6c4b6c7d-fa54-4634-9070-01779d28362f</t>
         </is>
       </c>
     </row>
@@ -8068,15 +8068,15 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+          <t>กรมโยธาธิการและผังเมือง</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>1302</v>
+        <v>1507</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าระบบประชุมทางไกล (Web Conference Video Streaming) ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างงานปรับปรุงระบบดับเพลิงพิเศษอัตโนมัติ (Clean Agent Fire Suppression System) ภายในห้องคอมพิวเตอร์แม่ข่าย (Server Room) อาคาร 4 ชั้น 1 กรมโยธาธิการและผังเมือง ถนนพระราม 9 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>★ (ระบบประชุมทางไกล)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6c4b6c7d-fa54-4634-9070-01779d28362f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a61be7d0-de39-476c-b4f8-7a3ec47bbd62</t>
         </is>
       </c>
     </row>
@@ -8103,15 +8103,15 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>กรมโยธาธิการและผังเมือง</t>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>1507</v>
+        <v>1611</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างงานปรับปรุงระบบดับเพลิงพิเศษอัตโนมัติ (Clean Agent Fire Suppression System) ภายในห้องคอมพิวเตอร์แม่ข่าย (Server Room) อาคาร 4 ชั้น 1 กรมโยธาธิการและผังเมือง ถนนพระราม 9 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการถ่ายเอกสารพร้อมเครื่องถ่ายเอกสาร กระดาษ วัสดุสิ้นเปลือง และพนักงานประจำเครื่องของสำนักงาน ป.ป.ส. ดินแดง/สำนักงาน ป.ป.ส. ทุ่งสองห้อง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (กระดาษ)</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a61be7d0-de39-476c-b4f8-7a3ec47bbd62</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=325eb565-d1b7-456f-86c5-076a6e3f94fd</t>
         </is>
       </c>
     </row>
@@ -8138,15 +8138,15 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>1611</v>
+        <v>2102</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการถ่ายเอกสารพร้อมเครื่องถ่ายเอกสาร กระดาษ วัสดุสิ้นเปลือง และพนักงานประจำเครื่องของสำนักงาน ป.ป.ส. ดินแดง/สำนักงาน ป.ป.ส. ทุ่งสองห้อง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องนึ่งฆ่าเชื้อจุลินทรีย์ด้วยไอน้ำระบบอัตโนมัติ ขนาดไม่น้อยกว่า 850 ลิตร ห้องนึ่งทรงเหลี่ยมชนิด 1 ประตู โรงพยาบาลบ้านลาด ตำบลท่าช้าง อำเภอบ้านลาด จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -8156,12 +8156,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>★ (กระดาษ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=325eb565-d1b7-456f-86c5-076a6e3f94fd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4d2f3086-64b4-4e82-a4f3-6299ee3aa880</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องนึ่งฆ่าเชื้อจุลินทรีย์ด้วยไอน้ำระบบอัตโนมัติ ขนาดไม่น้อยกว่า 850 ลิตร ห้องนึ่งทรงเหลี่ยมชนิด 1 ประตู โรงพยาบาลบ้านลาด ตำบลท่าช้าง อำเภอบ้านลาด จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องล้างเครื่องมืออัลตร้าโซนิก ชนิด 3 หลุมล้าง ขนาดความจุไม่น้อยกว่า 80 ลิตร โรงพยาบาลชะอำ ตำบลชะอำ อำเภอชะอำ จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4d2f3086-64b4-4e82-a4f3-6299ee3aa880</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b7c95cfb-63e4-43a3-9eeb-4e9c5df71f85</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องล้างเครื่องมืออัลตร้าโซนิก ชนิด 3 หลุมล้าง ขนาดความจุไม่น้อยกว่า 80 ลิตร โรงพยาบาลชะอำ ตำบลชะอำ อำเภอชะอำ จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่ายกลาง (Backbone) กระทรวงสาธารณสุข ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b7c95cfb-63e4-43a3-9eeb-4e9c5df71f85</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3a5cafe5-5313-4cb0-ab08-4b09c244ba61</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่ายกลาง (Backbone) กระทรวงสาธารณสุข ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนและคาร์บอนไดออกไซด์ในเลือด ของโรงพยาบาลในจังหวัดสุรินทร์ 7 แห่ง จำนวน 12 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3a5cafe5-5313-4cb0-ab08-4b09c244ba61</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d5f4c614-78c4-4363-a75d-31e52b8e81d7</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนและคาร์บอนไดออกไซด์ในเลือด ของโรงพยาบาลในจังหวัดสุรินทร์ 7 แห่ง จำนวน 12 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 8 เตียง ของโรงพยาบาลท่าตูม จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d5f4c614-78c4-4363-a75d-31e52b8e81d7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=261f4b2d-359f-4fbc-9c62-4971724a772f</t>
         </is>
       </c>
     </row>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 8 เตียง ของโรงพยาบาลท่าตูม จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันขนาดใหญ่ ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 6 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -8336,27 +8336,27 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=261f4b2d-359f-4fbc-9c62-4971724a772f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9cc00102-4e57-443e-a94c-3787d155fe6b</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สำนักงานคณะกรรมการคุ้มครองผู้บริโภค</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>2102</v>
+        <v>103</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันขนาดใหญ่ ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 6 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาเครือข่าย เครื่องคอมพิวเตอร์แม่ข่าย เครื่องคอมพิวเตอร์ อุปกรณ์คอมพิวเตอร์และห้องปฏิบัติการคอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -8366,12 +8366,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9cc00102-4e57-443e-a94c-3787d155fe6b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6f8747c6-3579-4b1b-992e-7c6f55a197b3</t>
         </is>
       </c>
     </row>
@@ -8383,15 +8383,15 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการคุ้มครองผู้บริโภค</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>103</v>
+        <v>204</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการบำรุงรักษาเครือข่าย เครื่องคอมพิวเตอร์แม่ข่าย เครื่องคอมพิวเตอร์ อุปกรณ์คอมพิวเตอร์และห้องปฏิบัติการคอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ประจำอาคาร งานก่อสร้างโรงเลี้ยง 400 คน (แบบ กห 08 - 7) ของ มทบ.29 ค่ายกฤษณ์สีวะรา อ.เมือง จว.ส.น. แผนงานเพิ่มเติมระหว่างปีงบประมาณ พ.ศ. 2569 ให้กับ ช.2 พัน.202 ดำเนินการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -8401,12 +8401,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6f8747c6-3579-4b1b-992e-7c6f55a197b3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=daeb7717-b81c-405b-94a2-aa71f55ea8af</t>
         </is>
       </c>
     </row>
@@ -8418,15 +8418,15 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กองทัพอากาศ</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ประจำอาคาร งานก่อสร้างโรงเลี้ยง 400 คน (แบบ กห 08 - 7) ของ มทบ.29 ค่ายกฤษณ์สีวะรา อ.เมือง จว.ส.น. แผนงานเพิ่มเติมระหว่างปีงบประมาณ พ.ศ. 2569 ให้กับ ช.2 พัน.202 ดำเนินการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องพิมพ์สีแผ่นไวนิล จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=daeb7717-b81c-405b-94a2-aa71f55ea8af</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e4172805-a5ea-4e60-b1e4-787b55b54a34</t>
         </is>
       </c>
     </row>
@@ -8453,15 +8453,15 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>กองทัพอากาศ</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>206</v>
+        <v>704</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องพิมพ์สีแผ่นไวนิล จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน เครื่องปรับอากาศแบบแยกส่วน ชนิดแขวน ระบบ Inverter ขนาด 30,000 บีทียู จำนวน 12 เครื่อง พร้อมติดตั้ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -8471,12 +8471,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>★ (เครื่องพิมพ์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e4172805-a5ea-4e60-b1e4-787b55b54a34</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dc7ebea2-3d95-4ced-a85f-84f2cb8e77c2</t>
         </is>
       </c>
     </row>
@@ -8488,15 +8488,15 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมปศุสัตว์</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน เครื่องปรับอากาศแบบแยกส่วน ชนิดแขวน ระบบ Inverter ขนาด 30,000 บีทียู จำนวน 12 เครื่อง พร้อมติดตั้ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์  จำนวน  5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dc7ebea2-3d95-4ced-a85f-84f2cb8e77c2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a7913502-7863-4804-9095-3f717c939f36</t>
         </is>
       </c>
     </row>
@@ -8523,15 +8523,15 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>กรมปศุสัตว์</t>
+          <t>กรมส่งเสริมการเกษตร</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์  จำนวน  5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์ สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม สำนักงานเกษตรอำเภอนาวัง ตำบลนาเหล่าอำเภอนาวัง  จังหวัดหนองบัวลำภู  จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a7913502-7863-4804-9095-3f717c939f36</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1cb87987-0702-433c-8678-5f41220c5aa5</t>
         </is>
       </c>
     </row>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์ สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม สำนักงานเกษตรอำเภอนาวัง ตำบลนาเหล่าอำเภอนาวัง  จังหวัดหนองบัวลำภู  จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบ ไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 4 ล้อ แบบดับเบิ้ลแค็บ  พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม ศูนย์ส่งเสริมเทคโนโลยีการเกษตรด้านอารักขาพืช จังหวัดพิษณุโลก ตำบลอรัญญิก อำเภอเมืองพิษณุโลก จังหวัดพิษณุโลก 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1cb87987-0702-433c-8678-5f41220c5aa5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=21728512-3d55-4336-a433-756fa816ccd6</t>
         </is>
       </c>
     </row>
@@ -8593,15 +8593,15 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเกษตร</t>
+          <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>711</v>
+        <v>804</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบ ไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 4 ล้อ แบบดับเบิ้ลแค็บ  พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม ศูนย์ส่งเสริมเทคโนโลยีการเกษตรด้านอารักขาพืช จังหวัดพิษณุโลก ตำบลอรัญญิก อำเภอเมืองพิษณุโลก จังหวัดพิษณุโลก 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและซ่อมแซมระบบคอมพิวเตอร์แม่ข่ายและอุปกรณ์ตามโครงการพัฒนาระบบฐานข้อมูลกลางเพื่อบูรณาการข้อมูลสนับสนุนการให้บริการของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=21728512-3d55-4336-a433-756fa816ccd6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1089b549-2663-46b4-8f30-3b752498b76d</t>
         </is>
       </c>
     </row>
@@ -8628,15 +8628,15 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและซ่อมแซมระบบคอมพิวเตอร์แม่ข่ายและอุปกรณ์ตามโครงการพัฒนาระบบฐานข้อมูลกลางเพื่อบูรณาการข้อมูลสนับสนุนการให้บริการของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 7 รายการ ศูนย์สร้างทางลำปาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1089b549-2663-46b4-8f30-3b752498b76d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=74dbade6-07ca-4df1-9aaa-c33e529e04b5</t>
         </is>
       </c>
     </row>
@@ -8671,7 +8671,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 7 รายการ ศูนย์สร้างทางลำปาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=74dbade6-07ca-4df1-9aaa-c33e529e04b5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=486fc308-1dd1-40ac-9b5f-16595e40c39d</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องสำรองไฟฟ้า ขนาด 2 kVA จำนวน 138 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -8716,12 +8716,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (เครื่องสำรองไฟฟ้า, เครื่องสำรองไฟ)</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=486fc308-1dd1-40ac-9b5f-16595e40c39d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=66aa18c1-0eb7-4c9c-bc97-eb6c9f84ea61</t>
         </is>
       </c>
     </row>
@@ -8733,15 +8733,15 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>กรมอุตุนิยมวิทยา</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>806</v>
+        <v>1104</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องสำรองไฟฟ้า ขนาด 2 kVA จำนวน 138 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาเครื่องสำรองไฟฟ้าต่อเนื่อง (UPS) และเครื่องกำเนิดไฟฟ้า (Generator) ประจำปีงบประมาณ พ.ศ.๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=66aa18c1-0eb7-4c9c-bc97-eb6c9f84ea61</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b04b2aed-150c-4a6a-9fe6-de4abe606304</t>
         </is>
       </c>
     </row>
@@ -8768,15 +8768,15 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>กรมอุตุนิยมวิทยา</t>
+          <t>กรมเจรจาการค้าระหว่างประเทศ</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>1104</v>
+        <v>1306</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาเครื่องสำรองไฟฟ้าต่อเนื่อง (UPS) และเครื่องกำเนิดไฟฟ้า (Generator) ประจำปีงบประมาณ พ.ศ.๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการปรับปรุงระบบสายสัญญาณเครือข่าย ระบบไฟฟ้า และระบบโทรศัพท์พร้อมอุปกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>★ (เครื่องสำรองไฟฟ้า, เครื่องสำรองไฟ)</t>
+          <t>★ (สายสัญญาณ)</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b04b2aed-150c-4a6a-9fe6-de4abe606304</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bac0b85b-275a-4ed6-a580-b3e8bfeb237f</t>
         </is>
       </c>
     </row>
@@ -8803,15 +8803,15 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>กรมเจรจาการค้าระหว่างประเทศ</t>
+          <t>กรมส่งเสริมการค้าระหว่างประเทศ</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการปรับปรุงระบบสายสัญญาณเครือข่าย ระบบไฟฟ้า และระบบโทรศัพท์พร้อมอุปกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาระบบคอมพิวเตอร์และระบบเครือข่ายพร้อมอุปกรณ์ ปี ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>★ (สายสัญญาณ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bac0b85b-275a-4ed6-a580-b3e8bfeb237f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f059ad38-40c4-42cf-9270-e3def8289626</t>
         </is>
       </c>
     </row>
@@ -8838,15 +8838,15 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการค้าระหว่างประเทศ</t>
+          <t>กรมการปกครอง</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>1309</v>
+        <v>1503</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการบำรุงรักษาระบบคอมพิวเตอร์และระบบเครือข่ายพร้อมอุปกรณ์ ปี ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อวัสดุสำหรับเครื่องพิมพ์คอมพิวเตอร์เพื่อสนับสนุนการดำเนินงานในระบบสารสนเทศทรัพยากรบุคคลระดับกรม (DPIS) ประจำปีงบประมาณ  พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -8856,12 +8856,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f059ad38-40c4-42cf-9270-e3def8289626</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ec8d68fe-3f09-45d1-a6c2-b10acc4b8aff</t>
         </is>
       </c>
     </row>
@@ -8873,15 +8873,15 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>กรมการปกครอง</t>
+          <t>กรมการศาสนา</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>1503</v>
+        <v>1803</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อวัสดุสำหรับเครื่องพิมพ์คอมพิวเตอร์เพื่อสนับสนุนการดำเนินงานในระบบสารสนเทศทรัพยากรบุคคลระดับกรม (DPIS) ประจำปีงบประมาณ  พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อหมึกเครื่องพิมพ์ (ครั้งที่ 3) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -8891,12 +8891,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, เครื่องพิมพ์)</t>
+          <t>★ (หมึกเครื่องพิมพ์, เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ec8d68fe-3f09-45d1-a6c2-b10acc4b8aff</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cad3c999-2a59-4f98-9a16-5cd0e9b965e5</t>
         </is>
       </c>
     </row>
@@ -8908,15 +8908,15 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>กรมการศาสนา</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>1803</v>
+        <v>2102</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อหมึกเครื่องพิมพ์ (ครั้งที่ 3) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ กล้องจุลทรรศน์ตรวจตาชนิดลำแสงแคบพร้อมระบบเก็บภาพดิจิตอล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -8926,12 +8926,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>★ (หมึกเครื่องพิมพ์, เครื่องพิมพ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cad3c999-2a59-4f98-9a16-5cd0e9b965e5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b7dc6e3c-c6d3-4740-8dfd-746b3c47ce99</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ กล้องจุลทรรศน์ตรวจตาชนิดลำแสงแคบพร้อมระบบเก็บภาพดิจิตอล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดใหญ่ ของโรงพยาบาลในจังหวัดสุรินทร์ 2 แห่ง จำนวน 7 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b7dc6e3c-c6d3-4740-8dfd-746b3c47ce99</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9e482ce2-8b0c-4125-ac7c-be9fb421af4d</t>
         </is>
       </c>
     </row>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดใหญ่ ของโรงพยาบาลในจังหวัดสุรินทร์ 2 แห่ง จำนวน 7 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงแบบพกพาไม่ต้องชาร์จไฟฟ้าพร้อมระบบแพทย์ทางไกล ของโรงพยาบาลชุมชน 3 แห่ง จำนวน 4 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9e482ce2-8b0c-4125-ac7c-be9fb421af4d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=49ab0e04-32b5-4441-9d77-b629429b1571</t>
         </is>
       </c>
     </row>
@@ -9021,7 +9021,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงแบบพกพาไม่ต้องชาร์จไฟฟ้าพร้อมระบบแพทย์ทางไกล ของโรงพยาบาลชุมชน 3 แห่ง จำนวน 4 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ เครื่องตรวจวิเคราะห์แยกชั้นจอประสาทตาชนิดถ่ายภาพจอประสาทตา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=49ab0e04-32b5-4441-9d77-b629429b1571</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=165b7f39-161c-4e36-abf9-9ab28afdef12</t>
         </is>
       </c>
     </row>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ เครื่องตรวจวิเคราะห์แยกชั้นจอประสาทตาชนิดถ่ายภาพจอประสาทตา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องรับสัญญาณภาพเอกซเรย์เป็นดิจิตอล ชนิดชุดรับภาพแฟลตพาแนลไร้สาย โรงพยาบาลแก่งกระจาน ตำบลวังจันทร์ อำเภอแก่งกระจาน จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=165b7f39-161c-4e36-abf9-9ab28afdef12</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=23fd4481-d3c5-4060-a810-ba6addb1516c</t>
         </is>
       </c>
     </row>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องรับสัญญาณภาพเอกซเรย์เป็นดิจิตอล ชนิดชุดรับภาพแฟลตพาแนลไร้สาย โรงพยาบาลแก่งกระจาน ตำบลวังจันทร์ อำเภอแก่งกระจาน จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๒ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=23fd4481-d3c5-4060-a810-ba6addb1516c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e59b2ed4-9af0-48e9-a768-f2323d942f2e</t>
         </is>
       </c>
     </row>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๒ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิคพร้อมภาควัดออกซิเจนและคาร์บอนไดออกไซด์ในเลือด จำนวน 25 เครื่อง งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาล ในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e59b2ed4-9af0-48e9-a768-f2323d942f2e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b80f6866-243b-41ee-8a1f-f04456bc5061</t>
         </is>
       </c>
     </row>
@@ -9153,15 +9153,15 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>2102</v>
+        <v>2107</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิคพร้อมภาควัดออกซิเจนและคาร์บอนไดออกไซด์ในเลือด จำนวน 25 เครื่อง งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาล ในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ 11 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b80f6866-243b-41ee-8a1f-f04456bc5061</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fa5cc489-cfac-46c2-b92b-18e107acc682</t>
         </is>
       </c>
     </row>
@@ -9188,15 +9188,15 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>กรมสนับสนุนบริการสุขภาพ</t>
+          <t>กรมอนามัย</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>2107</v>
+        <v>2109</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ 11 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fa5cc489-cfac-46c2-b92b-18e107acc682</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=eada32a9-3333-40e2-ad51-54e8d12647cf</t>
         </is>
       </c>
     </row>
@@ -9223,15 +9223,15 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>กรมอนามัย</t>
+          <t>สำนักงานพระพุทธศาสนาแห่งชาติ</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>2109</v>
+        <v>2503</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน ๑๒ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -9241,32 +9241,32 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=eada32a9-3333-40e2-ad51-54e8d12647cf</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=54340df1-ec2b-4471-bb8f-6779c938e36b</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>สำนักงานพระพุทธศาสนาแห่งชาติ</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>2503</v>
+        <v>204</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน ๑๒ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ประจำอาคาร จำนวน 14 รายการ เพิื่อใช้ในงานปรับปรุงอาคารของ กรมทหารม้าที่ 1 รักษาพระองค์ (กองร้อยสนับสนุนส่วนหน้า 1 กองพันซ่อมบำรุง กรมสนับสนุนที่ 12 ) เป็น โรงเรียนหน่วยเฉพาะกิจทหารมหาดเล็กรักษาพระองค์ ส่วนที่ 2 เป็นแผนงานเพิ่มเติมระหว่างปีงบประมาณ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=54340df1-ec2b-4471-bb8f-6779c938e36b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dca076ec-64c4-4fee-9ef2-8a6665ae36fb</t>
         </is>
       </c>
     </row>
@@ -9301,7 +9301,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ประจำอาคาร จำนวน 14 รายการ เพิื่อใช้ในงานปรับปรุงอาคารของ กรมทหารม้าที่ 1 รักษาพระองค์ (กองร้อยสนับสนุนส่วนหน้า 1 กองพันซ่อมบำรุง กรมสนับสนุนที่ 12 ) เป็น โรงเรียนหน่วยเฉพาะกิจทหารมหาดเล็กรักษาพระองค์ ส่วนที่ 2 เป็นแผนงานเพิ่มเติมระหว่างปีงบประมาณ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ประจำอาคาร จำนวน 2 รายการ เพื่อใช้ในงานซ่อมแซมอาคารแหล่งสมาคมนายทหาร หมายเลข 144/30 ของ  กรมทหารปืนใหญ่ที่ 2 รักษาพระองค์ เป็นแผนงานเพิ่มเติมระหว่างปีงบประมาณ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dca076ec-64c4-4fee-9ef2-8a6665ae36fb</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1c52e71e-02d3-4d1f-bea4-a37dea913a20</t>
         </is>
       </c>
     </row>
@@ -9328,15 +9328,15 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กรมบัญชีกลาง</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>204</v>
+        <v>304</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ประจำอาคาร จำนวน 2 รายการ เพื่อใช้ในงานซ่อมแซมอาคารแหล่งสมาคมนายทหาร หมายเลข 144/30 ของ  กรมทหารปืนใหญ่ที่ 2 รักษาพระองค์ เป็นแผนงานเพิ่มเติมระหว่างปีงบประมาณ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างทำความสะอาดอาคารศูนย์คอมพิวเตอร์หลักของกรมบัญชีกลาง (Data Center) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1c52e71e-02d3-4d1f-bea4-a37dea913a20</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=27271442-a270-4c56-a150-8d5f8833fed3</t>
         </is>
       </c>
     </row>
@@ -9363,15 +9363,15 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>กรมบัญชีกลาง</t>
+          <t>กรมศุลกากร</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างทำความสะอาดอาคารศูนย์คอมพิวเตอร์หลักของกรมบัญชีกลาง (Data Center) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อเครื่องปรับอากาศแบบแยกส่วน ติดผนัง ขนาด 18000 บีทียู จำนวน 24 เครื่อง และขนาด 12000 บีทียู จำนวน 24 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=27271442-a270-4c56-a150-8d5f8833fed3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=38f0f8e6-37c7-4c1b-85f7-816a83796f90</t>
         </is>
       </c>
     </row>
@@ -9398,15 +9398,15 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>กรมศุลกากร</t>
+          <t>กรมชลประทาน</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>305</v>
+        <v>703</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อเครื่องปรับอากาศแบบแยกส่วน ติดผนัง ขนาด 18000 บีทียู จำนวน 24 เครื่อง และขนาด 12000 บีทียู จำนวน 24 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจัดหาและติดตั้งเครื่องสูบน้ำชนิดหอยโข่งแบบ Horizontal Split Case ขับด้วยมอเตอร์ไฟฟ้าอัตราสูบน้ำ ๐.๒๐ ลบ.ม./วินาที ระยะยกน้ำไม่น้อยกว่า ๔๕ เมตร และอื่นๆ รวม ๔ รายการ  สำหรับงานสถานีสูบน้ำด้วยไฟฟ้าพร้อมระบบส่งน้ำ บ้านสุขสำราญ ตำบลเหล่าต่างคำ อำเภอโพนพิสัย จังหวัดหนองคาย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=38f0f8e6-37c7-4c1b-85f7-816a83796f90</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=824576ac-9b6f-4dcc-af9a-f70ac3b918df</t>
         </is>
       </c>
     </row>
@@ -9433,15 +9433,15 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>กรมชลประทาน</t>
+          <t>กรมการข้าว</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>703</v>
+        <v>718</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจัดหาและติดตั้งเครื่องสูบน้ำชนิดหอยโข่งแบบ Horizontal Split Case ขับด้วยมอเตอร์ไฟฟ้าอัตราสูบน้ำ ๐.๒๐ ลบ.ม./วินาที ระยะยกน้ำไม่น้อยกว่า ๔๕ เมตร และอื่นๆ รวม ๔ รายการ  สำหรับงานสถานีสูบน้ำด้วยไฟฟ้าพร้อมระบบส่งน้ำ บ้านสุขสำราญ ตำบลเหล่าต่างคำ อำเภอโพนพิสัย จังหวัดหนองคาย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การเกษตร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=824576ac-9b6f-4dcc-af9a-f70ac3b918df</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=144b5b77-0cf7-4926-847e-f0fd1bd8f4b6</t>
         </is>
       </c>
     </row>
@@ -9468,15 +9468,15 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>กรมการข้าว</t>
+          <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>718</v>
+        <v>805</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การเกษตร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบงานสารสนเทศ ระบบเครือข่าย และบริการแก้ไขคอมพิวเตอร์และอุปกรณ์ต่อพ่วง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=144b5b77-0cf7-4926-847e-f0fd1bd8f4b6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f9ae0aa5-414d-4a63-88c4-8cc52f83f6ef</t>
         </is>
       </c>
     </row>
@@ -9503,15 +9503,15 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
+          <t>กรมทางหลวงชนบท</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบงานสารสนเทศ ระบบเครือข่าย และบริการแก้ไขคอมพิวเตอร์และอุปกรณ์ต่อพ่วง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องพิมพ์ Tag Thermal Printer จำนวน 2 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f9ae0aa5-414d-4a63-88c4-8cc52f83f6ef</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=754696e0-bbea-44e1-9a55-42fce741c6ae</t>
         </is>
       </c>
     </row>
@@ -9538,15 +9538,15 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>กรมทางหลวงชนบท</t>
+          <t>กรมพัฒนาพลังงานทดแทนและอนุรักษ์พลังงาน</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>807</v>
+        <v>1205</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องพิมพ์ Tag Thermal Printer จำนวน 2 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์ อุปกรณ์เครือข่ายและอุปกรณ์หน่วยความจำสำรองสำหรับระบบฐานข้อมูล  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>★ (เครื่องพิมพ์)</t>
+          <t>★ (คอมพิวเตอร์, หน่วยความจำ, อุปกรณ์เครือข่าย)</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=754696e0-bbea-44e1-9a55-42fce741c6ae</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6b70ca7e-b8a0-4edd-a187-b48e924a78fa</t>
         </is>
       </c>
     </row>
@@ -9573,15 +9573,15 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>กรมพัฒนาพลังงานทดแทนและอนุรักษ์พลังงาน</t>
+          <t>กรมการปกครอง</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>1205</v>
+        <v>1503</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์ อุปกรณ์เครือข่ายและอุปกรณ์หน่วยความจำสำรองสำหรับระบบฐานข้อมูล  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อวัสดุผงหมึกและดรัมสำหรับเครื่องพิมพ์คอมพิวเตอร์ จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, หน่วยความจำ, อุปกรณ์เครือข่าย)</t>
+          <t>★ (ดรัม, คอมพิวเตอร์, เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6b70ca7e-b8a0-4edd-a187-b48e924a78fa</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ce5f2a5e-58b0-4355-b3f5-66c43c2247d8</t>
         </is>
       </c>
     </row>
@@ -9608,15 +9608,15 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>กรมการปกครอง</t>
+          <t>กรมสอบสวนคดีพิเศษ</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>1503</v>
+        <v>1608</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อวัสดุผงหมึกและดรัมสำหรับเครื่องพิมพ์คอมพิวเตอร์ จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องคอมพิวเตอร์ประสิทธิภาพสูงสำหรับประมวลผลความสัมพันธ์ทางธุรกรรมและวิเคราะห์เส้นทางการเงินของคดีพิเศษและเรื่องสืบสวน กรมสอบสวนคดีพิเศษ  แขวงทุ่งสองห้อง เขตหลักสี่ กรุงเทพมหานคร 3 ชุด ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -9626,12 +9626,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>★ (ดรัม, คอมพิวเตอร์, เครื่องพิมพ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ce5f2a5e-58b0-4355-b3f5-66c43c2247d8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cd272b14-6e4a-4165-9eab-d4725c6ca271</t>
         </is>
       </c>
     </row>
@@ -9643,15 +9643,15 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>กรมสอบสวนคดีพิเศษ</t>
+          <t>สำนักงานประกันสังคม</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>1608</v>
+        <v>1706</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องคอมพิวเตอร์ประสิทธิภาพสูงสำหรับประมวลผลความสัมพันธ์ทางธุรกรรมและวิเคราะห์เส้นทางการเงินของคดีพิเศษและเรื่องสืบสวน กรมสอบสวนคดีพิเศษ  แขวงทุ่งสองห้อง เขตหลักสี่ กรุงเทพมหานคร 3 ชุด ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อวัสดุคอมพิวเตอร์ จำนวน ๑ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cd272b14-6e4a-4165-9eab-d4725c6ca271</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a2ef415e-d086-45a2-854c-add8955d6fdb</t>
         </is>
       </c>
     </row>
@@ -9678,15 +9678,15 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>สำนักงานประกันสังคม</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>1706</v>
+        <v>2102</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อวัสดุคอมพิวเตอร์ จำนวน ๑ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตาม   การทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดใหญ่ จำนวน 12 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ.2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -9696,12 +9696,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a2ef415e-d086-45a2-854c-add8955d6fdb</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5a6e7a1-9557-4e6f-8ecc-2de9fdd94405</t>
         </is>
       </c>
     </row>
@@ -9713,15 +9713,15 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>2102</v>
+        <v>2107</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตาม   การทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดใหญ่ จำนวน 12 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ.2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ  จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5a6e7a1-9557-4e6f-8ecc-2de9fdd94405</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fdb52cbf-ad05-423e-b1d8-e2f17eae5c8d</t>
         </is>
       </c>
     </row>
@@ -9748,15 +9748,15 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>กรมสนับสนุนบริการสุขภาพ</t>
+          <t>สำนักงานตำรวจแห่งชาติ</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>2107</v>
+        <v>2507</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ  จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดหาคอมพิวเตอร์ (Notebook) สำหรับนักเรียนนายร้อยตำรวจรุ่นที่ 84 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fdb52cbf-ad05-423e-b1d8-e2f17eae5c8d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c5ba14d7-29e1-4cb6-a64d-e89688b4e1f1</t>
         </is>
       </c>
     </row>
@@ -9783,15 +9783,15 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>สำนักงานตำรวจแห่งชาติ</t>
+          <t>สำนักงานอัยการสูงสุด</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดหาคอมพิวเตอร์ (Notebook) สำหรับนักเรียนนายร้อยตำรวจรุ่นที่ 84 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c5ba14d7-29e1-4cb6-a64d-e89688b4e1f1</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=caeb26b1-ae0a-40d1-878c-18926a5cd2cd</t>
         </is>
       </c>
     </row>
@@ -9818,15 +9818,15 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>สำนักงานอัยการสูงสุด</t>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามการทุจริตแห่งชาติ</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>2509</v>
+        <v>2605</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์พกพาแบบหน้าจอสัมผัส จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -9836,12 +9836,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, คอมพิวเตอร์พกพา)</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=caeb26b1-ae0a-40d1-878c-18926a5cd2cd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=380be6fa-be50-4cc9-a85d-d4912f73145e</t>
         </is>
       </c>
     </row>
@@ -9853,15 +9853,15 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามการทุจริตแห่งชาติ</t>
+          <t>องค์การบริหารส่วนจังหวัดระยอง</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>2605</v>
+        <v>2210101</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์พกพาแบบหน้าจอสัมผัส จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 2 รายการ ดังนี้ (1) รถยนต์โดยสารปรับอากาศ ไม่น้อยกว่า 22 ที่นั่ง แบบขับเคลื่อนด้วยระบบไฟฟ้า จำนวน 2 คัน  (2) รถยนต์โดยสารปรับอากาศ ไม่น้อยกว่า 40 ที่นั่ง แบบขับเคลื่อนด้วยระบบไฟฟ้า จำนวน 2 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, คอมพิวเตอร์พกพา)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=380be6fa-be50-4cc9-a85d-d4912f73145e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=56da4e4f-a0c5-43d9-b499-ef666d60c6ae</t>
         </is>
       </c>
     </row>
@@ -9888,15 +9888,15 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>องค์การบริหารส่วนจังหวัดระยอง</t>
+          <t>มหาวิทยาลัยเชียงใหม่</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>2210101</v>
+        <v>1450100400</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 2 รายการ ดังนี้ (1) รถยนต์โดยสารปรับอากาศ ไม่น้อยกว่า 22 ที่นั่ง แบบขับเคลื่อนด้วยระบบไฟฟ้า จำนวน 2 คัน  (2) รถยนต์โดยสารปรับอากาศ ไม่น้อยกว่า 40 ที่นั่ง แบบขับเคลื่อนด้วยระบบไฟฟ้า จำนวน 2 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=56da4e4f-a0c5-43d9-b499-ef666d60c6ae</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=37e13d96-615f-47ec-98fa-80e208e1c3cd</t>
         </is>
       </c>
     </row>
@@ -9931,7 +9931,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อรายการครุภัณฑ์ระบบบันไดเลื่อน จำนวน 2 รายการ (ตามรายละเอียดแนบท้าย) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=37e13d96-615f-47ec-98fa-80e208e1c3cd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0552eafd-ca4e-4f42-b20b-de0194dda26f</t>
         </is>
       </c>
     </row>
@@ -9966,7 +9966,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อรายการครุภัณฑ์ระบบบันไดเลื่อน จำนวน 2 รายการ (ตามรายละเอียดแนบท้าย) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อรายการครุภัณฑ์ลิฟต์ จำนวน 2 รายการ (ตามรายละเอียดแนบท้าย) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -9981,27 +9981,27 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0552eafd-ca4e-4f42-b20b-de0194dda26f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ccd9e657-8e19-4067-9762-ca2a3da4e3af</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>มหาวิทยาลัยเชียงใหม่</t>
+          <t>กองอำนวยการรักษาความมั่นคงภายใน</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>1450100400</v>
+        <v>119</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อรายการครุภัณฑ์ลิฟต์ จำนวน 2 รายการ (ตามรายละเอียดแนบท้าย) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อวัสดุสำนักงาน ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ สนับสนุน นขต.กอ.รมน. (ส่วนกลาง) ครั้งที่ ๒        ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (วัสดุสำนักงาน)</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ccd9e657-8e19-4067-9762-ca2a3da4e3af</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=245d59e4-9af3-49a2-b319-a01e5d97af03</t>
         </is>
       </c>
     </row>
@@ -10028,17 +10028,15 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>กองอำนวยการรักษาความมั่นคงภายใน</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>0119</t>
-        </is>
+          <t>กองทัพบก</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>204</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อวัสดุสำนักงาน ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ สนับสนุน นขต.กอ.รมน. (ส่วนกลาง) ครั้งที่ ๒        ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อระบบคอมพิวเตอร์และอุปกรณ์ เพื่อสนับสนุนการใช้งานข่าวกรอง ฝขว.ศปก.ทบ. จำนวน ๑๘ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -10048,12 +10046,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>★ (วัสดุสำนักงาน)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=245d59e4-9af3-49a2-b319-a01e5d97af03</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=500e03b5-e6b1-4ade-b4e0-75cee602b358</t>
         </is>
       </c>
     </row>
@@ -10065,17 +10063,15 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>0204</t>
-        </is>
+          <t>กองทัพเรือ</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>205</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อระบบคอมพิวเตอร์และอุปกรณ์ เพื่อสนับสนุนการใช้งานข่าวกรอง ฝขว.ศปก.ทบ. จำนวน ๑๘ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์เครื่องช่วยการศึกษา สาย ยศ.ทร. ในการปรับปรุงอาคาร กพร.ทร.แห่งใหม่ (อาคาร บก.พธ.ทร.เดิม) จำนวน ๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -10085,12 +10081,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=500e03b5-e6b1-4ade-b4e0-75cee602b358</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ee6ef62-218a-4804-b810-005dc5140bcf</t>
         </is>
       </c>
     </row>
@@ -10102,17 +10098,15 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>กองทัพเรือ</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>0205</t>
-        </is>
+          <t>กองบัญชาการกองทัพไทย</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>208</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์เครื่องช่วยการศึกษา สาย ยศ.ทร. ในการปรับปรุงอาคาร กพร.ทร.แห่งใหม่ (อาคาร บก.พธ.ทร.เดิม) จำนวน ๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างผลิตครุภัณฑ์งานบ้านงานครัว พร้อมติดตั้ง ณ ครัวห้องอาหาร ๖/๑ และ ๖/๒ อาคาร ๑ บก.ทท. งบประมาณเพิ่มเติมระหว่างปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -10127,7 +10121,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ee6ef62-218a-4804-b810-005dc5140bcf</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=78cb42b4-9ab9-4e73-b45c-e4dff9b52cfd</t>
         </is>
       </c>
     </row>
@@ -10142,14 +10136,12 @@
           <t>กองบัญชาการกองทัพไทย</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>0208</t>
-        </is>
+      <c r="C278" t="n">
+        <v>208</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างผลิตครุภัณฑ์งานบ้านงานครัว พร้อมติดตั้ง ณ ครัวห้องอาหาร ๖/๑ และ ๖/๒ อาคาร ๑ บก.ทท. งบประมาณเพิ่มเติมระหว่างปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์งานบ้านงานครัว พร้อมติดตั้ง ณ ครัวห้องอาหาร 6/1 และ 6/2 อาคาร 1 บก.ทท. ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -10164,7 +10156,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=78cb42b4-9ab9-4e73-b45c-e4dff9b52cfd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b75a499d-7f24-4c81-8f7c-efa6f5c08c11</t>
         </is>
       </c>
     </row>
@@ -10176,17 +10168,15 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>กองบัญชาการกองทัพไทย</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>0208</t>
-        </is>
+          <t>กรมบัญชีกลาง</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>304</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์งานบ้านงานครัว พร้อมติดตั้ง ณ ครัวห้องอาหาร 6/1 และ 6/2 อาคาร 1 บก.ทท. ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์คอมพิวเตอร์สำหรับห้องประชุม 4 (ห้องปฏิบัติการคอมพิวเตอร์) อาคาร 9 ชั้น 7 กรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -10196,12 +10186,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b75a499d-7f24-4c81-8f7c-efa6f5c08c11</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b3a0480b-6840-48c0-aaba-8b41474df7ba</t>
         </is>
       </c>
     </row>
@@ -10213,17 +10203,15 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>กรมบัญชีกลาง</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>0304</t>
-        </is>
+          <t>กรมสรรพากร</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>307</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์คอมพิวเตอร์สำหรับห้องประชุม 4 (ห้องปฏิบัติการคอมพิวเตอร์) อาคาร 9 ชั้น 7 กรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภท รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -10233,12 +10221,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b3a0480b-6840-48c0-aaba-8b41474df7ba</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2f4faa45-b32a-4d9e-b08c-b82d5884c153</t>
         </is>
       </c>
     </row>
@@ -10250,17 +10238,15 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>กรมสรรพากร</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>0307</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงการพัฒนาสังคมและความมั่นคงของมนุษย์</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>602</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภท รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาและเพิ่มประสิทธิภาพระบบสมุดพกครอบครัวอิเล็กทรอนิกส์ (MSO-Logbook) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -10270,12 +10256,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (สมุด)</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2f4faa45-b32a-4d9e-b08c-b82d5884c153</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1026aa3b-bb28-4576-aadf-d4cf4a678716</t>
         </is>
       </c>
     </row>
@@ -10287,17 +10273,15 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการพัฒนาสังคมและความมั่นคงของมนุษย์</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>0602</t>
-        </is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>704</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาและเพิ่มประสิทธิภาพระบบสมุดพกครอบครัวอิเล็กทรอนิกส์ (MSO-Logbook) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี. หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บพร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -10307,12 +10291,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>★ (สมุด)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1026aa3b-bb28-4576-aadf-d4cf4a678716</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a73013cc-9e52-49f3-b910-4e936275bfe1</t>
         </is>
       </c>
     </row>
@@ -10324,17 +10308,15 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>0704</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>2102</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี. หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บพร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องตรวจสมรรถภาพปอดด้วยเครื่องคอมพิวเตอร์ จำนวน ๓ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -10344,12 +10326,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a73013cc-9e52-49f3-b910-4e936275bfe1</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=10b04086-63b0-4d42-95a0-904c88c6e41f</t>
         </is>
       </c>
     </row>
@@ -10364,14 +10346,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C284" t="n">
+        <v>2102</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องตรวจสมรรถภาพปอดด้วยเครื่องคอมพิวเตอร์ จำนวน ๓ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องให้การรักษาอาการปวดและกระตุ้นเซลล์ประสาทส่วนปลายด้วยสนามแม่เหล็กไฟฟ้า (PMS) สำหรับโรงพยาบาลกงไกรลาศ จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -10381,12 +10361,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=10b04086-63b0-4d42-95a0-904c88c6e41f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4a641a15-b74d-402f-ab9c-60aa9fb564a7</t>
         </is>
       </c>
     </row>
@@ -10401,14 +10381,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C285" t="n">
+        <v>2102</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องให้การรักษาอาการปวดและกระตุ้นเซลล์ประสาทส่วนปลายด้วยสนามแม่เหล็กไฟฟ้า (PMS) สำหรับโรงพยาบาลกงไกรลาศ จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องเอกซเรย์ทั่วไปขนาดไม่น้อยกว่า ๑,๐๐๐ mA. แบบแขวนเพดาน สำหรับโรงพยาบาลศรีนคร จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -10423,7 +10401,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4a641a15-b74d-402f-ab9c-60aa9fb564a7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a37d5071-0a7d-4d2f-84fe-d0f774026ac5</t>
         </is>
       </c>
     </row>
@@ -10438,14 +10416,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C286" t="n">
+        <v>2102</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องเอกซเรย์ทั่วไปขนาดไม่น้อยกว่า ๑,๐๐๐ mA. แบบแขวนเพดาน สำหรับโรงพยาบาลศรีนคร จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูง ชนิด 2 หัวตรวจ สำหรับโรงพยาบาลทุ่งเสลี่ยม จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -10460,7 +10436,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a37d5071-0a7d-4d2f-84fe-d0f774026ac5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9aa030b2-096a-4e59-a881-6f2d1737ed5f</t>
         </is>
       </c>
     </row>
@@ -10475,14 +10451,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C287" t="n">
+        <v>2102</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูง ชนิด 2 หัวตรวจ สำหรับโรงพยาบาลทุ่งเสลี่ยม จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องตรวจอวัยวะภายในด้วยเครื่องเสียงความถี่สูงระดับความคมชัดสูง ๓ หัวตรวจ ชนิดเคลื่อนย้ายได้ สำหรับโรงพยาบาลบ้านด่านลานหอย จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -10497,7 +10471,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9aa030b2-096a-4e59-a881-6f2d1737ed5f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afe2fdf2-3a41-4668-9d7c-c5718e064adc</t>
         </is>
       </c>
     </row>
@@ -10512,14 +10486,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C288" t="n">
+        <v>2102</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องตรวจอวัยวะภายในด้วยเครื่องเสียงความถี่สูงระดับความคมชัดสูง ๓ หัวตรวจ ชนิดเคลื่อนย้ายได้ สำหรับโรงพยาบาลบ้านด่านลานหอย จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องให้การรักษาทางกายภาพด้วยคลื่นแม่เหล็กไฟฟ้า  สำหรับโรงพยาบาลศรีสัชนาลัย จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -10534,7 +10506,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afe2fdf2-3a41-4668-9d7c-c5718e064adc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1eeea1f2-b27e-42f8-b37f-8cd9d17e4bb2</t>
         </is>
       </c>
     </row>
@@ -10549,14 +10521,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C289" t="n">
+        <v>2102</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องให้การรักษาทางกายภาพด้วยคลื่นแม่เหล็กไฟฟ้า  สำหรับโรงพยาบาลศรีสัชนาลัย จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนในเลือด ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 5 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -10571,7 +10541,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1eeea1f2-b27e-42f8-b37f-8cd9d17e4bb2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a54472bd-463e-4919-a81a-3790d34b7b27</t>
         </is>
       </c>
     </row>
@@ -10586,14 +10556,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C290" t="n">
+        <v>2102</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนในเลือด ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 5 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องผลิตออกซิเจน ขนาด 10 ลิตร จำนวน 39 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย-กัมพูชา ปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -10608,7 +10576,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a54472bd-463e-4919-a81a-3790d34b7b27</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1bc9002a-e6eb-4764-add9-7faccb225729</t>
         </is>
       </c>
     </row>
@@ -10623,14 +10591,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C291" t="n">
+        <v>2102</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องผลิตออกซิเจน ขนาด 10 ลิตร จำนวน 39 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย-กัมพูชา ปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ รายการเตียงผ่าตัดศัลยกรรมออร์โธปิดิกส์ จำนวน ๒ เตียง สำหรับโรงพยาบาลลับแลและโรงพยาบาลพิชัย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -10645,7 +10611,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1bc9002a-e6eb-4764-add9-7faccb225729</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=30fcc177-cd34-422d-af09-c8aa1f9cb406</t>
         </is>
       </c>
     </row>
@@ -10660,14 +10626,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C292" t="n">
+        <v>2102</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ รายการเตียงผ่าตัดศัลยกรรมออร์โธปิดิกส์ จำนวน ๒ เตียง สำหรับโรงพยาบาลลับแลและโรงพยาบาลพิชัย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างปรับปรุงสายสัญญาณอินเทอร์เน็ตอาคาร 1 และสายไฟฟ้าอาคาร 9 สำนักงานปลัดกระทรวงสาธารณสุข ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -10677,12 +10641,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (สายสัญญาณ)</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=30fcc177-cd34-422d-af09-c8aa1f9cb406</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afd11c75-a6db-43e5-a0f3-035fadd64936</t>
         </is>
       </c>
     </row>
@@ -10697,14 +10661,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C293" t="n">
+        <v>2102</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างปรับปรุงสายสัญญาณอินเทอร์เน็ตอาคาร 1 และสายไฟฟ้าอาคาร 9 สำนักงานปลัดกระทรวงสาธารณสุข ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องตรวจสมรรถภาพปอดด้วยเครื่องคอมพิวเตอร์ จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -10714,12 +10676,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>★ (สายสัญญาณ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afd11c75-a6db-43e5-a0f3-035fadd64936</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=de38cd7a-4053-4ddd-a509-d16c262cf02a</t>
         </is>
       </c>
     </row>
@@ -10731,17 +10693,15 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+          <t>กรมอนามัย</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>2109</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องตรวจสมรรถภาพปอดด้วยเครื่องคอมพิวเตอร์ จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ทางการแพทย์ เครื่องวิเคราะห์องค์ประกอบร่างกายแบบแยกส่วนของโรงพยาบาล ส่งเสริมสุขภาพ ศูนย์อนามัยที่ ๖ ชลบุรี ปีงบประมาณ พ.ศ. ๒๕๗๐ จำนวน ๑ รายการ ( จำนวน ๒ เครื่อง) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -10751,34 +10711,34 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=de38cd7a-4053-4ddd-a509-d16c262cf02a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=adb22b5a-03b6-4872-8f4a-1ba04569341a</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>กรมอนามัย</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>0204</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ทางการแพทย์ เครื่องวิเคราะห์องค์ประกอบร่างกายแบบแยกส่วนของโรงพยาบาล ส่งเสริมสุขภาพ ศูนย์อนามัยที่ ๖ ชลบุรี ปีงบประมาณ พ.ศ. ๒๕๗๐ จำนวน ๑ รายการ ( จำนวน ๒ เครื่อง) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อระบบคอมพิวเตอร์และอุปกรณ์ เพื่อสนับสนุนการใช้งานข่าวกรอง ฝขว.ศปก.ทบ. จำนวน ๑๘ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -10788,12 +10748,419 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=72ad4c14-ee7b-4d77-ba81-e913d7b8443f</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>กรมบัญชีกลาง</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>0304</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องพิมพ์ Multifunction และเครื่องสแกนเนอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>★ (เครื่องพิมพ์, เครื่องสแกนเนอร์)</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9b179ddf-4f24-4f03-b0f6-03f51948ebb5</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>0704</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อเครื่องปรับอากาศแบบแยกส่วน (ราคารวมค่าติดตั้ง) แบบตั้งพื้นหรือแบบแขวน(ระบบ Inverter) ขนาดไม่ต่ำกว่า 36,000 บีทียู จำนวน 13 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>★ (เครื่องปรับอากาศ)</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4fb39309-585d-4309-976d-68ffb35f0d13</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้องานจัดซื้อครุภัณฑ์สำนักงาน จำนวน 21 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b933c10a-3d2b-48e7-8733-9ad758013b0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>0909</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์โครงการเพิ่มประสิทธิภาพการตอบโต้สถานการณ์เฝ้าระวังและผลักดันช้างป่าออกนอกพื้นที่อนุรักษ์ (ครั้งที่ 2) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
           <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=adb22b5a-03b6-4872-8f4a-1ba04569341a</t>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1a53dd55-3e32-4691-875b-bed5b618267e</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>สำนักงานนโยบายและแผนทรัพยากรธรรมชาติและสิ่งแวดล้อม</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>0911</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อวัสดุคอมพิวเตอร์ จำนวน ๑๐๘ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4e0b8c2a-5098-46b1-9662-a1a768115472</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>กรมพินิจและคุ้มครองเด็กและเยาวชน</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ รายการเครื่องรับส่งวิทยุ ระบบ VHF FM ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=50900d02-0860-49e6-924a-4ce90e349f51</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>กรมพินิจและคุ้มครองเด็กและเยาวชน</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์สำรวจ จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=27e6a7f1-e8b3-4713-a4cf-8e1017c95588</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง สำหรับโรงพยาบาลทุ่งเสลี่ยมและโรงพยาบาลคีรีมาศ จำนวน 2 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b637756a-f1db-43ca-8088-8bb65d244bc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ ยูนิตทำฟัน สำหรับโรงพยาบาลศรีนคร และโรงพยาบาลส่งเสริมสุขภาพตำบลวังทอง จำนวน 2 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=47778085-c309-4c79-a29b-e1847ea7456e</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องช่วยนวดหัวใจและฟื้นคืนชีพผู้ป่วยอัติโนมัติ สำหรับโรงพยาบาลทุ่งเสลี่ยม จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=772263bc-9e51-4b12-87ea-8b731c25646a</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>กรมสุขภาพจิต</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>2108</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๖ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a2d6c763-d384-410d-8363-44f98d922641</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202609.xlsx
+++ b/Backup/eGP_Monthly_Main_202609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G306"/>
+  <dimension ref="A1:G322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10028,15 +10028,15 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กองทัพเรือ</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อระบบคอมพิวเตอร์และอุปกรณ์ เพื่อสนับสนุนการใช้งานข่าวกรอง ฝขว.ศปก.ทบ. จำนวน ๑๘ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์เครื่องช่วยการศึกษา สาย ยศ.ทร. ในการปรับปรุงอาคาร กพร.ทร.แห่งใหม่ (อาคาร บก.พธ.ทร.เดิม) จำนวน ๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=500e03b5-e6b1-4ade-b4e0-75cee602b358</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ee6ef62-218a-4804-b810-005dc5140bcf</t>
         </is>
       </c>
     </row>
@@ -10063,15 +10063,15 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>กองทัพเรือ</t>
+          <t>กองบัญชาการกองทัพไทย</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์เครื่องช่วยการศึกษา สาย ยศ.ทร. ในการปรับปรุงอาคาร กพร.ทร.แห่งใหม่ (อาคาร บก.พธ.ทร.เดิม) จำนวน ๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างผลิตครุภัณฑ์งานบ้านงานครัว พร้อมติดตั้ง ณ ครัวห้องอาหาร ๖/๑ และ ๖/๒ อาคาร ๑ บก.ทท. งบประมาณเพิ่มเติมระหว่างปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ee6ef62-218a-4804-b810-005dc5140bcf</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=78cb42b4-9ab9-4e73-b45c-e4dff9b52cfd</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างผลิตครุภัณฑ์งานบ้านงานครัว พร้อมติดตั้ง ณ ครัวห้องอาหาร ๖/๑ และ ๖/๒ อาคาร ๑ บก.ทท. งบประมาณเพิ่มเติมระหว่างปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์งานบ้านงานครัว พร้อมติดตั้ง ณ ครัวห้องอาหาร 6/1 และ 6/2 อาคาร 1 บก.ทท. ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=78cb42b4-9ab9-4e73-b45c-e4dff9b52cfd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b75a499d-7f24-4c81-8f7c-efa6f5c08c11</t>
         </is>
       </c>
     </row>
@@ -10133,15 +10133,15 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>กองบัญชาการกองทัพไทย</t>
+          <t>กรมบัญชีกลาง</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>208</v>
+        <v>304</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์งานบ้านงานครัว พร้อมติดตั้ง ณ ครัวห้องอาหาร 6/1 และ 6/2 อาคาร 1 บก.ทท. ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์คอมพิวเตอร์สำหรับห้องประชุม 4 (ห้องปฏิบัติการคอมพิวเตอร์) อาคาร 9 ชั้น 7 กรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -10151,12 +10151,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b75a499d-7f24-4c81-8f7c-efa6f5c08c11</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b3a0480b-6840-48c0-aaba-8b41474df7ba</t>
         </is>
       </c>
     </row>
@@ -10168,15 +10168,15 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>กรมบัญชีกลาง</t>
+          <t>กรมสรรพากร</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์คอมพิวเตอร์สำหรับห้องประชุม 4 (ห้องปฏิบัติการคอมพิวเตอร์) อาคาร 9 ชั้น 7 กรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภท รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b3a0480b-6840-48c0-aaba-8b41474df7ba</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2f4faa45-b32a-4d9e-b08c-b82d5884c153</t>
         </is>
       </c>
     </row>
@@ -10203,15 +10203,15 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>กรมสรรพากร</t>
+          <t>สำนักงานปลัดกระทรวงการพัฒนาสังคมและความมั่นคงของมนุษย์</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>307</v>
+        <v>602</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภท รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาและเพิ่มประสิทธิภาพระบบสมุดพกครอบครัวอิเล็กทรอนิกส์ (MSO-Logbook) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (สมุด)</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2f4faa45-b32a-4d9e-b08c-b82d5884c153</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1026aa3b-bb28-4576-aadf-d4cf4a678716</t>
         </is>
       </c>
     </row>
@@ -10238,15 +10238,15 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการพัฒนาสังคมและความมั่นคงของมนุษย์</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>602</v>
+        <v>704</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาและเพิ่มประสิทธิภาพระบบสมุดพกครอบครัวอิเล็กทรอนิกส์ (MSO-Logbook) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี. หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บพร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>★ (สมุด)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1026aa3b-bb28-4576-aadf-d4cf4a678716</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a73013cc-9e52-49f3-b910-4e936275bfe1</t>
         </is>
       </c>
     </row>
@@ -10273,15 +10273,15 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>704</v>
+        <v>2102</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี. หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บพร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องตรวจสมรรถภาพปอดด้วยเครื่องคอมพิวเตอร์ จำนวน ๓ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a73013cc-9e52-49f3-b910-4e936275bfe1</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=10b04086-63b0-4d42-95a0-904c88c6e41f</t>
         </is>
       </c>
     </row>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องตรวจสมรรถภาพปอดด้วยเครื่องคอมพิวเตอร์ จำนวน ๓ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องให้การรักษาอาการปวดและกระตุ้นเซลล์ประสาทส่วนปลายด้วยสนามแม่เหล็กไฟฟ้า (PMS) สำหรับโรงพยาบาลกงไกรลาศ จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -10326,12 +10326,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=10b04086-63b0-4d42-95a0-904c88c6e41f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4a641a15-b74d-402f-ab9c-60aa9fb564a7</t>
         </is>
       </c>
     </row>
@@ -10351,7 +10351,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องให้การรักษาอาการปวดและกระตุ้นเซลล์ประสาทส่วนปลายด้วยสนามแม่เหล็กไฟฟ้า (PMS) สำหรับโรงพยาบาลกงไกรลาศ จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องเอกซเรย์ทั่วไปขนาดไม่น้อยกว่า ๑,๐๐๐ mA. แบบแขวนเพดาน สำหรับโรงพยาบาลศรีนคร จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4a641a15-b74d-402f-ab9c-60aa9fb564a7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a37d5071-0a7d-4d2f-84fe-d0f774026ac5</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องเอกซเรย์ทั่วไปขนาดไม่น้อยกว่า ๑,๐๐๐ mA. แบบแขวนเพดาน สำหรับโรงพยาบาลศรีนคร จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูง ชนิด 2 หัวตรวจ สำหรับโรงพยาบาลทุ่งเสลี่ยม จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a37d5071-0a7d-4d2f-84fe-d0f774026ac5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9aa030b2-096a-4e59-a881-6f2d1737ed5f</t>
         </is>
       </c>
     </row>
@@ -10421,7 +10421,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูง ชนิด 2 หัวตรวจ สำหรับโรงพยาบาลทุ่งเสลี่ยม จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องตรวจอวัยวะภายในด้วยเครื่องเสียงความถี่สูงระดับความคมชัดสูง ๓ หัวตรวจ ชนิดเคลื่อนย้ายได้ สำหรับโรงพยาบาลบ้านด่านลานหอย จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9aa030b2-096a-4e59-a881-6f2d1737ed5f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afe2fdf2-3a41-4668-9d7c-c5718e064adc</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องตรวจอวัยวะภายในด้วยเครื่องเสียงความถี่สูงระดับความคมชัดสูง ๓ หัวตรวจ ชนิดเคลื่อนย้ายได้ สำหรับโรงพยาบาลบ้านด่านลานหอย จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องให้การรักษาทางกายภาพด้วยคลื่นแม่เหล็กไฟฟ้า  สำหรับโรงพยาบาลศรีสัชนาลัย จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afe2fdf2-3a41-4668-9d7c-c5718e064adc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1eeea1f2-b27e-42f8-b37f-8cd9d17e4bb2</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องให้การรักษาทางกายภาพด้วยคลื่นแม่เหล็กไฟฟ้า  สำหรับโรงพยาบาลศรีสัชนาลัย จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนในเลือด ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 5 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1eeea1f2-b27e-42f8-b37f-8cd9d17e4bb2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a54472bd-463e-4919-a81a-3790d34b7b27</t>
         </is>
       </c>
     </row>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนในเลือด ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 5 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องผลิตออกซิเจน ขนาด 10 ลิตร จำนวน 39 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย-กัมพูชา ปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a54472bd-463e-4919-a81a-3790d34b7b27</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1bc9002a-e6eb-4764-add9-7faccb225729</t>
         </is>
       </c>
     </row>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องผลิตออกซิเจน ขนาด 10 ลิตร จำนวน 39 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย-กัมพูชา ปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ รายการเตียงผ่าตัดศัลยกรรมออร์โธปิดิกส์ จำนวน ๒ เตียง สำหรับโรงพยาบาลลับแลและโรงพยาบาลพิชัย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1bc9002a-e6eb-4764-add9-7faccb225729</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=30fcc177-cd34-422d-af09-c8aa1f9cb406</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ รายการเตียงผ่าตัดศัลยกรรมออร์โธปิดิกส์ จำนวน ๒ เตียง สำหรับโรงพยาบาลลับแลและโรงพยาบาลพิชัย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างปรับปรุงสายสัญญาณอินเทอร์เน็ตอาคาร 1 และสายไฟฟ้าอาคาร 9 สำนักงานปลัดกระทรวงสาธารณสุข ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -10606,12 +10606,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (สายสัญญาณ)</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=30fcc177-cd34-422d-af09-c8aa1f9cb406</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afd11c75-a6db-43e5-a0f3-035fadd64936</t>
         </is>
       </c>
     </row>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างปรับปรุงสายสัญญาณอินเทอร์เน็ตอาคาร 1 และสายไฟฟ้าอาคาร 9 สำนักงานปลัดกระทรวงสาธารณสุข ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องตรวจสมรรถภาพปอดด้วยเครื่องคอมพิวเตอร์ จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -10641,12 +10641,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>★ (สายสัญญาณ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afd11c75-a6db-43e5-a0f3-035fadd64936</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=de38cd7a-4053-4ddd-a509-d16c262cf02a</t>
         </is>
       </c>
     </row>
@@ -10658,15 +10658,15 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมอนามัย</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>2102</v>
+        <v>2109</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องตรวจสมรรถภาพปอดด้วยเครื่องคอมพิวเตอร์ จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ทางการแพทย์ เครื่องวิเคราะห์องค์ประกอบร่างกายแบบแยกส่วนของโรงพยาบาล ส่งเสริมสุขภาพ ศูนย์อนามัยที่ ๖ ชลบุรี ปีงบประมาณ พ.ศ. ๒๕๗๐ จำนวน ๑ รายการ ( จำนวน ๒ เครื่อง) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -10676,32 +10676,32 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=de38cd7a-4053-4ddd-a509-d16c262cf02a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=adb22b5a-03b6-4872-8f4a-1ba04569341a</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>กรมอนามัย</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>2109</v>
+        <v>204</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ทางการแพทย์ เครื่องวิเคราะห์องค์ประกอบร่างกายแบบแยกส่วนของโรงพยาบาล ส่งเสริมสุขภาพ ศูนย์อนามัยที่ ๖ ชลบุรี ปีงบประมาณ พ.ศ. ๒๕๗๐ จำนวน ๑ รายการ ( จำนวน ๒ เครื่อง) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อระบบคอมพิวเตอร์และอุปกรณ์ เพื่อสนับสนุนการใช้งานข่าวกรอง ฝขว.ศปก.ทบ. จำนวน ๑๘ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=adb22b5a-03b6-4872-8f4a-1ba04569341a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=72ad4c14-ee7b-4d77-ba81-e913d7b8443f</t>
         </is>
       </c>
     </row>
@@ -10728,17 +10728,15 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>0204</t>
-        </is>
+          <t>กรมบัญชีกลาง</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>304</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อระบบคอมพิวเตอร์และอุปกรณ์ เพื่อสนับสนุนการใช้งานข่าวกรอง ฝขว.ศปก.ทบ. จำนวน ๑๘ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องพิมพ์ Multifunction และเครื่องสแกนเนอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -10748,12 +10746,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องพิมพ์, เครื่องสแกนเนอร์)</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=72ad4c14-ee7b-4d77-ba81-e913d7b8443f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9b179ddf-4f24-4f03-b0f6-03f51948ebb5</t>
         </is>
       </c>
     </row>
@@ -10765,17 +10763,15 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>กรมบัญชีกลาง</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>0304</t>
-        </is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>704</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องพิมพ์ Multifunction และเครื่องสแกนเนอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อเครื่องปรับอากาศแบบแยกส่วน (ราคารวมค่าติดตั้ง) แบบตั้งพื้นหรือแบบแขวน(ระบบ Inverter) ขนาดไม่ต่ำกว่า 36,000 บีทียู จำนวน 13 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -10785,12 +10781,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>★ (เครื่องพิมพ์, เครื่องสแกนเนอร์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9b179ddf-4f24-4f03-b0f6-03f51948ebb5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4fb39309-585d-4309-976d-68ffb35f0d13</t>
         </is>
       </c>
     </row>
@@ -10802,17 +10798,15 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>0704</t>
-        </is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>806</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อเครื่องปรับอากาศแบบแยกส่วน (ราคารวมค่าติดตั้ง) แบบตั้งพื้นหรือแบบแขวน(ระบบ Inverter) ขนาดไม่ต่ำกว่า 36,000 บีทียู จำนวน 13 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้องานจัดซื้อครุภัณฑ์สำนักงาน จำนวน 21 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -10822,12 +10816,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4fb39309-585d-4309-976d-68ffb35f0d13</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b933c10a-3d2b-48e7-8733-9ad758013b0a</t>
         </is>
       </c>
     </row>
@@ -10839,17 +10833,15 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>0806</t>
-        </is>
+          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>909</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้องานจัดซื้อครุภัณฑ์สำนักงาน จำนวน 21 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์โครงการเพิ่มประสิทธิภาพการตอบโต้สถานการณ์เฝ้าระวังและผลักดันช้างป่าออกนอกพื้นที่อนุรักษ์ (ครั้งที่ 2) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -10859,12 +10851,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b933c10a-3d2b-48e7-8733-9ad758013b0a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1a53dd55-3e32-4691-875b-bed5b618267e</t>
         </is>
       </c>
     </row>
@@ -10876,17 +10868,15 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>0909</t>
-        </is>
+          <t>สำนักงานนโยบายและแผนทรัพยากรธรรมชาติและสิ่งแวดล้อม</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>911</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์โครงการเพิ่มประสิทธิภาพการตอบโต้สถานการณ์เฝ้าระวังและผลักดันช้างป่าออกนอกพื้นที่อนุรักษ์ (ครั้งที่ 2) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อวัสดุคอมพิวเตอร์ จำนวน ๑๐๘ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -10896,12 +10886,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1a53dd55-3e32-4691-875b-bed5b618267e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4e0b8c2a-5098-46b1-9662-a1a768115472</t>
         </is>
       </c>
     </row>
@@ -10913,17 +10903,15 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>สำนักงานนโยบายและแผนทรัพยากรธรรมชาติและสิ่งแวดล้อม</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>0911</t>
-        </is>
+          <t>กรมพินิจและคุ้มครองเด็กและเยาวชน</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>1606</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อวัสดุคอมพิวเตอร์ จำนวน ๑๐๘ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ รายการเครื่องรับส่งวิทยุ ระบบ VHF FM ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -10933,12 +10921,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4e0b8c2a-5098-46b1-9662-a1a768115472</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=50900d02-0860-49e6-924a-4ce90e349f51</t>
         </is>
       </c>
     </row>
@@ -10953,14 +10941,12 @@
           <t>กรมพินิจและคุ้มครองเด็กและเยาวชน</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>1606</t>
-        </is>
+      <c r="C301" t="n">
+        <v>1606</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ รายการเครื่องรับส่งวิทยุ ระบบ VHF FM ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์สำรวจ จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -10975,7 +10961,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=50900d02-0860-49e6-924a-4ce90e349f51</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=27e6a7f1-e8b3-4713-a4cf-8e1017c95588</t>
         </is>
       </c>
     </row>
@@ -10987,17 +10973,15 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>กรมพินิจและคุ้มครองเด็กและเยาวชน</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>1606</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>2102</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์สำรวจ จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง สำหรับโรงพยาบาลทุ่งเสลี่ยมและโรงพยาบาลคีรีมาศ จำนวน 2 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -11012,7 +10996,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=27e6a7f1-e8b3-4713-a4cf-8e1017c95588</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b637756a-f1db-43ca-8088-8bb65d244bc6</t>
         </is>
       </c>
     </row>
@@ -11027,14 +11011,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C303" t="n">
+        <v>2102</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง สำหรับโรงพยาบาลทุ่งเสลี่ยมและโรงพยาบาลคีรีมาศ จำนวน 2 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ ยูนิตทำฟัน สำหรับโรงพยาบาลศรีนคร และโรงพยาบาลส่งเสริมสุขภาพตำบลวังทอง จำนวน 2 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -11049,7 +11031,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b637756a-f1db-43ca-8088-8bb65d244bc6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=47778085-c309-4c79-a29b-e1847ea7456e</t>
         </is>
       </c>
     </row>
@@ -11064,14 +11046,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C304" t="n">
+        <v>2102</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ ยูนิตทำฟัน สำหรับโรงพยาบาลศรีนคร และโรงพยาบาลส่งเสริมสุขภาพตำบลวังทอง จำนวน 2 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องช่วยนวดหัวใจและฟื้นคืนชีพผู้ป่วยอัติโนมัติ สำหรับโรงพยาบาลทุ่งเสลี่ยม จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -11086,7 +11066,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=47778085-c309-4c79-a29b-e1847ea7456e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=772263bc-9e51-4b12-87ea-8b731c25646a</t>
         </is>
       </c>
     </row>
@@ -11098,17 +11078,15 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+          <t>กรมสุขภาพจิต</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>2108</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องช่วยนวดหัวใจและฟื้นคืนชีพผู้ป่วยอัติโนมัติ สำหรับโรงพยาบาลทุ่งเสลี่ยม จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๖ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -11118,34 +11096,34 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=772263bc-9e51-4b12-87ea-8b731c25646a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a2d6c763-d384-410d-8363-44f98d922641</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>กรมสุขภาพจิต</t>
+          <t>สำนักงานคณะกรรมการนโยบายที่ดินแห่งชาติ</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>0142</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๖ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องพิมพ์ ขนาด A0 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -11155,12 +11133,604 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
+          <t>★ (เครื่องพิมพ์)</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b524d474-1d00-4330-872e-db4cd85cc6a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการนโยบายที่ดินแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>0142</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์เพิ่มเติม ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
           <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a2d6c763-d384-410d-8363-44f98d922641</t>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ef813d9a-008b-48f6-807d-47af8175bf30</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>กองทัพบก</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>0204</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ประจำอาคาร จำนวน 4 รายการ เพื่อใช้ในงานซ่อมปรับปรุงอาคารแฟลตนายทหารชั้นประทวนจุ 56 ครอบครัว หมายเลข 423/29 (ป.116) ของ กองพันทหารช่างที่ 112 กรมทหารช่างที่ 1 รักษาพระองค์ เป็นแผนงานเพิ่มเติมระหว่างปีงบประมาณ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c57e6e7d-84ff-41ad-986d-268777a7d6c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงเกษตรและสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>0702</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างดูแลบำรุงรักษาระบบคอมพิวเตอร์และเครือข่าย สำนักงานปลัดกระทรวงเกษตรและสหกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=968489c9-089d-4081-9d28-c41ee46b7166</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>กรมชลประทาน</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>0703</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างจัดทำและติดตั้งบานระบายตรงชนิดสองบาน ขนาด 6.00x5.00 เมตร พร้อมจัดหาและติดตั้งเกียร์มอเตอร์ไฟฟ้า ขนาด 3 กิโลวัตต์ 200 รอบต่อนาทีสำหรับเครื่องกว้าน 12 ตัน และอุปกรณ์อื่นๆ จำนวน 4 รายการ ปตร.คลองปากง่าม ตำบลหัวสะพาน อำเภอเมืองเพชรบุรี จังหวัดเพชรบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>★ (มอเตอร์)</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5e9f210c-ac94-45bc-bdd6-fc5490c2019e</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>กรมประมง</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>0705</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ เครื่องกำเนิดไฟฟ้า ขนาด ๕๐๐ กิโลวัตต์ พร้อมตู้ควบคุม จำนวน ๑ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fbcaead1-29c0-4ccc-b4f3-c6029e986951</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>กรมการขนส่งทางบก</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>0804</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาคอมพิวเตอร์แม่ข่ายและซอฟต์แวร์ระบบ Smart Bus Terminal เพื่ออำนวยความสะดวกและปลอดภัยในการโดยสารด้วยรถสาธารณะ ด้วยการใช้เทคโนโลยีสารสนเทศ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ซอฟต์แวร์)</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9f2eadf5-f0d6-454d-92ce-830a13a9368f</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>กรมท่าอากาศยาน</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้ออุปกรณ์เครือข่ายและอุปกรณ์ความมั่นคงปลอดภัยและเสถียรภาพการ ณ ท่าอากาศยาน ๒๖ แห่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>★ (อุปกรณ์เครือข่าย)</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3224492-d946-48af-92fc-ba14c8c18c21</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน 13 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8b49083c-95ec-4358-b45b-4c5ea43d22bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>กรมทรัพยากรน้ำบาดาล</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>0907</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้ออุปกรณ์เพื่อซ่อมแซมระบบปรับปรุงคุณภาพน้ำดื่มสะอาด จำนวน ๒๙๙ ชุด โครงการศึกษา ประเมินความเสียหายและฟื้นฟูเพื่อการพัฒนาและอนุรักษ์ทรัพยากรน้ำบาดาลในพื้นที่ประสบมหาอุทกภัยภาคใต้ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>★ (น้ำดื่ม)</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=57c8fe20-b280-4b2e-8fc6-c8ac87d2d313</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>กรมการค้าภายใน</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้ออุปกรณ์กระจายสัญญาณแบบไรัสาย พร้อมติดตั้ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=16d1d6a0-874d-40e3-b570-9428b853237b</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>กรมพัฒนาธุรกิจการค้า</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>1308</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องคอมพิวเตอร์และอุปกรณ์ทดแทน ปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0026be70-8492-4e93-b52e-fe570444ea01</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>กรมการปกครอง</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a853a12e-1590-4be6-a161-1851415f448c</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมการปกครองท้องถิ่น</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>1508</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อการจัดซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 7 รายการ ประจำปีงบประมาณ พ.ศ. 2570 ของสำนักงานท้องถิ่นจังหวัดอุทัยธานี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=398251c5-ded9-4f36-ab4f-2b062cabfa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>กรมพินิจและคุ้มครองเด็กและเยาวชน</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดระดับคาร์บอนมอนออกไซด์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ea8b731b-a755-4b4b-b550-259b6b24af7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>กรมพัฒนาฝีมือแรงงาน</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>1704</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ที่มีราคาต่อหน่วยต่ำกว่า 1 ล่้านบาท ครุภัณฑ์ไฟฟ้าและวิทยุ (ระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop)  ขนาด 3 เฟส 15 กิโลวัตต์ ตำบลบ้านโปร่ง อำเภอหนองโดน จังหวัดสระบุรี จำนวน 1 ระบบ และระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop) ขนาด 3 เฟส 20 กิโลวัตต์ ตำบลบ้านโปร่ง อำเภอหนองโดน จังหวัดสระบุรี จำนวน 1 ระบบ)  ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5a36822b-e8f7-4a53-941e-49ef30ea4c9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ จำนวน ๓ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2c7df3d6-3d32-4bd7-9ecd-1c6edc996677</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202609.xlsx
+++ b/Backup/eGP_Monthly_Main_202609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G322"/>
+  <dimension ref="A1:G352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11116,10 +11116,8 @@
           <t>สำนักงานคณะกรรมการนโยบายที่ดินแห่งชาติ</t>
         </is>
       </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>0142</t>
-        </is>
+      <c r="C306" t="n">
+        <v>142</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -11153,10 +11151,8 @@
           <t>สำนักงานคณะกรรมการนโยบายที่ดินแห่งชาติ</t>
         </is>
       </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>0142</t>
-        </is>
+      <c r="C307" t="n">
+        <v>142</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -11190,10 +11186,8 @@
           <t>กองทัพบก</t>
         </is>
       </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>0204</t>
-        </is>
+      <c r="C308" t="n">
+        <v>204</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -11227,10 +11221,8 @@
           <t>สำนักงานปลัดกระทรวงเกษตรและสหกรณ์</t>
         </is>
       </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>0702</t>
-        </is>
+      <c r="C309" t="n">
+        <v>702</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -11264,10 +11256,8 @@
           <t>กรมชลประทาน</t>
         </is>
       </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>0703</t>
-        </is>
+      <c r="C310" t="n">
+        <v>703</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -11301,10 +11291,8 @@
           <t>กรมประมง</t>
         </is>
       </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>0705</t>
-        </is>
+      <c r="C311" t="n">
+        <v>705</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -11338,10 +11326,8 @@
           <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>0804</t>
-        </is>
+      <c r="C312" t="n">
+        <v>804</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -11375,10 +11361,8 @@
           <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
+      <c r="C313" t="n">
+        <v>805</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -11412,10 +11396,8 @@
           <t>กรมทางหลวง</t>
         </is>
       </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>0806</t>
-        </is>
+      <c r="C314" t="n">
+        <v>806</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -11449,10 +11431,8 @@
           <t>กรมทรัพยากรน้ำบาดาล</t>
         </is>
       </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>0907</t>
-        </is>
+      <c r="C315" t="n">
+        <v>907</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -11486,10 +11466,8 @@
           <t>กรมการค้าภายใน</t>
         </is>
       </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>1304</t>
-        </is>
+      <c r="C316" t="n">
+        <v>1304</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -11523,10 +11501,8 @@
           <t>กรมพัฒนาธุรกิจการค้า</t>
         </is>
       </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>1308</t>
-        </is>
+      <c r="C317" t="n">
+        <v>1308</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -11560,10 +11536,8 @@
           <t>กรมการปกครอง</t>
         </is>
       </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>1503</t>
-        </is>
+      <c r="C318" t="n">
+        <v>1503</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -11597,10 +11571,8 @@
           <t>กรมส่งเสริมการปกครองท้องถิ่น</t>
         </is>
       </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>1508</t>
-        </is>
+      <c r="C319" t="n">
+        <v>1508</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -11634,10 +11606,8 @@
           <t>กรมพินิจและคุ้มครองเด็กและเยาวชน</t>
         </is>
       </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>1606</t>
-        </is>
+      <c r="C320" t="n">
+        <v>1606</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -11671,10 +11641,8 @@
           <t>กรมพัฒนาฝีมือแรงงาน</t>
         </is>
       </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>1704</t>
-        </is>
+      <c r="C321" t="n">
+        <v>1704</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -11708,29 +11676,1137 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C322" t="inlineStr">
+      <c r="C322" t="n">
+        <v>2102</v>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ จำนวน ๓ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2c7df3d6-3d32-4bd7-9ecd-1c6edc996677</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>กองบัญชาการกองทัพไทย</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างผลิตครุภัณฑ์งานบ้านงานครัว พร้อมติดตั้ง ณ ครัวห้องอาหาร ๖/๑ และ ๖/๒ อาคาร ๑ บก.ทท. งบประมาณเพิ่มเติมระหว่างปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0206dc5f-1749-42e1-926b-c40fa1b0790b</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>กองบัญชาการกองทัพไทย</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์งานบ้านงานครัว ณ ครัวห้องอาหาร 6/1 และ 6/2 อาคาร 1 บก.ทท. งบประมาณเพิ่มเติมระหว่างปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cc985455-9962-4480-9fe9-d808bf294cdd</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงการคลัง</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>0302</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างการจ้างเหมาบริการบำรุงรักษา ซ่อมแซม และแก้ไขอุปกรณ์เครือข่ายและระบบประชุมทางไกล ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>★ (อุปกรณ์เครือข่าย, ระบบประชุมทางไกล)</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9befc47f-3a0c-485e-a092-61c7ce73b9c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>สำนักงานบริหารหนี้สาธารณะ</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>0309</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดหาหน่วยความจำหลัก (RAM) สำหรับเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, หน่วยความจำ)</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d1f5fe37-48d4-46a5-a2a5-1e42e4a12d7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>กรมการท่องเที่ยว</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>0504</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 12 รายการ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=19cd5e47-5ce2-4fd5-9409-2e340668402f</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>กรมการท่องเที่ยว</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>0504</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อวัสดุสำนักงาน ประจำปีงบประมาณ พ.ศ. 2569  จำนวน 97 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>★ (วัสดุสำนักงาน)</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c4c7adc7-cc9b-41ce-9e05-2b3d0139c927</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงการพัฒนาสังคมและความมั่นคงของมนุษย์</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>0602</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์และอุปกรณ์เพื่อเพิ่มประสิทธิภาพในการปฏิบัติงานหน่วยงานในพื้นที่จังหวัดชายแดนภาคใต้ (สงขลา ปัตตานี ยะลา และนราธิวาส) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=24711251-d07c-48d5-8bdb-38d59fb52ef4</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงการพัฒนาสังคมและความมั่นคงของมนุษย์</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>0602</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาซ่อมแซมแก้ไขเครื่องคอมพิวเตอร์พร้อมโปรแกรมอุปกรณ์คอมพิวเตอร์และโสตทัศนูปกรณ์ (ส่วนกลาง) ประจำปีงบประมาณ พ.ศ. 2570 ครั้งที่ 2 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3e9fb3bb-2fcf-447d-b16f-a0708dddad18</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>กรมการข้าว</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>0718</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การเกษตร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=358d7616-5b03-40b6-8e0a-cefd43ffa7c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>กรมการขนส่งทางบก</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>0804</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมระบบสนับสนุน ศูนย์คอมพิวเตอร์ส่วนกลาง และศูนย์ระบบข้อมูลกลางและสำรองข้อมูล (นนทบุรี) ของกรมการขนส่งทางบกที่ใช้ในการสนับสนุนการปฏิบัติงานด้านความปลอดภัย ทั้งส่วนกลางและส่วนภูมิภาค ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ffb1ab1a-8b13-424a-a0b9-82aeabd4a7f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>กรมท่าอากาศยาน</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้ออุปกรณ์ควบคุมจอแสดงผล Flight Information Display สำหรับท่าอากาศยาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>★ (จอแสดงผล)</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a81d531c-fd6f-413c-b3b6-acdd4de90430</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>กรมป่าไม้</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>0912</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์เพื่อเพิ่มประสิทธิภาพการจัดทำโครงข่ายหมุดหลักฐานแผนที่และการสำรวจรังวัดเพื่อจัดทำแผนที่แสดงแนวเขตป่าสงวนแห่งชาติ จำนวน ๒๘ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cc77ea8d-97e1-45d5-aedf-39417f46d256</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>องค์การกระจายเสียงและแพร่ภาพสาธารณะแห่งประเทศไทย(ส.ส.ท.)</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>0915</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้ออุปกรณ์จอแสดงผลภาพความละเอียด 4K (Professional Broadcast Monitor) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>★ (จอแสดงผล)</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c9200624-f187-4a68-b96b-2710ebba7083</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>1202</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>ประกวดราคาเช่าเช่ารถส่วนภูมิภาค รถยนต์ไฟฟ้า ประเภทแบตเตอรี่ (BEV) ขนาดความจุของแบตเตอรี่มากกว่า 50 กิโลวัตต์ชั่วโมง (kWh) และกำลังมอเตอร์ไฟฟ้าสูงสุด ไม่เกิน 150 กิโลวัตต์ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>★ (มอเตอร์)</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6682a0c9-e041-4a68-9c49-d4803a7d2ec9</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>กรมการจัดหางาน</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>1703</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างจ้างผลิตและเผยแพร่สื่อประชาสัมพันธ์รูปแบบสื่อโทรทัศน์ สื่อวิทยุ สื่อโฆษณา ในโรงภาพยนตร์ และสื่อป้ายประชาสัมพันธ์จอดิจิทัล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>★ (โทรทัศน์)</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6b16630a-851d-4285-be3b-b92e5b89b3f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>กรมพัฒนาฝีมือแรงงาน</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>1704</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์โครงการจัดหาครุภัณฑ์คอมพิวเตอร์แท็บเล็ต ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, แท็บเล็ต, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fcba4f1d-218b-4aed-9f5d-9a442ab81e87</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมวัฒนธรรม</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>1805</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์สำนักงาน จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2d71ed68-e74a-4854-ab7a-80754eb2e6c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมการเรียนรู้</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๑๙ รายการ ของกรมส่งเสริมการเรียนรู้ ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=321f85d4-75ae-4c7b-8b72-16fdca22a9fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
         <is>
           <t>2102</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ จำนวน ๓ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
-        </is>
-      </c>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>★ (ครุภัณฑ์)</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2c7df3d6-3d32-4bd7-9ecd-1c6edc996677</t>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดความดันโลหิตชนิดอัตโนมัติ วัดความอิ่มตัวของออกซิเจนในเลือด อุณหภูมิร่างกาย พร้อมระบบเชื่อมต่อฐานข้อมูล จำนวน 34 เครื่อง งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d0ff2fb1-0f33-427b-a238-2e2e93dba2dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องเอกซเรย์เคลื่อนที่ขนาดไม่น้อยกว่า 300 mA.ขับเคลื่อน ด้วยมอเตอร์ไฟฟ้า โรงพยาบาลวังสะพุง ตำบลวังสะพุง อำเภอวังสะพุง จังหวัดเลย ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>★ (มอเตอร์)</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=eccfee9c-8e58-4406-9d64-98150e467dc4</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องเอกซเรย์เคลื่อนที่ดิจิตอลไม่น้อยกว่า 300 mA. จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=00b4843f-9e23-4dc4-ad4a-ddffa8e9e173</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการเครื่องผลิตออกซิเจนขนาด ๑๐ ลิตร  จำนวน  ๑๒๐  เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f4ee01c6-d2a9-4067-8182-aca37b0dc986</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องเอกซเรย์เคลื่อนที่ระบบแพทย์ทางไกลแบบพกพาพร้อมชุดรับสัญญาณภาพดิจิตอลแบบไร้สาย ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 4 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d21ee284-b4ec-4b00-b103-1743272bab84</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องเอกซเรย์คอมพิวเตอร์สำหรับงานทันตกรรม (Dental CT) โรงพยาบาลโพนพิสัย ตำบลจุมพล อำเภอโพนพิสัย จังหวัดหนองคาย 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c9d1794d-a7c9-46aa-addf-b688d11337ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจคลื่นไฟฟ้าหัวใจ พร้อมเชื่อมต่อระบบแพทย์ทางไกล ของโรงพยาบาลในจังหวัดสุรินทร์ 5 แห่ง จำนวน 7 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c73e2ea6-2d38-41c5-96a6-159980babdd8</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจคลื่นไฟฟ้าหัวใจพร้อมระบบวิเคราะห์ผลและจัดเก็บภาพในระบบเครือข่าย ของโรงพยาบาลส่งเสริมสุขภาพตำบลและโรงพยาบาลชุมชน  5 แห่ง จำนวน 6 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bfd52be9-af0a-45e6-978d-679a48f70057</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดกลาง ของโรงพยาบาลชุมชน 10 แห่ง จำนวน 40 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=91baf8a4-d4fe-470d-b554-7e9a6b54deb1</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ เครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 6 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง โรงพยาบาลโป่งน้ำร้อน ตำบลทับไทร อำเภอโป่งน้ำร้อน จังหวัดจันทบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=73a507fa-8ae5-4aad-ae9f-983ec140a858</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>2107</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ (กลุ่มเครื่องมือใช้ในห้องปฏิบัติการ) จำนวน ๓ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=27664fff-0d3d-4ba7-ab7a-46fe45870ffa</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>2107</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน 3 รายการ เพื่อใช้ในกิจกรรมงานวิศวกรรมความปลอดภัย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1b8e73ca-f574-4f14-868a-65a273dfc3e4</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202609.xlsx
+++ b/Backup/eGP_Monthly_Main_202609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G352"/>
+  <dimension ref="A1:G368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9433,15 +9433,15 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>กรมการข้าว</t>
+          <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>718</v>
+        <v>805</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การเกษตร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบงานสารสนเทศ ระบบเครือข่าย และบริการแก้ไขคอมพิวเตอร์และอุปกรณ์ต่อพ่วง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=144b5b77-0cf7-4926-847e-f0fd1bd8f4b6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f9ae0aa5-414d-4a63-88c4-8cc52f83f6ef</t>
         </is>
       </c>
     </row>
@@ -9468,15 +9468,15 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
+          <t>กรมทางหลวงชนบท</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบงานสารสนเทศ ระบบเครือข่าย และบริการแก้ไขคอมพิวเตอร์และอุปกรณ์ต่อพ่วง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องพิมพ์ Tag Thermal Printer จำนวน 2 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f9ae0aa5-414d-4a63-88c4-8cc52f83f6ef</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=754696e0-bbea-44e1-9a55-42fce741c6ae</t>
         </is>
       </c>
     </row>
@@ -9503,15 +9503,15 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>กรมทางหลวงชนบท</t>
+          <t>กรมพัฒนาพลังงานทดแทนและอนุรักษ์พลังงาน</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>807</v>
+        <v>1205</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องพิมพ์ Tag Thermal Printer จำนวน 2 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์ อุปกรณ์เครือข่ายและอุปกรณ์หน่วยความจำสำรองสำหรับระบบฐานข้อมูล  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>★ (เครื่องพิมพ์)</t>
+          <t>★ (คอมพิวเตอร์, หน่วยความจำ, อุปกรณ์เครือข่าย)</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=754696e0-bbea-44e1-9a55-42fce741c6ae</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6b70ca7e-b8a0-4edd-a187-b48e924a78fa</t>
         </is>
       </c>
     </row>
@@ -9538,15 +9538,15 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>กรมพัฒนาพลังงานทดแทนและอนุรักษ์พลังงาน</t>
+          <t>กรมการปกครอง</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>1205</v>
+        <v>1503</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์ อุปกรณ์เครือข่ายและอุปกรณ์หน่วยความจำสำรองสำหรับระบบฐานข้อมูล  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อวัสดุผงหมึกและดรัมสำหรับเครื่องพิมพ์คอมพิวเตอร์ จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, หน่วยความจำ, อุปกรณ์เครือข่าย)</t>
+          <t>★ (ดรัม, คอมพิวเตอร์, เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6b70ca7e-b8a0-4edd-a187-b48e924a78fa</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ce5f2a5e-58b0-4355-b3f5-66c43c2247d8</t>
         </is>
       </c>
     </row>
@@ -9573,15 +9573,15 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>กรมการปกครอง</t>
+          <t>กรมสอบสวนคดีพิเศษ</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>1503</v>
+        <v>1608</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อวัสดุผงหมึกและดรัมสำหรับเครื่องพิมพ์คอมพิวเตอร์ จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องคอมพิวเตอร์ประสิทธิภาพสูงสำหรับประมวลผลความสัมพันธ์ทางธุรกรรมและวิเคราะห์เส้นทางการเงินของคดีพิเศษและเรื่องสืบสวน กรมสอบสวนคดีพิเศษ  แขวงทุ่งสองห้อง เขตหลักสี่ กรุงเทพมหานคร 3 ชุด ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>★ (ดรัม, คอมพิวเตอร์, เครื่องพิมพ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ce5f2a5e-58b0-4355-b3f5-66c43c2247d8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cd272b14-6e4a-4165-9eab-d4725c6ca271</t>
         </is>
       </c>
     </row>
@@ -9608,15 +9608,15 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>กรมสอบสวนคดีพิเศษ</t>
+          <t>สำนักงานประกันสังคม</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>1608</v>
+        <v>1706</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องคอมพิวเตอร์ประสิทธิภาพสูงสำหรับประมวลผลความสัมพันธ์ทางธุรกรรมและวิเคราะห์เส้นทางการเงินของคดีพิเศษและเรื่องสืบสวน กรมสอบสวนคดีพิเศษ  แขวงทุ่งสองห้อง เขตหลักสี่ กรุงเทพมหานคร 3 ชุด ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อวัสดุคอมพิวเตอร์ จำนวน ๑ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cd272b14-6e4a-4165-9eab-d4725c6ca271</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a2ef415e-d086-45a2-854c-add8955d6fdb</t>
         </is>
       </c>
     </row>
@@ -9643,15 +9643,15 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>สำนักงานประกันสังคม</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>1706</v>
+        <v>2102</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อวัสดุคอมพิวเตอร์ จำนวน ๑ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตาม   การทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดใหญ่ จำนวน 12 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ.2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -9661,12 +9661,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a2ef415e-d086-45a2-854c-add8955d6fdb</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5a6e7a1-9557-4e6f-8ecc-2de9fdd94405</t>
         </is>
       </c>
     </row>
@@ -9678,15 +9678,15 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>2102</v>
+        <v>2107</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตาม   การทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดใหญ่ จำนวน 12 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ.2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ  จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5a6e7a1-9557-4e6f-8ecc-2de9fdd94405</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fdb52cbf-ad05-423e-b1d8-e2f17eae5c8d</t>
         </is>
       </c>
     </row>
@@ -9713,15 +9713,15 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>กรมสนับสนุนบริการสุขภาพ</t>
+          <t>สำนักงานตำรวจแห่งชาติ</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>2107</v>
+        <v>2507</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ  จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดหาคอมพิวเตอร์ (Notebook) สำหรับนักเรียนนายร้อยตำรวจรุ่นที่ 84 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fdb52cbf-ad05-423e-b1d8-e2f17eae5c8d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c5ba14d7-29e1-4cb6-a64d-e89688b4e1f1</t>
         </is>
       </c>
     </row>
@@ -9748,15 +9748,15 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>สำนักงานตำรวจแห่งชาติ</t>
+          <t>สำนักงานอัยการสูงสุด</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดหาคอมพิวเตอร์ (Notebook) สำหรับนักเรียนนายร้อยตำรวจรุ่นที่ 84 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c5ba14d7-29e1-4cb6-a64d-e89688b4e1f1</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=caeb26b1-ae0a-40d1-878c-18926a5cd2cd</t>
         </is>
       </c>
     </row>
@@ -9783,15 +9783,15 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>สำนักงานอัยการสูงสุด</t>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามการทุจริตแห่งชาติ</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>2509</v>
+        <v>2605</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์พกพาแบบหน้าจอสัมผัส จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, คอมพิวเตอร์พกพา)</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=caeb26b1-ae0a-40d1-878c-18926a5cd2cd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=380be6fa-be50-4cc9-a85d-d4912f73145e</t>
         </is>
       </c>
     </row>
@@ -9818,15 +9818,15 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามการทุจริตแห่งชาติ</t>
+          <t>องค์การบริหารส่วนจังหวัดระยอง</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>2605</v>
+        <v>2210101</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์พกพาแบบหน้าจอสัมผัส จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 2 รายการ ดังนี้ (1) รถยนต์โดยสารปรับอากาศ ไม่น้อยกว่า 22 ที่นั่ง แบบขับเคลื่อนด้วยระบบไฟฟ้า จำนวน 2 คัน  (2) รถยนต์โดยสารปรับอากาศ ไม่น้อยกว่า 40 ที่นั่ง แบบขับเคลื่อนด้วยระบบไฟฟ้า จำนวน 2 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -9836,12 +9836,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, คอมพิวเตอร์พกพา)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=380be6fa-be50-4cc9-a85d-d4912f73145e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=56da4e4f-a0c5-43d9-b499-ef666d60c6ae</t>
         </is>
       </c>
     </row>
@@ -9853,15 +9853,15 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>องค์การบริหารส่วนจังหวัดระยอง</t>
+          <t>มหาวิทยาลัยเชียงใหม่</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>2210101</v>
+        <v>1450100400</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 2 รายการ ดังนี้ (1) รถยนต์โดยสารปรับอากาศ ไม่น้อยกว่า 22 ที่นั่ง แบบขับเคลื่อนด้วยระบบไฟฟ้า จำนวน 2 คัน  (2) รถยนต์โดยสารปรับอากาศ ไม่น้อยกว่า 40 ที่นั่ง แบบขับเคลื่อนด้วยระบบไฟฟ้า จำนวน 2 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=56da4e4f-a0c5-43d9-b499-ef666d60c6ae</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=37e13d96-615f-47ec-98fa-80e208e1c3cd</t>
         </is>
       </c>
     </row>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อรายการครุภัณฑ์ระบบบันไดเลื่อน จำนวน 2 รายการ (ตามรายละเอียดแนบท้าย) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=37e13d96-615f-47ec-98fa-80e208e1c3cd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0552eafd-ca4e-4f42-b20b-de0194dda26f</t>
         </is>
       </c>
     </row>
@@ -9931,7 +9931,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อรายการครุภัณฑ์ระบบบันไดเลื่อน จำนวน 2 รายการ (ตามรายละเอียดแนบท้าย) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อรายการครุภัณฑ์ลิฟต์ จำนวน 2 รายการ (ตามรายละเอียดแนบท้าย) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -9946,27 +9946,27 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0552eafd-ca4e-4f42-b20b-de0194dda26f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ccd9e657-8e19-4067-9762-ca2a3da4e3af</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>มหาวิทยาลัยเชียงใหม่</t>
+          <t>กองอำนวยการรักษาความมั่นคงภายใน</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>1450100400</v>
+        <v>119</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อรายการครุภัณฑ์ลิฟต์ จำนวน 2 รายการ (ตามรายละเอียดแนบท้าย) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อวัสดุสำนักงาน ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ สนับสนุน นขต.กอ.รมน. (ส่วนกลาง) ครั้งที่ ๒        ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (วัสดุสำนักงาน)</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ccd9e657-8e19-4067-9762-ca2a3da4e3af</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=245d59e4-9af3-49a2-b319-a01e5d97af03</t>
         </is>
       </c>
     </row>
@@ -9993,15 +9993,15 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>กองอำนวยการรักษาความมั่นคงภายใน</t>
+          <t>กองทัพเรือ</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>119</v>
+        <v>205</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อวัสดุสำนักงาน ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ สนับสนุน นขต.กอ.รมน. (ส่วนกลาง) ครั้งที่ ๒        ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์เครื่องช่วยการศึกษา สาย ยศ.ทร. ในการปรับปรุงอาคาร กพร.ทร.แห่งใหม่ (อาคาร บก.พธ.ทร.เดิม) จำนวน ๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>★ (วัสดุสำนักงาน)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=245d59e4-9af3-49a2-b319-a01e5d97af03</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ee6ef62-218a-4804-b810-005dc5140bcf</t>
         </is>
       </c>
     </row>
@@ -10028,15 +10028,15 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>กองทัพเรือ</t>
+          <t>กองบัญชาการกองทัพไทย</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์เครื่องช่วยการศึกษา สาย ยศ.ทร. ในการปรับปรุงอาคาร กพร.ทร.แห่งใหม่ (อาคาร บก.พธ.ทร.เดิม) จำนวน ๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์งานบ้านงานครัว พร้อมติดตั้ง ณ ครัวห้องอาหาร 6/1 และ 6/2 อาคาร 1 บก.ทท. ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ee6ef62-218a-4804-b810-005dc5140bcf</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b75a499d-7f24-4c81-8f7c-efa6f5c08c11</t>
         </is>
       </c>
     </row>
@@ -10063,15 +10063,15 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>กองบัญชาการกองทัพไทย</t>
+          <t>กรมบัญชีกลาง</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>208</v>
+        <v>304</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างผลิตครุภัณฑ์งานบ้านงานครัว พร้อมติดตั้ง ณ ครัวห้องอาหาร ๖/๑ และ ๖/๒ อาคาร ๑ บก.ทท. งบประมาณเพิ่มเติมระหว่างปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์คอมพิวเตอร์สำหรับห้องประชุม 4 (ห้องปฏิบัติการคอมพิวเตอร์) อาคาร 9 ชั้น 7 กรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -10081,12 +10081,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=78cb42b4-9ab9-4e73-b45c-e4dff9b52cfd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b3a0480b-6840-48c0-aaba-8b41474df7ba</t>
         </is>
       </c>
     </row>
@@ -10098,15 +10098,15 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>กองบัญชาการกองทัพไทย</t>
+          <t>กรมสรรพากร</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>208</v>
+        <v>307</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์งานบ้านงานครัว พร้อมติดตั้ง ณ ครัวห้องอาหาร 6/1 และ 6/2 อาคาร 1 บก.ทท. ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภท รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b75a499d-7f24-4c81-8f7c-efa6f5c08c11</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2f4faa45-b32a-4d9e-b08c-b82d5884c153</t>
         </is>
       </c>
     </row>
@@ -10133,15 +10133,15 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>กรมบัญชีกลาง</t>
+          <t>สำนักงานปลัดกระทรวงการพัฒนาสังคมและความมั่นคงของมนุษย์</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>304</v>
+        <v>602</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์คอมพิวเตอร์สำหรับห้องประชุม 4 (ห้องปฏิบัติการคอมพิวเตอร์) อาคาร 9 ชั้น 7 กรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาและเพิ่มประสิทธิภาพระบบสมุดพกครอบครัวอิเล็กทรอนิกส์ (MSO-Logbook) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -10151,12 +10151,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (สมุด)</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b3a0480b-6840-48c0-aaba-8b41474df7ba</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1026aa3b-bb28-4576-aadf-d4cf4a678716</t>
         </is>
       </c>
     </row>
@@ -10168,15 +10168,15 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>กรมสรรพากร</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>307</v>
+        <v>704</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภท รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี. หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บพร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2f4faa45-b32a-4d9e-b08c-b82d5884c153</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a73013cc-9e52-49f3-b910-4e936275bfe1</t>
         </is>
       </c>
     </row>
@@ -10203,15 +10203,15 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการพัฒนาสังคมและความมั่นคงของมนุษย์</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>602</v>
+        <v>2102</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาและเพิ่มประสิทธิภาพระบบสมุดพกครอบครัวอิเล็กทรอนิกส์ (MSO-Logbook) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องตรวจสมรรถภาพปอดด้วยเครื่องคอมพิวเตอร์ จำนวน ๓ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>★ (สมุด)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1026aa3b-bb28-4576-aadf-d4cf4a678716</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=10b04086-63b0-4d42-95a0-904c88c6e41f</t>
         </is>
       </c>
     </row>
@@ -10238,15 +10238,15 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>704</v>
+        <v>2102</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี. หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บพร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องให้การรักษาอาการปวดและกระตุ้นเซลล์ประสาทส่วนปลายด้วยสนามแม่เหล็กไฟฟ้า (PMS) สำหรับโรงพยาบาลกงไกรลาศ จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a73013cc-9e52-49f3-b910-4e936275bfe1</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4a641a15-b74d-402f-ab9c-60aa9fb564a7</t>
         </is>
       </c>
     </row>
@@ -10281,7 +10281,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องตรวจสมรรถภาพปอดด้วยเครื่องคอมพิวเตอร์ จำนวน ๓ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องเอกซเรย์ทั่วไปขนาดไม่น้อยกว่า ๑,๐๐๐ mA. แบบแขวนเพดาน สำหรับโรงพยาบาลศรีนคร จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=10b04086-63b0-4d42-95a0-904c88c6e41f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a37d5071-0a7d-4d2f-84fe-d0f774026ac5</t>
         </is>
       </c>
     </row>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องให้การรักษาอาการปวดและกระตุ้นเซลล์ประสาทส่วนปลายด้วยสนามแม่เหล็กไฟฟ้า (PMS) สำหรับโรงพยาบาลกงไกรลาศ จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูง ชนิด 2 หัวตรวจ สำหรับโรงพยาบาลทุ่งเสลี่ยม จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4a641a15-b74d-402f-ab9c-60aa9fb564a7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9aa030b2-096a-4e59-a881-6f2d1737ed5f</t>
         </is>
       </c>
     </row>
@@ -10351,7 +10351,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องเอกซเรย์ทั่วไปขนาดไม่น้อยกว่า ๑,๐๐๐ mA. แบบแขวนเพดาน สำหรับโรงพยาบาลศรีนคร จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องตรวจอวัยวะภายในด้วยเครื่องเสียงความถี่สูงระดับความคมชัดสูง ๓ หัวตรวจ ชนิดเคลื่อนย้ายได้ สำหรับโรงพยาบาลบ้านด่านลานหอย จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a37d5071-0a7d-4d2f-84fe-d0f774026ac5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afe2fdf2-3a41-4668-9d7c-c5718e064adc</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูง ชนิด 2 หัวตรวจ สำหรับโรงพยาบาลทุ่งเสลี่ยม จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องให้การรักษาทางกายภาพด้วยคลื่นแม่เหล็กไฟฟ้า  สำหรับโรงพยาบาลศรีสัชนาลัย จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9aa030b2-096a-4e59-a881-6f2d1737ed5f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1eeea1f2-b27e-42f8-b37f-8cd9d17e4bb2</t>
         </is>
       </c>
     </row>
@@ -10421,7 +10421,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องตรวจอวัยวะภายในด้วยเครื่องเสียงความถี่สูงระดับความคมชัดสูง ๓ หัวตรวจ ชนิดเคลื่อนย้ายได้ สำหรับโรงพยาบาลบ้านด่านลานหอย จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนในเลือด ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 5 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afe2fdf2-3a41-4668-9d7c-c5718e064adc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a54472bd-463e-4919-a81a-3790d34b7b27</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องให้การรักษาทางกายภาพด้วยคลื่นแม่เหล็กไฟฟ้า  สำหรับโรงพยาบาลศรีสัชนาลัย จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องผลิตออกซิเจน ขนาด 10 ลิตร จำนวน 39 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย-กัมพูชา ปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1eeea1f2-b27e-42f8-b37f-8cd9d17e4bb2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1bc9002a-e6eb-4764-add9-7faccb225729</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนในเลือด ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 5 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ รายการเตียงผ่าตัดศัลยกรรมออร์โธปิดิกส์ จำนวน ๒ เตียง สำหรับโรงพยาบาลลับแลและโรงพยาบาลพิชัย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a54472bd-463e-4919-a81a-3790d34b7b27</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=30fcc177-cd34-422d-af09-c8aa1f9cb406</t>
         </is>
       </c>
     </row>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องผลิตออกซิเจน ขนาด 10 ลิตร จำนวน 39 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย-กัมพูชา ปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างปรับปรุงสายสัญญาณอินเทอร์เน็ตอาคาร 1 และสายไฟฟ้าอาคาร 9 สำนักงานปลัดกระทรวงสาธารณสุข ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (สายสัญญาณ)</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1bc9002a-e6eb-4764-add9-7faccb225729</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afd11c75-a6db-43e5-a0f3-035fadd64936</t>
         </is>
       </c>
     </row>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ รายการเตียงผ่าตัดศัลยกรรมออร์โธปิดิกส์ จำนวน ๒ เตียง สำหรับโรงพยาบาลลับแลและโรงพยาบาลพิชัย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องตรวจสมรรถภาพปอดด้วยเครื่องคอมพิวเตอร์ จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -10571,12 +10571,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=30fcc177-cd34-422d-af09-c8aa1f9cb406</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=de38cd7a-4053-4ddd-a509-d16c262cf02a</t>
         </is>
       </c>
     </row>
@@ -10588,15 +10588,15 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมอนามัย</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>2102</v>
+        <v>2109</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างปรับปรุงสายสัญญาณอินเทอร์เน็ตอาคาร 1 และสายไฟฟ้าอาคาร 9 สำนักงานปลัดกระทรวงสาธารณสุข ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ทางการแพทย์ เครื่องวิเคราะห์องค์ประกอบร่างกายแบบแยกส่วนของโรงพยาบาล ส่งเสริมสุขภาพ ศูนย์อนามัยที่ ๖ ชลบุรี ปีงบประมาณ พ.ศ. ๒๕๗๐ จำนวน ๑ รายการ ( จำนวน ๒ เครื่อง) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -10606,32 +10606,32 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>★ (สายสัญญาณ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afd11c75-a6db-43e5-a0f3-035fadd64936</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=adb22b5a-03b6-4872-8f4a-1ba04569341a</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>2102</v>
+        <v>204</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องตรวจสมรรถภาพปอดด้วยเครื่องคอมพิวเตอร์ จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อระบบคอมพิวเตอร์และอุปกรณ์ เพื่อสนับสนุนการใช้งานข่าวกรอง ฝขว.ศปก.ทบ. จำนวน ๑๘ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -10646,27 +10646,27 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=de38cd7a-4053-4ddd-a509-d16c262cf02a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=72ad4c14-ee7b-4d77-ba81-e913d7b8443f</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>กรมอนามัย</t>
+          <t>กรมบัญชีกลาง</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>2109</v>
+        <v>304</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ทางการแพทย์ เครื่องวิเคราะห์องค์ประกอบร่างกายแบบแยกส่วนของโรงพยาบาล ส่งเสริมสุขภาพ ศูนย์อนามัยที่ ๖ ชลบุรี ปีงบประมาณ พ.ศ. ๒๕๗๐ จำนวน ๑ รายการ ( จำนวน ๒ เครื่อง) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องพิมพ์ Multifunction และเครื่องสแกนเนอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -10676,12 +10676,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องพิมพ์, เครื่องสแกนเนอร์)</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=adb22b5a-03b6-4872-8f4a-1ba04569341a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9b179ddf-4f24-4f03-b0f6-03f51948ebb5</t>
         </is>
       </c>
     </row>
@@ -10693,15 +10693,15 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>204</v>
+        <v>704</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อระบบคอมพิวเตอร์และอุปกรณ์ เพื่อสนับสนุนการใช้งานข่าวกรอง ฝขว.ศปก.ทบ. จำนวน ๑๘ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อเครื่องปรับอากาศแบบแยกส่วน (ราคารวมค่าติดตั้ง) แบบตั้งพื้นหรือแบบแขวน(ระบบ Inverter) ขนาดไม่ต่ำกว่า 36,000 บีทียู จำนวน 13 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=72ad4c14-ee7b-4d77-ba81-e913d7b8443f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4fb39309-585d-4309-976d-68ffb35f0d13</t>
         </is>
       </c>
     </row>
@@ -10728,15 +10728,15 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>กรมบัญชีกลาง</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>304</v>
+        <v>806</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องพิมพ์ Multifunction และเครื่องสแกนเนอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้องานจัดซื้อครุภัณฑ์สำนักงาน จำนวน 21 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>★ (เครื่องพิมพ์, เครื่องสแกนเนอร์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9b179ddf-4f24-4f03-b0f6-03f51948ebb5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b933c10a-3d2b-48e7-8733-9ad758013b0a</t>
         </is>
       </c>
     </row>
@@ -10763,15 +10763,15 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>704</v>
+        <v>909</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อเครื่องปรับอากาศแบบแยกส่วน (ราคารวมค่าติดตั้ง) แบบตั้งพื้นหรือแบบแขวน(ระบบ Inverter) ขนาดไม่ต่ำกว่า 36,000 บีทียู จำนวน 13 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์โครงการเพิ่มประสิทธิภาพการตอบโต้สถานการณ์เฝ้าระวังและผลักดันช้างป่าออกนอกพื้นที่อนุรักษ์ (ครั้งที่ 2) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4fb39309-585d-4309-976d-68ffb35f0d13</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1a53dd55-3e32-4691-875b-bed5b618267e</t>
         </is>
       </c>
     </row>
@@ -10798,15 +10798,15 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>สำนักงานนโยบายและแผนทรัพยากรธรรมชาติและสิ่งแวดล้อม</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>806</v>
+        <v>911</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้องานจัดซื้อครุภัณฑ์สำนักงาน จำนวน 21 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อวัสดุคอมพิวเตอร์ จำนวน ๑๐๘ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b933c10a-3d2b-48e7-8733-9ad758013b0a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4e0b8c2a-5098-46b1-9662-a1a768115472</t>
         </is>
       </c>
     </row>
@@ -10833,15 +10833,15 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
+          <t>กรมพินิจและคุ้มครองเด็กและเยาวชน</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>909</v>
+        <v>1606</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์โครงการเพิ่มประสิทธิภาพการตอบโต้สถานการณ์เฝ้าระวังและผลักดันช้างป่าออกนอกพื้นที่อนุรักษ์ (ครั้งที่ 2) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ รายการเครื่องรับส่งวิทยุ ระบบ VHF FM ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1a53dd55-3e32-4691-875b-bed5b618267e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=50900d02-0860-49e6-924a-4ce90e349f51</t>
         </is>
       </c>
     </row>
@@ -10868,15 +10868,15 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>สำนักงานนโยบายและแผนทรัพยากรธรรมชาติและสิ่งแวดล้อม</t>
+          <t>กรมพินิจและคุ้มครองเด็กและเยาวชน</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>911</v>
+        <v>1606</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อวัสดุคอมพิวเตอร์ จำนวน ๑๐๘ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์สำรวจ จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -10886,12 +10886,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4e0b8c2a-5098-46b1-9662-a1a768115472</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=27e6a7f1-e8b3-4713-a4cf-8e1017c95588</t>
         </is>
       </c>
     </row>
@@ -10903,15 +10903,15 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>กรมพินิจและคุ้มครองเด็กและเยาวชน</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>1606</v>
+        <v>2102</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ รายการเครื่องรับส่งวิทยุ ระบบ VHF FM ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง สำหรับโรงพยาบาลทุ่งเสลี่ยมและโรงพยาบาลคีรีมาศ จำนวน 2 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=50900d02-0860-49e6-924a-4ce90e349f51</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b637756a-f1db-43ca-8088-8bb65d244bc6</t>
         </is>
       </c>
     </row>
@@ -10938,15 +10938,15 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>กรมพินิจและคุ้มครองเด็กและเยาวชน</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>1606</v>
+        <v>2102</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์สำรวจ จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ ยูนิตทำฟัน สำหรับโรงพยาบาลศรีนคร และโรงพยาบาลส่งเสริมสุขภาพตำบลวังทอง จำนวน 2 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=27e6a7f1-e8b3-4713-a4cf-8e1017c95588</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=47778085-c309-4c79-a29b-e1847ea7456e</t>
         </is>
       </c>
     </row>
@@ -10981,7 +10981,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง สำหรับโรงพยาบาลทุ่งเสลี่ยมและโรงพยาบาลคีรีมาศ จำนวน 2 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องช่วยนวดหัวใจและฟื้นคืนชีพผู้ป่วยอัติโนมัติ สำหรับโรงพยาบาลทุ่งเสลี่ยม จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b637756a-f1db-43ca-8088-8bb65d244bc6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=772263bc-9e51-4b12-87ea-8b731c25646a</t>
         </is>
       </c>
     </row>
@@ -11008,15 +11008,15 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมสุขภาพจิต</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>2102</v>
+        <v>2108</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ ยูนิตทำฟัน สำหรับโรงพยาบาลศรีนคร และโรงพยาบาลส่งเสริมสุขภาพตำบลวังทอง จำนวน 2 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๖ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -11026,32 +11026,32 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=47778085-c309-4c79-a29b-e1847ea7456e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a2d6c763-d384-410d-8363-44f98d922641</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สำนักงานคณะกรรมการนโยบายที่ดินแห่งชาติ</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>2102</v>
+        <v>142</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องช่วยนวดหัวใจและฟื้นคืนชีพผู้ป่วยอัติโนมัติ สำหรับโรงพยาบาลทุ่งเสลี่ยม จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องพิมพ์ ขนาด A0 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -11061,32 +11061,32 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=772263bc-9e51-4b12-87ea-8b731c25646a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b524d474-1d00-4330-872e-db4cd85cc6a0</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>กรมสุขภาพจิต</t>
+          <t>สำนักงานคณะกรรมการนโยบายที่ดินแห่งชาติ</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>2108</v>
+        <v>142</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๖ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์เพิ่มเติม ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a2d6c763-d384-410d-8363-44f98d922641</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ef813d9a-008b-48f6-807d-47af8175bf30</t>
         </is>
       </c>
     </row>
@@ -11113,15 +11113,15 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการนโยบายที่ดินแห่งชาติ</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องพิมพ์ ขนาด A0 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ประจำอาคาร จำนวน 4 รายการ เพื่อใช้ในงานซ่อมปรับปรุงอาคารแฟลตนายทหารชั้นประทวนจุ 56 ครอบครัว หมายเลข 423/29 (ป.116) ของ กองพันทหารช่างที่ 112 กรมทหารช่างที่ 1 รักษาพระองค์ เป็นแผนงานเพิ่มเติมระหว่างปีงบประมาณ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -11131,12 +11131,12 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>★ (เครื่องพิมพ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b524d474-1d00-4330-872e-db4cd85cc6a0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c57e6e7d-84ff-41ad-986d-268777a7d6c1</t>
         </is>
       </c>
     </row>
@@ -11148,15 +11148,15 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการนโยบายที่ดินแห่งชาติ</t>
+          <t>สำนักงานปลัดกระทรวงเกษตรและสหกรณ์</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>142</v>
+        <v>702</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์เพิ่มเติม ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างดูแลบำรุงรักษาระบบคอมพิวเตอร์และเครือข่าย สำนักงานปลัดกระทรวงเกษตรและสหกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -11166,12 +11166,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ef813d9a-008b-48f6-807d-47af8175bf30</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=968489c9-089d-4081-9d28-c41ee46b7166</t>
         </is>
       </c>
     </row>
@@ -11183,15 +11183,15 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กรมชลประทาน</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>204</v>
+        <v>703</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ประจำอาคาร จำนวน 4 รายการ เพื่อใช้ในงานซ่อมปรับปรุงอาคารแฟลตนายทหารชั้นประทวนจุ 56 ครอบครัว หมายเลข 423/29 (ป.116) ของ กองพันทหารช่างที่ 112 กรมทหารช่างที่ 1 รักษาพระองค์ เป็นแผนงานเพิ่มเติมระหว่างปีงบประมาณ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจัดทำและติดตั้งบานระบายตรงชนิดสองบาน ขนาด 6.00x5.00 เมตร พร้อมจัดหาและติดตั้งเกียร์มอเตอร์ไฟฟ้า ขนาด 3 กิโลวัตต์ 200 รอบต่อนาทีสำหรับเครื่องกว้าน 12 ตัน และอุปกรณ์อื่นๆ จำนวน 4 รายการ ปตร.คลองปากง่าม ตำบลหัวสะพาน อำเภอเมืองเพชรบุรี จังหวัดเพชรบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -11201,12 +11201,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c57e6e7d-84ff-41ad-986d-268777a7d6c1</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5e9f210c-ac94-45bc-bdd6-fc5490c2019e</t>
         </is>
       </c>
     </row>
@@ -11218,15 +11218,15 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงเกษตรและสหกรณ์</t>
+          <t>กรมประมง</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างดูแลบำรุงรักษาระบบคอมพิวเตอร์และเครือข่าย สำนักงานปลัดกระทรวงเกษตรและสหกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ เครื่องกำเนิดไฟฟ้า ขนาด ๕๐๐ กิโลวัตต์ พร้อมตู้ควบคุม จำนวน ๑ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -11236,12 +11236,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=968489c9-089d-4081-9d28-c41ee46b7166</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fbcaead1-29c0-4ccc-b4f3-c6029e986951</t>
         </is>
       </c>
     </row>
@@ -11253,15 +11253,15 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>กรมชลประทาน</t>
+          <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>703</v>
+        <v>804</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจัดทำและติดตั้งบานระบายตรงชนิดสองบาน ขนาด 6.00x5.00 เมตร พร้อมจัดหาและติดตั้งเกียร์มอเตอร์ไฟฟ้า ขนาด 3 กิโลวัตต์ 200 รอบต่อนาทีสำหรับเครื่องกว้าน 12 ตัน และอุปกรณ์อื่นๆ จำนวน 4 รายการ ปตร.คลองปากง่าม ตำบลหัวสะพาน อำเภอเมืองเพชรบุรี จังหวัดเพชรบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาคอมพิวเตอร์แม่ข่ายและซอฟต์แวร์ระบบ Smart Bus Terminal เพื่ออำนวยความสะดวกและปลอดภัยในการโดยสารด้วยรถสาธารณะ ด้วยการใช้เทคโนโลยีสารสนเทศ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -11271,12 +11271,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5e9f210c-ac94-45bc-bdd6-fc5490c2019e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9f2eadf5-f0d6-454d-92ce-830a13a9368f</t>
         </is>
       </c>
     </row>
@@ -11288,15 +11288,15 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>กรมประมง</t>
+          <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>705</v>
+        <v>805</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ เครื่องกำเนิดไฟฟ้า ขนาด ๕๐๐ กิโลวัตต์ พร้อมตู้ควบคุม จำนวน ๑ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้ออุปกรณ์เครือข่ายและอุปกรณ์ความมั่นคงปลอดภัยและเสถียรภาพการ ณ ท่าอากาศยาน ๒๖ แห่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -11306,12 +11306,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (อุปกรณ์เครือข่าย)</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fbcaead1-29c0-4ccc-b4f3-c6029e986951</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3224492-d946-48af-92fc-ba14c8c18c21</t>
         </is>
       </c>
     </row>
@@ -11323,15 +11323,15 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาคอมพิวเตอร์แม่ข่ายและซอฟต์แวร์ระบบ Smart Bus Terminal เพื่ออำนวยความสะดวกและปลอดภัยในการโดยสารด้วยรถสาธารณะ ด้วยการใช้เทคโนโลยีสารสนเทศ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน 13 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -11341,12 +11341,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ซอฟต์แวร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9f2eadf5-f0d6-454d-92ce-830a13a9368f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8b49083c-95ec-4358-b45b-4c5ea43d22bc</t>
         </is>
       </c>
     </row>
@@ -11358,15 +11358,15 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
+          <t>กรมทรัพยากรน้ำบาดาล</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>805</v>
+        <v>907</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้ออุปกรณ์เครือข่ายและอุปกรณ์ความมั่นคงปลอดภัยและเสถียรภาพการ ณ ท่าอากาศยาน ๒๖ แห่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้ออุปกรณ์เพื่อซ่อมแซมระบบปรับปรุงคุณภาพน้ำดื่มสะอาด จำนวน ๒๙๙ ชุด โครงการศึกษา ประเมินความเสียหายและฟื้นฟูเพื่อการพัฒนาและอนุรักษ์ทรัพยากรน้ำบาดาลในพื้นที่ประสบมหาอุทกภัยภาคใต้ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -11376,12 +11376,12 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>★ (อุปกรณ์เครือข่าย)</t>
+          <t>★ (น้ำดื่ม)</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3224492-d946-48af-92fc-ba14c8c18c21</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=57c8fe20-b280-4b2e-8fc6-c8ac87d2d313</t>
         </is>
       </c>
     </row>
@@ -11393,15 +11393,15 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>กรมการค้าภายใน</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>806</v>
+        <v>1304</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน 13 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้ออุปกรณ์กระจายสัญญาณแบบไรัสาย พร้อมติดตั้ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -11411,12 +11411,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8b49083c-95ec-4358-b45b-4c5ea43d22bc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=16d1d6a0-874d-40e3-b570-9428b853237b</t>
         </is>
       </c>
     </row>
@@ -11428,15 +11428,15 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>กรมทรัพยากรน้ำบาดาล</t>
+          <t>กรมพัฒนาธุรกิจการค้า</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>907</v>
+        <v>1308</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้ออุปกรณ์เพื่อซ่อมแซมระบบปรับปรุงคุณภาพน้ำดื่มสะอาด จำนวน ๒๙๙ ชุด โครงการศึกษา ประเมินความเสียหายและฟื้นฟูเพื่อการพัฒนาและอนุรักษ์ทรัพยากรน้ำบาดาลในพื้นที่ประสบมหาอุทกภัยภาคใต้ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องคอมพิวเตอร์และอุปกรณ์ทดแทน ปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -11446,12 +11446,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>★ (น้ำดื่ม)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=57c8fe20-b280-4b2e-8fc6-c8ac87d2d313</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0026be70-8492-4e93-b52e-fe570444ea01</t>
         </is>
       </c>
     </row>
@@ -11463,15 +11463,15 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>กรมการค้าภายใน</t>
+          <t>กรมการปกครอง</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>1304</v>
+        <v>1503</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้ออุปกรณ์กระจายสัญญาณแบบไรัสาย พร้อมติดตั้ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -11481,12 +11481,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=16d1d6a0-874d-40e3-b570-9428b853237b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a853a12e-1590-4be6-a161-1851415f448c</t>
         </is>
       </c>
     </row>
@@ -11498,15 +11498,15 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>กรมพัฒนาธุรกิจการค้า</t>
+          <t>กรมส่งเสริมการปกครองท้องถิ่น</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>1308</v>
+        <v>1508</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องคอมพิวเตอร์และอุปกรณ์ทดแทน ปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อการจัดซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 7 รายการ ประจำปีงบประมาณ พ.ศ. 2570 ของสำนักงานท้องถิ่นจังหวัดอุทัยธานี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0026be70-8492-4e93-b52e-fe570444ea01</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=398251c5-ded9-4f36-ab4f-2b062cabfa7d</t>
         </is>
       </c>
     </row>
@@ -11533,15 +11533,15 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>กรมการปกครอง</t>
+          <t>กรมพินิจและคุ้มครองเด็กและเยาวชน</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>1503</v>
+        <v>1606</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดระดับคาร์บอนมอนออกไซด์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -11556,7 +11556,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a853a12e-1590-4be6-a161-1851415f448c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ea8b731b-a755-4b4b-b550-259b6b24af7e</t>
         </is>
       </c>
     </row>
@@ -11568,15 +11568,15 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการปกครองท้องถิ่น</t>
+          <t>กรมพัฒนาฝีมือแรงงาน</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>1508</v>
+        <v>1704</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อการจัดซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 7 รายการ ประจำปีงบประมาณ พ.ศ. 2570 ของสำนักงานท้องถิ่นจังหวัดอุทัยธานี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ที่มีราคาต่อหน่วยต่ำกว่า 1 ล่้านบาท ครุภัณฑ์ไฟฟ้าและวิทยุ (ระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop)  ขนาด 3 เฟส 15 กิโลวัตต์ ตำบลบ้านโปร่ง อำเภอหนองโดน จังหวัดสระบุรี จำนวน 1 ระบบ และระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop) ขนาด 3 เฟส 20 กิโลวัตต์ ตำบลบ้านโปร่ง อำเภอหนองโดน จังหวัดสระบุรี จำนวน 1 ระบบ)  ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=398251c5-ded9-4f36-ab4f-2b062cabfa7d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5a36822b-e8f7-4a53-941e-49ef30ea4c9b</t>
         </is>
       </c>
     </row>
@@ -11603,15 +11603,15 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>กรมพินิจและคุ้มครองเด็กและเยาวชน</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>1606</v>
+        <v>2102</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดระดับคาร์บอนมอนออกไซด์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ จำนวน ๓ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -11626,27 +11626,27 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ea8b731b-a755-4b4b-b550-259b6b24af7e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2c7df3d6-3d32-4bd7-9ecd-1c6edc996677</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>กรมพัฒนาฝีมือแรงงาน</t>
+          <t>กองบัญชาการกองทัพไทย</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>1704</v>
+        <v>208</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ที่มีราคาต่อหน่วยต่ำกว่า 1 ล่้านบาท ครุภัณฑ์ไฟฟ้าและวิทยุ (ระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop)  ขนาด 3 เฟส 15 กิโลวัตต์ ตำบลบ้านโปร่ง อำเภอหนองโดน จังหวัดสระบุรี จำนวน 1 ระบบ และระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop) ขนาด 3 เฟส 20 กิโลวัตต์ ตำบลบ้านโปร่ง อำเภอหนองโดน จังหวัดสระบุรี จำนวน 1 ระบบ)  ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างผลิตครุภัณฑ์งานบ้านงานครัว พร้อมติดตั้ง ณ ครัวห้องอาหาร ๖/๑ และ ๖/๒ อาคาร ๑ บก.ทท. งบประมาณเพิ่มเติมระหว่างปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -11661,27 +11661,27 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5a36822b-e8f7-4a53-941e-49ef30ea4c9b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0206dc5f-1749-42e1-926b-c40fa1b0790b</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กองบัญชาการกองทัพไทย</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>2102</v>
+        <v>208</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ จำนวน ๓ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์งานบ้านงานครัว ณ ครัวห้องอาหาร 6/1 และ 6/2 อาคาร 1 บก.ทท. งบประมาณเพิ่มเติมระหว่างปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2c7df3d6-3d32-4bd7-9ecd-1c6edc996677</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cc985455-9962-4480-9fe9-d808bf294cdd</t>
         </is>
       </c>
     </row>
@@ -11708,17 +11708,15 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>กองบัญชาการกองทัพไทย</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>0208</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงการคลัง</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>302</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างผลิตครุภัณฑ์งานบ้านงานครัว พร้อมติดตั้ง ณ ครัวห้องอาหาร ๖/๑ และ ๖/๒ อาคาร ๑ บก.ทท. งบประมาณเพิ่มเติมระหว่างปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างการจ้างเหมาบริการบำรุงรักษา ซ่อมแซม และแก้ไขอุปกรณ์เครือข่ายและระบบประชุมทางไกล ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -11728,12 +11726,12 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (อุปกรณ์เครือข่าย, ระบบประชุมทางไกล)</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0206dc5f-1749-42e1-926b-c40fa1b0790b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9befc47f-3a0c-485e-a092-61c7ce73b9c6</t>
         </is>
       </c>
     </row>
@@ -11745,17 +11743,15 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>กองบัญชาการกองทัพไทย</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>0208</t>
-        </is>
+          <t>สำนักงานบริหารหนี้สาธารณะ</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>309</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์งานบ้านงานครัว ณ ครัวห้องอาหาร 6/1 และ 6/2 อาคาร 1 บก.ทท. งบประมาณเพิ่มเติมระหว่างปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดหาหน่วยความจำหลัก (RAM) สำหรับเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -11765,12 +11761,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, หน่วยความจำ)</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cc985455-9962-4480-9fe9-d808bf294cdd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d1f5fe37-48d4-46a5-a2a5-1e42e4a12d7d</t>
         </is>
       </c>
     </row>
@@ -11782,17 +11778,15 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการคลัง</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>0302</t>
-        </is>
+          <t>กรมการท่องเที่ยว</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>504</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างการจ้างเหมาบริการบำรุงรักษา ซ่อมแซม และแก้ไขอุปกรณ์เครือข่ายและระบบประชุมทางไกล ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 12 รายการ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -11802,12 +11796,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>★ (อุปกรณ์เครือข่าย, ระบบประชุมทางไกล)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9befc47f-3a0c-485e-a092-61c7ce73b9c6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=19cd5e47-5ce2-4fd5-9409-2e340668402f</t>
         </is>
       </c>
     </row>
@@ -11819,17 +11813,15 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>สำนักงานบริหารหนี้สาธารณะ</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>0309</t>
-        </is>
+          <t>กรมการท่องเที่ยว</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>504</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดหาหน่วยความจำหลัก (RAM) สำหรับเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อวัสดุสำนักงาน ประจำปีงบประมาณ พ.ศ. 2569  จำนวน 97 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -11839,12 +11831,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, หน่วยความจำ)</t>
+          <t>★ (วัสดุสำนักงาน)</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d1f5fe37-48d4-46a5-a2a5-1e42e4a12d7d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c4c7adc7-cc9b-41ce-9e05-2b3d0139c927</t>
         </is>
       </c>
     </row>
@@ -11856,17 +11848,15 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>กรมการท่องเที่ยว</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>0504</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงการพัฒนาสังคมและความมั่นคงของมนุษย์</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>602</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 12 รายการ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์และอุปกรณ์เพื่อเพิ่มประสิทธิภาพในการปฏิบัติงานหน่วยงานในพื้นที่จังหวัดชายแดนภาคใต้ (สงขลา ปัตตานี ยะลา และนราธิวาส) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -11881,7 +11871,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=19cd5e47-5ce2-4fd5-9409-2e340668402f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=24711251-d07c-48d5-8bdb-38d59fb52ef4</t>
         </is>
       </c>
     </row>
@@ -11893,17 +11883,15 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>กรมการท่องเที่ยว</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>0504</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงการพัฒนาสังคมและความมั่นคงของมนุษย์</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>602</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อวัสดุสำนักงาน ประจำปีงบประมาณ พ.ศ. 2569  จำนวน 97 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาซ่อมแซมแก้ไขเครื่องคอมพิวเตอร์พร้อมโปรแกรมอุปกรณ์คอมพิวเตอร์และโสตทัศนูปกรณ์ (ส่วนกลาง) ประจำปีงบประมาณ พ.ศ. 2570 ครั้งที่ 2 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -11913,12 +11901,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>★ (วัสดุสำนักงาน)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c4c7adc7-cc9b-41ce-9e05-2b3d0139c927</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3e9fb3bb-2fcf-447d-b16f-a0708dddad18</t>
         </is>
       </c>
     </row>
@@ -11930,17 +11918,15 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการพัฒนาสังคมและความมั่นคงของมนุษย์</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>0602</t>
-        </is>
+          <t>กรมการข้าว</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>718</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์และอุปกรณ์เพื่อเพิ่มประสิทธิภาพในการปฏิบัติงานหน่วยงานในพื้นที่จังหวัดชายแดนภาคใต้ (สงขลา ปัตตานี ยะลา และนราธิวาส) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การเกษตร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -11950,12 +11936,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=24711251-d07c-48d5-8bdb-38d59fb52ef4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=358d7616-5b03-40b6-8e0a-cefd43ffa7c5</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11953,15 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการพัฒนาสังคมและความมั่นคงของมนุษย์</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>0602</t>
-        </is>
+          <t>กรมการขนส่งทางบก</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>804</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาซ่อมแซมแก้ไขเครื่องคอมพิวเตอร์พร้อมโปรแกรมอุปกรณ์คอมพิวเตอร์และโสตทัศนูปกรณ์ (ส่วนกลาง) ประจำปีงบประมาณ พ.ศ. 2570 ครั้งที่ 2 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมระบบสนับสนุน ศูนย์คอมพิวเตอร์ส่วนกลาง และศูนย์ระบบข้อมูลกลางและสำรองข้อมูล (นนทบุรี) ของกรมการขนส่งทางบกที่ใช้ในการสนับสนุนการปฏิบัติงานด้านความปลอดภัย ทั้งส่วนกลางและส่วนภูมิภาค ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -11992,7 +11976,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3e9fb3bb-2fcf-447d-b16f-a0708dddad18</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ffb1ab1a-8b13-424a-a0b9-82aeabd4a7f0</t>
         </is>
       </c>
     </row>
@@ -12004,17 +11988,15 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>กรมการข้าว</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>0718</t>
-        </is>
+          <t>กรมท่าอากาศยาน</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>805</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การเกษตร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้ออุปกรณ์ควบคุมจอแสดงผล Flight Information Display สำหรับท่าอากาศยาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -12024,12 +12006,12 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (จอแสดงผล)</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=358d7616-5b03-40b6-8e0a-cefd43ffa7c5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a81d531c-fd6f-413c-b3b6-acdd4de90430</t>
         </is>
       </c>
     </row>
@@ -12041,17 +12023,15 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>0804</t>
-        </is>
+          <t>กรมป่าไม้</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>912</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมระบบสนับสนุน ศูนย์คอมพิวเตอร์ส่วนกลาง และศูนย์ระบบข้อมูลกลางและสำรองข้อมูล (นนทบุรี) ของกรมการขนส่งทางบกที่ใช้ในการสนับสนุนการปฏิบัติงานด้านความปลอดภัย ทั้งส่วนกลางและส่วนภูมิภาค ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์เพื่อเพิ่มประสิทธิภาพการจัดทำโครงข่ายหมุดหลักฐานแผนที่และการสำรวจรังวัดเพื่อจัดทำแผนที่แสดงแนวเขตป่าสงวนแห่งชาติ จำนวน ๒๘ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -12061,12 +12041,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ffb1ab1a-8b13-424a-a0b9-82aeabd4a7f0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cc77ea8d-97e1-45d5-aedf-39417f46d256</t>
         </is>
       </c>
     </row>
@@ -12078,17 +12058,15 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
+          <t>องค์การกระจายเสียงและแพร่ภาพสาธารณะแห่งประเทศไทย(ส.ส.ท.)</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>915</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้ออุปกรณ์ควบคุมจอแสดงผล Flight Information Display สำหรับท่าอากาศยาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้ออุปกรณ์จอแสดงผลภาพความละเอียด 4K (Professional Broadcast Monitor) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -12103,7 +12081,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a81d531c-fd6f-413c-b3b6-acdd4de90430</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c9200624-f187-4a68-b96b-2710ebba7083</t>
         </is>
       </c>
     </row>
@@ -12115,17 +12093,15 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>กรมป่าไม้</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>0912</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>1202</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์เพื่อเพิ่มประสิทธิภาพการจัดทำโครงข่ายหมุดหลักฐานแผนที่และการสำรวจรังวัดเพื่อจัดทำแผนที่แสดงแนวเขตป่าสงวนแห่งชาติ จำนวน ๒๘ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าเช่ารถส่วนภูมิภาค รถยนต์ไฟฟ้า ประเภทแบตเตอรี่ (BEV) ขนาดความจุของแบตเตอรี่มากกว่า 50 กิโลวัตต์ชั่วโมง (kWh) และกำลังมอเตอร์ไฟฟ้าสูงสุด ไม่เกิน 150 กิโลวัตต์ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -12135,12 +12111,12 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cc77ea8d-97e1-45d5-aedf-39417f46d256</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6682a0c9-e041-4a68-9c49-d4803a7d2ec9</t>
         </is>
       </c>
     </row>
@@ -12152,17 +12128,15 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>องค์การกระจายเสียงและแพร่ภาพสาธารณะแห่งประเทศไทย(ส.ส.ท.)</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>0915</t>
-        </is>
+          <t>กรมการจัดหางาน</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>1703</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้ออุปกรณ์จอแสดงผลภาพความละเอียด 4K (Professional Broadcast Monitor) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างผลิตและเผยแพร่สื่อประชาสัมพันธ์รูปแบบสื่อโทรทัศน์ สื่อวิทยุ สื่อโฆษณา ในโรงภาพยนตร์ และสื่อป้ายประชาสัมพันธ์จอดิจิทัล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -12172,12 +12146,12 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>★ (จอแสดงผล)</t>
+          <t>★ (โทรทัศน์)</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c9200624-f187-4a68-b96b-2710ebba7083</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6b16630a-851d-4285-be3b-b92e5b89b3f2</t>
         </is>
       </c>
     </row>
@@ -12189,17 +12163,15 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>1202</t>
-        </is>
+          <t>กรมพัฒนาฝีมือแรงงาน</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>1704</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าเช่ารถส่วนภูมิภาค รถยนต์ไฟฟ้า ประเภทแบตเตอรี่ (BEV) ขนาดความจุของแบตเตอรี่มากกว่า 50 กิโลวัตต์ชั่วโมง (kWh) และกำลังมอเตอร์ไฟฟ้าสูงสุด ไม่เกิน 150 กิโลวัตต์ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์โครงการจัดหาครุภัณฑ์คอมพิวเตอร์แท็บเล็ต ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -12209,12 +12181,12 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, แท็บเล็ต, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6682a0c9-e041-4a68-9c49-d4803a7d2ec9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fcba4f1d-218b-4aed-9f5d-9a442ab81e87</t>
         </is>
       </c>
     </row>
@@ -12226,17 +12198,15 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>กรมการจัดหางาน</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>1703</t>
-        </is>
+          <t>กรมส่งเสริมวัฒนธรรม</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>1805</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างผลิตและเผยแพร่สื่อประชาสัมพันธ์รูปแบบสื่อโทรทัศน์ สื่อวิทยุ สื่อโฆษณา ในโรงภาพยนตร์ และสื่อป้ายประชาสัมพันธ์จอดิจิทัล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์สำนักงาน จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -12246,12 +12216,12 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>★ (โทรทัศน์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6b16630a-851d-4285-be3b-b92e5b89b3f2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2d71ed68-e74a-4854-ab7a-80754eb2e6c2</t>
         </is>
       </c>
     </row>
@@ -12263,17 +12233,15 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>กรมพัฒนาฝีมือแรงงาน</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>1704</t>
-        </is>
+          <t>กรมส่งเสริมการเรียนรู้</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>2033</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์โครงการจัดหาครุภัณฑ์คอมพิวเตอร์แท็บเล็ต ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๑๙ รายการ ของกรมส่งเสริมการเรียนรู้ ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -12283,12 +12251,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, แท็บเล็ต, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fcba4f1d-218b-4aed-9f5d-9a442ab81e87</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=321f85d4-75ae-4c7b-8b72-16fdca22a9fb</t>
         </is>
       </c>
     </row>
@@ -12300,17 +12268,15 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมวัฒนธรรม</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>2102</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์สำนักงาน จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดความดันโลหิตชนิดอัตโนมัติ วัดความอิ่มตัวของออกซิเจนในเลือด อุณหภูมิร่างกาย พร้อมระบบเชื่อมต่อฐานข้อมูล จำนวน 34 เครื่อง งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -12320,12 +12286,12 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2d71ed68-e74a-4854-ab7a-80754eb2e6c2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d0ff2fb1-0f33-427b-a238-2e2e93dba2dd</t>
         </is>
       </c>
     </row>
@@ -12337,17 +12303,15 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเรียนรู้</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>2102</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๑๙ รายการ ของกรมส่งเสริมการเรียนรู้ ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องเอกซเรย์เคลื่อนที่ขนาดไม่น้อยกว่า 300 mA.ขับเคลื่อน ด้วยมอเตอร์ไฟฟ้า โรงพยาบาลวังสะพุง ตำบลวังสะพุง อำเภอวังสะพุง จังหวัดเลย ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -12357,12 +12321,12 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=321f85d4-75ae-4c7b-8b72-16fdca22a9fb</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=eccfee9c-8e58-4406-9d64-98150e467dc4</t>
         </is>
       </c>
     </row>
@@ -12377,14 +12341,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C341" t="n">
+        <v>2102</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดความดันโลหิตชนิดอัตโนมัติ วัดความอิ่มตัวของออกซิเจนในเลือด อุณหภูมิร่างกาย พร้อมระบบเชื่อมต่อฐานข้อมูล จำนวน 34 เครื่อง งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องเอกซเรย์เคลื่อนที่ดิจิตอลไม่น้อยกว่า 300 mA. จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -12399,7 +12361,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d0ff2fb1-0f33-427b-a238-2e2e93dba2dd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=00b4843f-9e23-4dc4-ad4a-ddffa8e9e173</t>
         </is>
       </c>
     </row>
@@ -12414,14 +12376,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C342" t="n">
+        <v>2102</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องเอกซเรย์เคลื่อนที่ขนาดไม่น้อยกว่า 300 mA.ขับเคลื่อน ด้วยมอเตอร์ไฟฟ้า โรงพยาบาลวังสะพุง ตำบลวังสะพุง อำเภอวังสะพุง จังหวัดเลย ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการเครื่องผลิตออกซิเจนขนาด ๑๐ ลิตร  จำนวน  ๑๒๐  เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -12431,12 +12391,12 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=eccfee9c-8e58-4406-9d64-98150e467dc4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f4ee01c6-d2a9-4067-8182-aca37b0dc986</t>
         </is>
       </c>
     </row>
@@ -12451,14 +12411,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C343" t="n">
+        <v>2102</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องเอกซเรย์เคลื่อนที่ดิจิตอลไม่น้อยกว่า 300 mA. จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องเอกซเรย์เคลื่อนที่ระบบแพทย์ทางไกลแบบพกพาพร้อมชุดรับสัญญาณภาพดิจิตอลแบบไร้สาย ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 4 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -12473,7 +12431,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=00b4843f-9e23-4dc4-ad4a-ddffa8e9e173</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d21ee284-b4ec-4b00-b103-1743272bab84</t>
         </is>
       </c>
     </row>
@@ -12488,14 +12446,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C344" t="n">
+        <v>2102</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการเครื่องผลิตออกซิเจนขนาด ๑๐ ลิตร  จำนวน  ๑๒๐  เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องเอกซเรย์คอมพิวเตอร์สำหรับงานทันตกรรม (Dental CT) โรงพยาบาลโพนพิสัย ตำบลจุมพล อำเภอโพนพิสัย จังหวัดหนองคาย 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -12505,12 +12461,12 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f4ee01c6-d2a9-4067-8182-aca37b0dc986</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c9d1794d-a7c9-46aa-addf-b688d11337ba</t>
         </is>
       </c>
     </row>
@@ -12525,14 +12481,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C345" t="n">
+        <v>2102</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องเอกซเรย์เคลื่อนที่ระบบแพทย์ทางไกลแบบพกพาพร้อมชุดรับสัญญาณภาพดิจิตอลแบบไร้สาย ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 4 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจคลื่นไฟฟ้าหัวใจ พร้อมเชื่อมต่อระบบแพทย์ทางไกล ของโรงพยาบาลในจังหวัดสุรินทร์ 5 แห่ง จำนวน 7 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -12547,7 +12501,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d21ee284-b4ec-4b00-b103-1743272bab84</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c73e2ea6-2d38-41c5-96a6-159980babdd8</t>
         </is>
       </c>
     </row>
@@ -12562,14 +12516,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C346" t="n">
+        <v>2102</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องเอกซเรย์คอมพิวเตอร์สำหรับงานทันตกรรม (Dental CT) โรงพยาบาลโพนพิสัย ตำบลจุมพล อำเภอโพนพิสัย จังหวัดหนองคาย 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจคลื่นไฟฟ้าหัวใจพร้อมระบบวิเคราะห์ผลและจัดเก็บภาพในระบบเครือข่าย ของโรงพยาบาลส่งเสริมสุขภาพตำบลและโรงพยาบาลชุมชน  5 แห่ง จำนวน 6 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -12579,12 +12531,12 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c9d1794d-a7c9-46aa-addf-b688d11337ba</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bfd52be9-af0a-45e6-978d-679a48f70057</t>
         </is>
       </c>
     </row>
@@ -12599,14 +12551,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C347" t="n">
+        <v>2102</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจคลื่นไฟฟ้าหัวใจ พร้อมเชื่อมต่อระบบแพทย์ทางไกล ของโรงพยาบาลในจังหวัดสุรินทร์ 5 แห่ง จำนวน 7 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดกลาง ของโรงพยาบาลชุมชน 10 แห่ง จำนวน 40 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -12621,7 +12571,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c73e2ea6-2d38-41c5-96a6-159980babdd8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=91baf8a4-d4fe-470d-b554-7e9a6b54deb1</t>
         </is>
       </c>
     </row>
@@ -12636,14 +12586,12 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C348" t="n">
+        <v>2102</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจคลื่นไฟฟ้าหัวใจพร้อมระบบวิเคราะห์ผลและจัดเก็บภาพในระบบเครือข่าย ของโรงพยาบาลส่งเสริมสุขภาพตำบลและโรงพยาบาลชุมชน  5 แห่ง จำนวน 6 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ เครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 6 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง โรงพยาบาลโป่งน้ำร้อน ตำบลทับไทร อำเภอโป่งน้ำร้อน จังหวัดจันทบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -12658,7 +12606,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bfd52be9-af0a-45e6-978d-679a48f70057</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=73a507fa-8ae5-4aad-ae9f-983ec140a858</t>
         </is>
       </c>
     </row>
@@ -12670,17 +12618,15 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>2107</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดกลาง ของโรงพยาบาลชุมชน 10 แห่ง จำนวน 40 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ (กลุ่มเครื่องมือใช้ในห้องปฏิบัติการ) จำนวน ๓ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -12695,7 +12641,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=91baf8a4-d4fe-470d-b554-7e9a6b54deb1</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=27664fff-0d3d-4ba7-ab7a-46fe45870ffa</t>
         </is>
       </c>
     </row>
@@ -12707,17 +12653,15 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>2107</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ เครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 6 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง โรงพยาบาลโป่งน้ำร้อน ตำบลทับไทร อำเภอโป่งน้ำร้อน จังหวัดจันทบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน 3 รายการ เพื่อใช้ในกิจกรรมงานวิศวกรรมความปลอดภัย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -12732,29 +12676,29 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=73a507fa-8ae5-4aad-ae9f-983ec140a858</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1b8e73ca-f574-4f14-868a-65a273dfc3e4</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>กรมสนับสนุนบริการสุขภาพ</t>
+          <t>สำนักงานปลัดสำนักนายกรัฐมนตรี</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>0101</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ (กลุ่มเครื่องมือใช้ในห้องปฏิบัติการ) จำนวน ๓ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดหาครุภัณฑ์สำนักงาน จํานวน ๖ รายการ ให้กับกองจิตอาสาภาครัฐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -12764,34 +12708,34 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=27664fff-0d3d-4ba7-ab7a-46fe45870ffa</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=20a76c1a-1fc3-4b45-bde6-6893a5de5ff5</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>กรมสนับสนุนบริการสุขภาพ</t>
+          <t>กรมสรรพสามิต</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>0306</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน 3 รายการ เพื่อใช้ในกิจกรรมงานวิศวกรรมความปลอดภัย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อเครื่องคอมพิวเตอร์และอุปกรณ์ทดแทน กรณีที่ได้รับความเสียหาย จากเหตุมหาอุทกภัย สำนักงานสรรพสามิตภาคที่ 9 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -12801,12 +12745,604 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1b8e73ca-f574-4f14-868a-65a273dfc3e4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=295785a1-f08f-49fe-adbf-c6f1f5aaefdd</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงการพัฒนาสังคมและความมั่นคงของมนุษย์</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>0602</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์และอุปกรณ์เพื่อเพิ่มประสิทธิภาพในการปฏิบัติงานให้หน่วยงาน สังกัด สป.พม. ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=49d873f5-5a94-465a-bd0d-42601300fe67</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงเกษตรและสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>0702</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 11 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=85284b50-5494-4bff-aef3-e81b40dffb23</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>กรมวิชาการเกษตร</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>0709</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การเกษตร รถฟาร์มแทรกเตอร์ ชนิดขับเคลื่อน 4 ล้อ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8472193c-f7a7-46ea-a054-3baa2082dcfa</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>กรมการข้าว</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>0718</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ee204364-3ba2-42f8-a8f1-7755af4c942d</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างก่อสร้างโครงการก่อสร้างป้ายชื่ออาคารกระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>★ (ป้ายชื่อ)</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d0cbaa04-2515-4981-b3da-1d90f278d003</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการดิจิทัลเพื่อเศรษฐกิจและสังคมแห่งชาติ (สดช.)</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>1109</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างจ้างเหมาบริหารจัดการระบบคอมพิวเตอร์และเครือข่าย ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8fe9a7d5-edf3-4ade-9614-5502384bd3ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>กรมที่ดิน</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อซื้ออุปกรณ์คอมพิวเตอร์ จำนวน 2 รายการ (709 ชุด) สำหรับสำนักงานที่ดินอิเล็กทรอนิกส์ทั้งระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a2fcf17a-d837-4bdf-a253-27b5fc102ec5</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงยุติธรรม</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>1602</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงานอาคารบูรณาการของกระทรวงยุติธรรมจังหวัดเพชรบุรี ๑ โครงการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=844a75f7-3fb0-4dd5-b8a0-3c9702bd04a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงแรงงาน</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>1702</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดหาครุภัณฑ์คอมพิวเตอร์เพื่อทดแทนและเพิ่มประสิทธิภาพให้หน่วยงานในสังกัดสำนักงานปลัดกระทรวงแรงงาน ปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=31eaaa08-4229-42f7-83a8-404ac0543044</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>กรมพัฒนาฝีมือแรงงาน</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>1704</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์โครงการยกระดับระบบการทดสอบมาตรฐานฝีมือแรงงานแห่งชาติด้วยวิธีการทางอิเล็กทรอนิกส์ (E-Testing System) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6887879e-5220-4238-a6f0-8d33deb570e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมวัฒนธรรม</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>1805</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์เครื่องปรับอากาศ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์, เครื่องปรับอากาศ)</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d2c128eb-d286-4202-be10-9625a8edd148</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องเอกซเรย์เคลื่อนที่ระบบแพทย์ทางไกลแบบพกพา พร้อมชุดรับสัญญาณภาพดิจิตอลแบบไร้สาย และระบบจัดเก็บภาพทางรังสีแบบออนไลน์ ของโรงพยาบาลในจังหวัดสุรินทร์ 3 แห่ง จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b4f04823-d63f-476e-ab20-d8119507a82e</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจอวัยวะภายในด้วยคลื่นความถี่สูงพกพาได้พร้อมระบบ Worklist และระบบอ่านผลการแพทย์ทางไกล ของโรงพยาบาลในจังหวัดสุรินทร์ 9 แห่ง จำนวน 10 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2e0c2a2a-4da8-4bd3-bf23-3a9e6b69512f</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยนวดหัวใจและฟื้นคืนชีพผู้ป่วยอัตโนมัติ ของโรงพยาบาลในจังหวัดสุรินทร์ 12 แห่ง จำนวน 14 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e3896a18-a634-4878-b192-029042091d8c</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องรับสัญญาณภาพเอกซเรย์เป็นดิจิตอลชนิดชุดรับภาพแฟลตพาแนลไร้สาย ของโรงพยาบาลในจังหวัดสุรินทร์ 6 แห่ง จำนวน 7 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c93b6fe5-c3b6-4b31-a383-f0c9b466eaab</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องตรวจสมรรถภาพปอดด้วยเครื่องคอมพิวเตอร์ จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=58fe6a28-e217-444d-be04-3538e54580ff</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202609.xlsx
+++ b/Backup/eGP_Monthly_Main_202609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G368"/>
+  <dimension ref="A1:G395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3448,15 +3448,15 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงแรงงาน</t>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามการทุจริตในภาครัฐ</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1702</v>
+        <v>2517</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดหาครุภัณฑ์คอมพิวเตอร์เพื่อทดแทนและเพิ่มประสิทธิภาพให้หน่วยงานในสังกัดสำนักงานปลัดกระทรวงแรงงาน ปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาเครื่องคอมพิวเตอร์แม่ข่าย และระบบความปลอดภัยทางไซเบอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=eea981aa-edb1-4fdf-8067-e5fb7c92e854</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=39110c90-d236-47eb-913a-cb6b3cab18ba</t>
         </is>
       </c>
     </row>
@@ -3483,15 +3483,15 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามการทุจริตในภาครัฐ</t>
+          <t>สำนักงานการตรวจเงินแผ่นดิน</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2517</v>
+        <v>2606</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการบำรุงรักษาเครื่องคอมพิวเตอร์แม่ข่าย และระบบความปลอดภัยทางไซเบอร์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างเหมาบริการขนย้ายเครื่องแม่ข่าย และอุปกรณ์พร้อมติดตั้ง ณ ศูนย์ข้อมูลหลัก ของสำนักงานการตรวจเงินแผ่นดิน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องแม่ข่าย)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=39110c90-d236-47eb-913a-cb6b3cab18ba</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a89ffef4-4bf7-41f2-83ef-2e02a1a4e80c</t>
         </is>
       </c>
     </row>
@@ -3518,15 +3518,15 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>สำนักงานการตรวจเงินแผ่นดิน</t>
+          <t>สำนักงานปลัดกระทรวงการอุดมศึกษา วิทยาศาสตร์ วิจัยและนวัตกรรม</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2606</v>
+        <v>23002</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างเหมาบริการขนย้ายเครื่องแม่ข่าย และอุปกรณ์พร้อมติดตั้ง ณ ศูนย์ข้อมูลหลัก ของสำนักงานการตรวจเงินแผ่นดิน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างเหมาบริการบำรุงรักษาเครื่องปรับอากาศ แบบรวมอะไหล่ จำนวน 606 เครื่อง ภายในอาคารอุดมศึกษา 1 อาคารอุดมศึกษา 2 อาคารพระจอมเกล้า และอาคารอเนกประสงค์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3536,32 +3536,32 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>★ (เครื่องแม่ข่าย)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a89ffef4-4bf7-41f2-83ef-2e02a1a4e80c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4ed51246-9d93-42ff-bb32-e9acb8e03644</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการอุดมศึกษา วิทยาศาสตร์ วิจัยและนวัตกรรม</t>
+          <t>สำนักงานบริหารและพัฒนาองค์ความรู้ (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>23002</v>
+        <v>125</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างเหมาบริการบำรุงรักษาเครื่องปรับอากาศ แบบรวมอะไหล่ จำนวน 606 เครื่อง ภายในอาคารอุดมศึกษา 1 อาคารอุดมศึกษา 2 อาคารพระจอมเกล้า และอาคารอเนกประสงค์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3571,12 +3571,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4ed51246-9d93-42ff-bb32-e9acb8e03644</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=22d2e215-7492-48e1-8b48-52ebf11afb3d</t>
         </is>
       </c>
     </row>
@@ -3588,15 +3588,15 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>สำนักงานบริหารและพัฒนาองค์ความรู้ (องค์การมหาชน)</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>125</v>
+        <v>204</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์คอมพิวเตอร์ ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ พร้อมอุปกรณ์ จำนวน ๘๐ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=22d2e215-7492-48e1-8b48-52ebf11afb3d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ed207e86-fa08-4bf6-b096-f66e9ea91205</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์ พร้อมอุปกรณ์ จำนวน ๘๐ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อสป.สาย ส. ตามโครงการจัดหาอุปกรณ์คอมพิวเตอร์ เพื่อสนับสนุนงานออกแบบสถาปัตยกรรม วิศวกรรมและงานประมาณราคา (ยย.ทบ.) จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ed207e86-fa08-4bf6-b096-f66e9ea91205</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a5d0fbe1-af34-494f-b408-da6f60a04c26</t>
         </is>
       </c>
     </row>
@@ -3658,15 +3658,15 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กรมธนารักษ์</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>204</v>
+        <v>303</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อสป.สาย ส. ตามโครงการจัดหาอุปกรณ์คอมพิวเตอร์ เพื่อสนับสนุนงานออกแบบสถาปัตยกรรม วิศวกรรมและงานประมาณราคา (ยย.ทบ.) จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์อาคารเก็บพัสดุสำนักงานธนารักษ์พื้นที่ชลบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a5d0fbe1-af34-494f-b408-da6f60a04c26</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=606b64be-13e1-468a-84bd-c7c5b46221da</t>
         </is>
       </c>
     </row>
@@ -3693,15 +3693,15 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>กรมธนารักษ์</t>
+          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>303</v>
+        <v>402</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์อาคารเก็บพัสดุสำนักงานธนารักษ์พื้นที่ชลบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาดูแล บำรุงรักษา และล้างทำความสะอาดระบบเครื่องปรับอากาศ ณ อาคารกระทรวงการต่างประเทศ ถนนศรีอยุธยา และศูนย์ราชการเฉลิมพระเกียรติฯ อาคาร B ชั้น 7 - 8 รวม 2 แห่ง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=606b64be-13e1-468a-84bd-c7c5b46221da</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4c0225b9-4c8b-4bbd-80d4-d42eccd0092e</t>
         </is>
       </c>
     </row>
@@ -3728,15 +3728,15 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
+          <t>กรมกิจการเด็กและเยาวชน</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>402</v>
+        <v>605</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาดูแล บำรุงรักษา และล้างทำความสะอาดระบบเครื่องปรับอากาศ ณ อาคารกระทรวงการต่างประเทศ ถนนศรีอยุธยา และศูนย์ราชการเฉลิมพระเกียรติฯ อาคาร B ชั้น 7 - 8 รวม 2 แห่ง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาเครื่องคอมพิวเตอร์ อุปกรณ์ต่อพ่วง และระบบสารสนเทศ ของ ดย. ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4c0225b9-4c8b-4bbd-80d4-d42eccd0092e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cb192597-9852-49f1-81d0-f9bd008c7f6d</t>
         </is>
       </c>
     </row>
@@ -3763,15 +3763,15 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>กรมกิจการเด็กและเยาวชน</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>605</v>
+        <v>704</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาเครื่องคอมพิวเตอร์ อุปกรณ์ต่อพ่วง และระบบสารสนเทศ ของ ดย. ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อครุภัณฑ์ยานพาหนะและขนส่งรถโดยสารขนาด 12 ที่นั่ง (ดีเซล) จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cb192597-9852-49f1-81d0-f9bd008c7f6d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3d257d5-116f-4d11-9cba-b2af7ffd9693</t>
         </is>
       </c>
     </row>
@@ -3798,15 +3798,15 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมประมง</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อประกวดราคาจัดซื้อครุภัณฑ์ยานพาหนะและขนส่งรถโดยสารขนาด 12 ที่นั่ง (ดีเซล) จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างการจัดจ้างบำรุงรักษาครุภัณฑ์คอมพิวเตอร์สำหรับการรักษาความปลอดภัยของระบบเครือข่ายและคอมพิวเตอร์ จำนวน 1 งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3d257d5-116f-4d11-9cba-b2af7ffd9693</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=29210ba8-e1c2-4d7e-80d4-6acfeb801f71</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างการจัดจ้างบำรุงรักษาครุภัณฑ์คอมพิวเตอร์สำหรับการรักษาความปลอดภัยของระบบเครือข่ายและคอมพิวเตอร์ จำนวน 1 งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างการจัดจ้างบำรุงรักษาอุปกรณ์กระจายสัญญาณ จำนวน ๑ งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=29210ba8-e1c2-4d7e-80d4-6acfeb801f71</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b2bbd6f5-c7a5-4bc3-be9e-fc1ddf4ac0a8</t>
         </is>
       </c>
     </row>
@@ -3868,15 +3868,15 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>กรมประมง</t>
+          <t>สำนักงานมาตรฐานสินค้าเกษตรและอาหารแห่งชาติ</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>705</v>
+        <v>714</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างการจัดจ้างบำรุงรักษาอุปกรณ์กระจายสัญญาณ จำนวน ๑ งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการจ้างเหมาดูแลและบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์และระบบคอมพิวเตอร์พร้อมอุปกรณ์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b2bbd6f5-c7a5-4bc3-be9e-fc1ddf4ac0a8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d133e360-c57e-4330-bff5-2f10cf027da9</t>
         </is>
       </c>
     </row>
@@ -3903,15 +3903,15 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>สำนักงานมาตรฐานสินค้าเกษตรและอาหารแห่งชาติ</t>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>714</v>
+        <v>1302</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการจ้างเหมาดูแลและบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์และระบบคอมพิวเตอร์พร้อมอุปกรณ์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องคอมพิวเตอร์และอุปกรณ์ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d133e360-c57e-4330-bff5-2f10cf027da9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=04549f6b-e678-4005-91df-2993ee4bdb83</t>
         </is>
       </c>
     </row>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องคอมพิวเตอร์และอุปกรณ์ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่ายของสำนักงานพาณิชย์จังหวัด 76 จังหวัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=04549f6b-e678-4005-91df-2993ee4bdb83</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f1e51f04-f935-4983-8200-42b44f480fc9</t>
         </is>
       </c>
     </row>
@@ -3973,15 +3973,15 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+          <t>สถาบันส่งเสริมศิลปหัตถกรรมไทย (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1302</v>
+        <v>1311</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่ายของสำนักงานพาณิชย์จังหวัด 76 จังหวัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการจัดหาพนักงานดูแลหอนิทรรศการและห้องสมุด ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (สมุด)</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f1e51f04-f935-4983-8200-42b44f480fc9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ff1d2fa-ba06-4da0-bc6c-023504d3c9d6</t>
         </is>
       </c>
     </row>
@@ -4008,15 +4008,15 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>สถาบันส่งเสริมศิลปหัตถกรรมไทย (องค์การมหาชน)</t>
+          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1311</v>
+        <v>1808</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการจัดหาพนักงานดูแลหอนิทรรศการและห้องสมุด ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์อื่นๆ (เครื่องแต่งกายโขน-ละคร) จำนวน 7 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>★ (สมุด)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ff1d2fa-ba06-4da0-bc6c-023504d3c9d6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8e14fee9-d40a-4d5f-b4ec-b5dd1cbdcc29</t>
         </is>
       </c>
     </row>
@@ -4043,15 +4043,15 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
+          <t>กรมส่งเสริมการเรียนรู้</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1808</v>
+        <v>2033</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์อื่นๆ (เครื่องแต่งกายโขน-ละคร) จำนวน 7 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4061,12 +4061,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8e14fee9-d40a-4d5f-b4ec-b5dd1cbdcc29</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=988b1f6a-eb89-4ed1-bbe5-4e82ba43054b</t>
         </is>
       </c>
     </row>
@@ -4078,15 +4078,15 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเรียนรู้</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2033</v>
+        <v>2102</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการตู้เย็นเก็บเลือดขนาดไม่น้อยกว่า 20 คิว ของโรงพยาบาลในจังหวัดสุรินทร์ 6 แห่ง จำนวน 7 ตู้ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์, ตู้เย็น)</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=988b1f6a-eb89-4ed1-bbe5-4e82ba43054b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dfce18c4-7835-4a43-8ba6-fb9a2b9ab472</t>
         </is>
       </c>
     </row>
@@ -4113,15 +4113,15 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมอนามัย</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2102</v>
+        <v>2109</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการตู้เย็นเก็บเลือดขนาดไม่น้อยกว่า 20 คิว ของโรงพยาบาลในจังหวัดสุรินทร์ 6 แห่ง จำนวน 7 ตู้ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่าย กรมอนามัย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4131,12 +4131,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์, ตู้เย็น)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dfce18c4-7835-4a43-8ba6-fb9a2b9ab472</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0f1ebcb1-8a09-4209-922e-0e2e49160cba</t>
         </is>
       </c>
     </row>
@@ -4148,15 +4148,15 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>กรมอนามัย</t>
+          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>2109</v>
+        <v>2113</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่าย กรมอนามัย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์แม่ข่าย (Outsource System) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0f1ebcb1-8a09-4209-922e-0e2e49160cba</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1c3629ca-59d6-4b8a-839b-92b06d6a1c43</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์แม่ข่าย (Outsource System) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์เครือข่าย (Outsource Network) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4206,27 +4206,27 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1c3629ca-59d6-4b8a-839b-92b06d6a1c43</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b44df475-19c0-4304-b42e-0c379f2f6a07</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+          <t>กองทัพอากาศ</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2113</v>
+        <v>206</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์เครือข่าย (Outsource Network) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโต๊ะและเก้าอี้ประชุม จำนวน ๒ รายการ (แจ้งที่ ๘๙๖/๖๙) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (โต๊ะ, เก้าอี้)</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b44df475-19c0-4304-b42e-0c379f2f6a07</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c197cbba-6119-4a85-8655-64df092381b8</t>
         </is>
       </c>
     </row>
@@ -4253,15 +4253,15 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>กองทัพอากาศ</t>
+          <t>กรมศุลกากร</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>206</v>
+        <v>305</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโต๊ะและเก้าอี้ประชุม จำนวน ๒ รายการ (แจ้งที่ ๘๙๖/๖๙) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องปรับอากาศ แบบฝังฝ้าสี่ทิศทาง (ระบบ Inverter) ขนาด 48,000 บีทียู ด่านศุลกากรปาดังเบซาร์ ตำบลปาดังเบซาร์ อำเภอสะเดา จังหวัดสงขลา 12 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>★ (โต๊ะ, เก้าอี้)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c197cbba-6119-4a85-8655-64df092381b8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7ffdc802-88d9-422f-a01b-27711177cb61</t>
         </is>
       </c>
     </row>
@@ -4288,15 +4288,15 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>กรมศุลกากร</t>
+          <t>กรมสรรพากร</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องปรับอากาศ แบบฝังฝ้าสี่ทิศทาง (ระบบ Inverter) ขนาด 48,000 บีทียู ด่านศุลกากรปาดังเบซาร์ ตำบลปาดังเบซาร์ อำเภอสะเดา จังหวัดสงขลา 12 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบ ไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 2,400 ซีซี  หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ จำนวน 5 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7ffdc802-88d9-422f-a01b-27711177cb61</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e642705c-f34c-41db-ad86-705717edf0ea</t>
         </is>
       </c>
     </row>
@@ -4323,15 +4323,15 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>กรมสรรพากร</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>307</v>
+        <v>704</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบ ไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 2,400 ซีซี  หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ จำนวน 5 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e642705c-f34c-41db-ad86-705717edf0ea</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5b0cc17-68bd-4696-805e-f78e075178e3</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุด ไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4376,12 +4376,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5b0cc17-68bd-4696-805e-f78e075178e3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=106210e4-0233-403f-957c-c894b083d53b</t>
         </is>
       </c>
     </row>
@@ -4393,15 +4393,15 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมส่งเสริมการเกษตร</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุด ไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดชื้อครุภัณฑ์ยานพาหนะและขนส่ง ประจำปีงบประมาณ พ.ศ 2570 โดยวิธีประกวดอิเล็กทรอนิกส์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=106210e4-0233-403f-957c-c894b083d53b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ec4d9c1c-1aa5-4b14-b3ea-60845e7335fb</t>
         </is>
       </c>
     </row>
@@ -4428,15 +4428,15 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเกษตร</t>
+          <t>กรมส่งเสริมสหกรณ์</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดชื้อครุภัณฑ์ยานพาหนะและขนส่ง ประจำปีงบประมาณ พ.ศ 2570 โดยวิธีประกวดอิเล็กทรอนิกส์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาบรรทุกขนาด 1 ตัน หลังคาไฟเบอร์กลาส หรือเหล็กหรือพลาสติกวิศวกรรม สำนักงานสหกรณ์จังหวัดศรีสะเกษ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ec4d9c1c-1aa5-4b14-b3ea-60845e7335fb</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=51b057ec-ffcf-432e-bf86-fe4029225a82</t>
         </is>
       </c>
     </row>
@@ -4463,15 +4463,15 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมสหกรณ์</t>
+          <t>กรมพัฒนาธุรกิจการค้า</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>712</v>
+        <v>1308</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาบรรทุกขนาด 1 ตัน หลังคาไฟเบอร์กลาส หรือเหล็กหรือพลาสติกวิศวกรรม สำนักงานสหกรณ์จังหวัดศรีสะเกษ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องคอมพิวเตอร์ลูกข่ายและอุปกรณ์ต่อพ่วง ปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=51b057ec-ffcf-432e-bf86-fe4029225a82</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=be5cf0cb-614f-4d37-aac0-190b90321cb6</t>
         </is>
       </c>
     </row>
@@ -4498,15 +4498,15 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>กรมพัฒนาธุรกิจการค้า</t>
+          <t>กรมโยธาธิการและผังเมือง</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1308</v>
+        <v>1507</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องคอมพิวเตอร์ลูกข่ายและอุปกรณ์ต่อพ่วง ปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างโครงการจัดหาสิ่งก่อสร้างและครุภัณฑ์ประกอบ อาคารสำนักงานแห่งใหม่ของสำนักงบประมาณ แขวงพญาไท เขตพญาไท กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=be5cf0cb-614f-4d37-aac0-190b90321cb6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8b31f2b3-f6fd-4e5c-979f-8575feda4bbf</t>
         </is>
       </c>
     </row>
@@ -4533,15 +4533,15 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>กรมโยธาธิการและผังเมือง</t>
+          <t>กรมการศาสนา</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1507</v>
+        <v>1803</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างโครงการจัดหาสิ่งก่อสร้างและครุภัณฑ์ประกอบ อาคารสำนักงานแห่งใหม่ของสำนักงบประมาณ แขวงพญาไท เขตพญาไท กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อวัสดุสำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (วัสดุสำนักงาน)</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8b31f2b3-f6fd-4e5c-979f-8575feda4bbf</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=07f7d716-619d-4e73-9518-7f683a4a05ed</t>
         </is>
       </c>
     </row>
@@ -4568,15 +4568,15 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>กรมการศาสนา</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1803</v>
+        <v>2102</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อวัสดุสำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการชุดกระเป๋าปฐมพยาบาลสนามประจำตัวเจ้าหน้าที่ (IFAK) ของโรงพยาบาลชุมชน 11 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบล 40 แห่ง จำนวน 117 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4586,12 +4586,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>★ (วัสดุสำนักงาน)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=07f7d716-619d-4e73-9518-7f683a4a05ed</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=197d72c1-0e0f-4f3d-a377-6f7e052fd668</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการชุดกระเป๋าปฐมพยาบาลสนามประจำตัวเจ้าหน้าที่ (IFAK) ของโรงพยาบาลชุมชน 11 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบล 40 แห่ง จำนวน 117 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=197d72c1-0e0f-4f3d-a377-6f7e052fd668</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a903de26-6f92-4b12-bcdc-87924b3b825b</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อสิทธิ์ใช้งานซอฟต์แวร์จัดการความเสี่ยงเกี่ยวกับระบบสารสนเทศ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a903de26-6f92-4b12-bcdc-87924b3b825b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f182625c-e015-489e-84e0-ac3c9c8dc788</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อสิทธิ์ใช้งานซอฟต์แวร์จัดการความเสี่ยงเกี่ยวกับระบบสารสนเทศ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ กล้องถ่ายภาพจอประสาทตาดิจิตอล (Digital Fundus Camera) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>★ (ซอฟต์แวร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f182625c-e015-489e-84e0-ac3c9c8dc788</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=810bd451-770f-4032-86a0-1216954db79a</t>
         </is>
       </c>
     </row>
@@ -4708,15 +4708,15 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สำนักงานคณะกรรมการอาหารและยา</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>2102</v>
+        <v>2110</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ กล้องถ่ายภาพจอประสาทตาดิจิตอล (Digital Fundus Camera) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=810bd451-770f-4032-86a0-1216954db79a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=69d9687c-b7f1-405c-843e-92b98ad29261</t>
         </is>
       </c>
     </row>
@@ -4743,15 +4743,15 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการอาหารและยา</t>
+          <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2110</v>
+        <v>2117</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อติดตั้งระบบกล้องวงจรปิด ของวิทยาลัยพยาบาลบรมราชชนนี นครศรีธรรมราช จำนวน 1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4761,32 +4761,32 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (กล้องวงจรปิด)</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=69d9687c-b7f1-405c-843e-92b98ad29261</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afa9b388-be98-4ed1-8fa9-0c791e5acf34</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>กรมธนารักษ์</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2117</v>
+        <v>303</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อติดตั้งระบบกล้องวงจรปิด ของวิทยาลัยพยาบาลบรมราชชนนี นครศรีธรรมราช จำนวน 1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการทำความสะอาดศูนย์คอมพิวเตอร์แห่งใหม่ ของกรมธนารักษ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>★ (กล้องวงจรปิด)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afa9b388-be98-4ed1-8fa9-0c791e5acf34</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=36f30dd7-0674-4711-a8ba-e71eee8e8ed2</t>
         </is>
       </c>
     </row>
@@ -4813,15 +4813,15 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>กรมธนารักษ์</t>
+          <t>สำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>303</v>
+        <v>502</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการทำความสะอาดศูนย์คอมพิวเตอร์แห่งใหม่ ของกรมธนารักษ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการค่าใช้จ่ายโครงการค่าจ้างบำรุงรักษาและซ่อมแซมห้องปฏิบัติการระบบเครือข่ายคอมพิวเตอร์ (Data Center) ของสำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=36f30dd7-0674-4711-a8ba-e71eee8e8ed2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=056989d3-d491-44ed-b887-fca9a5a8f472</t>
         </is>
       </c>
     </row>
@@ -4848,15 +4848,15 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา</t>
+          <t>กรมส่งเสริมและพัฒนาคุณภาพชีวิตคนพิการ</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>502</v>
+        <v>607</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการค่าใช้จ่ายโครงการค่าจ้างบำรุงรักษาและซ่อมแซมห้องปฏิบัติการระบบเครือข่ายคอมพิวเตอร์ (Data Center) ของสำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์งานบ้านงานครัวและครุภัณฑ์สำนักงาน จำนวน ๒๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=056989d3-d491-44ed-b887-fca9a5a8f472</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f387eaf-54e2-4cf6-8c1c-826da6e3d09e</t>
         </is>
       </c>
     </row>
@@ -4883,15 +4883,15 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมและพัฒนาคุณภาพชีวิตคนพิการ</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>607</v>
+        <v>704</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์งานบ้านงานครัวและครุภัณฑ์สำนักงาน จำนวน ๒๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องปรับอากาศแบบแยกส่วน (ราคารวมค่าติดตั้ง) แบบตั้งพื้นหรือแบบแขวน(ระบบ Inverter) ขนาดไม่ต่ำกว่า 36,000 บีทียู จำนวน 13 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f387eaf-54e2-4cf6-8c1c-826da6e3d09e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=08075ad1-9390-4520-9d46-f5c2637228e2</t>
         </is>
       </c>
     </row>
@@ -4918,15 +4918,15 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมส่งเสริมสหกรณ์</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องปรับอากาศแบบแยกส่วน (ราคารวมค่าติดตั้ง) แบบตั้งพื้นหรือแบบแขวน(ระบบ Inverter) ขนาดไม่ต่ำกว่า 36,000 บีทียู จำนวน 13 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=08075ad1-9390-4520-9d46-f5c2637228e2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=282d8226-b5a6-422f-ad5a-96682acbb042</t>
         </is>
       </c>
     </row>
@@ -4953,15 +4953,15 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมสหกรณ์</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>712</v>
+        <v>806</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องตรวจวัดปริมาณแอลกอฮอล์ จำนวน 10 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (แอลกอฮอล์)</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=282d8226-b5a6-422f-ad5a-96682acbb042</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=152668c9-b054-48b8-9423-57975423ef48</t>
         </is>
       </c>
     </row>
@@ -4988,15 +4988,15 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>กรมการเปลี่ยนแปลงสภาพภูมิอากาศและสิ่งแวดล้อม</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>806</v>
+        <v>908</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องตรวจวัดปริมาณแอลกอฮอล์ จำนวน 10 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาอุปกรณ์ห้อง Data center และเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>★ (แอลกอฮอล์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=152668c9-b054-48b8-9423-57975423ef48</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3fa0cd84-f2db-47df-b581-c3555885f305</t>
         </is>
       </c>
     </row>
@@ -5023,15 +5023,15 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>กรมการเปลี่ยนแปลงสภาพภูมิอากาศและสิ่งแวดล้อม</t>
+          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>908</v>
+        <v>1202</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาอุปกรณ์ห้อง Data center และเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์เครือข่ายและอุปกรณ์คอมพิวเตอร์แม่ข่าย และอุปกรณ์สำรองข้อมูล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3fa0cd84-f2db-47df-b581-c3555885f305</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=86fe9b9f-c1ba-4f83-8b12-70dbc5d76baa</t>
         </is>
       </c>
     </row>
@@ -5058,15 +5058,15 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1202</v>
+        <v>1302</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์เครือข่ายและอุปกรณ์คอมพิวเตอร์แม่ข่าย และอุปกรณ์สำรองข้อมูล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์สำหรับงานจดทะเบียนและตรวจสอบธุรกิจผิดกฎหมาย กลุ่มทะเบียนธุรกิจและอำนวยความสะดวกทางการค้าของสำนักงานพาณิชย์จังหวัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=86fe9b9f-c1ba-4f83-8b12-70dbc5d76baa</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=06246921-2a22-4f4d-822b-d5abae1c7c8c</t>
         </is>
       </c>
     </row>
@@ -5093,15 +5093,15 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+          <t>กรมสอบสวนคดีพิเศษ</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1302</v>
+        <v>1608</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์สำหรับงานจดทะเบียนและตรวจสอบธุรกิจผิดกฎหมาย กลุ่มทะเบียนธุรกิจและอำนวยความสะดวกทางการค้าของสำนักงานพาณิชย์จังหวัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าเช่าใช้บริการสายสัญญาณเชื่อมโยงเครือข่ายอินเตอร์เน็ตพร้อมระบบ Internet Data Center ประจำปีงบประมาณ พ.ศ. 2570 (เดือนตุลาคม 2569  เดือนกันยายน 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (สายสัญญาณ)</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=06246921-2a22-4f4d-822b-d5abae1c7c8c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f0c10124-df0c-410d-961c-bb4afe1ea16a</t>
         </is>
       </c>
     </row>
@@ -5128,15 +5128,15 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>กรมสอบสวนคดีพิเศษ</t>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าเช่าใช้บริการสายสัญญาณเชื่อมโยงเครือข่ายอินเตอร์เน็ตพร้อมระบบ Internet Data Center ประจำปีงบประมาณ พ.ศ. 2570 (เดือนตุลาคม 2569  เดือนกันยายน 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบประชุมทางไกลผ่านจอภาพ (Video Conference)  ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>★ (สายสัญญาณ)</t>
+          <t>★ (จอภาพ, ระบบประชุมทางไกล)</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f0c10124-df0c-410d-961c-bb4afe1ea16a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bb2e1625-bd6e-49b0-bf5e-6f3975c796e5</t>
         </is>
       </c>
     </row>
@@ -5163,15 +5163,15 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1611</v>
+        <v>2102</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบประชุมทางไกลผ่านจอภาพ (Video Conference)  ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันขนาดกลาง โรงพยาบาลเขาย้อย ตำบลเขาย้อย อำเภอเขาย้อย จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>★ (จอภาพ, ระบบประชุมทางไกล)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bb2e1625-bd6e-49b0-bf5e-6f3975c796e5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4d438ead-6d3b-40c3-8e25-0c855ca2699d</t>
         </is>
       </c>
     </row>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันขนาดกลาง โรงพยาบาลเขาย้อย ตำบลเขาย้อย อำเภอเขาย้อย จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง โรงพยาบาลหนองหญ้าปล้อง ตำบลหนองหญ้าปล้อง อำเภอหนองหญ้าปล้อง จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4d438ead-6d3b-40c3-8e25-0c855ca2699d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=38179365-12e6-43e5-ac4b-973f7d7d62c9</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง โรงพยาบาลหนองหญ้าปล้อง ตำบลหนองหญ้าปล้อง อำเภอหนองหญ้าปล้อง จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดัน ขนาดใหญ่ จำนวน 2 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=38179365-12e6-43e5-ac4b-973f7d7d62c9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2c8651ab-6342-4cf7-b1d4-44acb01ef167</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดัน ขนาดใหญ่ จำนวน 2 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดเล็ก ของโรงพยาบาลชุมชน 2 แห่ง จำนวน 6 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2c8651ab-6342-4cf7-b1d4-44acb01ef167</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=092dea18-169e-423d-bdf4-cbb905df5ef4</t>
         </is>
       </c>
     </row>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดเล็ก ของโรงพยาบาลชุมชน 2 แห่ง จำนวน 6 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องเอกซเรย์เคลื่อนที่ขนาดไม่น้อยกว่า 300 mA.ขับเคลื่อนด้วยมอเตอร์ไฟฟ้า ของโรงพยาบาลในจังหวัดสุรินทร์ 3 แห่ง จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์, มอเตอร์)</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=092dea18-169e-423d-bdf4-cbb905df5ef4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=587ceaac-9b51-4f53-a40b-ba6307295dbc</t>
         </is>
       </c>
     </row>
@@ -5338,15 +5338,15 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมการแพทย์แผนไทยและการแพทย์ทางเลือก</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>2102</v>
+        <v>2105</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องเอกซเรย์เคลื่อนที่ขนาดไม่น้อยกว่า 300 mA.ขับเคลื่อนด้วยมอเตอร์ไฟฟ้า ของโรงพยาบาลในจังหวัดสุรินทร์ 3 แห่ง จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างบำรุงรักษาและซ่อมแซมแก้ไขปัญหาเครื่องคอมพิวเตอร์แม่ข่ายและอุปกรณ์ระบบเครือข่าย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์, มอเตอร์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=587ceaac-9b51-4f53-a40b-ba6307295dbc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a18ab514-a7bf-42a3-be34-78ab2073afdd</t>
         </is>
       </c>
     </row>
@@ -5373,15 +5373,15 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>กรมการแพทย์แผนไทยและการแพทย์ทางเลือก</t>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างบำรุงรักษาและซ่อมแซมแก้ไขปัญหาเครื่องคอมพิวเตอร์แม่ข่ายและอุปกรณ์ระบบเครือข่าย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน ๙ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -5391,12 +5391,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a18ab514-a7bf-42a3-be34-78ab2073afdd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70e80b61-ece5-4761-bcba-cb1ce4f2a872</t>
         </is>
       </c>
     </row>
@@ -5408,15 +5408,15 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>กรมวิทยาศาสตร์การแพทย์</t>
+          <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>2106</v>
+        <v>2117</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน ๙ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อึครุภัณฑ์สำนักงาน รายการเครื่องปรับอากาศและพัดลม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ, พัดลม)</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70e80b61-ece5-4761-bcba-cb1ce4f2a872</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8cf26d57-cf1b-4ebf-8134-fcf45b7f7c54</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อึครุภัณฑ์สำนักงาน รายการเครื่องปรับอากาศและพัดลม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง (รถยนต์บรรทุกโดยสาร 6 ล้อ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ, พัดลม)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8cf26d57-cf1b-4ebf-8134-fcf45b7f7c54</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=37a7653e-4e42-4513-bc7a-c74cd6a83f90</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>สถาบันเทคโนโลยีป้องกันประเทศ</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>2117</v>
+        <v>209</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง (รถยนต์บรรทุกโดยสาร 6 ล้อ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างซ่อมบำรุงตามวงรอบเครื่องปรับอากาศ อาคาร สป. (แจ้งวัฒนะ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=37a7653e-4e42-4513-bc7a-c74cd6a83f90</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=97592008-d14e-46f6-93ee-062a71e2e9a9</t>
         </is>
       </c>
     </row>
@@ -5513,15 +5513,15 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>สถาบันเทคโนโลยีป้องกันประเทศ</t>
+          <t>สำนักงานปลัดกระทรวงการคลัง</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>209</v>
+        <v>302</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างซ่อมบำรุงตามวงรอบเครื่องปรับอากาศ อาคาร สป. (แจ้งวัฒนะ) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อการจัดซื้อหมึกพิมพ์สำหรับ GFMIS Terminal Set เพื่อใช้งานในระบบ New GFMIS Thai ของกรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5531,12 +5531,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (หมึกพิมพ์)</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=97592008-d14e-46f6-93ee-062a71e2e9a9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=95f4ee7d-0617-43e5-8099-6f58ee3f83c4</t>
         </is>
       </c>
     </row>
@@ -5548,15 +5548,15 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการคลัง</t>
+          <t>กรมชลประทาน</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>302</v>
+        <v>703</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อการจัดซื้อหมึกพิมพ์สำหรับ GFMIS Terminal Set เพื่อใช้งานในระบบ New GFMIS Thai ของกรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจัดหาและติดตั้งเครื่องสูบน้ำชนิดหอยโข่งแบบ Horizontal Split Case ขับด้วยมอเตอร์ไฟฟ้าอัตราสูบน้ำ ๐.๒๕ ลบ.ม. /วินาที ระยะยกน้ำไม่น้อยกว่า ๔๕ เมตร และอื่นๆ รวม ๔ รายการ  สำหรับงานสถานีสูบน้ำด้วยไฟฟ้าพร้อมระบบส่งน้ำ บ้านสุขสำราญ ตำบลเหล่าต่างคำ อำเภอโพนพิสัย จังหวัดหนองคาย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>★ (หมึกพิมพ์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=95f4ee7d-0617-43e5-8099-6f58ee3f83c4</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=766b91be-9aee-491f-bc67-3378c2319ca0</t>
         </is>
       </c>
     </row>
@@ -5583,15 +5583,15 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>กรมชลประทาน</t>
+          <t>กรมประมง</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจัดหาและติดตั้งเครื่องสูบน้ำชนิดหอยโข่งแบบ Horizontal Split Case ขับด้วยมอเตอร์ไฟฟ้าอัตราสูบน้ำ ๐.๒๕ ลบ.ม. /วินาที ระยะยกน้ำไม่น้อยกว่า ๔๕ เมตร และอื่นๆ รวม ๔ รายการ  สำหรับงานสถานีสูบน้ำด้วยไฟฟ้าพร้อมระบบส่งน้ำ บ้านสุขสำราญ ตำบลเหล่าต่างคำ อำเภอโพนพิสัย จังหวัดหนองคาย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน 4 รายการ วิธีประกาศเชิญชวน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=766b91be-9aee-491f-bc67-3378c2319ca0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6af84224-9211-4bd4-b2c3-7790e12e9c3f</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน 4 รายการ วิธีประกาศเชิญชวน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน 4 รายการ  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6af84224-9211-4bd4-b2c3-7790e12e9c3f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=106fd353-637b-4b85-b19c-e5222b434807</t>
         </is>
       </c>
     </row>
@@ -5653,15 +5653,15 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>กรมประมง</t>
+          <t>สำนักงานเศรษฐกิจการเกษตร</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน 4 รายการ  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์หรือระบบสารสนเทศ (โครงการจ้างบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์เครือข่ายและเครื่องคอมพิวเตอร์แม่ข่าย ประจำปีงบประมาณ พ.ศ. 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=106fd353-637b-4b85-b19c-e5222b434807</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e3936fb8-2fe4-4ded-a393-134ec5675427</t>
         </is>
       </c>
     </row>
@@ -5688,15 +5688,15 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>สำนักงานเศรษฐกิจการเกษตร</t>
+          <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>715</v>
+        <v>804</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์หรือระบบสารสนเทศ (โครงการจ้างบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์เครือข่ายและเครื่องคอมพิวเตอร์แม่ข่าย ประจำปีงบประมาณ พ.ศ. 2570) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์พร้อมอุปกรณ์ของระบบการคุ้มครองผู้โดยสารและ การบังคับใช้กฎหมายทั่วไทย (1584 และปรับทั่วไทย) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e3936fb8-2fe4-4ded-a393-134ec5675427</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f5c51a3c-9d4b-4662-a9c5-a560b97ab60f</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์พร้อมอุปกรณ์ของระบบการคุ้มครองผู้โดยสารและ การบังคับใช้กฎหมายทั่วไทย (1584 และปรับทั่วไทย) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างรั้ว ประตูทางเข้า - ออก ป้ายชื่อสำนักงาน และป้อมยามรักษาการณ์ สำนักงานขนส่งจังหวัดลำปาง ตำบลพระบาท อำเภอเมือง จังหวัดลำปาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ป้ายชื่อ)</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f5c51a3c-9d4b-4662-a9c5-a560b97ab60f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f104579c-ae74-4bdb-a71c-250b1777b2c9</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างรั้ว ประตูทางเข้า - ออก ป้ายชื่อสำนักงาน และป้อมยามรักษาการณ์ สำนักงานขนส่งจังหวัดลำปาง ตำบลพระบาท อำเภอเมือง จังหวัดลำปาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขเครื่องคอมพิวเตอร์พร้อมอุปกรณ์ที่ใช้ในการพัฒนาความรู้สารสนเทศ  ด้านความปลอดภัยของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>★ (ป้ายชื่อ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f104579c-ae74-4bdb-a71c-250b1777b2c9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a8c5a924-f969-4f66-a783-51c748bd5141</t>
         </is>
       </c>
     </row>
@@ -5793,15 +5793,15 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
+          <t>กรมอุตุนิยมวิทยา</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>804</v>
+        <v>1104</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขเครื่องคอมพิวเตอร์พร้อมอุปกรณ์ที่ใช้ในการพัฒนาความรู้สารสนเทศ  ด้านความปลอดภัยของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาอุปกรณ์กระจายสัญญาณหลัก (Core Switch) ประจำปีงบประมาณ พ.ศ.2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a8c5a924-f969-4f66-a783-51c748bd5141</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b6951565-26a5-4131-b672-af48d4974842</t>
         </is>
       </c>
     </row>
@@ -5828,15 +5828,15 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>กรมอุตุนิยมวิทยา</t>
+          <t>กรมที่ดิน</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1104</v>
+        <v>1505</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาอุปกรณ์กระจายสัญญาณหลัก (Core Switch) ประจำปีงบประมาณ พ.ศ.2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโต๊ะและเก้าอี้เพื่อใช้ในราชการของสำนักงานที่ดินจังหวัดพิษณุโลก และสาขา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>★ (อุปกรณ์กระจายสัญญาณ)</t>
+          <t>★ (โต๊ะ, เก้าอี้)</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b6951565-26a5-4131-b672-af48d4974842</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=06a6ae3e-1109-434c-becf-df99302f96f5</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโต๊ะและเก้าอี้เพื่อใช้ในราชการของสำนักงานที่ดินจังหวัดพิษณุโลก และสาขา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบงานและอุปกรณ์คอมพิวเตอร์ ตามโครงการพัฒนาระบบสารสนเทศที่ดิน (ระยะที่ ๒) ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -5881,12 +5881,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>★ (โต๊ะ, เก้าอี้)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=06a6ae3e-1109-434c-becf-df99302f96f5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0e343fde-5a22-4f02-b2b3-bcf7cfd99bf2</t>
         </is>
       </c>
     </row>
@@ -5898,15 +5898,15 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>กรมที่ดิน</t>
+          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1505</v>
+        <v>1808</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบงานและอุปกรณ์คอมพิวเตอร์ ตามโครงการพัฒนาระบบสารสนเทศที่ดิน (ระยะที่ ๒) ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์การศึกษา (ห้องเรียนอัจฉริยะไฮบริด Smart Hybrid Classroom) ห้องเรียนวิชาชีพ จำนวน 1 ห้อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0e343fde-5a22-4f02-b2b3-bcf7cfd99bf2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a6ddc2c9-4ad2-4cd7-93c9-2b5e9a715cfd</t>
         </is>
       </c>
     </row>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์การศึกษา (ห้องเรียนอัจฉริยะไฮบริด Smart Hybrid Classroom) ห้องเรียนวิชาชีพ จำนวน 1 ห้อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์โฆษณาแะเผยแพร่ (ระบบภาพ LED Display พร้อมติดตั้งภายนอกอาคาร) จำนวน  1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a6ddc2c9-4ad2-4cd7-93c9-2b5e9a715cfd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7b99fd52-1723-486a-a5ce-43a450641ed9</t>
         </is>
       </c>
     </row>
@@ -5968,15 +5968,15 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>สถาบันบัณฑิตพัฒนศิลป์</t>
+          <t>สำนักงานนวัตกรรมแห่งชาติ (องค์การมหาชน)</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1808</v>
+        <v>1913</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์โฆษณาแะเผยแพร่ (ระบบภาพ LED Display พร้อมติดตั้งภายนอกอาคาร) จำนวน  1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจ้างเหมาบริการบำรุงรักษาอุปกรณ์ภายในศูนย์ข้อมูลคอมพิวเตอร์(Data Center) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -5986,12 +5986,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7b99fd52-1723-486a-a5ce-43a450641ed9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70ea1f2e-64d2-48c7-888f-f39d061663c3</t>
         </is>
       </c>
     </row>
@@ -6003,15 +6003,15 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>สำนักงานนวัตกรรมแห่งชาติ (องค์การมหาชน)</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1913</v>
+        <v>2102</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจ้างเหมาบริการบำรุงรักษาอุปกรณ์ภายในศูนย์ข้อมูลคอมพิวเตอร์(Data Center) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70ea1f2e-64d2-48c7-888f-f39d061663c3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5dcaa2f-3e4d-49bc-9324-4c94f510ab5f</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องควบคุมการให้สารน้ำทางหลอดเลือดดำชนิด 1 สาย ของโรงพยาบาลในจังหวัดสุรินทร์ 9 แห่ง จำนวน 66 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5dcaa2f-3e4d-49bc-9324-4c94f510ab5f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=af446873-e18e-4ed1-bd5c-bd34b74e9b76</t>
         </is>
       </c>
     </row>
@@ -6073,15 +6073,15 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมการแพทย์</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องควบคุมการให้สารน้ำทางหลอดเลือดดำชนิด 1 สาย ของโรงพยาบาลในจังหวัดสุรินทร์ 9 แห่ง จำนวน 66 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์เครื่องเสริมสร้างความแข็งแรงของกล้ามเนื้ออุ้งเชิงกราน รักษาอาการปัสสาวะเล็ด ลดอาการปวดจากกล้ามเนื้อและระบบประสาทบริเวณ อุ้งเชิงกรานและหลังด้วยคลื่นแม่เหล็กไฟฟ้า สถาบันเวชศาสตร์สมเด็จพระสังฆราชญาณสังวรเพื่อผู้สูงอายุ ตำบลตลาดขวัญ อำเภอเมือง จังหวัดนนทบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -6096,27 +6096,27 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=af446873-e18e-4ed1-bd5c-bd34b74e9b76</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=543d641e-2bab-40db-bddc-5b9d81caf16b</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>กรมการแพทย์</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>2103</v>
+        <v>204</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์เครื่องเสริมสร้างความแข็งแรงของกล้ามเนื้ออุ้งเชิงกราน รักษาอาการปัสสาวะเล็ด ลดอาการปวดจากกล้ามเนื้อและระบบประสาทบริเวณ อุ้งเชิงกรานและหลังด้วยคลื่นแม่เหล็กไฟฟ้า สถาบันเวชศาสตร์สมเด็จพระสังฆราชญาณสังวรเพื่อผู้สูงอายุ ตำบลตลาดขวัญ อำเภอเมือง จังหวัดนนทบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำหรับงานซ่อมปรับปรุงสนามกีฬาของ หน่วยบัญชาการสงครามพิเศษ เพื่อรองรับการแข่งขันกีฬา กองทัพบก ครั้งที่ 74 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=543d641e-2bab-40db-bddc-5b9d81caf16b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=91712891-37fd-4bbc-ae6c-0044106ce3a9</t>
         </is>
       </c>
     </row>
@@ -6143,15 +6143,15 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>204</v>
+        <v>704</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์สำหรับงานซ่อมปรับปรุงสนามกีฬาของ หน่วยบัญชาการสงครามพิเศษ เพื่อรองรับการแข่งขันกีฬา กองทัพบก ครั้งที่ 74 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะ รถโดยสารขนาด 12 ที่นั่ง (ดีเซล) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=91712891-37fd-4bbc-ae6c-0044106ce3a9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6d9307c6-812c-4689-9154-bd79b77edeed</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะ รถโดยสารขนาด 12 ที่นั่ง (ดีเซล) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องคอมพิวเตอร์โน๊ตบุ๊ค สำหรับงานประมวลผล พร้อมชุดโปรแกรมระบบปฏิบัติการสำหรับคอมพิวเตอร์และเครี่องคอมพิวเตอร์โน๊ตบุ๊ค แบบสิทธิการใช้งานภายในสำนักงาน ประเภทติดตั้งมาจากโรงงาน (OEM) ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย ชุดโปรแกรมจัดการสำนักงาน แบบที่ 2   ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย และชุดโปรแกรมป้องกันไวรัส จำนวน 21 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, โน๊ตบุ๊ค, ระบบปฏิบัติการ, โปรแกรมป้องกันไวรัส)</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6d9307c6-812c-4689-9154-bd79b77edeed</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ac28390d-f1a5-41e3-8fed-7350ce5638bc</t>
         </is>
       </c>
     </row>
@@ -6213,15 +6213,15 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>704</v>
+        <v>805</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องคอมพิวเตอร์โน๊ตบุ๊ค สำหรับงานประมวลผล พร้อมชุดโปรแกรมระบบปฏิบัติการสำหรับคอมพิวเตอร์และเครี่องคอมพิวเตอร์โน๊ตบุ๊ค แบบสิทธิการใช้งานภายในสำนักงาน ประเภทติดตั้งมาจากโรงงาน (OEM) ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย ชุดโปรแกรมจัดการสำนักงาน แบบที่ 2   ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย และชุดโปรแกรมป้องกันไวรัส จำนวน 21 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานหัวหิน ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -6231,12 +6231,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, โน๊ตบุ๊ค, ระบบปฏิบัติการ, โปรแกรมป้องกันไวรัส)</t>
+          <t>★ (รถเข็น)</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ac28390d-f1a5-41e3-8fed-7350ce5638bc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f40b4d90-5120-4848-a5d2-b177de8a9a09</t>
         </is>
       </c>
     </row>
@@ -6248,15 +6248,15 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
+          <t>กรมพัฒนาธุรกิจการค้า</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>805</v>
+        <v>1308</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาทำความสะอาดอาคารที่พักผู้โดยสาร รวมทั้งอาคารทำการต่างๆ และเก็บรถเข็นสัมภาระผู้โดยสาร ที่ท่าอากาศยานหัวหิน ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์แม่ข่ายและอุปกรณ์รักษาความปลอดภัย ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -6266,12 +6266,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>★ (รถเข็น)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f40b4d90-5120-4848-a5d2-b177de8a9a09</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=652c12bb-908d-48aa-a87c-f244b33e9ad3</t>
         </is>
       </c>
     </row>
@@ -6283,15 +6283,15 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>กรมพัฒนาธุรกิจการค้า</t>
+          <t>กรมที่ดิน</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1308</v>
+        <v>1505</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์แม่ข่ายและอุปกรณ์รักษาความปลอดภัย ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมอุปกรณ์ รวม ๘ รายการ สำหรับใช้ในราชการกองเทคโนโลยีทำแผนที่ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -6301,12 +6301,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=652c12bb-908d-48aa-a87c-f244b33e9ad3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c85d670f-a209-4413-8ade-5dba1d3d0298</t>
         </is>
       </c>
     </row>
@@ -6318,15 +6318,15 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>กรมที่ดิน</t>
+          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1505</v>
+        <v>1905</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมอุปกรณ์ รวม ๘ รายการ สำหรับใช้ในราชการกองเทคโนโลยีทำแผนที่ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์โครงการห้องปฏิบัติการทดสอบด้านวิศวกรรมการใช้งาน (Usability Engineering) ผลิตภัณฑ์ซอฟต์แวร์หุ่นยนต์ทางการแพทย์และเครื่องมือแพทย์ตามมาตรฐานสากล (Usability Engineering Laboratories for Software, Medical Robotics, and Medical Devices under International Standards) จํานวน ๑ ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ซอฟต์แวร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c85d670f-a209-4413-8ade-5dba1d3d0298</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0415b5bd-8794-467b-9e54-5ae4bdabae87</t>
         </is>
       </c>
     </row>
@@ -6353,15 +6353,15 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1905</v>
+        <v>2102</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์โครงการห้องปฏิบัติการทดสอบด้านวิศวกรรมการใช้งาน (Usability Engineering) ผลิตภัณฑ์ซอฟต์แวร์หุ่นยนต์ทางการแพทย์และเครื่องมือแพทย์ตามมาตรฐานสากล (Usability Engineering Laboratories for Software, Medical Robotics, and Medical Devices under International Standards) จํานวน ๑ ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องอุ่นเลือดและส่วนประกอบของเลือดชนิดไม่สัมผัสน้ำสามารถอุ่นเลือดได้ พร้อมกันไม่น้อยกว่า 3 ถุง จำนวน 4 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย -  กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>★ (ซอฟต์แวร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0415b5bd-8794-467b-9e54-5ae4bdabae87</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2157b09f-d16e-4bcf-b720-de1088bc7b0e</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องอุ่นเลือดและส่วนประกอบของเลือดชนิดไม่สัมผัสน้ำสามารถอุ่นเลือดได้ พร้อมกันไม่น้อยกว่า 3 ถุง จำนวน 4 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย -  กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องควบคุมการให้สารละลายโดยใช้กระบอกฉีด ของโรงพยาบาลในจังหวัดสุรินทร์ 5 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบลสำเภาลูน จำนวน 26 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2157b09f-d16e-4bcf-b720-de1088bc7b0e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=33f2d0df-213d-44c4-a6fa-d31b0eb2e1f6</t>
         </is>
       </c>
     </row>
@@ -6423,15 +6423,15 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>2102</v>
+        <v>2106</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องควบคุมการให้สารละลายโดยใช้กระบอกฉีด ของโรงพยาบาลในจังหวัดสุรินทร์ 5 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบลสำเภาลูน จำนวน 26 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาซ่อมแซมแก้ไขระบบเครือข่ายและเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=33f2d0df-213d-44c4-a6fa-d31b0eb2e1f6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=77d1f891-c26e-4f3d-a9e2-7ca16c4196b3</t>
         </is>
       </c>
     </row>
@@ -6458,15 +6458,15 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>กรมวิทยาศาสตร์การแพทย์</t>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาซ่อมแซมแก้ไขระบบเครือข่ายและเครื่องคอมพิวเตอร์แม่ข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=77d1f891-c26e-4f3d-a9e2-7ca16c4196b3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b600d06e-5f90-400c-80fc-24c6ae2ef280</t>
         </is>
       </c>
     </row>
@@ -6493,15 +6493,15 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>กรมสนับสนุนบริการสุขภาพ</t>
+          <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>2107</v>
+        <v>2117</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ไฟฟ้าและวิทยุ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์วิทยาศาสตร์การแพทย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b600d06e-5f90-400c-80fc-24c6ae2ef280</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a3db48e8-9e8b-4535-84a6-a14f5811619b</t>
         </is>
       </c>
     </row>
@@ -6528,15 +6528,15 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>สถาบันพระบรมราชชนก</t>
+          <t>สำนักงานพระพุทธศาสนาแห่งชาติ</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>2117</v>
+        <v>2503</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์วิทยาศาสตร์การแพทย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -6546,32 +6546,32 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a3db48e8-9e8b-4535-84a6-a14f5811619b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=285cc870-c52b-429d-b866-52f939bc7fd0</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>สำนักงานพระพุทธศาสนาแห่งชาติ</t>
+          <t>กรมพัฒนาที่ดิน</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>2503</v>
+        <v>708</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจอแสดงผล LED พร้อมอุปกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -6581,12 +6581,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (จอแสดงผล)</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=285cc870-c52b-429d-b866-52f939bc7fd0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=45d8cd64-624e-4582-a8d1-3fe3d01e41b6</t>
         </is>
       </c>
     </row>
@@ -6598,15 +6598,15 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>กรมพัฒนาที่ดิน</t>
+          <t>กรมการข้าว</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจอแสดงผล LED พร้อมอุปกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องปรับอากาศ แบบแยกส่วน แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -6616,12 +6616,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>★ (จอแสดงผล)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=45d8cd64-624e-4582-a8d1-3fe3d01e41b6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2475fb18-8633-42d5-8fe6-f520615dc6f7</t>
         </is>
       </c>
     </row>
@@ -6633,15 +6633,15 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>กรมการข้าว</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>718</v>
+        <v>806</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องปรับอากาศ แบบแยกส่วน แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร จำนวน 5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ และ ครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 13 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -6651,12 +6651,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2475fb18-8633-42d5-8fe6-f520615dc6f7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0b00828b-7442-420e-85c9-ad09d2f6e16f</t>
         </is>
       </c>
     </row>
@@ -6668,15 +6668,15 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>กรมทรัพยากรน้ำบาดาล</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>806</v>
+        <v>907</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ และ ครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 13 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องสูบน้ำไฟฟ้าชนิดมอเตอร์จุ่มใต้น้ำ พร้อมอุปกรณ์ และชุดฝาปิดปากบ่อน้ำบาดาล จำนวน ๖ ชุด โครงการพัฒนาน้ำบาดาลเพื่อความมั่นคงระดับชุมชน ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ (งบเหลือจ่าย) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0b00828b-7442-420e-85c9-ad09d2f6e16f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=03ba8462-a0d1-4d13-92c2-a7ae76fed3d0</t>
         </is>
       </c>
     </row>
@@ -6703,15 +6703,15 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>กรมทรัพยากรน้ำบาดาล</t>
+          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องสูบน้ำไฟฟ้าชนิดมอเตอร์จุ่มใต้น้ำ พร้อมอุปกรณ์ และชุดฝาปิดปากบ่อน้ำบาดาล จำนวน ๖ ชุด โครงการพัฒนาน้ำบาดาลเพื่อความมั่นคงระดับชุมชน ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ (งบเหลือจ่าย) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทเรือหางยาวสำหรับการลาดตระเวนพื้นที่ทางน้ำ เพื่อเพิ่มประสิทธิภาพการปฏิบัติงานอุทยานแห่งชาติเขาแหลม จังหวัดกาญจนบุรี  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=03ba8462-a0d1-4d13-92c2-a7ae76fed3d0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63f7333f-eb0c-40fa-8c06-5f683d543bce</t>
         </is>
       </c>
     </row>
@@ -6738,15 +6738,15 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
+          <t>กรมการปกครอง</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>909</v>
+        <v>1503</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทเรือหางยาวสำหรับการลาดตระเวนพื้นที่ทางน้ำ เพื่อเพิ่มประสิทธิภาพการปฏิบัติงานอุทยานแห่งชาติเขาแหลม จังหวัดกาญจนบุรี  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อวัสดุครุภัณฑ์สำนักงานที่ทำการปกครองอำเภอตาพระยา จังหวัดสระแก้ว ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -6756,12 +6756,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=63f7333f-eb0c-40fa-8c06-5f683d543bce</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=de60da4a-56f9-434f-bd1c-60d19d95f672</t>
         </is>
       </c>
     </row>
@@ -6773,15 +6773,15 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>กรมการปกครอง</t>
+          <t>กรมที่ดิน</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อวัสดุครุภัณฑ์สำนักงานที่ทำการปกครองอำเภอตาพระยา จังหวัดสระแก้ว ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์เพื่อการบริหารจัดการหน่วยงานส่วนกลาง (Hardware และ Software) ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=de60da4a-56f9-434f-bd1c-60d19d95f672</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a80802ed-6d42-4b60-b93c-de21fb24e5c0</t>
         </is>
       </c>
     </row>
@@ -6808,15 +6808,15 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>กรมที่ดิน</t>
+          <t>กรมการจัดหางาน</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1505</v>
+        <v>1703</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์เพื่อการบริหารจัดการหน่วยงานส่วนกลาง (Hardware และ Software) ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ทดแทนและเพิ่มประสิทธิภาพของสำนักบริหารแรงงานต่างด้าว ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -6826,12 +6826,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a80802ed-6d42-4b60-b93c-de21fb24e5c0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f3092a7e-5bf1-488f-8f3f-6657ba0fe2fd</t>
         </is>
       </c>
     </row>
@@ -6843,15 +6843,15 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>กรมการจัดหางาน</t>
+          <t>กรมพัฒนาฝีมือแรงงาน</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ทดแทนและเพิ่มประสิทธิภาพของสำนักบริหารแรงงานต่างด้าว ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ (ระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop) ขนาด 3 เฟส 15 กิโลวัตต์ ตำบลบ่อ อำเภอขลุง จังหวัดจันทบุรี จำนวน 1 ระบบ และระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop) ขนาด 3 เฟส 20 กิโลวัตต์ ตำบลบ่อ อำเภอขลุง จังหวัดจันทบุรี จำนวน 1 ระบบ) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -6861,12 +6861,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f3092a7e-5bf1-488f-8f3f-6657ba0fe2fd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d90e4389-d0ce-48d4-b93a-03874d22d178</t>
         </is>
       </c>
     </row>
@@ -6878,15 +6878,15 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>กรมพัฒนาฝีมือแรงงาน</t>
+          <t>กรมการศาสนา</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1704</v>
+        <v>1803</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ (ระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop) ขนาด 3 เฟส 15 กิโลวัตต์ ตำบลบ่อ อำเภอขลุง จังหวัดจันทบุรี จำนวน 1 ระบบ และระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop) ขนาด 3 เฟส 20 กิโลวัตต์ ตำบลบ่อ อำเภอขลุง จังหวัดจันทบุรี จำนวน 1 ระบบ) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อหมึกเครื่องพิมพ์ (ครั้งที่ 2)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -6896,12 +6896,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (หมึกเครื่องพิมพ์, เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d90e4389-d0ce-48d4-b93a-03874d22d178</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8ffdb256-bac2-4342-bdf6-7616e2ae5b25</t>
         </is>
       </c>
     </row>
@@ -6913,15 +6913,15 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>กรมการศาสนา</t>
+          <t>สถาบันมาตรวิทยาแห่งชาติ</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1803</v>
+        <v>1907</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อหมึกเครื่องพิมพ์ (ครั้งที่ 2)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างค่าบำรุงรักษาอุปกรณ์เครือข่ายประจำอาคาร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>★ (หมึกเครื่องพิมพ์, เครื่องพิมพ์)</t>
+          <t>★ (อุปกรณ์เครือข่าย)</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8ffdb256-bac2-4342-bdf6-7616e2ae5b25</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b698a86e-10e2-45f2-be5e-f7ec03fa0ce9</t>
         </is>
       </c>
     </row>
@@ -6948,15 +6948,15 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>สถาบันมาตรวิทยาแห่งชาติ</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1907</v>
+        <v>2102</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างค่าบำรุงรักษาอุปกรณ์เครือข่ายประจำอาคาร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการรถพยาบาลพร้อมอุปกรณ์ช่วยชีวิตชั้นสูง ของโรงพยาบาลชุมชน 4 แห่ง จำนวน 4 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>★ (อุปกรณ์เครือข่าย)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b698a86e-10e2-45f2-be5e-f7ec03fa0ce9</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f77b490-654b-45ac-9d8e-cc1f4f3fd4fb</t>
         </is>
       </c>
     </row>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการรถพยาบาลพร้อมอุปกรณ์ช่วยชีวิตชั้นสูง ของโรงพยาบาลชุมชน 4 แห่ง จำนวน 4 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดออกซิเจนในเลือดอัตโนมัติชนิดพกพา จำนวน 39 เครื่องๆ งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f77b490-654b-45ac-9d8e-cc1f4f3fd4fb</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f13af428-4413-4d73-9542-bd582ed6e240</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดออกซิเจนในเลือดอัตโนมัติชนิดพกพา จำนวน 39 เครื่องๆ งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจคลื่นไฟฟ้าหัวใจ พร้อมเชื่อมต่อระบบแพทย์ทางไกล จำนวน 27 เครื่อง งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f13af428-4413-4d73-9542-bd582ed6e240</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9350a991-2cda-4337-b005-93d114caf75c</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจคลื่นไฟฟ้าหัวใจ พร้อมเชื่อมต่อระบบแพทย์ทางไกล จำนวน 27 เครื่อง งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการตู้เย็นเก็บเลือด ขนาดไม่น้อยกว่า 20 คิว จำนวน 4 ตู้ งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์  การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -7071,12 +7071,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์, ตู้เย็น)</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9350a991-2cda-4337-b005-93d114caf75c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=83dc4a91-4e74-465d-b378-562e91d2b662</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการตู้เย็นเก็บเลือด ขนาดไม่น้อยกว่า 20 คิว จำนวน 4 ตู้ งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์  การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ เครื่องให้การรักษาอาการปวดและกระตุ้นเซลล์ประสาทส่วนปลายด้วยสนามแม่เหล็กไฟฟ้า(PMS) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -7106,12 +7106,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์, ตู้เย็น)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=83dc4a91-4e74-465d-b378-562e91d2b662</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=35bbde9c-eb8e-445f-b94e-915454477995</t>
         </is>
       </c>
     </row>
@@ -7123,15 +7123,15 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>2102</v>
+        <v>2106</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ เครื่องให้การรักษาอาการปวดและกระตุ้นเซลล์ประสาทส่วนปลายด้วยสนามแม่เหล็กไฟฟ้า(PMS) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมระบบปฏิบัติการและชุดโปรแกรมจัดการสำนักงาน จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ระบบปฏิบัติการ, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=35bbde9c-eb8e-445f-b94e-915454477995</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=414ac115-ac50-4d65-a54d-d2a9e03b621b</t>
         </is>
       </c>
     </row>
@@ -7158,15 +7158,15 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>กรมวิทยาศาสตร์การแพทย์</t>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์พร้อมระบบปฏิบัติการและชุดโปรแกรมจัดการสำนักงาน จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ เครื่องวิเคราะห์การทำงานตู้อบเด็ก จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -7176,32 +7176,32 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ระบบปฏิบัติการ, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=414ac115-ac50-4d65-a54d-d2a9e03b621b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9d04622a-81b1-4cfd-9a05-6c2aec6751f7</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>กรมสนับสนุนบริการสุขภาพ</t>
+          <t>กรมบัญชีกลาง</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>2107</v>
+        <v>304</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ เครื่องวิเคราะห์การทำงานตู้อบเด็ก จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาและซ่อมแซมแก้ไขเครื่องปรับอากาศ (แบบรวมอะไหล่) จำนวน 474 เครื่อง ซ่อมแซมแก้ไขระบบไฟฟ้า และระบบสุขาภิบาล อาคาร 3 อาคาร 9 อาคารใหม่ ชั้นใต้ดิน และห้องลิฟต์ กรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -7211,12 +7211,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9d04622a-81b1-4cfd-9a05-6c2aec6751f7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=273a8add-ac17-48f1-8ff9-c94a946e8273</t>
         </is>
       </c>
     </row>
@@ -7228,15 +7228,15 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>กรมบัญชีกลาง</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>304</v>
+        <v>704</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาและซ่อมแซมแก้ไขเครื่องปรับอากาศ (แบบรวมอะไหล่) จำนวน 474 เครื่อง ซ่อมแซมแก้ไขระบบไฟฟ้า และระบบสุขาภิบาล อาคาร 3 อาคาร 9 อาคารใหม่ ชั้นใต้ดิน และห้องลิฟต์ กรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ พร้อมชุดโปรแกรมปฎิบัติงาน โปรแกรมจัดการสำนักงาน และโปรแกรมป้องกันไวรัส จำนวน 18 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (คอมพิวเตอร์, โปรแกรมป้องกันไวรัส, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=273a8add-ac17-48f1-8ff9-c94a946e8273</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0511e3cd-537d-45d3-880c-de7433b1eb48</t>
         </is>
       </c>
     </row>
@@ -7263,15 +7263,15 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมประมง</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ พร้อมชุดโปรแกรมปฎิบัติงาน โปรแกรมจัดการสำนักงาน และโปรแกรมป้องกันไวรัส จำนวน 18 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อชุดจอภาพ LED พร้อมงานติดตั้งสำหรับห้องประชุมอานนท์ กรมประมง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -7281,12 +7281,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, โปรแกรมป้องกันไวรัส, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (จอภาพ)</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0511e3cd-537d-45d3-880c-de7433b1eb48</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b0679766-012d-497b-8e41-2296e1c7ba51</t>
         </is>
       </c>
     </row>
@@ -7298,15 +7298,15 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>กรมประมง</t>
+          <t>กรมปศุสัตว์</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อชุดจอภาพ LED พร้อมงานติดตั้งสำหรับห้องประชุมอานนท์ กรมประมง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -7316,12 +7316,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>★ (จอภาพ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b0679766-012d-497b-8e41-2296e1c7ba51</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f70d294-53f0-4fd1-b9bc-ef06d20b1657</t>
         </is>
       </c>
     </row>
@@ -7333,15 +7333,15 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>กรมปศุสัตว์</t>
+          <t>สำนักงานนโยบายและแผนการขนส่งและจราจร</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>706</v>
+        <v>808</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์ของ สนข. ประจำปีงบประมาณ พ.ศ. 2570  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f70d294-53f0-4fd1-b9bc-ef06d20b1657</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=069d5584-a6b1-426d-9714-115f2fdc7025</t>
         </is>
       </c>
     </row>
@@ -7368,15 +7368,15 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>สำนักงานนโยบายและแผนการขนส่งและจราจร</t>
+          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>808</v>
+        <v>904</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบคอมพิวเตอร์ของ สนข. ประจำปีงบประมาณ พ.ศ. 2570  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาและเพิ่มประสิทธิภาพระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรทางทะเลและชายฝั่ง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=069d5584-a6b1-426d-9714-115f2fdc7025</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f112758f-839d-4660-91b5-12181a1297d2</t>
         </is>
       </c>
     </row>
@@ -7403,15 +7403,15 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
+          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>904</v>
+        <v>1202</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการบำรุงรักษาและเพิ่มประสิทธิภาพระบบเครือข่ายคอมพิวเตอร์ กรมทรัพยากรทางทะเลและชายฝั่ง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่ารถส่วนภูมิภาค รถยนต์ไฟฟ้า ประเภทแบตเตอรี่ (BEV) ขนาดความจุของแบตเตอรี่มากกว่า 50 กิโลวัตต์ชั่วโมง (kWh) และกำลังมอเตอร์ไฟฟ้าสูงสุด ไม่เกิน 150 กิโลวัตต์ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f112758f-839d-4660-91b5-12181a1297d2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=40cb45e4-0e08-48b9-a763-7a9aa44d7959</t>
         </is>
       </c>
     </row>
@@ -7438,15 +7438,15 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพลังงาน</t>
+          <t>กรมการปกครอง</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>1202</v>
+        <v>1503</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่ารถส่วนภูมิภาค รถยนต์ไฟฟ้า ประเภทแบตเตอรี่ (BEV) ขนาดความจุของแบตเตอรี่มากกว่า 50 กิโลวัตต์ชั่วโมง (kWh) และกำลังมอเตอร์ไฟฟ้าสูงสุด ไม่เกิน 150 กิโลวัตต์ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 5 รายการ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=40cb45e4-0e08-48b9-a763-7a9aa44d7959</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ac3547dc-0f12-4694-b5a3-e216678ce172</t>
         </is>
       </c>
     </row>
@@ -7473,15 +7473,15 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>กรมการปกครอง</t>
+          <t>กรมการศาสนา</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1503</v>
+        <v>1803</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์โฆษณาและเผยแพร่ จำนวน 5 รายการ ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อวัสดุสำนักงานส่วนกลาง ประจำปีงบประมาณ พ.ศ. 2569 (ครั้งที่ 2)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (วัสดุสำนักงาน)</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ac3547dc-0f12-4694-b5a3-e216678ce172</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c6f2fbd0-4267-42c4-926d-d8fc49d8a3ff</t>
         </is>
       </c>
     </row>
@@ -7508,15 +7508,15 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>กรมการศาสนา</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1803</v>
+        <v>2102</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อวัสดุสำนักงานส่วนกลาง ประจำปีงบประมาณ พ.ศ. 2569 (ครั้งที่ 2)  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องผลิตออกซิเจนขนาด 5 ลิตร ของโรงพยาบาลสนม และโรงพยาบาลส่งเสริมสุขภาพตำบล 18 แห่ง จำนวน 33 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>★ (วัสดุสำนักงาน)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c6f2fbd0-4267-42c4-926d-d8fc49d8a3ff</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=655601b1-75a6-4eee-9bc7-ee3ce427abf6</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องผลิตออกซิเจนขนาด 5 ลิตร ของโรงพยาบาลสนม และโรงพยาบาลส่งเสริมสุขภาพตำบล 18 แห่ง จำนวน 33 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดความดันโลหิตชนิดอัตโนมัติ วัดความอิ่มตัวของออกซิเจนในเลือด อุณหภูมิร่างกาย พร้อมระบบเชื่อมต่อฐานข้อมูล ของโรงพยาบาลในจังหวัดสุรินทร์ 12 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบล 10 แห่ง จำนวน 50 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=655601b1-75a6-4eee-9bc7-ee3ce427abf6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=65a2753e-e63f-4be2-b228-0fe250379934</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดความดันโลหิตชนิดอัตโนมัติ วัดความอิ่มตัวของออกซิเจนในเลือด อุณหภูมิร่างกาย พร้อมระบบเชื่อมต่อฐานข้อมูล ของโรงพยาบาลในจังหวัดสุรินทร์ 12 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบล 10 แห่ง จำนวน 50 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการชุดอุปกรณ์เคลื่อนย้ายผู้ป่วยในสถานการณ์ฉุกเฉิน ของโรงพยาบาลชุมชน 8 แห่ง จำนวน 10 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=65a2753e-e63f-4be2-b228-0fe250379934</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=886059b7-d984-4e19-b7d7-6d90ebc9b2e0</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการชุดอุปกรณ์เคลื่อนย้ายผู้ป่วยในสถานการณ์ฉุกเฉิน ของโรงพยาบาลชุมชน 8 แห่ง จำนวน 10 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงชนิดสี 2 หัวตรวจ ของโรงพยาบาลชุมชน 6 แห่ง จำนวน 8 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=886059b7-d984-4e19-b7d7-6d90ebc9b2e0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fc233297-ee25-42e4-bc90-16f41ac8db6a</t>
         </is>
       </c>
     </row>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงชนิดสี 2 หัวตรวจ ของโรงพยาบาลชุมชน 6 แห่ง จำนวน 8 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดออกซิเจนในเลือดอัตโนมัติชนิดพกพา ของโรงพยาบาลส่งเสริมสุขภาพตำบลและโรงพยาบาลชุมชน 24 แห่ง จำนวน 68 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fc233297-ee25-42e4-bc90-16f41ac8db6a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3d2922a2-6499-49fa-b182-1e95dc5131d7</t>
         </is>
       </c>
     </row>
@@ -7691,7 +7691,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดออกซิเจนในเลือดอัตโนมัติชนิดพกพา ของโรงพยาบาลส่งเสริมสุขภาพตำบลและโรงพยาบาลชุมชน 24 แห่ง จำนวน 68 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องเอกซเรย์ทั่วไปขนาดไม่น้อยกว่า 500 mA. แบบแขวนเพดาน โรงพยาบาลแก่งกระจาน ตำบลวังจันทร์ อำเภอแก่งกระจาน จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -7706,27 +7706,27 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3d2922a2-6499-49fa-b182-1e95dc5131d7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6f21d5fd-56e9-4486-915b-90fd4be0f39b</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กองทัพอากาศ</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>2102</v>
+        <v>206</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องเอกซเรย์ทั่วไปขนาดไม่น้อยกว่า 500 mA. แบบแขวนเพดาน โรงพยาบาลแก่งกระจาน ตำบลวังจันทร์ อำเภอแก่งกระจาน จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบริการบำรุงรักษาเครื่องเอกซเรย์ควบคุมด้วยระบบคอมพิวเตอร์ขนาดไม่น้อยกว่า 300 mA พร้อมอุปกรณ์ ยี่ห้อ DRGEM รุ่น GXR-52S ของ โรงพยาบาลกองบิน กองบิน 1, โรงพยาบาลกองบิน กองบิน 2, โรงพยาบาลกองบิน กองบิน 7, โรงพยาบาลกองบิน กองบิน 41, โรงพยาบาลกองบิน กองบิน 46 จำนวน ๑ งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6f21d5fd-56e9-4486-915b-90fd4be0f39b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ffb67ab2-d749-4ab0-87f1-1b11432ab218</t>
         </is>
       </c>
     </row>
@@ -7753,15 +7753,15 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>กองทัพอากาศ</t>
+          <t>กรมธนารักษ์</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>206</v>
+        <v>303</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบริการบำรุงรักษาเครื่องเอกซเรย์ควบคุมด้วยระบบคอมพิวเตอร์ขนาดไม่น้อยกว่า 300 mA พร้อมอุปกรณ์ ยี่ห้อ DRGEM รุ่น GXR-52S ของ โรงพยาบาลกองบิน กองบิน 1, โรงพยาบาลกองบิน กองบิน 2, โรงพยาบาลกองบิน กองบิน 7, โรงพยาบาลกองบิน กองบิน 41, โรงพยาบาลกองบิน กองบิน 46 จำนวน ๑ งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องอากาศยานซึ่งไม่มีนักบิน (Drone)  พร้อมชุดอุปกรณ์ภาคสนามและระบบซอฟต์แวร์ประมวลผลแผนที่ความละเอียดสูง จำนวน 12 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ffb67ab2-d749-4ab0-87f1-1b11432ab218</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e88cabea-0e2e-4af8-8b8b-4aa4e7eb040a</t>
         </is>
       </c>
     </row>
@@ -7788,15 +7788,15 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>กรมธนารักษ์</t>
+          <t>สำนักงานเศรษฐกิจการคลัง</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องอากาศยานซึ่งไม่มีนักบิน (Drone)  พร้อมชุดอุปกรณ์ภาคสนามและระบบซอฟต์แวร์ประมวลผลแผนที่ความละเอียดสูง จำนวน 12 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์สำหรับโครงการพัฒนาระบบสารสนเทศสถาบันการเงินประชาชนของสำนักงานเศรษฐกิจการคลัง (ระบบงาน PFI) ประจำปีงบประมาณ พ.ศ. 2570  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>★ (ซอฟต์แวร์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e88cabea-0e2e-4af8-8b8b-4aa4e7eb040a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a787a49a-4035-46d3-b8a4-a996ac96341d</t>
         </is>
       </c>
     </row>
@@ -7823,15 +7823,15 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>สำนักงานเศรษฐกิจการคลัง</t>
+          <t>กรมพัฒนาสังคมและสวัสดิการ</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>311</v>
+        <v>603</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์สำหรับโครงการพัฒนาระบบสารสนเทศสถาบันการเงินประชาชนของสำนักงานเศรษฐกิจการคลัง (ระบบงาน PFI) ประจำปีงบประมาณ พ.ศ. 2570  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์สำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a787a49a-4035-46d3-b8a4-a996ac96341d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=857f0ccd-d38e-47b0-8d6d-913ef2cb1583</t>
         </is>
       </c>
     </row>
@@ -7858,15 +7858,15 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>กรมพัฒนาสังคมและสวัสดิการ</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>603</v>
+        <v>704</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์สำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=857f0ccd-d38e-47b0-8d6d-913ef2cb1583</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=01c185be-f27c-41bc-868e-accd57e4a95c</t>
         </is>
       </c>
     </row>
@@ -7893,15 +7893,15 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>704</v>
+        <v>804</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์พร้อมอุปกรณ์สำหรับศูนย์รวมข้อมูลการขนส่งด้วยรถบรรทุกเพื่อส่งเสริมการขนส่งด้วยรถบรรทุกให้มีประสิทธิภาพ ปลอดภัยและได้มาตรฐาน (TDSC) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -7911,12 +7911,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=01c185be-f27c-41bc-868e-accd57e4a95c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70381c19-a073-41d0-8f0b-08c5e68fca7c</t>
         </is>
       </c>
     </row>
@@ -7928,15 +7928,15 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
+          <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์พร้อมอุปกรณ์สำหรับศูนย์รวมข้อมูลการขนส่งด้วยรถบรรทุกเพื่อส่งเสริมการขนส่งด้วยรถบรรทุกให้มีประสิทธิภาพ ปลอดภัยและได้มาตรฐาน (TDSC) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบไฟฟ้า ตู้สวิตช์บอร์ด ๒๖ ท่าอากาศยาน และกรมท่าอากาศยาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -7946,12 +7946,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (สวิตช์)</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=70381c19-a073-41d0-8f0b-08c5e68fca7c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7f19e47d-04ea-4596-a45a-a42e0fd28eea</t>
         </is>
       </c>
     </row>
@@ -7963,15 +7963,15 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
+          <t>กรมป่าไม้</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>805</v>
+        <v>912</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบไฟฟ้า ตู้สวิตช์บอร์ด ๒๖ ท่าอากาศยาน และกรมท่าอากาศยาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>★ (สวิตช์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7f19e47d-04ea-4596-a45a-a42e0fd28eea</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fd72b9d1-6722-4578-b8e5-e2d45779204d</t>
         </is>
       </c>
     </row>
@@ -7998,15 +7998,15 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>กรมป่าไม้</t>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>912</v>
+        <v>1302</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาเช่าระบบประชุมทางไกล (Web Conference Video Streaming) ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ระบบประชุมทางไกล)</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fd72b9d1-6722-4578-b8e5-e2d45779204d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6c4b6c7d-fa54-4634-9070-01779d28362f</t>
         </is>
       </c>
     </row>
@@ -8033,15 +8033,15 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+          <t>กรมโยธาธิการและผังเมือง</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>1302</v>
+        <v>1507</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>ประกวดราคาเช่าระบบประชุมทางไกล (Web Conference Video Streaming) ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างก่อสร้างงานปรับปรุงระบบดับเพลิงพิเศษอัตโนมัติ (Clean Agent Fire Suppression System) ภายในห้องคอมพิวเตอร์แม่ข่าย (Server Room) อาคาร 4 ชั้น 1 กรมโยธาธิการและผังเมือง ถนนพระราม 9 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>★ (ระบบประชุมทางไกล)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6c4b6c7d-fa54-4634-9070-01779d28362f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a61be7d0-de39-476c-b4f8-7a3ec47bbd62</t>
         </is>
       </c>
     </row>
@@ -8068,15 +8068,15 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>กรมโยธาธิการและผังเมือง</t>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>1507</v>
+        <v>1611</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างก่อสร้างงานปรับปรุงระบบดับเพลิงพิเศษอัตโนมัติ (Clean Agent Fire Suppression System) ภายในห้องคอมพิวเตอร์แม่ข่าย (Server Room) อาคาร 4 ชั้น 1 กรมโยธาธิการและผังเมือง ถนนพระราม 9 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการถ่ายเอกสารพร้อมเครื่องถ่ายเอกสาร กระดาษ วัสดุสิ้นเปลือง และพนักงานประจำเครื่องของสำนักงาน ป.ป.ส. ดินแดง/สำนักงาน ป.ป.ส. ทุ่งสองห้อง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (กระดาษ)</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a61be7d0-de39-476c-b4f8-7a3ec47bbd62</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=325eb565-d1b7-456f-86c5-076a6e3f94fd</t>
         </is>
       </c>
     </row>
@@ -8103,15 +8103,15 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>1611</v>
+        <v>2102</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการถ่ายเอกสารพร้อมเครื่องถ่ายเอกสาร กระดาษ วัสดุสิ้นเปลือง และพนักงานประจำเครื่องของสำนักงาน ป.ป.ส. ดินแดง/สำนักงาน ป.ป.ส. ทุ่งสองห้อง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องนึ่งฆ่าเชื้อจุลินทรีย์ด้วยไอน้ำระบบอัตโนมัติ ขนาดไม่น้อยกว่า 850 ลิตร ห้องนึ่งทรงเหลี่ยมชนิด 1 ประตู โรงพยาบาลบ้านลาด ตำบลท่าช้าง อำเภอบ้านลาด จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>★ (กระดาษ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=325eb565-d1b7-456f-86c5-076a6e3f94fd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4d2f3086-64b4-4e82-a4f3-6299ee3aa880</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องนึ่งฆ่าเชื้อจุลินทรีย์ด้วยไอน้ำระบบอัตโนมัติ ขนาดไม่น้อยกว่า 850 ลิตร ห้องนึ่งทรงเหลี่ยมชนิด 1 ประตู โรงพยาบาลบ้านลาด ตำบลท่าช้าง อำเภอบ้านลาด จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องล้างเครื่องมืออัลตร้าโซนิก ชนิด 3 หลุมล้าง ขนาดความจุไม่น้อยกว่า 80 ลิตร โรงพยาบาลชะอำ ตำบลชะอำ อำเภอชะอำ จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4d2f3086-64b4-4e82-a4f3-6299ee3aa880</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b7c95cfb-63e4-43a3-9eeb-4e9c5df71f85</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องล้างเครื่องมืออัลตร้าโซนิก ชนิด 3 หลุมล้าง ขนาดความจุไม่น้อยกว่า 80 ลิตร โรงพยาบาลชะอำ ตำบลชะอำ อำเภอชะอำ จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่ายกลาง (Backbone) กระทรวงสาธารณสุข ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b7c95cfb-63e4-43a3-9eeb-4e9c5df71f85</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3a5cafe5-5313-4cb0-ab08-4b09c244ba61</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์และเครือข่ายกลาง (Backbone) กระทรวงสาธารณสุข ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนและคาร์บอนไดออกไซด์ในเลือด ของโรงพยาบาลในจังหวัดสุรินทร์ 7 แห่ง จำนวน 12 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3a5cafe5-5313-4cb0-ab08-4b09c244ba61</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d5f4c614-78c4-4363-a75d-31e52b8e81d7</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนและคาร์บอนไดออกไซด์ในเลือด ของโรงพยาบาลในจังหวัดสุรินทร์ 7 แห่ง จำนวน 12 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 8 เตียง ของโรงพยาบาลท่าตูม จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d5f4c614-78c4-4363-a75d-31e52b8e81d7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=261f4b2d-359f-4fbc-9c62-4971724a772f</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 8 เตียง ของโรงพยาบาลท่าตูม จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันขนาดใหญ่ ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 6 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -8301,27 +8301,27 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=261f4b2d-359f-4fbc-9c62-4971724a772f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9cc00102-4e57-443e-a94c-3787d155fe6b</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สำนักงานคณะกรรมการคุ้มครองผู้บริโภค</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>2102</v>
+        <v>103</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันขนาดใหญ่ ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 6 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาเครือข่าย เครื่องคอมพิวเตอร์แม่ข่าย เครื่องคอมพิวเตอร์ อุปกรณ์คอมพิวเตอร์และห้องปฏิบัติการคอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -8331,12 +8331,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9cc00102-4e57-443e-a94c-3787d155fe6b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6f8747c6-3579-4b1b-992e-7c6f55a197b3</t>
         </is>
       </c>
     </row>
@@ -8348,15 +8348,15 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการคุ้มครองผู้บริโภค</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>103</v>
+        <v>204</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการบำรุงรักษาเครือข่าย เครื่องคอมพิวเตอร์แม่ข่าย เครื่องคอมพิวเตอร์ อุปกรณ์คอมพิวเตอร์และห้องปฏิบัติการคอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ประจำอาคาร งานก่อสร้างโรงเลี้ยง 400 คน (แบบ กห 08 - 7) ของ มทบ.29 ค่ายกฤษณ์สีวะรา อ.เมือง จว.ส.น. แผนงานเพิ่มเติมระหว่างปีงบประมาณ พ.ศ. 2569 ให้กับ ช.2 พัน.202 ดำเนินการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -8366,12 +8366,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6f8747c6-3579-4b1b-992e-7c6f55a197b3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=daeb7717-b81c-405b-94a2-aa71f55ea8af</t>
         </is>
       </c>
     </row>
@@ -8383,15 +8383,15 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กองทัพอากาศ</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ประจำอาคาร งานก่อสร้างโรงเลี้ยง 400 คน (แบบ กห 08 - 7) ของ มทบ.29 ค่ายกฤษณ์สีวะรา อ.เมือง จว.ส.น. แผนงานเพิ่มเติมระหว่างปีงบประมาณ พ.ศ. 2569 ให้กับ ช.2 พัน.202 ดำเนินการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องพิมพ์สีแผ่นไวนิล จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -8401,12 +8401,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=daeb7717-b81c-405b-94a2-aa71f55ea8af</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e4172805-a5ea-4e60-b1e4-787b55b54a34</t>
         </is>
       </c>
     </row>
@@ -8418,15 +8418,15 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>กองทัพอากาศ</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>206</v>
+        <v>704</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องพิมพ์สีแผ่นไวนิล จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน เครื่องปรับอากาศแบบแยกส่วน ชนิดแขวน ระบบ Inverter ขนาด 30,000 บีทียู จำนวน 12 เครื่อง พร้อมติดตั้ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>★ (เครื่องพิมพ์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e4172805-a5ea-4e60-b1e4-787b55b54a34</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dc7ebea2-3d95-4ced-a85f-84f2cb8e77c2</t>
         </is>
       </c>
     </row>
@@ -8453,15 +8453,15 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมปศุสัตว์</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน เครื่องปรับอากาศแบบแยกส่วน ชนิดแขวน ระบบ Inverter ขนาด 30,000 บีทียู จำนวน 12 เครื่อง พร้อมติดตั้ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์  จำนวน  5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -8471,12 +8471,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์, เครื่องปรับอากาศ)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dc7ebea2-3d95-4ced-a85f-84f2cb8e77c2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a7913502-7863-4804-9095-3f717c939f36</t>
         </is>
       </c>
     </row>
@@ -8488,15 +8488,15 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>กรมปศุสัตว์</t>
+          <t>กรมส่งเสริมการเกษตร</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์  จำนวน  5 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์ สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม สำนักงานเกษตรอำเภอนาวัง ตำบลนาเหล่าอำเภอนาวัง  จังหวัดหนองบัวลำภู  จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a7913502-7863-4804-9095-3f717c939f36</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1cb87987-0702-433c-8678-5f41220c5aa5</t>
         </is>
       </c>
     </row>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์ สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม สำนักงานเกษตรอำเภอนาวัง ตำบลนาเหล่าอำเภอนาวัง  จังหวัดหนองบัวลำภู  จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบ ไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 4 ล้อ แบบดับเบิ้ลแค็บ  พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม ศูนย์ส่งเสริมเทคโนโลยีการเกษตรด้านอารักขาพืช จังหวัดพิษณุโลก ตำบลอรัญญิก อำเภอเมืองพิษณุโลก จังหวัดพิษณุโลก 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1cb87987-0702-433c-8678-5f41220c5aa5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=21728512-3d55-4336-a433-756fa816ccd6</t>
         </is>
       </c>
     </row>
@@ -8558,15 +8558,15 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการเกษตร</t>
+          <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>711</v>
+        <v>804</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบ ไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 4 ล้อ แบบดับเบิ้ลแค็บ  พร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม ศูนย์ส่งเสริมเทคโนโลยีการเกษตรด้านอารักขาพืช จังหวัดพิษณุโลก ตำบลอรัญญิก อำเภอเมืองพิษณุโลก จังหวัดพิษณุโลก 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและซ่อมแซมระบบคอมพิวเตอร์แม่ข่ายและอุปกรณ์ตามโครงการพัฒนาระบบฐานข้อมูลกลางเพื่อบูรณาการข้อมูลสนับสนุนการให้บริการของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=21728512-3d55-4336-a433-756fa816ccd6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1089b549-2663-46b4-8f30-3b752498b76d</t>
         </is>
       </c>
     </row>
@@ -8593,15 +8593,15 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบริการบำรุงรักษาและซ่อมแซมระบบคอมพิวเตอร์แม่ข่ายและอุปกรณ์ตามโครงการพัฒนาระบบฐานข้อมูลกลางเพื่อบูรณาการข้อมูลสนับสนุนการให้บริการของกรมการขนส่งทางบก ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 7 รายการ ศูนย์สร้างทางลำปาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1089b549-2663-46b4-8f30-3b752498b76d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=74dbade6-07ca-4df1-9aaa-c33e529e04b5</t>
         </is>
       </c>
     </row>
@@ -8636,7 +8636,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 7 รายการ ศูนย์สร้างทางลำปาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=74dbade6-07ca-4df1-9aaa-c33e529e04b5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=486fc308-1dd1-40ac-9b5f-16595e40c39d</t>
         </is>
       </c>
     </row>
@@ -8671,7 +8671,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องสำรองไฟฟ้า ขนาด 2 kVA จำนวน 138 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -8681,12 +8681,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (เครื่องสำรองไฟฟ้า, เครื่องสำรองไฟ)</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=486fc308-1dd1-40ac-9b5f-16595e40c39d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=66aa18c1-0eb7-4c9c-bc97-eb6c9f84ea61</t>
         </is>
       </c>
     </row>
@@ -8698,15 +8698,15 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>กรมอุตุนิยมวิทยา</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>806</v>
+        <v>1104</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องสำรองไฟฟ้า ขนาด 2 kVA จำนวน 138 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาเครื่องสำรองไฟฟ้าต่อเนื่อง (UPS) และเครื่องกำเนิดไฟฟ้า (Generator) ประจำปีงบประมาณ พ.ศ.๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=66aa18c1-0eb7-4c9c-bc97-eb6c9f84ea61</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b04b2aed-150c-4a6a-9fe6-de4abe606304</t>
         </is>
       </c>
     </row>
@@ -8733,15 +8733,15 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>กรมอุตุนิยมวิทยา</t>
+          <t>กรมเจรจาการค้าระหว่างประเทศ</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>1104</v>
+        <v>1306</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาเครื่องสำรองไฟฟ้าต่อเนื่อง (UPS) และเครื่องกำเนิดไฟฟ้า (Generator) ประจำปีงบประมาณ พ.ศ.๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการปรับปรุงระบบสายสัญญาณเครือข่าย ระบบไฟฟ้า และระบบโทรศัพท์พร้อมอุปกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -8751,12 +8751,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>★ (เครื่องสำรองไฟฟ้า, เครื่องสำรองไฟ)</t>
+          <t>★ (สายสัญญาณ)</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b04b2aed-150c-4a6a-9fe6-de4abe606304</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bac0b85b-275a-4ed6-a580-b3e8bfeb237f</t>
         </is>
       </c>
     </row>
@@ -8768,15 +8768,15 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>กรมเจรจาการค้าระหว่างประเทศ</t>
+          <t>กรมส่งเสริมการค้าระหว่างประเทศ</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการปรับปรุงระบบสายสัญญาณเครือข่าย ระบบไฟฟ้า และระบบโทรศัพท์พร้อมอุปกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างโครงการบำรุงรักษาระบบคอมพิวเตอร์และระบบเครือข่ายพร้อมอุปกรณ์ ปี ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>★ (สายสัญญาณ)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bac0b85b-275a-4ed6-a580-b3e8bfeb237f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f059ad38-40c4-42cf-9270-e3def8289626</t>
         </is>
       </c>
     </row>
@@ -8803,15 +8803,15 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>กรมส่งเสริมการค้าระหว่างประเทศ</t>
+          <t>กรมการปกครอง</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>1309</v>
+        <v>1503</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างโครงการบำรุงรักษาระบบคอมพิวเตอร์และระบบเครือข่ายพร้อมอุปกรณ์ ปี ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อวัสดุสำหรับเครื่องพิมพ์คอมพิวเตอร์เพื่อสนับสนุนการดำเนินงานในระบบสารสนเทศทรัพยากรบุคคลระดับกรม (DPIS) ประจำปีงบประมาณ  พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f059ad38-40c4-42cf-9270-e3def8289626</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ec8d68fe-3f09-45d1-a6c2-b10acc4b8aff</t>
         </is>
       </c>
     </row>
@@ -8838,15 +8838,15 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>กรมการปกครอง</t>
+          <t>กรมการศาสนา</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>1503</v>
+        <v>1803</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อวัสดุสำหรับเครื่องพิมพ์คอมพิวเตอร์เพื่อสนับสนุนการดำเนินงานในระบบสารสนเทศทรัพยากรบุคคลระดับกรม (DPIS) ประจำปีงบประมาณ  พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อหมึกเครื่องพิมพ์ (ครั้งที่ 3) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -8856,12 +8856,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, เครื่องพิมพ์)</t>
+          <t>★ (หมึกเครื่องพิมพ์, เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ec8d68fe-3f09-45d1-a6c2-b10acc4b8aff</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cad3c999-2a59-4f98-9a16-5cd0e9b965e5</t>
         </is>
       </c>
     </row>
@@ -8873,15 +8873,15 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>กรมการศาสนา</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>1803</v>
+        <v>2102</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อหมึกเครื่องพิมพ์ (ครั้งที่ 3) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ กล้องจุลทรรศน์ตรวจตาชนิดลำแสงแคบพร้อมระบบเก็บภาพดิจิตอล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -8891,12 +8891,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>★ (หมึกเครื่องพิมพ์, เครื่องพิมพ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cad3c999-2a59-4f98-9a16-5cd0e9b965e5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b7dc6e3c-c6d3-4740-8dfd-746b3c47ce99</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ กล้องจุลทรรศน์ตรวจตาชนิดลำแสงแคบพร้อมระบบเก็บภาพดิจิตอล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดใหญ่ ของโรงพยาบาลในจังหวัดสุรินทร์ 2 แห่ง จำนวน 7 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b7dc6e3c-c6d3-4740-8dfd-746b3c47ce99</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9e482ce2-8b0c-4125-ac7c-be9fb421af4d</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดใหญ่ ของโรงพยาบาลในจังหวัดสุรินทร์ 2 แห่ง จำนวน 7 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงแบบพกพาไม่ต้องชาร์จไฟฟ้าพร้อมระบบแพทย์ทางไกล ของโรงพยาบาลชุมชน 3 แห่ง จำนวน 4 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9e482ce2-8b0c-4125-ac7c-be9fb421af4d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=49ab0e04-32b5-4441-9d77-b629429b1571</t>
         </is>
       </c>
     </row>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงแบบพกพาไม่ต้องชาร์จไฟฟ้าพร้อมระบบแพทย์ทางไกล ของโรงพยาบาลชุมชน 3 แห่ง จำนวน 4 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ เครื่องตรวจวิเคราะห์แยกชั้นจอประสาทตาชนิดถ่ายภาพจอประสาทตา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=49ab0e04-32b5-4441-9d77-b629429b1571</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=165b7f39-161c-4e36-abf9-9ab28afdef12</t>
         </is>
       </c>
     </row>
@@ -9021,7 +9021,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ เครื่องตรวจวิเคราะห์แยกชั้นจอประสาทตาชนิดถ่ายภาพจอประสาทตา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องรับสัญญาณภาพเอกซเรย์เป็นดิจิตอล ชนิดชุดรับภาพแฟลตพาแนลไร้สาย โรงพยาบาลแก่งกระจาน ตำบลวังจันทร์ อำเภอแก่งกระจาน จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=165b7f39-161c-4e36-abf9-9ab28afdef12</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=23fd4481-d3c5-4060-a810-ba6addb1516c</t>
         </is>
       </c>
     </row>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 1 รายการ รายการเครื่องรับสัญญาณภาพเอกซเรย์เป็นดิจิตอล ชนิดชุดรับภาพแฟลตพาแนลไร้สาย โรงพยาบาลแก่งกระจาน ตำบลวังจันทร์ อำเภอแก่งกระจาน จังหวัดเพชรบุรี 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๒ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=23fd4481-d3c5-4060-a810-ba6addb1516c</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e59b2ed4-9af0-48e9-a768-f2323d942f2e</t>
         </is>
       </c>
     </row>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๒ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิคพร้อมภาควัดออกซิเจนและคาร์บอนไดออกไซด์ในเลือด จำนวน 25 เครื่อง งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาล ในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e59b2ed4-9af0-48e9-a768-f2323d942f2e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b80f6866-243b-41ee-8a1f-f04456bc5061</t>
         </is>
       </c>
     </row>
@@ -9118,15 +9118,15 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>2102</v>
+        <v>2107</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิคพร้อมภาควัดออกซิเจนและคาร์บอนไดออกไซด์ในเลือด จำนวน 25 เครื่อง งบประมาณกองสลากการกุศลในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาล ในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ 11 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b80f6866-243b-41ee-8a1f-f04456bc5061</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fa5cc489-cfac-46c2-b92b-18e107acc682</t>
         </is>
       </c>
     </row>
@@ -9153,15 +9153,15 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>กรมสนับสนุนบริการสุขภาพ</t>
+          <t>กรมอนามัย</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>2107</v>
+        <v>2109</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ 11 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fa5cc489-cfac-46c2-b92b-18e107acc682</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=eada32a9-3333-40e2-ad51-54e8d12647cf</t>
         </is>
       </c>
     </row>
@@ -9188,15 +9188,15 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>กรมอนามัย</t>
+          <t>สำนักงานพระพุทธศาสนาแห่งชาติ</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>2109</v>
+        <v>2503</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน ๑๒ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -9206,32 +9206,32 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=eada32a9-3333-40e2-ad51-54e8d12647cf</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=54340df1-ec2b-4471-bb8f-6779c938e36b</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>สำนักงานพระพุทธศาสนาแห่งชาติ</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>2503</v>
+        <v>204</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน ๑๒ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ประจำอาคาร จำนวน 14 รายการ เพิื่อใช้ในงานปรับปรุงอาคารของ กรมทหารม้าที่ 1 รักษาพระองค์ (กองร้อยสนับสนุนส่วนหน้า 1 กองพันซ่อมบำรุง กรมสนับสนุนที่ 12 ) เป็น โรงเรียนหน่วยเฉพาะกิจทหารมหาดเล็กรักษาพระองค์ ส่วนที่ 2 เป็นแผนงานเพิ่มเติมระหว่างปีงบประมาณ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=54340df1-ec2b-4471-bb8f-6779c938e36b</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dca076ec-64c4-4fee-9ef2-8a6665ae36fb</t>
         </is>
       </c>
     </row>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ประจำอาคาร จำนวน 14 รายการ เพิื่อใช้ในงานปรับปรุงอาคารของ กรมทหารม้าที่ 1 รักษาพระองค์ (กองร้อยสนับสนุนส่วนหน้า 1 กองพันซ่อมบำรุง กรมสนับสนุนที่ 12 ) เป็น โรงเรียนหน่วยเฉพาะกิจทหารมหาดเล็กรักษาพระองค์ ส่วนที่ 2 เป็นแผนงานเพิ่มเติมระหว่างปีงบประมาณ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ประจำอาคาร จำนวน 2 รายการ เพื่อใช้ในงานซ่อมแซมอาคารแหล่งสมาคมนายทหาร หมายเลข 144/30 ของ  กรมทหารปืนใหญ่ที่ 2 รักษาพระองค์ เป็นแผนงานเพิ่มเติมระหว่างปีงบประมาณ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dca076ec-64c4-4fee-9ef2-8a6665ae36fb</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1c52e71e-02d3-4d1f-bea4-a37dea913a20</t>
         </is>
       </c>
     </row>
@@ -9293,15 +9293,15 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กรมบัญชีกลาง</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>204</v>
+        <v>304</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ประจำอาคาร จำนวน 2 รายการ เพื่อใช้ในงานซ่อมแซมอาคารแหล่งสมาคมนายทหาร หมายเลข 144/30 ของ  กรมทหารปืนใหญ่ที่ 2 รักษาพระองค์ เป็นแผนงานเพิ่มเติมระหว่างปีงบประมาณ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างทำความสะอาดอาคารศูนย์คอมพิวเตอร์หลักของกรมบัญชีกลาง (Data Center) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1c52e71e-02d3-4d1f-bea4-a37dea913a20</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=27271442-a270-4c56-a150-8d5f8833fed3</t>
         </is>
       </c>
     </row>
@@ -9328,15 +9328,15 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>กรมบัญชีกลาง</t>
+          <t>กรมศุลกากร</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างทำความสะอาดอาคารศูนย์คอมพิวเตอร์หลักของกรมบัญชีกลาง (Data Center) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อเครื่องปรับอากาศแบบแยกส่วน ติดผนัง ขนาด 18000 บีทียู จำนวน 24 เครื่อง และขนาด 12000 บีทียู จำนวน 24 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=27271442-a270-4c56-a150-8d5f8833fed3</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=38f0f8e6-37c7-4c1b-85f7-816a83796f90</t>
         </is>
       </c>
     </row>
@@ -9363,15 +9363,15 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>กรมศุลกากร</t>
+          <t>กรมชลประทาน</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>305</v>
+        <v>703</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อเครื่องปรับอากาศแบบแยกส่วน ติดผนัง ขนาด 18000 บีทียู จำนวน 24 เครื่อง และขนาด 12000 บีทียู จำนวน 24 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจัดหาและติดตั้งเครื่องสูบน้ำชนิดหอยโข่งแบบ Horizontal Split Case ขับด้วยมอเตอร์ไฟฟ้าอัตราสูบน้ำ ๐.๒๐ ลบ.ม./วินาที ระยะยกน้ำไม่น้อยกว่า ๔๕ เมตร และอื่นๆ รวม ๔ รายการ  สำหรับงานสถานีสูบน้ำด้วยไฟฟ้าพร้อมระบบส่งน้ำ บ้านสุขสำราญ ตำบลเหล่าต่างคำ อำเภอโพนพิสัย จังหวัดหนองคาย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=38f0f8e6-37c7-4c1b-85f7-816a83796f90</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=824576ac-9b6f-4dcc-af9a-f70ac3b918df</t>
         </is>
       </c>
     </row>
@@ -9398,15 +9398,15 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>กรมชลประทาน</t>
+          <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>703</v>
+        <v>805</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจัดหาและติดตั้งเครื่องสูบน้ำชนิดหอยโข่งแบบ Horizontal Split Case ขับด้วยมอเตอร์ไฟฟ้าอัตราสูบน้ำ ๐.๒๐ ลบ.ม./วินาที ระยะยกน้ำไม่น้อยกว่า ๔๕ เมตร และอื่นๆ รวม ๔ รายการ  สำหรับงานสถานีสูบน้ำด้วยไฟฟ้าพร้อมระบบส่งน้ำ บ้านสุขสำราญ ตำบลเหล่าต่างคำ อำเภอโพนพิสัย จังหวัดหนองคาย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบงานสารสนเทศ ระบบเครือข่าย และบริการแก้ไขคอมพิวเตอร์และอุปกรณ์ต่อพ่วง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=824576ac-9b6f-4dcc-af9a-f70ac3b918df</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f9ae0aa5-414d-4a63-88c4-8cc52f83f6ef</t>
         </is>
       </c>
     </row>
@@ -9433,15 +9433,15 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>กรมท่าอากาศยาน</t>
+          <t>กรมทางหลวงชนบท</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบงานสารสนเทศ ระบบเครือข่าย และบริการแก้ไขคอมพิวเตอร์และอุปกรณ์ต่อพ่วง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องพิมพ์ Tag Thermal Printer จำนวน 2 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f9ae0aa5-414d-4a63-88c4-8cc52f83f6ef</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=754696e0-bbea-44e1-9a55-42fce741c6ae</t>
         </is>
       </c>
     </row>
@@ -9468,15 +9468,15 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>กรมทางหลวงชนบท</t>
+          <t>กรมพัฒนาพลังงานทดแทนและอนุรักษ์พลังงาน</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>807</v>
+        <v>1205</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องพิมพ์ Tag Thermal Printer จำนวน 2 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์ อุปกรณ์เครือข่ายและอุปกรณ์หน่วยความจำสำรองสำหรับระบบฐานข้อมูล  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>★ (เครื่องพิมพ์)</t>
+          <t>★ (คอมพิวเตอร์, หน่วยความจำ, อุปกรณ์เครือข่าย)</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=754696e0-bbea-44e1-9a55-42fce741c6ae</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6b70ca7e-b8a0-4edd-a187-b48e924a78fa</t>
         </is>
       </c>
     </row>
@@ -9503,15 +9503,15 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>กรมพัฒนาพลังงานทดแทนและอนุรักษ์พลังงาน</t>
+          <t>กรมการปกครอง</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>1205</v>
+        <v>1503</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาระบบคอมพิวเตอร์ อุปกรณ์เครือข่ายและอุปกรณ์หน่วยความจำสำรองสำหรับระบบฐานข้อมูล  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อวัสดุผงหมึกและดรัมสำหรับเครื่องพิมพ์คอมพิวเตอร์ จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, หน่วยความจำ, อุปกรณ์เครือข่าย)</t>
+          <t>★ (ดรัม, คอมพิวเตอร์, เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6b70ca7e-b8a0-4edd-a187-b48e924a78fa</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ce5f2a5e-58b0-4355-b3f5-66c43c2247d8</t>
         </is>
       </c>
     </row>
@@ -9538,15 +9538,15 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>กรมการปกครอง</t>
+          <t>กรมสอบสวนคดีพิเศษ</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>1503</v>
+        <v>1608</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อวัสดุผงหมึกและดรัมสำหรับเครื่องพิมพ์คอมพิวเตอร์ จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องคอมพิวเตอร์ประสิทธิภาพสูงสำหรับประมวลผลความสัมพันธ์ทางธุรกรรมและวิเคราะห์เส้นทางการเงินของคดีพิเศษและเรื่องสืบสวน กรมสอบสวนคดีพิเศษ  แขวงทุ่งสองห้อง เขตหลักสี่ กรุงเทพมหานคร 3 ชุด ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>★ (ดรัม, คอมพิวเตอร์, เครื่องพิมพ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ce5f2a5e-58b0-4355-b3f5-66c43c2247d8</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cd272b14-6e4a-4165-9eab-d4725c6ca271</t>
         </is>
       </c>
     </row>
@@ -9573,15 +9573,15 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>กรมสอบสวนคดีพิเศษ</t>
+          <t>สำนักงานประกันสังคม</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>1608</v>
+        <v>1706</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องคอมพิวเตอร์ประสิทธิภาพสูงสำหรับประมวลผลความสัมพันธ์ทางธุรกรรมและวิเคราะห์เส้นทางการเงินของคดีพิเศษและเรื่องสืบสวน กรมสอบสวนคดีพิเศษ  แขวงทุ่งสองห้อง เขตหลักสี่ กรุงเทพมหานคร 3 ชุด ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อวัสดุคอมพิวเตอร์ จำนวน ๑ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=cd272b14-6e4a-4165-9eab-d4725c6ca271</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a2ef415e-d086-45a2-854c-add8955d6fdb</t>
         </is>
       </c>
     </row>
@@ -9608,15 +9608,15 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>สำนักงานประกันสังคม</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>1706</v>
+        <v>2102</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อวัสดุคอมพิวเตอร์ จำนวน ๑ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตาม   การทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดใหญ่ จำนวน 12 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ.2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -9626,12 +9626,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a2ef415e-d086-45a2-854c-add8955d6fdb</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5a6e7a1-9557-4e6f-8ecc-2de9fdd94405</t>
         </is>
       </c>
     </row>
@@ -9643,15 +9643,15 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>2102</v>
+        <v>2107</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องติดตาม   การทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดใหญ่ จำนวน 12 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ.2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ  จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b5a6e7a1-9557-4e6f-8ecc-2de9fdd94405</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fdb52cbf-ad05-423e-b1d8-e2f17eae5c8d</t>
         </is>
       </c>
     </row>
@@ -9678,15 +9678,15 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>กรมสนับสนุนบริการสุขภาพ</t>
+          <t>สำนักงานตำรวจแห่งชาติ</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>2107</v>
+        <v>2507</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ  จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดหาคอมพิวเตอร์ (Notebook) สำหรับนักเรียนนายร้อยตำรวจรุ่นที่ 84 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -9696,12 +9696,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fdb52cbf-ad05-423e-b1d8-e2f17eae5c8d</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c5ba14d7-29e1-4cb6-a64d-e89688b4e1f1</t>
         </is>
       </c>
     </row>
@@ -9713,15 +9713,15 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>สำนักงานตำรวจแห่งชาติ</t>
+          <t>สำนักงานอัยการสูงสุด</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดหาคอมพิวเตอร์ (Notebook) สำหรับนักเรียนนายร้อยตำรวจรุ่นที่ 84 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c5ba14d7-29e1-4cb6-a64d-e89688b4e1f1</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=caeb26b1-ae0a-40d1-878c-18926a5cd2cd</t>
         </is>
       </c>
     </row>
@@ -9748,15 +9748,15 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>สำนักงานอัยการสูงสุด</t>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามการทุจริตแห่งชาติ</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>2509</v>
+        <v>2605</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์พกพาแบบหน้าจอสัมผัส จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, คอมพิวเตอร์พกพา)</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=caeb26b1-ae0a-40d1-878c-18926a5cd2cd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=380be6fa-be50-4cc9-a85d-d4912f73145e</t>
         </is>
       </c>
     </row>
@@ -9783,15 +9783,15 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามการทุจริตแห่งชาติ</t>
+          <t>องค์การบริหารส่วนจังหวัดระยอง</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>2605</v>
+        <v>2210101</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์พกพาแบบหน้าจอสัมผัส จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 2 รายการ ดังนี้ (1) รถยนต์โดยสารปรับอากาศ ไม่น้อยกว่า 22 ที่นั่ง แบบขับเคลื่อนด้วยระบบไฟฟ้า จำนวน 2 คัน  (2) รถยนต์โดยสารปรับอากาศ ไม่น้อยกว่า 40 ที่นั่ง แบบขับเคลื่อนด้วยระบบไฟฟ้า จำนวน 2 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, คอมพิวเตอร์พกพา)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=380be6fa-be50-4cc9-a85d-d4912f73145e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=56da4e4f-a0c5-43d9-b499-ef666d60c6ae</t>
         </is>
       </c>
     </row>
@@ -9818,15 +9818,15 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>องค์การบริหารส่วนจังหวัดระยอง</t>
+          <t>มหาวิทยาลัยเชียงใหม่</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>2210101</v>
+        <v>1450100400</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง จำนวน 2 รายการ ดังนี้ (1) รถยนต์โดยสารปรับอากาศ ไม่น้อยกว่า 22 ที่นั่ง แบบขับเคลื่อนด้วยระบบไฟฟ้า จำนวน 2 คัน  (2) รถยนต์โดยสารปรับอากาศ ไม่น้อยกว่า 40 ที่นั่ง แบบขับเคลื่อนด้วยระบบไฟฟ้า จำนวน 2 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=56da4e4f-a0c5-43d9-b499-ef666d60c6ae</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=37e13d96-615f-47ec-98fa-80e208e1c3cd</t>
         </is>
       </c>
     </row>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ จำนวน 3 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อรายการครุภัณฑ์ระบบบันไดเลื่อน จำนวน 2 รายการ (ตามรายละเอียดแนบท้าย) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=37e13d96-615f-47ec-98fa-80e208e1c3cd</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0552eafd-ca4e-4f42-b20b-de0194dda26f</t>
         </is>
       </c>
     </row>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อรายการครุภัณฑ์ระบบบันไดเลื่อน จำนวน 2 รายการ (ตามรายละเอียดแนบท้าย) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อรายการครุภัณฑ์ลิฟต์ จำนวน 2 รายการ (ตามรายละเอียดแนบท้าย) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -9911,27 +9911,27 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0552eafd-ca4e-4f42-b20b-de0194dda26f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ccd9e657-8e19-4067-9762-ca2a3da4e3af</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>มหาวิทยาลัยเชียงใหม่</t>
+          <t>กองอำนวยการรักษาความมั่นคงภายใน</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>1450100400</v>
+        <v>119</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อรายการครุภัณฑ์ลิฟต์ จำนวน 2 รายการ (ตามรายละเอียดแนบท้าย) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อวัสดุสำนักงาน ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ สนับสนุน นขต.กอ.รมน. (ส่วนกลาง) ครั้งที่ ๒        ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -9941,12 +9941,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (วัสดุสำนักงาน)</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ccd9e657-8e19-4067-9762-ca2a3da4e3af</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=245d59e4-9af3-49a2-b319-a01e5d97af03</t>
         </is>
       </c>
     </row>
@@ -9958,15 +9958,15 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>กองอำนวยการรักษาความมั่นคงภายใน</t>
+          <t>กองทัพเรือ</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>119</v>
+        <v>205</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อวัสดุสำนักงาน ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ สนับสนุน นขต.กอ.รมน. (ส่วนกลาง) ครั้งที่ ๒        ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์เครื่องช่วยการศึกษา สาย ยศ.ทร. ในการปรับปรุงอาคาร กพร.ทร.แห่งใหม่ (อาคาร บก.พธ.ทร.เดิม) จำนวน ๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>★ (วัสดุสำนักงาน)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=245d59e4-9af3-49a2-b319-a01e5d97af03</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ee6ef62-218a-4804-b810-005dc5140bcf</t>
         </is>
       </c>
     </row>
@@ -9993,15 +9993,15 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>กองทัพเรือ</t>
+          <t>กองบัญชาการกองทัพไทย</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์เครื่องช่วยการศึกษา สาย ยศ.ทร. ในการปรับปรุงอาคาร กพร.ทร.แห่งใหม่ (อาคาร บก.พธ.ทร.เดิม) จำนวน ๕ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์งานบ้านงานครัว พร้อมติดตั้ง ณ ครัวห้องอาหาร 6/1 และ 6/2 อาคาร 1 บก.ทท. ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ee6ef62-218a-4804-b810-005dc5140bcf</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b75a499d-7f24-4c81-8f7c-efa6f5c08c11</t>
         </is>
       </c>
     </row>
@@ -10028,15 +10028,15 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>กองบัญชาการกองทัพไทย</t>
+          <t>กรมบัญชีกลาง</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>208</v>
+        <v>304</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์งานบ้านงานครัว พร้อมติดตั้ง ณ ครัวห้องอาหาร 6/1 และ 6/2 อาคาร 1 บก.ทท. ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์คอมพิวเตอร์สำหรับห้องประชุม 4 (ห้องปฏิบัติการคอมพิวเตอร์) อาคาร 9 ชั้น 7 กรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b75a499d-7f24-4c81-8f7c-efa6f5c08c11</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b3a0480b-6840-48c0-aaba-8b41474df7ba</t>
         </is>
       </c>
     </row>
@@ -10063,15 +10063,15 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>กรมบัญชีกลาง</t>
+          <t>กรมสรรพากร</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์คอมพิวเตอร์สำหรับห้องประชุม 4 (ห้องปฏิบัติการคอมพิวเตอร์) อาคาร 9 ชั้น 7 กรมบัญชีกลาง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภท รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -10081,12 +10081,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b3a0480b-6840-48c0-aaba-8b41474df7ba</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2f4faa45-b32a-4d9e-b08c-b82d5884c153</t>
         </is>
       </c>
     </row>
@@ -10098,15 +10098,15 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>กรมสรรพากร</t>
+          <t>สำนักงานปลัดกระทรวงการพัฒนาสังคมและความมั่นคงของมนุษย์</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>307</v>
+        <v>602</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภท รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างบำรุงรักษาและเพิ่มประสิทธิภาพระบบสมุดพกครอบครัวอิเล็กทรอนิกส์ (MSO-Logbook) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -10116,12 +10116,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (สมุด)</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2f4faa45-b32a-4d9e-b08c-b82d5884c153</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1026aa3b-bb28-4576-aadf-d4cf4a678716</t>
         </is>
       </c>
     </row>
@@ -10133,15 +10133,15 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงการพัฒนาสังคมและความมั่นคงของมนุษย์</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>602</v>
+        <v>704</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างบำรุงรักษาและเพิ่มประสิทธิภาพระบบสมุดพกครอบครัวอิเล็กทรอนิกส์ (MSO-Logbook) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี. หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บพร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -10151,12 +10151,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>★ (สมุด)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1026aa3b-bb28-4576-aadf-d4cf4a678716</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a73013cc-9e52-49f3-b910-4e936275bfe1</t>
         </is>
       </c>
     </row>
@@ -10168,15 +10168,15 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>704</v>
+        <v>2102</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี. หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บพร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องตรวจสมรรถภาพปอดด้วยเครื่องคอมพิวเตอร์ จำนวน ๓ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a73013cc-9e52-49f3-b910-4e936275bfe1</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=10b04086-63b0-4d42-95a0-904c88c6e41f</t>
         </is>
       </c>
     </row>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องตรวจสมรรถภาพปอดด้วยเครื่องคอมพิวเตอร์ จำนวน ๓ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องให้การรักษาอาการปวดและกระตุ้นเซลล์ประสาทส่วนปลายด้วยสนามแม่เหล็กไฟฟ้า (PMS) สำหรับโรงพยาบาลกงไกรลาศ จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=10b04086-63b0-4d42-95a0-904c88c6e41f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4a641a15-b74d-402f-ab9c-60aa9fb564a7</t>
         </is>
       </c>
     </row>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องให้การรักษาอาการปวดและกระตุ้นเซลล์ประสาทส่วนปลายด้วยสนามแม่เหล็กไฟฟ้า (PMS) สำหรับโรงพยาบาลกงไกรลาศ จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องเอกซเรย์ทั่วไปขนาดไม่น้อยกว่า ๑,๐๐๐ mA. แบบแขวนเพดาน สำหรับโรงพยาบาลศรีนคร จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4a641a15-b74d-402f-ab9c-60aa9fb564a7</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a37d5071-0a7d-4d2f-84fe-d0f774026ac5</t>
         </is>
       </c>
     </row>
@@ -10281,7 +10281,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องเอกซเรย์ทั่วไปขนาดไม่น้อยกว่า ๑,๐๐๐ mA. แบบแขวนเพดาน สำหรับโรงพยาบาลศรีนคร จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูง ชนิด 2 หัวตรวจ สำหรับโรงพยาบาลทุ่งเสลี่ยม จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a37d5071-0a7d-4d2f-84fe-d0f774026ac5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9aa030b2-096a-4e59-a881-6f2d1737ed5f</t>
         </is>
       </c>
     </row>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูง ชนิด 2 หัวตรวจ สำหรับโรงพยาบาลทุ่งเสลี่ยม จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องตรวจอวัยวะภายในด้วยเครื่องเสียงความถี่สูงระดับความคมชัดสูง ๓ หัวตรวจ ชนิดเคลื่อนย้ายได้ สำหรับโรงพยาบาลบ้านด่านลานหอย จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9aa030b2-096a-4e59-a881-6f2d1737ed5f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afe2fdf2-3a41-4668-9d7c-c5718e064adc</t>
         </is>
       </c>
     </row>
@@ -10351,7 +10351,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องตรวจอวัยวะภายในด้วยเครื่องเสียงความถี่สูงระดับความคมชัดสูง ๓ หัวตรวจ ชนิดเคลื่อนย้ายได้ สำหรับโรงพยาบาลบ้านด่านลานหอย จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องให้การรักษาทางกายภาพด้วยคลื่นแม่เหล็กไฟฟ้า  สำหรับโรงพยาบาลศรีสัชนาลัย จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afe2fdf2-3a41-4668-9d7c-c5718e064adc</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1eeea1f2-b27e-42f8-b37f-8cd9d17e4bb2</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องให้การรักษาทางกายภาพด้วยคลื่นแม่เหล็กไฟฟ้า  สำหรับโรงพยาบาลศรีสัชนาลัย จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนในเลือด ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 5 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1eeea1f2-b27e-42f8-b37f-8cd9d17e4bb2</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a54472bd-463e-4919-a81a-3790d34b7b27</t>
         </is>
       </c>
     </row>
@@ -10421,7 +10421,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนในเลือด ของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 5 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องผลิตออกซิเจน ขนาด 10 ลิตร จำนวน 39 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย-กัมพูชา ปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a54472bd-463e-4919-a81a-3790d34b7b27</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1bc9002a-e6eb-4764-add9-7faccb225729</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องผลิตออกซิเจน ขนาด 10 ลิตร จำนวน 39 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย-กัมพูชา ปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ รายการเตียงผ่าตัดศัลยกรรมออร์โธปิดิกส์ จำนวน ๒ เตียง สำหรับโรงพยาบาลลับแลและโรงพยาบาลพิชัย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1bc9002a-e6eb-4764-add9-7faccb225729</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=30fcc177-cd34-422d-af09-c8aa1f9cb406</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์และการแพทย์ รายการเตียงผ่าตัดศัลยกรรมออร์โธปิดิกส์ จำนวน ๒ เตียง สำหรับโรงพยาบาลลับแลและโรงพยาบาลพิชัย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างปรับปรุงสายสัญญาณอินเทอร์เน็ตอาคาร 1 และสายไฟฟ้าอาคาร 9 สำนักงานปลัดกระทรวงสาธารณสุข ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (สายสัญญาณ)</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=30fcc177-cd34-422d-af09-c8aa1f9cb406</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afd11c75-a6db-43e5-a0f3-035fadd64936</t>
         </is>
       </c>
     </row>
@@ -10518,15 +10518,15 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมอนามัย</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>2102</v>
+        <v>2109</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างปรับปรุงสายสัญญาณอินเทอร์เน็ตอาคาร 1 และสายไฟฟ้าอาคาร 9 สำนักงานปลัดกระทรวงสาธารณสุข ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ทางการแพทย์ เครื่องวิเคราะห์องค์ประกอบร่างกายแบบแยกส่วนของโรงพยาบาล ส่งเสริมสุขภาพ ศูนย์อนามัยที่ ๖ ชลบุรี ปีงบประมาณ พ.ศ. ๒๕๗๐ จำนวน ๑ รายการ ( จำนวน ๒ เครื่อง) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -10536,32 +10536,32 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>★ (สายสัญญาณ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=afd11c75-a6db-43e5-a0f3-035fadd64936</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=adb22b5a-03b6-4872-8f4a-1ba04569341a</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>2102</v>
+        <v>204</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องตรวจสมรรถภาพปอดด้วยเครื่องคอมพิวเตอร์ จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อระบบคอมพิวเตอร์และอุปกรณ์ เพื่อสนับสนุนการใช้งานข่าวกรอง ฝขว.ศปก.ทบ. จำนวน ๑๘ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -10576,27 +10576,27 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=de38cd7a-4053-4ddd-a509-d16c262cf02a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=72ad4c14-ee7b-4d77-ba81-e913d7b8443f</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>กรมอนามัย</t>
+          <t>กรมบัญชีกลาง</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>2109</v>
+        <v>304</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ทางการแพทย์ เครื่องวิเคราะห์องค์ประกอบร่างกายแบบแยกส่วนของโรงพยาบาล ส่งเสริมสุขภาพ ศูนย์อนามัยที่ ๖ ชลบุรี ปีงบประมาณ พ.ศ. ๒๕๗๐ จำนวน ๑ รายการ ( จำนวน ๒ เครื่อง) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องพิมพ์ Multifunction และเครื่องสแกนเนอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -10606,12 +10606,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องพิมพ์, เครื่องสแกนเนอร์)</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=adb22b5a-03b6-4872-8f4a-1ba04569341a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9b179ddf-4f24-4f03-b0f6-03f51948ebb5</t>
         </is>
       </c>
     </row>
@@ -10623,15 +10623,15 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>204</v>
+        <v>704</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อระบบคอมพิวเตอร์และอุปกรณ์ เพื่อสนับสนุนการใช้งานข่าวกรอง ฝขว.ศปก.ทบ. จำนวน ๑๘ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อจัดซื้อเครื่องปรับอากาศแบบแยกส่วน (ราคารวมค่าติดตั้ง) แบบตั้งพื้นหรือแบบแขวน(ระบบ Inverter) ขนาดไม่ต่ำกว่า 36,000 บีทียู จำนวน 13 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -10641,12 +10641,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (เครื่องปรับอากาศ)</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=72ad4c14-ee7b-4d77-ba81-e913d7b8443f</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4fb39309-585d-4309-976d-68ffb35f0d13</t>
         </is>
       </c>
     </row>
@@ -10658,15 +10658,15 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>กรมบัญชีกลาง</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>304</v>
+        <v>806</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องพิมพ์ Multifunction และเครื่องสแกนเนอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้องานจัดซื้อครุภัณฑ์สำนักงาน จำนวน 21 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -10676,12 +10676,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>★ (เครื่องพิมพ์, เครื่องสแกนเนอร์)</t>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9b179ddf-4f24-4f03-b0f6-03f51948ebb5</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b933c10a-3d2b-48e7-8733-9ad758013b0a</t>
         </is>
       </c>
     </row>
@@ -10693,15 +10693,15 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>กรมตรวจบัญชีสหกรณ์</t>
+          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>704</v>
+        <v>909</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อจัดซื้อเครื่องปรับอากาศแบบแยกส่วน (ราคารวมค่าติดตั้ง) แบบตั้งพื้นหรือแบบแขวน(ระบบ Inverter) ขนาดไม่ต่ำกว่า 36,000 บีทียู จำนวน 13 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์โครงการเพิ่มประสิทธิภาพการตอบโต้สถานการณ์เฝ้าระวังและผลักดันช้างป่าออกนอกพื้นที่อนุรักษ์ (ครั้งที่ 2) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>★ (เครื่องปรับอากาศ)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4fb39309-585d-4309-976d-68ffb35f0d13</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1a53dd55-3e32-4691-875b-bed5b618267e</t>
         </is>
       </c>
     </row>
@@ -10728,15 +10728,15 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>กรมทางหลวง</t>
+          <t>สำนักงานนโยบายและแผนทรัพยากรธรรมชาติและสิ่งแวดล้อม</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>806</v>
+        <v>911</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้องานจัดซื้อครุภัณฑ์สำนักงาน จำนวน 21 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อวัสดุคอมพิวเตอร์ จำนวน ๑๐๘ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b933c10a-3d2b-48e7-8733-9ad758013b0a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4e0b8c2a-5098-46b1-9662-a1a768115472</t>
         </is>
       </c>
     </row>
@@ -10763,15 +10763,15 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
+          <t>กรมพินิจและคุ้มครองเด็กและเยาวชน</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>909</v>
+        <v>1606</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์โครงการเพิ่มประสิทธิภาพการตอบโต้สถานการณ์เฝ้าระวังและผลักดันช้างป่าออกนอกพื้นที่อนุรักษ์ (ครั้งที่ 2) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ รายการเครื่องรับส่งวิทยุ ระบบ VHF FM ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1a53dd55-3e32-4691-875b-bed5b618267e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=50900d02-0860-49e6-924a-4ce90e349f51</t>
         </is>
       </c>
     </row>
@@ -10798,15 +10798,15 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>สำนักงานนโยบายและแผนทรัพยากรธรรมชาติและสิ่งแวดล้อม</t>
+          <t>กรมพินิจและคุ้มครองเด็กและเยาวชน</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>911</v>
+        <v>1606</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อวัสดุคอมพิวเตอร์ จำนวน ๑๐๘ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์สำรวจ จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4e0b8c2a-5098-46b1-9662-a1a768115472</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=27e6a7f1-e8b3-4713-a4cf-8e1017c95588</t>
         </is>
       </c>
     </row>
@@ -10833,15 +10833,15 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>กรมพินิจและคุ้มครองเด็กและเยาวชน</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>1606</v>
+        <v>2102</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์ไฟฟ้าและวิทยุ รายการเครื่องรับส่งวิทยุ ระบบ VHF FM ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง สำหรับโรงพยาบาลทุ่งเสลี่ยมและโรงพยาบาลคีรีมาศ จำนวน 2 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=50900d02-0860-49e6-924a-4ce90e349f51</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b637756a-f1db-43ca-8088-8bb65d244bc6</t>
         </is>
       </c>
     </row>
@@ -10868,15 +10868,15 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>กรมพินิจและคุ้มครองเด็กและเยาวชน</t>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>1606</v>
+        <v>2102</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์สำรวจ จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ ยูนิตทำฟัน สำหรับโรงพยาบาลศรีนคร และโรงพยาบาลส่งเสริมสุขภาพตำบลวังทอง จำนวน 2 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=27e6a7f1-e8b3-4713-a4cf-8e1017c95588</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=47778085-c309-4c79-a29b-e1847ea7456e</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง สำหรับโรงพยาบาลทุ่งเสลี่ยมและโรงพยาบาลคีรีมาศ จำนวน 2 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องช่วยนวดหัวใจและฟื้นคืนชีพผู้ป่วยอัติโนมัติ สำหรับโรงพยาบาลทุ่งเสลี่ยม จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b637756a-f1db-43ca-8088-8bb65d244bc6</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=772263bc-9e51-4b12-87ea-8b731c25646a</t>
         </is>
       </c>
     </row>
@@ -10938,15 +10938,15 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>กรมสุขภาพจิต</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>2102</v>
+        <v>2108</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ ยูนิตทำฟัน สำหรับโรงพยาบาลศรีนคร และโรงพยาบาลส่งเสริมสุขภาพตำบลวังทอง จำนวน 2 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๖ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -10956,32 +10956,32 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=47778085-c309-4c79-a29b-e1847ea7456e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a2d6c763-d384-410d-8363-44f98d922641</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+          <t>สำนักงานคณะกรรมการนโยบายที่ดินแห่งชาติ</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>2102</v>
+        <v>142</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องช่วยนวดหัวใจและฟื้นคืนชีพผู้ป่วยอัติโนมัติ สำหรับโรงพยาบาลทุ่งเสลี่ยม จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อเครื่องพิมพ์ ขนาด A0 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -10991,32 +10991,32 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (เครื่องพิมพ์)</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=772263bc-9e51-4b12-87ea-8b731c25646a</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b524d474-1d00-4330-872e-db4cd85cc6a0</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>กรมสุขภาพจิต</t>
+          <t>สำนักงานคณะกรรมการนโยบายที่ดินแห่งชาติ</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>2108</v>
+        <v>142</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๖ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์เพิ่มเติม ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a2d6c763-d384-410d-8363-44f98d922641</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ef813d9a-008b-48f6-807d-47af8175bf30</t>
         </is>
       </c>
     </row>
@@ -11043,15 +11043,15 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการนโยบายที่ดินแห่งชาติ</t>
+          <t>กองทัพบก</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อเครื่องพิมพ์ ขนาด A0 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ประจำอาคาร จำนวน 4 รายการ เพื่อใช้ในงานซ่อมปรับปรุงอาคารแฟลตนายทหารชั้นประทวนจุ 56 ครอบครัว หมายเลข 423/29 (ป.116) ของ กองพันทหารช่างที่ 112 กรมทหารช่างที่ 1 รักษาพระองค์ เป็นแผนงานเพิ่มเติมระหว่างปีงบประมาณ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>★ (เครื่องพิมพ์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b524d474-1d00-4330-872e-db4cd85cc6a0</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c57e6e7d-84ff-41ad-986d-268777a7d6c1</t>
         </is>
       </c>
     </row>
@@ -11078,15 +11078,15 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>สำนักงานคณะกรรมการนโยบายที่ดินแห่งชาติ</t>
+          <t>สำนักงานปลัดกระทรวงเกษตรและสหกรณ์</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>142</v>
+        <v>702</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์เพิ่มเติม ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างดูแลบำรุงรักษาระบบคอมพิวเตอร์และเครือข่าย สำนักงานปลัดกระทรวงเกษตรและสหกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+          <t>★ (คอมพิวเตอร์)</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ef813d9a-008b-48f6-807d-47af8175bf30</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=968489c9-089d-4081-9d28-c41ee46b7166</t>
         </is>
       </c>
     </row>
@@ -11113,15 +11113,15 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>กองทัพบก</t>
+          <t>กรมชลประทาน</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>204</v>
+        <v>703</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ประจำอาคาร จำนวน 4 รายการ เพื่อใช้ในงานซ่อมปรับปรุงอาคารแฟลตนายทหารชั้นประทวนจุ 56 ครอบครัว หมายเลข 423/29 (ป.116) ของ กองพันทหารช่างที่ 112 กรมทหารช่างที่ 1 รักษาพระองค์ เป็นแผนงานเพิ่มเติมระหว่างปีงบประมาณ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างจัดทำและติดตั้งบานระบายตรงชนิดสองบาน ขนาด 6.00x5.00 เมตร พร้อมจัดหาและติดตั้งเกียร์มอเตอร์ไฟฟ้า ขนาด 3 กิโลวัตต์ 200 รอบต่อนาทีสำหรับเครื่องกว้าน 12 ตัน และอุปกรณ์อื่นๆ จำนวน 4 รายการ ปตร.คลองปากง่าม ตำบลหัวสะพาน อำเภอเมืองเพชรบุรี จังหวัดเพชรบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -11131,12 +11131,12 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (มอเตอร์)</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c57e6e7d-84ff-41ad-986d-268777a7d6c1</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5e9f210c-ac94-45bc-bdd6-fc5490c2019e</t>
         </is>
       </c>
     </row>
@@ -11148,15 +11148,15 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>สำนักงานปลัดกระทรวงเกษตรและสหกรณ์</t>
+          <t>กรมประมง</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างดูแลบำรุงรักษาระบบคอมพิวเตอร์และเครือข่าย สำนักงานปลัดกระทรวงเกษตรและสหกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ เครื่องกำเนิดไฟฟ้า ขนาด ๕๐๐ กิโลวัตต์ พร้อมตู้ควบคุม จำนวน ๑ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -11166,12 +11166,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>★ (คอมพิวเตอร์)</t>
+          <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=968489c9-089d-4081-9d28-c41ee46b7166</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fbcaead1-29c0-4ccc-b4f3-c6029e986951</t>
         </is>
       </c>
     </row>
@@ -11183,15 +11183,15 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>กรมชลประทาน</t>
+          <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>703</v>
+        <v>804</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างจัดทำและติดตั้งบานระบายตรงชนิดสองบาน ขนาด 6.00x5.00 เมตร พร้อมจัดหาและติดตั้งเกียร์มอเตอร์ไฟฟ้า ขนาด 3 กิโลวัตต์ 200 รอบต่อนาทีสำหรับเครื่องกว้าน 12 ตัน และอุปกรณ์อื่นๆ จำนวน 4 รายการ ปตร.คลองปากง่าม ตำบลหัวสะพาน อำเภอเมืองเพชรบุรี จังหวัดเพชรบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาคอมพิวเตอร์แม่ข่ายและซอฟต์แวร์ระบบ Smart Bus Terminal เพื่ออำนวยความสะดวกและปลอดภัยในการโดยสารด้วยรถสาธารณะ ด้วยการใช้เทคโนโลยีสารสนเทศ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -11201,12 +11201,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>★ (มอเตอร์)</t>
+          <t>★ (คอมพิวเตอร์, ซอฟต์แวร์)</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5e9f210c-ac94-45bc-bdd6-fc5490c2019e</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9f2eadf5-f0d6-454d-92ce-830a13a9368f</t>
         </is>
       </c>
     </row>
@@ -11218,15 +11218,15 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>กรมประมง</t>
+          <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>705</v>
+        <v>805</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ เครื่องกำเนิดไฟฟ้า ขนาด ๕๐๐ กิโลวัตต์ พร้อมตู้ควบคุม จำนวน ๑ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+          <t>ประกวดราคาซื้ออุปกรณ์เครือข่ายและอุปกรณ์ความมั่นคงปลอดภัยและเสถียรภาพการ ณ ท่าอากาศยาน ๒๖ แห่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -11236,12 +11236,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>★ (ครุภัณฑ์)</t>
+          <t>★ (อุปกรณ์เครือข่าย)</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fbcaead1-29c0-4ccc-b4f3-c6029e986951</t>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3224492-d946-48af-92fc-ba14c8c18c21</t>
         </is>
       </c>
     </row>
@@ -11253,15 +11253,15 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>กรมการขนส่งทางบก</t>
+          <t>กรมทางหลวง</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>ประกวดราคาจ้างเหมาบำรุงรักษาคอมพิวเตอร์แม่ข่ายและซอฟต์แวร์ระบบ Smart Bus Terminal เพื่ออำนวยความสะดวกและปลอดภัยในการโดยสารด้วยรถสาธารณะ ด้วยการใช้เทคโนโลยีสารสนเทศ ประ